--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -36,7 +36,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +46,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,11 +66,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,24 +437,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>gap_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>volume_trend</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>premarket_score</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>premarket_action</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>buy_amount_usd</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>shares_to_buy</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>trim_price</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>No data available yet</t>
-        </is>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>KYTX</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>7.769999980926514</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.0029464435139859</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1.848363624307033</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>PREMARKET WATCH</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>6.215999984741211</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>9.712499976158142</v>
       </c>
     </row>
   </sheetData>
@@ -462,11 +562,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -474,7 +574,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
@@ -617,21 +717,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BFLY</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8.100000381469727</v>
+        <v>534.3900146484375</v>
       </c>
       <c r="E3" t="n">
         <v>82</v>
@@ -651,42 +751,42 @@
         <v>50</v>
       </c>
       <c r="J3" t="n">
-        <v>58.05825616673116</v>
+        <v>47.25110136960278</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0137844778510634</v>
+        <v>-0.0364229629329782</v>
       </c>
       <c r="L3" t="n">
-        <v>1.00619796262587</v>
+        <v>0.6544075267434142</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0949479297406228</v>
+        <v>-3.577422784539042</v>
       </c>
       <c r="N3" t="n">
-        <v>6.480000305175782</v>
+        <v>491.6388134765625</v>
       </c>
       <c r="O3" t="n">
-        <v>10.12500047683716</v>
+        <v>614.548516845703</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>BFLY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>534.3900146484375</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="E4" t="n">
         <v>82</v>
@@ -706,22 +806,22 @@
         <v>50</v>
       </c>
       <c r="J4" t="n">
-        <v>47.25110136960278</v>
+        <v>58.05825616673116</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0364229629329782</v>
+        <v>-0.0137844778510634</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6544075267434142</v>
+        <v>1.00619796262587</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.577422784539042</v>
+        <v>-0.0949479297406228</v>
       </c>
       <c r="N4" t="n">
-        <v>491.6388134765625</v>
+        <v>6.480000305175782</v>
       </c>
       <c r="O4" t="n">
-        <v>614.548516845703</v>
+        <v>10.12500047683716</v>
       </c>
     </row>
     <row r="5">
@@ -782,12 +882,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PUBM</t>
+          <t>BLZE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AdTech</t>
+          <t>Gaming/Digital Media</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +896,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.56999969482422</v>
+        <v>16.19000053405762</v>
       </c>
       <c r="E6" t="n">
         <v>79</v>
@@ -816,33 +916,33 @@
         <v>75</v>
       </c>
       <c r="J6" t="n">
-        <v>75.50561349871404</v>
+        <v>79.95545838351569</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0007380242613335</v>
+        <v>0.0005681948105162</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4552973151331601</v>
+        <v>0.5846786159230302</v>
       </c>
       <c r="M6" t="n">
-        <v>0.042571941463545</v>
+        <v>0.2137816411175577</v>
       </c>
       <c r="N6" t="n">
-        <v>10.85599975585938</v>
+        <v>12.95200042724609</v>
       </c>
       <c r="O6" t="n">
-        <v>16.96249961853028</v>
+        <v>20.23750066757202</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BLZE</t>
+          <t>PUBM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gaming/Digital Media</t>
+          <t>AdTech</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -851,7 +951,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.19000053405762</v>
+        <v>13.56999969482422</v>
       </c>
       <c r="E7" t="n">
         <v>79</v>
@@ -871,22 +971,22 @@
         <v>75</v>
       </c>
       <c r="J7" t="n">
-        <v>79.95545838351569</v>
+        <v>75.50561349871404</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0005681948105162</v>
+        <v>0.0007380242613335</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5846786159230302</v>
+        <v>0.4552973151331601</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2137816411175577</v>
+        <v>0.042571941463545</v>
       </c>
       <c r="N7" t="n">
-        <v>12.95200042724609</v>
+        <v>10.85599975585938</v>
       </c>
       <c r="O7" t="n">
-        <v>20.23750066757202</v>
+        <v>16.96249961853028</v>
       </c>
     </row>
     <row r="8">
@@ -1002,7 +1102,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,7 +1116,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>203.5299987792969</v>
+        <v>384.0499877929688</v>
       </c>
       <c r="E10" t="n">
         <v>71</v>
@@ -1036,33 +1136,33 @@
         <v>75</v>
       </c>
       <c r="J10" t="n">
-        <v>45.3606417209306</v>
+        <v>46.76644111895504</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0114714322654375</v>
+        <v>-0.0162387056463356</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7042751597422509</v>
+        <v>0.7186066924249777</v>
       </c>
       <c r="M10" t="n">
-        <v>1.206196025562167</v>
+        <v>3.038872772970159</v>
       </c>
       <c r="N10" t="n">
-        <v>187.2475988769532</v>
+        <v>353.3259887695313</v>
       </c>
       <c r="O10" t="n">
-        <v>234.0594985961914</v>
+        <v>441.6574859619141</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Electric Vehicles</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,10 +1171,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>394.760009765625</v>
+        <v>203.5299987792969</v>
       </c>
       <c r="E11" t="n">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1082,31 +1182,1622 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H11" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="I11" t="n">
         <v>75</v>
       </c>
       <c r="J11" t="n">
+        <v>45.3606417209306</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.0114714322654375</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.7042751597422509</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.206196025562167</v>
+      </c>
+      <c r="N11" t="n">
+        <v>187.2475988769532</v>
+      </c>
+      <c r="O11" t="n">
+        <v>234.0594985961914</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Internet/Software</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>352.510009765625</v>
+      </c>
+      <c r="E12" t="n">
+        <v>71</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>40</v>
+      </c>
+      <c r="H12" t="n">
+        <v>75</v>
+      </c>
+      <c r="I12" t="n">
+        <v>75</v>
+      </c>
+      <c r="J12" t="n">
+        <v>52.39629178665267</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.0027436600281235</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4547264581905489</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5974640052565006</v>
+      </c>
+      <c r="N12" t="n">
+        <v>324.309208984375</v>
+      </c>
+      <c r="O12" t="n">
+        <v>405.3865112304687</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>18.1299991607666</v>
+      </c>
+      <c r="E13" t="n">
+        <v>67</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>40</v>
+      </c>
+      <c r="H13" t="n">
+        <v>60</v>
+      </c>
+      <c r="I13" t="n">
+        <v>75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>60.23854340937944</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0111820594672281</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.252902011122615</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0328078631428616</v>
+      </c>
+      <c r="N13" t="n">
+        <v>14.50399932861328</v>
+      </c>
+      <c r="O13" t="n">
+        <v>22.66249895095825</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Internet/E-Commerce</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>247.3099975585937</v>
+      </c>
+      <c r="E14" t="n">
+        <v>67</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>40</v>
+      </c>
+      <c r="H14" t="n">
+        <v>60</v>
+      </c>
+      <c r="I14" t="n">
+        <v>75</v>
+      </c>
+      <c r="J14" t="n">
+        <v>67.81157428603623</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.0044020618210463</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6590365403224546</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.780135958077288</v>
+      </c>
+      <c r="N14" t="n">
+        <v>227.5251977539062</v>
+      </c>
+      <c r="O14" t="n">
+        <v>284.4064971923827</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ALAB</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>362.0499877929688</v>
+      </c>
+      <c r="E15" t="n">
+        <v>65</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>80</v>
+      </c>
+      <c r="H15" t="n">
+        <v>75</v>
+      </c>
+      <c r="I15" t="n">
+        <v>50</v>
+      </c>
+      <c r="J15" t="n">
+        <v>39.99174507130462</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.0297479323577886</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.009130937422583</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-10.00415359792669</v>
+      </c>
+      <c r="N15" t="n">
+        <v>289.639990234375</v>
+      </c>
+      <c r="O15" t="n">
+        <v>452.562484741211</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>937</v>
+      </c>
+      <c r="E16" t="n">
+        <v>65</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>80</v>
+      </c>
+      <c r="H16" t="n">
+        <v>75</v>
+      </c>
+      <c r="I16" t="n">
+        <v>50</v>
+      </c>
+      <c r="J16" t="n">
+        <v>32.2591555067534</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.0518891076021834</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.6460612178517311</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-28.83193491040208</v>
+      </c>
+      <c r="N16" t="n">
+        <v>749.6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1171.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CRDO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>236.8800048828125</v>
+      </c>
+      <c r="E17" t="n">
+        <v>65</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" t="n">
+        <v>75</v>
+      </c>
+      <c r="I17" t="n">
+        <v>50</v>
+      </c>
+      <c r="J17" t="n">
+        <v>35.03556650730233</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.0327398353762632</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.7710954963114622</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-4.078359216969876</v>
+      </c>
+      <c r="N17" t="n">
+        <v>189.50400390625</v>
+      </c>
+      <c r="O17" t="n">
+        <v>296.1000061035156</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>VRT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Data Centers</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>305.8699951171875</v>
+      </c>
+      <c r="E18" t="n">
+        <v>62</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>40</v>
+      </c>
+      <c r="H18" t="n">
+        <v>100</v>
+      </c>
+      <c r="I18" t="n">
+        <v>50</v>
+      </c>
+      <c r="J18" t="n">
+        <v>37.27464274525995</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.0217022618956923</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.5921605606804075</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.1480541656201379</v>
+      </c>
+      <c r="N18" t="n">
+        <v>281.4003955078125</v>
+      </c>
+      <c r="O18" t="n">
+        <v>351.7504943847656</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>421.5799865722656</v>
+      </c>
+      <c r="E19" t="n">
+        <v>62</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>40</v>
+      </c>
+      <c r="H19" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" t="n">
+        <v>50</v>
+      </c>
+      <c r="J19" t="n">
+        <v>37.838400646266</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.0006679828548723</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.033740369974669</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-3.711786865119478</v>
+      </c>
+      <c r="N19" t="n">
+        <v>387.8535876464844</v>
+      </c>
+      <c r="O19" t="n">
+        <v>484.8169845581055</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CBOE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>277.1300048828125</v>
+      </c>
+      <c r="E20" t="n">
+        <v>61</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>40</v>
+      </c>
+      <c r="H20" t="n">
+        <v>40</v>
+      </c>
+      <c r="I20" t="n">
+        <v>75</v>
+      </c>
+      <c r="J20" t="n">
+        <v>63.08948813870285</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.0012683117417138</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.8139347803176693</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5.61249043240821</v>
+      </c>
+      <c r="N20" t="n">
+        <v>254.9596044921875</v>
+      </c>
+      <c r="O20" t="n">
+        <v>318.6995056152344</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Biotech</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>103.7900009155273</v>
+      </c>
+      <c r="E21" t="n">
+        <v>56</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>40</v>
+      </c>
+      <c r="H21" t="n">
+        <v>25</v>
+      </c>
+      <c r="I21" t="n">
+        <v>75</v>
+      </c>
+      <c r="J21" t="n">
+        <v>64.40748321374801</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.008180004348712199</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.822520612694786</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.911196160245703</v>
+      </c>
+      <c r="N21" t="n">
+        <v>83.03200073242188</v>
+      </c>
+      <c r="O21" t="n">
+        <v>129.7375011444092</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>298.989990234375</v>
+      </c>
+      <c r="E22" t="n">
+        <v>55</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>40</v>
+      </c>
+      <c r="H22" t="n">
+        <v>75</v>
+      </c>
+      <c r="I22" t="n">
+        <v>50</v>
+      </c>
+      <c r="J22" t="n">
+        <v>25.12013387453341</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.0405393341640209</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.4408143064024243</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-9.368367243321137</v>
+      </c>
+      <c r="N22" t="n">
+        <v>239.1919921875</v>
+      </c>
+      <c r="O22" t="n">
+        <v>373.7374877929688</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>217.5299987792969</v>
+      </c>
+      <c r="E23" t="n">
+        <v>55</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>40</v>
+      </c>
+      <c r="H23" t="n">
+        <v>75</v>
+      </c>
+      <c r="I23" t="n">
+        <v>50</v>
+      </c>
+      <c r="J23" t="n">
+        <v>26.81350318140036</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.0304482114843208</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.5553666439051933</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-9.60956168128553</v>
+      </c>
+      <c r="N23" t="n">
+        <v>200.1275988769532</v>
+      </c>
+      <c r="O23" t="n">
+        <v>250.1594985961914</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>103.120002746582</v>
+      </c>
+      <c r="E24" t="n">
+        <v>55</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>40</v>
+      </c>
+      <c r="H24" t="n">
+        <v>75</v>
+      </c>
+      <c r="I24" t="n">
+        <v>50</v>
+      </c>
+      <c r="J24" t="n">
+        <v>23.43354907791833</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.0353695797192571</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.7544090688995503</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-3.642499733942029</v>
+      </c>
+      <c r="N24" t="n">
+        <v>94.87040252685549</v>
+      </c>
+      <c r="O24" t="n">
+        <v>118.5880031585694</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Data Storage</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>860.6599731445312</v>
+      </c>
+      <c r="E25" t="n">
+        <v>55</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>40</v>
+      </c>
+      <c r="H25" t="n">
+        <v>75</v>
+      </c>
+      <c r="I25" t="n">
+        <v>50</v>
+      </c>
+      <c r="J25" t="n">
+        <v>33.24526766433529</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.0450134431680942</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.9247854544826491</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-17.58862389405815</v>
+      </c>
+      <c r="N25" t="n">
+        <v>791.8071752929687</v>
+      </c>
+      <c r="O25" t="n">
+        <v>989.7589691162108</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NBIS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>210.509994506836</v>
+      </c>
+      <c r="E26" t="n">
+        <v>55</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>40</v>
+      </c>
+      <c r="H26" t="n">
+        <v>75</v>
+      </c>
+      <c r="I26" t="n">
+        <v>50</v>
+      </c>
+      <c r="J26" t="n">
+        <v>31.19082085488327</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.0308900004182012</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.5806093807901501</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-6.66147091221397</v>
+      </c>
+      <c r="N26" t="n">
+        <v>168.4079956054688</v>
+      </c>
+      <c r="O26" t="n">
+        <v>263.137493133545</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>25.95999908447266</v>
+      </c>
+      <c r="E27" t="n">
+        <v>54</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>40</v>
+      </c>
+      <c r="H27" t="n">
+        <v>40</v>
+      </c>
+      <c r="I27" t="n">
+        <v>50</v>
+      </c>
+      <c r="J27" t="n">
+        <v>41.46933662967547</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.0034549003924671</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.4286492863840204</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.0149246408257801</v>
+      </c>
+      <c r="N27" t="n">
+        <v>20.76799926757813</v>
+      </c>
+      <c r="O27" t="n">
+        <v>32.44999885559082</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Electric Vehicles</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>394.760009765625</v>
+      </c>
+      <c r="E28" t="n">
+        <v>49</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>35</v>
+      </c>
+      <c r="I28" t="n">
+        <v>75</v>
+      </c>
+      <c r="J28" t="n">
         <v>47.30190854550064</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K28" t="n">
         <v>-0.0077251921194358</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L28" t="n">
         <v>0.6671930828685395</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M28" t="n">
         <v>0.3816312784934397</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N28" t="n">
         <v>363.179208984375</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O28" t="n">
         <v>453.9740112304687</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>KYTX</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Biotech</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>7.769999980926514</v>
+      </c>
+      <c r="E29" t="n">
+        <v>39</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>75</v>
+      </c>
+      <c r="J29" t="n">
+        <v>45.20795488517063</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.0029464435139859</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.848363624307033</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-0.0068890358413925</v>
+      </c>
+      <c r="N29" t="n">
+        <v>6.215999984741211</v>
+      </c>
+      <c r="O29" t="n">
+        <v>9.712499976158142</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SOUN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AI Software</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>6.489999771118164</v>
+      </c>
+      <c r="E30" t="n">
+        <v>39</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>75</v>
+      </c>
+      <c r="J30" t="n">
+        <v>42.1686670849046</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.0045180321648213</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01945577479926</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.0561779742976243</v>
+      </c>
+      <c r="N30" t="n">
+        <v>5.191999816894532</v>
+      </c>
+      <c r="O30" t="n">
+        <v>8.112499713897705</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RKLB</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>76.73000335693359</v>
+      </c>
+      <c r="E31" t="n">
+        <v>33</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>35</v>
+      </c>
+      <c r="I31" t="n">
+        <v>50</v>
+      </c>
+      <c r="J31" t="n">
+        <v>32.22155183233293</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.0176456106739973</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.6575697356769336</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-1.60128212643402</v>
+      </c>
+      <c r="N31" t="n">
+        <v>61.38400268554688</v>
+      </c>
+      <c r="O31" t="n">
+        <v>95.91250419616701</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>IONQ</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Quantum Computing</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>38.88000106811523</v>
+      </c>
+      <c r="E32" t="n">
+        <v>33</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>35</v>
+      </c>
+      <c r="I32" t="n">
+        <v>50</v>
+      </c>
+      <c r="J32" t="n">
+        <v>15.99020298115008</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.0184321256247612</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.8126902787975192</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-1.449196603544823</v>
+      </c>
+      <c r="N32" t="n">
+        <v>31.10400085449219</v>
+      </c>
+      <c r="O32" t="n">
+        <v>48.60000133514404</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>27.65999984741211</v>
+      </c>
+      <c r="E33" t="n">
+        <v>33</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>35</v>
+      </c>
+      <c r="I33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J33" t="n">
+        <v>22.68907596697776</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-0.024690901380911</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.4071683783254234</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-0.1129581202809464</v>
+      </c>
+      <c r="N33" t="n">
+        <v>22.12799987792969</v>
+      </c>
+      <c r="O33" t="n">
+        <v>34.57499980926514</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ASTS</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Space/Telecom</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>67.58000183105469</v>
+      </c>
+      <c r="E34" t="n">
+        <v>32</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>50</v>
+      </c>
+      <c r="J34" t="n">
+        <v>44.76385902437732</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.018139686805653</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.556489071193276</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-0.7205249641778009</v>
+      </c>
+      <c r="N34" t="n">
+        <v>54.06400146484376</v>
+      </c>
+      <c r="O34" t="n">
+        <v>84.47500228881836</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CCJ</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Uranium/Nuclear Energy</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>90.1999969482422</v>
+      </c>
+      <c r="E35" t="n">
+        <v>29</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>75</v>
+      </c>
+      <c r="J35" t="n">
+        <v>18.63144679070228</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-0.0165641876578346</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.678865656267828</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-0.7934742332941171</v>
+      </c>
+      <c r="N35" t="n">
+        <v>82.98399719238283</v>
+      </c>
+      <c r="O35" t="n">
+        <v>103.7299964904785</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LUNR</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>15.14999961853027</v>
+      </c>
+      <c r="E36" t="n">
+        <v>22</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>50</v>
+      </c>
+      <c r="J36" t="n">
+        <v>22.01308672444488</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.0085687699657102</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.6791682315244271</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-0.2400474448421516</v>
+      </c>
+      <c r="N36" t="n">
+        <v>12.11999969482422</v>
+      </c>
+      <c r="O36" t="n">
+        <v>18.93749952316284</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SKHY</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>High Yield ETF</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>152.3500061035156</v>
+      </c>
+      <c r="E37" t="n">
+        <v>22</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>50</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>-0.0916016897377034</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>-0.999383875311628</v>
+      </c>
+      <c r="N37" t="n">
+        <v>140.1620056152344</v>
+      </c>
+      <c r="O37" t="n">
+        <v>175.202507019043</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Nuclear Energy</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>8.350000381469727</v>
+      </c>
+      <c r="E38" t="n">
+        <v>22</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>50</v>
+      </c>
+      <c r="J38" t="n">
+        <v>14.49631933236232</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-0.0188053182534636</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.161576507688255</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-0.1257283657885731</v>
+      </c>
+      <c r="N38" t="n">
+        <v>6.680000305175781</v>
+      </c>
+      <c r="O38" t="n">
+        <v>10.43750047683716</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Nuclear Energy</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>45.81000137329102</v>
+      </c>
+      <c r="E39" t="n">
+        <v>22</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>50</v>
+      </c>
+      <c r="J39" t="n">
+        <v>21.80922241156196</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-0.0231319813452317</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.6891719298066442</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-0.3462640816307631</v>
+      </c>
+      <c r="N39" t="n">
+        <v>36.64800109863281</v>
+      </c>
+      <c r="O39" t="n">
+        <v>57.26250171661377</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>JOBY</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>eVTOL/Aviation</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>7.480000019073486</v>
+      </c>
+      <c r="E40" t="n">
+        <v>22</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>50</v>
+      </c>
+      <c r="J40" t="n">
+        <v>19.79695935229539</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-0.0233160405739019</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.247613687725642</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-0.1257187896488844</v>
+      </c>
+      <c r="N40" t="n">
+        <v>5.98400001525879</v>
+      </c>
+      <c r="O40" t="n">
+        <v>9.350000023841858</v>
       </c>
     </row>
   </sheetData>
@@ -1151,14 +2842,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
@@ -1281,53 +2972,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>181.1499938964844</v>
+        <v>362.0499877929688</v>
       </c>
       <c r="C2" t="n">
-        <v>160.5955996704102</v>
+        <v>328.4705993652344</v>
       </c>
       <c r="D2" t="n">
-        <v>144.1334996414185</v>
+        <v>200.4233501052856</v>
       </c>
       <c r="E2" t="n">
-        <v>53.54415317550977</v>
+        <v>39.99174507130462</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1582480880170695</v>
+        <v>-0.0147495398528575</v>
       </c>
       <c r="G2" t="n">
-        <v>0.191619450107465</v>
+        <v>1.170628566608762</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4740824704710953</v>
+        <v>1.226492752192518</v>
       </c>
       <c r="I2" t="n">
-        <v>5.778986582872136</v>
+        <v>18.87209311075537</v>
       </c>
       <c r="J2" t="n">
-        <v>4.005723640600515</v>
+        <v>28.87624670868206</v>
       </c>
       <c r="K2" t="n">
-        <v>1.773262942271622</v>
+        <v>-10.00415359792669</v>
       </c>
       <c r="L2" t="n">
-        <v>1.980736671657304</v>
+        <v>-6.89888868607181</v>
       </c>
       <c r="M2" t="n">
-        <v>9112359</v>
+        <v>6245835</v>
       </c>
       <c r="N2" t="n">
-        <v>10396375.18</v>
+        <v>6189320.7</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8764938588913064</v>
+        <v>1.009130937422583</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0037174117418728</v>
+        <v>-0.0297479323577886</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -1335,10 +3026,10 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>10.84078325544085</v>
+        <v>47.61507088797433</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0598442374866193</v>
+        <v>0.1315151843485272</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1349,64 +3040,64 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BFLY</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.100000381469727</v>
+        <v>534.3900146484375</v>
       </c>
       <c r="C3" t="n">
-        <v>5.764399991035462</v>
+        <v>485.8411999511719</v>
       </c>
       <c r="D3" t="n">
-        <v>4.017199999094009</v>
+        <v>289.53119972229</v>
       </c>
       <c r="E3" t="n">
-        <v>58.05825616673116</v>
+        <v>47.25110136960278</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4260564482867148</v>
+        <v>0.0940526180638816</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8925233608417111</v>
+        <v>1.165012399968324</v>
       </c>
       <c r="H3" t="n">
-        <v>1.00495060840409</v>
+        <v>1.630260468891019</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6675626645364767</v>
+        <v>17.03245671433649</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7625105942770996</v>
+        <v>20.60987949887553</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0949479297406228</v>
+        <v>-3.577422784539042</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0967705380809897</v>
+        <v>-3.005596247274948</v>
       </c>
       <c r="M3" t="n">
-        <v>7965165</v>
+        <v>22515725</v>
       </c>
       <c r="N3" t="n">
-        <v>7916101.3</v>
+        <v>34406274.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.00619796262587</v>
+        <v>0.6544075267434142</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0137844778510634</v>
+        <v>-0.0364229629329782</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.7777856077466693</v>
+        <v>38.40574863978794</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0960229100144242</v>
+        <v>0.0718683874829775</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1417,53 +3108,53 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BLZE</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.19000053405762</v>
+        <v>247.3099975585937</v>
       </c>
       <c r="C4" t="n">
-        <v>9.651000032424928</v>
+        <v>253.7199996948243</v>
       </c>
       <c r="D4" t="n">
-        <v>6.520349990129471</v>
+        <v>233.4662000274658</v>
       </c>
       <c r="E4" t="n">
-        <v>79.95545838351569</v>
+        <v>67.81157428603623</v>
       </c>
       <c r="F4" t="n">
-        <v>1.116339912709505</v>
+        <v>0.0240155818959022</v>
       </c>
       <c r="G4" t="n">
-        <v>3.612535777221136</v>
+        <v>0.030930835748985</v>
       </c>
       <c r="H4" t="n">
-        <v>2.238000106811524</v>
+        <v>-0.0002829950797839</v>
       </c>
       <c r="I4" t="n">
-        <v>2.387645053357646</v>
+        <v>-1.050456348260468</v>
       </c>
       <c r="J4" t="n">
-        <v>2.173863412240089</v>
+        <v>-2.830592306337756</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2137816411175577</v>
+        <v>1.780135958077288</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3715229171689866</v>
+        <v>1.752601933393177</v>
       </c>
       <c r="M4" t="n">
-        <v>2289269</v>
+        <v>33220841</v>
       </c>
       <c r="N4" t="n">
-        <v>3915431.38</v>
+        <v>50408192.82</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5846786159230302</v>
+        <v>0.6590365403224546</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0005681948105162</v>
+        <v>-0.0044020618210463</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1471,10 +3162,10 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1.69085727419172</v>
+        <v>7.571425301688058</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1044383705012731</v>
+        <v>0.03061512019907</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1485,53 +3176,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PUBM</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.56999969482422</v>
+        <v>181.1499938964844</v>
       </c>
       <c r="C5" t="n">
-        <v>11.39380002975464</v>
+        <v>160.5955996704102</v>
       </c>
       <c r="D5" t="n">
-        <v>9.101925008296966</v>
+        <v>144.1334996414185</v>
       </c>
       <c r="E5" t="n">
-        <v>75.50561349871404</v>
+        <v>53.54415317550977</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2040815566672071</v>
+        <v>0.1582480880170695</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5687861610715199</v>
+        <v>0.191619450107465</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6212664134245443</v>
+        <v>0.4740824704710953</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6810486742976209</v>
+        <v>5.778986582872136</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6384767328340759</v>
+        <v>4.005723640600515</v>
       </c>
       <c r="K5" t="n">
-        <v>0.042571941463545</v>
+        <v>1.773262942271622</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0616822772464507</v>
+        <v>1.980736671657304</v>
       </c>
       <c r="M5" t="n">
-        <v>306656</v>
+        <v>9112359</v>
       </c>
       <c r="N5" t="n">
-        <v>673529.12</v>
+        <v>10396375.18</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4552973151331601</v>
+        <v>0.8764938588913064</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0007380242613335</v>
+        <v>-0.0037174117418728</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1539,10 +3230,10 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.5974428313119071</v>
+        <v>10.84078325544085</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0440267387433899</v>
+        <v>0.0598442374866193</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1553,64 +3244,64 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STTK</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.429999828338623</v>
+        <v>298.989990234375</v>
       </c>
       <c r="C6" t="n">
-        <v>5.949199991226196</v>
+        <v>311.1417984008789</v>
       </c>
       <c r="D6" t="n">
-        <v>4.476700005531311</v>
+        <v>182.1271249771118</v>
       </c>
       <c r="E6" t="n">
-        <v>64.1330123763551</v>
+        <v>25.12013387453341</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5382775340673356</v>
+        <v>-0.1263478343916499</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0502215884114906</v>
+        <v>0.8973853709871724</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3536841743870784</v>
+        <v>1.674568277893681</v>
       </c>
       <c r="I6" t="n">
-        <v>0.370541003841125</v>
+        <v>-4.89801759233734</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3059377744577766</v>
+        <v>4.470349650983797</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0646032293833483</v>
+        <v>-9.368367243321137</v>
       </c>
       <c r="L6" t="n">
-        <v>0.124170819681362</v>
+        <v>-9.295743678605769</v>
       </c>
       <c r="M6" t="n">
-        <v>863351</v>
+        <v>4941759</v>
       </c>
       <c r="N6" t="n">
-        <v>1214273.02</v>
+        <v>11210523.18</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7110023740789365</v>
+        <v>0.4408143064024243</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0015059867839982</v>
+        <v>-0.0405393341640209</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.6494855540139335</v>
+        <v>30.13700212751116</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1010086425121642</v>
+        <v>0.1007960236524543</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1621,64 +3312,64 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>534.3900146484375</v>
+        <v>67.58000183105469</v>
       </c>
       <c r="C7" t="n">
-        <v>485.8411999511719</v>
+        <v>86.13120018005371</v>
       </c>
       <c r="D7" t="n">
-        <v>289.53119972229</v>
+        <v>82.99554985046387</v>
       </c>
       <c r="E7" t="n">
-        <v>47.25110136960278</v>
+        <v>44.76385902437732</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0940526180638816</v>
+        <v>-0.3072980368775975</v>
       </c>
       <c r="G7" t="n">
-        <v>1.165012399968324</v>
+        <v>-0.3171668081487514</v>
       </c>
       <c r="H7" t="n">
-        <v>1.630260468891019</v>
+        <v>-0.308078190867192</v>
       </c>
       <c r="I7" t="n">
-        <v>17.03245671433649</v>
+        <v>-4.560100006332078</v>
       </c>
       <c r="J7" t="n">
-        <v>20.60987949887553</v>
+        <v>-3.839575042154277</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.577422784539042</v>
+        <v>-0.7205249641778009</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.005596247274948</v>
+        <v>-0.3496537910423321</v>
       </c>
       <c r="M7" t="n">
-        <v>22515725</v>
+        <v>12951297</v>
       </c>
       <c r="N7" t="n">
-        <v>34406274.5</v>
+        <v>23273227.94</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6544075267434142</v>
+        <v>0.556489071193276</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.0364229629329782</v>
+        <v>-0.018139686805653</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>38.40574863978794</v>
+        <v>7.066000257219587</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0718683874829775</v>
+        <v>0.1045575623819025</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1689,53 +3380,53 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>203.5299987792969</v>
+        <v>384.0499877929688</v>
       </c>
       <c r="C8" t="n">
-        <v>209.0846005249024</v>
+        <v>406.0224005126953</v>
       </c>
       <c r="D8" t="n">
-        <v>191.7959504699707</v>
+        <v>362.6720501708984</v>
       </c>
       <c r="E8" t="n">
-        <v>45.3606417209306</v>
+        <v>46.76644111895504</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0065407154284556</v>
+        <v>-0.0039422660019606</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0751148983365332</v>
+        <v>0.0113232068280941</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1009953375922463</v>
+        <v>0.1132851738817233</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.470477138528508</v>
+        <v>-4.49748843644312</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.676673164090676</v>
+        <v>-7.53636120941328</v>
       </c>
       <c r="K8" t="n">
-        <v>1.206196025562167</v>
+        <v>3.038872772970159</v>
       </c>
       <c r="L8" t="n">
-        <v>1.243094423058239</v>
+        <v>3.503419447292556</v>
       </c>
       <c r="M8" t="n">
-        <v>113202886</v>
+        <v>19865507</v>
       </c>
       <c r="N8" t="n">
-        <v>160736729.72</v>
+        <v>27644478.14</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7042751597422509</v>
+        <v>0.7186066924249777</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0114714322654375</v>
+        <v>-0.0162387056463356</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1743,10 +3434,10 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>6.897855486188616</v>
+        <v>15.15999494280134</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0338910997276057</v>
+        <v>0.0394740149060327</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1757,53 +3448,53 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>BFLY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>260.239990234375</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="C9" t="n">
-        <v>223.3829998779297</v>
+        <v>5.764399991035462</v>
       </c>
       <c r="D9" t="n">
-        <v>159.7822002410889</v>
+        <v>4.017199999094009</v>
       </c>
       <c r="E9" t="n">
-        <v>72.85664449359034</v>
+        <v>58.05825616673116</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1109972000148784</v>
+        <v>0.4260564482867148</v>
       </c>
       <c r="G9" t="n">
-        <v>1.364098709171339</v>
+        <v>0.8925233608417111</v>
       </c>
       <c r="H9" t="n">
-        <v>1.073790697780459</v>
+        <v>1.00495060840409</v>
       </c>
       <c r="I9" t="n">
-        <v>11.84447561317248</v>
+        <v>0.6675626645364767</v>
       </c>
       <c r="J9" t="n">
-        <v>11.44889912504316</v>
+        <v>0.7625105942770996</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3955764881293149</v>
+        <v>-0.0949479297406228</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8170337357042587</v>
+        <v>-0.0967705380809897</v>
       </c>
       <c r="M9" t="n">
-        <v>3995404</v>
+        <v>7965165</v>
       </c>
       <c r="N9" t="n">
-        <v>6159172.08</v>
+        <v>7916101.3</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6486917313081468</v>
+        <v>1.00619796262587</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0020967947775294</v>
+        <v>-0.0137844778510634</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1811,10 +3502,10 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>13.0058604649135</v>
+        <v>0.7777856077466693</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0499764100559652</v>
+        <v>0.0960229100144242</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1825,53 +3516,53 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>BLZE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>394.760009765625</v>
+        <v>16.19000053405762</v>
       </c>
       <c r="C10" t="n">
-        <v>409.6355993652344</v>
+        <v>9.651000032424928</v>
       </c>
       <c r="D10" t="n">
-        <v>417.9844500732422</v>
+        <v>6.520349990129471</v>
       </c>
       <c r="E10" t="n">
-        <v>47.30190854550064</v>
+        <v>79.95545838351569</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0109983319503641</v>
+        <v>1.116339912709505</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1201407261922502</v>
+        <v>3.612535777221136</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1129188083352672</v>
+        <v>2.238000106811524</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8584587141779139</v>
+        <v>2.387645053357646</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.240089992671354</v>
+        <v>2.173863412240089</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3816312784934397</v>
+        <v>0.2137816411175577</v>
       </c>
       <c r="L10" t="n">
-        <v>1.191718983171606</v>
+        <v>0.3715229171689866</v>
       </c>
       <c r="M10" t="n">
-        <v>32685743</v>
+        <v>2289269</v>
       </c>
       <c r="N10" t="n">
-        <v>48989930.86</v>
+        <v>3915431.38</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6671930828685395</v>
+        <v>0.5846786159230302</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0077251921194358</v>
+        <v>0.0005681948105162</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1879,10 +3570,10 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>19.89070565359933</v>
+        <v>1.69085727419172</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0503868303818533</v>
+        <v>0.1044383705012731</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1893,66 +3584,2018 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CBOE</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>277.1300048828125</v>
+      </c>
+      <c r="C11" t="n">
+        <v>301.489001159668</v>
+      </c>
+      <c r="D11" t="n">
+        <v>275.8806508636475</v>
+      </c>
+      <c r="E11" t="n">
+        <v>63.08948813870285</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.0634335566097992</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.0771561233832949</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0620041843989049</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-8.389997269254479</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-14.00248770166269</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.61249043240821</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.77123635252852</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1269398</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1559581.96</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.8139347803176693</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.0012683117417138</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>11.98213849748884</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.0432365254081946</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>103.7900009155273</v>
+      </c>
+      <c r="C12" t="n">
+        <v>112.6027996826172</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100.9755499267578</v>
+      </c>
+      <c r="E12" t="n">
+        <v>64.40748321374801</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1597944283508272</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.1379568139522107</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.0346014430916795</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7852899954126684</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-1.125906164833035</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.911196160245703</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.637134413002336</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1242983</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1511187.66</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.822520612694786</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.008180004348712199</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>6.049643925258091</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.0582873482213549</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CRDO</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>236.8800048828125</v>
+      </c>
+      <c r="C13" t="n">
+        <v>226.1213998413086</v>
+      </c>
+      <c r="D13" t="n">
+        <v>161.3880502319336</v>
+      </c>
+      <c r="E13" t="n">
+        <v>35.03556650730233</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.1053029304066459</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7630247380674873</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.574790637989232</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7.133377048530008</v>
+      </c>
+      <c r="J13" t="n">
+        <v>11.21173626549988</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-4.078359216969876</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-2.77502469175505</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6712455</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8705089.1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.7710954963114622</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.0327398353762632</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>28.31142861502511</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1195180176943644</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>352.510009765625</v>
+      </c>
+      <c r="C14" t="n">
+        <v>372.7972003173828</v>
+      </c>
+      <c r="D14" t="n">
+        <v>319.4152998352051</v>
+      </c>
+      <c r="E14" t="n">
+        <v>52.39629178665267</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.0147021254145659</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0971025254243502</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.0728611921592201</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-2.20383870768751</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-2.80130271294401</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.5974640052565006</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.141343376060255</v>
+      </c>
+      <c r="M14" t="n">
+        <v>15013162</v>
+      </c>
+      <c r="N14" t="n">
+        <v>33015809.24</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.4547264581905489</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.0027436600281235</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>10.05785696847098</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.0285321173579104</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>103.120002746582</v>
+      </c>
+      <c r="C15" t="n">
+        <v>117.1707998657227</v>
+      </c>
+      <c r="D15" t="n">
+        <v>62.83409996986389</v>
+      </c>
+      <c r="E15" t="n">
+        <v>23.43354907791833</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.1183310229670477</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.5820804274895581</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.263885937953676</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1.380027150532328</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.262472583409701</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-3.642499733942029</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-3.296169654456531</v>
+      </c>
+      <c r="M15" t="n">
+        <v>99602024</v>
+      </c>
+      <c r="N15" t="n">
+        <v>132026546.48</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.7544090688995503</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.0353695797192571</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>10.03500039236886</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.0973138103674214</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IONQ</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>38.88000106811523</v>
+      </c>
+      <c r="C16" t="n">
+        <v>55.01780014038086</v>
+      </c>
+      <c r="D16" t="n">
+        <v>48.86195004463196</v>
+      </c>
+      <c r="E16" t="n">
+        <v>15.99020298115008</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.329539576775829</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.3064516387463771</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.2137512544336695</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-3.828664268174151</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-2.379467664629328</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-1.449196603544823</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1.270452879257462</v>
+      </c>
+      <c r="M16" t="n">
+        <v>23643818</v>
+      </c>
+      <c r="N16" t="n">
+        <v>29093270.36</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.8126902787975192</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.0184321256247612</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>3.97057124546596</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.1021237432198054</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KYTX</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7.769999980926514</v>
+      </c>
+      <c r="C17" t="n">
+        <v>8.716799955368042</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8.183749969005584</v>
+      </c>
+      <c r="E17" t="n">
+        <v>45.20795488517063</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.0127064683718816</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.1812433963830317</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.0661057372682181</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1189289027810343</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.1258179386224268</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.0068890358413925</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.1053387520495297</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1952297</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1056229.94</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.848363624307033</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0029464435139859</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0.703214134488787</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.09050374983462139</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>LLY</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B18" t="n">
         <v>1181.869995117188</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C18" t="n">
         <v>1093.367601318359</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D18" t="n">
         <v>998.5020529174805</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E18" t="n">
         <v>63.59330391902413</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F18" t="n">
         <v>0.0180197638358101</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G18" t="n">
         <v>0.2714431828709958</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H18" t="n">
         <v>0.1112395445536644</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I18" t="n">
         <v>32.89004314048429</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J18" t="n">
         <v>36.35861605354793</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K18" t="n">
         <v>-3.468572913063639</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L18" t="n">
         <v>-0.8770421350267767</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M18" t="n">
         <v>1525845</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N18" t="n">
         <v>3313754.9</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O18" t="n">
         <v>0.460458013958727</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P18" t="n">
         <v>-0.0071261261474068</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="R18" t="n">
         <v>41.61715262276785</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S18" t="n">
         <v>0.0352129699499151</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LUNR</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>15.14999961853027</v>
+      </c>
+      <c r="C19" t="n">
+        <v>27.66040004730225</v>
+      </c>
+      <c r="D19" t="n">
+        <v>18.9955750322342</v>
+      </c>
+      <c r="E19" t="n">
+        <v>22.01308672444488</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.5055483054725967</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.3793527360412319</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.1837284453412545</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-3.381335397595574</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-3.141287952753423</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.2400474448421516</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.2227528480675804</v>
+      </c>
+      <c r="M19" t="n">
+        <v>9735521</v>
+      </c>
+      <c r="N19" t="n">
+        <v>14334476.42</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.6791682315244271</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.0085687699657102</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>1.668785776410784</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.110150879104291</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>217.5299987792969</v>
+      </c>
+      <c r="C20" t="n">
+        <v>232.6888000488281</v>
+      </c>
+      <c r="D20" t="n">
+        <v>127.4797001647949</v>
+      </c>
+      <c r="E20" t="n">
+        <v>26.81350318140036</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.2250721192654516</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6567402416094965</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.613914871286744</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-3.204063803227768</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6.405497878057763</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-9.60956168128553</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-9.135745020112926</v>
+      </c>
+      <c r="M20" t="n">
+        <v>25200253</v>
+      </c>
+      <c r="N20" t="n">
+        <v>45375885.06</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.5553666439051933</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.0304482114843208</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>22.82714407784598</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.1049379129588747</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>937</v>
+      </c>
+      <c r="C21" t="n">
+        <v>907.4182006835938</v>
+      </c>
+      <c r="D21" t="n">
+        <v>468.3365003204346</v>
+      </c>
+      <c r="E21" t="n">
+        <v>32.2591555067534</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.0591141367907767</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.196642923300117</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.715233735963033</v>
+      </c>
+      <c r="I21" t="n">
+        <v>11.82658795472946</v>
+      </c>
+      <c r="J21" t="n">
+        <v>40.65852286513154</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-28.83193491040208</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-28.47679485729119</v>
+      </c>
+      <c r="M21" t="n">
+        <v>35042195</v>
+      </c>
+      <c r="N21" t="n">
+        <v>54239743.9</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.6460612178517311</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.0518891076021834</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>97.98501586914062</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1045731225924659</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NBIS</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>210.509994506836</v>
+      </c>
+      <c r="C22" t="n">
+        <v>222.8711999511719</v>
+      </c>
+      <c r="D22" t="n">
+        <v>136.3346254730225</v>
+      </c>
+      <c r="E22" t="n">
+        <v>31.19082085488327</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.0527808256677213</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.36199532758812</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.149596587877373</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-4.446131681101804</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.215339231112166</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-6.66147091221397</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-7.117179030533046</v>
+      </c>
+      <c r="M22" t="n">
+        <v>10418641</v>
+      </c>
+      <c r="N22" t="n">
+        <v>17944320.82</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.5806093807901501</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.0308900004182012</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>26.59443010602678</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.1263333371336114</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>203.5299987792969</v>
+      </c>
+      <c r="C23" t="n">
+        <v>209.0846005249024</v>
+      </c>
+      <c r="D23" t="n">
+        <v>191.7959504699707</v>
+      </c>
+      <c r="E23" t="n">
+        <v>45.3606417209306</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.0065407154284556</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0751148983365332</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1009953375922463</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.470477138528508</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-2.676673164090676</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.206196025562167</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.243094423058239</v>
+      </c>
+      <c r="M23" t="n">
+        <v>113202886</v>
+      </c>
+      <c r="N23" t="n">
+        <v>160736729.72</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.7042751597422509</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.0114714322654375</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>6.897855486188616</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.0338910997276057</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CCJ</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>90.1999969482422</v>
+      </c>
+      <c r="C24" t="n">
+        <v>107.2673994445801</v>
+      </c>
+      <c r="D24" t="n">
+        <v>104.4071496582031</v>
+      </c>
+      <c r="E24" t="n">
+        <v>18.63144679070228</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.0886127529987983</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.2270779836588432</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.1613982986648418</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-3.944035004077562</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-3.150560770783445</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.7934742332941171</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.5758541077941897</v>
+      </c>
+      <c r="M24" t="n">
+        <v>5453444</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3248290.88</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.678865656267828</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.0165641876578346</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>4.846427917480469</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.0537298013464613</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>25.95999908447266</v>
+      </c>
+      <c r="C25" t="n">
+        <v>36.10280010223389</v>
+      </c>
+      <c r="D25" t="n">
+        <v>25.30039998531341</v>
+      </c>
+      <c r="E25" t="n">
+        <v>41.46933662967547</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.2402692281070749</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.2435897635398968</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1431087684288856</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.398414176127453</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-2.383489535301673</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.0149246408257801</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0551783542258297</v>
+      </c>
+      <c r="M25" t="n">
+        <v>5748224</v>
+      </c>
+      <c r="N25" t="n">
+        <v>13410086.48</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.4286492863840204</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.0034549003924671</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>2.413071359906878</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.0929534454933859</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PUBM</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>13.56999969482422</v>
+      </c>
+      <c r="C26" t="n">
+        <v>11.39380002975464</v>
+      </c>
+      <c r="D26" t="n">
+        <v>9.101925008296966</v>
+      </c>
+      <c r="E26" t="n">
+        <v>75.50561349871404</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.2040815566672071</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.5687861610715199</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6212664134245443</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.6810486742976209</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.6384767328340759</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.042571941463545</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0616822772464507</v>
+      </c>
+      <c r="M26" t="n">
+        <v>306656</v>
+      </c>
+      <c r="N26" t="n">
+        <v>673529.12</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.4552973151331601</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.0007380242613335</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>0.5974428313119071</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.0440267387433899</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RKLB</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>76.73000335693359</v>
+      </c>
+      <c r="C27" t="n">
+        <v>107.0883999633789</v>
+      </c>
+      <c r="D27" t="n">
+        <v>76.91300010681152</v>
+      </c>
+      <c r="E27" t="n">
+        <v>32.22155183233293</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.3315037099410254</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0865194048813213</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.0956982352765046</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-7.502857180160049</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-5.901575053726029</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.60128212643402</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1.41846552484385</v>
+      </c>
+      <c r="M27" t="n">
+        <v>18620205</v>
+      </c>
+      <c r="N27" t="n">
+        <v>28316700.1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.6575697356769336</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.0176456106739973</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>7.806785583496094</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.101743584542547</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>18.1299991607666</v>
+      </c>
+      <c r="C28" t="n">
+        <v>16.89759994506836</v>
+      </c>
+      <c r="D28" t="n">
+        <v>22.02237502574921</v>
+      </c>
+      <c r="E28" t="n">
+        <v>60.23854340937944</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.08758242818180249</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0633431068641061</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.3383211893001081</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.3961109768285347</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.363303113685673</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.0328078631428616</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.0683407053806285</v>
+      </c>
+      <c r="M28" t="n">
+        <v>96562789</v>
+      </c>
+      <c r="N28" t="n">
+        <v>77071301.78</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.252902011122615</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.0111820594672281</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>0.9592786516462054</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.052911124989023</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STTK</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>6.429999828338623</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5.949199991226196</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4.476700005531311</v>
+      </c>
+      <c r="E29" t="n">
+        <v>64.1330123763551</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.5382775340673356</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.0502215884114906</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3536841743870784</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.370541003841125</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.3059377744577766</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.0646032293833483</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.124170819681362</v>
+      </c>
+      <c r="M29" t="n">
+        <v>863351</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1214273.02</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.7110023740789365</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-0.0015059867839982</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>0.6474284103938511</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.1006887134802821</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>394.760009765625</v>
+      </c>
+      <c r="C30" t="n">
+        <v>409.6355993652344</v>
+      </c>
+      <c r="D30" t="n">
+        <v>417.9844500732422</v>
+      </c>
+      <c r="E30" t="n">
+        <v>47.30190854550064</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.0109983319503641</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1201407261922502</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.1129188083352672</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.8584587141779139</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-1.240089992671354</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.3816312784934397</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.191718983171606</v>
+      </c>
+      <c r="M30" t="n">
+        <v>32685743</v>
+      </c>
+      <c r="N30" t="n">
+        <v>48989930.86</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.6671930828685395</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-0.0077251921194358</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>19.89070565359933</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.0503868303818533</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>421.5799865722656</v>
+      </c>
+      <c r="C31" t="n">
+        <v>424.5066003417969</v>
+      </c>
+      <c r="D31" t="n">
+        <v>349.0248500061035</v>
+      </c>
+      <c r="E31" t="n">
+        <v>37.838400646266</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0012111507330756</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.1407310610095564</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3026603844254834</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.714938807848512</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6.42672567296799</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-3.711786865119478</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-2.826101363815375</v>
+      </c>
+      <c r="M31" t="n">
+        <v>14192963</v>
+      </c>
+      <c r="N31" t="n">
+        <v>13729717.26</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.033740369974669</v>
+      </c>
+      <c r="P31" t="n">
+        <v>-0.0006679828548723</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>21.50142996651786</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.051002017769722</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>VRT</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>305.8699951171875</v>
+      </c>
+      <c r="C32" t="n">
+        <v>324.7316009521484</v>
+      </c>
+      <c r="D32" t="n">
+        <v>237.6646502685547</v>
+      </c>
+      <c r="E32" t="n">
+        <v>37.27464274525995</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.0268228484738957</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0197026397868611</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.8698495640872399</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-1.147608980761959</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-0.9995548151418208</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.1480541656201379</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.6333687634440077</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3691757</v>
+      </c>
+      <c r="N32" t="n">
+        <v>6234385.14</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.5921605606804075</v>
+      </c>
+      <c r="P32" t="n">
+        <v>-0.0217022618956923</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>23.01642935616629</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.075249059154521</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>860.6599731445312</v>
+      </c>
+      <c r="C33" t="n">
+        <v>873.0957971191406</v>
+      </c>
+      <c r="D33" t="n">
+        <v>476.2953498840332</v>
+      </c>
+      <c r="E33" t="n">
+        <v>33.24526766433529</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.0085590819858302</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.6767844529691138</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.831025115942902</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-2.548893026430619</v>
+      </c>
+      <c r="J33" t="n">
+        <v>15.03973086762754</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-17.58862389405815</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-18.29337606210337</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4095064</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4428123.28</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.9247854544826491</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-0.0450134431680942</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>88.97071620396206</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.1033749901007899</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>27.65999984741211</v>
+      </c>
+      <c r="C34" t="n">
+        <v>33.44839981079102</v>
+      </c>
+      <c r="D34" t="n">
+        <v>34.46944990158081</v>
+      </c>
+      <c r="E34" t="n">
+        <v>22.68907596697776</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.1348138742105638</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.06507510892341729</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.0828912471037202</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-1.952459172100369</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-1.839501051819422</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.1129581202809464</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-0.1851025146949276</v>
+      </c>
+      <c r="M34" t="n">
+        <v>22683969</v>
+      </c>
+      <c r="N34" t="n">
+        <v>55711519.38</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.4071683783254234</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-0.024690901380911</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>1.90678528376988</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.06893656161564581</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DDOG</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>260.239990234375</v>
+      </c>
+      <c r="C35" t="n">
+        <v>223.3829998779297</v>
+      </c>
+      <c r="D35" t="n">
+        <v>159.7822002410889</v>
+      </c>
+      <c r="E35" t="n">
+        <v>72.85664449359034</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.1109972000148784</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.364098709171339</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.073790697780459</v>
+      </c>
+      <c r="I35" t="n">
+        <v>11.84447561317248</v>
+      </c>
+      <c r="J35" t="n">
+        <v>11.44889912504316</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.3955764881293149</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.8170337357042587</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3995404</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6159172.08</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.6486917313081468</v>
+      </c>
+      <c r="P35" t="n">
+        <v>-0.0020967947775294</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>13.0058604649135</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.0499764100559652</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SKHY</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>152.3500061035156</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>-1.249229844139535</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-0.249845968827907</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.999383875311628</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>56651863</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>-0.0916016897377034</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>8.350000381469727</v>
+      </c>
+      <c r="C37" t="n">
+        <v>11.01620002746582</v>
+      </c>
+      <c r="D37" t="n">
+        <v>18.60579996585846</v>
+      </c>
+      <c r="E37" t="n">
+        <v>14.49631933236232</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.1274816460040546</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-0.1283924375816173</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-0.5928815071532083</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-0.6289956274373996</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-0.5032672616488264</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-0.1257283657885731</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-0.1007332683507987</v>
+      </c>
+      <c r="M37" t="n">
+        <v>38662329</v>
+      </c>
+      <c r="N37" t="n">
+        <v>33284358.58</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.161576507688255</v>
+      </c>
+      <c r="P37" t="n">
+        <v>-0.0188053182534636</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R37" t="n">
+        <v>0.7357140268598285</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.0881094602693097</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>45.81000137329102</v>
+      </c>
+      <c r="C38" t="n">
+        <v>61.15459983825684</v>
+      </c>
+      <c r="D38" t="n">
+        <v>81.88404979705811</v>
+      </c>
+      <c r="E38" t="n">
+        <v>21.80922241156196</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.2082613050457644</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.1507229785021223</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.564998552508724</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-3.740426935138217</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-3.394162853507454</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-0.3462640816307631</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-0.2587766965285807</v>
+      </c>
+      <c r="M38" t="n">
+        <v>8659172</v>
+      </c>
+      <c r="N38" t="n">
+        <v>12564603.44</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.6891719298066442</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-0.0231319813452317</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>3.724300112043108</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.0812988430560169</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>JOBY</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>7.480000019073486</v>
+      </c>
+      <c r="C39" t="n">
+        <v>9.79479998588562</v>
+      </c>
+      <c r="D39" t="n">
+        <v>12.07090001583099</v>
+      </c>
+      <c r="E39" t="n">
+        <v>19.79695935229539</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.2008546695044591</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.1220657726306231</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.5139701200644334</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-0.5876672497065716</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-0.4619484600576871</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-0.1257187896488844</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-0.1157084245752973</v>
+      </c>
+      <c r="M39" t="n">
+        <v>46232455</v>
+      </c>
+      <c r="N39" t="n">
+        <v>37056707.1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.247613687725642</v>
+      </c>
+      <c r="P39" t="n">
+        <v>-0.0233160405739019</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>0.5634285722460065</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.0753246752418853</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SOUN</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>6.489999771118164</v>
+      </c>
+      <c r="C40" t="n">
+        <v>7.702400026321411</v>
+      </c>
+      <c r="D40" t="n">
+        <v>10.31352501630783</v>
+      </c>
+      <c r="E40" t="n">
+        <v>42.1686670849046</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-0.0728571755545479</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.0511696452722014</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.4476595939473903</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-0.2666229192549947</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-0.3228008935526191</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.0561779742976243</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.0674839355125665</v>
+      </c>
+      <c r="M40" t="n">
+        <v>29192847</v>
+      </c>
+      <c r="N40" t="n">
+        <v>28635716.94</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.01945577479926</v>
+      </c>
+      <c r="P40" t="n">
+        <v>-0.0045180321648213</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>0.4056714943477085</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.0625071662025367</v>
+      </c>
+      <c r="T40" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -2811,24 +2811,99 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>current_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>market_value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No data available yet</t>
-        </is>
+          <t>BLZE</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.74662492</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16.19000053405762</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12.08785785354073</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.05285969</v>
+      </c>
+      <c r="C3" t="n">
+        <v>352.510009765625</v>
+      </c>
+      <c r="D3" t="n">
+        <v>18.63356983810791</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6115135</v>
+      </c>
+      <c r="C4" t="n">
+        <v>18.1299991607666</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11.08673924179745</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.02721351</v>
+      </c>
+      <c r="C5" t="n">
+        <v>394.760009765625</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10.74280547335693</v>
       </c>
     </row>
   </sheetData>
@@ -4862,10 +4937,10 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>0.6474284103938511</v>
+        <v>0.6494855540139335</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1006887134802821</v>
+        <v>0.1010086425121642</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5612,23 +5687,484 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>usd_amount</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>transaction_fee</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>holding_key</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No data available yet</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>56.32</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>DEP-20250630</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Current workbook deposit row</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>406.05</v>
+      </c>
+      <c r="E3" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.20096</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.02721351</v>
+      </c>
+      <c r="H3" t="n">
+        <v>11.0500457355</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Imported current workbook buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ASTS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.20996</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.13442881</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11.050048182</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Imported current workbook buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.20096</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6115135</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11.050048945</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Imported current workbook buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BLZE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.20096</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.74662492</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11.050048816</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Imported current workbook buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IONQ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>53.489</v>
+      </c>
+      <c r="E7" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.21033</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.20695315</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11.06971704035</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Imported current workbook buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IONQ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>47.449</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.18329</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.20695315</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9.819720014350001</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Imported current workbook sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ASTS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>73.86799999999999</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.18516</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.13442881</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9.92998733708</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Imported current workbook sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.17994</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.02592479</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.470066539099999</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Imported current workbook buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>354.87</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.18161</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0269349</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.558387962999999</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Imported current workbook buy</t>
         </is>
       </c>
     </row>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -10,10 +10,12 @@
     <sheet name="PREMARKET_PLAYS" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="BUY_NOW" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="HOLDINGS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="MARKET_DATA" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="TRADE_LOG" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="MARKET_REGIME" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="INSTRUCTIONS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="CASH" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="DEPOSITS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="MARKET_DATA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="TRADE_LOG" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MARKET_REGIME" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="INSTRUCTIONS" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2917,6 +2919,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>total_deposits_usd</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>buy_spend_usd</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>buy_fees_usd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sell_proceeds_usd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>sell_fees_usd</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>cash_available_usd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>56.32</v>
+      </c>
+      <c r="B2" t="n">
+        <v>75.70999999999999</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.38472</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-1.753169999999994</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>amount_nzd</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>fx_rate</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>amount_usd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>56.32</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>56.32</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sharesies</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Current workbook deposit row</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:T40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4937,10 +5091,10 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>0.6494855540139335</v>
+        <v>0.6474284103938511</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1010086425121642</v>
+        <v>0.1006887134802821</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5681,24 +5835,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -5762,31 +5916,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>406.05</v>
+      </c>
       <c r="E2" t="n">
-        <v>56.32</v>
+        <v>11.26</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>DEP-20250630</t>
-        </is>
+        <v>0.20096</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.02721351</v>
+      </c>
+      <c r="H2" t="n">
+        <v>11.0500457355</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Current workbook deposit row</t>
+          <t>Imported current workbook buy</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5956,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5807,24 +5965,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>406.05</v>
+        <v>82.2</v>
       </c>
       <c r="E3" t="n">
         <v>11.26</v>
       </c>
       <c r="F3" t="n">
-        <v>0.20096</v>
+        <v>0.20996</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02721351</v>
+        <v>0.13442881</v>
       </c>
       <c r="H3" t="n">
-        <v>11.0500457355</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+        <v>11.050048182</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5840,7 +5996,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ASTS</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5849,24 +6005,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>82.2</v>
+        <v>18.07</v>
       </c>
       <c r="E4" t="n">
         <v>11.26</v>
       </c>
       <c r="F4" t="n">
-        <v>0.20996</v>
+        <v>0.20096</v>
       </c>
       <c r="G4" t="n">
-        <v>0.13442881</v>
+        <v>0.6115135</v>
       </c>
       <c r="H4" t="n">
-        <v>11.050048182</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+        <v>11.050048945</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5882,7 +6036,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>BLZE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5891,7 +6045,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.07</v>
+        <v>14.8</v>
       </c>
       <c r="E5" t="n">
         <v>11.26</v>
@@ -5900,15 +6054,13 @@
         <v>0.20096</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6115135</v>
+        <v>0.74662492</v>
       </c>
       <c r="H5" t="n">
-        <v>11.050048945</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+        <v>11.050048816</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5919,12 +6071,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BLZE</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5933,24 +6085,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.8</v>
+        <v>53.489</v>
       </c>
       <c r="E6" t="n">
-        <v>11.26</v>
+        <v>11.28</v>
       </c>
       <c r="F6" t="n">
-        <v>0.20096</v>
+        <v>0.21033</v>
       </c>
       <c r="G6" t="n">
-        <v>0.74662492</v>
+        <v>0.20695315</v>
       </c>
       <c r="H6" t="n">
-        <v>11.050048816</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+        <v>11.06971704035</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5961,7 +6111,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5971,44 +6121,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>53.489</v>
+        <v>47.449</v>
       </c>
       <c r="E7" t="n">
-        <v>11.28</v>
+        <v>9.65</v>
       </c>
       <c r="F7" t="n">
-        <v>0.21033</v>
+        <v>0.18329</v>
       </c>
       <c r="G7" t="n">
         <v>0.20695315</v>
       </c>
       <c r="H7" t="n">
-        <v>11.06971704035</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+        <v>9.819720014350001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Imported current workbook buy</t>
+          <t>Imported current workbook sell</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6017,24 +6165,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>47.449</v>
+        <v>73.86799999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>9.65</v>
+        <v>9.74</v>
       </c>
       <c r="F8" t="n">
-        <v>0.18329</v>
+        <v>0.18516</v>
       </c>
       <c r="G8" t="n">
-        <v>0.20695315</v>
+        <v>0.13442881</v>
       </c>
       <c r="H8" t="n">
-        <v>9.819720014350001</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+        <v>9.92998733708</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -6050,44 +6196,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ASTS</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>73.86799999999999</v>
+        <v>365.29</v>
       </c>
       <c r="E9" t="n">
-        <v>9.74</v>
+        <v>9.65</v>
       </c>
       <c r="F9" t="n">
-        <v>0.18516</v>
+        <v>0.17994</v>
       </c>
       <c r="G9" t="n">
-        <v>0.13442881</v>
+        <v>0.02592479</v>
       </c>
       <c r="H9" t="n">
-        <v>9.92998733708</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+        <v>9.470066539099999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Imported current workbook sell</t>
+          <t>Imported current workbook buy</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6101,68 +6245,24 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>365.29</v>
+        <v>354.87</v>
       </c>
       <c r="E10" t="n">
-        <v>9.65</v>
+        <v>9.74</v>
       </c>
       <c r="F10" t="n">
-        <v>0.17994</v>
+        <v>0.18161</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02592479</v>
+        <v>0.0269349</v>
       </c>
       <c r="H10" t="n">
-        <v>9.470066539099999</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+        <v>9.558387962999999</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
-        <is>
-          <t>Imported current workbook buy</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>354.87</v>
-      </c>
-      <c r="E11" t="n">
-        <v>9.74</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.18161</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.0269349</v>
-      </c>
-      <c r="H11" t="n">
-        <v>9.558387962999999</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>Imported current workbook buy</t>
         </is>
@@ -6173,7 +6273,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6215,13 +6315,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6246,7 +6346,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open PREMARKET_PLAYS during NZ evening US premarket window.</t>
+          <t>Check CASH first to see available buying power.</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6356,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Focus only on PREMARKET BUY first.</t>
+          <t>Open PREMARKET_PLAYS during NZ evening US premarket window.</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6366,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Check gap_pct, volume_trend, score, stop_loss and trim_price.</t>
+          <t>Focus only on PREMARKET BUY first.</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6376,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Position size is buy_amount_usd. Shares = shares_to_buy.</t>
+          <t>Check gap_pct, volume_trend, score, stop_loss and trim_price.</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6386,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Set stop loss immediately.</t>
+          <t>Position size is buy_amount_usd. Shares = shares_to_buy.</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6396,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Use trim_price as first profit-taking target.</t>
+          <t>Set stop loss immediately.</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6406,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Log all buys/sells in data/trades.csv.</t>
+          <t>Use trim_price as first profit-taking target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Log deposits in data/deposits.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Log buys/sells only in data/trades.csv.</t>
         </is>
       </c>
     </row>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -527,10 +527,10 @@
         <v>7.769999980926514</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.0029464435139859</v>
+        <v>0.0017678661083915</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.848363624307033</v>
+        <v>1.851830814176953</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>70</v>
@@ -704,7 +704,7 @@
         <v>-0.0037174117418728</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8764938588913064</v>
+        <v>0.8789262943053163</v>
       </c>
       <c r="M2" t="n">
         <v>1.773262942271622</v>
@@ -756,10 +756,10 @@
         <v>47.25110136960278</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0364229629329782</v>
+        <v>-0.0365484488215595</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6544075267434142</v>
+        <v>0.665160990480149</v>
       </c>
       <c r="M3" t="n">
         <v>-3.577422784539042</v>
@@ -814,7 +814,7 @@
         <v>-0.0137844778510634</v>
       </c>
       <c r="L4" t="n">
-        <v>1.00619796262587</v>
+        <v>1.006301320925231</v>
       </c>
       <c r="M4" t="n">
         <v>-0.0949479297406228</v>
@@ -869,7 +869,7 @@
         <v>-0.0071261261474068</v>
       </c>
       <c r="L5" t="n">
-        <v>0.460458013958727</v>
+        <v>0.6225647695355339</v>
       </c>
       <c r="M5" t="n">
         <v>-3.468572913063639</v>
@@ -921,10 +921,10 @@
         <v>79.95545838351569</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0005681948105162</v>
+        <v>0.0056818397330839</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5846786159230302</v>
+        <v>0.586453269151991</v>
       </c>
       <c r="M6" t="n">
         <v>0.2137816411175577</v>
@@ -979,7 +979,7 @@
         <v>0.0007380242613335</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4552973151331601</v>
+        <v>0.4649229581688092</v>
       </c>
       <c r="M7" t="n">
         <v>0.042571941463545</v>
@@ -1031,10 +1031,10 @@
         <v>72.85664449359034</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0020967947775294</v>
+        <v>-0.0032228665927801</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6486917313081468</v>
+        <v>0.6833935101223232</v>
       </c>
       <c r="M8" t="n">
         <v>0.3955764881293149</v>
@@ -1089,7 +1089,7 @@
         <v>-0.0015059867839982</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7110023740789365</v>
+        <v>0.7110421535831287</v>
       </c>
       <c r="M9" t="n">
         <v>0.0646032293833483</v>
@@ -1141,10 +1141,10 @@
         <v>46.76644111895504</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0162387056463356</v>
+        <v>-0.0162261925008566</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7186066924249777</v>
+        <v>0.7676989816870774</v>
       </c>
       <c r="M10" t="n">
         <v>3.038872772970159</v>
@@ -1199,7 +1199,7 @@
         <v>-0.0114714322654375</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7042751597422509</v>
+        <v>0.7517100898302004</v>
       </c>
       <c r="M11" t="n">
         <v>1.206196025562167</v>
@@ -1251,10 +1251,10 @@
         <v>52.39629178665267</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0027436600281235</v>
+        <v>-0.0027716844579075</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4547264581905489</v>
+        <v>0.479416037711002</v>
       </c>
       <c r="M12" t="n">
         <v>0.5974640052565006</v>
@@ -1306,10 +1306,10 @@
         <v>60.23854340937944</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0111820594672281</v>
+        <v>0.0114483570142134</v>
       </c>
       <c r="L13" t="n">
-        <v>1.252902011122615</v>
+        <v>1.264046667351417</v>
       </c>
       <c r="M13" t="n">
         <v>0.0328078631428616</v>
@@ -1361,10 +1361,10 @@
         <v>67.81157428603623</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0044020618210463</v>
+        <v>-0.0026901592563831</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6590365403224546</v>
+        <v>0.685952527362262</v>
       </c>
       <c r="M14" t="n">
         <v>1.780135958077288</v>
@@ -1416,10 +1416,10 @@
         <v>39.99174507130462</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0297479323577886</v>
+        <v>-0.0229072122118197</v>
       </c>
       <c r="L15" t="n">
-        <v>1.009130937422583</v>
+        <v>1.014159066720345</v>
       </c>
       <c r="M15" t="n">
         <v>-10.00415359792669</v>
@@ -1471,10 +1471,10 @@
         <v>32.2591555067534</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0518891076021834</v>
+        <v>-0.0513632068007362</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6460612178517311</v>
+        <v>0.6484706647892666</v>
       </c>
       <c r="M16" t="n">
         <v>-28.83193491040208</v>
@@ -1526,10 +1526,10 @@
         <v>35.03556650730233</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0327398353762632</v>
+        <v>-0.0359595173016396</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7710954963114622</v>
+        <v>0.7716095474188931</v>
       </c>
       <c r="M17" t="n">
         <v>-4.078359216969876</v>
@@ -1584,7 +1584,7 @@
         <v>-0.0217022618956923</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5921605606804075</v>
+        <v>0.5960186512249169</v>
       </c>
       <c r="M18" t="n">
         <v>-0.1480541656201379</v>
@@ -1639,7 +1639,7 @@
         <v>-0.0006679828548723</v>
       </c>
       <c r="L19" t="n">
-        <v>1.033740369974669</v>
+        <v>1.038906674058124</v>
       </c>
       <c r="M19" t="n">
         <v>-3.711786865119478</v>
@@ -1694,7 +1694,7 @@
         <v>-0.0012683117417138</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8139347803176693</v>
+        <v>0.9370039155890588</v>
       </c>
       <c r="M20" t="n">
         <v>5.61249043240821</v>
@@ -1749,7 +1749,7 @@
         <v>-0.008180004348712199</v>
       </c>
       <c r="L21" t="n">
-        <v>0.822520612694786</v>
+        <v>0.8319020612963752</v>
       </c>
       <c r="M21" t="n">
         <v>1.911196160245703</v>
@@ -1801,10 +1801,10 @@
         <v>25.12013387453341</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0405393341640209</v>
+        <v>-0.0369832753978448</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4408143064024243</v>
+        <v>0.4698277360705851</v>
       </c>
       <c r="M22" t="n">
         <v>-9.368367243321137</v>
@@ -1856,10 +1856,10 @@
         <v>26.81350318140036</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0304482114843208</v>
+        <v>-0.0298121320218837</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5553666439051933</v>
+        <v>0.560431924401771</v>
       </c>
       <c r="M23" t="n">
         <v>-9.60956168128553</v>
@@ -1911,10 +1911,10 @@
         <v>23.43354907791833</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0353695797192571</v>
+        <v>-0.0351419620325085</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7544090688995503</v>
+        <v>0.7611815955726389</v>
       </c>
       <c r="M24" t="n">
         <v>-3.642499733942029</v>
@@ -1966,10 +1966,10 @@
         <v>33.24526766433529</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0450134431680942</v>
+        <v>-0.0447525650500693</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9247854544826491</v>
+        <v>0.9326165149712228</v>
       </c>
       <c r="M25" t="n">
         <v>-17.58862389405815</v>
@@ -2021,10 +2021,10 @@
         <v>31.19082085488327</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.0308900004182012</v>
+        <v>-0.0316867363918898</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5806093807901501</v>
+        <v>0.5987661019638217</v>
       </c>
       <c r="M26" t="n">
         <v>-6.66147091221397</v>
@@ -2079,7 +2079,7 @@
         <v>-0.0034549003924671</v>
       </c>
       <c r="L27" t="n">
-        <v>0.4286492863840204</v>
+        <v>0.4293128861127736</v>
       </c>
       <c r="M27" t="n">
         <v>-0.0149246408257801</v>
@@ -2134,7 +2134,7 @@
         <v>-0.0077251921194358</v>
       </c>
       <c r="L28" t="n">
-        <v>0.6671930828685395</v>
+        <v>0.6680783600026209</v>
       </c>
       <c r="M28" t="n">
         <v>0.3816312784934397</v>
@@ -2186,10 +2186,10 @@
         <v>45.20795488517063</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0029464435139859</v>
+        <v>0.0017678661083915</v>
       </c>
       <c r="L29" t="n">
-        <v>1.848363624307033</v>
+        <v>1.851830814176953</v>
       </c>
       <c r="M29" t="n">
         <v>-0.0068890358413925</v>
@@ -2244,7 +2244,7 @@
         <v>-0.0045180321648213</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01945577479926</v>
+        <v>1.042917418281125</v>
       </c>
       <c r="M30" t="n">
         <v>0.0561779742976243</v>
@@ -2296,10 +2296,10 @@
         <v>32.22155183233293</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.0176456106739973</v>
+        <v>-0.0141905418668198</v>
       </c>
       <c r="L31" t="n">
-        <v>0.6575697356769336</v>
+        <v>0.6604898529491945</v>
       </c>
       <c r="M31" t="n">
         <v>-1.60128212643402</v>
@@ -2354,7 +2354,7 @@
         <v>-0.0184321256247612</v>
       </c>
       <c r="L32" t="n">
-        <v>0.8126902787975192</v>
+        <v>0.8152458403022232</v>
       </c>
       <c r="M32" t="n">
         <v>-1.449196603544823</v>
@@ -2406,10 +2406,10 @@
         <v>22.68907596697776</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.024690901380911</v>
+        <v>-0.0236665520640497</v>
       </c>
       <c r="L33" t="n">
-        <v>0.4071683783254234</v>
+        <v>0.4081000325851083</v>
       </c>
       <c r="M33" t="n">
         <v>-0.1129581202809464</v>
@@ -2461,10 +2461,10 @@
         <v>44.76385902437732</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.018139686805653</v>
+        <v>-0.0180032692351115</v>
       </c>
       <c r="L34" t="n">
-        <v>0.556489071193276</v>
+        <v>0.5578530772922595</v>
       </c>
       <c r="M34" t="n">
         <v>-0.7205249641778009</v>
@@ -2519,7 +2519,7 @@
         <v>-0.0165641876578346</v>
       </c>
       <c r="L35" t="n">
-        <v>1.678865656267828</v>
+        <v>1.909541795756696</v>
       </c>
       <c r="M35" t="n">
         <v>-0.7934742332941171</v>
@@ -2571,10 +2571,10 @@
         <v>22.01308672444488</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.0085687699657102</v>
+        <v>-0.0085500982745466</v>
       </c>
       <c r="L36" t="n">
-        <v>0.6791682315244271</v>
+        <v>0.7169100399332081</v>
       </c>
       <c r="M36" t="n">
         <v>-0.2400474448421516</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>152.3500061035156</v>
+        <v>153.5099945068359</v>
       </c>
       <c r="E37" t="n">
         <v>22</v>
@@ -2628,13 +2628,13 @@
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
-        <v>-0.999383875311628</v>
+        <v>-0.9253561253561428</v>
       </c>
       <c r="N37" t="n">
-        <v>140.1620056152344</v>
+        <v>141.2291949462891</v>
       </c>
       <c r="O37" t="n">
-        <v>175.202507019043</v>
+        <v>176.5364936828613</v>
       </c>
     </row>
     <row r="38">
@@ -2680,7 +2680,7 @@
         <v>-0.0188053182534636</v>
       </c>
       <c r="L38" t="n">
-        <v>1.161576507688255</v>
+        <v>1.170380854998263</v>
       </c>
       <c r="M38" t="n">
         <v>-0.1257283657885731</v>
@@ -2735,7 +2735,7 @@
         <v>-0.0231319813452317</v>
       </c>
       <c r="L39" t="n">
-        <v>0.6891719298066442</v>
+        <v>0.7994197935035359</v>
       </c>
       <c r="M39" t="n">
         <v>-0.3462640816307631</v>
@@ -2790,7 +2790,7 @@
         <v>-0.0233160405739019</v>
       </c>
       <c r="L40" t="n">
-        <v>1.247613687725642</v>
+        <v>1.305743056025744</v>
       </c>
       <c r="M40" t="n">
         <v>-0.1257187896488844</v>
@@ -3238,16 +3238,16 @@
         <v>-6.89888868607181</v>
       </c>
       <c r="M2" t="n">
-        <v>6245835</v>
+        <v>6277600</v>
       </c>
       <c r="N2" t="n">
-        <v>6189320.7</v>
+        <v>6189956</v>
       </c>
       <c r="O2" t="n">
-        <v>1.009130937422583</v>
+        <v>1.014159066720345</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0297479323577886</v>
+        <v>-0.0229072122118197</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -3306,16 +3306,16 @@
         <v>-3.005596247274948</v>
       </c>
       <c r="M3" t="n">
-        <v>22515725</v>
+        <v>22890700</v>
       </c>
       <c r="N3" t="n">
-        <v>34406274.5</v>
+        <v>34413774</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6544075267434142</v>
+        <v>0.665160990480149</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0364229629329782</v>
+        <v>-0.0365484488215595</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>38.40574863978794</v>
+        <v>38.40929303850447</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0718683874829775</v>
+        <v>0.071875020089537</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3374,16 +3374,16 @@
         <v>1.752601933393177</v>
       </c>
       <c r="M4" t="n">
-        <v>33220841</v>
+        <v>34596500</v>
       </c>
       <c r="N4" t="n">
-        <v>50408192.82</v>
+        <v>50435706</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6590365403224546</v>
+        <v>0.685952527362262</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0044020618210463</v>
+        <v>-0.0026901592563831</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>7.571425301688058</v>
+        <v>7.574996948242188</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03061512019907</v>
+        <v>0.0306295621811547</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3442,13 +3442,13 @@
         <v>1.980736671657304</v>
       </c>
       <c r="M5" t="n">
-        <v>9112359</v>
+        <v>9138100</v>
       </c>
       <c r="N5" t="n">
-        <v>10396375.18</v>
+        <v>10396890</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8764938588913064</v>
+        <v>0.8789262943053163</v>
       </c>
       <c r="P5" t="n">
         <v>-0.0037174117418728</v>
@@ -3510,16 +3510,16 @@
         <v>-9.295743678605769</v>
       </c>
       <c r="M6" t="n">
-        <v>4941759</v>
+        <v>5270100</v>
       </c>
       <c r="N6" t="n">
-        <v>11210523.18</v>
+        <v>11217090</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4408143064024243</v>
+        <v>0.4698277360705851</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0405393341640209</v>
+        <v>-0.0369832753978448</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -3578,16 +3578,16 @@
         <v>-0.3496537910423321</v>
       </c>
       <c r="M7" t="n">
-        <v>12951297</v>
+        <v>12983400</v>
       </c>
       <c r="N7" t="n">
-        <v>23273227.94</v>
+        <v>23273870</v>
       </c>
       <c r="O7" t="n">
-        <v>0.556489071193276</v>
+        <v>0.5578530772922595</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.018139686805653</v>
+        <v>-0.0180032692351115</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -3646,16 +3646,16 @@
         <v>3.503419447292556</v>
       </c>
       <c r="M8" t="n">
-        <v>19865507</v>
+        <v>21243800</v>
       </c>
       <c r="N8" t="n">
-        <v>27644478.14</v>
+        <v>27672044</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7186066924249777</v>
+        <v>0.7676989816870774</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0162387056463356</v>
+        <v>-0.0162261925008566</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -3714,13 +3714,13 @@
         <v>-0.0967705380809897</v>
       </c>
       <c r="M9" t="n">
-        <v>7965165</v>
+        <v>7966000</v>
       </c>
       <c r="N9" t="n">
-        <v>7916101.3</v>
+        <v>7916118</v>
       </c>
       <c r="O9" t="n">
-        <v>1.00619796262587</v>
+        <v>1.006301320925231</v>
       </c>
       <c r="P9" t="n">
         <v>-0.0137844778510634</v>
@@ -3782,16 +3782,16 @@
         <v>0.3715229171689866</v>
       </c>
       <c r="M10" t="n">
-        <v>2289269</v>
+        <v>2296300</v>
       </c>
       <c r="N10" t="n">
-        <v>3915431.38</v>
+        <v>3915572</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5846786159230302</v>
+        <v>0.586453269151991</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0005681948105162</v>
+        <v>0.0056818397330839</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -3850,13 +3850,13 @@
         <v>4.77123635252852</v>
       </c>
       <c r="M11" t="n">
-        <v>1269398</v>
+        <v>1465000</v>
       </c>
       <c r="N11" t="n">
-        <v>1559581.96</v>
+        <v>1563494</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8139347803176693</v>
+        <v>0.9370039155890588</v>
       </c>
       <c r="P11" t="n">
         <v>-0.0012683117417138</v>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>11.98213849748884</v>
+        <v>12.01285443987165</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0432365254081946</v>
+        <v>0.0433473612680497</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -3918,13 +3918,13 @@
         <v>2.637134413002336</v>
       </c>
       <c r="M12" t="n">
-        <v>1242983</v>
+        <v>1257400</v>
       </c>
       <c r="N12" t="n">
-        <v>1511187.66</v>
+        <v>1511476</v>
       </c>
       <c r="O12" t="n">
-        <v>0.822520612694786</v>
+        <v>0.8319020612963752</v>
       </c>
       <c r="P12" t="n">
         <v>-0.008180004348712199</v>
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>6.049643925258091</v>
+        <v>6.056072235107422</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0582873482213549</v>
+        <v>0.0583492839549769</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3986,16 +3986,16 @@
         <v>-2.77502469175505</v>
       </c>
       <c r="M13" t="n">
-        <v>6712455</v>
+        <v>6717000</v>
       </c>
       <c r="N13" t="n">
-        <v>8705089.1</v>
+        <v>8705180</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7710954963114622</v>
+        <v>0.7716095474188931</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.0327398353762632</v>
+        <v>-0.0359595173016396</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -4054,16 +4054,16 @@
         <v>1.141343376060255</v>
       </c>
       <c r="M14" t="n">
-        <v>15013162</v>
+        <v>15836200</v>
       </c>
       <c r="N14" t="n">
-        <v>33015809.24</v>
+        <v>33032270</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4547264581905489</v>
+        <v>0.479416037711002</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0027436600281235</v>
+        <v>-0.0027716844579075</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>10.05785696847098</v>
+        <v>10.05857195172991</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0285321173579104</v>
+        <v>0.0285341456216168</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4122,16 +4122,16 @@
         <v>-3.296169654456531</v>
       </c>
       <c r="M15" t="n">
-        <v>99602024</v>
+        <v>100510000</v>
       </c>
       <c r="N15" t="n">
-        <v>132026546.48</v>
+        <v>132044706</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7544090688995503</v>
+        <v>0.7611815955726389</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.0353695797192571</v>
+        <v>-0.0351419620325085</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -4190,13 +4190,13 @@
         <v>-1.270452879257462</v>
       </c>
       <c r="M16" t="n">
-        <v>23643818</v>
+        <v>23719400</v>
       </c>
       <c r="N16" t="n">
-        <v>29093270.36</v>
+        <v>29094782</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8126902787975192</v>
+        <v>0.8152458403022232</v>
       </c>
       <c r="P16" t="n">
         <v>-0.0184321256247612</v>
@@ -4258,16 +4258,16 @@
         <v>0.1053387520495297</v>
       </c>
       <c r="M17" t="n">
-        <v>1952297</v>
+        <v>1956100</v>
       </c>
       <c r="N17" t="n">
-        <v>1056229.94</v>
+        <v>1056306</v>
       </c>
       <c r="O17" t="n">
-        <v>1.848363624307033</v>
+        <v>1.851830814176953</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0029464435139859</v>
+        <v>0.0017678661083915</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -4326,13 +4326,13 @@
         <v>-0.8770421350267767</v>
       </c>
       <c r="M18" t="n">
-        <v>1525845</v>
+        <v>2069800</v>
       </c>
       <c r="N18" t="n">
-        <v>3313754.9</v>
+        <v>3324634</v>
       </c>
       <c r="O18" t="n">
-        <v>0.460458013958727</v>
+        <v>0.6225647695355339</v>
       </c>
       <c r="P18" t="n">
         <v>-0.0071261261474068</v>
@@ -4343,10 +4343,10 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>41.61715262276785</v>
+        <v>41.62001255580357</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0352129699499151</v>
+        <v>0.0352153897871624</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -4394,16 +4394,16 @@
         <v>-0.2227528480675804</v>
       </c>
       <c r="M19" t="n">
-        <v>9735521</v>
+        <v>10284400</v>
       </c>
       <c r="N19" t="n">
-        <v>14334476.42</v>
+        <v>14345454</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6791682315244271</v>
+        <v>0.7169100399332081</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.0085687699657102</v>
+        <v>-0.0085500982745466</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -4462,20 +4462,20 @@
         <v>-9.135745020112926</v>
       </c>
       <c r="M20" t="n">
-        <v>25200253</v>
+        <v>25432700</v>
       </c>
       <c r="N20" t="n">
-        <v>45375885.06</v>
+        <v>45380534</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5553666439051933</v>
+        <v>0.560431924401771</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.0304482114843208</v>
+        <v>-0.0298121320218837</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="R20" t="n">
@@ -4530,16 +4530,16 @@
         <v>-28.47679485729119</v>
       </c>
       <c r="M21" t="n">
-        <v>35042195</v>
+        <v>35174600</v>
       </c>
       <c r="N21" t="n">
-        <v>54239743.9</v>
+        <v>54242392</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6460612178517311</v>
+        <v>0.6484706647892666</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.0518891076021834</v>
+        <v>-0.0513632068007362</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -4598,16 +4598,16 @@
         <v>-7.117179030533046</v>
       </c>
       <c r="M22" t="n">
-        <v>10418641</v>
+        <v>10748400</v>
       </c>
       <c r="N22" t="n">
-        <v>17944320.82</v>
+        <v>17950916</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5806093807901501</v>
+        <v>0.5987661019638217</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.0308900004182012</v>
+        <v>-0.0316867363918898</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -4666,13 +4666,13 @@
         <v>1.243094423058239</v>
       </c>
       <c r="M23" t="n">
-        <v>113202886</v>
+        <v>120943800</v>
       </c>
       <c r="N23" t="n">
-        <v>160736729.72</v>
+        <v>160891548</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7042751597422509</v>
+        <v>0.7517100898302004</v>
       </c>
       <c r="P23" t="n">
         <v>-0.0114714322654375</v>
@@ -4683,10 +4683,10 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>6.897855486188616</v>
+        <v>6.922855922154018</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0338910997276057</v>
+        <v>0.0340139338852991</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -4734,13 +4734,13 @@
         <v>-0.5758541077941897</v>
       </c>
       <c r="M24" t="n">
-        <v>5453444</v>
+        <v>6232500</v>
       </c>
       <c r="N24" t="n">
-        <v>3248290.88</v>
+        <v>3263872</v>
       </c>
       <c r="O24" t="n">
-        <v>1.678865656267828</v>
+        <v>1.909541795756696</v>
       </c>
       <c r="P24" t="n">
         <v>-0.0165641876578346</v>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>4.846427917480469</v>
+        <v>4.847142355782645</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0537298013464613</v>
+        <v>0.0537377219487489</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -4802,13 +4802,13 @@
         <v>0.0551783542258297</v>
       </c>
       <c r="M25" t="n">
-        <v>5748224</v>
+        <v>5757200</v>
       </c>
       <c r="N25" t="n">
-        <v>13410086.48</v>
+        <v>13410266</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4286492863840204</v>
+        <v>0.4293128861127736</v>
       </c>
       <c r="P25" t="n">
         <v>-0.0034549003924671</v>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>2.413071359906878</v>
+        <v>2.413428579057966</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0929534454933859</v>
+        <v>0.09296720586178669</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -4870,13 +4870,13 @@
         <v>0.0616822772464507</v>
       </c>
       <c r="M26" t="n">
-        <v>306656</v>
+        <v>313200</v>
       </c>
       <c r="N26" t="n">
-        <v>673529.12</v>
+        <v>673660</v>
       </c>
       <c r="O26" t="n">
-        <v>0.4552973151331601</v>
+        <v>0.4649229581688092</v>
       </c>
       <c r="P26" t="n">
         <v>0.0007380242613335</v>
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>0.5974428313119071</v>
+        <v>0.597428526197161</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0440267387433899</v>
+        <v>0.0440256845713142</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4938,16 +4938,16 @@
         <v>-1.41846552484385</v>
       </c>
       <c r="M27" t="n">
-        <v>18620205</v>
+        <v>18704000</v>
       </c>
       <c r="N27" t="n">
-        <v>28316700.1</v>
+        <v>28318376</v>
       </c>
       <c r="O27" t="n">
-        <v>0.6575697356769336</v>
+        <v>0.6604898529491945</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.0176456106739973</v>
+        <v>-0.0141905418668198</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -5006,16 +5006,16 @@
         <v>0.0683407053806285</v>
       </c>
       <c r="M28" t="n">
-        <v>96562789</v>
+        <v>97444000</v>
       </c>
       <c r="N28" t="n">
-        <v>77071301.78</v>
+        <v>77088926</v>
       </c>
       <c r="O28" t="n">
-        <v>1.252902011122615</v>
+        <v>1.264046667351417</v>
       </c>
       <c r="P28" t="n">
-        <v>0.0111820594672281</v>
+        <v>0.0114483570142134</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>0.9592786516462054</v>
+        <v>0.9592857360839844</v>
       </c>
       <c r="S28" t="n">
-        <v>0.052911124989023</v>
+        <v>0.0529115157467785</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5074,13 +5074,13 @@
         <v>0.124170819681362</v>
       </c>
       <c r="M29" t="n">
-        <v>863351</v>
+        <v>863400</v>
       </c>
       <c r="N29" t="n">
-        <v>1214273.02</v>
+        <v>1214274</v>
       </c>
       <c r="O29" t="n">
-        <v>0.7110023740789365</v>
+        <v>0.7110421535831287</v>
       </c>
       <c r="P29" t="n">
         <v>-0.0015059867839982</v>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>0.6474284103938511</v>
+        <v>0.6494998591286796</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1006887134802821</v>
+        <v>0.1010108672579073</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5142,13 +5142,13 @@
         <v>1.191718983171606</v>
       </c>
       <c r="M30" t="n">
-        <v>32685743</v>
+        <v>32729700</v>
       </c>
       <c r="N30" t="n">
-        <v>48989930.86</v>
+        <v>48990810</v>
       </c>
       <c r="O30" t="n">
-        <v>0.6671930828685395</v>
+        <v>0.6680783600026209</v>
       </c>
       <c r="P30" t="n">
         <v>-0.0077251921194358</v>
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>19.89070565359933</v>
+        <v>19.89071219308036</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0503868303818533</v>
+        <v>0.0503868469475663</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -5210,13 +5210,13 @@
         <v>-2.826101363815375</v>
       </c>
       <c r="M31" t="n">
-        <v>14192963</v>
+        <v>14265400</v>
       </c>
       <c r="N31" t="n">
-        <v>13729717.26</v>
+        <v>13731166</v>
       </c>
       <c r="O31" t="n">
-        <v>1.033740369974669</v>
+        <v>1.038906674058124</v>
       </c>
       <c r="P31" t="n">
         <v>-0.0006679828548723</v>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>21.50142996651786</v>
+        <v>21.50642830984933</v>
       </c>
       <c r="S31" t="n">
-        <v>0.051002017769722</v>
+        <v>0.0510138739856019</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -5278,13 +5278,13 @@
         <v>0.6333687634440077</v>
       </c>
       <c r="M32" t="n">
-        <v>3691757</v>
+        <v>3716100</v>
       </c>
       <c r="N32" t="n">
-        <v>6234385.14</v>
+        <v>6234872</v>
       </c>
       <c r="O32" t="n">
-        <v>0.5921605606804075</v>
+        <v>0.5960186512249169</v>
       </c>
       <c r="P32" t="n">
         <v>-0.0217022618956923</v>
@@ -5346,16 +5346,16 @@
         <v>-18.29337606210337</v>
       </c>
       <c r="M33" t="n">
-        <v>4095064</v>
+        <v>4130400</v>
       </c>
       <c r="N33" t="n">
-        <v>4428123.28</v>
+        <v>4428830</v>
       </c>
       <c r="O33" t="n">
-        <v>0.9247854544826491</v>
+        <v>0.9326165149712228</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.0450134431680942</v>
+        <v>-0.0447525650500693</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -5414,16 +5414,16 @@
         <v>-0.1851025146949276</v>
       </c>
       <c r="M34" t="n">
-        <v>22683969</v>
+        <v>22736300</v>
       </c>
       <c r="N34" t="n">
-        <v>55711519.38</v>
+        <v>55712566</v>
       </c>
       <c r="O34" t="n">
-        <v>0.4071683783254234</v>
+        <v>0.4081000325851083</v>
       </c>
       <c r="P34" t="n">
-        <v>-0.024690901380911</v>
+        <v>-0.0236665520640497</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>1.90678528376988</v>
+        <v>1.90642820085798</v>
       </c>
       <c r="S34" t="n">
-        <v>0.06893656161564581</v>
+        <v>0.0689236518935247</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5482,16 +5482,16 @@
         <v>0.8170337357042587</v>
       </c>
       <c r="M35" t="n">
-        <v>3995404</v>
+        <v>4212100</v>
       </c>
       <c r="N35" t="n">
-        <v>6159172.08</v>
+        <v>6163506</v>
       </c>
       <c r="O35" t="n">
-        <v>0.6486917313081468</v>
+        <v>0.6833935101223232</v>
       </c>
       <c r="P35" t="n">
-        <v>-0.0020967947775294</v>
+        <v>-0.0032228665927801</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>13.0058604649135</v>
+        <v>13.0087160382952</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0499764100559652</v>
+        <v>0.0499873829021412</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>152.3500061035156</v>
+        <v>153.5099945068359</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
@@ -5526,19 +5526,19 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>-1.249229844139535</v>
+        <v>-1.156695156695179</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.249845968827907</v>
+        <v>-0.2313390313390357</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.999383875311628</v>
+        <v>-0.9253561253561428</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>56651863</v>
+        <v>56529633</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -5598,13 +5598,13 @@
         <v>-0.1007332683507987</v>
       </c>
       <c r="M37" t="n">
-        <v>38662329</v>
+        <v>38962400</v>
       </c>
       <c r="N37" t="n">
-        <v>33284358.58</v>
+        <v>33290360</v>
       </c>
       <c r="O37" t="n">
-        <v>1.161576507688255</v>
+        <v>1.170380854998263</v>
       </c>
       <c r="P37" t="n">
         <v>-0.0188053182534636</v>
@@ -5666,13 +5666,13 @@
         <v>-0.2587766965285807</v>
       </c>
       <c r="M38" t="n">
-        <v>8659172</v>
+        <v>10066900</v>
       </c>
       <c r="N38" t="n">
-        <v>12564603.44</v>
+        <v>12592758</v>
       </c>
       <c r="O38" t="n">
-        <v>0.6891719298066442</v>
+        <v>0.7994197935035359</v>
       </c>
       <c r="P38" t="n">
         <v>-0.0231319813452317</v>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>3.724300112043108</v>
+        <v>3.72428594316755</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0812988430560169</v>
+        <v>0.0812985337594631</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5734,13 +5734,13 @@
         <v>-0.1157084245752973</v>
       </c>
       <c r="M39" t="n">
-        <v>46232455</v>
+        <v>48444300</v>
       </c>
       <c r="N39" t="n">
-        <v>37056707.1</v>
+        <v>37100944</v>
       </c>
       <c r="O39" t="n">
-        <v>1.247613687725642</v>
+        <v>1.305743056025744</v>
       </c>
       <c r="P39" t="n">
         <v>-0.0233160405739019</v>
@@ -5802,13 +5802,13 @@
         <v>0.0674839355125665</v>
       </c>
       <c r="M40" t="n">
-        <v>29192847</v>
+        <v>29879000</v>
       </c>
       <c r="N40" t="n">
-        <v>28635716.94</v>
+        <v>28649440</v>
       </c>
       <c r="O40" t="n">
-        <v>1.01945577479926</v>
+        <v>1.042917418281125</v>
       </c>
       <c r="P40" t="n">
         <v>-0.0045180321648213</v>
@@ -5819,10 +5819,10 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>0.4056714943477085</v>
+        <v>0.4056429181780134</v>
       </c>
       <c r="S40" t="n">
-        <v>0.0625071662025367</v>
+        <v>0.0625027630945702</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -2927,7 +2927,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2964,7 +2964,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56.32</v>
+        <v>113.88</v>
       </c>
       <c r="B2" t="n">
         <v>75.70999999999999</v>
@@ -2979,7 +2979,7 @@
         <v>0.36845</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.753169999999994</v>
+        <v>55.80683</v>
       </c>
     </row>
   </sheetData>
@@ -2993,15 +2993,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3043,9 +3043,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56.32</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>99.81999999999999</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.564204</v>
+      </c>
       <c r="D2" t="n">
         <v>56.32</v>
       </c>
@@ -3056,7 +3058,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Current workbook deposit row</t>
+          <t>First deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.578559</v>
+      </c>
+      <c r="D3" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sharesies</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Second deposit</t>
         </is>
       </c>
     </row>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -452,7 +452,7 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -547,10 +547,10 @@
         <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>6.215999984741211</v>
+        <v>6.363571711948939</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>9.712499976158142</v>
+        <v>10.58285651888166</v>
       </c>
     </row>
   </sheetData>
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:T40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -582,6 +582,11 @@
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="28" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -652,12 +657,37 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>atr</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>stop_loss</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>trim_price</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>buy_amount_usd</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>shares_to_buy</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>decision_reasons</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>warnings</t>
         </is>
       </c>
     </row>
@@ -710,11 +740,26 @@
         <v>1.773262942271622</v>
       </c>
       <c r="N2" t="n">
-        <v>144.9199951171875</v>
+        <v>10.84078325544085</v>
       </c>
       <c r="O2" t="n">
-        <v>226.4374923706055</v>
-      </c>
+        <v>159.4684273856027</v>
+      </c>
+      <c r="P2" t="n">
+        <v>224.5131269182478</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0514785958588289</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -765,11 +810,26 @@
         <v>-3.577422784539042</v>
       </c>
       <c r="N3" t="n">
-        <v>491.6388134765625</v>
+        <v>38.40929303850447</v>
       </c>
       <c r="O3" t="n">
-        <v>614.548516845703</v>
-      </c>
+        <v>476.7760750906808</v>
+      </c>
+      <c r="P3" t="n">
+        <v>649.6178937639509</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0193726832181142</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -820,11 +880,26 @@
         <v>-0.0949479297406228</v>
       </c>
       <c r="N4" t="n">
-        <v>6.480000305175782</v>
+        <v>0.7777856077466693</v>
       </c>
       <c r="O4" t="n">
-        <v>10.12500047683716</v>
-      </c>
+        <v>6.544429165976388</v>
+      </c>
+      <c r="P4" t="n">
+        <v>11.2111428124564</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.7175091624757438</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -875,11 +950,26 @@
         <v>-3.468572913063639</v>
       </c>
       <c r="N5" t="n">
-        <v>1087.320395507812</v>
+        <v>41.62001255580357</v>
       </c>
       <c r="O5" t="n">
-        <v>1359.150494384766</v>
-      </c>
+        <v>1119.439976283482</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1306.730032784599</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.0118047734163998</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -901,11 +991,11 @@
         <v>16.19000053405762</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BUY SMALL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -930,11 +1020,26 @@
         <v>0.2137816411175577</v>
       </c>
       <c r="N6" t="n">
-        <v>12.95200042724609</v>
+        <v>1.69085727419172</v>
       </c>
       <c r="O6" t="n">
-        <v>20.23750066757202</v>
-      </c>
+        <v>12.80828598567418</v>
+      </c>
+      <c r="P6" t="n">
+        <v>22.9534296308245</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3300505066382809</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -956,11 +1061,11 @@
         <v>13.56999969482422</v>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BUY SMALL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -985,11 +1090,26 @@
         <v>0.042571941463545</v>
       </c>
       <c r="N7" t="n">
-        <v>10.85599975585938</v>
+        <v>0.597428526197161</v>
       </c>
       <c r="O7" t="n">
-        <v>16.96249961853028</v>
-      </c>
+        <v>12.3751426424299</v>
+      </c>
+      <c r="P7" t="n">
+        <v>15.95971379961287</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.9341172634529142</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1011,11 +1131,11 @@
         <v>260.239990234375</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BUY SMALL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1040,11 +1160,26 @@
         <v>0.3955764881293149</v>
       </c>
       <c r="N8" t="n">
-        <v>239.420791015625</v>
+        <v>13.0087160382952</v>
       </c>
       <c r="O8" t="n">
-        <v>299.2759887695312</v>
-      </c>
+        <v>240.7269161769322</v>
+      </c>
+      <c r="P8" t="n">
+        <v>299.2661383492606</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.0536109284642799</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1095,11 +1230,26 @@
         <v>0.0646032293833483</v>
       </c>
       <c r="N9" t="n">
-        <v>5.143999862670899</v>
+        <v>0.6494998591286796</v>
       </c>
       <c r="O9" t="n">
-        <v>8.037499785423279</v>
-      </c>
+        <v>5.131000110081263</v>
+      </c>
+      <c r="P9" t="n">
+        <v>9.027999264853342</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.4296138730104287</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1150,11 +1300,26 @@
         <v>3.038872772970159</v>
       </c>
       <c r="N10" t="n">
-        <v>353.3259887695313</v>
+        <v>15.15999494280134</v>
       </c>
       <c r="O10" t="n">
-        <v>441.6574859619141</v>
-      </c>
+        <v>361.3099953787668</v>
+      </c>
+      <c r="P10" t="n">
+        <v>429.5299726213728</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Above 200 SMA; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1205,11 +1370,26 @@
         <v>1.206196025562167</v>
       </c>
       <c r="N11" t="n">
-        <v>187.2475988769532</v>
+        <v>6.922855922154018</v>
       </c>
       <c r="O11" t="n">
-        <v>234.0594985961914</v>
-      </c>
+        <v>193.1457148960658</v>
+      </c>
+      <c r="P11" t="n">
+        <v>224.2985665457589</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Above 200 SMA; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1260,11 +1440,26 @@
         <v>0.5974640052565006</v>
       </c>
       <c r="N12" t="n">
-        <v>324.309208984375</v>
+        <v>10.05857195172991</v>
       </c>
       <c r="O12" t="n">
-        <v>405.3865112304687</v>
-      </c>
+        <v>337.4221518380301</v>
+      </c>
+      <c r="P12" t="n">
+        <v>382.6857256208148</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Above 200 SMA; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1315,30 +1510,45 @@
         <v>0.0328078631428616</v>
       </c>
       <c r="N13" t="n">
-        <v>14.50399932861328</v>
+        <v>0.9592857360839844</v>
       </c>
       <c r="O13" t="n">
-        <v>22.66249895095825</v>
-      </c>
+        <v>16.21142768859863</v>
+      </c>
+      <c r="P13" t="n">
+        <v>21.96714210510254</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Positive 1M return; Positive 3M return; MACD improving; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Internet/E-Commerce</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>247.3099975585937</v>
+        <v>236.8800048828125</v>
       </c>
       <c r="E14" t="n">
         <v>67</v>
@@ -1349,32 +1559,47 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H14" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I14" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J14" t="n">
-        <v>67.81157428603623</v>
+        <v>35.03556650730233</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0026901592563831</v>
+        <v>-0.0359595173016396</v>
       </c>
       <c r="L14" t="n">
-        <v>0.685952527362262</v>
+        <v>0.7716095474188931</v>
       </c>
       <c r="M14" t="n">
-        <v>1.780135958077288</v>
+        <v>-4.078359216969876</v>
       </c>
       <c r="N14" t="n">
-        <v>227.5251977539062</v>
+        <v>28.31142861502511</v>
       </c>
       <c r="O14" t="n">
-        <v>284.4064971923827</v>
-      </c>
+        <v>180.2571476527623</v>
+      </c>
+      <c r="P14" t="n">
+        <v>350.1257193429129</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 3M return; Positive 6M return</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1396,7 +1621,7 @@
         <v>362.0499877929688</v>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1425,33 +1650,48 @@
         <v>-10.00415359792669</v>
       </c>
       <c r="N15" t="n">
-        <v>289.639990234375</v>
+        <v>47.61507088797433</v>
       </c>
       <c r="O15" t="n">
-        <v>452.562484741211</v>
-      </c>
+        <v>266.8198460170201</v>
+      </c>
+      <c r="P15" t="n">
+        <v>552.5102713448662</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 3M return; Positive 6M return</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Internet/E-Commerce</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>937</v>
+        <v>247.3099975585937</v>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1459,37 +1699,52 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H16" t="n">
+        <v>60</v>
+      </c>
+      <c r="I16" t="n">
         <v>75</v>
       </c>
-      <c r="I16" t="n">
-        <v>50</v>
-      </c>
       <c r="J16" t="n">
-        <v>32.2591555067534</v>
+        <v>67.81157428603623</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0513632068007362</v>
+        <v>-0.0026901592563831</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6484706647892666</v>
+        <v>0.685952527362262</v>
       </c>
       <c r="M16" t="n">
-        <v>-28.83193491040208</v>
+        <v>1.780135958077288</v>
       </c>
       <c r="N16" t="n">
-        <v>749.6</v>
+        <v>7.574996948242188</v>
       </c>
       <c r="O16" t="n">
-        <v>1171.25</v>
-      </c>
+        <v>235.9475021362304</v>
+      </c>
+      <c r="P16" t="n">
+        <v>270.0349884033203</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Above 200 SMA; Positive 1M return; Positive 3M return; MACD improving; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,14 +1754,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>236.8800048828125</v>
+        <v>421.5799865722656</v>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1514,32 +1769,47 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H17" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
         <v>50</v>
       </c>
       <c r="J17" t="n">
-        <v>35.03556650730233</v>
+        <v>37.838400646266</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0359595173016396</v>
+        <v>-0.0006679828548723</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7716095474188931</v>
+        <v>1.038906674058124</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.078359216969876</v>
+        <v>-3.711786865119478</v>
       </c>
       <c r="N17" t="n">
-        <v>189.50400390625</v>
+        <v>21.50642830984933</v>
       </c>
       <c r="O17" t="n">
-        <v>296.1000061035156</v>
-      </c>
+        <v>389.3203441074916</v>
+      </c>
+      <c r="P17" t="n">
+        <v>486.0992715018136</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1561,7 +1831,7 @@
         <v>305.8699951171875</v>
       </c>
       <c r="E18" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1590,16 +1860,31 @@
         <v>-0.1480541656201379</v>
       </c>
       <c r="N18" t="n">
-        <v>281.4003955078125</v>
+        <v>23.01642935616629</v>
       </c>
       <c r="O18" t="n">
-        <v>351.7504943847656</v>
-      </c>
+        <v>271.3453510829381</v>
+      </c>
+      <c r="P18" t="n">
+        <v>374.9192831856864</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1609,14 +1894,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>421.5799865722656</v>
+        <v>937</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1624,31 +1909,50 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I19" t="n">
         <v>50</v>
       </c>
       <c r="J19" t="n">
-        <v>37.838400646266</v>
+        <v>32.2591555067534</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0006679828548723</v>
+        <v>-0.0513632068007362</v>
       </c>
       <c r="L19" t="n">
-        <v>1.038906674058124</v>
+        <v>0.6484706647892666</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.711786865119478</v>
+        <v>-28.83193491040208</v>
       </c>
       <c r="N19" t="n">
-        <v>387.8535876464844</v>
+        <v>97.98501586914062</v>
       </c>
       <c r="O19" t="n">
-        <v>484.8169845581055</v>
+        <v>741.0299682617188</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1328.940063476562</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 3M return; Positive 6M return</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>RSI weak</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1700,11 +2004,26 @@
         <v>5.61249043240821</v>
       </c>
       <c r="N20" t="n">
-        <v>254.9596044921875</v>
+        <v>12.01285443987165</v>
       </c>
       <c r="O20" t="n">
-        <v>318.6995056152344</v>
-      </c>
+        <v>259.110723223005</v>
+      </c>
+      <c r="P20" t="n">
+        <v>313.1685682024274</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Above 200 SMA; Positive 6M return; MACD improving; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1755,11 +2074,26 @@
         <v>1.911196160245703</v>
       </c>
       <c r="N21" t="n">
-        <v>83.03200073242188</v>
+        <v>6.056072235107422</v>
       </c>
       <c r="O21" t="n">
-        <v>129.7375011444092</v>
-      </c>
+        <v>91.6778564453125</v>
+      </c>
+      <c r="P21" t="n">
+        <v>128.014289855957</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Above 200 SMA; Positive 1M return; MACD improving; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1781,7 +2115,7 @@
         <v>298.989990234375</v>
       </c>
       <c r="E22" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1810,10 +2144,29 @@
         <v>-9.368367243321137</v>
       </c>
       <c r="N22" t="n">
-        <v>239.1919921875</v>
+        <v>30.13700212751116</v>
       </c>
       <c r="O22" t="n">
-        <v>373.7374877929688</v>
+        <v>238.7159859793527</v>
+      </c>
+      <c r="P22" t="n">
+        <v>419.5379987444196</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Above 200 SMA; Positive 3M return; Positive 6M return</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>RSI weak</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1836,7 +2189,7 @@
         <v>217.5299987792969</v>
       </c>
       <c r="E23" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1865,10 +2218,29 @@
         <v>-9.60956168128553</v>
       </c>
       <c r="N23" t="n">
-        <v>200.1275988769532</v>
+        <v>22.82714407784598</v>
       </c>
       <c r="O23" t="n">
-        <v>250.1594985961914</v>
+        <v>183.2892826625279</v>
+      </c>
+      <c r="P23" t="n">
+        <v>286.0114310128348</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Above 200 SMA; Positive 3M return; Positive 6M return</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>RSI weak</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1891,7 +2263,7 @@
         <v>103.120002746582</v>
       </c>
       <c r="E24" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1920,10 +2292,29 @@
         <v>-3.642499733942029</v>
       </c>
       <c r="N24" t="n">
-        <v>94.87040252685549</v>
+        <v>10.03500039236886</v>
       </c>
       <c r="O24" t="n">
-        <v>118.5880031585694</v>
+        <v>88.06750215802876</v>
+      </c>
+      <c r="P24" t="n">
+        <v>133.2250039236886</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Above 200 SMA; Positive 3M return; Positive 6M return</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>RSI weak</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1946,7 +2337,7 @@
         <v>860.6599731445312</v>
       </c>
       <c r="E25" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1975,10 +2366,29 @@
         <v>-17.58862389405815</v>
       </c>
       <c r="N25" t="n">
-        <v>791.8071752929687</v>
+        <v>88.97071620396206</v>
       </c>
       <c r="O25" t="n">
-        <v>989.7589691162108</v>
+        <v>727.2038988385882</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1127.572121756417</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Above 200 SMA; Positive 3M return; Positive 6M return</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>RSI weak</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -2001,7 +2411,7 @@
         <v>210.509994506836</v>
       </c>
       <c r="E26" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2030,33 +2440,52 @@
         <v>-6.66147091221397</v>
       </c>
       <c r="N26" t="n">
-        <v>168.4079956054688</v>
+        <v>26.59443010602678</v>
       </c>
       <c r="O26" t="n">
-        <v>263.137493133545</v>
+        <v>157.3211342947824</v>
+      </c>
+      <c r="P26" t="n">
+        <v>316.8877149309432</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Above 200 SMA; Positive 3M return; Positive 6M return</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>RSI weak</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Electric Vehicles</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>25.95999908447266</v>
+        <v>394.760009765625</v>
       </c>
       <c r="E27" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2064,54 +2493,69 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I27" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J27" t="n">
-        <v>41.46933662967547</v>
+        <v>47.30190854550064</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.0034549003924671</v>
+        <v>-0.0077251921194358</v>
       </c>
       <c r="L27" t="n">
-        <v>0.4293128861127736</v>
+        <v>0.6680783600026209</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0149246408257801</v>
+        <v>0.3816312784934397</v>
       </c>
       <c r="N27" t="n">
-        <v>20.76799926757813</v>
+        <v>19.89071219308036</v>
       </c>
       <c r="O27" t="n">
-        <v>32.44999885559082</v>
-      </c>
+        <v>364.9239414760045</v>
+      </c>
+      <c r="P27" t="n">
+        <v>454.4321463448661</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Positive 3M return; MACD improving; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Electric Vehicles</t>
+          <t>Space</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>394.760009765625</v>
+        <v>25.95999908447266</v>
       </c>
       <c r="E28" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2119,32 +2563,47 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H28" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I28" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J28" t="n">
-        <v>47.30190854550064</v>
+        <v>41.46933662967547</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.0077251921194358</v>
+        <v>-0.0034549003924671</v>
       </c>
       <c r="L28" t="n">
-        <v>0.6680783600026209</v>
+        <v>0.4293128861127736</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3816312784934397</v>
+        <v>-0.0149246408257801</v>
       </c>
       <c r="N28" t="n">
-        <v>363.179208984375</v>
+        <v>2.413428579057966</v>
       </c>
       <c r="O28" t="n">
-        <v>453.9740112304687</v>
-      </c>
+        <v>21.13314192635672</v>
+      </c>
+      <c r="P28" t="n">
+        <v>35.61371340070452</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Above 200 SMA; Positive 6M return</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2195,21 +2654,36 @@
         <v>-0.0068890358413925</v>
       </c>
       <c r="N29" t="n">
-        <v>6.215999984741211</v>
+        <v>0.703214134488787</v>
       </c>
       <c r="O29" t="n">
-        <v>9.712499976158142</v>
-      </c>
+        <v>6.363571711948939</v>
+      </c>
+      <c r="P29" t="n">
+        <v>10.58285651888166</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Volume surge; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AI Software</t>
+          <t>AI Infrastructure</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2218,10 +2692,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6.489999771118164</v>
+        <v>27.65999984741211</v>
       </c>
       <c r="E30" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2232,39 +2706,58 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I30" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J30" t="n">
-        <v>42.1686670849046</v>
+        <v>22.68907596697776</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.0045180321648213</v>
+        <v>-0.0236665520640497</v>
       </c>
       <c r="L30" t="n">
-        <v>1.042917418281125</v>
+        <v>0.4081000325851083</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0561779742976243</v>
+        <v>-0.1129581202809464</v>
       </c>
       <c r="N30" t="n">
-        <v>5.191999816894532</v>
+        <v>1.90642820085798</v>
       </c>
       <c r="O30" t="n">
-        <v>8.112499713897705</v>
+        <v>23.84714344569615</v>
+      </c>
+      <c r="P30" t="n">
+        <v>35.28571265084403</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Positive 3M return</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>RSI weak</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Quantum Computing</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>76.73000335693359</v>
+        <v>38.88000106811523</v>
       </c>
       <c r="E31" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2293,33 +2786,52 @@
         <v>50</v>
       </c>
       <c r="J31" t="n">
-        <v>32.22155183233293</v>
+        <v>15.99020298115008</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.0141905418668198</v>
+        <v>-0.0184321256247612</v>
       </c>
       <c r="L31" t="n">
-        <v>0.6604898529491945</v>
+        <v>0.8152458403022232</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.60128212643402</v>
+        <v>-1.449196603544823</v>
       </c>
       <c r="N31" t="n">
-        <v>61.38400268554688</v>
+        <v>3.97057124546596</v>
       </c>
       <c r="O31" t="n">
-        <v>95.91250419616701</v>
+        <v>30.93885857718331</v>
+      </c>
+      <c r="P31" t="n">
+        <v>54.76228604997908</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Positive 3M return</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>RSI weak</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Quantum Computing</t>
+          <t>Space</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2328,10 +2840,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>38.88000106811523</v>
+        <v>76.73000335693359</v>
       </c>
       <c r="E32" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2348,33 +2860,52 @@
         <v>50</v>
       </c>
       <c r="J32" t="n">
-        <v>15.99020298115008</v>
+        <v>32.22155183233293</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.0184321256247612</v>
+        <v>-0.0141905418668198</v>
       </c>
       <c r="L32" t="n">
-        <v>0.8152458403022232</v>
+        <v>0.6604898529491945</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.449196603544823</v>
+        <v>-1.60128212643402</v>
       </c>
       <c r="N32" t="n">
-        <v>31.10400085449219</v>
+        <v>7.806785583496094</v>
       </c>
       <c r="O32" t="n">
-        <v>48.60000133514404</v>
+        <v>61.11643218994141</v>
+      </c>
+      <c r="P32" t="n">
+        <v>107.957145690918</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Positive 3M return</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>RSI weak</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AI Infrastructure</t>
+          <t>AI Software</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2383,10 +2914,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>27.65999984741211</v>
+        <v>6.489999771118164</v>
       </c>
       <c r="E33" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2397,51 +2928,66 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J33" t="n">
-        <v>22.68907596697776</v>
+        <v>42.1686670849046</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.0236665520640497</v>
+        <v>-0.0045180321648213</v>
       </c>
       <c r="L33" t="n">
-        <v>0.4081000325851083</v>
+        <v>1.042917418281125</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1129581202809464</v>
+        <v>0.0561779742976243</v>
       </c>
       <c r="N33" t="n">
-        <v>22.12799987792969</v>
+        <v>0.4056429181780134</v>
       </c>
       <c r="O33" t="n">
-        <v>34.57499980926514</v>
-      </c>
+        <v>5.678713934762137</v>
+      </c>
+      <c r="P33" t="n">
+        <v>8.112571443830218</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>MACD improving</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ASTS</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Space/Telecom</t>
+          <t>Uranium/Nuclear Energy</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>67.58000183105469</v>
+        <v>90.1999969482422</v>
       </c>
       <c r="E34" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2455,48 +3001,67 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J34" t="n">
-        <v>44.76385902437732</v>
+        <v>18.63144679070228</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.0180032692351115</v>
+        <v>-0.0165641876578346</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5578530772922595</v>
+        <v>1.909541795756696</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7205249641778009</v>
+        <v>-0.7934742332941171</v>
       </c>
       <c r="N34" t="n">
-        <v>54.06400146484376</v>
+        <v>4.847142355782645</v>
       </c>
       <c r="O34" t="n">
-        <v>84.47500228881836</v>
+        <v>82.92928341456823</v>
+      </c>
+      <c r="P34" t="n">
+        <v>104.7414240155901</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Volume surge</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>RSI weak</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Uranium/Nuclear Energy</t>
+          <t>Space/Telecom</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>90.1999969482422</v>
+        <v>67.58000183105469</v>
       </c>
       <c r="E35" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2510,45 +3075,56 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J35" t="n">
-        <v>18.63144679070228</v>
+        <v>44.76385902437732</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.0165641876578346</v>
+        <v>-0.0180032692351115</v>
       </c>
       <c r="L35" t="n">
-        <v>1.909541795756696</v>
+        <v>0.5578530772922595</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7934742332941171</v>
+        <v>-0.7205249641778009</v>
       </c>
       <c r="N35" t="n">
-        <v>82.98399719238283</v>
+        <v>7.066000257219587</v>
       </c>
       <c r="O35" t="n">
-        <v>103.7299964904785</v>
-      </c>
+        <v>53.44800131661552</v>
+      </c>
+      <c r="P35" t="n">
+        <v>95.84400285993304</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LUNR</t>
+          <t>SKHY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>High Yield ETF</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15.14999961853027</v>
+        <v>153.5099945068359</v>
       </c>
       <c r="E36" t="n">
         <v>22</v>
@@ -2567,46 +3143,55 @@
       <c r="I36" t="n">
         <v>50</v>
       </c>
-      <c r="J36" t="n">
-        <v>22.01308672444488</v>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
-        <v>-0.0085500982745466</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.7169100399332081</v>
-      </c>
+        <v>-0.0916016897377034</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
-        <v>-0.2400474448421516</v>
-      </c>
-      <c r="N36" t="n">
-        <v>12.11999969482422</v>
-      </c>
+        <v>-0.9253561253561428</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
-        <v>18.93749952316284</v>
+        <v>141.2291949462891</v>
+      </c>
+      <c r="P36" t="n">
+        <v>178.0715936279297</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Missing volume trend; Missing ATR; Missing RSI</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SKHY</t>
+          <t>LUNR</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>High Yield ETF</t>
+          <t>Space</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>153.5099945068359</v>
+        <v>15.14999961853027</v>
       </c>
       <c r="E37" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2622,19 +3207,38 @@
       <c r="I37" t="n">
         <v>50</v>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>22.01308672444488</v>
+      </c>
       <c r="K37" t="n">
-        <v>-0.0916016897377034</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
+        <v>-0.0085500982745466</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.7169100399332081</v>
+      </c>
       <c r="M37" t="n">
-        <v>-0.9253561253561428</v>
+        <v>-0.2400474448421516</v>
       </c>
       <c r="N37" t="n">
-        <v>141.2291949462891</v>
+        <v>1.668785776410784</v>
       </c>
       <c r="O37" t="n">
-        <v>176.5364936828613</v>
+        <v>11.8124280657087</v>
+      </c>
+      <c r="P37" t="n">
+        <v>21.82514272417341</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>RSI weak</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -2657,7 +3261,7 @@
         <v>8.350000381469727</v>
       </c>
       <c r="E38" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2686,10 +3290,25 @@
         <v>-0.1257283657885731</v>
       </c>
       <c r="N38" t="n">
-        <v>6.680000305175781</v>
+        <v>0.7357140268598285</v>
       </c>
       <c r="O38" t="n">
-        <v>10.43750047683716</v>
+        <v>6.87857232775007</v>
+      </c>
+      <c r="P38" t="n">
+        <v>11.29285648890904</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>RSI weak</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -2712,7 +3331,7 @@
         <v>45.81000137329102</v>
       </c>
       <c r="E39" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2741,10 +3360,25 @@
         <v>-0.3462640816307631</v>
       </c>
       <c r="N39" t="n">
-        <v>36.64800109863281</v>
+        <v>3.72428594316755</v>
       </c>
       <c r="O39" t="n">
-        <v>57.26250171661377</v>
+        <v>38.36142948695591</v>
+      </c>
+      <c r="P39" t="n">
+        <v>60.70714514596122</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>RSI weak</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -2767,7 +3401,7 @@
         <v>7.480000019073486</v>
       </c>
       <c r="E40" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2796,10 +3430,25 @@
         <v>-0.1257187896488844</v>
       </c>
       <c r="N40" t="n">
-        <v>5.98400001525879</v>
+        <v>0.5634285722460065</v>
       </c>
       <c r="O40" t="n">
-        <v>9.350000023841858</v>
+        <v>6.353142874581473</v>
+      </c>
+      <c r="P40" t="n">
+        <v>9.733714308057513</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>RSI weak</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3001,7 +3650,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3084,7 +3733,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Second deposit</t>
+          <t>Second deposit test</t>
         </is>
       </c>
     </row>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -38,7 +38,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,21 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -68,12 +83,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -585,8 +614,8 @@
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
+    <col width="35" customWidth="1" min="19" max="19"/>
+    <col width="35" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -692,2760 +721,2760 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>ANET</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Networking</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>181.1499938964844</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="3" t="n">
         <v>53.54415317550977</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="3" t="n">
         <v>-0.0037174117418728</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>0.8789262943053163</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="3" t="n">
         <v>1.773262942271622</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="3" t="n">
         <v>10.84078325544085</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="3" t="n">
         <v>159.4684273856027</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="3" t="n">
         <v>224.5131269182478</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="3" t="n">
         <v>9.33</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="3" t="n">
         <v>0.0514785958588289</v>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>534.3900146484375</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="3" t="n">
         <v>47.25110136960278</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="3" t="n">
         <v>-0.0365484488215595</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>0.665160990480149</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="3" t="n">
         <v>-3.577422784539042</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="3" t="n">
         <v>38.40929303850447</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="3" t="n">
         <v>476.7760750906808</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="3" t="n">
         <v>649.6178937639509</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="3" t="n">
         <v>10.35</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="3" t="n">
         <v>0.0193726832181142</v>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>BFLY</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>8.100000381469727</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="3" t="n">
         <v>58.05825616673116</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="3" t="n">
         <v>-0.0137844778510634</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>1.006301320925231</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="3" t="n">
         <v>-0.0949479297406228</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="3" t="n">
         <v>0.7777856077466693</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="3" t="n">
         <v>6.544429165976388</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="3" t="n">
         <v>11.2111428124564</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="3" t="n">
         <v>5.81</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R4" s="3" t="n">
         <v>0.7175091624757438</v>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>LLY</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Healthcare/Pharma</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>1181.869995117188</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="3" t="n">
         <v>63.59330391902413</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="3" t="n">
         <v>-0.0071261261474068</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>0.6225647695355339</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="3" t="n">
         <v>-3.468572913063639</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="3" t="n">
         <v>41.62001255580357</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="3" t="n">
         <v>1119.439976283482</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="3" t="n">
         <v>1306.730032784599</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="3" t="n">
         <v>13.95</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5" s="3" t="n">
         <v>0.0118047734163998</v>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>BLZE</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Gaming/Digital Media</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>16.19000053405762</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="3" t="n">
         <v>79.95545838351569</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="3" t="n">
         <v>0.0056818397330839</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>0.586453269151991</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="3" t="n">
         <v>0.2137816411175577</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="3" t="n">
         <v>1.69085727419172</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="3" t="n">
         <v>12.80828598567418</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="3" t="n">
         <v>22.9534296308245</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="3" t="n">
         <v>5.34</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R6" s="3" t="n">
         <v>0.3300505066382809</v>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>PUBM</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>AdTech</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>13.56999969482422</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="3" t="n">
         <v>75.50561349871404</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="3" t="n">
         <v>0.0007380242613335</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>0.4649229581688092</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="3" t="n">
         <v>0.042571941463545</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="3" t="n">
         <v>0.597428526197161</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" s="3" t="n">
         <v>12.3751426424299</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="3" t="n">
         <v>15.95971379961287</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="3" t="n">
         <v>12.68</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R7" s="3" t="n">
         <v>0.9341172634529142</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>DDOG</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Cloud Software</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>260.239990234375</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="3" t="n">
         <v>72.85664449359034</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="3" t="n">
         <v>-0.0032228665927801</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>0.6833935101223232</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="3" t="n">
         <v>0.3955764881293149</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="3" t="n">
         <v>13.0087160382952</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="3" t="n">
         <v>240.7269161769322</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8" s="3" t="n">
         <v>299.2661383492606</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8" s="3" t="n">
         <v>13.95</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R8" s="3" t="n">
         <v>0.0536109284642799</v>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>STTK</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="2" t="n">
         <v>6.429999828338623</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="2" t="n">
         <v>78</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>BUY SMALL</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="2" t="n">
         <v>64.1330123763551</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="2" t="n">
         <v>-0.0015059867839982</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="2" t="n">
         <v>0.7110421535831287</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="2" t="n">
         <v>0.0646032293833483</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="2" t="n">
         <v>0.6494998591286796</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="2" t="n">
         <v>5.131000110081263</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" s="2" t="n">
         <v>9.027999264853342</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="2" t="n">
         <v>2.76</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R9" s="2" t="n">
         <v>0.4296138730104287</v>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="4" t="n">
         <v>384.0499877929688</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="4" t="n">
         <v>46.76644111895504</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="4" t="n">
         <v>-0.0162261925008566</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="4" t="n">
         <v>0.7676989816870774</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="4" t="n">
         <v>3.038872772970159</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="4" t="n">
         <v>15.15999494280134</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="4" t="n">
         <v>361.3099953787668</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10" s="4" t="n">
         <v>429.5299726213728</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Q10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
         <is>
           <t>Above 200 SMA; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="4" t="n">
         <v>203.5299987792969</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="4" t="n">
         <v>45.3606417209306</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="4" t="n">
         <v>-0.0114714322654375</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="4" t="n">
         <v>0.7517100898302004</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="4" t="n">
         <v>1.206196025562167</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="4" t="n">
         <v>6.922855922154018</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="4" t="n">
         <v>193.1457148960658</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" s="4" t="n">
         <v>224.2985665457589</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr">
+      <c r="Q11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
         <is>
           <t>Above 200 SMA; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Internet/Software</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>352.510009765625</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="4" t="n">
         <v>52.39629178665267</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="4" t="n">
         <v>-0.0027716844579075</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="4" t="n">
         <v>0.479416037711002</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="4" t="n">
         <v>0.5974640052565006</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="4" t="n">
         <v>10.05857195172991</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12" s="4" t="n">
         <v>337.4221518380301</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12" s="4" t="n">
         <v>382.6857256208148</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
+      <c r="Q12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
         <is>
           <t>Above 200 SMA; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
+      <c r="T12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SOFI</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Fintech</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="4" t="n">
         <v>18.1299991607666</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="4" t="n">
         <v>60.23854340937944</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="4" t="n">
         <v>0.0114483570142134</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="4" t="n">
         <v>1.264046667351417</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="4" t="n">
         <v>0.0328078631428616</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="4" t="n">
         <v>0.9592857360839844</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13" s="4" t="n">
         <v>16.21142768859863</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13" s="4" t="n">
         <v>21.96714210510254</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
+      <c r="Q13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
         <is>
           <t>Above 50 SMA; Positive 1M return; Positive 3M return; MACD improving; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
+      <c r="T13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>CRDO</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="4" t="n">
         <v>236.8800048828125</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="4" t="n">
         <v>35.03556650730233</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="4" t="n">
         <v>-0.0359595173016396</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="4" t="n">
         <v>0.7716095474188931</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="4" t="n">
         <v>-4.078359216969876</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="4" t="n">
         <v>28.31142861502511</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14" s="4" t="n">
         <v>180.2571476527623</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14" s="4" t="n">
         <v>350.1257193429129</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr">
+      <c r="Q14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
         <is>
           <t>Above 50 SMA; Above 200 SMA; Positive 3M return; Positive 6M return</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
+      <c r="T14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>ALAB</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="4" t="n">
         <v>362.0499877929688</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="4" t="n">
         <v>39.99174507130462</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="4" t="n">
         <v>-0.0229072122118197</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="4" t="n">
         <v>1.014159066720345</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="4" t="n">
         <v>-10.00415359792669</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="4" t="n">
         <v>47.61507088797433</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15" s="4" t="n">
         <v>266.8198460170201</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" s="4" t="n">
         <v>552.5102713448662</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr">
+      <c r="Q15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
         <is>
           <t>Above 50 SMA; Above 200 SMA; Positive 3M return; Positive 6M return</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
+      <c r="T15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Internet/E-Commerce</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="4" t="n">
         <v>247.3099975585937</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="4" t="n">
         <v>67.81157428603623</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="4" t="n">
         <v>-0.0026901592563831</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="4" t="n">
         <v>0.685952527362262</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="4" t="n">
         <v>1.780135958077288</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="4" t="n">
         <v>7.574996948242188</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16" s="4" t="n">
         <v>235.9475021362304</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P16" s="4" t="n">
         <v>270.0349884033203</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="inlineStr">
+      <c r="Q16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
         <is>
           <t>Above 200 SMA; Positive 1M return; Positive 3M return; MACD improving; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
+      <c r="T16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>TSM</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>421.5799865722656</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="4" t="n">
         <v>37.838400646266</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="4" t="n">
         <v>-0.0006679828548723</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="4" t="n">
         <v>1.038906674058124</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="4" t="n">
         <v>-3.711786865119478</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="4" t="n">
         <v>21.50642830984933</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17" s="4" t="n">
         <v>389.3203441074916</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17" s="4" t="n">
         <v>486.0992715018136</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="inlineStr">
+      <c r="Q17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
         <is>
           <t>Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
+      <c r="T17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>VRT</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Data Centers</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="4" t="n">
         <v>305.8699951171875</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="4" t="n">
         <v>37.27464274525995</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="4" t="n">
         <v>-0.0217022618956923</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="4" t="n">
         <v>0.5960186512249169</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="4" t="n">
         <v>-0.1480541656201379</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="4" t="n">
         <v>23.01642935616629</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18" s="4" t="n">
         <v>271.3453510829381</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18" s="4" t="n">
         <v>374.9192831856864</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="inlineStr">
+      <c r="Q18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
         <is>
           <t>Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
+      <c r="T18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="5" t="n">
         <v>937</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="5" t="n">
         <v>32.2591555067534</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="5" t="n">
         <v>-0.0513632068007362</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="5" t="n">
         <v>0.6484706647892666</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="5" t="n">
         <v>-28.83193491040208</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="5" t="n">
         <v>97.98501586914062</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19" s="5" t="n">
         <v>741.0299682617188</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P19" s="5" t="n">
         <v>1328.940063476562</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr">
+      <c r="Q19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="5" t="inlineStr">
         <is>
           <t>Above 50 SMA; Above 200 SMA; Positive 3M return; Positive 6M return</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T19" s="5" t="inlineStr">
         <is>
           <t>RSI weak</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>CBOE</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="4" t="n">
         <v>277.1300048828125</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="4" t="n">
         <v>63.08948813870285</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="4" t="n">
         <v>-0.0012683117417138</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="4" t="n">
         <v>0.9370039155890588</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="4" t="n">
         <v>5.61249043240821</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="4" t="n">
         <v>12.01285443987165</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20" s="4" t="n">
         <v>259.110723223005</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P20" s="4" t="n">
         <v>313.1685682024274</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="inlineStr">
+      <c r="Q20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
         <is>
           <t>Above 200 SMA; Positive 6M return; MACD improving; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
+      <c r="T20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>CELC</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Biotech</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="4" t="n">
         <v>103.7900009155273</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="4" t="n">
         <v>64.40748321374801</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="4" t="n">
         <v>-0.008180004348712199</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="4" t="n">
         <v>0.8319020612963752</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="4" t="n">
         <v>1.911196160245703</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="4" t="n">
         <v>6.056072235107422</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21" s="4" t="n">
         <v>91.6778564453125</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21" s="4" t="n">
         <v>128.014289855957</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="inlineStr">
+      <c r="Q21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
         <is>
           <t>Above 200 SMA; Positive 1M return; MACD improving; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
+      <c r="T21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>ARM</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="5" t="n">
         <v>298.989990234375</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="5" t="n">
         <v>25.12013387453341</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="5" t="n">
         <v>-0.0369832753978448</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="5" t="n">
         <v>0.4698277360705851</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="5" t="n">
         <v>-9.368367243321137</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="5" t="n">
         <v>30.13700212751116</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" s="5" t="n">
         <v>238.7159859793527</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22" s="5" t="n">
         <v>419.5379987444196</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="inlineStr">
+      <c r="Q22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5" t="inlineStr">
         <is>
           <t>Above 200 SMA; Positive 3M return; Positive 6M return</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T22" s="5" t="inlineStr">
         <is>
           <t>RSI weak</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>MRVL</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="5" t="n">
         <v>217.5299987792969</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="5" t="n">
         <v>26.81350318140036</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" s="5" t="n">
         <v>-0.0298121320218837</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="5" t="n">
         <v>0.560431924401771</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23" s="5" t="n">
         <v>-9.60956168128553</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" s="5" t="n">
         <v>22.82714407784598</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23" s="5" t="n">
         <v>183.2892826625279</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P23" s="5" t="n">
         <v>286.0114310128348</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="inlineStr">
+      <c r="Q23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="5" t="inlineStr">
         <is>
           <t>Above 200 SMA; Positive 3M return; Positive 6M return</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T23" s="5" t="inlineStr">
         <is>
           <t>RSI weak</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>INTC</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="5" t="n">
         <v>103.120002746582</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" s="5" t="n">
         <v>23.43354907791833</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24" s="5" t="n">
         <v>-0.0351419620325085</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="5" t="n">
         <v>0.7611815955726389</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24" s="5" t="n">
         <v>-3.642499733942029</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24" s="5" t="n">
         <v>10.03500039236886</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O24" s="5" t="n">
         <v>88.06750215802876</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P24" s="5" t="n">
         <v>133.2250039236886</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="inlineStr">
+      <c r="Q24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="5" t="inlineStr">
         <is>
           <t>Above 200 SMA; Positive 3M return; Positive 6M return</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T24" s="5" t="inlineStr">
         <is>
           <t>RSI weak</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>STX</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Data Storage</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="5" t="n">
         <v>860.6599731445312</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" s="5" t="n">
         <v>33.24526766433529</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25" s="5" t="n">
         <v>-0.0447525650500693</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="5" t="n">
         <v>0.9326165149712228</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25" s="5" t="n">
         <v>-17.58862389405815</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25" s="5" t="n">
         <v>88.97071620396206</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O25" s="5" t="n">
         <v>727.2038988385882</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P25" s="5" t="n">
         <v>1127.572121756417</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="inlineStr">
+      <c r="Q25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="5" t="inlineStr">
         <is>
           <t>Above 200 SMA; Positive 3M return; Positive 6M return</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T25" s="5" t="inlineStr">
         <is>
           <t>RSI weak</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>NBIS</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>AI Infrastructure</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="5" t="n">
         <v>210.509994506836</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" s="5" t="n">
         <v>31.19082085488327</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26" s="5" t="n">
         <v>-0.0316867363918898</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26" s="5" t="n">
         <v>0.5987661019638217</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26" s="5" t="n">
         <v>-6.66147091221397</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26" s="5" t="n">
         <v>26.59443010602678</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O26" s="5" t="n">
         <v>157.3211342947824</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P26" s="5" t="n">
         <v>316.8877149309432</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="inlineStr">
+      <c r="Q26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="5" t="inlineStr">
         <is>
           <t>Above 200 SMA; Positive 3M return; Positive 6M return</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T26" s="5" t="inlineStr">
         <is>
           <t>RSI weak</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Electric Vehicles</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="4" t="n">
         <v>394.760009765625</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
+      <c r="G27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" s="4" t="n">
         <v>47.30190854550064</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27" s="4" t="n">
         <v>-0.0077251921194358</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27" s="4" t="n">
         <v>0.6680783600026209</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" s="4" t="n">
         <v>0.3816312784934397</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27" s="4" t="n">
         <v>19.89071219308036</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O27" s="4" t="n">
         <v>364.9239414760045</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P27" s="4" t="n">
         <v>454.4321463448661</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="inlineStr">
+      <c r="Q27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="4" t="inlineStr">
         <is>
           <t>Positive 3M return; MACD improving; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
+      <c r="T27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Space</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="4" t="n">
         <v>25.95999908447266</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" s="4" t="n">
         <v>41.46933662967547</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K28" s="4" t="n">
         <v>-0.0034549003924671</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28" s="4" t="n">
         <v>0.4293128861127736</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28" s="4" t="n">
         <v>-0.0149246408257801</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N28" s="4" t="n">
         <v>2.413428579057966</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O28" s="4" t="n">
         <v>21.13314192635672</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P28" s="4" t="n">
         <v>35.61371340070452</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="inlineStr">
+      <c r="Q28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="4" t="inlineStr">
         <is>
           <t>Above 200 SMA; Positive 6M return</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
+      <c r="T28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>KYTX</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Biotech</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>7.769999980926514</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
+      <c r="G29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" s="4" t="n">
         <v>45.20795488517063</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29" s="4" t="n">
         <v>0.0017678661083915</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" s="4" t="n">
         <v>1.851830814176953</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29" s="4" t="n">
         <v>-0.0068890358413925</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29" s="4" t="n">
         <v>0.703214134488787</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O29" s="4" t="n">
         <v>6.363571711948939</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P29" s="4" t="n">
         <v>10.58285651888166</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="inlineStr">
+      <c r="Q29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="4" t="inlineStr">
         <is>
           <t>Volume surge; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
+      <c r="T29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>SMCI</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>AI Infrastructure</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="5" t="n">
         <v>27.65999984741211</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" s="5" t="n">
         <v>22.68907596697776</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30" s="5" t="n">
         <v>-0.0236665520640497</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30" s="5" t="n">
         <v>0.4081000325851083</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30" s="5" t="n">
         <v>-0.1129581202809464</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N30" s="5" t="n">
         <v>1.90642820085798</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O30" s="5" t="n">
         <v>23.84714344569615</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P30" s="5" t="n">
         <v>35.28571265084403</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="inlineStr">
+      <c r="Q30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="5" t="inlineStr">
         <is>
           <t>Positive 3M return</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T30" s="5" t="inlineStr">
         <is>
           <t>RSI weak</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>IONQ</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Quantum Computing</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="5" t="n">
         <v>38.88000106811523</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" s="5" t="n">
         <v>15.99020298115008</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31" s="5" t="n">
         <v>-0.0184321256247612</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31" s="5" t="n">
         <v>0.8152458403022232</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31" s="5" t="n">
         <v>-1.449196603544823</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N31" s="5" t="n">
         <v>3.97057124546596</v>
       </c>
-      <c r="O31" t="n">
+      <c r="O31" s="5" t="n">
         <v>30.93885857718331</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P31" s="5" t="n">
         <v>54.76228604997908</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="inlineStr">
+      <c r="Q31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="5" t="inlineStr">
         <is>
           <t>Positive 3M return</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T31" s="5" t="inlineStr">
         <is>
           <t>RSI weak</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>RKLB</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Space</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="5" t="n">
         <v>76.73000335693359</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" s="5" t="n">
         <v>32.22155183233293</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K32" s="5" t="n">
         <v>-0.0141905418668198</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L32" s="5" t="n">
         <v>0.6604898529491945</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M32" s="5" t="n">
         <v>-1.60128212643402</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N32" s="5" t="n">
         <v>7.806785583496094</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O32" s="5" t="n">
         <v>61.11643218994141</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P32" s="5" t="n">
         <v>107.957145690918</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="inlineStr">
+      <c r="Q32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="5" t="inlineStr">
         <is>
           <t>Positive 3M return</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T32" s="5" t="inlineStr">
         <is>
           <t>RSI weak</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>SOUN</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>AI Software</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>6.489999771118164</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
+      <c r="G33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" s="4" t="n">
         <v>42.1686670849046</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K33" s="4" t="n">
         <v>-0.0045180321648213</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33" s="4" t="n">
         <v>1.042917418281125</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M33" s="4" t="n">
         <v>0.0561779742976243</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N33" s="4" t="n">
         <v>0.4056429181780134</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O33" s="4" t="n">
         <v>5.678713934762137</v>
       </c>
-      <c r="P33" t="n">
+      <c r="P33" s="4" t="n">
         <v>8.112571443830218</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="inlineStr">
+      <c r="Q33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="4" t="inlineStr">
         <is>
           <t>MACD improving</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
+      <c r="T33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>CCJ</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Uranium/Nuclear Energy</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="5" t="n">
         <v>90.1999969482422</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" s="5" t="n">
         <v>18.63144679070228</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K34" s="5" t="n">
         <v>-0.0165641876578346</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L34" s="5" t="n">
         <v>1.909541795756696</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M34" s="5" t="n">
         <v>-0.7934742332941171</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N34" s="5" t="n">
         <v>4.847142355782645</v>
       </c>
-      <c r="O34" t="n">
+      <c r="O34" s="5" t="n">
         <v>82.92928341456823</v>
       </c>
-      <c r="P34" t="n">
+      <c r="P34" s="5" t="n">
         <v>104.7414240155901</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="inlineStr">
+      <c r="Q34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="5" t="inlineStr">
         <is>
           <t>Volume surge</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="T34" s="5" t="inlineStr">
         <is>
           <t>RSI weak</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>ASTS</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Space/Telecom</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>67.58000183105469</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
+      <c r="G35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" s="4" t="n">
         <v>44.76385902437732</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K35" s="4" t="n">
         <v>-0.0180032692351115</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35" s="4" t="n">
         <v>0.5578530772922595</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35" s="4" t="n">
         <v>-0.7205249641778009</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N35" s="4" t="n">
         <v>7.066000257219587</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O35" s="4" t="n">
         <v>53.44800131661552</v>
       </c>
-      <c r="P35" t="n">
+      <c r="P35" s="4" t="n">
         <v>95.84400285993304</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
+      <c r="Q35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="4" t="inlineStr"/>
+      <c r="T35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>SKHY</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>High Yield ETF</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="5" t="n">
         <v>153.5099945068359</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
+      <c r="G36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="n">
         <v>-0.0916016897377034</v>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="n">
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="n">
         <v>-0.9253561253561428</v>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="n">
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="n">
         <v>141.2291949462891</v>
       </c>
-      <c r="P36" t="n">
+      <c r="P36" s="5" t="n">
         <v>178.0715936279297</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr">
+      <c r="Q36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="5" t="inlineStr"/>
+      <c r="T36" s="5" t="inlineStr">
         <is>
           <t>Missing volume trend; Missing ATR; Missing RSI</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>LUNR</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Space</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="5" t="n">
         <v>15.14999961853027</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" s="5" t="n">
         <v>22.01308672444488</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K37" s="5" t="n">
         <v>-0.0085500982745466</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L37" s="5" t="n">
         <v>0.7169100399332081</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M37" s="5" t="n">
         <v>-0.2400474448421516</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N37" s="5" t="n">
         <v>1.668785776410784</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O37" s="5" t="n">
         <v>11.8124280657087</v>
       </c>
-      <c r="P37" t="n">
+      <c r="P37" s="5" t="n">
         <v>21.82514272417341</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr">
+      <c r="Q37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="5" t="inlineStr"/>
+      <c r="T37" s="5" t="inlineStr">
         <is>
           <t>RSI weak</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>SMR</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="5" t="n">
         <v>8.350000381469727</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
+      <c r="G38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" s="5" t="n">
         <v>14.49631933236232</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K38" s="5" t="n">
         <v>-0.0188053182534636</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L38" s="5" t="n">
         <v>1.170380854998263</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M38" s="5" t="n">
         <v>-0.1257283657885731</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N38" s="5" t="n">
         <v>0.7357140268598285</v>
       </c>
-      <c r="O38" t="n">
+      <c r="O38" s="5" t="n">
         <v>6.87857232775007</v>
       </c>
-      <c r="P38" t="n">
+      <c r="P38" s="5" t="n">
         <v>11.29285648890904</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr">
+      <c r="Q38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="5" t="inlineStr"/>
+      <c r="T38" s="5" t="inlineStr">
         <is>
           <t>RSI weak</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>OKLO</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="5" t="n">
         <v>45.81000137329102</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
+      <c r="G39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" s="5" t="n">
         <v>21.80922241156196</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K39" s="5" t="n">
         <v>-0.0231319813452317</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L39" s="5" t="n">
         <v>0.7994197935035359</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M39" s="5" t="n">
         <v>-0.3462640816307631</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N39" s="5" t="n">
         <v>3.72428594316755</v>
       </c>
-      <c r="O39" t="n">
+      <c r="O39" s="5" t="n">
         <v>38.36142948695591</v>
       </c>
-      <c r="P39" t="n">
+      <c r="P39" s="5" t="n">
         <v>60.70714514596122</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr">
+      <c r="Q39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="5" t="inlineStr"/>
+      <c r="T39" s="5" t="inlineStr">
         <is>
           <t>RSI weak</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>JOBY</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>eVTOL/Aviation</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="5" t="n">
         <v>7.480000019073486</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
+      <c r="G40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" s="5" t="n">
         <v>19.79695935229539</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K40" s="5" t="n">
         <v>-0.0233160405739019</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L40" s="5" t="n">
         <v>1.305743056025744</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M40" s="5" t="n">
         <v>-0.1257187896488844</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N40" s="5" t="n">
         <v>0.5634285722460065</v>
       </c>
-      <c r="O40" t="n">
+      <c r="O40" s="5" t="n">
         <v>6.353142874581473</v>
       </c>
-      <c r="P40" t="n">
+      <c r="P40" s="5" t="n">
         <v>9.733714308057513</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr">
+      <c r="Q40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="5" t="inlineStr"/>
+      <c r="T40" s="5" t="inlineStr">
         <is>
           <t>RSI weak</t>
         </is>
@@ -3494,66 +3523,66 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>BLZE</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="6" t="n">
         <v>0.74662492</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="6" t="n">
         <v>16.19000053405762</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="6" t="n">
         <v>12.08785785354073</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="6" t="n">
         <v>0.05285969</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="6" t="n">
         <v>352.510009765625</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="6" t="n">
         <v>18.63356983810791</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>SOFI</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="6" t="n">
         <v>0.6115135</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="6" t="n">
         <v>18.1299991607666</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>11.08673924179745</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="6" t="n">
         <v>0.02721351</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="6" t="n">
         <v>394.760009765625</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>10.74280547335693</v>
       </c>
     </row>
@@ -3612,22 +3641,22 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="6" t="n">
         <v>113.88</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="6" t="n">
         <v>75.70999999999999</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="6" t="n">
         <v>1.38472</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="6" t="n">
         <v>19.39</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="6" t="n">
         <v>0.36845</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="6" t="n">
         <v>55.80683</v>
       </c>
     </row>
@@ -3686,52 +3715,52 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="6" t="n">
         <v>99.81999999999999</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="6" t="n">
         <v>0.564204</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="6" t="n">
         <v>56.32</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Sharesies</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>First deposit</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="6" t="n">
         <v>99.5</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="6" t="n">
         <v>0.578559</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="6" t="n">
         <v>57.56</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Sharesies</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Second deposit test</t>
         </is>
@@ -3876,2632 +3905,2632 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>ALAB</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="6" t="n">
         <v>362.0499877929688</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="6" t="n">
         <v>328.4705993652344</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="6" t="n">
         <v>200.4233501052856</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="6" t="n">
         <v>39.99174507130462</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="6" t="n">
         <v>-0.0147495398528575</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="6" t="n">
         <v>1.170628566608762</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="6" t="n">
         <v>1.226492752192518</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="6" t="n">
         <v>18.87209311075537</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="6" t="n">
         <v>28.87624670868206</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="6" t="n">
         <v>-10.00415359792669</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="6" t="n">
         <v>-6.89888868607181</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="6" t="n">
         <v>6277600</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="6" t="n">
         <v>6189956</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="6" t="n">
         <v>1.014159066720345</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="6" t="n">
         <v>-0.0229072122118197</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="6" t="n">
         <v>47.61507088797433</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="6" t="n">
         <v>0.1315151843485272</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="6" t="n">
         <v>534.3900146484375</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="6" t="n">
         <v>485.8411999511719</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="6" t="n">
         <v>289.53119972229</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="6" t="n">
         <v>47.25110136960278</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="6" t="n">
         <v>0.0940526180638816</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="6" t="n">
         <v>1.165012399968324</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="6" t="n">
         <v>1.630260468891019</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="6" t="n">
         <v>17.03245671433649</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="6" t="n">
         <v>20.60987949887553</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="6" t="n">
         <v>-3.577422784539042</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="6" t="n">
         <v>-3.005596247274948</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="6" t="n">
         <v>22890700</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="6" t="n">
         <v>34413774</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="6" t="n">
         <v>0.665160990480149</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="6" t="n">
         <v>-0.0365484488215595</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>DOWN</t>
         </is>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="6" t="n">
         <v>38.40929303850447</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="6" t="n">
         <v>0.071875020089537</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="6" t="n">
         <v>247.3099975585937</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="6" t="n">
         <v>253.7199996948243</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>233.4662000274658</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="6" t="n">
         <v>67.81157428603623</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>0.0240155818959022</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="6" t="n">
         <v>0.030930835748985</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="6" t="n">
         <v>-0.0002829950797839</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="6" t="n">
         <v>-1.050456348260468</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="6" t="n">
         <v>-2.830592306337756</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="6" t="n">
         <v>1.780135958077288</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="6" t="n">
         <v>1.752601933393177</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="6" t="n">
         <v>34596500</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="6" t="n">
         <v>50435706</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="6" t="n">
         <v>0.685952527362262</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="6" t="n">
         <v>-0.0026901592563831</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R4" t="n">
+      <c r="R4" s="6" t="n">
         <v>7.574996948242188</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4" s="6" t="n">
         <v>0.0306295621811547</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T4" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>ANET</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="6" t="n">
         <v>181.1499938964844</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="6" t="n">
         <v>160.5955996704102</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>144.1334996414185</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="6" t="n">
         <v>53.54415317550977</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6" t="n">
         <v>0.1582480880170695</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="6" t="n">
         <v>0.191619450107465</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="6" t="n">
         <v>0.4740824704710953</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="6" t="n">
         <v>5.778986582872136</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="6" t="n">
         <v>4.005723640600515</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="6" t="n">
         <v>1.773262942271622</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="6" t="n">
         <v>1.980736671657304</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="6" t="n">
         <v>9138100</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="6" t="n">
         <v>10396890</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="6" t="n">
         <v>0.8789262943053163</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="6" t="n">
         <v>-0.0037174117418728</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R5" t="n">
+      <c r="R5" s="6" t="n">
         <v>10.84078325544085</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5" s="6" t="n">
         <v>0.0598442374866193</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T5" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>ARM</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="6" t="n">
         <v>298.989990234375</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="6" t="n">
         <v>311.1417984008789</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>182.1271249771118</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="6" t="n">
         <v>25.12013387453341</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>-0.1263478343916499</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="6" t="n">
         <v>0.8973853709871724</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="6" t="n">
         <v>1.674568277893681</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="6" t="n">
         <v>-4.89801759233734</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="6" t="n">
         <v>4.470349650983797</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="6" t="n">
         <v>-9.368367243321137</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="6" t="n">
         <v>-9.295743678605769</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="6" t="n">
         <v>5270100</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="6" t="n">
         <v>11217090</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="6" t="n">
         <v>0.4698277360705851</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="6" t="n">
         <v>-0.0369832753978448</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>DOWN</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="R6" s="6" t="n">
         <v>30.13700212751116</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S6" s="6" t="n">
         <v>0.1007960236524543</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T6" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>ASTS</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="6" t="n">
         <v>67.58000183105469</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="6" t="n">
         <v>86.13120018005371</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>82.99554985046387</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="6" t="n">
         <v>44.76385902437732</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="6" t="n">
         <v>-0.3072980368775975</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="6" t="n">
         <v>-0.3171668081487514</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="6" t="n">
         <v>-0.308078190867192</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="6" t="n">
         <v>-4.560100006332078</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="6" t="n">
         <v>-3.839575042154277</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="6" t="n">
         <v>-0.7205249641778009</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="6" t="n">
         <v>-0.3496537910423321</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="6" t="n">
         <v>12983400</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="6" t="n">
         <v>23273870</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" s="6" t="n">
         <v>0.5578530772922595</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="6" t="n">
         <v>-0.0180032692351115</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="R7" s="6" t="n">
         <v>7.066000257219587</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S7" s="6" t="n">
         <v>0.1045575623819025</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T7" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="6" t="n">
         <v>384.0499877929688</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="6" t="n">
         <v>406.0224005126953</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>362.6720501708984</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="6" t="n">
         <v>46.76644111895504</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>-0.0039422660019606</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="6" t="n">
         <v>0.0113232068280941</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="6" t="n">
         <v>0.1132851738817233</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="6" t="n">
         <v>-4.49748843644312</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="6" t="n">
         <v>-7.53636120941328</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="6" t="n">
         <v>3.038872772970159</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="6" t="n">
         <v>3.503419447292556</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="6" t="n">
         <v>21243800</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="6" t="n">
         <v>27672044</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="6" t="n">
         <v>0.7676989816870774</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8" s="6" t="n">
         <v>-0.0162261925008566</v>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="R8" s="6" t="n">
         <v>15.15999494280134</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S8" s="6" t="n">
         <v>0.0394740149060327</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T8" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>BFLY</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="6" t="n">
         <v>8.100000381469727</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="6" t="n">
         <v>5.764399991035462</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>4.017199999094009</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="6" t="n">
         <v>58.05825616673116</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>0.4260564482867148</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="6" t="n">
         <v>0.8925233608417111</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="6" t="n">
         <v>1.00495060840409</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="6" t="n">
         <v>0.6675626645364767</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="6" t="n">
         <v>0.7625105942770996</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="6" t="n">
         <v>-0.0949479297406228</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="6" t="n">
         <v>-0.0967705380809897</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="6" t="n">
         <v>7966000</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="6" t="n">
         <v>7916118</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="6" t="n">
         <v>1.006301320925231</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" s="6" t="n">
         <v>-0.0137844778510634</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="R9" s="6" t="n">
         <v>0.7777856077466693</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S9" s="6" t="n">
         <v>0.0960229100144242</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T9" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>BLZE</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="6" t="n">
         <v>16.19000053405762</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="6" t="n">
         <v>9.651000032424928</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>6.520349990129471</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="6" t="n">
         <v>79.95545838351569</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>1.116339912709505</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="6" t="n">
         <v>3.612535777221136</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="6" t="n">
         <v>2.238000106811524</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="6" t="n">
         <v>2.387645053357646</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="6" t="n">
         <v>2.173863412240089</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="6" t="n">
         <v>0.2137816411175577</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="6" t="n">
         <v>0.3715229171689866</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="6" t="n">
         <v>2296300</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="6" t="n">
         <v>3915572</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="6" t="n">
         <v>0.586453269151991</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10" s="6" t="n">
         <v>0.0056818397330839</v>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="R10" s="6" t="n">
         <v>1.69085727419172</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S10" s="6" t="n">
         <v>0.1044383705012731</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T10" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>CBOE</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="6" t="n">
         <v>277.1300048828125</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="6" t="n">
         <v>301.489001159668</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>275.8806508636475</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="6" t="n">
         <v>63.08948813870285</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="6" t="n">
         <v>-0.0634335566097992</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="6" t="n">
         <v>-0.0771561233832949</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="6" t="n">
         <v>0.0620041843989049</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="6" t="n">
         <v>-8.389997269254479</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="6" t="n">
         <v>-14.00248770166269</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="6" t="n">
         <v>5.61249043240821</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="6" t="n">
         <v>4.77123635252852</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="6" t="n">
         <v>1465000</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="6" t="n">
         <v>1563494</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="6" t="n">
         <v>0.9370039155890588</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" s="6" t="n">
         <v>-0.0012683117417138</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="R11" s="6" t="n">
         <v>12.01285443987165</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S11" s="6" t="n">
         <v>0.0433473612680497</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T11" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>CELC</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="6" t="n">
         <v>103.7900009155273</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="6" t="n">
         <v>112.6027996826172</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>100.9755499267578</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="6" t="n">
         <v>64.40748321374801</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>0.1597944283508272</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="6" t="n">
         <v>-0.1379568139522107</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="6" t="n">
         <v>-0.0346014430916795</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="6" t="n">
         <v>0.7852899954126684</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="6" t="n">
         <v>-1.125906164833035</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="6" t="n">
         <v>1.911196160245703</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="6" t="n">
         <v>2.637134413002336</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="6" t="n">
         <v>1257400</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="6" t="n">
         <v>1511476</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12" s="6" t="n">
         <v>0.8319020612963752</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12" s="6" t="n">
         <v>-0.008180004348712199</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R12" t="n">
+      <c r="R12" s="6" t="n">
         <v>6.056072235107422</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S12" s="6" t="n">
         <v>0.0583492839549769</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T12" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>CRDO</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="6" t="n">
         <v>236.8800048828125</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="6" t="n">
         <v>226.1213998413086</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="6" t="n">
         <v>161.3880502319336</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="6" t="n">
         <v>35.03556650730233</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="6" t="n">
         <v>-0.1053029304066459</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="6" t="n">
         <v>0.7630247380674873</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="6" t="n">
         <v>0.574790637989232</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="6" t="n">
         <v>7.133377048530008</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="6" t="n">
         <v>11.21173626549988</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="6" t="n">
         <v>-4.078359216969876</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="6" t="n">
         <v>-2.77502469175505</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="6" t="n">
         <v>6717000</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="6" t="n">
         <v>8705180</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13" s="6" t="n">
         <v>0.7716095474188931</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13" s="6" t="n">
         <v>-0.0359595173016396</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" s="6" t="inlineStr">
         <is>
           <t>DOWN</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="R13" s="6" t="n">
         <v>28.31142861502511</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S13" s="6" t="n">
         <v>0.1195180176943644</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T13" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="6" t="n">
         <v>352.510009765625</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="6" t="n">
         <v>372.7972003173828</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="6" t="n">
         <v>319.4152998352051</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="6" t="n">
         <v>52.39629178665267</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="6" t="n">
         <v>-0.0147021254145659</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="6" t="n">
         <v>0.0971025254243502</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="6" t="n">
         <v>0.0728611921592201</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="6" t="n">
         <v>-2.20383870768751</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="6" t="n">
         <v>-2.80130271294401</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="6" t="n">
         <v>0.5974640052565006</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="6" t="n">
         <v>1.141343376060255</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="6" t="n">
         <v>15836200</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="6" t="n">
         <v>33032270</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14" s="6" t="n">
         <v>0.479416037711002</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14" s="6" t="n">
         <v>-0.0027716844579075</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="R14" s="6" t="n">
         <v>10.05857195172991</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S14" s="6" t="n">
         <v>0.0285341456216168</v>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T14" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>INTC</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="6" t="n">
         <v>103.120002746582</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="6" t="n">
         <v>117.1707998657227</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="6" t="n">
         <v>62.83409996986389</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="6" t="n">
         <v>23.43354907791833</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="6" t="n">
         <v>-0.1183310229670477</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="6" t="n">
         <v>0.5820804274895581</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="6" t="n">
         <v>1.263885937953676</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="6" t="n">
         <v>-1.380027150532328</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="6" t="n">
         <v>2.262472583409701</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="6" t="n">
         <v>-3.642499733942029</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="6" t="n">
         <v>-3.296169654456531</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="6" t="n">
         <v>100510000</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="6" t="n">
         <v>132044706</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15" s="6" t="n">
         <v>0.7611815955726389</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" s="6" t="n">
         <v>-0.0351419620325085</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" s="6" t="inlineStr">
         <is>
           <t>DOWN</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="R15" s="6" t="n">
         <v>10.03500039236886</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S15" s="6" t="n">
         <v>0.0973138103674214</v>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T15" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>IONQ</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="6" t="n">
         <v>38.88000106811523</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="6" t="n">
         <v>55.01780014038086</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="6" t="n">
         <v>48.86195004463196</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="6" t="n">
         <v>15.99020298115008</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="6" t="n">
         <v>-0.329539576775829</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="6" t="n">
         <v>0.3064516387463771</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="6" t="n">
         <v>-0.2137512544336695</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="6" t="n">
         <v>-3.828664268174151</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="6" t="n">
         <v>-2.379467664629328</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="6" t="n">
         <v>-1.449196603544823</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="6" t="n">
         <v>-1.270452879257462</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="6" t="n">
         <v>23719400</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="6" t="n">
         <v>29094782</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16" s="6" t="n">
         <v>0.8152458403022232</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P16" s="6" t="n">
         <v>-0.0184321256247612</v>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R16" t="n">
+      <c r="R16" s="6" t="n">
         <v>3.97057124546596</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S16" s="6" t="n">
         <v>0.1021237432198054</v>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T16" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>KYTX</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="6" t="n">
         <v>7.769999980926514</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="6" t="n">
         <v>8.716799955368042</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="6" t="n">
         <v>8.183749969005584</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="6" t="n">
         <v>45.20795488517063</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="6" t="n">
         <v>-0.0127064683718816</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="6" t="n">
         <v>-0.1812433963830317</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="6" t="n">
         <v>-0.0661057372682181</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="6" t="n">
         <v>0.1189289027810343</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="6" t="n">
         <v>0.1258179386224268</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="6" t="n">
         <v>-0.0068890358413925</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="6" t="n">
         <v>0.1053387520495297</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="6" t="n">
         <v>1956100</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="6" t="n">
         <v>1056306</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17" s="6" t="n">
         <v>1.851830814176953</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17" s="6" t="n">
         <v>0.0017678661083915</v>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R17" t="n">
+      <c r="R17" s="6" t="n">
         <v>0.703214134488787</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S17" s="6" t="n">
         <v>0.09050374983462139</v>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T17" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>LLY</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="6" t="n">
         <v>1181.869995117188</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="6" t="n">
         <v>1093.367601318359</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="6" t="n">
         <v>998.5020529174805</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="6" t="n">
         <v>63.59330391902413</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="6" t="n">
         <v>0.0180197638358101</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="6" t="n">
         <v>0.2714431828709958</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="6" t="n">
         <v>0.1112395445536644</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="6" t="n">
         <v>32.89004314048429</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="6" t="n">
         <v>36.35861605354793</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="6" t="n">
         <v>-3.468572913063639</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="6" t="n">
         <v>-0.8770421350267767</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="6" t="n">
         <v>2069800</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="6" t="n">
         <v>3324634</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18" s="6" t="n">
         <v>0.6225647695355339</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18" s="6" t="n">
         <v>-0.0071261261474068</v>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q18" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R18" t="n">
+      <c r="R18" s="6" t="n">
         <v>41.62001255580357</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S18" s="6" t="n">
         <v>0.0352153897871624</v>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T18" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>LUNR</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="6" t="n">
         <v>15.14999961853027</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="6" t="n">
         <v>27.66040004730225</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="6" t="n">
         <v>18.9955750322342</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="6" t="n">
         <v>22.01308672444488</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="6" t="n">
         <v>-0.5055483054725967</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="6" t="n">
         <v>-0.3793527360412319</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="6" t="n">
         <v>-0.1837284453412545</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="6" t="n">
         <v>-3.381335397595574</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="6" t="n">
         <v>-3.141287952753423</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="6" t="n">
         <v>-0.2400474448421516</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="6" t="n">
         <v>-0.2227528480675804</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="6" t="n">
         <v>10284400</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="6" t="n">
         <v>14345454</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19" s="6" t="n">
         <v>0.7169100399332081</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P19" s="6" t="n">
         <v>-0.0085500982745466</v>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q19" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R19" t="n">
+      <c r="R19" s="6" t="n">
         <v>1.668785776410784</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S19" s="6" t="n">
         <v>0.110150879104291</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T19" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>MRVL</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="6" t="n">
         <v>217.5299987792969</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="6" t="n">
         <v>232.6888000488281</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="6" t="n">
         <v>127.4797001647949</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="6" t="n">
         <v>26.81350318140036</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="6" t="n">
         <v>-0.2250721192654516</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="6" t="n">
         <v>0.6567402416094965</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="6" t="n">
         <v>1.613914871286744</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="6" t="n">
         <v>-3.204063803227768</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="6" t="n">
         <v>6.405497878057763</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="6" t="n">
         <v>-9.60956168128553</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="6" t="n">
         <v>-9.135745020112926</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="6" t="n">
         <v>25432700</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="6" t="n">
         <v>45380534</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20" s="6" t="n">
         <v>0.560431924401771</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P20" s="6" t="n">
         <v>-0.0298121320218837</v>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q20" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R20" t="n">
+      <c r="R20" s="6" t="n">
         <v>22.82714407784598</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S20" s="6" t="n">
         <v>0.1049379129588747</v>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T20" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="6" t="n">
         <v>937</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="6" t="n">
         <v>907.4182006835938</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="6" t="n">
         <v>468.3365003204346</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="6" t="n">
         <v>32.2591555067534</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="6" t="n">
         <v>-0.0591141367907767</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="6" t="n">
         <v>1.196642923300117</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="6" t="n">
         <v>1.715233735963033</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="6" t="n">
         <v>11.82658795472946</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="6" t="n">
         <v>40.65852286513154</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="6" t="n">
         <v>-28.83193491040208</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="6" t="n">
         <v>-28.47679485729119</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="6" t="n">
         <v>35174600</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="6" t="n">
         <v>54242392</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21" s="6" t="n">
         <v>0.6484706647892666</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21" s="6" t="n">
         <v>-0.0513632068007362</v>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q21" s="6" t="inlineStr">
         <is>
           <t>DOWN</t>
         </is>
       </c>
-      <c r="R21" t="n">
+      <c r="R21" s="6" t="n">
         <v>97.98501586914062</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S21" s="6" t="n">
         <v>0.1045731225924659</v>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T21" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>NBIS</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="6" t="n">
         <v>210.509994506836</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="6" t="n">
         <v>222.8711999511719</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="6" t="n">
         <v>136.3346254730225</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="6" t="n">
         <v>31.19082085488327</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="6" t="n">
         <v>-0.0527808256677213</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="6" t="n">
         <v>0.36199532758812</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="6" t="n">
         <v>1.149596587877373</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" s="6" t="n">
         <v>-4.446131681101804</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="6" t="n">
         <v>2.215339231112166</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="6" t="n">
         <v>-6.66147091221397</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="6" t="n">
         <v>-7.117179030533046</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="6" t="n">
         <v>10748400</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="6" t="n">
         <v>17950916</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" s="6" t="n">
         <v>0.5987661019638217</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22" s="6" t="n">
         <v>-0.0316867363918898</v>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" s="6" t="inlineStr">
         <is>
           <t>DOWN</t>
         </is>
       </c>
-      <c r="R22" t="n">
+      <c r="R22" s="6" t="n">
         <v>26.59443010602678</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S22" s="6" t="n">
         <v>0.1263333371336114</v>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T22" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="6" t="n">
         <v>203.5299987792969</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="6" t="n">
         <v>209.0846005249024</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="6" t="n">
         <v>191.7959504699707</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="6" t="n">
         <v>45.3606417209306</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="6" t="n">
         <v>-0.0065407154284556</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="6" t="n">
         <v>0.0751148983365332</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="6" t="n">
         <v>0.1009953375922463</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" s="6" t="n">
         <v>-1.470477138528508</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="6" t="n">
         <v>-2.676673164090676</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" s="6" t="n">
         <v>1.206196025562167</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="6" t="n">
         <v>1.243094423058239</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23" s="6" t="n">
         <v>120943800</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" s="6" t="n">
         <v>160891548</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23" s="6" t="n">
         <v>0.7517100898302004</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P23" s="6" t="n">
         <v>-0.0114714322654375</v>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q23" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R23" t="n">
+      <c r="R23" s="6" t="n">
         <v>6.922855922154018</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S23" s="6" t="n">
         <v>0.0340139338852991</v>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T23" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>CCJ</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="6" t="n">
         <v>90.1999969482422</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="6" t="n">
         <v>107.2673994445801</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="6" t="n">
         <v>104.4071496582031</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="6" t="n">
         <v>18.63144679070228</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="6" t="n">
         <v>-0.0886127529987983</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" s="6" t="n">
         <v>-0.2270779836588432</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="6" t="n">
         <v>-0.1613982986648418</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" s="6" t="n">
         <v>-3.944035004077562</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" s="6" t="n">
         <v>-3.150560770783445</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24" s="6" t="n">
         <v>-0.7934742332941171</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="6" t="n">
         <v>-0.5758541077941897</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24" s="6" t="n">
         <v>6232500</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24" s="6" t="n">
         <v>3263872</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O24" s="6" t="n">
         <v>1.909541795756696</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P24" s="6" t="n">
         <v>-0.0165641876578346</v>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q24" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R24" t="n">
+      <c r="R24" s="6" t="n">
         <v>4.847142355782645</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S24" s="6" t="n">
         <v>0.0537377219487489</v>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T24" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="6" t="n">
         <v>25.95999908447266</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="6" t="n">
         <v>36.10280010223389</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="6" t="n">
         <v>25.30039998531341</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="6" t="n">
         <v>41.46933662967547</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="6" t="n">
         <v>-0.2402692281070749</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" s="6" t="n">
         <v>-0.2435897635398968</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" s="6" t="n">
         <v>0.1431087684288856</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" s="6" t="n">
         <v>-2.398414176127453</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" s="6" t="n">
         <v>-2.383489535301673</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25" s="6" t="n">
         <v>-0.0149246408257801</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="6" t="n">
         <v>0.0551783542258297</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25" s="6" t="n">
         <v>5757200</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25" s="6" t="n">
         <v>13410266</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O25" s="6" t="n">
         <v>0.4293128861127736</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P25" s="6" t="n">
         <v>-0.0034549003924671</v>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q25" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R25" t="n">
+      <c r="R25" s="6" t="n">
         <v>2.413428579057966</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S25" s="6" t="n">
         <v>0.09296720586178669</v>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T25" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>PUBM</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="6" t="n">
         <v>13.56999969482422</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="6" t="n">
         <v>11.39380002975464</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="6" t="n">
         <v>9.101925008296966</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="6" t="n">
         <v>75.50561349871404</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="6" t="n">
         <v>0.2040815566672071</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" s="6" t="n">
         <v>0.5687861610715199</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="6" t="n">
         <v>0.6212664134245443</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26" s="6" t="n">
         <v>0.6810486742976209</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" s="6" t="n">
         <v>0.6384767328340759</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26" s="6" t="n">
         <v>0.042571941463545</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26" s="6" t="n">
         <v>0.0616822772464507</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26" s="6" t="n">
         <v>313200</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26" s="6" t="n">
         <v>673660</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O26" s="6" t="n">
         <v>0.4649229581688092</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P26" s="6" t="n">
         <v>0.0007380242613335</v>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q26" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="R26" s="6" t="n">
         <v>0.597428526197161</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S26" s="6" t="n">
         <v>0.0440256845713142</v>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T26" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>RKLB</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="6" t="n">
         <v>76.73000335693359</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="6" t="n">
         <v>107.0883999633789</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="6" t="n">
         <v>76.91300010681152</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="6" t="n">
         <v>32.22155183233293</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="6" t="n">
         <v>-0.3315037099410254</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" s="6" t="n">
         <v>0.0865194048813213</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="6" t="n">
         <v>-0.0956982352765046</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" s="6" t="n">
         <v>-7.502857180160049</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" s="6" t="n">
         <v>-5.901575053726029</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27" s="6" t="n">
         <v>-1.60128212643402</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27" s="6" t="n">
         <v>-1.41846552484385</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" s="6" t="n">
         <v>18704000</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27" s="6" t="n">
         <v>28318376</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O27" s="6" t="n">
         <v>0.6604898529491945</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P27" s="6" t="n">
         <v>-0.0141905418668198</v>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q27" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R27" t="n">
+      <c r="R27" s="6" t="n">
         <v>7.806785583496094</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S27" s="6" t="n">
         <v>0.101743584542547</v>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T27" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>SOFI</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="6" t="n">
         <v>18.1299991607666</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="6" t="n">
         <v>16.89759994506836</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="6" t="n">
         <v>22.02237502574921</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="6" t="n">
         <v>60.23854340937944</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="6" t="n">
         <v>0.08758242818180249</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" s="6" t="n">
         <v>0.0633431068641061</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="6" t="n">
         <v>-0.3383211893001081</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" s="6" t="n">
         <v>0.3961109768285347</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" s="6" t="n">
         <v>0.363303113685673</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K28" s="6" t="n">
         <v>0.0328078631428616</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28" s="6" t="n">
         <v>0.0683407053806285</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28" s="6" t="n">
         <v>97444000</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N28" s="6" t="n">
         <v>77088926</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O28" s="6" t="n">
         <v>1.264046667351417</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P28" s="6" t="n">
         <v>0.0114483570142134</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q28" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R28" t="n">
+      <c r="R28" s="6" t="n">
         <v>0.9592857360839844</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S28" s="6" t="n">
         <v>0.0529115157467785</v>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T28" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>STTK</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="6" t="n">
         <v>6.429999828338623</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="6" t="n">
         <v>5.949199991226196</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="6" t="n">
         <v>4.476700005531311</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="6" t="n">
         <v>64.1330123763551</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="6" t="n">
         <v>0.5382775340673356</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" s="6" t="n">
         <v>-0.0502215884114906</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="6" t="n">
         <v>0.3536841743870784</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" s="6" t="n">
         <v>0.370541003841125</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" s="6" t="n">
         <v>0.3059377744577766</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29" s="6" t="n">
         <v>0.0646032293833483</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" s="6" t="n">
         <v>0.124170819681362</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29" s="6" t="n">
         <v>863400</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29" s="6" t="n">
         <v>1214274</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O29" s="6" t="n">
         <v>0.7110421535831287</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P29" s="6" t="n">
         <v>-0.0015059867839982</v>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q29" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R29" t="n">
+      <c r="R29" s="6" t="n">
         <v>0.6494998591286796</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S29" s="6" t="n">
         <v>0.1010108672579073</v>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T29" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="6" t="n">
         <v>394.760009765625</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="6" t="n">
         <v>409.6355993652344</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="6" t="n">
         <v>417.9844500732422</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="6" t="n">
         <v>47.30190854550064</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="6" t="n">
         <v>-0.0109983319503641</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" s="6" t="n">
         <v>0.1201407261922502</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" s="6" t="n">
         <v>-0.1129188083352672</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" s="6" t="n">
         <v>-0.8584587141779139</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" s="6" t="n">
         <v>-1.240089992671354</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30" s="6" t="n">
         <v>0.3816312784934397</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30" s="6" t="n">
         <v>1.191718983171606</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30" s="6" t="n">
         <v>32729700</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N30" s="6" t="n">
         <v>48990810</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O30" s="6" t="n">
         <v>0.6680783600026209</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P30" s="6" t="n">
         <v>-0.0077251921194358</v>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q30" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R30" t="n">
+      <c r="R30" s="6" t="n">
         <v>19.89071219308036</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S30" s="6" t="n">
         <v>0.0503868469475663</v>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T30" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>TSM</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="6" t="n">
         <v>421.5799865722656</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="6" t="n">
         <v>424.5066003417969</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="6" t="n">
         <v>349.0248500061035</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="6" t="n">
         <v>37.838400646266</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="6" t="n">
         <v>0.0012111507330756</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31" s="6" t="n">
         <v>0.1407310610095564</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="6" t="n">
         <v>0.3026603844254834</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" s="6" t="n">
         <v>2.714938807848512</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" s="6" t="n">
         <v>6.42672567296799</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31" s="6" t="n">
         <v>-3.711786865119478</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31" s="6" t="n">
         <v>-2.826101363815375</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31" s="6" t="n">
         <v>14265400</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N31" s="6" t="n">
         <v>13731166</v>
       </c>
-      <c r="O31" t="n">
+      <c r="O31" s="6" t="n">
         <v>1.038906674058124</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P31" s="6" t="n">
         <v>-0.0006679828548723</v>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q31" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R31" t="n">
+      <c r="R31" s="6" t="n">
         <v>21.50642830984933</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S31" s="6" t="n">
         <v>0.0510138739856019</v>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T31" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>VRT</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="6" t="n">
         <v>305.8699951171875</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="6" t="n">
         <v>324.7316009521484</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="6" t="n">
         <v>237.6646502685547</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="6" t="n">
         <v>37.27464274525995</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="6" t="n">
         <v>0.0268228484738957</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32" s="6" t="n">
         <v>0.0197026397868611</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="6" t="n">
         <v>0.8698495640872399</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" s="6" t="n">
         <v>-1.147608980761959</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" s="6" t="n">
         <v>-0.9995548151418208</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K32" s="6" t="n">
         <v>-0.1480541656201379</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L32" s="6" t="n">
         <v>0.6333687634440077</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M32" s="6" t="n">
         <v>3716100</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N32" s="6" t="n">
         <v>6234872</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O32" s="6" t="n">
         <v>0.5960186512249169</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P32" s="6" t="n">
         <v>-0.0217022618956923</v>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q32" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R32" t="n">
+      <c r="R32" s="6" t="n">
         <v>23.01642935616629</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S32" s="6" t="n">
         <v>0.075249059154521</v>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T32" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>STX</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="6" t="n">
         <v>860.6599731445312</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="6" t="n">
         <v>873.0957971191406</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="6" t="n">
         <v>476.2953498840332</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="6" t="n">
         <v>33.24526766433529</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="6" t="n">
         <v>-0.0085590819858302</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33" s="6" t="n">
         <v>0.6767844529691138</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="6" t="n">
         <v>1.831025115942902</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" s="6" t="n">
         <v>-2.548893026430619</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" s="6" t="n">
         <v>15.03973086762754</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K33" s="6" t="n">
         <v>-17.58862389405815</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33" s="6" t="n">
         <v>-18.29337606210337</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M33" s="6" t="n">
         <v>4130400</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N33" s="6" t="n">
         <v>4428830</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O33" s="6" t="n">
         <v>0.9326165149712228</v>
       </c>
-      <c r="P33" t="n">
+      <c r="P33" s="6" t="n">
         <v>-0.0447525650500693</v>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q33" s="6" t="inlineStr">
         <is>
           <t>DOWN</t>
         </is>
       </c>
-      <c r="R33" t="n">
+      <c r="R33" s="6" t="n">
         <v>88.97071620396206</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S33" s="6" t="n">
         <v>0.1033749901007899</v>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="T33" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>SMCI</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" s="6" t="n">
         <v>27.65999984741211</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="6" t="n">
         <v>33.44839981079102</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="6" t="n">
         <v>34.46944990158081</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="6" t="n">
         <v>22.68907596697776</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="6" t="n">
         <v>-0.1348138742105638</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34" s="6" t="n">
         <v>0.06507510892341729</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" s="6" t="n">
         <v>-0.0828912471037202</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34" s="6" t="n">
         <v>-1.952459172100369</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" s="6" t="n">
         <v>-1.839501051819422</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K34" s="6" t="n">
         <v>-0.1129581202809464</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L34" s="6" t="n">
         <v>-0.1851025146949276</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M34" s="6" t="n">
         <v>22736300</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N34" s="6" t="n">
         <v>55712566</v>
       </c>
-      <c r="O34" t="n">
+      <c r="O34" s="6" t="n">
         <v>0.4081000325851083</v>
       </c>
-      <c r="P34" t="n">
+      <c r="P34" s="6" t="n">
         <v>-0.0236665520640497</v>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q34" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R34" t="n">
+      <c r="R34" s="6" t="n">
         <v>1.90642820085798</v>
       </c>
-      <c r="S34" t="n">
+      <c r="S34" s="6" t="n">
         <v>0.0689236518935247</v>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="T34" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>DDOG</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" s="6" t="n">
         <v>260.239990234375</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="6" t="n">
         <v>223.3829998779297</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="6" t="n">
         <v>159.7822002410889</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="6" t="n">
         <v>72.85664449359034</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="6" t="n">
         <v>0.1109972000148784</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35" s="6" t="n">
         <v>1.364098709171339</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" s="6" t="n">
         <v>1.073790697780459</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35" s="6" t="n">
         <v>11.84447561317248</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" s="6" t="n">
         <v>11.44889912504316</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K35" s="6" t="n">
         <v>0.3955764881293149</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35" s="6" t="n">
         <v>0.8170337357042587</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35" s="6" t="n">
         <v>4212100</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N35" s="6" t="n">
         <v>6163506</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O35" s="6" t="n">
         <v>0.6833935101223232</v>
       </c>
-      <c r="P35" t="n">
+      <c r="P35" s="6" t="n">
         <v>-0.0032228665927801</v>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q35" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R35" t="n">
+      <c r="R35" s="6" t="n">
         <v>13.0087160382952</v>
       </c>
-      <c r="S35" t="n">
+      <c r="S35" s="6" t="n">
         <v>0.0499873829021412</v>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T35" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>SKHY</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="6" t="n">
         <v>153.5099945068359</v>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="n">
+      <c r="C36" s="6" t="inlineStr"/>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr"/>
+      <c r="F36" s="6" t="inlineStr"/>
+      <c r="G36" s="6" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr"/>
+      <c r="I36" s="6" t="n">
         <v>-1.156695156695179</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" s="6" t="n">
         <v>-0.2313390313390357</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K36" s="6" t="n">
         <v>-0.9253561253561428</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="L36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="6" t="n">
         <v>56529633</v>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
+      <c r="N36" s="6" t="inlineStr"/>
+      <c r="O36" s="6" t="inlineStr"/>
+      <c r="P36" s="6" t="n">
         <v>-0.0916016897377034</v>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q36" s="6" t="inlineStr">
         <is>
           <t>DOWN</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr">
+      <c r="R36" s="6" t="inlineStr"/>
+      <c r="S36" s="6" t="inlineStr"/>
+      <c r="T36" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>SMR</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="6" t="n">
         <v>8.350000381469727</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="6" t="n">
         <v>11.01620002746582</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="6" t="n">
         <v>18.60579996585846</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="6" t="n">
         <v>14.49631933236232</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="6" t="n">
         <v>-0.1274816460040546</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37" s="6" t="n">
         <v>-0.1283924375816173</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="6" t="n">
         <v>-0.5928815071532083</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37" s="6" t="n">
         <v>-0.6289956274373996</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" s="6" t="n">
         <v>-0.5032672616488264</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K37" s="6" t="n">
         <v>-0.1257283657885731</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L37" s="6" t="n">
         <v>-0.1007332683507987</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M37" s="6" t="n">
         <v>38962400</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N37" s="6" t="n">
         <v>33290360</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O37" s="6" t="n">
         <v>1.170380854998263</v>
       </c>
-      <c r="P37" t="n">
+      <c r="P37" s="6" t="n">
         <v>-0.0188053182534636</v>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q37" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R37" t="n">
+      <c r="R37" s="6" t="n">
         <v>0.7357140268598285</v>
       </c>
-      <c r="S37" t="n">
+      <c r="S37" s="6" t="n">
         <v>0.0881094602693097</v>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T37" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>OKLO</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="6" t="n">
         <v>45.81000137329102</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="6" t="n">
         <v>61.15459983825684</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="6" t="n">
         <v>81.88404979705811</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="6" t="n">
         <v>21.80922241156196</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="6" t="n">
         <v>-0.2082613050457644</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38" s="6" t="n">
         <v>-0.1507229785021223</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="6" t="n">
         <v>-0.564998552508724</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38" s="6" t="n">
         <v>-3.740426935138217</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" s="6" t="n">
         <v>-3.394162853507454</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K38" s="6" t="n">
         <v>-0.3462640816307631</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L38" s="6" t="n">
         <v>-0.2587766965285807</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M38" s="6" t="n">
         <v>10066900</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N38" s="6" t="n">
         <v>12592758</v>
       </c>
-      <c r="O38" t="n">
+      <c r="O38" s="6" t="n">
         <v>0.7994197935035359</v>
       </c>
-      <c r="P38" t="n">
+      <c r="P38" s="6" t="n">
         <v>-0.0231319813452317</v>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q38" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R38" t="n">
+      <c r="R38" s="6" t="n">
         <v>3.72428594316755</v>
       </c>
-      <c r="S38" t="n">
+      <c r="S38" s="6" t="n">
         <v>0.0812985337594631</v>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T38" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>JOBY</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="6" t="n">
         <v>7.480000019073486</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="6" t="n">
         <v>9.79479998588562</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="6" t="n">
         <v>12.07090001583099</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="6" t="n">
         <v>19.79695935229539</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="6" t="n">
         <v>-0.2008546695044591</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39" s="6" t="n">
         <v>-0.1220657726306231</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="6" t="n">
         <v>-0.5139701200644334</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" s="6" t="n">
         <v>-0.5876672497065716</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" s="6" t="n">
         <v>-0.4619484600576871</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K39" s="6" t="n">
         <v>-0.1257187896488844</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L39" s="6" t="n">
         <v>-0.1157084245752973</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M39" s="6" t="n">
         <v>48444300</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N39" s="6" t="n">
         <v>37100944</v>
       </c>
-      <c r="O39" t="n">
+      <c r="O39" s="6" t="n">
         <v>1.305743056025744</v>
       </c>
-      <c r="P39" t="n">
+      <c r="P39" s="6" t="n">
         <v>-0.0233160405739019</v>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q39" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R39" t="n">
+      <c r="R39" s="6" t="n">
         <v>0.5634285722460065</v>
       </c>
-      <c r="S39" t="n">
+      <c r="S39" s="6" t="n">
         <v>0.0753246752418853</v>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="T39" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>SOUN</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="6" t="n">
         <v>6.489999771118164</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="6" t="n">
         <v>7.702400026321411</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="6" t="n">
         <v>10.31352501630783</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="6" t="n">
         <v>42.1686670849046</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="6" t="n">
         <v>-0.0728571755545479</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40" s="6" t="n">
         <v>-0.0511696452722014</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" s="6" t="n">
         <v>-0.4476595939473903</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40" s="6" t="n">
         <v>-0.2666229192549947</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" s="6" t="n">
         <v>-0.3228008935526191</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K40" s="6" t="n">
         <v>0.0561779742976243</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L40" s="6" t="n">
         <v>0.0674839355125665</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M40" s="6" t="n">
         <v>29879000</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N40" s="6" t="n">
         <v>28649440</v>
       </c>
-      <c r="O40" t="n">
+      <c r="O40" s="6" t="n">
         <v>1.042917418281125</v>
       </c>
-      <c r="P40" t="n">
+      <c r="P40" s="6" t="n">
         <v>-0.0045180321648213</v>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q40" s="6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="R40" t="n">
+      <c r="R40" s="6" t="n">
         <v>0.4056429181780134</v>
       </c>
-      <c r="S40" t="n">
+      <c r="S40" s="6" t="n">
         <v>0.0625027630945702</v>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="T40" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
@@ -6530,7 +6559,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6586,360 +6615,360 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Buy</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="6" t="n">
         <v>406.05</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="6" t="n">
         <v>11.26</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="6" t="n">
         <v>0.20096</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="6" t="n">
         <v>0.02721351</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="6" t="n">
         <v>11.0500457355</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Imported current workbook buy</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>ASTS</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Buy</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="6" t="n">
         <v>82.2</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="6" t="n">
         <v>11.26</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="6" t="n">
         <v>0.20996</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="6" t="n">
         <v>0.13442881</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="6" t="n">
         <v>11.050048182</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>Imported current workbook buy</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>SOFI</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Buy</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>18.07</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="6" t="n">
         <v>11.26</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>0.20096</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="6" t="n">
         <v>0.6115135</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="6" t="n">
         <v>11.050048945</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Imported current workbook buy</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>BLZE</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Buy</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>14.8</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="6" t="n">
         <v>11.26</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6" t="n">
         <v>0.20096</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="6" t="n">
         <v>0.74662492</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="6" t="n">
         <v>11.050048816</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>Imported current workbook buy</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>IONQ</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Buy</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>53.489</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="6" t="n">
         <v>11.28</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>0.21033</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="6" t="n">
         <v>0.20695315</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="6" t="n">
         <v>11.06971704035</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>Imported current workbook buy</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>IONQ</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Sell</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>47.449</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="6" t="n">
         <v>9.65</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="6" t="n">
         <v>0.18329</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="6" t="n">
         <v>0.20695315</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="6" t="n">
         <v>9.819720014350001</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>Imported current workbook sell</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>ASTS</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Sell</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>73.86799999999999</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="6" t="n">
         <v>9.74</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>0.18516</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="6" t="n">
         <v>0.13442881</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="6" t="n">
         <v>9.92998733708</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>Imported current workbook sell</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Buy</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>365.29</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="6" t="n">
         <v>9.65</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>0.17994</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="6" t="n">
         <v>0.02592479</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="6" t="n">
         <v>9.470066539099999</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>Imported current workbook buy</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Buy</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>354.87</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="6" t="n">
         <v>9.74</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>0.18161</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="6" t="n">
         <v>0.0269349</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="6" t="n">
         <v>9.558387962999999</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>Imported current workbook buy</t>
         </is>
@@ -6976,12 +7005,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Risk On</t>
         </is>
@@ -7002,7 +7031,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7018,92 +7047,92 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Check CASH first to see available buying power.</t>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Run GitHub Action or confirm latest scheduled run completed.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Open PREMARKET_PLAYS during NZ evening US premarket window.</t>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Open Dashboard / BUY_NOW and review BUY and BUY SMALL candidates first.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Focus only on PREMARKET BUY first.</t>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Check decision_reasons and warnings before placing any trade.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Check gap_pct, volume_trend, score, stop_loss and trim_price.</t>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Confirm cash_available_usd in CASH before trading.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Position size is buy_amount_usd. Shares = shares_to_buy.</t>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Use buy_amount_usd and shares_to_buy as suggested sizing only.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Set stop loss immediately.</t>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Set stop_loss immediately after entry.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Use trim_price as first profit-taking target.</t>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Use trim_price as first profit-taking reference.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Log deposits in data/deposits.csv.</t>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Log all buys/sells in data/trades.csv.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Log buys/sells only in data/trades.csv.</t>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Log deposits only in data/deposits.csv.</t>
         </is>
       </c>
     </row>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -52,12 +52,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
@@ -544,7 +544,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>KYTX</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -553,33 +553,115 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>7.769999980926514</v>
+        <v>369.8450012207031</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.0017678661083915</v>
+        <v>0.082723417254077</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.851830814176953</v>
+        <v>0.2543960078535687</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>PREMARKET WATCH</t>
+          <t>PREMARKET BUY</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>0.0324460245789264</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>6.363571711948939</v>
+        <v>276.9891575404576</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>10.58285651888166</v>
+        <v>555.5566885811942</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>987.3599853515624</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.0543756800501934</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.3691105013773031</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>PREMARKET BUY</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.0121536219596009</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>807.8299560546874</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>1346.420043945312</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CRDO</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>238.8999938964844</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.06596166699561611</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.2471155973482561</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>PREMARKET BUY</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.0502302231334489</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>185.3292781284877</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>346.0414254324777</v>
       </c>
     </row>
   </sheetData>
@@ -721,504 +803,504 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ANET</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Networking</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>181.1499938964844</v>
-      </c>
-      <c r="E2" s="3" t="n">
+      <c r="D2" s="2" t="n">
+        <v>182.634994506836</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>53.54415317550977</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>-0.0037174117418728</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.8789262943053163</v>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>1.773262942271622</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>10.84078325544085</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>159.4684273856027</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>224.5131269182478</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.0514785958588289</v>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="J2" s="2" t="n">
+        <v>62.44594972357781</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.0151807899125376</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0.3138506159908594</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>1.608514906429189</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>10.46220506940569</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>161.7105843680246</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>224.4838147844588</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0.0533413650657586</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>211.2200012207031</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>60.30225678806677</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.0229450115312453</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0.390917583540066</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>1.634998744915757</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>6.863571166992188</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>200.9246444702148</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>231.8107147216797</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.0660529657199552</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>534.3900146484375</v>
-      </c>
-      <c r="E3" s="3" t="n">
+      <c r="D4" s="2" t="n">
+        <v>555.3699951171875</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G4" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H4" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I4" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>47.25110136960278</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>-0.0365484488215595</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0.665160990480149</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>-3.577422784539042</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>38.40929303850447</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>476.7760750906808</v>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>649.6178937639509</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.0193726832181142</v>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="J4" s="2" t="n">
+        <v>55.86565004537624</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.0624019610194614</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0.4139132873326793</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>-2.597301163054709</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>38.05143519810268</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>498.2928423200335</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>669.5243007114956</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.0195548752049112</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>987.3599853515624</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>45.1502141583485</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.0543756800501934</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0.3691105013773031</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>-24.69993152187335</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>89.7650146484375</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>807.8299560546874</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>1346.420043945312</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.0062169911316303</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare/Pharma</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1154</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>57.41560404426107</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>-0.013419399271567</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0.3812196495005608</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>-7.021138416095418</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>41.49965122767857</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1091.750523158482</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>1278.498953683036</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.0120898678509532</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>BFLY</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>8.100000381469727</v>
-      </c>
-      <c r="E4" s="3" t="n">
+      <c r="D7" s="2" t="n">
+        <v>7.710000038146973</v>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G7" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H7" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I7" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>58.05825616673116</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>-0.0137844778510634</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>1.006301320925231</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>-0.0949479297406228</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>0.7777856077466693</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>6.544429165976388</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>11.2111428124564</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.7175091624757438</v>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="J7" s="2" t="n">
+        <v>50.38910466129628</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>-0.0049382666628676</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0.4330916809728698</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>-0.1206688011081675</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.7386070660182408</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>6.232785906110491</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>10.66442830221994</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.755568590764359</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>LLY</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Healthcare/Pharma</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>1181.869995117188</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="T7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ALAB</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>369.8450012207031</v>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G8" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H8" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I8" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>63.59330391902413</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>-0.0071261261474068</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0.6225647695355339</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>-3.468572913063639</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>41.62001255580357</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>1119.439976283482</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>1306.730032784599</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.0118047734163998</v>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="J8" s="2" t="n">
+        <v>46.14959731343965</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.082723417254077</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0.2543960078535687</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>-11.19183890588324</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>46.42792184012277</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>276.9891575404576</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>555.5566885811942</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.0120201007902473</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>BLZE</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Gaming/Digital Media</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>16.19000053405762</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>79.95545838351569</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.0056818397330839</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.586453269151991</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0.2137816411175577</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>1.69085727419172</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>12.80828598567418</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>22.9534296308245</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.3300505066382809</v>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>PUBM</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>AdTech</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>13.56999969482422</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>75.50561349871404</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0.0007380242613335</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0.4649229581688092</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0.042571941463545</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0.597428526197161</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>12.3751426424299</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>15.95971379961287</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>12.68</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.9341172634529142</v>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>DDOG</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Cloud Software</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>260.239990234375</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>72.85664449359034</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>-0.0032228665927801</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0.6833935101223232</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>0.3955764881293149</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>13.0087160382952</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>240.7269161769322</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>299.2661383492606</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.0536109284642799</v>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>STTK</t>
+          <t>BLZE</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Gaming/Digital Media</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1227,360 +1309,360 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6.429999828338623</v>
+        <v>17.1200008392334</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>BUY SMALL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
         <v>80</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>75</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>64.1330123763551</v>
+        <v>75.1381247005498</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.0015059867839982</v>
+        <v>0.0098826338563442</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0.7110421535831287</v>
+        <v>0.1840927394643399</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.0646032293833483</v>
+        <v>0.1432374274106971</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.6494998591286796</v>
+        <v>1.499500070299421</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>5.131000110081263</v>
+        <v>14.12100069863456</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>9.027999264853342</v>
+        <v>23.11800112043108</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>2.76</v>
+        <v>6.37</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.4296138730104287</v>
+        <v>0.3721695724152681</v>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>PUBM</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>AdTech</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>13.80500030517578</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>75.64245676712319</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>-0.0110537672736636</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0.2136791585954758</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.0375385811548205</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0.6038284982953753</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>12.59734330858503</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>16.22031429835728</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0.9242165640996444</v>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>DDOG</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Software</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>269.125</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>76.07259720135606</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>-0.0192129762097973</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0.3530761799701896</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>0.5733216154848417</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>13.84728785923549</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>248.3540682111468</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>310.6668635777065</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>0.0518409939619136</v>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>394.5700073242188</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>BUY SMALL</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>55.83900718527268</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.030087289573326</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0.34719360816042</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>3.328471821393368</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>15.00356619698661</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>372.0646580287389</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>439.5807059151786</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>0.0176796350977278</v>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>STTK</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>6.429999828338623</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>BUY SMALL</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>62.8078769713569</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0.0046656626141934</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0.2286261534058216</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>0.0210916334731448</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>0.6430713449205671</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>5.143857138497489</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>9.002285208020892</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>0.433908542503113</v>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
           <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>384.0499877929688</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>46.76644111895504</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>-0.0162261925008566</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0.7676989816870774</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>3.038872772970159</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>15.15999494280134</v>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v>361.3099953787668</v>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v>429.5299726213728</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="4" t="inlineStr">
-        <is>
-          <t>Above 200 SMA; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>203.5299987792969</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>45.3606417209306</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>-0.0114714322654375</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>0.7517100898302004</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>1.206196025562167</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>6.922855922154018</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>193.1457148960658</v>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v>224.2985665457589</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="4" t="inlineStr">
-        <is>
-          <t>Above 200 SMA; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Internet/Software</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>352.510009765625</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>52.39629178665267</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>-0.0027716844579075</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0.479416037711002</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0.5974640052565006</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>10.05857195172991</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>337.4221518380301</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>382.6857256208148</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="4" t="inlineStr">
-        <is>
-          <t>Above 200 SMA; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SOFI</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Fintech</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>18.1299991607666</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>60.23854340937944</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0.0114483570142134</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>1.264046667351417</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>0.0328078631428616</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>0.9592857360839844</v>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v>16.21142768859863</v>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v>21.96714210510254</v>
-      </c>
-      <c r="Q13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="4" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Positive 1M return; Positive 3M return; MACD improving; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T13" s="4" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Internet/Software</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>236.8800048828125</v>
+        <v>356.6700134277344</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
@@ -1588,34 +1670,34 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>75</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>35.03556650730233</v>
+        <v>58.83340486164004</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.0359595173016396</v>
+        <v>-0.0040282924977889</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.7716095474188931</v>
+        <v>0.233640186442379</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.078359216969876</v>
+        <v>0.5162715592141147</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>28.31142861502511</v>
+        <v>9.923573085239957</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>180.2571476527623</v>
+        <v>341.7846537998744</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>350.1257193429129</v>
+        <v>386.4407326834543</v>
       </c>
       <c r="Q14" s="4" t="n">
         <v>0</v>
@@ -1625,7 +1707,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 3M return; Positive 6M return</t>
+          <t>Above 200 SMA; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
         </is>
       </c>
       <c r="T14" s="4" t="inlineStr"/>
@@ -1633,12 +1715,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>CELC</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1647,10 +1729,10 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>362.0499877929688</v>
+        <v>105</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
@@ -1658,34 +1740,34 @@
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H15" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="I15" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="I15" s="4" t="n">
-        <v>50</v>
-      </c>
       <c r="J15" s="4" t="n">
-        <v>39.99174507130462</v>
+        <v>65.08260145047174</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.0229072122118197</v>
+        <v>0</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.014159066720345</v>
+        <v>0.3128789884849992</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-10.00415359792669</v>
+        <v>1.443488052737651</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>47.61507088797433</v>
+        <v>5.971429007393973</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>266.8198460170201</v>
+        <v>93.05714198521206</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>552.5102713448662</v>
+        <v>128.8857160295759</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
@@ -1695,7 +1777,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 3M return; Positive 6M return</t>
+          <t>Above 200 SMA; Positive 1M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
         </is>
       </c>
       <c r="T15" s="4" t="inlineStr"/>
@@ -1703,21 +1785,21 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Internet/E-Commerce</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>247.3099975585937</v>
+        <v>18.56500053405762</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>67</v>
@@ -1737,25 +1819,25 @@
         <v>75</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>67.81157428603623</v>
+        <v>62.08528783568838</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.0026901592563831</v>
+        <v>0.0044125718372439</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.685952527362262</v>
+        <v>0.621015908503146</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.780135958077288</v>
+        <v>0.0332653298772992</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>7.574996948242188</v>
+        <v>0.9414285932268416</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>235.9475021362304</v>
+        <v>16.68214334760393</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>270.0349884033203</v>
+        <v>22.33071490696499</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
@@ -1765,7 +1847,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>Above 200 SMA; Positive 1M return; Positive 3M return; MACD improving; RSI in momentum zone</t>
+          <t>Above 50 SMA; Positive 1M return; Positive 3M return; MACD improving; RSI in momentum zone</t>
         </is>
       </c>
       <c r="T16" s="4" t="inlineStr"/>
@@ -1773,7 +1855,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1783,14 +1865,14 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>421.5799865722656</v>
+        <v>238.8999938964844</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
@@ -1798,34 +1880,34 @@
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>50</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>37.838400646266</v>
+        <v>41.32581837733308</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.0006679828548723</v>
+        <v>0.06596166699561611</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.038906674058124</v>
+        <v>0.2471155973482561</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.711786865119478</v>
+        <v>-4.654773997876911</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>21.50642830984933</v>
+        <v>26.78535788399833</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>389.3203441074916</v>
+        <v>185.3292781284877</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>486.0992715018136</v>
+        <v>346.0414254324777</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
@@ -1835,7 +1917,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return</t>
+          <t>Above 50 SMA; Above 200 SMA; Positive 3M return; Positive 6M return</t>
         </is>
       </c>
       <c r="T17" s="4" t="inlineStr"/>
@@ -1843,12 +1925,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Data Centers</t>
+          <t>Data Storage</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1857,10 +1939,10 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>305.8699951171875</v>
+        <v>879.0700073242188</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
@@ -1868,34 +1950,34 @@
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>50</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>37.27464274525995</v>
+        <v>37.90452722844881</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.0217022618956923</v>
+        <v>0.0451049293978258</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.5960186512249169</v>
+        <v>0.4228736150835138</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.1480541656201379</v>
+        <v>-15.18710314343369</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>23.01642935616629</v>
+        <v>84.29928588867188</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>271.3453510829381</v>
+        <v>752.6210784912109</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>374.9192831856864</v>
+        <v>1131.967864990234</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
@@ -1905,94 +1987,90 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return</t>
+          <t>Above 50 SMA; Above 200 SMA; Positive 3M return; Positive 6M return</t>
         </is>
       </c>
       <c r="T18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>937</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>421.5050048828125</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="H19" s="5" t="n">
+      <c r="G19" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="H19" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="I19" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="J19" s="5" t="n">
-        <v>32.2591555067534</v>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>-0.0513632068007362</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>0.6484706647892666</v>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v>-28.83193491040208</v>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v>97.98501586914062</v>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v>741.0299682617188</v>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v>1328.940063476562</v>
-      </c>
-      <c r="Q19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="5" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 3M return; Positive 6M return</t>
-        </is>
-      </c>
-      <c r="T19" s="5" t="inlineStr">
-        <is>
-          <t>RSI weak</t>
-        </is>
-      </c>
+      <c r="J19" s="4" t="n">
+        <v>45.29803446596495</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>0.0220361706931489</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0.629088124181334</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>-4.135715765307372</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>19.97285679408482</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>391.5457196916853</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>481.423575265067</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>Above 200 SMA; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>CBOE</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Internet/E-Commerce</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2001,10 +2079,10 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>277.1300048828125</v>
+        <v>246.1929016113281</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
@@ -2015,31 +2093,31 @@
         <v>40</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>75</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>63.08948813870285</v>
+        <v>64.89615497050171</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.0012683117417138</v>
+        <v>-0.0071974396379796</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.9370039155890588</v>
+        <v>0.2683335641644078</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>5.61249043240821</v>
+        <v>1.658591598998686</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>12.01285443987165</v>
+        <v>7.47785404750279</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>259.110723223005</v>
+        <v>234.9761205400739</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>313.1685682024274</v>
+        <v>268.6264637538364</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
@@ -2049,7 +2127,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>Above 200 SMA; Positive 6M return; MACD improving; RSI in momentum zone</t>
+          <t>Above 200 SMA; Positive 1M return; MACD improving; RSI in momentum zone</t>
         </is>
       </c>
       <c r="T20" s="4" t="inlineStr"/>
@@ -2057,24 +2135,24 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>CELC</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Data Centers</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>103.7900009155273</v>
+        <v>302.7901000976562</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
@@ -2085,31 +2163,31 @@
         <v>40</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>64.40748321374801</v>
+        <v>45.38102772596008</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.008180004348712199</v>
+        <v>0.031582057136426</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8319020612963752</v>
+        <v>0.3054586464007768</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.911196160245703</v>
+        <v>-0.8175126293686956</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>6.056072235107422</v>
+        <v>21.269287109375</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>91.6778564453125</v>
+        <v>270.8861694335937</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>128.014289855957</v>
+        <v>366.5979614257813</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
@@ -2119,7 +2197,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>Above 200 SMA; Positive 1M return; MACD improving; RSI in momentum zone</t>
+          <t>Above 200 SMA; Positive 6M return; RSI in momentum zone</t>
         </is>
       </c>
       <c r="T21" s="4" t="inlineStr"/>
@@ -2141,7 +2219,7 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>298.989990234375</v>
+        <v>282.2300109863281</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>53</v>
@@ -2161,25 +2239,25 @@
         <v>50</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>25.12013387453341</v>
+        <v>28.30257054769397</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.0369832753978448</v>
+        <v>0.0376936349020097</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.4698277360705851</v>
+        <v>0.507640731819666</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-9.368367243321137</v>
+        <v>-10.03311904104094</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>30.13700212751116</v>
+        <v>29.38128662109375</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>238.7159859793527</v>
+        <v>223.4674377441407</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>419.5379987444196</v>
+        <v>399.7551574707031</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>0</v>
@@ -2215,7 +2293,7 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>217.5299987792969</v>
+        <v>222.8399963378907</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>53</v>
@@ -2235,25 +2313,25 @@
         <v>50</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>26.81350318140036</v>
+        <v>33.59411998846861</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>-0.0298121320218837</v>
+        <v>0.0645198535414377</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.560431924401771</v>
+        <v>0.2599507294431511</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-9.60956168128553</v>
+        <v>-9.122317745159036</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>22.82714407784598</v>
+        <v>21.60285949707031</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>183.2892826625279</v>
+        <v>190.4357070922852</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>286.0114310128348</v>
+        <v>287.6485748291016</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>0</v>
@@ -2275,21 +2353,21 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>AI Infrastructure</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>103.120002746582</v>
+        <v>196.7700042724609</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>53</v>
@@ -2309,25 +2387,25 @@
         <v>50</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>23.43354907791833</v>
+        <v>30.35052655812525</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>-0.0351419620325085</v>
+        <v>0.0310198990532244</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.7611815955726389</v>
+        <v>0.5703496860734236</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>-3.642499733942029</v>
+        <v>-6.923687481942226</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>10.03500039236886</v>
+        <v>25.34157235281808</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>88.06750215802876</v>
+        <v>146.0868595668248</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>133.2250039236886</v>
+        <v>298.1362936837332</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>0</v>
@@ -2349,12 +2427,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Data Storage</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2363,7 +2441,7 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>860.6599731445312</v>
+        <v>106.75</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>53</v>
@@ -2383,25 +2461,25 @@
         <v>50</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>33.24526766433529</v>
+        <v>30.70294698798626</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>-0.0447525650500693</v>
+        <v>0.0469355722360184</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.9326165149712228</v>
+        <v>0.4121587629902415</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-17.58862389405815</v>
+        <v>-3.45759544953356</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>88.97071620396206</v>
+        <v>9.479286193847656</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>727.2038988385882</v>
+        <v>92.53107070922852</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>1127.572121756417</v>
+        <v>135.187858581543</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>0</v>
@@ -2421,100 +2499,96 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>NBIS</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>AI Infrastructure</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>210.509994506836</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>CBOE</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>275.4800109863281</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="G26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="I26" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="I26" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>31.19082085488327</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>-0.0316867363918898</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>0.5987661019638217</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>-6.66147091221397</v>
-      </c>
-      <c r="N26" s="5" t="n">
-        <v>26.59443010602678</v>
-      </c>
-      <c r="O26" s="5" t="n">
-        <v>157.3211342947824</v>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>316.8877149309432</v>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="5" t="inlineStr">
-        <is>
-          <t>Above 200 SMA; Positive 3M return; Positive 6M return</t>
-        </is>
-      </c>
-      <c r="T26" s="5" t="inlineStr">
-        <is>
-          <t>RSI weak</t>
-        </is>
-      </c>
+      <c r="J26" s="4" t="n">
+        <v>61.14814244093061</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>-0.0092015237095138</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>0.1907551761678488</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>5.867915420958891</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>11.86785343715123</v>
+      </c>
+      <c r="O26" s="4" t="n">
+        <v>257.6782308306013</v>
+      </c>
+      <c r="P26" s="4" t="n">
+        <v>311.0835712977818</v>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="4" t="inlineStr">
+        <is>
+          <t>Positive 6M return; MACD improving; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Electric Vehicles</t>
+          <t>Space</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>394.760009765625</v>
+        <v>25.54999923706055</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
@@ -2522,34 +2596,34 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>47.30190854550064</v>
+        <v>41.0456714719076</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.0077251921194358</v>
+        <v>0.0084746235925221</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.6680783600026209</v>
+        <v>0.1843132663587727</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.3816312784934397</v>
+        <v>-0.0625168789717189</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>19.89071219308036</v>
+        <v>2.366592815944127</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>364.9239414760045</v>
+        <v>20.81681360517229</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>454.4321463448661</v>
+        <v>35.01637050083706</v>
       </c>
       <c r="Q27" s="4" t="n">
         <v>0</v>
@@ -2559,7 +2633,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>Positive 3M return; MACD improving; RSI in momentum zone</t>
+          <t>Above 200 SMA; Positive 6M return</t>
         </is>
       </c>
       <c r="T27" s="4" t="inlineStr"/>
@@ -2567,7 +2641,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2581,10 +2655,10 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>25.95999908447266</v>
+        <v>79.56500244140625</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
@@ -2595,31 +2669,31 @@
         <v>40</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>50</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>41.46933662967547</v>
+        <v>37.83339740394094</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.0034549003924671</v>
+        <v>0.0264563885114627</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.4293128861127736</v>
+        <v>0.3523206887758023</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.0149246408257801</v>
+        <v>-1.397199623754095</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.413428579057966</v>
+        <v>7.732856750488281</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>21.13314192635672</v>
+        <v>64.09928894042969</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>35.61371340070452</v>
+        <v>110.4964294433594</v>
       </c>
       <c r="Q28" s="4" t="n">
         <v>0</v>
@@ -2629,7 +2703,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>Above 200 SMA; Positive 6M return</t>
+          <t>Above 200 SMA; Positive 3M return</t>
         </is>
       </c>
       <c r="T28" s="4" t="inlineStr"/>
@@ -2637,230 +2711,222 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>KYTX</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Electric Vehicles</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>395.7851867675781</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>54.21191253815941</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>0.0109940121352903</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>0.2955344232116517</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>-0.0693916780113828</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>18.56714085170201</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>367.9344754900251</v>
+      </c>
+      <c r="P29" s="4" t="n">
+        <v>451.4866093226842</v>
+      </c>
+      <c r="Q29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="4" t="inlineStr">
+        <is>
+          <t>Positive 3M return; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SOUN</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>AI Software</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
-        <v>7.769999980926514</v>
-      </c>
-      <c r="E29" s="4" t="n">
+      <c r="D30" s="4" t="n">
+        <v>6.764999866485596</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="4" t="n">
+      <c r="G30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>45.20795488517063</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>0.0017678661083915</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>1.851830814176953</v>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>-0.0068890358413925</v>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v>0.703214134488787</v>
-      </c>
-      <c r="O29" s="4" t="n">
-        <v>6.363571711948939</v>
-      </c>
-      <c r="P29" s="4" t="n">
-        <v>10.58285651888166</v>
-      </c>
-      <c r="Q29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="4" t="inlineStr">
-        <is>
-          <t>Volume surge; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>SMCI</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>AI Infrastructure</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="J30" s="4" t="n">
+        <v>56.98924378337604</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>-0.0154083063419491</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0.5741557411802292</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>0.0666394523638215</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>0.4006429399762835</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>5.963713986533029</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>8.367571626390729</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="4" t="inlineStr">
+        <is>
+          <t>MACD improving; RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ASTS</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Space/Telecom</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D30" s="5" t="n">
-        <v>27.65999984741211</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="D31" s="4" t="n">
+        <v>69.16999816894531</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="I30" s="5" t="n">
+      <c r="G31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="J30" s="5" t="n">
-        <v>22.68907596697776</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>-0.0236665520640497</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>0.4081000325851083</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>-0.1129581202809464</v>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>1.90642820085798</v>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v>23.84714344569615</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>35.28571265084403</v>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="5" t="inlineStr">
-        <is>
-          <t>Positive 3M return</t>
-        </is>
-      </c>
-      <c r="T30" s="5" t="inlineStr">
-        <is>
-          <t>RSI weak</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>IONQ</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Quantum Computing</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>38.88000106811523</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>15.99020298115008</v>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>-0.0184321256247612</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>0.8152458403022232</v>
-      </c>
-      <c r="M31" s="5" t="n">
-        <v>-1.449196603544823</v>
-      </c>
-      <c r="N31" s="5" t="n">
-        <v>3.97057124546596</v>
-      </c>
-      <c r="O31" s="5" t="n">
-        <v>30.93885857718331</v>
-      </c>
-      <c r="P31" s="5" t="n">
-        <v>54.76228604997908</v>
-      </c>
-      <c r="Q31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" s="5" t="inlineStr">
-        <is>
-          <t>Positive 3M return</t>
-        </is>
-      </c>
-      <c r="T31" s="5" t="inlineStr">
-        <is>
-          <t>RSI weak</t>
-        </is>
-      </c>
+      <c r="J31" s="4" t="n">
+        <v>46.62654509530972</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>0.0334417645102432</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>0.275152457062168</v>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>-0.7787341967854466</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>6.955285753522601</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>55.25942666190011</v>
+      </c>
+      <c r="P31" s="4" t="n">
+        <v>96.99114118303572</v>
+      </c>
+      <c r="Q31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="4" t="inlineStr">
+        <is>
+          <t>RSI in momentum zone</t>
+        </is>
+      </c>
+      <c r="T31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Quantum Computing</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -2869,7 +2935,7 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>76.73000335693359</v>
+        <v>39.0099983215332</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>31</v>
@@ -2889,25 +2955,25 @@
         <v>50</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>32.22155183233293</v>
+        <v>16.64305219071599</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.0141905418668198</v>
+        <v>0.0298353862022756</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.6604898529491945</v>
+        <v>0.3104873615510589</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>-1.60128212643402</v>
+        <v>-1.455271152931205</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>7.806785583496094</v>
+        <v>3.701071330479213</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>61.11643218994141</v>
+        <v>31.60785566057477</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>107.957145690918</v>
+        <v>53.81428364345005</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>0</v>
@@ -2927,84 +2993,88 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>SOUN</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>AI Software</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n">
-        <v>6.489999771118164</v>
-      </c>
-      <c r="E33" s="4" t="n">
+      <c r="D33" s="5" t="n">
+        <v>27.84000015258789</v>
+      </c>
+      <c r="E33" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>42.1686670849046</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>-0.0045180321648213</v>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>1.042917418281125</v>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v>0.0561779742976243</v>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v>0.4056429181780134</v>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v>5.678713934762137</v>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v>8.112571443830218</v>
-      </c>
-      <c r="Q33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" s="4" t="inlineStr">
-        <is>
-          <t>MACD improving</t>
-        </is>
-      </c>
-      <c r="T33" s="4" t="inlineStr"/>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>27.75974156663924</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0.0112075006381963</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>0.200730939013303</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>-0.0335603812894813</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>1.774999754769462</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>24.29000064304897</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>34.93999917166574</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <t>Positive 3M return</t>
+        </is>
+      </c>
+      <c r="T33" s="5" t="inlineStr">
+        <is>
+          <t>RSI weak</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>SKHY</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Uranium/Nuclear Energy</t>
+          <t>High Yield ETF</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -3013,10 +3083,10 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>90.1999969482422</v>
+        <v>184.4900054931641</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
@@ -3032,26 +3102,20 @@
       <c r="I34" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="J34" s="5" t="n">
-        <v>18.63144679070228</v>
-      </c>
+      <c r="J34" s="5" t="inlineStr"/>
       <c r="K34" s="5" t="n">
-        <v>-0.0165641876578346</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>1.909541795756696</v>
-      </c>
+        <v>0.0951078537291295</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="n">
-        <v>-0.7934742332941171</v>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v>4.847142355782645</v>
-      </c>
+        <v>0.5223382795505496</v>
+      </c>
+      <c r="N34" s="5" t="inlineStr"/>
       <c r="O34" s="5" t="n">
-        <v>82.92928341456823</v>
+        <v>169.730805053711</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>104.7414240155901</v>
+        <v>214.0084063720703</v>
       </c>
       <c r="Q34" s="5" t="n">
         <v>0</v>
@@ -3061,24 +3125,24 @@
       </c>
       <c r="S34" s="5" t="inlineStr">
         <is>
-          <t>Volume surge</t>
+          <t>MACD improving</t>
         </is>
       </c>
       <c r="T34" s="5" t="inlineStr">
         <is>
-          <t>RSI weak</t>
+          <t>Missing volume trend; Missing ATR; Missing RSI</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>ASTS</t>
+          <t>KYTX</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Space/Telecom</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3087,7 +3151,7 @@
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>67.58000183105469</v>
+        <v>7.804999828338623</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>24</v>
@@ -3107,25 +3171,25 @@
         <v>50</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>44.76385902437732</v>
+        <v>44.25022554353953</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.0180032692351115</v>
+        <v>0.018661516252568</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.5578530772922595</v>
+        <v>0.5597299361658986</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.7205249641778009</v>
+        <v>-0.07578355406954621</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>7.066000257219587</v>
+        <v>0.6941427503313337</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>53.44800131661552</v>
+        <v>6.416714327675956</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>95.84400285993304</v>
+        <v>10.58157082966396</v>
       </c>
       <c r="Q35" s="4" t="n">
         <v>0</v>
@@ -3139,24 +3203,24 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>SKHY</t>
+          <t>LUNR</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>High Yield ETF</t>
+          <t>Space</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>153.5099945068359</v>
+        <v>15.13000011444092</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -3172,20 +3236,26 @@
       <c r="I36" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="n">
+        <v>24.01784938056713</v>
+      </c>
       <c r="K36" s="5" t="n">
-        <v>-0.0916016897377034</v>
-      </c>
-      <c r="L36" s="5" t="inlineStr"/>
+        <v>0.0323432829789085</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>0.3137890375200967</v>
+      </c>
       <c r="M36" s="5" t="n">
-        <v>-0.9253561253561428</v>
-      </c>
-      <c r="N36" s="5" t="inlineStr"/>
+        <v>-0.210941478312526</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>1.623785904475621</v>
+      </c>
       <c r="O36" s="5" t="n">
-        <v>141.2291949462891</v>
+        <v>11.88242830548968</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>178.0715936279297</v>
+        <v>21.6251437323434</v>
       </c>
       <c r="Q36" s="5" t="n">
         <v>0</v>
@@ -3196,28 +3266,28 @@
       <c r="S36" s="5" t="inlineStr"/>
       <c r="T36" s="5" t="inlineStr">
         <is>
-          <t>Missing volume trend; Missing ATR; Missing RSI</t>
+          <t>RSI weak</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>LUNR</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Uranium/Nuclear Energy</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>15.14999961853027</v>
+        <v>91.44000244140624</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>20</v>
@@ -3237,25 +3307,25 @@
         <v>50</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>22.01308672444488</v>
+        <v>16.83770701730374</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.0085500982745466</v>
+        <v>0.0177384274683925</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.7169100399332081</v>
+        <v>0.7312825584700605</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>-0.2400474448421516</v>
+        <v>-0.7804217666388213</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>1.668785776410784</v>
+        <v>4.48357173374721</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>11.8124280657087</v>
+        <v>84.71464484078543</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>21.82514272417341</v>
+        <v>104.8907176426479</v>
       </c>
       <c r="Q37" s="5" t="n">
         <v>0</v>
@@ -3287,7 +3357,7 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>8.350000381469727</v>
+        <v>8.573800086975098</v>
       </c>
       <c r="E38" s="5" t="n">
         <v>20</v>
@@ -3307,25 +3377,25 @@
         <v>50</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>14.49631933236232</v>
+        <v>20.79309128159542</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.0188053182534636</v>
+        <v>0.0299401183926648</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>1.170380854998263</v>
+        <v>0.4296593404421607</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>-0.1257283657885731</v>
+        <v>-0.1159333540085283</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>0.7357140268598285</v>
+        <v>0.6735711097717285</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>6.87857232775007</v>
+        <v>7.226657867431641</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>11.29285648890904</v>
+        <v>11.26808452606201</v>
       </c>
       <c r="Q38" s="5" t="n">
         <v>0</v>
@@ -3357,7 +3427,7 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>45.81000137329102</v>
+        <v>45.81999969482422</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>20</v>
@@ -3377,25 +3447,25 @@
         <v>50</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>21.80922241156196</v>
+        <v>23.09511958709545</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>-0.0231319813452317</v>
+        <v>0.0251036384349932</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.7994197935035359</v>
+        <v>0.281522694219697</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>-0.3462640816307631</v>
+        <v>-0.3513657399980205</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>3.72428594316755</v>
+        <v>3.439085824148996</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>38.36142948695591</v>
+        <v>38.94182804652623</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>60.70714514596122</v>
+        <v>59.5763429914202</v>
       </c>
       <c r="Q39" s="5" t="n">
         <v>0</v>
@@ -3427,7 +3497,7 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>7.480000019073486</v>
+        <v>7.755000114440918</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>20</v>
@@ -3447,25 +3517,25 @@
         <v>50</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>19.79695935229539</v>
+        <v>27.01664839096489</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.0233160405739019</v>
+        <v>0.0100267124430337</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>1.305743056025744</v>
+        <v>0.6217934494930202</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>-0.1257187896488844</v>
+        <v>-0.1036413462820309</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>0.5634285722460065</v>
+        <v>0.5577142919812884</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>6.353142874581473</v>
+        <v>6.639571530478341</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>9.733714308057513</v>
+        <v>9.985857282366071</v>
       </c>
       <c r="Q40" s="5" t="n">
         <v>0</v>
@@ -3532,10 +3602,10 @@
         <v>0.74662492</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>16.19000053405762</v>
+        <v>17.1200008392334</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>12.08785785354073</v>
+        <v>12.78221925699257</v>
       </c>
     </row>
     <row r="3">
@@ -3548,10 +3618,10 @@
         <v>0.05285969</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>352.510009765625</v>
+        <v>356.6700134277344</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>18.63356983810791</v>
+        <v>18.85346634208588</v>
       </c>
     </row>
     <row r="4">
@@ -3564,10 +3634,10 @@
         <v>0.6115135</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>18.1299991607666</v>
+        <v>18.56500053405762</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>11.08673924179745</v>
+        <v>11.35274845408344</v>
       </c>
     </row>
     <row r="5">
@@ -3580,10 +3650,10 @@
         <v>0.02721351</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>394.760009765625</v>
+        <v>395.7851867675781</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>10.74280547335693</v>
+        <v>10.77070413795136</v>
       </c>
     </row>
   </sheetData>
@@ -3792,7 +3862,7 @@
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
@@ -3911,60 +3981,60 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>362.0499877929688</v>
+        <v>369.8450012207031</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>328.4705993652344</v>
+        <v>331.9726992797852</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>200.4233501052856</v>
+        <v>201.2462250900268</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>39.99174507130462</v>
+        <v>46.14959731343965</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>-0.0147495398528575</v>
+        <v>0.0073403441890798</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.170628566608762</v>
+        <v>1.167907315292186</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>1.226492752192518</v>
+        <v>1.143159213789976</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>18.87209311075537</v>
+        <v>14.88644807632801</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>28.87624670868206</v>
+        <v>26.07828698221125</v>
       </c>
       <c r="K2" s="6" t="n">
+        <v>-11.19183890588324</v>
+      </c>
+      <c r="L2" s="6" t="n">
         <v>-10.00415359792669</v>
       </c>
-      <c r="L2" s="6" t="n">
-        <v>-6.89888868607181</v>
-      </c>
       <c r="M2" s="6" t="n">
-        <v>6277600</v>
+        <v>1556406</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>6189956</v>
+        <v>6118044.12</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1.014159066720345</v>
+        <v>0.2543960078535687</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-0.0229072122118197</v>
+        <v>0.082723417254077</v>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="R2" s="6" t="n">
-        <v>47.61507088797433</v>
+        <v>46.42792184012277</v>
       </c>
       <c r="S2" s="6" t="n">
-        <v>0.1315151843485272</v>
+        <v>0.1255334577644248</v>
       </c>
       <c r="T2" s="6" t="inlineStr">
         <is>
@@ -3979,60 +4049,60 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>534.3900146484375</v>
+        <v>555.3699951171875</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>485.8411999511719</v>
+        <v>489.8588000488281</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>289.53119972229</v>
+        <v>291.5036496734619</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>47.25110136960278</v>
+        <v>55.86565004537624</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.0940526180638816</v>
+        <v>0.0856187563107262</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.165012399968324</v>
+        <v>1.177323790214419</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1.630260468891019</v>
+        <v>1.674033360242601</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>17.03245671433649</v>
+        <v>17.36325304505715</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>20.60987949887553</v>
+        <v>19.96055420811186</v>
       </c>
       <c r="K3" s="6" t="n">
+        <v>-2.597301163054709</v>
+      </c>
+      <c r="L3" s="6" t="n">
         <v>-3.577422784539042</v>
       </c>
-      <c r="L3" s="6" t="n">
-        <v>-3.005596247274948</v>
-      </c>
       <c r="M3" s="6" t="n">
-        <v>22890700</v>
+        <v>14011669</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>34413774</v>
+        <v>33851701.38</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.665160990480149</v>
+        <v>0.4139132873326793</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>-0.0365484488215595</v>
+        <v>0.0624019610194614</v>
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="R3" s="6" t="n">
-        <v>38.40929303850447</v>
+        <v>38.05143519810268</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0.071875020089537</v>
+        <v>0.0685154681251253</v>
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
@@ -4047,49 +4117,49 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>247.3099975585937</v>
+        <v>246.1929016113281</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>253.7199996948243</v>
+        <v>253.3426577758789</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>233.4662000274658</v>
+        <v>233.5961145019532</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>67.81157428603623</v>
+        <v>64.89615497050171</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0240155818959022</v>
+        <v>0.0320389790894786</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.030930835748985</v>
+        <v>-0.0113529138728935</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.0002829950797839</v>
+        <v>-0.0011242731691588</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-1.050456348260468</v>
+        <v>-0.7573528075893989</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-2.830592306337756</v>
+        <v>-2.415944406588085</v>
       </c>
       <c r="K4" s="6" t="n">
+        <v>1.658591598998686</v>
+      </c>
+      <c r="L4" s="6" t="n">
         <v>1.780135958077288</v>
       </c>
-      <c r="L4" s="6" t="n">
-        <v>1.752601933393177</v>
-      </c>
       <c r="M4" s="6" t="n">
-        <v>34596500</v>
+        <v>13061792</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>50435706</v>
+        <v>48677443.84</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.685952527362262</v>
+        <v>0.2683335641644078</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-0.0026901592563831</v>
+        <v>-0.0071974396379796</v>
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
@@ -4097,10 +4167,10 @@
         </is>
       </c>
       <c r="R4" s="6" t="n">
-        <v>7.574996948242188</v>
+        <v>7.47785404750279</v>
       </c>
       <c r="S4" s="6" t="n">
-        <v>0.0306295621811547</v>
+        <v>0.030373962850108</v>
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
@@ -4115,49 +4185,49 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>181.1499938964844</v>
+        <v>182.634994506836</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>160.5955996704102</v>
+        <v>160.7940994262695</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>144.1334996414185</v>
+        <v>144.3334746170044</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>53.54415317550977</v>
+        <v>62.44594972357781</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.1582480880170695</v>
+        <v>0.1188127196827621</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.191619450107465</v>
+        <v>0.1830990495801436</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.4740824704710953</v>
+        <v>0.4797844532199173</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5.778986582872136</v>
+        <v>6.016367273637002</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.005723640600515</v>
+        <v>4.407852367207813</v>
       </c>
       <c r="K5" s="6" t="n">
+        <v>1.608514906429189</v>
+      </c>
+      <c r="L5" s="6" t="n">
         <v>1.773262942271622</v>
       </c>
-      <c r="L5" s="6" t="n">
-        <v>1.980736671657304</v>
-      </c>
       <c r="M5" s="6" t="n">
-        <v>9138100</v>
+        <v>3244887</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>10396890</v>
+        <v>10338953.74</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.8789262943053163</v>
+        <v>0.3138506159908594</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-0.0037174117418728</v>
+        <v>0.0151807899125376</v>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
@@ -4165,10 +4235,10 @@
         </is>
       </c>
       <c r="R5" s="6" t="n">
-        <v>10.84078325544085</v>
+        <v>10.46220506940569</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>0.0598442374866193</v>
+        <v>0.0572847777484073</v>
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
@@ -4183,60 +4253,60 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>298.989990234375</v>
+        <v>282.2300109863281</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>311.1417984008789</v>
+        <v>312.5799984741211</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>182.1271249771118</v>
+        <v>182.8167750167847</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>25.12013387453341</v>
+        <v>28.30257054769397</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-0.1263478343916499</v>
+        <v>-0.2588692187817298</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.8973853709871724</v>
+        <v>0.7505893118060929</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1.674568277893681</v>
+        <v>1.53940986626112</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-4.89801759233734</v>
+        <v>-8.071049150317378</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>4.470349650983797</v>
+        <v>1.962069890723562</v>
       </c>
       <c r="K6" s="6" t="n">
+        <v>-10.03311904104094</v>
+      </c>
+      <c r="L6" s="6" t="n">
         <v>-9.368367243321137</v>
       </c>
-      <c r="L6" s="6" t="n">
-        <v>-9.295743678605769</v>
-      </c>
       <c r="M6" s="6" t="n">
-        <v>5270100</v>
+        <v>5673363</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>11217090</v>
+        <v>11175941.26</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4698277360705851</v>
+        <v>0.507640731819666</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-0.0369832753978448</v>
+        <v>0.0376936349020097</v>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="R6" s="6" t="n">
-        <v>30.13700212751116</v>
+        <v>29.38128662109375</v>
       </c>
       <c r="S6" s="6" t="n">
-        <v>0.1007960236524543</v>
+        <v>0.1041040480366102</v>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
@@ -4251,60 +4321,60 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>67.58000183105469</v>
+        <v>69.16999816894531</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>86.13120018005371</v>
+        <v>86.03660011291504</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>82.99554985046387</v>
+        <v>83.06889984130859</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>44.76385902437732</v>
+        <v>46.62654509530972</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.3072980368775975</v>
+        <v>-0.1606601735809845</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.3171668081487514</v>
+        <v>-0.2190358088825034</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.308078190867192</v>
+        <v>-0.2969814147979083</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-4.560100006332078</v>
+        <v>-4.812992788136086</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-3.839575042154277</v>
+        <v>-4.034258591350639</v>
       </c>
       <c r="K7" s="6" t="n">
+        <v>-0.7787341967854466</v>
+      </c>
+      <c r="L7" s="6" t="n">
         <v>-0.7205249641778009</v>
       </c>
-      <c r="L7" s="6" t="n">
-        <v>-0.3496537910423321</v>
-      </c>
       <c r="M7" s="6" t="n">
-        <v>12983400</v>
+        <v>6364689</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>23273870</v>
+        <v>23131499.78</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5578530772922595</v>
+        <v>0.275152457062168</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-0.0180032692351115</v>
+        <v>0.0334417645102432</v>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.066000257219587</v>
+        <v>6.955285753522601</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>0.1045575623819025</v>
+        <v>0.1005535049536152</v>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
@@ -4319,60 +4389,60 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>384.0499877929688</v>
+        <v>394.5700073242188</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>406.0224005126953</v>
+        <v>405.5652008056641</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>362.6720501708984</v>
+        <v>362.9483502197265</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>46.76644111895504</v>
+        <v>55.83900718527268</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.0039422660019606</v>
+        <v>0.0327165172883949</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.0113232068280941</v>
+        <v>0.0362151599063234</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.1132851738817233</v>
+        <v>0.1202692055785799</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-4.49748843644312</v>
+        <v>-3.37577143267157</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-7.53636120941328</v>
+        <v>-6.704243254064938</v>
       </c>
       <c r="K8" s="6" t="n">
+        <v>3.328471821393368</v>
+      </c>
+      <c r="L8" s="6" t="n">
         <v>3.038872772970159</v>
       </c>
-      <c r="L8" s="6" t="n">
-        <v>3.503419447292556</v>
-      </c>
       <c r="M8" s="6" t="n">
-        <v>21243800</v>
+        <v>9522151</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>27672044</v>
+        <v>27426055.02</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.7676989816870774</v>
+        <v>0.34719360816042</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-0.0162261925008566</v>
+        <v>0.030087289573326</v>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="R8" s="6" t="n">
-        <v>15.15999494280134</v>
+        <v>15.00356619698661</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>0.0394740149060327</v>
+        <v>0.038025105604791</v>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
@@ -4387,49 +4457,49 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>8.100000381469727</v>
+        <v>7.710000038146973</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>5.764399991035462</v>
+        <v>5.822799992561341</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4.017199999094009</v>
+        <v>4.04539999961853</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>58.05825616673116</v>
+        <v>50.38910466129628</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.4260564482867148</v>
+        <v>0.3916967673711176</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.8925233608417111</v>
+        <v>0.7364864726991935</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>1.00495060840409</v>
+        <v>0.8056206258984668</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.6675626645364767</v>
+        <v>0.6116745928918901</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.7625105942770996</v>
+        <v>0.7323433940000577</v>
       </c>
       <c r="K9" s="6" t="n">
+        <v>-0.1206688011081675</v>
+      </c>
+      <c r="L9" s="6" t="n">
         <v>-0.0949479297406228</v>
       </c>
-      <c r="L9" s="6" t="n">
-        <v>-0.0967705380809897</v>
-      </c>
       <c r="M9" s="6" t="n">
-        <v>7966000</v>
+        <v>3380823</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>7916118</v>
+        <v>7806252.46</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.006301320925231</v>
+        <v>0.4330916809728698</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-0.0137844778510634</v>
+        <v>-0.0049382666628676</v>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
@@ -4437,10 +4507,10 @@
         </is>
       </c>
       <c r="R9" s="6" t="n">
-        <v>0.7777856077466693</v>
+        <v>0.7386070660182408</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>0.0960229100144242</v>
+        <v>0.0957985813701446</v>
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
@@ -4455,49 +4525,49 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>16.19000053405762</v>
+        <v>17.1200008392334</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>9.651000032424928</v>
+        <v>9.907800045013428</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.520349990129471</v>
+        <v>6.553649994134903</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>79.95545838351569</v>
+        <v>75.1381247005498</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1.116339912709505</v>
+        <v>1.161616246756966</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>3.612535777221136</v>
+        <v>3.782123241363253</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>2.238000106811524</v>
+        <v>2.324271946059441</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>2.387645053357646</v>
+        <v>2.35291019650346</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>2.173863412240089</v>
+        <v>2.209672769092763</v>
       </c>
       <c r="K10" s="6" t="n">
+        <v>0.1432374274106971</v>
+      </c>
+      <c r="L10" s="6" t="n">
         <v>0.2137816411175577</v>
       </c>
-      <c r="L10" s="6" t="n">
-        <v>0.3715229171689866</v>
-      </c>
       <c r="M10" s="6" t="n">
-        <v>2296300</v>
+        <v>722140</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>3915572</v>
+        <v>3922696.8</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.586453269151991</v>
+        <v>0.1840927394643399</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.0056818397330839</v>
+        <v>0.0098826338563442</v>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
@@ -4505,10 +4575,10 @@
         </is>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.69085727419172</v>
+        <v>1.499500070299421</v>
       </c>
       <c r="S10" s="6" t="n">
-        <v>0.1044383705012731</v>
+        <v>0.0875876166351032</v>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
@@ -4523,49 +4593,49 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>277.1300048828125</v>
+        <v>275.4800109863281</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>301.489001159668</v>
+        <v>300.9968014526367</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>275.8806508636475</v>
+        <v>276.0421009063721</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>63.08948813870285</v>
+        <v>61.14814244093061</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.0634335566097992</v>
+        <v>-0.0658844814841987</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.0771561233832949</v>
+        <v>-0.0840232386157003</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.0620041843989049</v>
+        <v>0.0436034765783919</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-8.389997269254479</v>
+        <v>-6.667593425464077</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-14.00248770166269</v>
+        <v>-12.53550884642297</v>
       </c>
       <c r="K11" s="6" t="n">
+        <v>5.867915420958891</v>
+      </c>
+      <c r="L11" s="6" t="n">
         <v>5.61249043240821</v>
       </c>
-      <c r="L11" s="6" t="n">
-        <v>4.77123635252852</v>
-      </c>
       <c r="M11" s="6" t="n">
-        <v>1465000</v>
+        <v>295981</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>1563494</v>
+        <v>1551627.62</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.9370039155890588</v>
+        <v>0.1907551761678488</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-0.0012683117417138</v>
+        <v>-0.0092015237095138</v>
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
@@ -4573,10 +4643,10 @@
         </is>
       </c>
       <c r="R11" s="6" t="n">
-        <v>12.01285443987165</v>
+        <v>11.86785343715123</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>0.0433473612680497</v>
+        <v>0.0430806336716032</v>
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
@@ -4591,49 +4661,49 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>103.7900009155273</v>
+        <v>105</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>112.6027996826172</v>
+        <v>112.2757997131348</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>100.9755499267578</v>
+        <v>101.2306499290466</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>64.40748321374801</v>
+        <v>65.08260145047174</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.1597944283508272</v>
+        <v>0.1857707101221339</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.1379568139522107</v>
+        <v>-0.1311543125713421</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.0346014430916795</v>
+        <v>0.004688526014293</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.7852899954126684</v>
+        <v>0.6784539010890285</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-1.125906164833035</v>
+        <v>-0.7650341516486222</v>
       </c>
       <c r="K12" s="6" t="n">
+        <v>1.443488052737651</v>
+      </c>
+      <c r="L12" s="6" t="n">
         <v>1.911196160245703</v>
       </c>
-      <c r="L12" s="6" t="n">
-        <v>2.637134413002336</v>
-      </c>
       <c r="M12" s="6" t="n">
-        <v>1257400</v>
+        <v>471634</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>1511476</v>
+        <v>1507400.68</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.8319020612963752</v>
+        <v>0.3128789884849992</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-0.008180004348712199</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
@@ -4641,10 +4711,10 @@
         </is>
       </c>
       <c r="R12" s="6" t="n">
-        <v>6.056072235107422</v>
+        <v>5.971429007393973</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>0.0583492839549769</v>
+        <v>0.0568707524513711</v>
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
@@ -4659,60 +4729,60 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>236.8800048828125</v>
+        <v>238.8999938964844</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>226.1213998413086</v>
+        <v>227.4191998291016</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>161.3880502319336</v>
+        <v>161.835650177002</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>35.03556650730233</v>
+        <v>41.32581837733308</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.1053029304066459</v>
+        <v>-0.0474861599539188</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.7630247380674873</v>
+        <v>0.4976177751878818</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.574790637989232</v>
+        <v>0.5307232824061781</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>7.133377048530008</v>
+        <v>5.393268768153746</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>11.21173626549988</v>
+        <v>10.04804276603066</v>
       </c>
       <c r="K13" s="6" t="n">
+        <v>-4.654773997876911</v>
+      </c>
+      <c r="L13" s="6" t="n">
         <v>-4.078359216969876</v>
       </c>
-      <c r="L13" s="6" t="n">
-        <v>-2.77502469175505</v>
-      </c>
       <c r="M13" s="6" t="n">
-        <v>6717000</v>
+        <v>2139823</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>8705180</v>
+        <v>8659198.460000001</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.7716095474188931</v>
+        <v>0.2471155973482561</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-0.0359595173016396</v>
+        <v>0.06596166699561611</v>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="R13" s="6" t="n">
-        <v>28.31142861502511</v>
+        <v>26.78535788399833</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>0.1195180176943644</v>
+        <v>0.1121195419352101</v>
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
@@ -4727,49 +4797,49 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>352.510009765625</v>
+        <v>356.6700134277344</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>372.7972003173828</v>
+        <v>372.2346008300781</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>319.4152998352051</v>
+        <v>319.9629499053955</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>52.39629178665267</v>
+        <v>58.83340486164004</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.0147021254145659</v>
+        <v>-0.008368492296873699</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.0971025254243502</v>
+        <v>0.07137066926273709</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.0728611921592201</v>
+        <v>0.0747605290523016</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-2.20383870768751</v>
+        <v>-2.155963263926367</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-2.80130271294401</v>
+        <v>-2.672234823140482</v>
       </c>
       <c r="K14" s="6" t="n">
+        <v>0.5162715592141147</v>
+      </c>
+      <c r="L14" s="6" t="n">
         <v>0.5974640052565006</v>
       </c>
-      <c r="L14" s="6" t="n">
-        <v>1.141343376060255</v>
-      </c>
       <c r="M14" s="6" t="n">
-        <v>15836200</v>
+        <v>7415689</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>33032270</v>
+        <v>31739783.78</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.479416037711002</v>
+        <v>0.233640186442379</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>-0.0027716844579075</v>
+        <v>-0.0040282924977889</v>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
@@ -4777,10 +4847,10 @@
         </is>
       </c>
       <c r="R14" s="6" t="n">
-        <v>10.05857195172991</v>
+        <v>9.923573085239957</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>0.0285341456216168</v>
+        <v>0.0278228410341274</v>
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
@@ -4795,60 +4865,60 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>103.120002746582</v>
+        <v>106.75</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>117.1707998657227</v>
+        <v>117.416199798584</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>62.83409996986389</v>
+        <v>63.21174997329712</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>23.43354907791833</v>
+        <v>30.70294698798626</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.1183310229670477</v>
+        <v>-0.1430520971219415</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.5820804274895581</v>
+        <v>0.6729352405982301</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1.263885937953676</v>
+        <v>1.422832425618384</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-1.380027150532328</v>
+        <v>-2.059521728507249</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>2.262472583409701</v>
+        <v>1.398073721026311</v>
       </c>
       <c r="K15" s="6" t="n">
+        <v>-3.45759544953356</v>
+      </c>
+      <c r="L15" s="6" t="n">
         <v>-3.642499733942029</v>
       </c>
-      <c r="L15" s="6" t="n">
-        <v>-3.296169654456531</v>
-      </c>
       <c r="M15" s="6" t="n">
-        <v>100510000</v>
+        <v>53540898</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>132044706</v>
+        <v>129903577.96</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.7611815955726389</v>
+        <v>0.4121587629902415</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>-0.0351419620325085</v>
+        <v>0.0469355722360184</v>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="R15" s="6" t="n">
-        <v>10.03500039236886</v>
+        <v>9.479286193847656</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>0.0973138103674214</v>
+        <v>0.08879893390021221</v>
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
@@ -4863,49 +4933,49 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>38.88000106811523</v>
+        <v>39.0099983215332</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>55.01780014038086</v>
+        <v>54.89560012817383</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>48.86195004463196</v>
+        <v>48.68770003318787</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>15.99020298115008</v>
+        <v>16.64305219071599</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-0.329539576775829</v>
+        <v>-0.3256698470098641</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.3064516387463771</v>
+        <v>0.0908836731696092</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.2137512544336695</v>
+        <v>-0.2343474438196926</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-3.828664268174151</v>
+        <v>-4.198556605793336</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-2.379467664629328</v>
+        <v>-2.74328545286213</v>
       </c>
       <c r="K16" s="6" t="n">
+        <v>-1.455271152931205</v>
+      </c>
+      <c r="L16" s="6" t="n">
         <v>-1.449196603544823</v>
       </c>
-      <c r="L16" s="6" t="n">
-        <v>-1.270452879257462</v>
-      </c>
       <c r="M16" s="6" t="n">
-        <v>23719400</v>
+        <v>8944675</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>29094782</v>
+        <v>28808499.5</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.8152458403022232</v>
+        <v>0.3104873615510589</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.0184321256247612</v>
+        <v>0.0298353862022756</v>
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
@@ -4913,10 +4983,10 @@
         </is>
       </c>
       <c r="R16" s="6" t="n">
-        <v>3.97057124546596</v>
+        <v>3.701071330479213</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>0.1021237432198054</v>
+        <v>0.09487494205905279</v>
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
@@ -4931,49 +5001,49 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>7.769999980926514</v>
+        <v>7.804999828338623</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>8.716799955368042</v>
+        <v>8.696899948120118</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>8.183749969005584</v>
+        <v>8.190574967861176</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>45.20795488517063</v>
+        <v>44.25022554353953</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-0.0127064683718816</v>
+        <v>-0.0310366812371837</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.1812433963830317</v>
+        <v>-0.1661324663862905</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.0661057372682181</v>
+        <v>-0.0516403083276746</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.1189289027810343</v>
+        <v>0.031088496035494</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.1258179386224268</v>
+        <v>0.1068720501050402</v>
       </c>
       <c r="K17" s="6" t="n">
+        <v>-0.07578355406954621</v>
+      </c>
+      <c r="L17" s="6" t="n">
         <v>-0.0068890358413925</v>
       </c>
-      <c r="L17" s="6" t="n">
-        <v>0.1053387520495297</v>
-      </c>
       <c r="M17" s="6" t="n">
-        <v>1956100</v>
+        <v>587420</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1056306</v>
+        <v>1049470.4</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>1.851830814176953</v>
+        <v>0.5597299361658986</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.0017678661083915</v>
+        <v>0.018661516252568</v>
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
@@ -4981,10 +5051,10 @@
         </is>
       </c>
       <c r="R17" s="6" t="n">
-        <v>0.703214134488787</v>
+        <v>0.6941427503313337</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>0.09050374983462139</v>
+        <v>0.088935652222697</v>
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
@@ -4999,49 +5069,49 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1181.869995117188</v>
+        <v>1154</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1093.367601318359</v>
+        <v>1097.755601806641</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>998.5020529174805</v>
+        <v>1000.562803039551</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>63.59330391902413</v>
+        <v>57.41560404426107</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.0180197638358101</v>
+        <v>0.0185348631950572</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.2714431828709958</v>
+        <v>0.2509485094850949</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.1112395445536644</v>
+        <v>0.06753006475485659</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>32.89004314048429</v>
+        <v>27.58219303342866</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>36.35861605354793</v>
+        <v>34.60333144952408</v>
       </c>
       <c r="K18" s="6" t="n">
+        <v>-7.021138416095418</v>
+      </c>
+      <c r="L18" s="6" t="n">
         <v>-3.468572913063639</v>
       </c>
-      <c r="L18" s="6" t="n">
-        <v>-0.8770421350267767</v>
-      </c>
       <c r="M18" s="6" t="n">
-        <v>2069800</v>
+        <v>1213871</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>3324634</v>
+        <v>3184177.42</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.6225647695355339</v>
+        <v>0.3812196495005608</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-0.0071261261474068</v>
+        <v>-0.013419399271567</v>
       </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
@@ -5049,10 +5119,10 @@
         </is>
       </c>
       <c r="R18" s="6" t="n">
-        <v>41.62001255580357</v>
+        <v>41.49965122767857</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>0.0352153897871624</v>
+        <v>0.0359615695213852</v>
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
@@ -5067,60 +5137,60 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>15.14999961853027</v>
+        <v>15.13000011444092</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>27.66040004730225</v>
+        <v>27.45600004196167</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>18.9955750322342</v>
+        <v>19.0212750339508</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>22.01308672444488</v>
+        <v>24.01784938056713</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.5055483054725967</v>
+        <v>-0.4316303667375605</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.3793527360412319</v>
+        <v>-0.3607942515558348</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.1837284453412545</v>
+        <v>-0.2119791920193358</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-3.381335397595574</v>
+        <v>-3.40496480064408</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-3.141287952753423</v>
+        <v>-3.194023322331554</v>
       </c>
       <c r="K19" s="6" t="n">
+        <v>-0.210941478312526</v>
+      </c>
+      <c r="L19" s="6" t="n">
         <v>-0.2400474448421516</v>
       </c>
-      <c r="L19" s="6" t="n">
-        <v>-0.2227528480675804</v>
-      </c>
       <c r="M19" s="6" t="n">
-        <v>10284400</v>
+        <v>4473413</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>14345454</v>
+        <v>14256116.26</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.7169100399332081</v>
+        <v>0.3137890375200967</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-0.0085500982745466</v>
+        <v>0.0323432829789085</v>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.668785776410784</v>
+        <v>1.623785904475621</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.110150879104291</v>
+        <v>0.1073222665032096</v>
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
@@ -5135,60 +5205,60 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>217.5299987792969</v>
+        <v>222.8399963378907</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>232.6888000488281</v>
+        <v>233.8426000976562</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>127.4797001647949</v>
+        <v>128.1934501647949</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>26.81350318140036</v>
+        <v>33.59411998846861</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.2250721192654516</v>
+        <v>-0.2032892863338646</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.6567402416094965</v>
+        <v>0.6650974616230001</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>1.613914871286744</v>
+        <v>1.688382168883447</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-3.204063803227768</v>
+        <v>-4.997399303391035</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>6.405497878057763</v>
+        <v>4.124918441768004</v>
       </c>
       <c r="K20" s="6" t="n">
+        <v>-9.122317745159036</v>
+      </c>
+      <c r="L20" s="6" t="n">
         <v>-9.60956168128553</v>
       </c>
-      <c r="L20" s="6" t="n">
-        <v>-9.135745020112926</v>
-      </c>
       <c r="M20" s="6" t="n">
-        <v>25432700</v>
+        <v>11752122</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>45380534</v>
+        <v>45209036.44</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.560431924401771</v>
+        <v>0.2599507294431511</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-0.0298121320218837</v>
+        <v>0.0645198535414377</v>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="R20" s="6" t="n">
-        <v>22.82714407784598</v>
+        <v>21.60285949707031</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>0.1049379129588747</v>
+        <v>0.09694336677476</v>
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
@@ -5203,60 +5273,60 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>937</v>
+        <v>987.3599853515624</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>907.4182006835938</v>
+        <v>916.8222009277343</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>468.3365003204346</v>
+        <v>472.4647502136231</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>32.2591555067534</v>
+        <v>45.1502141583485</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>-0.0591141367907767</v>
+        <v>0.0058577236232377</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>1.196642923300117</v>
+        <v>1.120345268192729</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1.715233735963033</v>
+        <v>1.854714196925425</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>11.82658795472946</v>
+        <v>9.783608462789855</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>40.65852286513154</v>
+        <v>34.4835399846632</v>
       </c>
       <c r="K21" s="6" t="n">
+        <v>-24.69993152187335</v>
+      </c>
+      <c r="L21" s="6" t="n">
         <v>-28.83193491040208</v>
       </c>
-      <c r="L21" s="6" t="n">
-        <v>-28.47679485729119</v>
-      </c>
       <c r="M21" s="6" t="n">
-        <v>35174600</v>
+        <v>19898479</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>54242392</v>
+        <v>53909273.58</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.6484706647892666</v>
+        <v>0.3691105013773031</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-0.0513632068007362</v>
+        <v>0.0543756800501934</v>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="R21" s="6" t="n">
-        <v>97.98501586914062</v>
+        <v>89.7650146484375</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>0.1045731225924659</v>
+        <v>0.090914171102929</v>
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
@@ -5271,60 +5341,60 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>210.509994506836</v>
+        <v>196.7700042724609</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>222.8711999511719</v>
+        <v>224.0420001220703</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>136.3346254730225</v>
+        <v>136.7523254776001</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>31.19082085488327</v>
+        <v>30.35052655812525</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-0.0527808256677213</v>
+        <v>-0.153167482546069</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.36199532758812</v>
+        <v>0.2150796671974673</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>1.149596587877373</v>
+        <v>0.8333178134310608</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-4.446131681101804</v>
+        <v>-6.439270121315616</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>2.215339231112166</v>
+        <v>0.4844173606266095</v>
       </c>
       <c r="K22" s="6" t="n">
+        <v>-6.923687481942226</v>
+      </c>
+      <c r="L22" s="6" t="n">
         <v>-6.66147091221397</v>
       </c>
-      <c r="L22" s="6" t="n">
-        <v>-7.117179030533046</v>
-      </c>
       <c r="M22" s="6" t="n">
-        <v>10748400</v>
+        <v>10210092</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>17950916</v>
+        <v>17901459.84</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.5987661019638217</v>
+        <v>0.5703496860734236</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-0.0316867363918898</v>
+        <v>0.0310198990532244</v>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="R22" s="6" t="n">
-        <v>26.59443010602678</v>
+        <v>25.34157235281808</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>0.1263333371336114</v>
+        <v>0.1287877816871337</v>
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
@@ -5339,49 +5409,49 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>203.5299987792969</v>
+        <v>211.2200012207031</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>209.0846005249024</v>
+        <v>209.317600402832</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>191.7959504699707</v>
+        <v>191.9672004699707</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>45.3606417209306</v>
+        <v>60.30225678806677</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>-0.0065407154284556</v>
+        <v>0.029387390747845</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.0751148983365332</v>
+        <v>0.07485627767067821</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.1009953375922463</v>
+        <v>0.1421001321097259</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-1.470477138528508</v>
+        <v>-0.6329247329459804</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-2.676673164090676</v>
+        <v>-2.267923477861737</v>
       </c>
       <c r="K23" s="6" t="n">
+        <v>1.634998744915757</v>
+      </c>
+      <c r="L23" s="6" t="n">
         <v>1.206196025562167</v>
       </c>
-      <c r="L23" s="6" t="n">
-        <v>1.243094423058239</v>
-      </c>
       <c r="M23" s="6" t="n">
-        <v>120943800</v>
+        <v>61616072</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>160891548</v>
+        <v>157619085.44</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.7517100898302004</v>
+        <v>0.390917583540066</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-0.0114714322654375</v>
+        <v>0.0229450115312453</v>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
@@ -5389,10 +5459,10 @@
         </is>
       </c>
       <c r="R23" s="6" t="n">
-        <v>6.922855922154018</v>
+        <v>6.863571166992188</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>0.0340139338852991</v>
+        <v>0.0324948921850467</v>
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
@@ -5407,49 +5477,49 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>90.1999969482422</v>
+        <v>91.44000244140624</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>107.2673994445801</v>
+        <v>106.6353994750977</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>104.4071496582031</v>
+        <v>104.4488996887207</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>18.63144679070228</v>
+        <v>16.83770701730374</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>-0.0886127529987983</v>
+        <v>-0.09429473781097281</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.2270779836588432</v>
+        <v>-0.2121316184308715</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.1613982986648418</v>
+        <v>-0.1671372467538243</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-3.944035004077562</v>
+        <v>-4.126087979081973</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-3.150560770783445</v>
+        <v>-3.345666212443152</v>
       </c>
       <c r="K24" s="6" t="n">
+        <v>-0.7804217666388213</v>
+      </c>
+      <c r="L24" s="6" t="n">
         <v>-0.7934742332941171</v>
       </c>
-      <c r="L24" s="6" t="n">
-        <v>-0.5758541077941897</v>
-      </c>
       <c r="M24" s="6" t="n">
-        <v>6232500</v>
+        <v>2377597</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3263872</v>
+        <v>3251269.94</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>1.909541795756696</v>
+        <v>0.7312825584700605</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-0.0165641876578346</v>
+        <v>0.0177384274683925</v>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
@@ -5457,10 +5527,10 @@
         </is>
       </c>
       <c r="R24" s="6" t="n">
-        <v>4.847142355782645</v>
+        <v>4.48357173374721</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>0.0537377219487489</v>
+        <v>0.049032935411613</v>
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
@@ -5475,49 +5545,49 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>25.95999908447266</v>
+        <v>25.54999923706055</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>36.10280010223389</v>
+        <v>35.87440006256104</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>25.30039998531341</v>
+        <v>25.36849997997284</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>41.46933662967547</v>
+        <v>41.0456714719076</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.2402692281070749</v>
+        <v>-0.1797752953466632</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.2435897635398968</v>
+        <v>-0.2469791038238489</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.1431087684288856</v>
+        <v>0.0043238482977101</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-2.398414176127453</v>
+        <v>-2.461635634016321</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-2.383489535301673</v>
+        <v>-2.399118755044602</v>
       </c>
       <c r="K25" s="6" t="n">
+        <v>-0.0625168789717189</v>
+      </c>
+      <c r="L25" s="6" t="n">
         <v>-0.0149246408257801</v>
       </c>
-      <c r="L25" s="6" t="n">
-        <v>0.0551783542258297</v>
-      </c>
       <c r="M25" s="6" t="n">
-        <v>5757200</v>
+        <v>2450919</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>13410266</v>
+        <v>13297572.38</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.4293128861127736</v>
+        <v>0.1843132663587727</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-0.0034549003924671</v>
+        <v>0.0084746235925221</v>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
@@ -5525,10 +5595,10 @@
         </is>
       </c>
       <c r="R25" s="6" t="n">
-        <v>2.413428579057966</v>
+        <v>2.366592815944127</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>0.09296720586178669</v>
+        <v>0.0926259446814917</v>
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
@@ -5543,49 +5613,49 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>13.56999969482422</v>
+        <v>13.80500030517578</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>11.39380002975464</v>
+        <v>11.47430004119873</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>9.101925008296966</v>
+        <v>9.128750011920928</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>75.50561349871404</v>
+        <v>75.64245676712319</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.2040815566672071</v>
+        <v>0.2162995454796763</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.5687861610715199</v>
+        <v>0.5705347400553955</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.6212664134245443</v>
+        <v>0.608974408849742</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.6810486742976209</v>
+        <v>0.6853999592776017</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.6384767328340759</v>
+        <v>0.6478613781227811</v>
       </c>
       <c r="K26" s="6" t="n">
+        <v>0.0375385811548205</v>
+      </c>
+      <c r="L26" s="6" t="n">
         <v>0.042571941463545</v>
       </c>
-      <c r="L26" s="6" t="n">
-        <v>0.0616822772464507</v>
-      </c>
       <c r="M26" s="6" t="n">
-        <v>313200</v>
+        <v>141664</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>673660</v>
+        <v>662975.28</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.4649229581688092</v>
+        <v>0.2136791585954758</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.0007380242613335</v>
+        <v>-0.0110537672736636</v>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
@@ -5593,10 +5663,10 @@
         </is>
       </c>
       <c r="R26" s="6" t="n">
-        <v>0.597428526197161</v>
+        <v>0.6038284982953753</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>0.0440256845713142</v>
+        <v>0.0437398395470507</v>
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
@@ -5611,49 +5681,49 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>76.73000335693359</v>
+        <v>79.56500244140625</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>107.0883999633789</v>
+        <v>107.0294999694824</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>76.91300010681152</v>
+        <v>77.06737512588501</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>32.22155183233293</v>
+        <v>37.83339740394094</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-0.3315037099410254</v>
+        <v>-0.2229221318908395</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.0865194048813213</v>
+        <v>0.1017031445105758</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.0956982352765046</v>
+        <v>-0.0948236511920733</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-7.502857180160049</v>
+        <v>-7.648074583418648</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-5.901575053726029</v>
+        <v>-6.250874959664553</v>
       </c>
       <c r="K27" s="6" t="n">
+        <v>-1.397199623754095</v>
+      </c>
+      <c r="L27" s="6" t="n">
         <v>-1.60128212643402</v>
       </c>
-      <c r="L27" s="6" t="n">
-        <v>-1.41846552484385</v>
-      </c>
       <c r="M27" s="6" t="n">
-        <v>18704000</v>
+        <v>9923025</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>28318376</v>
+        <v>28164752.5</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.6604898529491945</v>
+        <v>0.3523206887758023</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-0.0141905418668198</v>
+        <v>0.0264563885114627</v>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
@@ -5661,10 +5731,10 @@
         </is>
       </c>
       <c r="R27" s="6" t="n">
-        <v>7.806785583496094</v>
+        <v>7.732856750488281</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>0.101743584542547</v>
+        <v>0.09718917254081599</v>
       </c>
       <c r="T27" s="6" t="inlineStr">
         <is>
@@ -5679,49 +5749,49 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>18.1299991607666</v>
+        <v>18.56500053405762</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>16.89759994506836</v>
+        <v>16.94689994812012</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>22.02237502574921</v>
+        <v>21.97300002574921</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>60.23854340937944</v>
+        <v>62.08528783568838</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.08758242818180249</v>
+        <v>0.1197225946613795</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.0633431068641061</v>
+        <v>0.0365717862772707</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.3383211893001081</v>
+        <v>-0.3020676591046031</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.3961109768285347</v>
+        <v>0.4048847760322971</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.363303113685673</v>
+        <v>0.3716194461549978</v>
       </c>
       <c r="K28" s="6" t="n">
+        <v>0.0332653298772992</v>
+      </c>
+      <c r="L28" s="6" t="n">
         <v>0.0328078631428616</v>
       </c>
-      <c r="L28" s="6" t="n">
-        <v>0.0683407053806285</v>
-      </c>
       <c r="M28" s="6" t="n">
-        <v>97444000</v>
+        <v>47284001</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>77088926</v>
+        <v>76139758.02</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.264046667351417</v>
+        <v>0.621015908503146</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.0114483570142134</v>
+        <v>0.0044125718372439</v>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
@@ -5729,10 +5799,10 @@
         </is>
       </c>
       <c r="R28" s="6" t="n">
-        <v>0.9592857360839844</v>
+        <v>0.9414285932268416</v>
       </c>
       <c r="S28" s="6" t="n">
-        <v>0.0529115157467785</v>
+        <v>0.050709860821161</v>
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
@@ -5750,46 +5820,46 @@
         <v>6.429999828338623</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>5.949199991226196</v>
+        <v>5.93479998588562</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>4.476700005531311</v>
+        <v>4.497100005149841</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>64.1330123763551</v>
+        <v>62.8078769713569</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.5382775340673356</v>
+        <v>0.301619383372341</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.0502215884114906</v>
+        <v>-0.0516224735455606</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.3536841743870784</v>
+        <v>0.4008713757260598</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.370541003841125</v>
+        <v>0.3323023162992076</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.3059377744577766</v>
+        <v>0.3112106828260628</v>
       </c>
       <c r="K29" s="6" t="n">
+        <v>0.0210916334731448</v>
+      </c>
+      <c r="L29" s="6" t="n">
         <v>0.0646032293833483</v>
       </c>
-      <c r="L29" s="6" t="n">
-        <v>0.124170819681362</v>
-      </c>
       <c r="M29" s="6" t="n">
-        <v>863400</v>
+        <v>277020</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>1214274</v>
+        <v>1211672.4</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.7110421535831287</v>
+        <v>0.2286261534058216</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.0015059867839982</v>
+        <v>0.0046656626141934</v>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
@@ -5797,10 +5867,10 @@
         </is>
       </c>
       <c r="R29" s="6" t="n">
-        <v>0.6494998591286796</v>
+        <v>0.6430713449205671</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>0.1010108672579073</v>
+        <v>0.1000110983030497</v>
       </c>
       <c r="T29" s="6" t="inlineStr">
         <is>
@@ -5815,49 +5885,49 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>394.760009765625</v>
+        <v>395.7851867675781</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>409.6355993652344</v>
+        <v>409.9187030029297</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>417.9844500732422</v>
+        <v>417.7494259643555</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>47.30190854550064</v>
+        <v>54.21191253815941</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-0.0109983319503641</v>
+        <v>-0.0261909950053679</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.1201407261922502</v>
+        <v>0.08672480368449891</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.1129188083352672</v>
+        <v>-0.1184399628019428</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.8584587141779139</v>
+        <v>-1.326829590185582</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-1.240089992671354</v>
+        <v>-1.257437912174199</v>
       </c>
       <c r="K30" s="6" t="n">
+        <v>-0.0693916780113828</v>
+      </c>
+      <c r="L30" s="6" t="n">
         <v>0.3816312784934397</v>
       </c>
-      <c r="L30" s="6" t="n">
-        <v>1.191718983171606</v>
-      </c>
       <c r="M30" s="6" t="n">
-        <v>32729700</v>
+        <v>14260868</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>48990810</v>
+        <v>48254507.36</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.6680783600026209</v>
+        <v>0.2955344232116517</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-0.0077251921194358</v>
+        <v>0.0109940121352903</v>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
@@ -5865,10 +5935,10 @@
         </is>
       </c>
       <c r="R30" s="6" t="n">
-        <v>19.89071219308036</v>
+        <v>18.56714085170201</v>
       </c>
       <c r="S30" s="6" t="n">
-        <v>0.0503868469475663</v>
+        <v>0.0469121671868063</v>
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
@@ -5883,49 +5953,49 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>421.5799865722656</v>
+        <v>421.5050048828125</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>424.5066003417969</v>
+        <v>425.0155004882813</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>349.0248500061035</v>
+        <v>349.7288250732422</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>37.838400646266</v>
+        <v>45.29803446596495</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.0012111507330756</v>
+        <v>-0.005720255313059</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.1407310610095564</v>
+        <v>0.1095448383208672</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.3026603844254834</v>
+        <v>0.2704735776009046</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>2.714938807848512</v>
+        <v>1.257080966333774</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>6.42672567296799</v>
+        <v>5.392796731641146</v>
       </c>
       <c r="K31" s="6" t="n">
+        <v>-4.135715765307372</v>
+      </c>
+      <c r="L31" s="6" t="n">
         <v>-3.711786865119478</v>
       </c>
-      <c r="L31" s="6" t="n">
-        <v>-2.826101363815375</v>
-      </c>
       <c r="M31" s="6" t="n">
-        <v>14265400</v>
+        <v>8585234</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>13731166</v>
+        <v>13647108.68</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.038906674058124</v>
+        <v>0.629088124181334</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.0006679828548723</v>
+        <v>0.0220361706931489</v>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
@@ -5933,10 +6003,10 @@
         </is>
       </c>
       <c r="R31" s="6" t="n">
-        <v>21.50642830984933</v>
+        <v>19.97285679408482</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>0.0510138739856019</v>
+        <v>0.0473846254794476</v>
       </c>
       <c r="T31" s="6" t="inlineStr">
         <is>
@@ -5951,60 +6021,60 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>305.8699951171875</v>
+        <v>302.7901000976562</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>324.7316009521484</v>
+        <v>324.2176031494141</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>237.6646502685547</v>
+        <v>238.470500793457</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>37.27464274525995</v>
+        <v>45.38102772596008</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.0268228484738957</v>
+        <v>-0.0002637931152617</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.0197026397868611</v>
+        <v>-0.0248620315776479</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.8698495640872399</v>
+        <v>0.7808039891283258</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-1.147608980761959</v>
+        <v>-2.02144560185269</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.9995548151418208</v>
+        <v>-1.203932972483995</v>
       </c>
       <c r="K32" s="6" t="n">
+        <v>-0.8175126293686956</v>
+      </c>
+      <c r="L32" s="6" t="n">
         <v>-0.1480541656201379</v>
       </c>
-      <c r="L32" s="6" t="n">
-        <v>0.6333687634440077</v>
-      </c>
       <c r="M32" s="6" t="n">
-        <v>3716100</v>
+        <v>1877670</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>6234872</v>
+        <v>6147051.4</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.5960186512249169</v>
+        <v>0.3054586464007768</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.0217022618956923</v>
+        <v>0.031582057136426</v>
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="R32" s="6" t="n">
-        <v>23.01642935616629</v>
+        <v>21.269287109375</v>
       </c>
       <c r="S32" s="6" t="n">
-        <v>0.075249059154521</v>
+        <v>0.0702443280097836</v>
       </c>
       <c r="T32" s="6" t="inlineStr">
         <is>
@@ -6019,60 +6089,60 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>860.6599731445312</v>
+        <v>879.0700073242188</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>873.0957971191406</v>
+        <v>877.2043969726562</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>476.2953498840332</v>
+        <v>479.5721999359131</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>33.24526766433529</v>
+        <v>37.90452722844881</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-0.0085590819858302</v>
+        <v>-0.0558192686991134</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.6767844529691138</v>
+        <v>0.6479266708551294</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1.831025115942902</v>
+        <v>1.7344468622704</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-2.548893026430619</v>
+        <v>-3.944148061664578</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>15.03973086762754</v>
+        <v>11.24295508176911</v>
       </c>
       <c r="K33" s="6" t="n">
+        <v>-15.18710314343369</v>
+      </c>
+      <c r="L33" s="6" t="n">
         <v>-17.58862389405815</v>
       </c>
-      <c r="L33" s="6" t="n">
-        <v>-18.29337606210337</v>
-      </c>
       <c r="M33" s="6" t="n">
-        <v>4130400</v>
+        <v>1833544</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>4428830</v>
+        <v>4335914.88</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.9326165149712228</v>
+        <v>0.4228736150835138</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.0447525650500693</v>
+        <v>0.0451049293978258</v>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="R33" s="6" t="n">
-        <v>88.97071620396206</v>
+        <v>84.29928588867188</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>0.1033749901007899</v>
+        <v>0.0958959868796668</v>
       </c>
       <c r="T33" s="6" t="inlineStr">
         <is>
@@ -6087,49 +6157,49 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>27.65999984741211</v>
+        <v>27.84000015258789</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>33.44839981079102</v>
+        <v>33.45719982147217</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>34.46944990158081</v>
+        <v>34.37764989852905</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>22.68907596697776</v>
+        <v>27.75974156663924</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>-0.1348138742105638</v>
+        <v>-0.0860144126931488</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.06507510892341729</v>
+        <v>0.0235293886653287</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.0828912471037202</v>
+        <v>-0.0756972318432225</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-1.952459172100369</v>
+        <v>-1.881451528431274</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-1.839501051819422</v>
+        <v>-1.847891147141793</v>
       </c>
       <c r="K34" s="6" t="n">
+        <v>-0.0335603812894813</v>
+      </c>
+      <c r="L34" s="6" t="n">
         <v>-0.1129581202809464</v>
       </c>
-      <c r="L34" s="6" t="n">
-        <v>-0.1851025146949276</v>
-      </c>
       <c r="M34" s="6" t="n">
-        <v>22736300</v>
+        <v>11143553</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>55712566</v>
+        <v>55514875.06</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.4081000325851083</v>
+        <v>0.200730939013303</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.0236665520640497</v>
+        <v>0.0112075006381963</v>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
@@ -6137,10 +6207,10 @@
         </is>
       </c>
       <c r="R34" s="6" t="n">
-        <v>1.90642820085798</v>
+        <v>1.774999754769462</v>
       </c>
       <c r="S34" s="6" t="n">
-        <v>0.0689236518935247</v>
+        <v>0.0637571747500319</v>
       </c>
       <c r="T34" s="6" t="inlineStr">
         <is>
@@ -6155,49 +6225,49 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>260.239990234375</v>
+        <v>269.125</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>223.3829998779297</v>
+        <v>226.1216998291016</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>159.7822002410889</v>
+        <v>160.4449752044678</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>72.85664449359034</v>
+        <v>76.07259720135606</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.1109972000148784</v>
+        <v>0.170617690930332</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>1.364098709171339</v>
+        <v>1.433978481891935</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1.073790697780459</v>
+        <v>1.126293755620553</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>11.84447561317248</v>
+        <v>12.16555114439922</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>11.44889912504316</v>
+        <v>11.59222952891438</v>
       </c>
       <c r="K35" s="6" t="n">
+        <v>0.5733216154848417</v>
+      </c>
+      <c r="L35" s="6" t="n">
         <v>0.3955764881293149</v>
       </c>
-      <c r="L35" s="6" t="n">
-        <v>0.8170337357042587</v>
-      </c>
       <c r="M35" s="6" t="n">
-        <v>4212100</v>
+        <v>2140740</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>6163506</v>
+        <v>6063110.8</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.6833935101223232</v>
+        <v>0.3530761799701896</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.0032228665927801</v>
+        <v>-0.0192129762097973</v>
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
@@ -6205,10 +6275,10 @@
         </is>
       </c>
       <c r="R35" s="6" t="n">
-        <v>13.0087160382952</v>
+        <v>13.84728785923549</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v>0.0499873829021412</v>
+        <v>0.0514529971546139</v>
       </c>
       <c r="T35" s="6" t="inlineStr">
         <is>
@@ -6223,7 +6293,7 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>153.5099945068359</v>
+        <v>184.4900054931641</v>
       </c>
       <c r="C36" s="6" t="inlineStr"/>
       <c r="D36" s="6" t="inlineStr"/>
@@ -6232,28 +6302,28 @@
       <c r="G36" s="6" t="inlineStr"/>
       <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" s="6" t="n">
-        <v>-1.156695156695179</v>
+        <v>0.4215838180991511</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.2313390313390357</v>
+        <v>-0.1007544614513983</v>
       </c>
       <c r="K36" s="6" t="n">
+        <v>0.5223382795505496</v>
+      </c>
+      <c r="L36" s="6" t="n">
         <v>-0.9253561253561428</v>
       </c>
-      <c r="L36" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" s="6" t="n">
-        <v>56529633</v>
+        <v>45657021</v>
       </c>
       <c r="N36" s="6" t="inlineStr"/>
       <c r="O36" s="6" t="inlineStr"/>
       <c r="P36" s="6" t="n">
-        <v>-0.0916016897377034</v>
+        <v>0.0951078537291295</v>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr"/>
@@ -6271,49 +6341,49 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>8.350000381469727</v>
+        <v>8.573800086975098</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>11.01620002746582</v>
+        <v>10.93847602844238</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>18.60579996585846</v>
+        <v>18.45031897544861</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>14.49631933236232</v>
+        <v>20.79309128159542</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-0.1274816460040546</v>
+        <v>-0.1330839444546926</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.1283924375816173</v>
+        <v>-0.1635316988316978</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.5928815071532083</v>
+        <v>-0.565223104182926</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.6289956274373996</v>
+        <v>-0.6481839541594869</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.5032672616488264</v>
+        <v>-0.5322506001509586</v>
       </c>
       <c r="K37" s="6" t="n">
+        <v>-0.1159333540085283</v>
+      </c>
+      <c r="L37" s="6" t="n">
         <v>-0.1257283657885731</v>
       </c>
-      <c r="L37" s="6" t="n">
-        <v>-0.1007332683507987</v>
-      </c>
       <c r="M37" s="6" t="n">
-        <v>38962400</v>
+        <v>14186772</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>33290360</v>
+        <v>33018651.44</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.170380854998263</v>
+        <v>0.4296593404421607</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-0.0188053182534636</v>
+        <v>0.0299401183926648</v>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
@@ -6321,10 +6391,10 @@
         </is>
       </c>
       <c r="R37" s="6" t="n">
-        <v>0.7357140268598285</v>
+        <v>0.6735711097717285</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>0.0881094602693097</v>
+        <v>0.0785615599779361</v>
       </c>
       <c r="T37" s="6" t="inlineStr">
         <is>
@@ -6339,49 +6409,49 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>45.81000137329102</v>
+        <v>45.81999969482422</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>61.15459983825684</v>
+        <v>60.62099983215332</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>81.88404979705811</v>
+        <v>81.45729980468749</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>21.80922241156196</v>
+        <v>23.09511958709545</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-0.2082613050457644</v>
+        <v>-0.2029918532427812</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.1507229785021223</v>
+        <v>-0.2178218118365793</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.564998552508724</v>
+        <v>-0.5529756127334222</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-3.740426935138217</v>
+        <v>-3.83337002850498</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-3.394162853507454</v>
+        <v>-3.48200428850696</v>
       </c>
       <c r="K38" s="6" t="n">
+        <v>-0.3513657399980205</v>
+      </c>
+      <c r="L38" s="6" t="n">
         <v>-0.3462640816307631</v>
       </c>
-      <c r="L38" s="6" t="n">
-        <v>-0.2587766965285807</v>
-      </c>
       <c r="M38" s="6" t="n">
-        <v>10066900</v>
+        <v>3482257</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>12592758</v>
+        <v>12369365.14</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.7994197935035359</v>
+        <v>0.281522694219697</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-0.0231319813452317</v>
+        <v>0.0251036384349932</v>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
@@ -6389,10 +6459,10 @@
         </is>
       </c>
       <c r="R38" s="6" t="n">
-        <v>3.72428594316755</v>
+        <v>3.439085824148996</v>
       </c>
       <c r="S38" s="6" t="n">
-        <v>0.0812985337594631</v>
+        <v>0.075056434898612</v>
       </c>
       <c r="T38" s="6" t="inlineStr">
         <is>
@@ -6407,49 +6477,49 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>7.480000019073486</v>
+        <v>7.755000114440918</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>9.79479998588562</v>
+        <v>9.766099996566773</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>12.07090001583099</v>
+        <v>12.02982501506805</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>19.79695935229539</v>
+        <v>27.01664839096489</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>-0.2008546695044591</v>
+        <v>-0.1524589685516761</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.1220657726306231</v>
+        <v>-0.1187500060959294</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.5139701200644334</v>
+        <v>-0.4967553412569786</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.5876672497065716</v>
+        <v>-0.5915001429102258</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.4619484600576871</v>
+        <v>-0.4878587966281948</v>
       </c>
       <c r="K39" s="6" t="n">
+        <v>-0.1036413462820309</v>
+      </c>
+      <c r="L39" s="6" t="n">
         <v>-0.1257187896488844</v>
       </c>
-      <c r="L39" s="6" t="n">
-        <v>-0.1157084245752973</v>
-      </c>
       <c r="M39" s="6" t="n">
-        <v>48444300</v>
+        <v>23068273</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>37100944</v>
+        <v>37099575.46</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.305743056025744</v>
+        <v>0.6217934494930202</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-0.0233160405739019</v>
+        <v>0.0100267124430337</v>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
@@ -6457,10 +6527,10 @@
         </is>
       </c>
       <c r="R39" s="6" t="n">
-        <v>0.5634285722460065</v>
+        <v>0.5577142919812884</v>
       </c>
       <c r="S39" s="6" t="n">
-        <v>0.0753246752418853</v>
+        <v>0.0719167354933683</v>
       </c>
       <c r="T39" s="6" t="inlineStr">
         <is>
@@ -6475,49 +6545,49 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>6.489999771118164</v>
+        <v>6.764999866485596</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>7.702400026321411</v>
+        <v>7.678500022888183</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>10.31352501630783</v>
+        <v>10.25845001220703</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>42.1686670849046</v>
+        <v>56.98924378337604</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>-0.0728571755545479</v>
+        <v>-0.0195652502921663</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.0511696452722014</v>
+        <v>-0.0294117546451774</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.4476595939473903</v>
+        <v>-0.4152981810784416</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.2666229192549947</v>
+        <v>-0.2395015780978422</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.3228008935526191</v>
+        <v>-0.3061410304616637</v>
       </c>
       <c r="K40" s="6" t="n">
+        <v>0.0666394523638215</v>
+      </c>
+      <c r="L40" s="6" t="n">
         <v>0.0561779742976243</v>
       </c>
-      <c r="L40" s="6" t="n">
-        <v>0.0674839355125665</v>
-      </c>
       <c r="M40" s="6" t="n">
-        <v>29879000</v>
+        <v>16404989</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>28649440</v>
+        <v>28572367.78</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.042917418281125</v>
+        <v>0.5741557411802292</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-0.0045180321648213</v>
+        <v>-0.0154083063419491</v>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
@@ -6525,10 +6595,10 @@
         </is>
       </c>
       <c r="R40" s="6" t="n">
-        <v>0.4056429181780134</v>
+        <v>0.4006429399762835</v>
       </c>
       <c r="S40" s="6" t="n">
-        <v>0.0625027630945702</v>
+        <v>0.0592229043434433</v>
       </c>
       <c r="T40" s="6" t="inlineStr">
         <is>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00D9EAF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,10 +91,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>369.8450012207031</v>
+        <v>368.0950012207031</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.082723417254077</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.2543960078535687</v>
+        <v>0.2652982180935547</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>75</v>
@@ -573,13 +573,13 @@
         <v>12</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.0324460245789264</v>
+        <v>0.032600279710957</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>276.9891575404576</v>
+        <v>275.2391575404576</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>555.5566885811942</v>
+        <v>507.3787667410714</v>
       </c>
     </row>
     <row r="3">
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>987.3599853515624</v>
+        <v>988.1630859375</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.0543756800501934</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.3691105013773031</v>
+        <v>0.380063686150926</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>75</v>
@@ -614,13 +614,13 @@
         <v>12</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.0121536219596009</v>
+        <v>0.0121437444595648</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>807.8299560546874</v>
+        <v>808.633056640625</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1346.420043945312</v>
+        <v>1257.458129882812</v>
       </c>
     </row>
     <row r="4">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>238.8999938964844</v>
+        <v>239.25</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.06596166699561611</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.2471155973482561</v>
+        <v>0.2601719598812185</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>75</v>
@@ -655,13 +655,13 @@
         <v>12</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.0502302231334489</v>
+        <v>0.0501567398119122</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>185.3292781284877</v>
+        <v>185.6792842320033</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>346.0414254324777</v>
+        <v>319.606073651995</v>
       </c>
     </row>
   </sheetData>
@@ -675,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -695,9 +695,11 @@
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="35" customWidth="1" min="19" max="19"/>
-    <col width="35" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="35" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -768,19 +770,19 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>trim_price</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>atr</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>stop_loss</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>trim_price</t>
-        </is>
-      </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>buy_amount_usd</t>
@@ -793,10 +795,20 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>risk_budget_usd</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>max_position_usd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>decision_reasons</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>warnings</t>
         </is>
@@ -819,7 +831,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>182.634994506836</v>
+        <v>182.8500061035156</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>89</v>
@@ -839,38 +851,44 @@
         <v>75</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>62.44594972357781</v>
+        <v>62.54404908025502</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.0151807899125376</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.3138506159908594</v>
+        <v>0.3267114381879226</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1.608514906429189</v>
+        <v>1.622236444222988</v>
       </c>
       <c r="N2" s="2" t="n">
+        <v>161.9255959647042</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>214.2366213117327</v>
+      </c>
+      <c r="P2" s="2" t="n">
         <v>10.46220506940569</v>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>161.7105843680246</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>224.4838147844588</v>
-      </c>
       <c r="Q2" s="2" t="n">
-        <v>9.74</v>
+        <v>9.75</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>0.0533413650657586</v>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr"/>
+        <v>0.053341</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -889,7 +907,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>211.2200012207031</v>
+        <v>211.3099975585937</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>89</v>
@@ -909,38 +927,44 @@
         <v>75</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>60.30225678806677</v>
+        <v>60.36799095758673</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.0229450115312453</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.390917583540066</v>
+        <v>0.4210526239435837</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1.634998744915757</v>
+        <v>1.640742100952084</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>6.863571166992188</v>
+        <v>200.9964267185756</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>200.9246444702148</v>
+        <v>225.0614253452846</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>231.8107147216797</v>
+        <v>6.875713893345424</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>13.95</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.0660529657199552</v>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr"/>
+        <v>0.066025</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -959,7 +983,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>555.3699951171875</v>
+        <v>557.6199951171875</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>82</v>
@@ -979,38 +1003,44 @@
         <v>50</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>55.86565004537624</v>
+        <v>56.19119939331</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0.0624019610194614</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.4139132873326793</v>
+        <v>0.4259170811245481</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>-2.597301163054709</v>
+        <v>-2.45371141946487</v>
       </c>
       <c r="N4" s="2" t="n">
+        <v>500.5428423200335</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>633.7228655133929</v>
+      </c>
+      <c r="P4" s="2" t="n">
         <v>38.05143519810268</v>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>498.2928423200335</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>669.5243007114956</v>
-      </c>
       <c r="Q4" s="2" t="n">
-        <v>10.86</v>
+        <v>10.9</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.0195548752049112</v>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr"/>
+        <v>0.019555</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1029,7 +1059,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>987.3599853515624</v>
+        <v>988.1630859375</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>82</v>
@@ -1049,38 +1079,44 @@
         <v>50</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>45.1502141583485</v>
+        <v>45.2164692088228</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0.0543756800501934</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.3691105013773031</v>
+        <v>0.380063686150926</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-24.69993152187335</v>
+        <v>-24.64867951866817</v>
       </c>
       <c r="N5" s="2" t="n">
+        <v>808.633056640625</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>1257.458129882812</v>
+      </c>
+      <c r="P5" s="2" t="n">
         <v>89.7650146484375</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>807.8299560546874</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>1346.420043945312</v>
       </c>
       <c r="Q5" s="2" t="n">
         <v>6.14</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.0062169911316303</v>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr"/>
+        <v>0.006217</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1099,7 +1135,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1154</v>
+        <v>1157.699951171875</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>82</v>
@@ -1119,38 +1155,44 @@
         <v>50</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>57.41560404426107</v>
+        <v>58.0950473448579</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>-0.013419399271567</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.3812196495005608</v>
+        <v>0.3970135193890146</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-7.021138416095418</v>
+        <v>-6.785016176066783</v>
       </c>
       <c r="N6" s="2" t="n">
+        <v>1095.450474330357</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1240.699253627232</v>
+      </c>
+      <c r="P6" s="2" t="n">
         <v>41.49965122767857</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>1091.750523158482</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>1278.498953683036</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>13.95</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.0120898678509532</v>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr"/>
+        <v>0.012051</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1169,7 +1211,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7.710000038146973</v>
+        <v>7.625</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>82</v>
@@ -1189,38 +1231,44 @@
         <v>50</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>50.38910466129628</v>
+        <v>49.56937729178416</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>-0.0049382666628676</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.4330916809728698</v>
+        <v>0.4660121255074218</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-0.1206688011081675</v>
+        <v>-0.1260933049671196</v>
       </c>
       <c r="N7" s="2" t="n">
+        <v>6.147785867963519</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>9.840821198054725</v>
+      </c>
+      <c r="P7" s="2" t="n">
         <v>0.7386070660182408</v>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>6.232785906110491</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>10.66442830221994</v>
-      </c>
       <c r="Q7" s="2" t="n">
-        <v>5.83</v>
+        <v>5.76</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.755568590764359</v>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr"/>
+        <v>0.755569</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1239,7 +1287,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>369.8450012207031</v>
+        <v>368.0950012207031</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>82</v>
@@ -1259,948 +1307,1040 @@
         <v>50</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46.14959731343965</v>
+        <v>45.88121563095124</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0.082723417254077</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.2543960078535687</v>
+        <v>0.2652982180935547</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-11.19183890588324</v>
+        <v>-11.30351981756416</v>
       </c>
       <c r="N8" s="2" t="n">
+        <v>275.2391575404576</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>507.3787667410714</v>
+      </c>
+      <c r="P8" s="2" t="n">
         <v>46.42792184012277</v>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>276.9891575404576</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>555.5566885811942</v>
-      </c>
       <c r="Q8" s="2" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.0120201007902473</v>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr"/>
+        <v>0.01202</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>BLZE</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Gaming/Digital Media</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>17.1200008392334</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
+      <c r="D9" s="3" t="n">
+        <v>17.04999923706055</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>BUY SMALL</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J9" s="2" t="n">
-        <v>75.1381247005498</v>
-      </c>
-      <c r="K9" s="2" t="n">
+      <c r="J9" s="3" t="n">
+        <v>74.97682986607725</v>
+      </c>
+      <c r="K9" s="3" t="n">
         <v>0.0098826338563442</v>
       </c>
-      <c r="L9" s="2" t="n">
-        <v>0.1840927394643399</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>0.1432374274106971</v>
-      </c>
-      <c r="N9" s="2" t="n">
+      <c r="L9" s="3" t="n">
+        <v>0.1947934971779053</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>0.1387700886965315</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>14.0509990964617</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>21.54849944795881</v>
+      </c>
+      <c r="P9" s="3" t="n">
         <v>1.499500070299421</v>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>14.12100069863456</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>23.11800112043108</v>
-      </c>
-      <c r="Q9" s="2" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>0.3721695724152681</v>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.186085</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>RSI overbought</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>PUBM</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>AdTech</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>13.80500030517578</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
+      <c r="D10" s="3" t="n">
+        <v>13.76000022888184</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>BUY SMALL</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J10" s="2" t="n">
-        <v>75.64245676712319</v>
-      </c>
-      <c r="K10" s="2" t="n">
+      <c r="J10" s="3" t="n">
+        <v>75.39503211062105</v>
+      </c>
+      <c r="K10" s="3" t="n">
         <v>-0.0110537672736636</v>
       </c>
-      <c r="L10" s="2" t="n">
-        <v>0.2136791585954758</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.0375385811548205</v>
-      </c>
-      <c r="N10" s="2" t="n">
+      <c r="L10" s="3" t="n">
+        <v>0.2241632566493904</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0.0346667814141248</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>12.55234323229108</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>15.57148572376796</v>
+      </c>
+      <c r="P10" s="3" t="n">
         <v>0.6038284982953753</v>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>12.59734330858503</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>16.22031429835728</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>12.76</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.9242165640996444</v>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.462108</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>RSI overbought</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>DDOG</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Cloud Software</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>269.125</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n">
+      <c r="D11" s="3" t="n">
+        <v>269.489990234375</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>BUY SMALL</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J11" s="2" t="n">
-        <v>76.07259720135606</v>
-      </c>
-      <c r="K11" s="2" t="n">
+      <c r="J11" s="3" t="n">
+        <v>76.16602114423313</v>
+      </c>
+      <c r="K11" s="3" t="n">
         <v>-0.0192129762097973</v>
       </c>
-      <c r="L11" s="2" t="n">
-        <v>0.3530761799701896</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>0.5733216154848417</v>
-      </c>
-      <c r="N11" s="2" t="n">
+      <c r="L11" s="3" t="n">
+        <v>0.363604012071255</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>0.5966144395589303</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>248.7190584455218</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>297.184565952846</v>
+      </c>
+      <c r="P11" s="3" t="n">
         <v>13.84728785923549</v>
       </c>
-      <c r="O11" s="2" t="n">
-        <v>248.3540682111468</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>310.6668635777065</v>
-      </c>
-      <c r="Q11" s="2" t="n">
+      <c r="Q11" s="3" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>0.025885</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T11" s="3" t="n">
         <v>13.95</v>
       </c>
-      <c r="R11" s="2" t="n">
-        <v>0.0518409939619136</v>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>RSI overbought</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>394.5700073242188</v>
-      </c>
-      <c r="E12" s="3" t="n">
+      <c r="D12" s="4" t="n">
+        <v>393.7349853515625</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>BUY SMALL</t>
         </is>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J12" s="3" t="n">
-        <v>55.83900718527268</v>
-      </c>
-      <c r="K12" s="3" t="n">
+      <c r="J12" s="4" t="n">
+        <v>55.53833938277076</v>
+      </c>
+      <c r="K12" s="4" t="n">
         <v>0.030087289573326</v>
       </c>
-      <c r="L12" s="3" t="n">
-        <v>0.34719360816042</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>3.328471821393368</v>
-      </c>
-      <c r="N12" s="3" t="n">
+      <c r="L12" s="4" t="n">
+        <v>0.35862833201275</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>3.275182669862051</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>371.2296360560826</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>423.7421177455357</v>
+      </c>
+      <c r="P12" s="4" t="n">
         <v>15.00356619698661</v>
       </c>
-      <c r="O12" s="3" t="n">
-        <v>372.0646580287389</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>439.5807059151786</v>
-      </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="4" t="n">
         <v>6.98</v>
       </c>
-      <c r="R12" s="3" t="n">
-        <v>0.0176796350977278</v>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t>Above 200 SMA; Positive 1M return; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr"/>
+      <c r="R12" s="4" t="n">
+        <v>0.017717</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>Positive momentum; MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>STTK</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>6.429999828338623</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>BUY SMALL</t>
         </is>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="J13" s="4" t="n">
         <v>62.8078769713569</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="4" t="n">
         <v>0.0046656626141934</v>
       </c>
-      <c r="L13" s="3" t="n">
-        <v>0.2286261534058216</v>
-      </c>
-      <c r="M13" s="3" t="n">
+      <c r="L13" s="4" t="n">
+        <v>0.241781972360957</v>
+      </c>
+      <c r="M13" s="4" t="n">
         <v>0.0210916334731448</v>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="N13" s="4" t="n">
+        <v>5.143857138497489</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>8.359213863100324</v>
+      </c>
+      <c r="P13" s="4" t="n">
         <v>0.6430713449205671</v>
       </c>
-      <c r="O13" s="3" t="n">
-        <v>5.143857138497489</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>9.002285208020892</v>
-      </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="4" t="n">
         <v>2.79</v>
       </c>
-      <c r="R13" s="3" t="n">
-        <v>0.433908542503113</v>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 1M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr"/>
+      <c r="R13" s="4" t="n">
+        <v>0.433909</v>
+      </c>
+      <c r="S13" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>Strong trend; MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Internet/Software</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>356.6700134277344</v>
+        <v>239.25</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>BUY SMALL</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>75</v>
       </c>
       <c r="I14" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>41.43323997010419</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.06596166699561611</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0.2601719598812185</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>-4.632437426028641</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>185.6792842320033</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>319.606073651995</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>26.78535788399833</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>0.010417</v>
+      </c>
+      <c r="S14" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Internet/Software</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>357.8699951171875</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="J14" s="4" t="n">
-        <v>58.83340486164004</v>
-      </c>
-      <c r="K14" s="4" t="n">
+      <c r="I15" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>59.64509105642299</v>
+      </c>
+      <c r="K15" s="5" t="n">
         <v>-0.0040282924977889</v>
       </c>
-      <c r="L14" s="4" t="n">
-        <v>0.233640186442379</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0.5162715592141147</v>
-      </c>
-      <c r="N14" s="4" t="n">
+      <c r="L15" s="5" t="n">
+        <v>0.2463434442892674</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0.5928515872589877</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>342.9846354893276</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>377.7171412876674</v>
+      </c>
+      <c r="P15" s="5" t="n">
         <v>9.923573085239957</v>
       </c>
-      <c r="O14" s="4" t="n">
-        <v>341.7846537998744</v>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v>386.4407326834543</v>
-      </c>
-      <c r="Q14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="4" t="inlineStr">
-        <is>
-          <t>Above 200 SMA; Positive 3M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="Q15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>Positive momentum; MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="V15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>CELC</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Biotech</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="E15" s="4" t="n">
+      <c r="D16" s="5" t="n">
+        <v>104.9100036621094</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G16" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H16" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I16" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="J15" s="4" t="n">
-        <v>65.08260145047174</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>0.3128789884849992</v>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v>1.443488052737651</v>
-      </c>
-      <c r="N15" s="4" t="n">
+      <c r="J16" s="5" t="n">
+        <v>65.01839145146317</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>0.3585139638253107</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>1.437744696701323</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>92.96714564732144</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>122.8242906842913</v>
+      </c>
+      <c r="P16" s="5" t="n">
         <v>5.971429007393973</v>
       </c>
-      <c r="O15" s="4" t="n">
-        <v>93.05714198521206</v>
-      </c>
-      <c r="P15" s="4" t="n">
-        <v>128.8857160295759</v>
-      </c>
-      <c r="Q15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="4" t="inlineStr">
-        <is>
-          <t>Above 200 SMA; Positive 1M return; Positive 6M return; MACD improving; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="Q16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T16" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="V16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>SOFI</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Fintech</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
-        <v>18.56500053405762</v>
-      </c>
-      <c r="E16" s="4" t="n">
+      <c r="D17" s="5" t="n">
+        <v>18.59499931335449</v>
+      </c>
+      <c r="E17" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G17" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H17" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I17" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="J16" s="4" t="n">
-        <v>62.08528783568838</v>
-      </c>
-      <c r="K16" s="4" t="n">
+      <c r="J17" s="5" t="n">
+        <v>62.29968817312163</v>
+      </c>
+      <c r="K17" s="5" t="n">
         <v>0.0044125718372439</v>
       </c>
-      <c r="L16" s="4" t="n">
-        <v>0.621015908503146</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>0.0332653298772992</v>
-      </c>
-      <c r="N16" s="4" t="n">
+      <c r="L17" s="5" t="n">
+        <v>0.6652128389936749</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0.0351797818894123</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>16.7121421269008</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>21.41928509303501</v>
+      </c>
+      <c r="P17" s="5" t="n">
         <v>0.9414285932268416</v>
       </c>
-      <c r="O16" s="4" t="n">
-        <v>16.68214334760393</v>
-      </c>
-      <c r="P16" s="4" t="n">
-        <v>22.33071490696499</v>
-      </c>
-      <c r="Q16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="4" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Positive 1M return; Positive 3M return; MACD improving; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>CRDO</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="Q17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T17" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="V17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>238.8999938964844</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>422.3099975585938</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G18" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>45.57065028514946</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0.0220361706931489</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>0.6586487344952262</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>-4.084343013348712</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>392.3507123674665</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>462.2557111467634</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>19.97285679408482</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>Positive momentum</t>
+        </is>
+      </c>
+      <c r="V18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Data Storage</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>881.2999877929688</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H19" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I19" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J17" s="4" t="n">
-        <v>41.32581837733308</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>0.06596166699561611</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>0.2471155973482561</v>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v>-4.654773997876911</v>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v>26.78535788399833</v>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v>185.3292781284877</v>
-      </c>
-      <c r="P17" s="4" t="n">
-        <v>346.0414254324777</v>
-      </c>
-      <c r="Q17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="4" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 3M return; Positive 6M return</t>
-        </is>
-      </c>
-      <c r="T17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>STX</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Data Storage</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="J19" s="5" t="n">
+        <v>38.11380958860197</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0.0451049293978258</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0.4517719065777259</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>-15.04479099955905</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>754.8510589599609</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>1049.898559570312</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>84.29928588867188</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T19" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum</t>
+        </is>
+      </c>
+      <c r="V19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>VRT</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Data Centers</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
-        <v>879.0700073242188</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="D20" s="5" t="n">
+        <v>303.4923095703125</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="H18" s="4" t="n">
+      <c r="G20" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>45.57138320604898</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0.031582057136426</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0.3167818315827367</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>-0.7726992613131298</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>271.58837890625</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>346.0308837890625</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>21.269287109375</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U20" s="5" t="inlineStr"/>
+      <c r="V20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Internet/E-Commerce</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>246.0800018310547</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I21" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="I18" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>37.90452722844881</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>0.0451049293978258</v>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>0.4228736150835138</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>-15.18710314343369</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>84.29928588867188</v>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v>752.6210784912109</v>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v>1131.967864990234</v>
-      </c>
-      <c r="Q18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="4" t="inlineStr">
-        <is>
-          <t>Above 50 SMA; Above 200 SMA; Positive 3M return; Positive 6M return</t>
-        </is>
-      </c>
-      <c r="T18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>TSM</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>421.5050048828125</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>45.29803446596495</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>0.0220361706931489</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>0.629088124181334</v>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v>-4.135715765307372</v>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v>19.97285679408482</v>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v>391.5457196916853</v>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v>481.423575265067</v>
-      </c>
-      <c r="Q19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="4" t="inlineStr">
-        <is>
-          <t>Above 200 SMA; Positive 3M return; Positive 6M return; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Internet/E-Commerce</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>246.1929016113281</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>64.89615497050171</v>
-      </c>
-      <c r="K20" s="4" t="n">
+      <c r="J21" s="5" t="n">
+        <v>64.71600352674133</v>
+      </c>
+      <c r="K21" s="5" t="n">
         <v>-0.0071974396379796</v>
       </c>
-      <c r="L20" s="4" t="n">
-        <v>0.2683335641644078</v>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>1.658591598998686</v>
-      </c>
-      <c r="N20" s="4" t="n">
+      <c r="L21" s="5" t="n">
+        <v>0.2904367729668282</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>1.65138659877611</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>234.8632207598005</v>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>261.0357099260603</v>
+      </c>
+      <c r="P21" s="5" t="n">
         <v>7.47785404750279</v>
       </c>
-      <c r="O20" s="4" t="n">
-        <v>234.9761205400739</v>
-      </c>
-      <c r="P20" s="4" t="n">
-        <v>268.6264637538364</v>
-      </c>
-      <c r="Q20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="4" t="inlineStr">
-        <is>
-          <t>Above 200 SMA; Positive 1M return; MACD improving; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>VRT</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Data Centers</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>302.7901000976562</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>45.38102772596008</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>0.031582057136426</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>0.3054586464007768</v>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>-0.8175126293686956</v>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>21.269287109375</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>270.8861694335937</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>366.5979614257813</v>
-      </c>
-      <c r="Q21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="4" t="inlineStr">
-        <is>
-          <t>Above 200 SMA; Positive 6M return; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T21" s="4" t="inlineStr"/>
+      <c r="Q21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T21" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="V21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2219,10 +2359,10 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>282.2300109863281</v>
+        <v>285.5400085449219</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
@@ -2239,42 +2379,44 @@
         <v>50</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>28.30257054769397</v>
+        <v>28.79400118305021</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>0.0376936349020097</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.507640731819666</v>
+        <v>0.5345029925370236</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-10.03311904104094</v>
+        <v>-9.8218827296093</v>
       </c>
       <c r="N22" s="5" t="n">
+        <v>226.7774353027344</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>373.6838684082031</v>
+      </c>
+      <c r="P22" s="5" t="n">
         <v>29.38128662109375</v>
       </c>
-      <c r="O22" s="5" t="n">
-        <v>223.4674377441407</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>399.7551574707031</v>
-      </c>
       <c r="Q22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S22" s="5" t="inlineStr">
-        <is>
-          <t>Above 200 SMA; Positive 3M return; Positive 6M return</t>
-        </is>
-      </c>
-      <c r="T22" s="5" t="inlineStr">
-        <is>
-          <t>RSI weak</t>
-        </is>
-      </c>
+      <c r="S22" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T22" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U22" s="5" t="inlineStr">
+        <is>
+          <t>Positive momentum</t>
+        </is>
+      </c>
+      <c r="V22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2293,10 +2435,10 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>222.8399963378907</v>
+        <v>223.0299987792969</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -2313,42 +2455,44 @@
         <v>50</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>33.59411998846861</v>
+        <v>33.66770296216299</v>
       </c>
       <c r="K23" s="5" t="n">
         <v>0.0645198535414377</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.2599507294431511</v>
+        <v>0.2684116598641259</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-9.122317745159036</v>
+        <v>-9.110192233228853</v>
       </c>
       <c r="N23" s="5" t="n">
+        <v>190.6257095336914</v>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>266.2357177734375</v>
+      </c>
+      <c r="P23" s="5" t="n">
         <v>21.60285949707031</v>
       </c>
-      <c r="O23" s="5" t="n">
-        <v>190.4357070922852</v>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v>287.6485748291016</v>
-      </c>
       <c r="Q23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S23" s="5" t="inlineStr">
-        <is>
-          <t>Above 200 SMA; Positive 3M return; Positive 6M return</t>
-        </is>
-      </c>
-      <c r="T23" s="5" t="inlineStr">
-        <is>
-          <t>RSI weak</t>
-        </is>
-      </c>
+      <c r="S23" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T23" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U23" s="5" t="inlineStr">
+        <is>
+          <t>Positive momentum</t>
+        </is>
+      </c>
+      <c r="V23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2367,10 +2511,10 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>196.7700042724609</v>
+        <v>193.9100036621093</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -2387,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>30.35052655812525</v>
+        <v>29.92199908218262</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>0.0310198990532244</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.5703496860734236</v>
+        <v>0.6231393959985919</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>-6.923687481942226</v>
+        <v>-7.10620603941196</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>25.34157235281808</v>
+        <v>142.7897164481026</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>146.0868595668248</v>
+        <v>270.5904344831194</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>298.1362936837332</v>
+        <v>25.56014360700335</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>0</v>
@@ -2413,16 +2557,18 @@
       <c r="R24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S24" s="5" t="inlineStr">
-        <is>
-          <t>Above 200 SMA; Positive 3M return; Positive 6M return</t>
-        </is>
-      </c>
-      <c r="T24" s="5" t="inlineStr">
-        <is>
-          <t>RSI weak</t>
-        </is>
-      </c>
+      <c r="S24" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>Positive momentum</t>
+        </is>
+      </c>
+      <c r="V24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2441,10 +2587,10 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>106.75</v>
+        <v>107.4000015258789</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -2461,462 +2607,484 @@
         <v>50</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>30.70294698798626</v>
+        <v>31.37724628863623</v>
       </c>
       <c r="K25" s="5" t="n">
         <v>0.0469355722360184</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.4121587629902415</v>
+        <v>0.4293606824387826</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-3.45759544953356</v>
+        <v>-3.416113870674052</v>
       </c>
       <c r="N25" s="5" t="n">
+        <v>93.18107223510742</v>
+      </c>
+      <c r="O25" s="5" t="n">
+        <v>126.3585739135742</v>
+      </c>
+      <c r="P25" s="5" t="n">
         <v>9.479286193847656</v>
       </c>
-      <c r="O25" s="5" t="n">
-        <v>92.53107070922852</v>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v>135.187858581543</v>
-      </c>
       <c r="Q25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S25" s="5" t="inlineStr">
-        <is>
-          <t>Above 200 SMA; Positive 3M return; Positive 6M return</t>
-        </is>
-      </c>
-      <c r="T25" s="5" t="inlineStr">
-        <is>
-          <t>RSI weak</t>
-        </is>
-      </c>
+      <c r="S25" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T25" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>Positive momentum</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>25.60000038146973</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>41.16938033603359</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0.0084746235925221</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0.1941426174546727</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>-0.0593259227473152</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>20.84728622436523</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>32.72907161712646</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>2.376357078552246</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T26" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U26" s="5" t="inlineStr"/>
+      <c r="V26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>CBOE</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
-        <v>275.4800109863281</v>
-      </c>
-      <c r="E26" s="4" t="n">
+      <c r="D27" s="5" t="n">
+        <v>275.3500061035156</v>
+      </c>
+      <c r="E27" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="4" t="n">
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="I26" s="4" t="n">
+      <c r="I27" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>61.14814244093061</v>
-      </c>
-      <c r="K26" s="4" t="n">
+      <c r="J27" s="5" t="n">
+        <v>61.05015706408463</v>
+      </c>
+      <c r="K27" s="5" t="n">
         <v>-0.0092015237095138</v>
       </c>
-      <c r="L26" s="4" t="n">
-        <v>0.1907551761678488</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>5.867915420958891</v>
-      </c>
-      <c r="N26" s="4" t="n">
+      <c r="L27" s="5" t="n">
+        <v>0.1979807697475212</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>5.859618813052931</v>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v>257.5482259477888</v>
+      </c>
+      <c r="O27" s="5" t="n">
+        <v>299.0857129778181</v>
+      </c>
+      <c r="P27" s="5" t="n">
         <v>11.86785343715123</v>
       </c>
-      <c r="O26" s="4" t="n">
-        <v>257.6782308306013</v>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v>311.0835712977818</v>
-      </c>
-      <c r="Q26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="4" t="inlineStr">
-        <is>
-          <t>Positive 6M return; MACD improving; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T27" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U27" s="5" t="inlineStr">
+        <is>
+          <t>MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="V27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Electric Vehicles</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>395.7550048828125</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>54.20369849720209</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0.0109940121352903</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>0.3097804369237979</v>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>-0.0713178153867408</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>367.9042936052595</v>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>432.8892865862165</v>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>18.56714085170201</v>
+      </c>
+      <c r="Q28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T28" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U28" s="5" t="inlineStr"/>
+      <c r="V28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>RKLB</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Space</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n">
-        <v>25.54999923706055</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="D29" s="5" t="n">
+        <v>79.67500305175781</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G29" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="H27" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="I27" s="4" t="n">
+      <c r="H29" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="I29" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J27" s="4" t="n">
-        <v>41.0456714719076</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>0.0084746235925221</v>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v>0.1843132663587727</v>
-      </c>
-      <c r="M27" s="4" t="n">
-        <v>-0.0625168789717189</v>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v>2.366592815944127</v>
-      </c>
-      <c r="O27" s="4" t="n">
-        <v>20.81681360517229</v>
-      </c>
-      <c r="P27" s="4" t="n">
-        <v>35.01637050083706</v>
-      </c>
-      <c r="Q27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="4" t="inlineStr">
-        <is>
-          <t>Above 200 SMA; Positive 6M return</t>
-        </is>
-      </c>
-      <c r="T27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>RKLB</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="J29" s="5" t="n">
+        <v>37.94018845028621</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0.0264563885114627</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>0.363046347956758</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>-1.39017964178294</v>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>64.20928955078125</v>
+      </c>
+      <c r="O29" s="5" t="n">
+        <v>102.8735733032227</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>7.732856750488281</v>
+      </c>
+      <c r="Q29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T29" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U29" s="5" t="inlineStr"/>
+      <c r="V29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>SOUN</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>AI Software</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
-        <v>79.56500244140625</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="D30" s="5" t="n">
+        <v>6.804999828338623</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="H28" s="4" t="n">
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>57.71669781062163</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>-0.0154083063419491</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0.6503429138916187</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>0.0691921564820778</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>5.998713970184326</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>8.014428615570068</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0.4031429290771484</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T30" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U30" s="5" t="inlineStr">
+        <is>
+          <t>MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="V30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>27.7947998046875</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="I31" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J28" s="4" t="n">
-        <v>37.83339740394094</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>0.0264563885114627</v>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v>0.3523206887758023</v>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v>-1.397199623754095</v>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v>7.732856750488281</v>
-      </c>
-      <c r="O28" s="4" t="n">
-        <v>64.09928894042969</v>
-      </c>
-      <c r="P28" s="4" t="n">
-        <v>110.4964294433594</v>
-      </c>
-      <c r="Q28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="4" t="inlineStr">
-        <is>
-          <t>Above 200 SMA; Positive 3M return</t>
-        </is>
-      </c>
-      <c r="T28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Electric Vehicles</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>395.7851867675781</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>54.21191253815941</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>0.0109940121352903</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>0.2955344232116517</v>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>-0.0693916780113828</v>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v>18.56714085170201</v>
-      </c>
-      <c r="O29" s="4" t="n">
-        <v>367.9344754900251</v>
-      </c>
-      <c r="P29" s="4" t="n">
-        <v>451.4866093226842</v>
-      </c>
-      <c r="Q29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="4" t="inlineStr">
-        <is>
-          <t>Positive 3M return; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>SOUN</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>AI Software</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>6.764999866485596</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>56.98924378337604</v>
-      </c>
-      <c r="K30" s="4" t="n">
-        <v>-0.0154083063419491</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>0.5741557411802292</v>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v>0.0666394523638215</v>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v>0.4006429399762835</v>
-      </c>
-      <c r="O30" s="4" t="n">
-        <v>5.963713986533029</v>
-      </c>
-      <c r="P30" s="4" t="n">
-        <v>8.367571626390729</v>
-      </c>
-      <c r="Q30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="4" t="inlineStr">
-        <is>
-          <t>MACD improving; RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>ASTS</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Space/Telecom</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>69.16999816894531</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>46.62654509530972</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>0.0334417645102432</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>0.275152457062168</v>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v>-0.7787341967854466</v>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v>6.955285753522601</v>
-      </c>
-      <c r="O31" s="4" t="n">
-        <v>55.25942666190011</v>
-      </c>
-      <c r="P31" s="4" t="n">
-        <v>96.99114118303572</v>
-      </c>
-      <c r="Q31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" s="4" t="inlineStr">
-        <is>
-          <t>RSI in momentum zone</t>
-        </is>
-      </c>
-      <c r="T31" s="4" t="inlineStr"/>
+      <c r="J31" s="5" t="n">
+        <v>27.49372623544604</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0.0112075006381963</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>0.2075141411721247</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>-0.0364449618962279</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>24.24480029514857</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>33.11979906899589</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>1.774999754769462</v>
+      </c>
+      <c r="Q31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T31" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U31" s="5" t="inlineStr"/>
+      <c r="V31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -2935,10 +3103,10 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>39.0099983215332</v>
+        <v>39.06000137329102</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -2955,52 +3123,50 @@
         <v>50</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>16.64305219071599</v>
+        <v>16.79038701584251</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>0.0298353862022756</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.3104873615510589</v>
+        <v>0.3311449574224561</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>-1.455271152931205</v>
+        <v>-1.452080074984266</v>
       </c>
       <c r="N32" s="5" t="n">
+        <v>31.65785871233259</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>50.16321536472866</v>
+      </c>
+      <c r="P32" s="5" t="n">
         <v>3.701071330479213</v>
       </c>
-      <c r="O32" s="5" t="n">
-        <v>31.60785566057477</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>53.81428364345005</v>
-      </c>
       <c r="Q32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S32" s="5" t="inlineStr">
-        <is>
-          <t>Positive 3M return</t>
-        </is>
-      </c>
-      <c r="T32" s="5" t="inlineStr">
-        <is>
-          <t>RSI weak</t>
-        </is>
-      </c>
+      <c r="S32" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U32" s="5" t="inlineStr"/>
+      <c r="V32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>AI Infrastructure</t>
+          <t>Space/Telecom</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -3009,10 +3175,10 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>27.84000015258789</v>
+        <v>69.48989868164062</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -3023,31 +3189,31 @@
         <v>0</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>50</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>27.75974156663924</v>
+        <v>46.93608515837733</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.0112075006381963</v>
+        <v>0.0334417645102432</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.200730939013303</v>
+        <v>0.2819463443126206</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>-0.0335603812894813</v>
+        <v>-0.7583188934111513</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>1.774999754769462</v>
+        <v>55.57932717459542</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>24.29000064304897</v>
+        <v>90.35575594220842</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>34.93999917166574</v>
+        <v>6.955285753522601</v>
       </c>
       <c r="Q33" s="5" t="n">
         <v>0</v>
@@ -3055,150 +3221,160 @@
       <c r="R33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S33" s="5" t="inlineStr">
-        <is>
-          <t>Positive 3M return</t>
-        </is>
-      </c>
-      <c r="T33" s="5" t="inlineStr">
-        <is>
-          <t>RSI weak</t>
-        </is>
-      </c>
+      <c r="S33" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T33" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U33" s="5" t="inlineStr"/>
+      <c r="V33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
+          <t>KYTX</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Biotech</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>7.829999923706055</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>44.50549105057007</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0.018661516252568</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0.5979421758434895</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>-0.07418810638797831</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>6.441714423043387</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>9.912428174700056</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0.6941427503313337</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T34" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U34" s="5" t="inlineStr"/>
+      <c r="V34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
           <t>SKHY</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>High Yield ETF</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n">
-        <v>184.4900054931641</v>
-      </c>
-      <c r="E34" s="5" t="n">
+      <c r="D35" s="3" t="n">
+        <v>184.4600067138672</v>
+      </c>
+      <c r="E35" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="5" t="n">
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="5" t="n">
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="n">
         <v>0.0951078537291295</v>
       </c>
-      <c r="L34" s="5" t="inlineStr"/>
-      <c r="M34" s="5" t="n">
-        <v>0.5223382795505496</v>
-      </c>
-      <c r="N34" s="5" t="inlineStr"/>
-      <c r="O34" s="5" t="n">
-        <v>169.730805053711</v>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>214.0084063720703</v>
-      </c>
-      <c r="Q34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="5" t="inlineStr">
-        <is>
-          <t>MACD improving</t>
-        </is>
-      </c>
-      <c r="T34" s="5" t="inlineStr">
-        <is>
-          <t>Missing volume trend; Missing ATR; Missing RSI</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>KYTX</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Biotech</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>7.804999828338623</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>44.25022554353953</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>0.018661516252568</v>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v>0.5597299361658986</v>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v>-0.07578355406954621</v>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v>0.6941427503313337</v>
-      </c>
-      <c r="O35" s="4" t="n">
-        <v>6.416714327675956</v>
-      </c>
-      <c r="P35" s="4" t="n">
-        <v>10.58157082966396</v>
-      </c>
-      <c r="Q35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="4" t="inlineStr"/>
-      <c r="T35" s="4" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="n">
+        <v>0.5204238275384478</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>169.7032061767578</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>212.1290077209472</v>
+      </c>
+      <c r="P35" s="3" t="inlineStr"/>
+      <c r="Q35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>Missing ATR</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3217,10 +3393,10 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>15.13000011444092</v>
+        <v>15.10999965667725</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -3237,25 +3413,25 @@
         <v>50</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>24.01784938056713</v>
+        <v>23.97503582866533</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>0.0323432829789085</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.3137890375200967</v>
+        <v>0.3308554198893791</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>-0.210941478312526</v>
+        <v>-0.2122178608022866</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>1.623785904475621</v>
+        <v>11.86101354871478</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>11.88242830548968</v>
+        <v>19.98347881862095</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>21.6251437323434</v>
+        <v>1.624493053981236</v>
       </c>
       <c r="Q36" s="5" t="n">
         <v>0</v>
@@ -3263,12 +3439,14 @@
       <c r="R36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S36" s="5" t="inlineStr"/>
-      <c r="T36" s="5" t="inlineStr">
-        <is>
-          <t>RSI weak</t>
-        </is>
-      </c>
+      <c r="S36" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T36" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U36" s="5" t="inlineStr"/>
+      <c r="V36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3290,7 +3468,7 @@
         <v>91.44000244140624</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
@@ -3313,32 +3491,34 @@
         <v>0.0177384274683925</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.7312825584700605</v>
+        <v>0.7758579724205982</v>
       </c>
       <c r="M37" s="5" t="n">
         <v>-0.7804217666388213</v>
       </c>
       <c r="N37" s="5" t="n">
+        <v>84.71464484078543</v>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>100.4071459089007</v>
+      </c>
+      <c r="P37" s="5" t="n">
         <v>4.48357173374721</v>
       </c>
-      <c r="O37" s="5" t="n">
-        <v>84.71464484078543</v>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v>104.8907176426479</v>
-      </c>
       <c r="Q37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R37" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S37" s="5" t="inlineStr"/>
-      <c r="T37" s="5" t="inlineStr">
-        <is>
-          <t>RSI weak</t>
-        </is>
-      </c>
+      <c r="S37" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T37" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U37" s="5" t="inlineStr"/>
+      <c r="V37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3357,10 +3537,10 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>8.573800086975098</v>
+        <v>8.559900283813477</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
@@ -3377,38 +3557,40 @@
         <v>50</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>20.79309128159542</v>
+        <v>20.51078645679097</v>
       </c>
       <c r="K38" s="5" t="n">
         <v>0.0299401183926648</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.4296593404421607</v>
+        <v>0.467624741481268</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>-0.1159333540085283</v>
+        <v>-0.1168204069738293</v>
       </c>
       <c r="N38" s="5" t="n">
+        <v>7.21275806427002</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>10.58061361312866</v>
+      </c>
+      <c r="P38" s="5" t="n">
         <v>0.6735711097717285</v>
       </c>
-      <c r="O38" s="5" t="n">
-        <v>7.226657867431641</v>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v>11.26808452606201</v>
-      </c>
       <c r="Q38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R38" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S38" s="5" t="inlineStr"/>
-      <c r="T38" s="5" t="inlineStr">
-        <is>
-          <t>RSI weak</t>
-        </is>
-      </c>
+      <c r="S38" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T38" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U38" s="5" t="inlineStr"/>
+      <c r="V38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3427,10 +3609,10 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>45.81999969482422</v>
+        <v>45.66999816894531</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
@@ -3447,25 +3629,25 @@
         <v>50</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>23.09511958709545</v>
+        <v>22.90686414096366</v>
       </c>
       <c r="K39" s="5" t="n">
         <v>0.0251036384349932</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.281522694219697</v>
+        <v>0.3007363629922642</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>-0.3513657399980205</v>
+        <v>-0.3609384869486964</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>3.439085824148996</v>
+        <v>38.78325489589146</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>38.94182804652623</v>
+        <v>56.00011307852608</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>59.5763429914202</v>
+        <v>3.443371636526925</v>
       </c>
       <c r="Q39" s="5" t="n">
         <v>0</v>
@@ -3473,12 +3655,14 @@
       <c r="R39" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S39" s="5" t="inlineStr"/>
-      <c r="T39" s="5" t="inlineStr">
-        <is>
-          <t>RSI weak</t>
-        </is>
-      </c>
+      <c r="S39" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T39" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U39" s="5" t="inlineStr"/>
+      <c r="V39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3497,10 +3681,10 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>7.755000114440918</v>
+        <v>7.71999979019165</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
@@ -3517,38 +3701,40 @@
         <v>50</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>27.01664839096489</v>
+        <v>26.35658618633685</v>
       </c>
       <c r="K40" s="5" t="n">
         <v>0.0100267124430337</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0.6217934494930202</v>
+        <v>0.7593603373994126</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>-0.1036413462820309</v>
+        <v>-0.1058749852084818</v>
       </c>
       <c r="N40" s="5" t="n">
+        <v>6.604571206229074</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>9.393142666135516</v>
+      </c>
+      <c r="P40" s="5" t="n">
         <v>0.5577142919812884</v>
       </c>
-      <c r="O40" s="5" t="n">
-        <v>6.639571530478341</v>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v>9.985857282366071</v>
-      </c>
       <c r="Q40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S40" s="5" t="inlineStr"/>
-      <c r="T40" s="5" t="inlineStr">
-        <is>
-          <t>RSI weak</t>
-        </is>
-      </c>
+      <c r="S40" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T40" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="U40" s="5" t="inlineStr"/>
+      <c r="V40" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3602,10 +3788,10 @@
         <v>0.74662492</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>17.1200008392334</v>
+        <v>17.04999923706055</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>12.78221925699257</v>
+        <v>12.72995431637039</v>
       </c>
     </row>
     <row r="3">
@@ -3618,10 +3804,10 @@
         <v>0.05285969</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>356.6700134277344</v>
+        <v>357.8699951171875</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>18.85346634208588</v>
+        <v>18.91689700219604</v>
       </c>
     </row>
     <row r="4">
@@ -3634,10 +3820,10 @@
         <v>0.6115135</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>18.56500053405762</v>
+        <v>18.59499931335449</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>11.35274845408344</v>
+        <v>11.371093112607</v>
       </c>
     </row>
     <row r="5">
@@ -3650,10 +3836,10 @@
         <v>0.02721351</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>395.7851867675781</v>
+        <v>395.7550048828125</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>10.77070413795136</v>
+        <v>10.76988278292847</v>
       </c>
     </row>
   </sheetData>
@@ -3981,46 +4167,46 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>369.8450012207031</v>
+        <v>368.0950012207031</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>331.9726992797852</v>
+        <v>331.9376992797851</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>201.2462250900268</v>
+        <v>201.2374750900269</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>46.14959731343965</v>
+        <v>45.88121563095124</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.0073403441890798</v>
+        <v>0.0025738998772397</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.167907315292186</v>
+        <v>1.157649402411819</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>1.143159213789976</v>
+        <v>1.133018401796429</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>14.88644807632801</v>
+        <v>14.74684693672685</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>26.07828698221125</v>
+        <v>26.05036675429102</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-11.19183890588324</v>
+        <v>-11.30351981756416</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>-10.00415359792669</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>1556406</v>
+        <v>1623462</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>6118044.12</v>
+        <v>6119385.24</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>0.2543960078535687</v>
+        <v>0.2652982180935547</v>
       </c>
       <c r="P2" s="6" t="n">
         <v>0.082723417254077</v>
@@ -4034,7 +4220,7 @@
         <v>46.42792184012277</v>
       </c>
       <c r="S2" s="6" t="n">
-        <v>0.1255334577644248</v>
+        <v>0.1261302698655378</v>
       </c>
       <c r="T2" s="6" t="inlineStr">
         <is>
@@ -4049,46 +4235,46 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>555.3699951171875</v>
+        <v>557.6199951171875</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>489.8588000488281</v>
+        <v>489.9038000488281</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>291.5036496734619</v>
+        <v>291.5148996734619</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>55.86565004537624</v>
+        <v>56.19119939331</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.0856187563107262</v>
+        <v>0.0900169813195939</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.177323790214419</v>
+        <v>1.186144897892281</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1.674033360242601</v>
+        <v>1.684866813820294</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>17.36325304505715</v>
+        <v>17.54274022454445</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>19.96055420811186</v>
+        <v>19.99645164400932</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-2.597301163054709</v>
+        <v>-2.45371141946487</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>-3.577422784539042</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>14011669</v>
+        <v>14421509</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>33851701.38</v>
+        <v>33859898.18</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.4139132873326793</v>
+        <v>0.4259170811245481</v>
       </c>
       <c r="P3" s="6" t="n">
         <v>0.0624019610194614</v>
@@ -4102,7 +4288,7 @@
         <v>38.05143519810268</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0.0685154681251253</v>
+        <v>0.06823900780334451</v>
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
@@ -4117,46 +4303,46 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>246.1929016113281</v>
+        <v>246.0800018310547</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>253.3426577758789</v>
+        <v>253.3403997802734</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>233.5961145019532</v>
+        <v>233.5955500030518</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>64.89615497050171</v>
+        <v>64.71600352674133</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0320389790894786</v>
+        <v>0.031565703973867</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.0113529138728935</v>
+        <v>-0.0118062902215256</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.0011242731691588</v>
+        <v>-0.0015823401944126</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.7573528075893989</v>
+        <v>-0.7663590578676178</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-2.415944406588085</v>
+        <v>-2.417745656643728</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>1.658591598998686</v>
+        <v>1.65138659877611</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>1.780135958077288</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>13061792</v>
+        <v>14144006</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>48677443.84</v>
+        <v>48699088.12</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.2683335641644078</v>
+        <v>0.2904367729668282</v>
       </c>
       <c r="P4" s="6" t="n">
         <v>-0.0071974396379796</v>
@@ -4170,7 +4356,7 @@
         <v>7.47785404750279</v>
       </c>
       <c r="S4" s="6" t="n">
-        <v>0.030373962850108</v>
+        <v>0.0303878982113982</v>
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
@@ -4185,46 +4371,46 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>182.634994506836</v>
+        <v>182.8500061035156</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>160.7940994262695</v>
+        <v>160.7983996582031</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>144.3334746170044</v>
+        <v>144.3345496749878</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>62.44594972357781</v>
+        <v>62.54404908025502</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.1188127196827621</v>
+        <v>0.1201298698263813</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.1830990495801436</v>
+        <v>0.1844918824069923</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.4797844532199173</v>
+        <v>0.4815265663285675</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>6.016367273637002</v>
+        <v>6.033519195879251</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.407852367207813</v>
+        <v>4.411282751656263</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>1.608514906429189</v>
+        <v>1.622236444222988</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>1.773262942271622</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>3244887</v>
+        <v>3378729</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>10338953.74</v>
+        <v>10341630.58</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.3138506159908594</v>
+        <v>0.3267114381879226</v>
       </c>
       <c r="P5" s="6" t="n">
         <v>0.0151807899125376</v>
@@ -4238,7 +4424,7 @@
         <v>10.46220506940569</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>0.0572847777484073</v>
+        <v>0.0572174171188312</v>
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
@@ -4253,46 +4439,46 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>282.2300109863281</v>
+        <v>285.5400085449219</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>312.5799984741211</v>
+        <v>312.646198425293</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>182.8167750167847</v>
+        <v>182.8333250045776</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>28.30257054769397</v>
+        <v>28.79400118305021</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-0.2588692187817298</v>
+        <v>-0.2501772265026026</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.7505893118060929</v>
+        <v>0.7711202480021699</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1.53940986626112</v>
+        <v>1.569192101071012</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-8.071049150317378</v>
+        <v>-7.807003761027829</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>1.962069890723562</v>
+        <v>2.014878968581472</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-10.03311904104094</v>
+        <v>-9.8218827296093</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>-9.368367243321137</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>5673363</v>
+        <v>5976818</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>11175941.26</v>
+        <v>11182010.36</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.507640731819666</v>
+        <v>0.5345029925370236</v>
       </c>
       <c r="P6" s="6" t="n">
         <v>0.0376936349020097</v>
@@ -4306,7 +4492,7 @@
         <v>29.38128662109375</v>
       </c>
       <c r="S6" s="6" t="n">
-        <v>0.1041040480366102</v>
+        <v>0.1028972674295882</v>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
@@ -4321,46 +4507,46 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>69.16999816894531</v>
+        <v>69.48989868164062</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>86.03660011291504</v>
+        <v>86.04299812316894</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>83.06889984130859</v>
+        <v>83.07049934387207</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>46.62654509530972</v>
+        <v>46.93608515837733</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.1606601735809845</v>
+        <v>-0.1567783570723123</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.2190358088825034</v>
+        <v>-0.2154239706325592</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.2969814147979083</v>
+        <v>-0.2937300628853178</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-4.812992788136086</v>
+        <v>-4.787473658918216</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-4.034258591350639</v>
+        <v>-4.029154765507065</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>-0.7787341967854466</v>
+        <v>-0.7583188934111513</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>-0.7205249641778009</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>6364689</v>
+        <v>6522733</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>23131499.78</v>
+        <v>23134660.66</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.275152457062168</v>
+        <v>0.2819463443126206</v>
       </c>
       <c r="P7" s="6" t="n">
         <v>0.0334417645102432</v>
@@ -4374,7 +4560,7 @@
         <v>6.955285753522601</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>0.1005535049536152</v>
+        <v>0.1000906014467999</v>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
@@ -4389,46 +4575,46 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>394.5700073242188</v>
+        <v>393.7349853515625</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>405.5652008056641</v>
+        <v>405.5485003662109</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>362.9483502197265</v>
+        <v>362.9441751098633</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>55.83900718527268</v>
+        <v>55.53833938277076</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0327165172883949</v>
+        <v>0.0305309964240272</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.0362151599063234</v>
+        <v>0.0340222349225187</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.1202692055785799</v>
+        <v>0.1178983984098036</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-3.37577143267157</v>
+        <v>-3.442382872085716</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-6.704243254064938</v>
+        <v>-6.717565541947767</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>3.328471821393368</v>
+        <v>3.275182669862051</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>3.038872772970159</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>9522151</v>
+        <v>9838026</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>27426055.02</v>
+        <v>27432372.52</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.34719360816042</v>
+        <v>0.35862833201275</v>
       </c>
       <c r="P8" s="6" t="n">
         <v>0.030087289573326</v>
@@ -4442,7 +4628,7 @@
         <v>15.00356619698661</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>0.038025105604791</v>
+        <v>0.0381057481686318</v>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
@@ -4457,46 +4643,46 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>7.710000038146973</v>
+        <v>7.625</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>5.822799992561341</v>
+        <v>5.821099991798401</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4.04539999961853</v>
+        <v>4.044974999427796</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>50.38910466129628</v>
+        <v>49.56937729178416</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.3916967673711176</v>
+        <v>0.3763538000909261</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.7364864726991935</v>
+        <v>0.717342320210109</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.8056206258984668</v>
+        <v>0.785714293690819</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.6116745928918901</v>
+        <v>0.6048939630682</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.7323433940000577</v>
+        <v>0.7309872680353197</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-0.1206688011081675</v>
+        <v>-0.1260933049671196</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>-0.0949479297406228</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>3380823</v>
+        <v>3640226</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>7806252.46</v>
+        <v>7811440.52</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4330916809728698</v>
+        <v>0.4660121255074218</v>
       </c>
       <c r="P9" s="6" t="n">
         <v>-0.0049382666628676</v>
@@ -4510,7 +4696,7 @@
         <v>0.7386070660182408</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>0.0957985813701446</v>
+        <v>0.0968665004614086</v>
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
@@ -4525,46 +4711,46 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>17.1200008392334</v>
+        <v>17.04999923706055</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>9.907800045013428</v>
+        <v>9.906400012969971</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.553649994134903</v>
+        <v>6.553299986124038</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>75.1381247005498</v>
+        <v>74.97682986607725</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1.161616246756966</v>
+        <v>1.152777660709173</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>3.782123241363253</v>
+        <v>3.762569720786531</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>2.324271946059441</v>
+        <v>2.310679402199914</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>2.35291019650346</v>
+        <v>2.347326023110753</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>2.209672769092763</v>
+        <v>2.208555934414222</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1432374274106971</v>
+        <v>0.1387700886965315</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>0.2137816411175577</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>722140</v>
+        <v>764280</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>3922696.8</v>
+        <v>3923539.6</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.1840927394643399</v>
+        <v>0.1947934971779053</v>
       </c>
       <c r="P10" s="6" t="n">
         <v>0.0098826338563442</v>
@@ -4578,7 +4764,7 @@
         <v>1.499500070299421</v>
       </c>
       <c r="S10" s="6" t="n">
-        <v>0.0875876166351032</v>
+        <v>0.0879472221347698</v>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
@@ -4593,46 +4779,46 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>275.4800109863281</v>
+        <v>275.3500061035156</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>300.9968014526367</v>
+        <v>300.9942013549805</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>276.0421009063721</v>
+        <v>276.041450881958</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>61.14814244093061</v>
+        <v>61.05015706408463</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.0658844814841987</v>
+        <v>-0.0663253104869391</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.0840232386157003</v>
+        <v>-0.08445550755273271</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.0436034765783919</v>
+        <v>0.0431109778769813</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-6.667593425464077</v>
+        <v>-6.677964185346525</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-12.53550884642297</v>
+        <v>-12.53758299839946</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>5.867915420958891</v>
+        <v>5.859618813052931</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>5.61249043240821</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>295981</v>
+        <v>307237</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>1551627.62</v>
+        <v>1551852.74</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.1907551761678488</v>
+        <v>0.1979807697475212</v>
       </c>
       <c r="P11" s="6" t="n">
         <v>-0.0092015237095138</v>
@@ -4646,7 +4832,7 @@
         <v>11.86785343715123</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>0.0430806336716032</v>
+        <v>0.0431009739389277</v>
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
@@ -4661,46 +4847,46 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>105</v>
+        <v>104.9100036621094</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>112.2757997131348</v>
+        <v>112.273999786377</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>101.2306499290466</v>
+        <v>101.2301999473572</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>65.08260145047174</v>
+        <v>65.01839145146317</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.1857707101221339</v>
+        <v>0.1847543765841439</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.1311543125713421</v>
+        <v>-0.1318990071433482</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.004688526014293</v>
+        <v>0.0038273994613213</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.6784539010890285</v>
+        <v>0.6712747060436186</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.7650341516486222</v>
+        <v>-0.7664699906577042</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>1.443488052737651</v>
+        <v>1.437744696701323</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>1.911196160245703</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>471634</v>
+        <v>540921</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>1507400.68</v>
+        <v>1508786.42</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.3128789884849992</v>
+        <v>0.3585139638253107</v>
       </c>
       <c r="P12" s="6" t="n">
         <v>0</v>
@@ -4714,7 +4900,7 @@
         <v>5.971429007393973</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>0.0568707524513711</v>
+        <v>0.0569195386421542</v>
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
@@ -4729,46 +4915,46 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>238.8999938964844</v>
+        <v>239.25</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>227.4191998291016</v>
+        <v>227.4261999511719</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>161.835650177002</v>
+        <v>161.8374002075195</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>41.32581837733308</v>
+        <v>41.43323997010419</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.0474861599539188</v>
+        <v>-0.0460906569559418</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4976177751878818</v>
+        <v>0.4998118956376145</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.5307232824061781</v>
+        <v>0.5329659048646274</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.393268768153746</v>
+        <v>5.421189482964081</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>10.04804276603066</v>
+        <v>10.05362690899272</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>-4.654773997876911</v>
+        <v>-4.632437426028641</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>-4.078359216969876</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>2139823</v>
+        <v>2253472</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>8659198.460000001</v>
+        <v>8661471.439999999</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2471155973482561</v>
+        <v>0.2601719598812185</v>
       </c>
       <c r="P13" s="6" t="n">
         <v>0.06596166699561611</v>
@@ -4782,7 +4968,7 @@
         <v>26.78535788399833</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>0.1121195419352101</v>
+        <v>0.1119555188463879</v>
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
@@ -4797,46 +4983,46 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>356.6700134277344</v>
+        <v>357.8699951171875</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>372.2346008300781</v>
+        <v>372.2586004638672</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>319.9629499053955</v>
+        <v>319.9689498138428</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>58.83340486164004</v>
+        <v>59.64509105642299</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.008368492296873699</v>
+        <v>-0.0050322442044344</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.07137066926273709</v>
+        <v>0.0749751920354173</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.0747605290523016</v>
+        <v>0.0783764566796769</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-2.155963263926367</v>
+        <v>-2.060238228870276</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-2.672234823140482</v>
+        <v>-2.653089816129264</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.5162715592141147</v>
+        <v>0.5928515872589877</v>
       </c>
       <c r="L14" s="6" t="n">
         <v>0.5974640052565006</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>7415689</v>
+        <v>7820884</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>31739783.78</v>
+        <v>31747887.68</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.233640186442379</v>
+        <v>0.2463434442892674</v>
       </c>
       <c r="P14" s="6" t="n">
         <v>-0.0040282924977889</v>
@@ -4850,7 +5036,7 @@
         <v>9.923573085239957</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>0.0278228410341274</v>
+        <v>0.0277295476587535</v>
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
@@ -4865,46 +5051,46 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>106.75</v>
+        <v>107.4000015258789</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>117.416199798584</v>
+        <v>117.4291998291016</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>63.21174997329712</v>
+        <v>63.21499998092651</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>30.70294698798626</v>
+        <v>31.37724628863623</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.1430520971219415</v>
+        <v>-0.1378341351128598</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.6729352405982301</v>
+        <v>0.683121755437438</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1.422832425618384</v>
+        <v>1.437585069867572</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-2.059521728507249</v>
+        <v>-2.007669754932863</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>1.398073721026311</v>
+        <v>1.408444115741188</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-3.45759544953356</v>
+        <v>-3.416113870674052</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>-3.642499733942029</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>53540898</v>
+        <v>55794844</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>129903577.96</v>
+        <v>129948656.88</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.4121587629902415</v>
+        <v>0.4293606824387826</v>
       </c>
       <c r="P15" s="6" t="n">
         <v>0.0469355722360184</v>
@@ -4918,7 +5104,7 @@
         <v>9.479286193847656</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>0.08879893390021221</v>
+        <v>0.0882615089308313</v>
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
@@ -4933,46 +5119,46 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>39.0099983215332</v>
+        <v>39.06000137329102</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>54.89560012817383</v>
+        <v>54.89660018920898</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>48.68770003318787</v>
+        <v>48.68795004844665</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>16.64305219071599</v>
+        <v>16.79038701584251</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-0.3256698470098641</v>
+        <v>-0.3248054899990307</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.0908836731696092</v>
+        <v>0.09228196886605231</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.2343474438196926</v>
+        <v>-0.2333660296683863</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-4.198556605793336</v>
+        <v>-4.194567758359661</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-2.74328545286213</v>
+        <v>-2.742487683375395</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-1.455271152931205</v>
+        <v>-1.452080074984266</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>-1.449196603544823</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>8944675</v>
+        <v>9543757</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>28808499.5</v>
+        <v>28820481.14</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.3104873615510589</v>
+        <v>0.3311449574224561</v>
       </c>
       <c r="P16" s="6" t="n">
         <v>0.0298353862022756</v>
@@ -4986,7 +5172,7 @@
         <v>3.701071330479213</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>0.09487494205905279</v>
+        <v>0.09475348695225549</v>
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
@@ -5001,46 +5187,46 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>7.804999828338623</v>
+        <v>7.829999923706055</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>8.696899948120118</v>
+        <v>8.697399950027465</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>8.190574967861176</v>
+        <v>8.190699968338013</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>44.25022554353953</v>
+        <v>44.50549105057007</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-0.0310366812371837</v>
+        <v>-0.0279330071936995</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.1661324663862905</v>
+        <v>-0.1634615159285523</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.0516403083276746</v>
+        <v>-0.0486026294992456</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.031088496035494</v>
+        <v>0.0330828056374539</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.1068720501050402</v>
+        <v>0.1072709120254322</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.07578355406954621</v>
+        <v>-0.07418810638797831</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>-0.0068890358413925</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>587420</v>
+        <v>628008</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1049470.4</v>
+        <v>1050282.16</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5597299361658986</v>
+        <v>0.5979421758434895</v>
       </c>
       <c r="P17" s="6" t="n">
         <v>0.018661516252568</v>
@@ -5054,7 +5240,7 @@
         <v>0.6941427503313337</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>0.088935652222697</v>
+        <v>0.088651693115571</v>
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
@@ -5069,46 +5255,46 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1154</v>
+        <v>1157.699951171875</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1097.755601806641</v>
+        <v>1097.829600830078</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1000.562803039551</v>
+        <v>1000.58130279541</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>57.41560404426107</v>
+        <v>58.0950473448579</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.0185348631950572</v>
+        <v>0.0218004864712046</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.2509485094850949</v>
+        <v>0.2549592966632792</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.06753006475485659</v>
+        <v>0.0709527762922062</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>27.58219303342866</v>
+        <v>27.87734583346446</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>34.60333144952408</v>
+        <v>34.66236200953124</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-7.021138416095418</v>
+        <v>-6.785016176066783</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>-3.468572913063639</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>1213871</v>
+        <v>1264564</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>3184177.42</v>
+        <v>3185191.28</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.3812196495005608</v>
+        <v>0.3970135193890146</v>
       </c>
       <c r="P18" s="6" t="n">
         <v>-0.013419399271567</v>
@@ -5122,7 +5308,7 @@
         <v>41.49965122767857</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>0.0359615695213852</v>
+        <v>0.0358466381428718</v>
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
@@ -5137,46 +5323,46 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>15.13000011444092</v>
+        <v>15.10999965667725</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>27.45600004196167</v>
+        <v>27.4556000328064</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>19.0212750339508</v>
+        <v>19.02117503166198</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>24.01784938056713</v>
+        <v>23.97503582866533</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.4316303667375605</v>
+        <v>-0.4323816987110064</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.3607942515558348</v>
+        <v>-0.361639222307808</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.2119791920193358</v>
+        <v>-0.2130208824864672</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-3.40496480064408</v>
+        <v>-3.406560278756281</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-3.194023322331554</v>
+        <v>-3.194342417953994</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.210941478312526</v>
+        <v>-0.2122178608022866</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>-0.2400474448421516</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>4473413</v>
+        <v>4718334</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>14256116.26</v>
+        <v>14261014.68</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.3137890375200967</v>
+        <v>0.3308554198893791</v>
       </c>
       <c r="P19" s="6" t="n">
         <v>0.0323432829789085</v>
@@ -5187,10 +5373,10 @@
         </is>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.623785904475621</v>
+        <v>1.624493053981236</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.1073222665032096</v>
+        <v>0.1075111244799637</v>
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
@@ -5205,46 +5391,46 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>222.8399963378907</v>
+        <v>223.0299987792969</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>233.8426000976562</v>
+        <v>233.8464001464844</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>128.1934501647949</v>
+        <v>128.194400177002</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>33.59411998846861</v>
+        <v>33.66770296216299</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.2032892863338646</v>
+        <v>-0.2026099783856562</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.6650974616230001</v>
+        <v>0.6665171914205541</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>1.688382168883447</v>
+        <v>1.690674392828498</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-4.997399303391035</v>
+        <v>-4.982242413478303</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>4.124918441768004</v>
+        <v>4.127949819750549</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-9.122317745159036</v>
+        <v>-9.110192233228853</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>-9.60956168128553</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>11752122</v>
+        <v>12136697</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>45209036.44</v>
+        <v>45216727.94</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.2599507294431511</v>
+        <v>0.2684116598641259</v>
       </c>
       <c r="P20" s="6" t="n">
         <v>0.0645198535414377</v>
@@ -5258,7 +5444,7 @@
         <v>21.60285949707031</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>0.09694336677476</v>
+        <v>0.0968607793360021</v>
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
@@ -5273,46 +5459,46 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>987.3599853515624</v>
+        <v>988.1630859375</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>916.8222009277343</v>
+        <v>916.8382629394532</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>472.4647502136231</v>
+        <v>472.4687657165528</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>45.1502141583485</v>
+        <v>45.2164692088228</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.0058577236232377</v>
+        <v>0.0066758699317739</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>1.120345268192729</v>
+        <v>1.122069918322914</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1.854714196925425</v>
+        <v>1.857036169334929</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>9.783608462789855</v>
+        <v>9.847673466796325</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>34.4835399846632</v>
+        <v>34.4963529854645</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-24.69993152187335</v>
+        <v>-24.64867951866817</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>-28.83193491040208</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>19898479</v>
+        <v>20493480</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>53909273.58</v>
+        <v>53921173.6</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.3691105013773031</v>
+        <v>0.380063686150926</v>
       </c>
       <c r="P21" s="6" t="n">
         <v>0.0543756800501934</v>
@@ -5326,7 +5512,7 @@
         <v>89.7650146484375</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>0.090914171102929</v>
+        <v>0.09084028327497649</v>
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
@@ -5341,46 +5527,46 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>196.7700042724609</v>
+        <v>193.9100036621093</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>224.0420001220703</v>
+        <v>223.9848001098633</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>136.7523254776001</v>
+        <v>136.7380254745484</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>30.35052655812525</v>
+        <v>29.92199908218262</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-0.153167482546069</v>
+        <v>-0.1654759719712673</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.2150796671974673</v>
+        <v>0.1974188016470521</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.8333178134310608</v>
+        <v>0.8066710179259846</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-6.439270121315616</v>
+        <v>-6.667418318152784</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.4844173606266095</v>
+        <v>0.438787721259176</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-6.923687481942226</v>
+        <v>-7.10620603941196</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>-6.66147091221397</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>10210092</v>
+        <v>11167031</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>17901459.84</v>
+        <v>17920598.62</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.5703496860734236</v>
+        <v>0.6231393959985919</v>
       </c>
       <c r="P22" s="6" t="n">
         <v>0.0310198990532244</v>
@@ -5391,10 +5577,10 @@
         </is>
       </c>
       <c r="R22" s="6" t="n">
-        <v>25.34157235281808</v>
+        <v>25.56014360700335</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>0.1287877816871337</v>
+        <v>0.1318144661146117</v>
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
@@ -5409,46 +5595,46 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>211.2200012207031</v>
+        <v>211.3099975585937</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>209.317600402832</v>
+        <v>209.3194003295899</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>191.9672004699707</v>
+        <v>191.9676504516601</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>60.30225678806677</v>
+        <v>60.36799095758673</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.029387390747845</v>
+        <v>0.0298259907615874</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.07485627767067821</v>
+        <v>0.07531425100743649</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.1421001321097259</v>
+        <v>0.1425867566187699</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.6329247329459804</v>
+        <v>-0.6257455379005705</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-2.267923477861737</v>
+        <v>-2.266487638852655</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1.634998744915757</v>
+        <v>1.640742100952084</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>1.206196025562167</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>61616072</v>
+        <v>66406268</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>157619085.44</v>
+        <v>157714889.36</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.390917583540066</v>
+        <v>0.4210526239435837</v>
       </c>
       <c r="P23" s="6" t="n">
         <v>0.0229450115312453</v>
@@ -5459,10 +5645,10 @@
         </is>
       </c>
       <c r="R23" s="6" t="n">
-        <v>6.863571166992188</v>
+        <v>6.875713893345424</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>0.0324948921850467</v>
+        <v>0.0325385167421568</v>
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
@@ -5510,13 +5696,13 @@
         <v>-0.7934742332941171</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>2377597</v>
+        <v>2524808</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3251269.94</v>
+        <v>3254214.16</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.7312825584700605</v>
+        <v>0.7758579724205982</v>
       </c>
       <c r="P24" s="6" t="n">
         <v>0.0177384274683925</v>
@@ -5545,46 +5731,46 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>25.54999923706055</v>
+        <v>25.60000038146973</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>35.87440006256104</v>
+        <v>35.87540008544922</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>25.36849997997284</v>
+        <v>25.36874998569489</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>41.0456714719076</v>
+        <v>41.16938033603359</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.1797752953466632</v>
+        <v>-0.1781701221517513</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.2469791038238489</v>
+        <v>-0.2455054479452914</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.0043238482977101</v>
+        <v>0.0062893020461187</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-2.461635634016321</v>
+        <v>-2.457646938735817</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-2.399118755044602</v>
+        <v>-2.398321015988501</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.0625168789717189</v>
+        <v>-0.0593259227473152</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>-0.0149246408257801</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>2450919</v>
+        <v>2582135</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>13297572.38</v>
+        <v>13300196.7</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.1843132663587727</v>
+        <v>0.1941426174546727</v>
       </c>
       <c r="P25" s="6" t="n">
         <v>0.0084746235925221</v>
@@ -5595,10 +5781,10 @@
         </is>
       </c>
       <c r="R25" s="6" t="n">
-        <v>2.366592815944127</v>
+        <v>2.376357078552246</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>0.0926259446814917</v>
+        <v>0.0928264469977252</v>
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
@@ -5613,46 +5799,46 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>13.80500030517578</v>
+        <v>13.76000022888184</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>11.47430004119873</v>
+        <v>11.47340003967285</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>9.128750011920928</v>
+        <v>9.128525011539461</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>75.64245676712319</v>
+        <v>75.39503211062105</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.2162995454796763</v>
+        <v>0.2123347811817462</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.5705347400553955</v>
+        <v>0.5654152774286336</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.608974408849742</v>
+        <v>0.6037296446662819</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.6853999592776017</v>
+        <v>0.681810209601732</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.6478613781227811</v>
+        <v>0.6471434281876072</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.0375385811548205</v>
+        <v>0.0346667814141248</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>0.042571941463545</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>141664</v>
+        <v>148646</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>662975.28</v>
+        <v>663114.92</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.2136791585954758</v>
+        <v>0.2241632566493904</v>
       </c>
       <c r="P26" s="6" t="n">
         <v>-0.0110537672736636</v>
@@ -5666,7 +5852,7 @@
         <v>0.6038284982953753</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>0.0437398395470507</v>
+        <v>0.0438828843205944</v>
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
@@ -5681,46 +5867,46 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>79.56500244140625</v>
+        <v>79.67500305175781</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>107.0294999694824</v>
+        <v>107.0316999816895</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>77.06737512588501</v>
+        <v>77.06792512893676</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>37.83339740394094</v>
+        <v>37.94018845028621</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-0.2229221318908395</v>
+        <v>-0.2218478022589683</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.1017031445105758</v>
+        <v>0.1032262767245368</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.0948236511920733</v>
+        <v>-0.0935722221995587</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-7.648074583418648</v>
+        <v>-7.639299605954704</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-6.250874959664553</v>
+        <v>-6.249119964171764</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-1.397199623754095</v>
+        <v>-1.39017964178294</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>-1.60128212643402</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>9923025</v>
+        <v>10227320</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>28164752.5</v>
+        <v>28170838.4</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.3523206887758023</v>
+        <v>0.363046347956758</v>
       </c>
       <c r="P27" s="6" t="n">
         <v>0.0264563885114627</v>
@@ -5734,7 +5920,7 @@
         <v>7.732856750488281</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>0.09718917254081599</v>
+        <v>0.0970549915820514</v>
       </c>
       <c r="T27" s="6" t="inlineStr">
         <is>
@@ -5749,46 +5935,46 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>18.56500053405762</v>
+        <v>18.59499931335449</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>16.94689994812012</v>
+        <v>16.94749992370605</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>21.97300002574921</v>
+        <v>21.97315001964569</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>62.08528783568838</v>
+        <v>62.29968817312163</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.1197225946613795</v>
+        <v>0.1215319299710848</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.0365717862772707</v>
+        <v>0.0382467600099596</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.3020676591046031</v>
+        <v>-0.3009398854629992</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.4048847760322971</v>
+        <v>0.4072778410474384</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.3716194461549978</v>
+        <v>0.3720980591580261</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.0332653298772992</v>
+        <v>0.0351797818894123</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>0.0328078631428616</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>47284001</v>
+        <v>50694519</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>76139758.02</v>
+        <v>76207968.38</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.621015908503146</v>
+        <v>0.6652128389936749</v>
       </c>
       <c r="P28" s="6" t="n">
         <v>0.0044125718372439</v>
@@ -5802,7 +5988,7 @@
         <v>0.9414285932268416</v>
       </c>
       <c r="S28" s="6" t="n">
-        <v>0.050709860821161</v>
+        <v>0.0506280520564864</v>
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
@@ -5850,13 +6036,13 @@
         <v>0.0646032293833483</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>277020</v>
+        <v>293038</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>1211672.4</v>
+        <v>1211992.76</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2286261534058216</v>
+        <v>0.241781972360957</v>
       </c>
       <c r="P29" s="6" t="n">
         <v>0.0046656626141934</v>
@@ -5885,46 +6071,46 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>395.7851867675781</v>
+        <v>395.7550048828125</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>409.9187030029297</v>
+        <v>409.9180993652344</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>417.7494259643555</v>
+        <v>417.7492750549316</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>54.21191253815941</v>
+        <v>54.20369849720209</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-0.0261909950053679</v>
+        <v>-0.0262652559735777</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.08672480368449891</v>
+        <v>0.08664193195535549</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.1184399628019428</v>
+        <v>-0.1185071890255263</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-1.326829590185582</v>
+        <v>-1.32923726190478</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-1.257437912174199</v>
+        <v>-1.257919446518039</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.0693916780113828</v>
+        <v>-0.0713178153867408</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>0.3816312784934397</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>14260868</v>
+        <v>14952588</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>48254507.36</v>
+        <v>48268341.76</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2955344232116517</v>
+        <v>0.3097804369237979</v>
       </c>
       <c r="P30" s="6" t="n">
         <v>0.0109940121352903</v>
@@ -5938,7 +6124,7 @@
         <v>18.56714085170201</v>
       </c>
       <c r="S30" s="6" t="n">
-        <v>0.0469121671868063</v>
+        <v>0.0469157448992968</v>
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
@@ -5953,46 +6139,46 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>421.5050048828125</v>
+        <v>422.3099975585938</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>425.0155004882813</v>
+        <v>425.0316003417969</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>349.7288250732422</v>
+        <v>349.7328500366211</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>45.29803446596495</v>
+        <v>45.57065028514946</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-0.005720255313059</v>
+        <v>-0.0038213741541671</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.1095448383208672</v>
+        <v>0.1116638534166607</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.2704735776009046</v>
+        <v>0.2728999353259491</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>1.257080966333774</v>
+        <v>1.321296906282101</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>5.392796731641146</v>
+        <v>5.405639919630812</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-4.135715765307372</v>
+        <v>-4.084343013348712</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>-3.711786865119478</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>8585234</v>
+        <v>8994036</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>13647108.68</v>
+        <v>13655284.72</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.629088124181334</v>
+        <v>0.6586487344952262</v>
       </c>
       <c r="P31" s="6" t="n">
         <v>0.0220361706931489</v>
@@ -6006,7 +6192,7 @@
         <v>19.97285679408482</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>0.0473846254794476</v>
+        <v>0.0472943025491923</v>
       </c>
       <c r="T31" s="6" t="inlineStr">
         <is>
@@ -6021,46 +6207,46 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>302.7901000976562</v>
+        <v>303.4923095703125</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>324.2176031494141</v>
+        <v>324.2316473388672</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>238.470500793457</v>
+        <v>238.4740118408203</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>45.38102772596008</v>
+        <v>45.57138320604898</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-0.0002637931152617</v>
+        <v>0.0020547246777753</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.0248620315776479</v>
+        <v>-0.0226005602866378</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.7808039891283258</v>
+        <v>0.7849339043062218</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-2.02144560185269</v>
+        <v>-1.965428891783233</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-1.203932972483995</v>
+        <v>-1.192729630470103</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.8175126293686956</v>
+        <v>-0.7726992613131298</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>-0.1480541656201379</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>1877670</v>
+        <v>1947718</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>6147051.4</v>
+        <v>6148452.36</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3054586464007768</v>
+        <v>0.3167818315827367</v>
       </c>
       <c r="P32" s="6" t="n">
         <v>0.031582057136426</v>
@@ -6074,7 +6260,7 @@
         <v>21.269287109375</v>
       </c>
       <c r="S32" s="6" t="n">
-        <v>0.0702443280097836</v>
+        <v>0.0700817992373127</v>
       </c>
       <c r="T32" s="6" t="inlineStr">
         <is>
@@ -6089,46 +6275,46 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>879.0700073242188</v>
+        <v>881.2999877929688</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>877.2043969726562</v>
+        <v>877.2489965820313</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>479.5721999359131</v>
+        <v>479.5833498382568</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>37.90452722844881</v>
+        <v>38.11380958860197</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-0.0558192686991134</v>
+        <v>-0.0534241186288932</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.6479266708551294</v>
+        <v>0.6521070481394426</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1.7344468622704</v>
+        <v>1.741383469190091</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-3.944148061664578</v>
+        <v>-3.766257881821275</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>11.24295508176911</v>
+        <v>11.27853311773778</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-15.18710314343369</v>
+        <v>-15.04479099955905</v>
       </c>
       <c r="L33" s="6" t="n">
         <v>-17.58862389405815</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>1833544</v>
+        <v>1959987</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>4335914.88</v>
+        <v>4338443.74</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.4228736150835138</v>
+        <v>0.4517719065777259</v>
       </c>
       <c r="P33" s="6" t="n">
         <v>0.0451049293978258</v>
@@ -6142,7 +6328,7 @@
         <v>84.29928588867188</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>0.0958959868796668</v>
+        <v>0.09565333831421211</v>
       </c>
       <c r="T33" s="6" t="inlineStr">
         <is>
@@ -6157,46 +6343,46 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>27.84000015258789</v>
+        <v>27.7947998046875</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>33.45719982147217</v>
+        <v>33.45629581451416</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>34.37764989852905</v>
+        <v>34.37742389678955</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>27.75974156663924</v>
+        <v>27.49372623544604</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>-0.0860144126931488</v>
+        <v>-0.0874983374882559</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.0235293886653287</v>
+        <v>0.0218676112156024</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.0756972318432225</v>
+        <v>-0.0771979073625112</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-1.881451528431274</v>
+        <v>-1.885057254189708</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-1.847891147141793</v>
+        <v>-1.84861229229348</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.0335603812894813</v>
+        <v>-0.0364449618962279</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>-0.1129581202809464</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>11143553</v>
+        <v>11521691</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>55514875.06</v>
+        <v>55522437.82</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.200730939013303</v>
+        <v>0.2075141411721247</v>
       </c>
       <c r="P34" s="6" t="n">
         <v>0.0112075006381963</v>
@@ -6210,7 +6396,7 @@
         <v>1.774999754769462</v>
       </c>
       <c r="S34" s="6" t="n">
-        <v>0.0637571747500319</v>
+        <v>0.06386085768713159</v>
       </c>
       <c r="T34" s="6" t="inlineStr">
         <is>
@@ -6225,46 +6411,46 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>269.125</v>
+        <v>269.489990234375</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>226.1216998291016</v>
+        <v>226.128999633789</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>160.4449752044678</v>
+        <v>160.4468001556396</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>76.07259720135606</v>
+        <v>76.16602114423313</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.170617690930332</v>
+        <v>0.1722052952977308</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>1.433978481891935</v>
+        <v>1.437279469821594</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1.126293755620553</v>
+        <v>1.129177458198218</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>12.16555114439922</v>
+        <v>12.19466717449183</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>11.59222952891438</v>
+        <v>11.5980527349329</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.5733216154848417</v>
+        <v>0.5966144395589303</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>0.3955764881293149</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>2140740</v>
+        <v>2205039</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>6063110.8</v>
+        <v>6064396.78</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.3530761799701896</v>
+        <v>0.363604012071255</v>
       </c>
       <c r="P35" s="6" t="n">
         <v>-0.0192129762097973</v>
@@ -6278,7 +6464,7 @@
         <v>13.84728785923549</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v>0.0514529971546139</v>
+        <v>0.0513833105533624</v>
       </c>
       <c r="T35" s="6" t="inlineStr">
         <is>
@@ -6293,7 +6479,7 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>184.4900054931641</v>
+        <v>184.4600067138672</v>
       </c>
       <c r="C36" s="6" t="inlineStr"/>
       <c r="D36" s="6" t="inlineStr"/>
@@ -6302,19 +6488,19 @@
       <c r="G36" s="6" t="inlineStr"/>
       <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" s="6" t="n">
-        <v>0.4215838180991511</v>
+        <v>0.419190753084024</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.1007544614513983</v>
+        <v>-0.1012330744544238</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.5223382795505496</v>
+        <v>0.5204238275384478</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>-0.9253561253561428</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>45657021</v>
+        <v>47160529</v>
       </c>
       <c r="N36" s="6" t="inlineStr"/>
       <c r="O36" s="6" t="inlineStr"/>
@@ -6341,46 +6527,46 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>8.573800086975098</v>
+        <v>8.559900283813477</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>10.93847602844238</v>
+        <v>10.93819803237915</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>18.45031897544861</v>
+        <v>18.4502494764328</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>20.79309128159542</v>
+        <v>20.51078645679097</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-0.1330839444546926</v>
+        <v>-0.134489384563803</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.1635316988316978</v>
+        <v>-0.1648877771889291</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.565223104182926</v>
+        <v>-0.5659279623799649</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.6481839541594869</v>
+        <v>-0.6492927703661131</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.5322506001509586</v>
+        <v>-0.5324723633922838</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.1159333540085283</v>
+        <v>-0.1168204069738293</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>-0.1257283657885731</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>14186772</v>
+        <v>15452173</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>33018651.44</v>
+        <v>33043959.46</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.4296593404421607</v>
+        <v>0.467624741481268</v>
       </c>
       <c r="P37" s="6" t="n">
         <v>0.0299401183926648</v>
@@ -6394,7 +6580,7 @@
         <v>0.6735711097717285</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>0.0785615599779361</v>
+        <v>0.0786891304149222</v>
       </c>
       <c r="T37" s="6" t="inlineStr">
         <is>
@@ -6409,46 +6595,46 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>45.81999969482422</v>
+        <v>45.66999816894531</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>60.62099983215332</v>
+        <v>60.61799980163574</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>81.45729980468749</v>
+        <v>81.4565497970581</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>23.09511958709545</v>
+        <v>22.90686414096366</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-0.2029918532427812</v>
+        <v>-0.2056010291255345</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.2178218118365793</v>
+        <v>-0.2203824386919951</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.5529756127334222</v>
+        <v>-0.554439042254192</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-3.83337002850498</v>
+        <v>-3.845335962193325</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-3.48200428850696</v>
+        <v>-3.484397475244628</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.3513657399980205</v>
+        <v>-0.3609384869486964</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>-0.3462640816307631</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>3482257</v>
+        <v>3721356</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>12369365.14</v>
+        <v>12374147.12</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.281522694219697</v>
+        <v>0.3007363629922642</v>
       </c>
       <c r="P38" s="6" t="n">
         <v>0.0251036384349932</v>
@@ -6459,10 +6645,10 @@
         </is>
       </c>
       <c r="R38" s="6" t="n">
-        <v>3.439085824148996</v>
+        <v>3.443371636526925</v>
       </c>
       <c r="S38" s="6" t="n">
-        <v>0.075056434898612</v>
+        <v>0.075396798217267</v>
       </c>
       <c r="T38" s="6" t="inlineStr">
         <is>
@@ -6477,46 +6663,46 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>7.755000114440918</v>
+        <v>7.71999979019165</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>9.766099996566773</v>
+        <v>9.765399990081788</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>12.02982501506805</v>
+        <v>12.02965001344681</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>27.01664839096489</v>
+        <v>26.35658618633685</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>-0.1524589685516761</v>
+        <v>-0.1562841407602504</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.1187500060959294</v>
+        <v>-0.122727315583504</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.4967553412569786</v>
+        <v>-0.4990266147544372</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.5915001429102258</v>
+        <v>-0.5942921915682895</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.4878587966281948</v>
+        <v>-0.4884172063598076</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.1036413462820309</v>
+        <v>-0.1058749852084818</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>-0.1257187896488844</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>23068273</v>
+        <v>28250652</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>37099575.46</v>
+        <v>37203223.04</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.6217934494930202</v>
+        <v>0.7593603373994126</v>
       </c>
       <c r="P39" s="6" t="n">
         <v>0.0100267124430337</v>
@@ -6530,7 +6716,7 @@
         <v>0.5577142919812884</v>
       </c>
       <c r="S39" s="6" t="n">
-        <v>0.0719167354933683</v>
+        <v>0.0722427858987601</v>
       </c>
       <c r="T39" s="6" t="inlineStr">
         <is>
@@ -6545,46 +6731,46 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>6.764999866485596</v>
+        <v>6.804999828338623</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>7.678500022888183</v>
+        <v>7.679300022125244</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>10.25845001220703</v>
+        <v>10.2586500120163</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>56.98924378337604</v>
+        <v>57.71669781062163</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>-0.0195652502921663</v>
+        <v>-0.0137681544515616</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.0294117546451774</v>
+        <v>-0.0236728790272302</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.4152981810784416</v>
+        <v>-0.4118409673439486</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.2395015780978422</v>
+        <v>-0.2363106979500218</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.3061410304616637</v>
+        <v>-0.3055028544320996</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.0666394523638215</v>
+        <v>0.0691921564820778</v>
       </c>
       <c r="L40" s="6" t="n">
         <v>0.0561779742976243</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>16404989</v>
+        <v>18610524</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>28572367.78</v>
+        <v>28616478.48</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.5741557411802292</v>
+        <v>0.6503429138916187</v>
       </c>
       <c r="P40" s="6" t="n">
         <v>-0.0154083063419491</v>
@@ -6595,10 +6781,10 @@
         </is>
       </c>
       <c r="R40" s="6" t="n">
-        <v>0.4006429399762835</v>
+        <v>0.4031429290771484</v>
       </c>
       <c r="S40" s="6" t="n">
-        <v>0.0592229043434433</v>
+        <v>0.0592421659436796</v>
       </c>
       <c r="T40" s="6" t="inlineStr">
         <is>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>368.0950012207031</v>
+        <v>371.7000122070313</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.082723417254077</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.2652982180935547</v>
+        <v>0.2759004286252026</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>75</v>
@@ -573,13 +573,13 @@
         <v>12</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.032600279710957</v>
+        <v>0.0322840990204654</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>275.2391575404576</v>
+        <v>278.8441685267858</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>507.3787667410714</v>
+        <v>510.9837777273996</v>
       </c>
     </row>
     <row r="3">
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>988.1630859375</v>
+        <v>986.6900024414062</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.0543756800501934</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.380063686150926</v>
+        <v>0.3894289129247086</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>75</v>
@@ -614,13 +614,13 @@
         <v>12</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.0121437444595648</v>
+        <v>0.0121618745201714</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>808.633056640625</v>
+        <v>807.1599731445312</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1257.458129882812</v>
+        <v>1255.985046386719</v>
       </c>
     </row>
     <row r="4">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>239.25</v>
+        <v>239.6999969482422</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.06596166699561611</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.2601719598812185</v>
+        <v>0.2703109591354888</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>75</v>
@@ -655,13 +655,13 @@
         <v>12</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.0501567398119122</v>
+        <v>0.0500625788601538</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>185.6792842320033</v>
+        <v>186.1292811802456</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>319.606073651995</v>
+        <v>320.0560706002371</v>
       </c>
     </row>
   </sheetData>
@@ -675,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:Y40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -698,8 +698,11 @@
     <col width="15" customWidth="1" min="18" max="18"/>
     <col width="17" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="35" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="23" customWidth="1" min="23" max="23"/>
+    <col width="35" customWidth="1" min="24" max="24"/>
+    <col width="23" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -805,10 +808,25 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>holding_return_pct</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sell_signal</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>exit_reason</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>decision_reasons</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>warnings</t>
         </is>
@@ -831,7 +849,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>182.8500061035156</v>
+        <v>182.0500030517578</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>89</v>
@@ -851,28 +869,28 @@
         <v>75</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>62.54404908025502</v>
+        <v>62.17642691523031</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.0151807899125376</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.3267114381879226</v>
+        <v>0.3418439357313785</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1.622236444222988</v>
+        <v>1.571182118412793</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>161.9255959647042</v>
+        <v>161.1255929129464</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>214.2366213117327</v>
+        <v>213.4366182599749</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>10.46220506940569</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>9.75</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0.053341</v>
@@ -883,12 +901,15 @@
       <c r="T2" s="2" t="n">
         <v>13.95</v>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -907,7 +928,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>211.3099975585937</v>
+        <v>210.6649932861328</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>89</v>
@@ -927,22 +948,22 @@
         <v>75</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>60.36799095758673</v>
+        <v>59.89200508010831</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.0229450115312453</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.4210526239435837</v>
+        <v>0.4415302049413213</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1.640742100952084</v>
+        <v>1.599579435131218</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>200.9964267185756</v>
+        <v>200.3514224461147</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>225.0614253452846</v>
+        <v>224.4164210728237</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>6.875713893345424</v>
@@ -951,7 +972,7 @@
         <v>13.95</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.066025</v>
+        <v>0.06622699999999999</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>1.12</v>
@@ -959,12 +980,15 @@
       <c r="T3" s="2" t="n">
         <v>13.95</v>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -983,7 +1007,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>557.6199951171875</v>
+        <v>554.8200073242188</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>82</v>
@@ -1003,28 +1027,28 @@
         <v>50</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>56.19119939331</v>
+        <v>55.78533584693042</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0.0624019610194614</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.4259170811245481</v>
+        <v>0.4361500707930983</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>-2.45371141946487</v>
+        <v>-2.632400099130137</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>500.5428423200335</v>
+        <v>497.7428545270647</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>633.7228655133929</v>
+        <v>630.9228777204241</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>38.05143519810268</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>10.9</v>
+        <v>10.85</v>
       </c>
       <c r="R4" s="2" t="n">
         <v>0.019555</v>
@@ -1035,12 +1059,15 @@
       <c r="T4" s="2" t="n">
         <v>13.95</v>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1059,7 +1086,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>988.1630859375</v>
+        <v>986.6900024414062</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>82</v>
@@ -1079,28 +1106,28 @@
         <v>50</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>45.2164692088228</v>
+        <v>45.09481845458335</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0.0543756800501934</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.380063686150926</v>
+        <v>0.3894289129247086</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-24.64867951866817</v>
+        <v>-24.74268826599728</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>808.633056640625</v>
+        <v>807.1599731445312</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1257.458129882812</v>
+        <v>1255.985046386719</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>89.7650146484375</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>6.14</v>
+        <v>6.13</v>
       </c>
       <c r="R5" s="2" t="n">
         <v>0.006217</v>
@@ -1111,12 +1138,15 @@
       <c r="T5" s="2" t="n">
         <v>13.95</v>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1135,7 +1165,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1157.699951171875</v>
+        <v>1156.650024414062</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>82</v>
@@ -1155,22 +1185,22 @@
         <v>50</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>58.0950473448579</v>
+        <v>57.90061457309466</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>-0.013419399271567</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.3970135193890146</v>
+        <v>0.4068960451700752</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-6.785016176066783</v>
+        <v>-6.852020048930058</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1095.450474330357</v>
+        <v>1094.400547572545</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1240.699253627232</v>
+        <v>1239.64932686942</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>41.49965122767857</v>
@@ -1179,7 +1209,7 @@
         <v>13.95</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.012051</v>
+        <v>0.012062</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>1.12</v>
@@ -1187,12 +1217,15 @@
       <c r="T6" s="2" t="n">
         <v>13.95</v>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="V6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1211,7 +1244,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7.625</v>
+        <v>7.670000076293945</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>82</v>
@@ -1231,28 +1264,28 @@
         <v>50</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>49.56937729178416</v>
+        <v>50</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>-0.0049382666628676</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.4660121255074218</v>
+        <v>0.4792892163534802</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-0.1260933049671196</v>
+        <v>-0.1232215052264239</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>6.147785867963519</v>
+        <v>6.192785944257464</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>9.840821198054725</v>
+        <v>9.885821274348668</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>0.7386070660182408</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>5.76</v>
+        <v>5.8</v>
       </c>
       <c r="R7" s="2" t="n">
         <v>0.755569</v>
@@ -1263,12 +1296,15 @@
       <c r="T7" s="2" t="n">
         <v>13.95</v>
       </c>
-      <c r="U7" s="2" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="V7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1287,7 +1323,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>368.0950012207031</v>
+        <v>371.7000122070313</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>82</v>
@@ -1307,28 +1343,28 @@
         <v>50</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>45.88121563095124</v>
+        <v>46.43119251769661</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0.082723417254077</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.2652982180935547</v>
+        <v>0.2759004286252026</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-11.30351981756416</v>
+        <v>-11.07345643837971</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>275.2391575404576</v>
+        <v>278.8441685267858</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>507.3787667410714</v>
+        <v>510.9837777273996</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>46.42792184012277</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="R8" s="2" t="n">
         <v>0.01202</v>
@@ -1339,12 +1375,15 @@
       <c r="T8" s="2" t="n">
         <v>13.95</v>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1363,7 +1402,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>17.04999923706055</v>
+        <v>16.8799991607666</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>79</v>
@@ -1383,31 +1422,31 @@
         <v>75</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>74.97682986607725</v>
+        <v>74.57627042542499</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>0.0098826338563442</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.1947934971779053</v>
+        <v>0.2041913379434426</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.1387700886965315</v>
+        <v>0.1279210809786271</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>14.0509990964617</v>
+        <v>13.88099902016776</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>21.54849944795881</v>
+        <v>21.37849937166487</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.499500070299421</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.186085</v>
+        <v>0</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>1.12</v>
@@ -1415,12 +1454,17 @@
       <c r="T9" s="3" t="n">
         <v>13.95</v>
       </c>
-      <c r="U9" s="3" t="inlineStr">
+      <c r="U9" s="3" t="n">
+        <v>0.1201687092347426</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="V9" s="3" t="inlineStr">
+      <c r="Y9" s="3" t="inlineStr">
         <is>
           <t>RSI overbought</t>
         </is>
@@ -1443,7 +1487,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>13.76000022888184</v>
+        <v>13.72999954223633</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>79</v>
@@ -1463,28 +1507,28 @@
         <v>75</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>75.39503211062105</v>
+        <v>75.22726711162801</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>-0.0110537672736636</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.2241632566493904</v>
+        <v>0.2325674667297119</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.0346667814141248</v>
+        <v>0.0327522076794828</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>12.55234323229108</v>
+        <v>12.52234254564558</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>15.57148572376796</v>
+        <v>15.54148503712245</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.6038284982953753</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>6.36</v>
+        <v>6.34</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>0.462108</v>
@@ -1495,12 +1539,15 @@
       <c r="T10" s="3" t="n">
         <v>13.95</v>
       </c>
-      <c r="U10" s="3" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="V10" s="3" t="inlineStr">
+      <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>RSI overbought</t>
         </is>
@@ -1523,7 +1570,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>269.489990234375</v>
+        <v>268.2900085449219</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>79</v>
@@ -1543,22 +1590,22 @@
         <v>75</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>76.16602114423313</v>
+        <v>75.85609116382497</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>-0.0192129762097973</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.363604012071255</v>
+        <v>0.3754677871346104</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.5966144395589303</v>
+        <v>0.5200344115140574</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>248.7190584455218</v>
+        <v>247.5190767560686</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>297.184565952846</v>
+        <v>295.9845842633928</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>13.84728785923549</v>
@@ -1567,7 +1614,7 @@
         <v>6.98</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.025885</v>
+        <v>0.026001</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>1.12</v>
@@ -1575,12 +1622,15 @@
       <c r="T11" s="3" t="n">
         <v>13.95</v>
       </c>
-      <c r="U11" s="3" t="inlineStr">
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="V11" s="3" t="inlineStr">
+      <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>RSI overbought</t>
         </is>
@@ -1603,7 +1653,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>393.7349853515625</v>
+        <v>392.8800048828125</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>79</v>
@@ -1623,22 +1673,22 @@
         <v>75</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>55.53833938277076</v>
+        <v>55.22621319204223</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0.030087289573326</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.35862833201275</v>
+        <v>0.3674262701458883</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.275182669862051</v>
+        <v>3.220619813736693</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>371.2296360560826</v>
+        <v>370.3746555873326</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>423.7421177455357</v>
+        <v>422.8871372767857</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>15.00356619698661</v>
@@ -1647,7 +1697,7 @@
         <v>6.98</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.017717</v>
+        <v>0.017756</v>
       </c>
       <c r="S12" s="4" t="n">
         <v>1.12</v>
@@ -1655,12 +1705,15 @@
       <c r="T12" s="4" t="n">
         <v>13.95</v>
       </c>
-      <c r="U12" s="4" t="inlineStr">
+      <c r="U12" s="4" t="inlineStr"/>
+      <c r="V12" s="4" t="inlineStr"/>
+      <c r="W12" s="4" t="inlineStr"/>
+      <c r="X12" s="4" t="inlineStr">
         <is>
           <t>Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="V12" s="4" t="inlineStr"/>
+      <c r="Y12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1679,7 +1732,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6.429999828338623</v>
+        <v>6.409999847412109</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>78</v>
@@ -1699,28 +1752,28 @@
         <v>75</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>62.8078769713569</v>
+        <v>62.49999561730699</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>0.0046656626141934</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.241781972360957</v>
+        <v>0.2493406696662838</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.0210916334731448</v>
+        <v>0.0198152814140169</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>5.143857138497489</v>
+        <v>5.123857157570975</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>8.359213863100324</v>
+        <v>8.33921388217381</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0.6430713449205671</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="R13" s="4" t="n">
         <v>0.433909</v>
@@ -1731,12 +1784,15 @@
       <c r="T13" s="4" t="n">
         <v>13.95</v>
       </c>
-      <c r="U13" s="4" t="inlineStr">
+      <c r="U13" s="4" t="inlineStr"/>
+      <c r="V13" s="4" t="inlineStr"/>
+      <c r="W13" s="4" t="inlineStr"/>
+      <c r="X13" s="4" t="inlineStr">
         <is>
           <t>Strong trend; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="V13" s="4" t="inlineStr"/>
+      <c r="Y13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1755,7 +1811,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>239.25</v>
+        <v>239.6999969482422</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>75</v>
@@ -1775,28 +1831,28 @@
         <v>50</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>41.43323997010419</v>
+        <v>41.5707735141641</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>0.06596166699561611</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2601719598812185</v>
+        <v>0.2703109591354888</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.632437426028641</v>
+        <v>-4.603719672066736</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>185.6792842320033</v>
+        <v>186.1292811802456</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>319.606073651995</v>
+        <v>320.0560706002371</v>
       </c>
       <c r="P14" s="4" t="n">
         <v>26.78535788399833</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="R14" s="4" t="n">
         <v>0.010417</v>
@@ -1807,12 +1863,15 @@
       <c r="T14" s="4" t="n">
         <v>13.95</v>
       </c>
-      <c r="U14" s="4" t="inlineStr">
+      <c r="U14" s="4" t="inlineStr"/>
+      <c r="V14" s="4" t="inlineStr"/>
+      <c r="W14" s="4" t="inlineStr"/>
+      <c r="X14" s="4" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="V14" s="4" t="inlineStr"/>
+      <c r="Y14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1831,7 +1890,7 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>357.8699951171875</v>
+        <v>358.3150024414062</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>71</v>
@@ -1851,25 +1910,25 @@
         <v>75</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>59.64509105642299</v>
+        <v>59.93802393421079</v>
       </c>
       <c r="K15" s="5" t="n">
         <v>-0.0040282924977889</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.2463434442892674</v>
+        <v>0.2634020235235434</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>0.5928515872589877</v>
+        <v>0.6212509150724284</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>342.9846354893276</v>
+        <v>343.3696430751256</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>377.7171412876674</v>
+        <v>378.2421482631138</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>9.923573085239957</v>
+        <v>9.963572910853795</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1883,12 +1942,17 @@
       <c r="T15" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U15" s="5" t="inlineStr">
+      <c r="U15" s="5" t="n">
+        <v>-0.0231864077519594</v>
+      </c>
+      <c r="V15" s="5" t="inlineStr"/>
+      <c r="W15" s="5" t="inlineStr"/>
+      <c r="X15" s="5" t="inlineStr">
         <is>
           <t>Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="V15" s="5" t="inlineStr"/>
+      <c r="Y15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1907,7 +1971,7 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>104.9100036621094</v>
+        <v>104.8600006103516</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>68</v>
@@ -1927,22 +1991,22 @@
         <v>75</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>65.01839145146317</v>
+        <v>64.98261344099689</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0.3585139638253107</v>
+        <v>0.3676589234010302</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>1.437744696701323</v>
+        <v>1.434553618754394</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>92.96714564732144</v>
+        <v>92.91714259556362</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>122.8242906842913</v>
+        <v>122.7742876325335</v>
       </c>
       <c r="P16" s="5" t="n">
         <v>5.971429007393973</v>
@@ -1959,12 +2023,15 @@
       <c r="T16" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U16" s="5" t="inlineStr">
+      <c r="U16" s="5" t="inlineStr"/>
+      <c r="V16" s="5" t="inlineStr"/>
+      <c r="W16" s="5" t="inlineStr"/>
+      <c r="X16" s="5" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="V16" s="5" t="inlineStr"/>
+      <c r="Y16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1983,7 +2050,7 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>18.59499931335449</v>
+        <v>18.69009971618652</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>67</v>
@@ -2003,22 +2070,22 @@
         <v>75</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>62.29968817312163</v>
+        <v>62.96362228035989</v>
       </c>
       <c r="K17" s="5" t="n">
         <v>0.0044125718372439</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.6652128389936749</v>
+        <v>0.7285697256002156</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0.0351797818894123</v>
+        <v>0.0412488674262686</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>16.7121421269008</v>
+        <v>16.80724252973284</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>21.41928509303501</v>
+        <v>21.51438549586705</v>
       </c>
       <c r="P17" s="5" t="n">
         <v>0.9414285932268416</v>
@@ -2035,12 +2102,17 @@
       <c r="T17" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U17" s="5" t="inlineStr">
+      <c r="U17" s="5" t="n">
+        <v>0.0158420768008933</v>
+      </c>
+      <c r="V17" s="5" t="inlineStr"/>
+      <c r="W17" s="5" t="inlineStr"/>
+      <c r="X17" s="5" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="V17" s="5" t="inlineStr"/>
+      <c r="Y17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2059,7 +2131,7 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>422.3099975585938</v>
+        <v>422.5</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>65</v>
@@ -2079,22 +2151,22 @@
         <v>50</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>45.57065028514946</v>
+        <v>45.63563934448866</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>0.0220361706931489</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.6586487344952262</v>
+        <v>0.6817053059486297</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>-4.084343013348712</v>
+        <v>-4.072217501418504</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>392.3507123674665</v>
+        <v>392.5407148088728</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>462.2557111467634</v>
+        <v>462.4457135881697</v>
       </c>
       <c r="P18" s="5" t="n">
         <v>19.97285679408482</v>
@@ -2111,12 +2183,15 @@
       <c r="T18" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U18" s="5" t="inlineStr">
+      <c r="U18" s="5" t="inlineStr"/>
+      <c r="V18" s="5" t="inlineStr"/>
+      <c r="W18" s="5" t="inlineStr"/>
+      <c r="X18" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="V18" s="5" t="inlineStr"/>
+      <c r="Y18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2135,7 +2210,7 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>881.2999877929688</v>
+        <v>883.1300048828125</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>65</v>
@@ -2155,22 +2230,22 @@
         <v>50</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>38.11380958860197</v>
+        <v>38.28450466392492</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>0.0451049293978258</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.4517719065777259</v>
+        <v>0.4882103629934356</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>-15.04479099955905</v>
+        <v>-14.92800358413886</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>754.8510589599609</v>
+        <v>756.6810760498047</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>1049.898559570312</v>
+        <v>1051.728576660156</v>
       </c>
       <c r="P19" s="5" t="n">
         <v>84.29928588867188</v>
@@ -2187,12 +2262,15 @@
       <c r="T19" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U19" s="5" t="inlineStr">
+      <c r="U19" s="5" t="inlineStr"/>
+      <c r="V19" s="5" t="inlineStr"/>
+      <c r="W19" s="5" t="inlineStr"/>
+      <c r="X19" s="5" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="V19" s="5" t="inlineStr"/>
+      <c r="Y19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2211,7 +2289,7 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>303.4923095703125</v>
+        <v>303.7749938964844</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>62</v>
@@ -2231,22 +2309,22 @@
         <v>50</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>45.57138320604898</v>
+        <v>45.64846508307077</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>0.031582057136426</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.3167818315827367</v>
+        <v>0.3276570768944706</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>-0.7726992613131298</v>
+        <v>-0.7546590080189728</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>271.58837890625</v>
+        <v>271.8710632324219</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>346.0308837890625</v>
+        <v>346.3135681152344</v>
       </c>
       <c r="P20" s="5" t="n">
         <v>21.269287109375</v>
@@ -2265,6 +2343,9 @@
       </c>
       <c r="U20" s="5" t="inlineStr"/>
       <c r="V20" s="5" t="inlineStr"/>
+      <c r="W20" s="5" t="inlineStr"/>
+      <c r="X20" s="5" t="inlineStr"/>
+      <c r="Y20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2283,7 +2364,7 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>246.0800018310547</v>
+        <v>246.4550018310547</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>56</v>
@@ -2303,22 +2384,22 @@
         <v>75</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>64.71600352674133</v>
+        <v>65.31827411205957</v>
       </c>
       <c r="K21" s="5" t="n">
         <v>-0.0071974396379796</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.2904367729668282</v>
+        <v>0.303846270874105</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>1.65138659877611</v>
+        <v>1.675318222707727</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>234.8632207598005</v>
+        <v>235.2382207598005</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>261.0357099260603</v>
+        <v>261.4107099260603</v>
       </c>
       <c r="P21" s="5" t="n">
         <v>7.47785404750279</v>
@@ -2335,12 +2416,15 @@
       <c r="T21" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U21" s="5" t="inlineStr">
+      <c r="U21" s="5" t="inlineStr"/>
+      <c r="V21" s="5" t="inlineStr"/>
+      <c r="W21" s="5" t="inlineStr"/>
+      <c r="X21" s="5" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="V21" s="5" t="inlineStr"/>
+      <c r="Y21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2359,7 +2443,7 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>285.5400085449219</v>
+        <v>284.6789855957031</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>55</v>
@@ -2379,22 +2463,22 @@
         <v>50</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>28.79400118305021</v>
+        <v>28.66453145202405</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>0.0376936349020097</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.5345029925370236</v>
+        <v>0.5487393878708714</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-9.8218827296093</v>
+        <v>-9.876831202721863</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>226.7774353027344</v>
+        <v>225.9164123535156</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>373.6838684082031</v>
+        <v>372.8228454589844</v>
       </c>
       <c r="P22" s="5" t="n">
         <v>29.38128662109375</v>
@@ -2411,12 +2495,15 @@
       <c r="T22" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U22" s="5" t="inlineStr">
+      <c r="U22" s="5" t="inlineStr"/>
+      <c r="V22" s="5" t="inlineStr"/>
+      <c r="W22" s="5" t="inlineStr"/>
+      <c r="X22" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="V22" s="5" t="inlineStr"/>
+      <c r="Y22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2435,7 +2522,7 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>223.0299987792969</v>
+        <v>223.2400054931641</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>55</v>
@@ -2455,22 +2542,22 @@
         <v>50</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>33.66770296216299</v>
+        <v>33.74884357057235</v>
       </c>
       <c r="K23" s="5" t="n">
         <v>0.0645198535414377</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.2684116598641259</v>
+        <v>0.2746769101179065</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-9.110192233228853</v>
+        <v>-9.096790095363808</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>190.6257095336914</v>
+        <v>190.8357162475587</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>266.2357177734375</v>
+        <v>266.4457244873047</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>21.60285949707031</v>
@@ -2487,12 +2574,15 @@
       <c r="T23" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U23" s="5" t="inlineStr">
+      <c r="U23" s="5" t="inlineStr"/>
+      <c r="V23" s="5" t="inlineStr"/>
+      <c r="W23" s="5" t="inlineStr"/>
+      <c r="X23" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="V23" s="5" t="inlineStr"/>
+      <c r="Y23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2511,7 +2601,7 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>193.9100036621093</v>
+        <v>195.6199951171875</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>55</v>
@@ -2531,22 +2621,22 @@
         <v>50</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>29.92199908218262</v>
+        <v>30.17674820438588</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>0.0310198990532244</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.6231393959985919</v>
+        <v>0.6586716750145929</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>-7.10620603941196</v>
+        <v>-6.997078379600713</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>142.7897164481026</v>
+        <v>144.4997079031808</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>270.5904344831194</v>
+        <v>272.3004259381976</v>
       </c>
       <c r="P24" s="5" t="n">
         <v>25.56014360700335</v>
@@ -2563,12 +2653,15 @@
       <c r="T24" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U24" s="5" t="inlineStr">
+      <c r="U24" s="5" t="inlineStr"/>
+      <c r="V24" s="5" t="inlineStr"/>
+      <c r="W24" s="5" t="inlineStr"/>
+      <c r="X24" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="V24" s="5" t="inlineStr"/>
+      <c r="Y24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2587,7 +2680,7 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>107.4000015258789</v>
+        <v>107.254997253418</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>55</v>
@@ -2607,22 +2700,22 @@
         <v>50</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>31.37724628863623</v>
+        <v>31.22796125679511</v>
       </c>
       <c r="K25" s="5" t="n">
         <v>0.0469355722360184</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.4293606824387826</v>
+        <v>0.4429696145707189</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-3.416113870674052</v>
+        <v>-3.425367704586084</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>93.18107223510742</v>
+        <v>93.03606796264648</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>126.3585739135742</v>
+        <v>126.2135696411133</v>
       </c>
       <c r="P25" s="5" t="n">
         <v>9.479286193847656</v>
@@ -2639,12 +2732,15 @@
       <c r="T25" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U25" s="5" t="inlineStr">
+      <c r="U25" s="5" t="inlineStr"/>
+      <c r="V25" s="5" t="inlineStr"/>
+      <c r="W25" s="5" t="inlineStr"/>
+      <c r="X25" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="V25" s="5" t="inlineStr"/>
+      <c r="Y25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2663,7 +2759,7 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>25.60000038146973</v>
+        <v>25.67000007629395</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>54</v>
@@ -2683,22 +2779,22 @@
         <v>50</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>41.16938033603359</v>
+        <v>41.34382605723892</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>0.0084746235925221</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.1941426174546727</v>
+        <v>0.2070816213511476</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>-0.0593259227473152</v>
+        <v>-0.0548587057556839</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>20.84728622436523</v>
+        <v>20.91728591918945</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>32.72907161712646</v>
+        <v>32.79907131195068</v>
       </c>
       <c r="P26" s="5" t="n">
         <v>2.376357078552246</v>
@@ -2717,6 +2813,9 @@
       </c>
       <c r="U26" s="5" t="inlineStr"/>
       <c r="V26" s="5" t="inlineStr"/>
+      <c r="W26" s="5" t="inlineStr"/>
+      <c r="X26" s="5" t="inlineStr"/>
+      <c r="Y26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2735,7 +2834,7 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>275.3500061035156</v>
+        <v>275.4800109863281</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>51</v>
@@ -2755,22 +2854,22 @@
         <v>75</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>61.05015706408463</v>
+        <v>61.14814244093061</v>
       </c>
       <c r="K27" s="5" t="n">
         <v>-0.0092015237095138</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>0.1979807697475212</v>
+        <v>0.2055225252788215</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>5.859618813052931</v>
+        <v>5.867915420958891</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>257.5482259477888</v>
+        <v>257.6782308306013</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>299.0857129778181</v>
+        <v>299.2157178606306</v>
       </c>
       <c r="P27" s="5" t="n">
         <v>11.86785343715123</v>
@@ -2787,84 +2886,104 @@
       <c r="T27" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U27" s="5" t="inlineStr">
+      <c r="U27" s="5" t="inlineStr"/>
+      <c r="V27" s="5" t="inlineStr"/>
+      <c r="W27" s="5" t="inlineStr"/>
+      <c r="X27" s="5" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="V27" s="5" t="inlineStr"/>
+      <c r="Y27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Electric Vehicles</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D28" s="5" t="n">
-        <v>395.7550048828125</v>
-      </c>
-      <c r="E28" s="5" t="n">
+      <c r="D28" s="3" t="n">
+        <v>395.3999938964844</v>
+      </c>
+      <c r="E28" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="5" t="n">
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="I28" s="5" t="n">
+      <c r="I28" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J28" s="5" t="n">
-        <v>54.20369849720209</v>
-      </c>
-      <c r="K28" s="5" t="n">
+      <c r="J28" s="3" t="n">
+        <v>54.10686010531468</v>
+      </c>
+      <c r="K28" s="3" t="n">
         <v>0.0109940121352903</v>
       </c>
-      <c r="L28" s="5" t="n">
-        <v>0.3097804369237979</v>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v>-0.0713178153867408</v>
-      </c>
-      <c r="N28" s="5" t="n">
-        <v>367.9042936052595</v>
-      </c>
-      <c r="O28" s="5" t="n">
-        <v>432.8892865862165</v>
-      </c>
-      <c r="P28" s="5" t="n">
+      <c r="L28" s="3" t="n">
+        <v>0.3192118151093351</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>-0.09397378716380771</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>367.5492826189313</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>432.5342755998884</v>
+      </c>
+      <c r="P28" s="3" t="n">
         <v>18.56714085170201</v>
       </c>
-      <c r="Q28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="5" t="n">
+      <c r="Q28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="T28" s="5" t="n">
+      <c r="T28" s="3" t="n">
         <v>13.95</v>
       </c>
-      <c r="U28" s="5" t="inlineStr"/>
-      <c r="V28" s="5" t="inlineStr"/>
+      <c r="U28" s="3" t="n">
+        <v>-0.0436213489830091</v>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>Signal score weakened</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr"/>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>Signal score weakened</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2883,7 +3002,7 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>79.67500305175781</v>
+        <v>79.76999664306641</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>43</v>
@@ -2903,22 +3022,22 @@
         <v>50</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>37.94018845028621</v>
+        <v>38.03211555661516</v>
       </c>
       <c r="K29" s="5" t="n">
         <v>0.0264563885114627</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.363046347956758</v>
+        <v>0.372958001988891</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>-1.39017964178294</v>
+        <v>-1.384117372707981</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>64.20928955078125</v>
+        <v>64.30428314208984</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>102.8735733032227</v>
+        <v>102.9685668945312</v>
       </c>
       <c r="P29" s="5" t="n">
         <v>7.732856750488281</v>
@@ -2937,6 +3056,9 @@
       </c>
       <c r="U29" s="5" t="inlineStr"/>
       <c r="V29" s="5" t="inlineStr"/>
+      <c r="W29" s="5" t="inlineStr"/>
+      <c r="X29" s="5" t="inlineStr"/>
+      <c r="Y29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -2955,7 +3077,7 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>6.804999828338623</v>
+        <v>6.824999809265137</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>39</v>
@@ -2975,25 +3097,25 @@
         <v>75</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>57.71669781062163</v>
+        <v>58.071274466897</v>
       </c>
       <c r="K30" s="5" t="n">
         <v>-0.0154083063419491</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.6503429138916187</v>
+        <v>0.7074789426578535</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.0691921564820778</v>
+        <v>0.0704685085412049</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>5.998713970184326</v>
+        <v>6.01371397290911</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>8.014428615570068</v>
+        <v>8.041928563799177</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.4031429290771484</v>
+        <v>0.4056429181780134</v>
       </c>
       <c r="Q30" s="5" t="n">
         <v>0</v>
@@ -3007,12 +3129,15 @@
       <c r="T30" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U30" s="5" t="inlineStr">
+      <c r="U30" s="5" t="inlineStr"/>
+      <c r="V30" s="5" t="inlineStr"/>
+      <c r="W30" s="5" t="inlineStr"/>
+      <c r="X30" s="5" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="V30" s="5" t="inlineStr"/>
+      <c r="Y30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3031,7 +3156,7 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>27.7947998046875</v>
+        <v>27.79500007629395</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>33</v>
@@ -3051,22 +3176,22 @@
         <v>50</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>27.49372623544604</v>
+        <v>27.49490920476378</v>
       </c>
       <c r="K31" s="5" t="n">
         <v>0.0112075006381963</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.2075141411721247</v>
+        <v>0.214932902334642</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>-0.0364449618962279</v>
+        <v>-0.0364321810301755</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>24.24480029514857</v>
+        <v>24.24500056675502</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>33.11979906899589</v>
+        <v>33.11999934060233</v>
       </c>
       <c r="P31" s="5" t="n">
         <v>1.774999754769462</v>
@@ -3085,6 +3210,9 @@
       </c>
       <c r="U31" s="5" t="inlineStr"/>
       <c r="V31" s="5" t="inlineStr"/>
+      <c r="W31" s="5" t="inlineStr"/>
+      <c r="X31" s="5" t="inlineStr"/>
+      <c r="Y31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3103,7 +3231,7 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>39.06000137329102</v>
+        <v>39.2599983215332</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>33</v>
@@ -3123,22 +3251,22 @@
         <v>50</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>16.79038701584251</v>
+        <v>17.37451029198574</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>0.0298353862022756</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.3311449574224561</v>
+        <v>0.3452389555509</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>-1.452080074984266</v>
+        <v>-1.439316736976789</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>31.65785871233259</v>
+        <v>31.85785566057477</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>50.16321536472866</v>
+        <v>50.36321231297084</v>
       </c>
       <c r="P32" s="5" t="n">
         <v>3.701071330479213</v>
@@ -3157,6 +3285,9 @@
       </c>
       <c r="U32" s="5" t="inlineStr"/>
       <c r="V32" s="5" t="inlineStr"/>
+      <c r="W32" s="5" t="inlineStr"/>
+      <c r="X32" s="5" t="inlineStr"/>
+      <c r="Y32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3175,7 +3306,7 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>69.48989868164062</v>
+        <v>69.59999847412109</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>32</v>
@@ -3195,22 +3326,22 @@
         <v>50</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>46.93608515837733</v>
+        <v>47.04179037230127</v>
       </c>
       <c r="K33" s="5" t="n">
         <v>0.0334417645102432</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.2819463443126206</v>
+        <v>0.2900078826669925</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>-0.7583188934111513</v>
+        <v>-0.7512925818682357</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>55.57932717459542</v>
+        <v>55.68942696707589</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>90.35575594220842</v>
+        <v>90.46585573468889</v>
       </c>
       <c r="P33" s="5" t="n">
         <v>6.955285753522601</v>
@@ -3229,6 +3360,9 @@
       </c>
       <c r="U33" s="5" t="inlineStr"/>
       <c r="V33" s="5" t="inlineStr"/>
+      <c r="W33" s="5" t="inlineStr"/>
+      <c r="X33" s="5" t="inlineStr"/>
+      <c r="Y33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3247,7 +3381,7 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>7.829999923706055</v>
+        <v>7.820000171661377</v>
       </c>
       <c r="E34" s="5" t="n">
         <v>32</v>
@@ -3267,22 +3401,22 @@
         <v>50</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>44.50549105057007</v>
+        <v>44.40366879365192</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>0.018661516252568</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0.5979421758434895</v>
+        <v>0.6202266874214982</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>-0.07418810638797831</v>
+        <v>-0.0748262672022259</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>6.441714423043387</v>
+        <v>6.431714670998709</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>9.912428174700056</v>
+        <v>9.902428422655378</v>
       </c>
       <c r="P34" s="5" t="n">
         <v>0.6941427503313337</v>
@@ -3301,6 +3435,9 @@
       </c>
       <c r="U34" s="5" t="inlineStr"/>
       <c r="V34" s="5" t="inlineStr"/>
+      <c r="W34" s="5" t="inlineStr"/>
+      <c r="X34" s="5" t="inlineStr"/>
+      <c r="Y34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -3319,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>184.4600067138672</v>
+        <v>185.9349975585937</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>29</v>
@@ -3344,13 +3481,13 @@
       </c>
       <c r="L35" s="3" t="inlineStr"/>
       <c r="M35" s="3" t="n">
-        <v>0.5204238275384478</v>
+        <v>0.614554297401346</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>169.7032061767578</v>
+        <v>171.0601977539062</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>212.1290077209472</v>
+        <v>213.8252471923828</v>
       </c>
       <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="3" t="n">
@@ -3365,12 +3502,15 @@
       <c r="T35" s="3" t="n">
         <v>13.95</v>
       </c>
-      <c r="U35" s="3" t="inlineStr">
+      <c r="U35" s="3" t="inlineStr"/>
+      <c r="V35" s="3" t="inlineStr"/>
+      <c r="W35" s="3" t="inlineStr"/>
+      <c r="X35" s="3" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="V35" s="3" t="inlineStr">
+      <c r="Y35" s="3" t="inlineStr">
         <is>
           <t>Missing ATR</t>
         </is>
@@ -3393,7 +3533,7 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>15.10999965667725</v>
+        <v>15.09000015258789</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>22</v>
@@ -3413,22 +3553,22 @@
         <v>50</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>23.97503582866533</v>
+        <v>23.93237667223939</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>0.0323432829789085</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.3308554198893791</v>
+        <v>0.3495804430746287</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>-0.2122178608022866</v>
+        <v>-0.2134941824307819</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>11.86101354871478</v>
+        <v>11.84101404462542</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>19.98347881862095</v>
+        <v>19.9634793145316</v>
       </c>
       <c r="P36" s="5" t="n">
         <v>1.624493053981236</v>
@@ -3447,6 +3587,9 @@
       </c>
       <c r="U36" s="5" t="inlineStr"/>
       <c r="V36" s="5" t="inlineStr"/>
+      <c r="W36" s="5" t="inlineStr"/>
+      <c r="X36" s="5" t="inlineStr"/>
+      <c r="Y36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3465,7 +3608,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>91.44000244140624</v>
+        <v>91.61000061035156</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>22</v>
@@ -3485,22 +3628,22 @@
         <v>50</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>16.83770701730374</v>
+        <v>17.3715982489269</v>
       </c>
       <c r="K37" s="5" t="n">
         <v>0.0177384274683925</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.7758579724205982</v>
+        <v>0.7936155602489158</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>-0.7804217666388213</v>
+        <v>-0.7695728806434405</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>84.71464484078543</v>
+        <v>84.88464300973075</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>100.4071459089007</v>
+        <v>100.577144077846</v>
       </c>
       <c r="P37" s="5" t="n">
         <v>4.48357173374721</v>
@@ -3519,6 +3662,9 @@
       </c>
       <c r="U37" s="5" t="inlineStr"/>
       <c r="V37" s="5" t="inlineStr"/>
+      <c r="W37" s="5" t="inlineStr"/>
+      <c r="X37" s="5" t="inlineStr"/>
+      <c r="Y37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3537,7 +3683,7 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>8.559900283813477</v>
+        <v>8.564999580383301</v>
       </c>
       <c r="E38" s="5" t="n">
         <v>22</v>
@@ -3557,22 +3703,22 @@
         <v>50</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>20.51078645679097</v>
+        <v>20.61458650817841</v>
       </c>
       <c r="K38" s="5" t="n">
         <v>0.0299401183926648</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.467624741481268</v>
+        <v>0.4909641662446321</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>-0.1168204069738293</v>
+        <v>-0.1164949817796282</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>7.21275806427002</v>
+        <v>7.217857360839844</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>10.58061361312866</v>
+        <v>10.58571290969849</v>
       </c>
       <c r="P38" s="5" t="n">
         <v>0.6735711097717285</v>
@@ -3591,6 +3737,9 @@
       </c>
       <c r="U38" s="5" t="inlineStr"/>
       <c r="V38" s="5" t="inlineStr"/>
+      <c r="W38" s="5" t="inlineStr"/>
+      <c r="X38" s="5" t="inlineStr"/>
+      <c r="Y38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3609,7 +3758,7 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>45.66999816894531</v>
+        <v>45.86000061035156</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>22</v>
@@ -3629,22 +3778,22 @@
         <v>50</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>22.90686414096366</v>
+        <v>23.24043212585009</v>
       </c>
       <c r="K39" s="5" t="n">
         <v>0.0251036384349932</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.3007363629922642</v>
+        <v>0.3113981236054748</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>-0.3609384869486964</v>
+        <v>-0.348812975018494</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>38.78325489589146</v>
+        <v>38.97325733729771</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>56.00011307852608</v>
+        <v>56.19011551993233</v>
       </c>
       <c r="P39" s="5" t="n">
         <v>3.443371636526925</v>
@@ -3663,6 +3812,9 @@
       </c>
       <c r="U39" s="5" t="inlineStr"/>
       <c r="V39" s="5" t="inlineStr"/>
+      <c r="W39" s="5" t="inlineStr"/>
+      <c r="X39" s="5" t="inlineStr"/>
+      <c r="Y39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3681,7 +3833,7 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>7.71999979019165</v>
+        <v>7.735000133514404</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>22</v>
@@ -3701,22 +3853,22 @@
         <v>50</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>26.35658618633685</v>
+        <v>26.64093014772622</v>
       </c>
       <c r="K40" s="5" t="n">
         <v>0.0100267124430337</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0.7593603373994126</v>
+        <v>0.842033201074178</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>-0.1058749852084818</v>
+        <v>-0.1049176983411601</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>6.604571206229074</v>
+        <v>6.619571549551828</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>9.393142666135516</v>
+        <v>9.40814300945827</v>
       </c>
       <c r="P40" s="5" t="n">
         <v>0.5577142919812884</v>
@@ -3735,6 +3887,9 @@
       </c>
       <c r="U40" s="5" t="inlineStr"/>
       <c r="V40" s="5" t="inlineStr"/>
+      <c r="W40" s="5" t="inlineStr"/>
+      <c r="X40" s="5" t="inlineStr"/>
+      <c r="Y40" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3747,13 +3902,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3769,12 +3928,32 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>avg_cost</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>current_price</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>market_value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>cost_basis</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>unrealized_pnl</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>holding_return_pct</t>
         </is>
       </c>
     </row>
@@ -3788,10 +3967,22 @@
         <v>0.74662492</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>17.04999923706055</v>
+        <v>15.06915790595363</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>12.72995431637039</v>
+        <v>16.8799991607666</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>12.60302802300743</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>11.251008816</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>1.35201920700743</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>0.1201687092347426</v>
       </c>
     </row>
     <row r="3">
@@ -3804,10 +3995,22 @@
         <v>0.05285969</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>357.8699951171875</v>
+        <v>366.8202462424581</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>18.91689700219604</v>
+        <v>358.3150024414062</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>18.94041995140197</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>19.3900045021</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>-0.4495845506980203</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>-0.0231864077519594</v>
       </c>
     </row>
     <row r="4">
@@ -3820,10 +4023,22 @@
         <v>0.6115135</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>18.59499931335449</v>
+        <v>18.39862725025694</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>11.371093112607</v>
+        <v>18.69009971618652</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>11.42924829279423</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>11.251008945</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1782393477942285</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.0158420768008933</v>
       </c>
     </row>
     <row r="5">
@@ -3836,10 +4051,22 @@
         <v>0.02721351</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>395.7550048828125</v>
+        <v>413.4345674446258</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>10.76988278292847</v>
+        <v>395.3999938964844</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>10.76022168790192</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>11.2510057355</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.4907840475980833</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.0436213489830091</v>
       </c>
     </row>
   </sheetData>
@@ -4043,7 +4270,7 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
@@ -4167,46 +4394,46 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>368.0950012207031</v>
+        <v>371.7000122070313</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>331.9376992797851</v>
+        <v>332.0097994995117</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>201.2374750900269</v>
+        <v>201.2555001449585</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>45.88121563095124</v>
+        <v>46.43119251769661</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.0025738998772397</v>
+        <v>0.0123928050828994</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.157649402411819</v>
+        <v>1.178780767343545</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>1.133018401796429</v>
+        <v>1.153908538166158</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>14.74684693672685</v>
+        <v>15.03442616070743</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>26.05036675429102</v>
+        <v>26.10788259908713</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-11.30351981756416</v>
+        <v>-11.07345643837971</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>-10.00415359792669</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>1623462</v>
+        <v>1688701</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>6119385.24</v>
+        <v>6120690.02</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>0.2652982180935547</v>
+        <v>0.2759004286252026</v>
       </c>
       <c r="P2" s="6" t="n">
         <v>0.082723417254077</v>
@@ -4220,7 +4447,7 @@
         <v>46.42792184012277</v>
       </c>
       <c r="S2" s="6" t="n">
-        <v>0.1261302698655378</v>
+        <v>0.1249069688334127</v>
       </c>
       <c r="T2" s="6" t="inlineStr">
         <is>
@@ -4235,46 +4462,46 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>557.6199951171875</v>
+        <v>554.8200073242188</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>489.9038000488281</v>
+        <v>489.8478002929688</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>291.5148996734619</v>
+        <v>291.5008997344971</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>56.19119939331</v>
+        <v>55.78533584693042</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.0900169813195939</v>
+        <v>0.0845436585037897</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.186144897892281</v>
+        <v>1.175167567306291</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1.684866813820294</v>
+        <v>1.671385241476634</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>17.54274022454445</v>
+        <v>17.31937937496286</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>19.99645164400932</v>
+        <v>19.951779474093</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-2.45371141946487</v>
+        <v>-2.632400099130137</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>-3.577422784539042</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>14421509</v>
+        <v>14771046</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>33859898.18</v>
+        <v>33866888.92</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.4259170811245481</v>
+        <v>0.4361500707930983</v>
       </c>
       <c r="P3" s="6" t="n">
         <v>0.0624019610194614</v>
@@ -4288,7 +4515,7 @@
         <v>38.05143519810268</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0.06823900780334451</v>
+        <v>0.06858338685660741</v>
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
@@ -4303,46 +4530,46 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>246.0800018310547</v>
+        <v>246.4550018310547</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>253.3403997802734</v>
+        <v>253.3478997802735</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>233.5955500030518</v>
+        <v>233.5974250030518</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>64.71600352674133</v>
+        <v>65.31827411205957</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.031565703973867</v>
+        <v>0.0331377014385605</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.0118062902215256</v>
+        <v>-0.0103003871070526</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.0015823401944126</v>
+        <v>-6.085685711909594e-05</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.7663590578676178</v>
+        <v>-0.7364445279530969</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-2.417745656643728</v>
+        <v>-2.411762750660824</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>1.65138659877611</v>
+        <v>1.675318222707727</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>1.780135958077288</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>14144006</v>
+        <v>14801029</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>48699088.12</v>
+        <v>48712228.58</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.2904367729668282</v>
+        <v>0.303846270874105</v>
       </c>
       <c r="P4" s="6" t="n">
         <v>-0.0071974396379796</v>
@@ -4356,7 +4583,7 @@
         <v>7.47785404750279</v>
       </c>
       <c r="S4" s="6" t="n">
-        <v>0.0303878982113982</v>
+        <v>0.0303416607167456</v>
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
@@ -4371,46 +4598,46 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>182.8500061035156</v>
+        <v>182.0500030517578</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>160.7983996582031</v>
+        <v>160.782399597168</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>144.3345496749878</v>
+        <v>144.330549659729</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>62.54404908025502</v>
+        <v>62.17642691523031</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.1201298698263813</v>
+        <v>0.1152290916786416</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.1844918824069923</v>
+        <v>0.1793095083896159</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.4815265663285675</v>
+        <v>0.475044609890173</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>6.033519195879251</v>
+        <v>5.969701288616506</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.411282751656263</v>
+        <v>4.398519170203713</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>1.622236444222988</v>
+        <v>1.571182118412793</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>1.773262942271622</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>3378729</v>
+        <v>3536301</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>10341630.58</v>
+        <v>10344782.02</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.3267114381879226</v>
+        <v>0.3418439357313785</v>
       </c>
       <c r="P5" s="6" t="n">
         <v>0.0151807899125376</v>
@@ -4424,7 +4651,7 @@
         <v>10.46220506940569</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>0.0572174171188312</v>
+        <v>0.0574688541281223</v>
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
@@ -4439,46 +4666,46 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>285.5400085449219</v>
+        <v>284.6789855957031</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>312.646198425293</v>
+        <v>312.6289779663086</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>182.8333250045776</v>
+        <v>182.8290198898316</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>28.79400118305021</v>
+        <v>28.66453145202405</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-0.2501772265026026</v>
+        <v>-0.2524382568188729</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.7711202480021699</v>
+        <v>0.7657795772249751</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1.569192101071012</v>
+        <v>1.561444908755489</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-7.807003761027829</v>
+        <v>-7.875689352418533</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>2.014878968581472</v>
+        <v>2.001141850303332</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-9.8218827296093</v>
+        <v>-9.876831202721863</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>-9.368367243321137</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>5976818</v>
+        <v>6137776</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>11182010.36</v>
+        <v>11185229.52</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.5345029925370236</v>
+        <v>0.5487393878708714</v>
       </c>
       <c r="P6" s="6" t="n">
         <v>0.0376936349020097</v>
@@ -4492,7 +4719,7 @@
         <v>29.38128662109375</v>
       </c>
       <c r="S6" s="6" t="n">
-        <v>0.1028972674295882</v>
+        <v>0.1032084843200214</v>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
@@ -4507,46 +4734,46 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>69.48989868164062</v>
+        <v>69.59999847412109</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>86.04299812316894</v>
+        <v>86.04520011901856</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>83.07049934387207</v>
+        <v>83.07104984283447</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>46.93608515837733</v>
+        <v>47.04179037230127</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.1567783570723123</v>
+        <v>-0.1554423567375484</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.2154239706325592</v>
+        <v>-0.2141808884053962</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.2937300628853178</v>
+        <v>-0.2926110488273499</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-4.787473658918216</v>
+        <v>-4.778690769489572</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-4.029154765507065</v>
+        <v>-4.027398187621336</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>-0.7583188934111513</v>
+        <v>-0.7512925818682357</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>-0.7205249641778009</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>6522733</v>
+        <v>6710322</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>23134660.66</v>
+        <v>23138412.44</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.2819463443126206</v>
+        <v>0.2900078826669925</v>
       </c>
       <c r="P7" s="6" t="n">
         <v>0.0334417645102432</v>
@@ -4560,7 +4787,7 @@
         <v>6.955285753522601</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>0.1000906014467999</v>
+        <v>0.09993226876447039</v>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
@@ -4575,46 +4802,46 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>393.7349853515625</v>
+        <v>392.8800048828125</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>405.5485003662109</v>
+        <v>405.5314007568359</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>362.9441751098633</v>
+        <v>362.9399002075195</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>55.53833938277076</v>
+        <v>55.22621319204223</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0305309964240272</v>
+        <v>0.0282932377610591</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.0340222349225187</v>
+        <v>0.0317768951686163</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.1178983984098036</v>
+        <v>0.1154709247733578</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-3.442382872085716</v>
+        <v>-3.510586442242413</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-6.717565541947767</v>
+        <v>-6.731206255979107</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>3.275182669862051</v>
+        <v>3.220619813736693</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>3.038872772970159</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>9838026</v>
+        <v>10081161</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>27432372.52</v>
+        <v>27437235.22</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.35862833201275</v>
+        <v>0.3674262701458883</v>
       </c>
       <c r="P8" s="6" t="n">
         <v>0.030087289573326</v>
@@ -4628,7 +4855,7 @@
         <v>15.00356619698661</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>0.0381057481686318</v>
+        <v>0.0381886734130484</v>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
@@ -4643,46 +4870,46 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>7.625</v>
+        <v>7.670000076293945</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>5.821099991798401</v>
+        <v>5.82199999332428</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4.044974999427796</v>
+        <v>4.045199999809265</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>49.56937729178416</v>
+        <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.3763538000909261</v>
+        <v>0.3844765576006379</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.717342320210109</v>
+        <v>0.7274774723979485</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.785714293690819</v>
+        <v>0.7962529532915108</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.6048939630682</v>
+        <v>0.6084837127440696</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.7309872680353197</v>
+        <v>0.7317052179704936</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-0.1260933049671196</v>
+        <v>-0.1232215052264239</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>-0.0949479297406228</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>3640226</v>
+        <v>3744943</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>7811440.52</v>
+        <v>7813534.86</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4660121255074218</v>
+        <v>0.4792892163534802</v>
       </c>
       <c r="P9" s="6" t="n">
         <v>-0.0049382666628676</v>
@@ -4696,7 +4923,7 @@
         <v>0.7386070660182408</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>0.0968665004614086</v>
+        <v>0.09629818235609811</v>
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
@@ -4711,46 +4938,46 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>17.04999923706055</v>
+        <v>16.8799991607666</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>9.906400012969971</v>
+        <v>9.903000011444092</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.553299986124038</v>
+        <v>6.552449985742569</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>74.97682986607725</v>
+        <v>74.57627042542499</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1.152777660709173</v>
+        <v>1.131313004818223</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>3.762569720786531</v>
+        <v>3.715083664943837</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>2.310679402199914</v>
+        <v>2.277669679258964</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>2.347326023110753</v>
+        <v>2.333764763463373</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>2.208555934414222</v>
+        <v>2.205843682484746</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1387700886965315</v>
+        <v>0.1279210809786271</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>0.2137816411175577</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>764280</v>
+        <v>801304</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>3923539.6</v>
+        <v>3924280.08</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.1947934971779053</v>
+        <v>0.2041913379434426</v>
       </c>
       <c r="P10" s="6" t="n">
         <v>0.0098826338563442</v>
@@ -4764,7 +4991,7 @@
         <v>1.499500070299421</v>
       </c>
       <c r="S10" s="6" t="n">
-        <v>0.0879472221347698</v>
+        <v>0.0888329469698458</v>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
@@ -4779,46 +5006,46 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>275.3500061035156</v>
+        <v>275.4800109863281</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>300.9942013549805</v>
+        <v>300.9968014526367</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>276.041450881958</v>
+        <v>276.0421009063721</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>61.05015706408463</v>
+        <v>61.14814244093061</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.0663253104869391</v>
+        <v>-0.0658844814841987</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.08445550755273271</v>
+        <v>-0.0840232386157003</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.0431109778769813</v>
+        <v>0.0436034765783919</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-6.677964185346525</v>
+        <v>-6.667593425464077</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-12.53758299839946</v>
+        <v>-12.53550884642297</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>5.859618813052931</v>
+        <v>5.867915420958891</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>5.61249043240821</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>307237</v>
+        <v>318989</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>1551852.74</v>
+        <v>1552087.78</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.1979807697475212</v>
+        <v>0.2055225252788215</v>
       </c>
       <c r="P11" s="6" t="n">
         <v>-0.0092015237095138</v>
@@ -4832,7 +5059,7 @@
         <v>11.86785343715123</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>0.0431009739389277</v>
+        <v>0.0430806336716032</v>
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
@@ -4847,46 +5074,46 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>104.9100036621094</v>
+        <v>104.8600006103516</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>112.273999786377</v>
+        <v>112.2729997253418</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>101.2301999473572</v>
+        <v>101.2299499320984</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>65.01839145146317</v>
+        <v>64.98261344099689</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.1847543765841439</v>
+        <v>0.1841896894013712</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.1318990071433482</v>
+        <v>-0.1323127684374249</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.0038273994613213</v>
+        <v>0.0033489471530663</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.6712747060436186</v>
+        <v>0.6672858586099579</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.7664699906577042</v>
+        <v>-0.7672677601444363</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>1.437744696701323</v>
+        <v>1.434553618754394</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>1.911196160245703</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>540921</v>
+        <v>554821</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>1508786.42</v>
+        <v>1509064.42</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.3585139638253107</v>
+        <v>0.3676589234010302</v>
       </c>
       <c r="P12" s="6" t="n">
         <v>0</v>
@@ -4900,7 +5127,7 @@
         <v>5.971429007393973</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>0.0569195386421542</v>
+        <v>0.0569466810283852</v>
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
@@ -4915,46 +5142,46 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>239.25</v>
+        <v>239.6999969482422</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>227.4261999511719</v>
+        <v>227.4351998901367</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>161.8374002075195</v>
+        <v>161.8396501922607</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>41.43323997010419</v>
+        <v>41.5707735141641</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.0460906569559418</v>
+        <v>-0.0442964822714296</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4998118956376145</v>
+        <v>0.5026328393198476</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.5329659048646274</v>
+        <v>0.5358492067620082</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.421189482964081</v>
+        <v>5.457086675416463</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>10.05362690899272</v>
+        <v>10.0608063474832</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>-4.632437426028641</v>
+        <v>-4.603719672066736</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>-4.078359216969876</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>2253472</v>
+        <v>2341768</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>8661471.439999999</v>
+        <v>8663237.359999999</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2601719598812185</v>
+        <v>0.2703109591354888</v>
       </c>
       <c r="P13" s="6" t="n">
         <v>0.06596166699561611</v>
@@ -4968,7 +5195,7 @@
         <v>26.78535788399833</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>0.1119555188463879</v>
+        <v>0.1117453409470923</v>
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
@@ -4983,46 +5210,46 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>357.8699951171875</v>
+        <v>358.3150024414062</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>372.2586004638672</v>
+        <v>372.2675006103516</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>319.9689498138428</v>
+        <v>319.9711748504639</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>59.64509105642299</v>
+        <v>59.93802393421079</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.0050322442044344</v>
+        <v>-0.0037950129619953</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.0749751920354173</v>
+        <v>0.0763119116272694</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.0783764566796769</v>
+        <v>0.07971740570595789</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-2.060238228870276</v>
+        <v>-2.024739069103475</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-2.653089816129264</v>
+        <v>-2.645989984175904</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.5928515872589877</v>
+        <v>0.6212509150724284</v>
       </c>
       <c r="L14" s="6" t="n">
         <v>0.5974640052565006</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>7820884</v>
+        <v>8365326</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>31747887.68</v>
+        <v>31758776.52</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.2463434442892674</v>
+        <v>0.2634020235235434</v>
       </c>
       <c r="P14" s="6" t="n">
         <v>-0.0040282924977889</v>
@@ -5033,10 +5260,10 @@
         </is>
       </c>
       <c r="R14" s="6" t="n">
-        <v>9.923573085239957</v>
+        <v>9.963572910853795</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>0.0277295476587535</v>
+        <v>0.027806742232299</v>
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
@@ -5051,46 +5278,46 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>107.4000015258789</v>
+        <v>107.254997253418</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>117.4291998291016</v>
+        <v>117.4262997436524</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>63.21499998092651</v>
+        <v>63.21427495956421</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>31.37724628863623</v>
+        <v>31.22796125679511</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.1378341351128598</v>
+        <v>-0.1389981735877428</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.683121755437438</v>
+        <v>0.6808493174286585</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1.437585069867572</v>
+        <v>1.434294006137628</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-2.007669754932863</v>
+        <v>-2.019237047322904</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>1.408444115741188</v>
+        <v>1.40613065726318</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-3.416113870674052</v>
+        <v>-3.425367704586084</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>-3.642499733942029</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>55794844</v>
+        <v>57579114</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>129948656.88</v>
+        <v>129984342.28</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.4293606824387826</v>
+        <v>0.4429696145707189</v>
       </c>
       <c r="P15" s="6" t="n">
         <v>0.0469355722360184</v>
@@ -5104,7 +5331,7 @@
         <v>9.479286193847656</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>0.0882615089308313</v>
+        <v>0.0883808348011082</v>
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
@@ -5119,46 +5346,46 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>39.06000137329102</v>
+        <v>39.2599983215332</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>54.89660018920898</v>
+        <v>54.90060012817383</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>48.68795004844665</v>
+        <v>48.68895003318787</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>16.79038701584251</v>
+        <v>17.37451029198574</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-0.3248054899990307</v>
+        <v>-0.3213483257204239</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.09228196886605231</v>
+        <v>0.0978747249518869</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.2333660296683863</v>
+        <v>-0.2294406725487126</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-4.194567758359661</v>
+        <v>-4.178613585850314</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-2.742487683375395</v>
+        <v>-2.739296848873526</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-1.452080074984266</v>
+        <v>-1.439316736976789</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>-1.449196603544823</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>9543757</v>
+        <v>9952777</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>28820481.14</v>
+        <v>28828661.54</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.3311449574224561</v>
+        <v>0.3452389555509</v>
       </c>
       <c r="P16" s="6" t="n">
         <v>0.0298353862022756</v>
@@ -5172,7 +5399,7 @@
         <v>3.701071330479213</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>0.09475348695225549</v>
+        <v>0.0942707969615286</v>
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
@@ -5187,46 +5414,46 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>7.829999923706055</v>
+        <v>7.820000171661377</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>8.697399950027465</v>
+        <v>8.697199954986573</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>8.190699968338013</v>
+        <v>8.190649969577789</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>44.50549105057007</v>
+        <v>44.40366879365192</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-0.0279330071936995</v>
+        <v>-0.029174441292498</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.1634615159285523</v>
+        <v>-0.1645298655451619</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.0486026294992456</v>
+        <v>-0.0498176662672744</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.0330828056374539</v>
+        <v>0.0322851046196444</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.1072709120254322</v>
+        <v>0.1071113718218703</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.07418810638797831</v>
+        <v>-0.0748262672022259</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>-0.0068890358413925</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>628008</v>
+        <v>651707</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1050282.16</v>
+        <v>1050756.14</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5979421758434895</v>
+        <v>0.6202266874214982</v>
       </c>
       <c r="P17" s="6" t="n">
         <v>0.018661516252568</v>
@@ -5240,7 +5467,7 @@
         <v>0.6941427503313337</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>0.088651693115571</v>
+        <v>0.0887650556385936</v>
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
@@ -5255,46 +5482,46 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1157.699951171875</v>
+        <v>1156.650024414062</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1097.829600830078</v>
+        <v>1097.808602294922</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1000.58130279541</v>
+        <v>1000.576053161621</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>58.0950473448579</v>
+        <v>57.90061457309466</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.0218004864712046</v>
+        <v>0.0208738079559245</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.2549592966632792</v>
+        <v>0.2538211646764905</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.0709527762922062</v>
+        <v>0.0699815211970975</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>27.87734583346446</v>
+        <v>27.79359099238536</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>34.66236200953124</v>
+        <v>34.64561104131542</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-6.785016176066783</v>
+        <v>-6.852020048930058</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>-3.468572913063639</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>1264564</v>
+        <v>1296300</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>3185191.28</v>
+        <v>3185826</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.3970135193890146</v>
+        <v>0.4068960451700752</v>
       </c>
       <c r="P18" s="6" t="n">
         <v>-0.013419399271567</v>
@@ -5308,7 +5535,7 @@
         <v>41.49965122767857</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>0.0358466381428718</v>
+        <v>0.035879177237472</v>
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
@@ -5323,46 +5550,46 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>15.10999965667725</v>
+        <v>15.09000015258789</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>27.4556000328064</v>
+        <v>27.45520004272461</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>19.02117503166198</v>
+        <v>19.02107503414154</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>23.97503582866533</v>
+        <v>23.93237667223939</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.4323816987110064</v>
+        <v>-0.4331329948589719</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.361639222307808</v>
+        <v>-0.3624841527693582</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.2130208824864672</v>
+        <v>-0.2140625232830634</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-3.406560278756281</v>
+        <v>-3.4081556807919</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-3.194342417953994</v>
+        <v>-3.194661498361118</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.2122178608022866</v>
+        <v>-0.2134941824307819</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>-0.2400474448421516</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>4718334</v>
+        <v>4987252</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>14261014.68</v>
+        <v>14266393.04</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.3308554198893791</v>
+        <v>0.3495804430746287</v>
       </c>
       <c r="P19" s="6" t="n">
         <v>0.0323432829789085</v>
@@ -5376,7 +5603,7 @@
         <v>1.624493053981236</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.1075111244799637</v>
+        <v>0.1076536141520608</v>
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
@@ -5391,46 +5618,46 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>223.0299987792969</v>
+        <v>223.2400054931641</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>233.8464001464844</v>
+        <v>233.8506002807617</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>128.194400177002</v>
+        <v>128.1954502105713</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>33.66770296216299</v>
+        <v>33.74884357057235</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.2026099783856562</v>
+        <v>-0.2018591499812879</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.6665171914205541</v>
+        <v>0.6680863964642205</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>1.690674392828498</v>
+        <v>1.693207951947976</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-4.982242413478303</v>
+        <v>-4.965489741146996</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>4.127949819750549</v>
+        <v>4.131300354216811</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-9.110192233228853</v>
+        <v>-9.096790095363808</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>-9.60956168128553</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>12136697</v>
+        <v>12421556</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>45216727.94</v>
+        <v>45222425.12</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.2684116598641259</v>
+        <v>0.2746769101179065</v>
       </c>
       <c r="P20" s="6" t="n">
         <v>0.0645198535414377</v>
@@ -5444,7 +5671,7 @@
         <v>21.60285949707031</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>0.0968607793360021</v>
+        <v>0.09676966030056749</v>
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
@@ -5459,46 +5686,46 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>988.1630859375</v>
+        <v>986.6900024414062</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>916.8382629394532</v>
+        <v>916.8088012695312</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>472.4687657165528</v>
+        <v>472.4614002990722</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>45.2164692088228</v>
+        <v>45.09481845458335</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.0066758699317739</v>
+        <v>0.0051751888893269</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>1.122069918322914</v>
+        <v>1.118906486882573</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1.857036169334929</v>
+        <v>1.852777102295608</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>9.847673466796325</v>
+        <v>9.730162532634949</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>34.4963529854645</v>
+        <v>34.47285079863222</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-24.64867951866817</v>
+        <v>-24.74268826599728</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>-28.83193491040208</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20493480</v>
+        <v>21002428</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>53921173.6</v>
+        <v>53931352.56</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.380063686150926</v>
+        <v>0.3894289129247086</v>
       </c>
       <c r="P21" s="6" t="n">
         <v>0.0543756800501934</v>
@@ -5512,7 +5739,7 @@
         <v>89.7650146484375</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>0.09084028327497649</v>
+        <v>0.090975903704637</v>
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
@@ -5527,46 +5754,46 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>193.9100036621093</v>
+        <v>195.6199951171875</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>223.9848001098633</v>
+        <v>224.0189999389648</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>136.7380254745484</v>
+        <v>136.7465754318237</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>29.92199908218262</v>
+        <v>30.17674820438588</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-0.1654759719712673</v>
+        <v>-0.1581167386669705</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.1974188016470521</v>
+        <v>0.2079782151909468</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.8066710179259846</v>
+        <v>0.8226031098472144</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-6.667418318152784</v>
+        <v>-6.531008743388725</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.438787721259176</v>
+        <v>0.4660696362119878</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-7.10620603941196</v>
+        <v>-6.997078379600713</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>-6.66147091221397</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>11167031</v>
+        <v>11812291</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>17920598.62</v>
+        <v>17933503.82</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6231393959985919</v>
+        <v>0.6586716750145929</v>
       </c>
       <c r="P22" s="6" t="n">
         <v>0.0310198990532244</v>
@@ -5580,7 +5807,7 @@
         <v>25.56014360700335</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>0.1318144661146117</v>
+        <v>0.1306622239290588</v>
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
@@ -5595,46 +5822,46 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>211.3099975585937</v>
+        <v>210.6649932861328</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>209.3194003295899</v>
+        <v>209.3065002441406</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>191.9676504516601</v>
+        <v>191.9644254302979</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>60.36799095758673</v>
+        <v>59.89200508010831</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.0298259907615874</v>
+        <v>0.0266825419347123</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.07531425100743649</v>
+        <v>0.0720319534628273</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.1425867566187699</v>
+        <v>0.1390991159572245</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.6257455379005705</v>
+        <v>-0.6771988701766531</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-2.266487638852655</v>
+        <v>-2.276778305307872</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1.640742100952084</v>
+        <v>1.599579435131218</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>1.206196025562167</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>66406268</v>
+        <v>69664661</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>157714889.36</v>
+        <v>157780057.22</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.4210526239435837</v>
+        <v>0.4415302049413213</v>
       </c>
       <c r="P23" s="6" t="n">
         <v>0.0229450115312453</v>
@@ -5648,7 +5875,7 @@
         <v>6.875713893345424</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>0.0325385167421568</v>
+        <v>0.0326381416584319</v>
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
@@ -5663,46 +5890,46 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>91.44000244140624</v>
+        <v>91.61000061035156</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>106.6353994750977</v>
+        <v>106.6387994384766</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>104.4488996887207</v>
+        <v>104.4497496795654</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>16.83770701730374</v>
+        <v>17.3715982489269</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>-0.09429473781097281</v>
+        <v>-0.0926109207498903</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.2121316184308715</v>
+        <v>-0.2106668745697536</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.1671372467538243</v>
+        <v>-0.1655888528424689</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-4.126087979081973</v>
+        <v>-4.112526871587747</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-3.345666212443152</v>
+        <v>-3.342953990944306</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.7804217666388213</v>
+        <v>-0.7695728806434405</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>-0.7934742332941171</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>2524808</v>
+        <v>2583527</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3254214.16</v>
+        <v>3255388.54</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.7758579724205982</v>
+        <v>0.7936155602489158</v>
       </c>
       <c r="P24" s="6" t="n">
         <v>0.0177384274683925</v>
@@ -5716,7 +5943,7 @@
         <v>4.48357173374721</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>0.049032935411613</v>
+        <v>0.0489419463363761</v>
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
@@ -5731,46 +5958,46 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>25.60000038146973</v>
+        <v>25.67000007629395</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>35.87540008544922</v>
+        <v>35.87680007934571</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>25.36874998569489</v>
+        <v>25.36909998416901</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>41.16938033603359</v>
+        <v>41.34382605723892</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.1781701221517513</v>
+        <v>-0.1759229409099713</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.2455054479452914</v>
+        <v>-0.2434423859295348</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.0062893020461187</v>
+        <v>0.0090408623194964</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-2.457646938735817</v>
+        <v>-2.452062917496278</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-2.398321015988501</v>
+        <v>-2.397204211740594</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.0593259227473152</v>
+        <v>-0.0548587057556839</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>-0.0149246408257801</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>2582135</v>
+        <v>2754942</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>13300196.7</v>
+        <v>13303652.84</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.1941426174546727</v>
+        <v>0.2070816213511476</v>
       </c>
       <c r="P25" s="6" t="n">
         <v>0.0084746235925221</v>
@@ -5784,7 +6011,7 @@
         <v>2.376357078552246</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>0.0928264469977252</v>
+        <v>0.09257331793881809</v>
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
@@ -5799,46 +6026,46 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>13.76000022888184</v>
+        <v>13.72999954223633</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>11.47340003967285</v>
+        <v>11.47280002593994</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>9.128525011539461</v>
+        <v>9.128375008106232</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>75.39503211062105</v>
+        <v>75.22726711162801</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.2123347811817462</v>
+        <v>0.2096915489670152</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.5654152774286336</v>
+        <v>0.5620022300138776</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.6037296446662819</v>
+        <v>0.6002330611100726</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.681810209601732</v>
+        <v>0.6794169924334295</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.6471434281876072</v>
+        <v>0.6466647847539466</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.0346667814141248</v>
+        <v>0.0327522076794828</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>0.042571941463545</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>148646</v>
+        <v>154245</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>663114.92</v>
+        <v>663226.9</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.2241632566493904</v>
+        <v>0.2325674667297119</v>
       </c>
       <c r="P26" s="6" t="n">
         <v>-0.0110537672736636</v>
@@ -5852,7 +6079,7 @@
         <v>0.6038284982953753</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>0.0438828843205944</v>
+        <v>0.0439787704608345</v>
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
@@ -5867,46 +6094,46 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>79.67500305175781</v>
+        <v>79.76999664306641</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>107.0316999816895</v>
+        <v>107.0335998535156</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>77.06792512893676</v>
+        <v>77.06840009689331</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>37.94018845028621</v>
+        <v>38.03211555661516</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-0.2218478022589683</v>
+        <v>-0.2209200398615189</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.1032262767245368</v>
+        <v>0.1045416130538494</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.0935722221995587</v>
+        <v>-0.0924915215208377</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-7.639299605954704</v>
+        <v>-7.631721769611005</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-6.249119964171764</v>
+        <v>-6.247604396903024</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-1.39017964178294</v>
+        <v>-1.384117372707981</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>-1.60128212643402</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>10227320</v>
+        <v>10508638</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>28170838.4</v>
+        <v>28176464.76</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.363046347956758</v>
+        <v>0.372958001988891</v>
       </c>
       <c r="P27" s="6" t="n">
         <v>0.0264563885114627</v>
@@ -5920,7 +6147,7 @@
         <v>7.732856750488281</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>0.0970549915820514</v>
+        <v>0.0969394142648546</v>
       </c>
       <c r="T27" s="6" t="inlineStr">
         <is>
@@ -5935,46 +6162,46 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>18.59499931335449</v>
+        <v>18.69009971618652</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>16.94749992370605</v>
+        <v>16.94940193176269</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>21.97315001964569</v>
+        <v>21.97362552165985</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>62.29968817312163</v>
+        <v>62.96362228035989</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.1215319299710848</v>
+        <v>0.1272677805904842</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.0382467600099596</v>
+        <v>0.0435566652942844</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.3009398854629992</v>
+        <v>-0.2973646824002849</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.4072778410474384</v>
+        <v>0.4148641979685088</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.3720980591580261</v>
+        <v>0.3736153305422402</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.0351797818894123</v>
+        <v>0.0412488674262686</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>0.0328078631428616</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>50694519</v>
+        <v>55594214</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>76207968.38</v>
+        <v>76305962.28</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6652128389936749</v>
+        <v>0.7285697256002156</v>
       </c>
       <c r="P28" s="6" t="n">
         <v>0.0044125718372439</v>
@@ -5988,7 +6215,7 @@
         <v>0.9414285932268416</v>
       </c>
       <c r="S28" s="6" t="n">
-        <v>0.0506280520564864</v>
+        <v>0.0503704425082076</v>
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
@@ -6003,46 +6230,46 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>6.429999828338623</v>
+        <v>6.409999847412109</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>5.93479998588562</v>
+        <v>5.93439998626709</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>4.497100005149841</v>
+        <v>4.497000005245209</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>62.8078769713569</v>
+        <v>62.49999561730699</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.301619383372341</v>
+        <v>0.2975708042843141</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.0516224735455606</v>
+        <v>-0.0545723231484529</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.4008713757260598</v>
+        <v>0.3965140815514099</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.3323023162992076</v>
+        <v>0.3307068762252978</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.3112106828260628</v>
+        <v>0.3108915948112808</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.0210916334731448</v>
+        <v>0.0198152814140169</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>0.0646032293833483</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>293038</v>
+        <v>302245</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>1211992.76</v>
+        <v>1212176.9</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.241781972360957</v>
+        <v>0.2493406696662838</v>
       </c>
       <c r="P29" s="6" t="n">
         <v>0.0046656626141934</v>
@@ -6056,7 +6283,7 @@
         <v>0.6430713449205671</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>0.1000110983030497</v>
+        <v>0.1003231451214764</v>
       </c>
       <c r="T29" s="6" t="inlineStr">
         <is>
@@ -6071,46 +6298,46 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>395.7550048828125</v>
+        <v>395.3999938964844</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>409.9180993652344</v>
+        <v>409.9109991455078</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>417.7492750549316</v>
+        <v>417.7475</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>54.20369849720209</v>
+        <v>54.10686010531468</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-0.0262652559735777</v>
+        <v>-0.0271387421648671</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.08664193195535549</v>
+        <v>0.0856671626680707</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.1185071890255263</v>
+        <v>-0.1192979298333598</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-1.32923726190478</v>
+        <v>-1.357557226626113</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-1.257919446518039</v>
+        <v>-1.263583439462306</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.0713178153867408</v>
+        <v>-0.09397378716380771</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>0.3816312784934397</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>14952588</v>
+        <v>15410750</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>48268341.76</v>
+        <v>48277505</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.3097804369237979</v>
+        <v>0.3192118151093351</v>
       </c>
       <c r="P30" s="6" t="n">
         <v>0.0109940121352903</v>
@@ -6124,7 +6351,7 @@
         <v>18.56714085170201</v>
       </c>
       <c r="S30" s="6" t="n">
-        <v>0.0469157448992968</v>
+        <v>0.0469578683315885</v>
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
@@ -6139,46 +6366,46 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>422.3099975585938</v>
+        <v>422.5</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>425.0316003417969</v>
+        <v>425.035400390625</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>349.7328500366211</v>
+        <v>349.7338000488281</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>45.57065028514946</v>
+        <v>45.63563934448866</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-0.0038213741541671</v>
+        <v>-0.0033731811867222</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.1116638534166607</v>
+        <v>0.1121640046027405</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.2728999353259491</v>
+        <v>0.2734726286005009</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>1.321296906282101</v>
+        <v>1.33645379619486</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>5.405639919630812</v>
+        <v>5.408671297613364</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-4.084343013348712</v>
+        <v>-4.072217501418504</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>-3.711786865119478</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>8994036</v>
+        <v>9313232</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>13655284.72</v>
+        <v>13661668.64</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.6586487344952262</v>
+        <v>0.6817053059486297</v>
       </c>
       <c r="P31" s="6" t="n">
         <v>0.0220361706931489</v>
@@ -6192,7 +6419,7 @@
         <v>19.97285679408482</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>0.0472943025491923</v>
+        <v>0.0472730338321534</v>
       </c>
       <c r="T31" s="6" t="inlineStr">
         <is>
@@ -6207,46 +6434,46 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>303.4923095703125</v>
+        <v>303.7749938964844</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>324.2316473388672</v>
+        <v>324.2373010253907</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>238.4740118408203</v>
+        <v>238.4754252624512</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>45.57138320604898</v>
+        <v>45.64846508307077</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.0020547246777753</v>
+        <v>0.0029880767124081</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.0226005602866378</v>
+        <v>-0.0216901731258978</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.7849339043062218</v>
+        <v>0.7865964599034774</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-1.965428891783233</v>
+        <v>-1.942878575165537</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-1.192729630470103</v>
+        <v>-1.188219567146564</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.7726992613131298</v>
+        <v>-0.7546590080189728</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>-0.1480541656201379</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>1947718</v>
+        <v>2015025</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>6148452.36</v>
+        <v>6149798.5</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3167818315827367</v>
+        <v>0.3276570768944706</v>
       </c>
       <c r="P32" s="6" t="n">
         <v>0.031582057136426</v>
@@ -6260,7 +6487,7 @@
         <v>21.269287109375</v>
       </c>
       <c r="S32" s="6" t="n">
-        <v>0.0700817992373127</v>
+        <v>0.0700165831181707</v>
       </c>
       <c r="T32" s="6" t="inlineStr">
         <is>
@@ -6275,46 +6502,46 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>881.2999877929688</v>
+        <v>883.1300048828125</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>877.2489965820313</v>
+        <v>877.2855969238282</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>479.5833498382568</v>
+        <v>479.5924999237061</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>38.11380958860197</v>
+        <v>38.28450466392492</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-0.0534241186288932</v>
+        <v>-0.0514585563189684</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.6521070481394426</v>
+        <v>0.6555376440480138</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1.741383469190091</v>
+        <v>1.747075944701178</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-3.766257881821275</v>
+        <v>-3.620273612546043</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>11.27853311773778</v>
+        <v>11.30772997159282</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-15.04479099955905</v>
+        <v>-14.92800358413886</v>
       </c>
       <c r="L33" s="6" t="n">
         <v>-17.58862389405815</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>1959987</v>
+        <v>2119632</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>4338443.74</v>
+        <v>4341636.64</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.4517719065777259</v>
+        <v>0.4882103629934356</v>
       </c>
       <c r="P33" s="6" t="n">
         <v>0.0451049293978258</v>
@@ -6328,7 +6555,7 @@
         <v>84.29928588867188</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>0.09565333831421211</v>
+        <v>0.0954551259979645</v>
       </c>
       <c r="T33" s="6" t="inlineStr">
         <is>
@@ -6343,46 +6570,46 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>27.7947998046875</v>
+        <v>27.79500007629395</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>33.45629581451416</v>
+        <v>33.45629981994629</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>34.37742389678955</v>
+        <v>34.37742489814758</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>27.49372623544604</v>
+        <v>27.49490920476378</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>-0.0874983374882559</v>
+        <v>-0.0874917625830535</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.0218676112156024</v>
+        <v>0.0218749741421033</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.0771979073625112</v>
+        <v>-0.07719125823897641</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-1.885057254189708</v>
+        <v>-1.885041278107142</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-1.84861229229348</v>
+        <v>-1.848609097076966</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.0364449618962279</v>
+        <v>-0.0364321810301755</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>-0.1129581202809464</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>11521691</v>
+        <v>11935377</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>55522437.82</v>
+        <v>55530711.54</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2075141411721247</v>
+        <v>0.214932902334642</v>
       </c>
       <c r="P34" s="6" t="n">
         <v>0.0112075006381963</v>
@@ -6396,7 +6623,7 @@
         <v>1.774999754769462</v>
       </c>
       <c r="S34" s="6" t="n">
-        <v>0.06386085768713159</v>
+        <v>0.0638603975498219</v>
       </c>
       <c r="T34" s="6" t="inlineStr">
         <is>
@@ -6411,46 +6638,46 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>269.489990234375</v>
+        <v>268.2900085449219</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>226.128999633789</v>
+        <v>226.105</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>160.4468001556396</v>
+        <v>160.4408002471924</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>76.16602114423313</v>
+        <v>75.85609116382497</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.1722052952977308</v>
+        <v>0.1669857140828072</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>1.437279469821594</v>
+        <v>1.426426781997002</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1.129177458198218</v>
+        <v>1.119696683193505</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>12.19466717449183</v>
+        <v>12.09894213943574</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>11.5980527349329</v>
+        <v>11.57890772792168</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.5966144395589303</v>
+        <v>0.5200344115140574</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>0.3955764881293149</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>2205039</v>
+        <v>2277530</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>6064396.78</v>
+        <v>6065846.6</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.363604012071255</v>
+        <v>0.3754677871346104</v>
       </c>
       <c r="P35" s="6" t="n">
         <v>-0.0192129762097973</v>
@@ -6464,7 +6691,7 @@
         <v>13.84728785923549</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v>0.0513833105533624</v>
+        <v>0.0516131328719121</v>
       </c>
       <c r="T35" s="6" t="inlineStr">
         <is>
@@ -6479,7 +6706,7 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>184.4600067138672</v>
+        <v>185.9349975585937</v>
       </c>
       <c r="C36" s="6" t="inlineStr"/>
       <c r="D36" s="6" t="inlineStr"/>
@@ -6488,19 +6715,19 @@
       <c r="G36" s="6" t="inlineStr"/>
       <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" s="6" t="n">
-        <v>0.419190753084024</v>
+        <v>0.5368538404126468</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.1012330744544238</v>
+        <v>-0.07770045698869921</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.5204238275384478</v>
+        <v>0.614554297401346</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>-0.9253561253561428</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>47160529</v>
+        <v>49039454</v>
       </c>
       <c r="N36" s="6" t="inlineStr"/>
       <c r="O36" s="6" t="inlineStr"/>
@@ -6527,46 +6754,46 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>8.559900283813477</v>
+        <v>8.564999580383301</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>10.93819803237915</v>
+        <v>10.93830001831055</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>18.4502494764328</v>
+        <v>18.45027497291565</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>20.51078645679097</v>
+        <v>20.61458650817841</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-0.134489384563803</v>
+        <v>-0.1339737833107386</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.1648877771889291</v>
+        <v>-0.1643902848406535</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.5659279623799649</v>
+        <v>-0.5656693773522072</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.6492927703661131</v>
+        <v>-0.6488859888733618</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.5324723633922838</v>
+        <v>-0.5323910070937335</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.1168204069738293</v>
+        <v>-0.1164949817796282</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>-0.1257283657885731</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>15452173</v>
+        <v>16231048</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>33043959.46</v>
+        <v>33059536.96</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.467624741481268</v>
+        <v>0.4909641662446321</v>
       </c>
       <c r="P37" s="6" t="n">
         <v>0.0299401183926648</v>
@@ -6580,7 +6807,7 @@
         <v>0.6735711097717285</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>0.0786891304149222</v>
+        <v>0.0786422817012659</v>
       </c>
       <c r="T37" s="6" t="inlineStr">
         <is>
@@ -6595,46 +6822,46 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>45.66999816894531</v>
+        <v>45.86000061035156</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>60.61799980163574</v>
+        <v>60.62179985046387</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>81.4565497970581</v>
+        <v>81.45749980926513</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>22.90686414096366</v>
+        <v>23.24043212585009</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-0.2056010291255345</v>
+        <v>-0.2022960641601671</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.2203824386919951</v>
+        <v>-0.2171389693258757</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.554439042254192</v>
+        <v>-0.5525853598990091</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-3.845335962193325</v>
+        <v>-3.830179072280572</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-3.484397475244628</v>
+        <v>-3.481366097262078</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.3609384869486964</v>
+        <v>-0.348812975018494</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>-0.3462640816307631</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>3721356</v>
+        <v>3854113</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>12374147.12</v>
+        <v>12376802.26</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.3007363629922642</v>
+        <v>0.3113981236054748</v>
       </c>
       <c r="P38" s="6" t="n">
         <v>0.0251036384349932</v>
@@ -6648,7 +6875,7 @@
         <v>3.443371636526925</v>
       </c>
       <c r="S38" s="6" t="n">
-        <v>0.075396798217267</v>
+        <v>0.0750844219515706</v>
       </c>
       <c r="T38" s="6" t="inlineStr">
         <is>
@@ -6663,46 +6890,46 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>7.71999979019165</v>
+        <v>7.735000133514404</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>9.765399990081788</v>
+        <v>9.765699996948245</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>12.02965001344681</v>
+        <v>12.02972501516342</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>26.35658618633685</v>
+        <v>26.64093014772622</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>-0.1562841407602504</v>
+        <v>-0.154644758907996</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.122727315583504</v>
+        <v>-0.121022731151955</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.4990266147544372</v>
+        <v>-0.4980531985655153</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.5942921915682895</v>
+        <v>-0.5930955829841373</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.4884172063598076</v>
+        <v>-0.4881778846429772</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.1058749852084818</v>
+        <v>-0.1049176983411601</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>-0.1257187896488844</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>28250652</v>
+        <v>31379033</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>37203223.04</v>
+        <v>37265790.66</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.7593603373994126</v>
+        <v>0.842033201074178</v>
       </c>
       <c r="P39" s="6" t="n">
         <v>0.0100267124430337</v>
@@ -6716,7 +6943,7 @@
         <v>0.5577142919812884</v>
       </c>
       <c r="S39" s="6" t="n">
-        <v>0.0722427858987601</v>
+        <v>0.0721026867943815</v>
       </c>
       <c r="T39" s="6" t="inlineStr">
         <is>
@@ -6731,46 +6958,46 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>6.804999828338623</v>
+        <v>6.824999809265137</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>7.679300022125244</v>
+        <v>7.679700021743774</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>10.2586500120163</v>
+        <v>10.25875001192093</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>57.71669781062163</v>
+        <v>58.071274466897</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>-0.0137681544515616</v>
+        <v>-0.0108696065312592</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.0236728790272302</v>
+        <v>-0.0208034412182567</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.4118409673439486</v>
+        <v>-0.4101123604767019</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.2363106979500218</v>
+        <v>-0.2347152578761129</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.3055028544320996</v>
+        <v>-0.3051837664173178</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.0691921564820778</v>
+        <v>0.0704685085412049</v>
       </c>
       <c r="L40" s="6" t="n">
         <v>0.0561779742976243</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>18610524</v>
+        <v>20269023</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>28616478.48</v>
+        <v>28649648.46</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.6503429138916187</v>
+        <v>0.7074789426578535</v>
       </c>
       <c r="P40" s="6" t="n">
         <v>-0.0154083063419491</v>
@@ -6781,10 +7008,10 @@
         </is>
       </c>
       <c r="R40" s="6" t="n">
-        <v>0.4031429290771484</v>
+        <v>0.4056429181780134</v>
       </c>
       <c r="S40" s="6" t="n">
-        <v>0.0592421659436796</v>
+        <v>0.0594348614672986</v>
       </c>
       <c r="T40" s="6" t="inlineStr">
         <is>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -473,14 +473,14 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>371.7000122070313</v>
+        <v>369.7999877929688</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.082723417254077</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.2759004286252026</v>
+        <v>0.2793673206823957</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>75</v>
@@ -573,13 +573,13 @@
         <v>12</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.0322840990204654</v>
+        <v>0.0324499740295236</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>278.8441685267858</v>
+        <v>276.9441441127233</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>510.9837777273996</v>
+        <v>509.0837533133371</v>
       </c>
     </row>
     <row r="3">
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>986.6900024414062</v>
+        <v>982.6099853515624</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.0543756800501934</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.3894289129247086</v>
+        <v>0.3930254157668736</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>75</v>
@@ -614,13 +614,13 @@
         <v>12</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.0121618745201714</v>
+        <v>0.0122123733514743</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>807.1599731445312</v>
+        <v>803.0799560546874</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1255.985046386719</v>
+        <v>1251.905029296875</v>
       </c>
     </row>
     <row r="4">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>239.6999969482422</v>
+        <v>238.6300964355469</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.06596166699561611</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.2703109591354888</v>
+        <v>0.2741969617663742</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>75</v>
@@ -655,13 +655,13 @@
         <v>12</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.0500625788601538</v>
+        <v>0.0502870349517759</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>186.1292811802456</v>
+        <v>185.0593806675502</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>320.0560706002371</v>
+        <v>318.9861700875418</v>
       </c>
     </row>
   </sheetData>
@@ -675,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y40"/>
+  <dimension ref="A1:AB40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -701,8 +701,11 @@
     <col width="21" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="23" customWidth="1" min="23" max="23"/>
-    <col width="35" customWidth="1" min="24" max="24"/>
-    <col width="23" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="35" customWidth="1" min="27" max="27"/>
+    <col width="23" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -823,10 +826,25 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>position_count</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>open_slots</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>position_rule</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>decision_reasons</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>warnings</t>
         </is>
@@ -849,7 +867,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>182.0500030517578</v>
+        <v>181.9550018310547</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>89</v>
@@ -869,22 +887,22 @@
         <v>75</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>62.17642691523031</v>
+        <v>62.13229147846583</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.0151807899125376</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.3418439357313785</v>
+        <v>0.3464883768441935</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1.571182118412793</v>
+        <v>1.565119362447711</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>161.1255929129464</v>
+        <v>161.0305916922433</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>213.4366182599749</v>
+        <v>213.3416170392718</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>10.46220506940569</v>
@@ -904,12 +922,23 @@
       <c r="U2" s="2" t="inlineStr"/>
       <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -928,7 +957,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>210.6649932861328</v>
+        <v>211.0950012207031</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>89</v>
@@ -948,22 +977,22 @@
         <v>75</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>59.89200508010831</v>
+        <v>60.21059301407551</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.0229450115312453</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.4415302049413213</v>
+        <v>0.4467218527117392</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1.599579435131218</v>
+        <v>1.627021536938551</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>200.3514224461147</v>
+        <v>200.781430380685</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>224.4164210728237</v>
+        <v>224.846429007394</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>6.875713893345424</v>
@@ -972,7 +1001,7 @@
         <v>13.95</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.06622699999999999</v>
+        <v>0.066092</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>1.12</v>
@@ -983,12 +1012,23 @@
       <c r="U3" s="2" t="inlineStr"/>
       <c r="V3" s="2" t="inlineStr"/>
       <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="X3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1007,7 +1047,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>554.8200073242188</v>
+        <v>554.9249877929688</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>82</v>
@@ -1027,22 +1067,22 @@
         <v>50</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>55.78533584693042</v>
+        <v>55.80068861027303</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0.0624019610194614</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.4361500707930983</v>
+        <v>0.4386895932335694</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>-2.632400099130137</v>
+        <v>-2.625700490868056</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>497.7428545270647</v>
+        <v>497.8478349958147</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>630.9228777204241</v>
+        <v>631.0278581891741</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>38.05143519810268</v>
@@ -1062,12 +1102,23 @@
       <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1086,7 +1137,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>986.6900024414062</v>
+        <v>982.6099853515624</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>82</v>
@@ -1106,28 +1157,28 @@
         <v>50</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>45.09481845458335</v>
+        <v>44.75504296621285</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0.0543756800501934</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.3894289129247086</v>
+        <v>0.3930254157668736</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-24.74268826599728</v>
+        <v>-25.00306542500729</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>807.1599731445312</v>
+        <v>803.0799560546874</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1255.985046386719</v>
+        <v>1251.905029296875</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>89.7650146484375</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>6.13</v>
+        <v>6.11</v>
       </c>
       <c r="R5" s="2" t="n">
         <v>0.006217</v>
@@ -1141,12 +1192,23 @@
       <c r="U5" s="2" t="inlineStr"/>
       <c r="V5" s="2" t="inlineStr"/>
       <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr">
+      <c r="X5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1165,7 +1227,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1156.650024414062</v>
+        <v>1157.2099609375</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>82</v>
@@ -1185,22 +1247,22 @@
         <v>50</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>57.90061457309466</v>
+        <v>58.0041452805042</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>-0.013419399271567</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.4068960451700752</v>
+        <v>0.4090329628657867</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-6.852020048930058</v>
+        <v>-6.816286208118143</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1094.400547572545</v>
+        <v>1094.960484095982</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1239.64932686942</v>
+        <v>1240.209263392857</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>41.49965122767857</v>
@@ -1209,7 +1271,7 @@
         <v>13.95</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.012062</v>
+        <v>0.012056</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>1.12</v>
@@ -1220,12 +1282,23 @@
       <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" s="2" t="inlineStr"/>
       <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
+      <c r="X6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1244,7 +1317,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7.670000076293945</v>
+        <v>7.675000190734863</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>82</v>
@@ -1264,22 +1337,22 @@
         <v>50</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>50</v>
+        <v>50.04831028267274</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>-0.0049382666628676</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.4792892163534802</v>
+        <v>0.4820637547508388</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-0.1232215052264239</v>
+        <v>-0.1229024096039831</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>6.192785944257464</v>
+        <v>6.197786058698382</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>9.885821274348668</v>
+        <v>9.890821388789586</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>0.7386070660182408</v>
@@ -1299,12 +1372,23 @@
       <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="2" t="inlineStr"/>
       <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr">
+      <c r="X7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1323,7 +1407,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>371.7000122070313</v>
+        <v>369.7999877929688</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>82</v>
@@ -1343,28 +1427,28 @@
         <v>50</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46.43119251769661</v>
+        <v>46.14272736888983</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0.082723417254077</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.2759004286252026</v>
+        <v>0.2793673206823957</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-11.07345643837971</v>
+        <v>-11.19471155768165</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>278.8441685267858</v>
+        <v>276.9441441127233</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>510.9837777273996</v>
+        <v>509.0837533133371</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>46.42792184012277</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="R8" s="2" t="n">
         <v>0.01202</v>
@@ -1378,12 +1462,23 @@
       <c r="U8" s="2" t="inlineStr"/>
       <c r="V8" s="2" t="inlineStr"/>
       <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="inlineStr">
+      <c r="X8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1402,7 +1497,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>16.8799991607666</v>
+        <v>16.8700008392334</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>79</v>
@@ -1422,22 +1517,22 @@
         <v>75</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>74.57627042542499</v>
+        <v>74.5523124039135</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>0.0098826338563442</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.2041913379434426</v>
+        <v>0.2057040933627727</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.1279210809786271</v>
+        <v>0.1272830114562815</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>13.88099902016776</v>
+        <v>13.87100069863456</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>21.37849937166487</v>
+        <v>21.36850105013166</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.499500070299421</v>
@@ -1455,16 +1550,27 @@
         <v>13.95</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>0.1201687092347426</v>
+        <v>0.1195052135307623</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
+      <c r="X9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
+      <c r="AB9" s="3" t="inlineStr">
         <is>
           <t>RSI overbought</t>
         </is>
@@ -1487,7 +1593,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>13.72999954223633</v>
+        <v>13.72000026702881</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>79</v>
@@ -1507,22 +1613,22 @@
         <v>75</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>75.22726711162801</v>
+        <v>75.17084129057541</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>-0.0110537672736636</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.2325674667297119</v>
+        <v>0.235268699636298</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.0327522076794828</v>
+        <v>0.0321140772958692</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>12.52234254564558</v>
+        <v>12.51234327043806</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>15.54148503712245</v>
+        <v>15.53148576191494</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.6038284982953753</v>
@@ -1542,12 +1648,23 @@
       <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr">
+      <c r="X10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
+      <c r="AB10" s="3" t="inlineStr">
         <is>
           <t>RSI overbought</t>
         </is>
@@ -1570,7 +1687,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>268.2900085449219</v>
+        <v>268.3299865722656</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>79</v>
@@ -1590,22 +1707,22 @@
         <v>75</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>75.85609116382497</v>
+        <v>75.86654638577177</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>-0.0192129762097973</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.3754677871346104</v>
+        <v>0.3775389596377526</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.5200344115140574</v>
+        <v>0.5225857158231797</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>247.5190767560686</v>
+        <v>247.5590547834124</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>295.9845842633928</v>
+        <v>296.0245622907366</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>13.84728785923549</v>
@@ -1614,7 +1731,7 @@
         <v>6.98</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.026001</v>
+        <v>0.025997</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>1.12</v>
@@ -1625,12 +1742,23 @@
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr"/>
       <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
+      <c r="X11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
+      <c r="AB11" s="3" t="inlineStr">
         <is>
           <t>RSI overbought</t>
         </is>
@@ -1653,7 +1781,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>392.8800048828125</v>
+        <v>393.3099060058594</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>79</v>
@@ -1673,22 +1801,22 @@
         <v>75</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>55.22621319204223</v>
+        <v>55.3837022728646</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0.030087289573326</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.3674262701458883</v>
+        <v>0.3702226400205015</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.220619813736693</v>
+        <v>3.248055099082121</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>370.3746555873326</v>
+        <v>370.8045567103795</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>422.8871372767857</v>
+        <v>423.3170383998326</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>15.00356619698661</v>
@@ -1697,7 +1825,7 @@
         <v>6.98</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.017756</v>
+        <v>0.017736</v>
       </c>
       <c r="S12" s="4" t="n">
         <v>1.12</v>
@@ -1708,12 +1836,23 @@
       <c r="U12" s="4" t="inlineStr"/>
       <c r="V12" s="4" t="inlineStr"/>
       <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr">
+      <c r="X12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr">
         <is>
           <t>Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="Y12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1732,7 +1871,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6.409999847412109</v>
+        <v>6.414999961853027</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>78</v>
@@ -1752,22 +1891,22 @@
         <v>75</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>62.49999561730699</v>
+        <v>62.57668446039076</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>0.0046656626141934</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2493406696662838</v>
+        <v>0.2529078200156134</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.0198152814140169</v>
+        <v>0.020134377036457</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>5.123857157570975</v>
+        <v>5.128857272011893</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>8.33921388217381</v>
+        <v>8.344213996614728</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0.6430713449205671</v>
@@ -1787,12 +1926,23 @@
       <c r="U13" s="4" t="inlineStr"/>
       <c r="V13" s="4" t="inlineStr"/>
       <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr">
+      <c r="X13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z13" s="4" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA13" s="4" t="inlineStr">
         <is>
           <t>Strong trend; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="Y13" s="4" t="inlineStr"/>
+      <c r="AB13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1811,7 +1961,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>239.6999969482422</v>
+        <v>238.6300964355469</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>75</v>
@@ -1831,28 +1981,28 @@
         <v>50</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>41.5707735141641</v>
+        <v>41.24271373225548</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>0.06596166699561611</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2703109591354888</v>
+        <v>0.2741969617663742</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.603719672066736</v>
+        <v>-4.671998223304254</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>186.1292811802456</v>
+        <v>185.0593806675502</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>320.0560706002371</v>
+        <v>318.9861700875418</v>
       </c>
       <c r="P14" s="4" t="n">
         <v>26.78535788399833</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="R14" s="4" t="n">
         <v>0.010417</v>
@@ -1866,12 +2016,23 @@
       <c r="U14" s="4" t="inlineStr"/>
       <c r="V14" s="4" t="inlineStr"/>
       <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr">
+      <c r="X14" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="Y14" s="4" t="inlineStr"/>
+      <c r="AB14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1890,7 +2051,7 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>358.3150024414062</v>
+        <v>358.5450134277344</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>71</v>
@@ -1910,22 +2071,22 @@
         <v>75</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>59.93802393421079</v>
+        <v>60.08777128483414</v>
       </c>
       <c r="K15" s="5" t="n">
         <v>-0.0040282924977889</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.2634020235235434</v>
+        <v>0.2685316087084209</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>0.6212509150724284</v>
+        <v>0.6359296788722668</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>343.3696430751256</v>
+        <v>343.5996540614537</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>378.2421482631138</v>
+        <v>378.472159249442</v>
       </c>
       <c r="P15" s="5" t="n">
         <v>9.963572910853795</v>
@@ -1943,35 +2104,46 @@
         <v>13.95</v>
       </c>
       <c r="U15" s="5" t="n">
-        <v>-0.0231864077519594</v>
+        <v>-0.0225593676998241</v>
       </c>
       <c r="V15" s="5" t="inlineStr"/>
       <c r="W15" s="5" t="inlineStr"/>
-      <c r="X15" s="5" t="inlineStr">
+      <c r="X15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y15" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z15" s="5" t="inlineStr">
+        <is>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AA15" s="5" t="inlineStr">
         <is>
           <t>Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="Y15" s="5" t="inlineStr"/>
+      <c r="AB15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>CELC</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Internet/E-Commerce</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>104.8600006103516</v>
+        <v>246.5249938964844</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>68</v>
@@ -1991,25 +2163,25 @@
         <v>75</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>64.98261344099689</v>
+        <v>65.43192876681358</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0</v>
+        <v>-0.0071974396379796</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0.3676589234010302</v>
+        <v>0.3079046776428261</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>1.434553618754394</v>
+        <v>1.67978495280924</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>92.91714259556362</v>
+        <v>235.3082128252302</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>122.7742876325335</v>
+        <v>261.48070199149</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>5.971429007393973</v>
+        <v>7.47785404750279</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -2026,22 +2198,33 @@
       <c r="U16" s="5" t="inlineStr"/>
       <c r="V16" s="5" t="inlineStr"/>
       <c r="W16" s="5" t="inlineStr"/>
-      <c r="X16" s="5" t="inlineStr">
+      <c r="X16" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y16" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z16" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA16" s="5" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="Y16" s="5" t="inlineStr"/>
+      <c r="AB16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>CELC</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -2050,10 +2233,10 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>18.69009971618652</v>
+        <v>104.9599990844727</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -2064,31 +2247,31 @@
         <v>40</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>75</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>62.96362228035989</v>
+        <v>65.05409098398465</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.0044125718372439</v>
+        <v>0</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.7285697256002156</v>
+        <v>0.3726839268372514</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0.0412488674262686</v>
+        <v>1.44093528775813</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>16.80724252973284</v>
+        <v>93.01714106968473</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>21.51438549586705</v>
+        <v>122.8742861066546</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0.9414285932268416</v>
+        <v>5.971429007393973</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -2102,39 +2285,48 @@
       <c r="T17" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U17" s="5" t="n">
-        <v>0.0158420768008933</v>
-      </c>
+      <c r="U17" s="5" t="inlineStr"/>
       <c r="V17" s="5" t="inlineStr"/>
       <c r="W17" s="5" t="inlineStr"/>
-      <c r="X17" s="5" t="inlineStr">
+      <c r="X17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y17" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z17" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA17" s="5" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="Y17" s="5" t="inlineStr"/>
+      <c r="AB17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>422.5</v>
+        <v>18.69499969482422</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -2145,31 +2337,31 @@
         <v>40</v>
       </c>
       <c r="H18" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="I18" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="I18" s="5" t="n">
-        <v>50</v>
-      </c>
       <c r="J18" s="5" t="n">
-        <v>45.63563934448866</v>
+        <v>62.99719808877189</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.0220361706931489</v>
+        <v>0.0044125718372439</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.6817053059486297</v>
+        <v>0.7497547252693841</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>-4.072217501418504</v>
+        <v>0.0415615726156839</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>392.5407148088728</v>
+        <v>16.81214250837053</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>462.4457135881697</v>
+        <v>21.51928547450474</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>19.97285679408482</v>
+        <v>0.9414285932268416</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -2183,25 +2375,38 @@
       <c r="T18" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U18" s="5" t="inlineStr"/>
+      <c r="U18" s="5" t="n">
+        <v>0.016108399857013</v>
+      </c>
       <c r="V18" s="5" t="inlineStr"/>
       <c r="W18" s="5" t="inlineStr"/>
-      <c r="X18" s="5" t="inlineStr">
-        <is>
-          <t>Positive momentum</t>
-        </is>
-      </c>
-      <c r="Y18" s="5" t="inlineStr"/>
+      <c r="X18" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z18" s="5" t="inlineStr">
+        <is>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AA18" s="5" t="inlineStr">
+        <is>
+          <t>MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="AB18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Data Storage</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2210,7 +2415,7 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>883.1300048828125</v>
+        <v>422.989990234375</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>65</v>
@@ -2221,7 +2426,7 @@
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>75</v>
@@ -2230,25 +2435,25 @@
         <v>50</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>38.28450466392492</v>
+        <v>45.80252323519223</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.0451049293978258</v>
+        <v>0.0220361706931489</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.4882103629934356</v>
+        <v>0.6894883407522808</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>-14.92800358413886</v>
+        <v>-4.040947469367188</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>756.6810760498047</v>
+        <v>393.0307050432477</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>1051.728576660156</v>
+        <v>462.9357038225447</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>84.29928588867188</v>
+        <v>19.97285679408482</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2265,22 +2470,33 @@
       <c r="U19" s="5" t="inlineStr"/>
       <c r="V19" s="5" t="inlineStr"/>
       <c r="W19" s="5" t="inlineStr"/>
-      <c r="X19" s="5" t="inlineStr">
-        <is>
-          <t>Strong trend; Positive momentum</t>
-        </is>
-      </c>
-      <c r="Y19" s="5" t="inlineStr"/>
+      <c r="X19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z19" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA19" s="5" t="inlineStr">
+        <is>
+          <t>Positive momentum</t>
+        </is>
+      </c>
+      <c r="AB19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Data Centers</t>
+          <t>Data Storage</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2289,10 +2505,10 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>303.7749938964844</v>
+        <v>881.9500122070312</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -2300,34 +2516,34 @@
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>50</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>45.64846508307077</v>
+        <v>38.17454872190672</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.031582057136426</v>
+        <v>0.0451049293978258</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.3276570768944706</v>
+        <v>0.4929302343268891</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>-0.7546590080189728</v>
+        <v>-15.00330796002907</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>271.8710632324219</v>
+        <v>755.5010833740234</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>346.3135681152344</v>
+        <v>1050.548583984375</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>21.269287109375</v>
+        <v>84.29928588867188</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2344,18 +2560,33 @@
       <c r="U20" s="5" t="inlineStr"/>
       <c r="V20" s="5" t="inlineStr"/>
       <c r="W20" s="5" t="inlineStr"/>
-      <c r="X20" s="5" t="inlineStr"/>
-      <c r="Y20" s="5" t="inlineStr"/>
+      <c r="X20" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z20" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA20" s="5" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum</t>
+        </is>
+      </c>
+      <c r="AB20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Internet/E-Commerce</t>
+          <t>Data Centers</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -2364,10 +2595,10 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>246.4550018310547</v>
+        <v>303.9100036621094</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -2378,31 +2609,31 @@
         <v>40</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>65.31827411205957</v>
+        <v>45.6853713981408</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.0071974396379796</v>
+        <v>0.031582057136426</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.303846270874105</v>
+        <v>0.3309603781661025</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>1.675318222707727</v>
+        <v>-0.746043000184238</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>235.2382207598005</v>
+        <v>272.0060729980469</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>261.4107099260603</v>
+        <v>346.4485778808594</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>7.47785404750279</v>
+        <v>21.269287109375</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2419,12 +2650,19 @@
       <c r="U21" s="5" t="inlineStr"/>
       <c r="V21" s="5" t="inlineStr"/>
       <c r="W21" s="5" t="inlineStr"/>
-      <c r="X21" s="5" t="inlineStr">
-        <is>
-          <t>MACD/volume acceleration</t>
-        </is>
-      </c>
-      <c r="Y21" s="5" t="inlineStr"/>
+      <c r="X21" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z21" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA21" s="5" t="inlineStr"/>
+      <c r="AB21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2443,7 +2681,7 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>284.6789855957031</v>
+        <v>284.6000061035156</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>55</v>
@@ -2463,22 +2701,22 @@
         <v>50</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>28.66453145202405</v>
+        <v>28.65271378907748</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>0.0376936349020097</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.5487393878708714</v>
+        <v>0.5519305243966304</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-9.876831202721863</v>
+        <v>-9.881871489402789</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>225.9164123535156</v>
+        <v>225.8374328613281</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>372.8228454589844</v>
+        <v>372.7438659667969</v>
       </c>
       <c r="P22" s="5" t="n">
         <v>29.38128662109375</v>
@@ -2498,12 +2736,23 @@
       <c r="U22" s="5" t="inlineStr"/>
       <c r="V22" s="5" t="inlineStr"/>
       <c r="W22" s="5" t="inlineStr"/>
-      <c r="X22" s="5" t="inlineStr">
+      <c r="X22" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y22" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z22" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA22" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="Y22" s="5" t="inlineStr"/>
+      <c r="AB22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2522,7 +2771,7 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>223.2400054931641</v>
+        <v>223.2899932861328</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>55</v>
@@ -2542,22 +2791,22 @@
         <v>50</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>33.74884357057235</v>
+        <v>33.76812818833493</v>
       </c>
       <c r="K23" s="5" t="n">
         <v>0.0645198535414377</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.2746769101179065</v>
+        <v>0.2761431904386516</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-9.096790095363808</v>
+        <v>-9.093599991197133</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>190.8357162475587</v>
+        <v>190.8857040405273</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>266.4457244873047</v>
+        <v>266.4957122802734</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>21.60285949707031</v>
@@ -2577,12 +2826,23 @@
       <c r="U23" s="5" t="inlineStr"/>
       <c r="V23" s="5" t="inlineStr"/>
       <c r="W23" s="5" t="inlineStr"/>
-      <c r="X23" s="5" t="inlineStr">
+      <c r="X23" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y23" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z23" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA23" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="Y23" s="5" t="inlineStr"/>
+      <c r="AB23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2601,7 +2861,7 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>195.6199951171875</v>
+        <v>195.7400054931641</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>55</v>
@@ -2621,22 +2881,22 @@
         <v>50</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>30.17674820438588</v>
+        <v>30.19478996682716</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>0.0310198990532244</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.6586716750145929</v>
+        <v>0.6636987578920163</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>-6.997078379600713</v>
+        <v>-6.989419597772017</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>144.4997079031808</v>
+        <v>144.6197182791574</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>272.3004259381976</v>
+        <v>272.4204363141741</v>
       </c>
       <c r="P24" s="5" t="n">
         <v>25.56014360700335</v>
@@ -2656,12 +2916,23 @@
       <c r="U24" s="5" t="inlineStr"/>
       <c r="V24" s="5" t="inlineStr"/>
       <c r="W24" s="5" t="inlineStr"/>
-      <c r="X24" s="5" t="inlineStr">
+      <c r="X24" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y24" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z24" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA24" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="Y24" s="5" t="inlineStr"/>
+      <c r="AB24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2680,7 +2951,7 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>107.254997253418</v>
+        <v>107.375</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>55</v>
@@ -2700,22 +2971,22 @@
         <v>50</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>31.22796125679511</v>
+        <v>31.35155293469214</v>
       </c>
       <c r="K25" s="5" t="n">
         <v>0.0469355722360184</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.4429696145707189</v>
+        <v>0.4461193870124323</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-3.425367704586084</v>
+        <v>-3.417709409647521</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>93.03606796264648</v>
+        <v>93.15607070922852</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>126.2135696411133</v>
+        <v>126.3335723876953</v>
       </c>
       <c r="P25" s="5" t="n">
         <v>9.479286193847656</v>
@@ -2735,12 +3006,23 @@
       <c r="U25" s="5" t="inlineStr"/>
       <c r="V25" s="5" t="inlineStr"/>
       <c r="W25" s="5" t="inlineStr"/>
-      <c r="X25" s="5" t="inlineStr">
+      <c r="X25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y25" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z25" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA25" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="Y25" s="5" t="inlineStr"/>
+      <c r="AB25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2759,7 +3041,7 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>25.67000007629395</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>54</v>
@@ -2779,22 +3061,22 @@
         <v>50</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>41.34382605723892</v>
+        <v>41.6717492429667</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>0.0084746235925221</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.2070816213511476</v>
+        <v>0.2121235612950105</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>-0.0548587057556839</v>
+        <v>-0.0465624630173051</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>20.91728591918945</v>
+        <v>21.04728507995605</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>32.79907131195068</v>
+        <v>32.92907047271729</v>
       </c>
       <c r="P26" s="5" t="n">
         <v>2.376357078552246</v>
@@ -2814,8 +3096,19 @@
       <c r="U26" s="5" t="inlineStr"/>
       <c r="V26" s="5" t="inlineStr"/>
       <c r="W26" s="5" t="inlineStr"/>
-      <c r="X26" s="5" t="inlineStr"/>
-      <c r="Y26" s="5" t="inlineStr"/>
+      <c r="X26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z26" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA26" s="5" t="inlineStr"/>
+      <c r="AB26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2834,7 +3127,7 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>275.4800109863281</v>
+        <v>276.0199890136719</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>51</v>
@@ -2854,22 +3147,22 @@
         <v>75</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>61.14814244093061</v>
+        <v>61.55851569211629</v>
       </c>
       <c r="K27" s="5" t="n">
         <v>-0.0092015237095138</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>0.2055225252788215</v>
+        <v>0.2085784934230437</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>5.867915420958891</v>
+        <v>5.902375557176857</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>257.6782308306013</v>
+        <v>258.2182088579451</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>299.2157178606306</v>
+        <v>299.7556958879744</v>
       </c>
       <c r="P27" s="5" t="n">
         <v>11.86785343715123</v>
@@ -2889,12 +3182,23 @@
       <c r="U27" s="5" t="inlineStr"/>
       <c r="V27" s="5" t="inlineStr"/>
       <c r="W27" s="5" t="inlineStr"/>
-      <c r="X27" s="5" t="inlineStr">
+      <c r="X27" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y27" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z27" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA27" s="5" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="Y27" s="5" t="inlineStr"/>
+      <c r="AB27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -2913,7 +3217,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>395.3999938964844</v>
+        <v>395.7807922363281</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>43</v>
@@ -2933,22 +3237,22 @@
         <v>50</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>54.10686010531468</v>
+        <v>54.21071674379002</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0.0109940121352903</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.3192118151093351</v>
+        <v>0.3225300464659174</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>-0.09397378716380771</v>
+        <v>-0.0696721267293503</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>367.5492826189313</v>
+        <v>367.9300809587751</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>432.5342755998884</v>
+        <v>432.9150739397322</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>18.56714085170201</v>
@@ -2966,7 +3270,7 @@
         <v>13.95</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>-0.0436213489830091</v>
+        <v>-0.0427002882642661</v>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
@@ -2978,8 +3282,19 @@
           <t>Signal score weakened</t>
         </is>
       </c>
-      <c r="X28" s="3" t="inlineStr"/>
-      <c r="Y28" s="3" t="inlineStr">
+      <c r="X28" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr"/>
+      <c r="AB28" s="3" t="inlineStr">
         <is>
           <t>Signal score weakened</t>
         </is>
@@ -3002,7 +3317,7 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>79.76999664306641</v>
+        <v>79.86000061035156</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>43</v>
@@ -3022,22 +3337,22 @@
         <v>50</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>38.03211555661516</v>
+        <v>38.11896320533445</v>
       </c>
       <c r="K29" s="5" t="n">
         <v>0.0264563885114627</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.372958001988891</v>
+        <v>0.3748810140799213</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>-1.384117372707981</v>
+        <v>-1.378373529781509</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>64.30428314208984</v>
+        <v>64.394287109375</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>102.9685668945312</v>
+        <v>103.0585708618164</v>
       </c>
       <c r="P29" s="5" t="n">
         <v>7.732856750488281</v>
@@ -3057,8 +3372,19 @@
       <c r="U29" s="5" t="inlineStr"/>
       <c r="V29" s="5" t="inlineStr"/>
       <c r="W29" s="5" t="inlineStr"/>
-      <c r="X29" s="5" t="inlineStr"/>
-      <c r="Y29" s="5" t="inlineStr"/>
+      <c r="X29" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y29" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z29" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA29" s="5" t="inlineStr"/>
+      <c r="AB29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3103,7 +3429,7 @@
         <v>-0.0154083063419491</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.7074789426578535</v>
+        <v>0.7155083019845888</v>
       </c>
       <c r="M30" s="5" t="n">
         <v>0.0704685085412049</v>
@@ -3132,12 +3458,23 @@
       <c r="U30" s="5" t="inlineStr"/>
       <c r="V30" s="5" t="inlineStr"/>
       <c r="W30" s="5" t="inlineStr"/>
-      <c r="X30" s="5" t="inlineStr">
+      <c r="X30" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z30" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA30" s="5" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="Y30" s="5" t="inlineStr"/>
+      <c r="AB30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3156,7 +3493,7 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>27.79500007629395</v>
+        <v>27.80999946594238</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>33</v>
@@ -3176,22 +3513,22 @@
         <v>50</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>27.49490920476378</v>
+        <v>27.58339839891339</v>
       </c>
       <c r="K31" s="5" t="n">
         <v>0.0112075006381963</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.214932902334642</v>
+        <v>0.2161936276811687</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>-0.0364321810301755</v>
+        <v>-0.0354749550241217</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>24.24500056675502</v>
+        <v>24.25999995640346</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>33.11999934060233</v>
+        <v>33.13499873025077</v>
       </c>
       <c r="P31" s="5" t="n">
         <v>1.774999754769462</v>
@@ -3211,8 +3548,19 @@
       <c r="U31" s="5" t="inlineStr"/>
       <c r="V31" s="5" t="inlineStr"/>
       <c r="W31" s="5" t="inlineStr"/>
-      <c r="X31" s="5" t="inlineStr"/>
-      <c r="Y31" s="5" t="inlineStr"/>
+      <c r="X31" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y31" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z31" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA31" s="5" t="inlineStr"/>
+      <c r="AB31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3231,7 +3579,7 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>39.2599983215332</v>
+        <v>39.22909927368164</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>33</v>
@@ -3251,22 +3599,22 @@
         <v>50</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>17.37451029198574</v>
+        <v>17.28480087008961</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>0.0298353862022756</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.3452389555509</v>
+        <v>0.3484123267180921</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>-1.439316736976789</v>
+        <v>-1.441288642024866</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>31.85785566057477</v>
+        <v>31.82695661272321</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>50.36321231297084</v>
+        <v>50.33231326511928</v>
       </c>
       <c r="P32" s="5" t="n">
         <v>3.701071330479213</v>
@@ -3286,8 +3634,19 @@
       <c r="U32" s="5" t="inlineStr"/>
       <c r="V32" s="5" t="inlineStr"/>
       <c r="W32" s="5" t="inlineStr"/>
-      <c r="X32" s="5" t="inlineStr"/>
-      <c r="Y32" s="5" t="inlineStr"/>
+      <c r="X32" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y32" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z32" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA32" s="5" t="inlineStr"/>
+      <c r="AB32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3306,7 +3665,7 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>69.59999847412109</v>
+        <v>69.66000366210938</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>32</v>
@@ -3326,22 +3685,22 @@
         <v>50</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>47.04179037230127</v>
+        <v>47.09922336809468</v>
       </c>
       <c r="K33" s="5" t="n">
         <v>0.0334417645102432</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.2900078826669925</v>
+        <v>0.291092015097882</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>-0.7512925818682357</v>
+        <v>-0.747463190953888</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>55.68942696707589</v>
+        <v>55.74943215506417</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>90.46585573468889</v>
+        <v>90.52586092267715</v>
       </c>
       <c r="P33" s="5" t="n">
         <v>6.955285753522601</v>
@@ -3361,8 +3720,19 @@
       <c r="U33" s="5" t="inlineStr"/>
       <c r="V33" s="5" t="inlineStr"/>
       <c r="W33" s="5" t="inlineStr"/>
-      <c r="X33" s="5" t="inlineStr"/>
-      <c r="Y33" s="5" t="inlineStr"/>
+      <c r="X33" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y33" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z33" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA33" s="5" t="inlineStr"/>
+      <c r="AB33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3407,7 +3777,7 @@
         <v>0.018661516252568</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0.6202266874214982</v>
+        <v>0.6281787580389391</v>
       </c>
       <c r="M34" s="5" t="n">
         <v>-0.0748262672022259</v>
@@ -3436,8 +3806,19 @@
       <c r="U34" s="5" t="inlineStr"/>
       <c r="V34" s="5" t="inlineStr"/>
       <c r="W34" s="5" t="inlineStr"/>
-      <c r="X34" s="5" t="inlineStr"/>
-      <c r="Y34" s="5" t="inlineStr"/>
+      <c r="X34" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y34" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z34" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA34" s="5" t="inlineStr"/>
+      <c r="AB34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -3456,7 +3837,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>185.9349975585937</v>
+        <v>185.1950073242188</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>29</v>
@@ -3481,13 +3862,13 @@
       </c>
       <c r="L35" s="3" t="inlineStr"/>
       <c r="M35" s="3" t="n">
-        <v>0.614554297401346</v>
+        <v>0.567329849395619</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>171.0601977539062</v>
+        <v>170.3794067382813</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>213.8252471923828</v>
+        <v>212.9742584228516</v>
       </c>
       <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="3" t="n">
@@ -3505,12 +3886,23 @@
       <c r="U35" s="3" t="inlineStr"/>
       <c r="V35" s="3" t="inlineStr"/>
       <c r="W35" s="3" t="inlineStr"/>
-      <c r="X35" s="3" t="inlineStr">
+      <c r="X35" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
+      <c r="AB35" s="3" t="inlineStr">
         <is>
           <t>Missing ATR</t>
         </is>
@@ -3533,7 +3925,7 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>15.09000015258789</v>
+        <v>15.10999965667725</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>22</v>
@@ -3553,22 +3945,22 @@
         <v>50</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>23.93237667223939</v>
+        <v>23.97503582866533</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>0.0323432829789085</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.3495804430746287</v>
+        <v>0.352179765116708</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>-0.2134941824307819</v>
+        <v>-0.2122178608022866</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>11.84101404462542</v>
+        <v>11.86101354871478</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>19.9634793145316</v>
+        <v>19.98347881862095</v>
       </c>
       <c r="P36" s="5" t="n">
         <v>1.624493053981236</v>
@@ -3588,8 +3980,19 @@
       <c r="U36" s="5" t="inlineStr"/>
       <c r="V36" s="5" t="inlineStr"/>
       <c r="W36" s="5" t="inlineStr"/>
-      <c r="X36" s="5" t="inlineStr"/>
-      <c r="Y36" s="5" t="inlineStr"/>
+      <c r="X36" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y36" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z36" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA36" s="5" t="inlineStr"/>
+      <c r="AB36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3608,7 +4011,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>91.61000061035156</v>
+        <v>91.63009643554688</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>22</v>
@@ -3628,22 +4031,22 @@
         <v>50</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>17.3715982489269</v>
+        <v>17.43425787840226</v>
       </c>
       <c r="K37" s="5" t="n">
         <v>0.0177384274683925</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.7936155602489158</v>
+        <v>0.7983897383411729</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>-0.7695728806434405</v>
+        <v>-0.7682904120269969</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>84.88464300973075</v>
+        <v>84.90473883492606</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>100.577144077846</v>
+        <v>100.5972399030413</v>
       </c>
       <c r="P37" s="5" t="n">
         <v>4.48357173374721</v>
@@ -3663,8 +4066,19 @@
       <c r="U37" s="5" t="inlineStr"/>
       <c r="V37" s="5" t="inlineStr"/>
       <c r="W37" s="5" t="inlineStr"/>
-      <c r="X37" s="5" t="inlineStr"/>
-      <c r="Y37" s="5" t="inlineStr"/>
+      <c r="X37" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y37" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z37" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA37" s="5" t="inlineStr"/>
+      <c r="AB37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3683,7 +4097,7 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>8.564999580383301</v>
+        <v>8.569999694824219</v>
       </c>
       <c r="E38" s="5" t="n">
         <v>22</v>
@@ -3703,22 +4117,22 @@
         <v>50</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>20.61458650817841</v>
+        <v>20.71610473444554</v>
       </c>
       <c r="K38" s="5" t="n">
         <v>0.0299401183926648</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.4909641662446321</v>
+        <v>0.4944922542698931</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>-0.1164949817796282</v>
+        <v>-0.1161758861571882</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>7.217857360839844</v>
+        <v>7.222857475280762</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>10.58571290969849</v>
+        <v>10.5907130241394</v>
       </c>
       <c r="P38" s="5" t="n">
         <v>0.6735711097717285</v>
@@ -3738,8 +4152,19 @@
       <c r="U38" s="5" t="inlineStr"/>
       <c r="V38" s="5" t="inlineStr"/>
       <c r="W38" s="5" t="inlineStr"/>
-      <c r="X38" s="5" t="inlineStr"/>
-      <c r="Y38" s="5" t="inlineStr"/>
+      <c r="X38" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y38" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z38" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA38" s="5" t="inlineStr"/>
+      <c r="AB38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3758,7 +4183,7 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>45.86000061035156</v>
+        <v>46.04000091552734</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>22</v>
@@ -3778,22 +4203,22 @@
         <v>50</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>23.24043212585009</v>
+        <v>23.88758665037871</v>
       </c>
       <c r="K39" s="5" t="n">
         <v>0.0251036384349932</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.3113981236054748</v>
+        <v>0.3141818906065142</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>-0.348812975018494</v>
+        <v>-0.3373257760557111</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>38.97325733729771</v>
+        <v>39.15325764247349</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>56.19011551993233</v>
+        <v>56.37011582510812</v>
       </c>
       <c r="P39" s="5" t="n">
         <v>3.443371636526925</v>
@@ -3813,8 +4238,19 @@
       <c r="U39" s="5" t="inlineStr"/>
       <c r="V39" s="5" t="inlineStr"/>
       <c r="W39" s="5" t="inlineStr"/>
-      <c r="X39" s="5" t="inlineStr"/>
-      <c r="Y39" s="5" t="inlineStr"/>
+      <c r="X39" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y39" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z39" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA39" s="5" t="inlineStr"/>
+      <c r="AB39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3833,7 +4269,7 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>7.735000133514404</v>
+        <v>7.744999885559082</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>22</v>
@@ -3853,22 +4289,22 @@
         <v>50</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>26.64093014772622</v>
+        <v>26.82926709831341</v>
       </c>
       <c r="K40" s="5" t="n">
         <v>0.0100267124430337</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0.842033201074178</v>
+        <v>0.8577808744897341</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>-0.1049176983411601</v>
+        <v>-0.1042795375269125</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>6.619571549551828</v>
+        <v>6.629571301596505</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>9.40814300945827</v>
+        <v>9.418142761502947</v>
       </c>
       <c r="P40" s="5" t="n">
         <v>0.5577142919812884</v>
@@ -3888,8 +4324,19 @@
       <c r="U40" s="5" t="inlineStr"/>
       <c r="V40" s="5" t="inlineStr"/>
       <c r="W40" s="5" t="inlineStr"/>
-      <c r="X40" s="5" t="inlineStr"/>
-      <c r="Y40" s="5" t="inlineStr"/>
+      <c r="X40" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y40" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z40" s="5" t="inlineStr">
+        <is>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA40" s="5" t="inlineStr"/>
+      <c r="AB40" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3908,7 +4355,7 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -3970,19 +4417,19 @@
         <v>15.06915790595363</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>16.8799991607666</v>
+        <v>16.8700008392334</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>12.60302802300743</v>
+        <v>12.59556302699257</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>11.251008816</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.35201920700743</v>
+        <v>1.34455421099257</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.1201687092347426</v>
+        <v>0.1195052135307623</v>
       </c>
     </row>
     <row r="3">
@@ -3998,19 +4445,19 @@
         <v>366.8202462424581</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>358.3150024414062</v>
+        <v>358.5450134277344</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.94041995140197</v>
+        <v>18.95257826083588</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>19.3900045021</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.4495845506980203</v>
+        <v>-0.4374262412641201</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.0231864077519594</v>
+        <v>-0.0225593676998241</v>
       </c>
     </row>
     <row r="4">
@@ -4026,19 +4473,19 @@
         <v>18.39862725025694</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>18.69009971618652</v>
+        <v>18.69499969482422</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>11.42924829279423</v>
+        <v>11.43224469588089</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>11.251008945</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.1782393477942285</v>
+        <v>0.1812357508808908</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.0158420768008933</v>
+        <v>0.016108399857013</v>
       </c>
     </row>
     <row r="5">
@@ -4054,19 +4501,19 @@
         <v>413.4345674446258</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>395.3999938964844</v>
+        <v>395.7807922363281</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.76022168790192</v>
+        <v>10.77058454733124</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>11.2510057355</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.4907840475980833</v>
+        <v>-0.4804211881687621</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.0436213489830091</v>
+        <v>-0.0427002882642661</v>
       </c>
     </row>
   </sheetData>
@@ -4270,7 +4717,7 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
@@ -4394,46 +4841,46 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>371.7000122070313</v>
+        <v>369.7999877929688</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>332.0097994995117</v>
+        <v>331.9717990112305</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>201.2555001449585</v>
+        <v>201.2460000228882</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>46.43119251769661</v>
+        <v>46.14272736888983</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.0123928050828994</v>
+        <v>0.0072177419053192</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.178780767343545</v>
+        <v>1.167643461680674</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>1.153908538166158</v>
+        <v>1.14289837224264</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>15.03442616070743</v>
+        <v>14.88285726158</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>26.10788259908713</v>
+        <v>26.07756881926165</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-11.07345643837971</v>
+        <v>-11.19471155768165</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>-10.00415359792669</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>1688701</v>
+        <v>1710040</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>6120690.02</v>
+        <v>6121116.8</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>0.2759004286252026</v>
+        <v>0.2793673206823957</v>
       </c>
       <c r="P2" s="6" t="n">
         <v>0.082723417254077</v>
@@ -4447,7 +4894,7 @@
         <v>46.42792184012277</v>
       </c>
       <c r="S2" s="6" t="n">
-        <v>0.1249069688334127</v>
+        <v>0.1255487381630615</v>
       </c>
       <c r="T2" s="6" t="inlineStr">
         <is>
@@ -4462,46 +4909,46 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>554.8200073242188</v>
+        <v>554.9249877929688</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>489.8478002929688</v>
+        <v>489.8498999023437</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>291.5008997344971</v>
+        <v>291.5014246368408</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>55.78533584693042</v>
+        <v>55.80068861027303</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.0845436585037897</v>
+        <v>0.08474887082516711</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.175167567306291</v>
+        <v>1.175579142425809</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1.671385241476634</v>
+        <v>1.671890708603197</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>17.31937937496286</v>
+        <v>17.32775388529046</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>19.951779474093</v>
+        <v>19.95345437615852</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-2.632400099130137</v>
+        <v>-2.625700490868056</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>-3.577422784539042</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>14771046</v>
+        <v>14857813</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>33866888.92</v>
+        <v>33868624.26</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.4361500707930983</v>
+        <v>0.4386895932335694</v>
       </c>
       <c r="P3" s="6" t="n">
         <v>0.0624019610194614</v>
@@ -4515,7 +4962,7 @@
         <v>38.05143519810268</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0.06858338685660741</v>
+        <v>0.06857041228119801</v>
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
@@ -4530,46 +4977,46 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>246.4550018310547</v>
+        <v>246.5249938964844</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>253.3478997802735</v>
+        <v>253.349299621582</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>233.5974250030518</v>
+        <v>233.5977749633789</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>65.31827411205957</v>
+        <v>65.43192876681358</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0331377014385605</v>
+        <v>0.0334311077036382</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.0103003871070526</v>
+        <v>-0.0100193170555353</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-6.085685711909594e-05</v>
+        <v>0.0002231211729983</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.7364445279530969</v>
+        <v>-0.7308611153262063</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-2.411762750660824</v>
+        <v>-2.410646068135446</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>1.675318222707727</v>
+        <v>1.67978495280924</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>1.780135958077288</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>14801029</v>
+        <v>14999948</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>48712228.58</v>
+        <v>48716206.96</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.303846270874105</v>
+        <v>0.3079046776428261</v>
       </c>
       <c r="P4" s="6" t="n">
         <v>-0.0071974396379796</v>
@@ -4583,7 +5030,7 @@
         <v>7.47785404750279</v>
       </c>
       <c r="S4" s="6" t="n">
-        <v>0.0303416607167456</v>
+        <v>0.0303330462737694</v>
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
@@ -4598,46 +5045,46 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>182.0500030517578</v>
+        <v>181.9550018310547</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>160.782399597168</v>
+        <v>160.7804995727539</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>144.330549659729</v>
+        <v>144.3300746536255</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>62.17642691523031</v>
+        <v>62.13229147846583</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.1152290916786416</v>
+        <v>0.114647119015653</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.1793095083896159</v>
+        <v>0.1786940959149896</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.475044609890173</v>
+        <v>0.4742748706087554</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5.969701288616506</v>
+        <v>5.962122843660154</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.398519170203713</v>
+        <v>4.397003481212443</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>1.571182118412793</v>
+        <v>1.565119362447711</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>1.773262942271622</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>3536301</v>
+        <v>3584682</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>10344782.02</v>
+        <v>10345749.64</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.3418439357313785</v>
+        <v>0.3464883768441935</v>
       </c>
       <c r="P5" s="6" t="n">
         <v>0.0151807899125376</v>
@@ -4651,7 +5098,7 @@
         <v>10.46220506940569</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>0.0574688541281223</v>
+        <v>0.057498859410965</v>
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
@@ -4666,46 +5113,46 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>284.6789855957031</v>
+        <v>284.6000061035156</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>312.6289779663086</v>
+        <v>312.6273983764648</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>182.8290198898316</v>
+        <v>182.8286249923706</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>28.66453145202405</v>
+        <v>28.65271378907748</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-0.2524382568188729</v>
+        <v>-0.2526456555024522</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.7657795772249751</v>
+        <v>0.7652896907866331</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1.561444908755489</v>
+        <v>1.560734278085872</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-7.875689352418533</v>
+        <v>-7.881989710769687</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>2.001141850303332</v>
+        <v>1.9998817786331</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-9.876831202721863</v>
+        <v>-9.881871489402789</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>-9.368367243321137</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>6137776</v>
+        <v>6173868</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>11185229.52</v>
+        <v>11185951.36</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.5487393878708714</v>
+        <v>0.5519305243966304</v>
       </c>
       <c r="P6" s="6" t="n">
         <v>0.0376936349020097</v>
@@ -4719,7 +5166,7 @@
         <v>29.38128662109375</v>
       </c>
       <c r="S6" s="6" t="n">
-        <v>0.1032084843200214</v>
+        <v>0.1032371257589049</v>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
@@ -4734,46 +5181,46 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>69.59999847412109</v>
+        <v>69.66000366210938</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>86.04520011901856</v>
+        <v>86.04640022277832</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>83.07104984283447</v>
+        <v>83.07134986877442</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>47.04179037230127</v>
+        <v>47.09922336809468</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.1554423567375484</v>
+        <v>-0.1547142268343596</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.2141808884053962</v>
+        <v>-0.2135033995469223</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.2926110488273499</v>
+        <v>-0.2920011780238076</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-4.778690769489572</v>
+        <v>-4.773904030846637</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-4.027398187621336</v>
+        <v>-4.026440839892749</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>-0.7512925818682357</v>
+        <v>-0.747463190953888</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>-0.7205249641778009</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>6710322</v>
+        <v>6735554</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>23138412.44</v>
+        <v>23138917.08</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.2900078826669925</v>
+        <v>0.291092015097882</v>
       </c>
       <c r="P7" s="6" t="n">
         <v>0.0334417645102432</v>
@@ -4787,7 +5234,7 @@
         <v>6.955285753522601</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>0.09993226876447039</v>
+        <v>0.0998461870208863</v>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
@@ -4802,46 +5249,46 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>392.8800048828125</v>
+        <v>393.3099060058594</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>405.5314007568359</v>
+        <v>405.5399987792969</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>362.9399002075195</v>
+        <v>362.9420497131348</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>55.22621319204223</v>
+        <v>55.3837022728646</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0282932377610591</v>
+        <v>0.0294184271630162</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.0317768951686163</v>
+        <v>0.0329058964933317</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.1154709247733578</v>
+        <v>0.1166915066236082</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-3.510586442242413</v>
+        <v>-3.476292335560629</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-6.731206255979107</v>
+        <v>-6.72434743464275</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>3.220619813736693</v>
+        <v>3.248055099082121</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>3.038872772970159</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>10081161</v>
+        <v>10158458</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>27437235.22</v>
+        <v>27438781.16</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3674262701458883</v>
+        <v>0.3702226400205015</v>
       </c>
       <c r="P8" s="6" t="n">
         <v>0.030087289573326</v>
@@ -4855,7 +5302,7 @@
         <v>15.00356619698661</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>0.0381886734130484</v>
+        <v>0.038146931892336</v>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
@@ -4870,46 +5317,46 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>7.670000076293945</v>
+        <v>7.675000190734863</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>5.82199999332428</v>
+        <v>5.822099995613098</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4.045199999809265</v>
+        <v>4.045225000381469</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>50</v>
+        <v>50.04831028267274</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.3844765576006379</v>
+        <v>0.3853791053398705</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.7274774723979485</v>
+        <v>0.7286036242845428</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.7962529532915108</v>
+        <v>0.797423940285247</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.6084837127440696</v>
+        <v>0.6088825822721207</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.7317052179704936</v>
+        <v>0.7317849918761038</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-0.1232215052264239</v>
+        <v>-0.1229024096039831</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>-0.0949479297406228</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>3744943</v>
+        <v>3766833</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>7813534.86</v>
+        <v>7813972.66</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4792892163534802</v>
+        <v>0.4820637547508388</v>
       </c>
       <c r="P9" s="6" t="n">
         <v>-0.0049382666628676</v>
@@ -4923,7 +5370,7 @@
         <v>0.7386070660182408</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>0.09629818235609811</v>
+        <v>0.0962354459495486</v>
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
@@ -4938,46 +5385,46 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>16.8799991607666</v>
+        <v>16.8700008392334</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>9.903000011444092</v>
+        <v>9.902800045013429</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.552449985742569</v>
+        <v>6.552399994134903</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>74.57627042542499</v>
+        <v>74.5523124039135</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1.131313004818223</v>
+        <v>1.130050590495383</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>3.715083664943837</v>
+        <v>3.712290837640407</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>2.277669679258964</v>
+        <v>2.275728257637982</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>2.333764763463373</v>
+        <v>2.332967176560441</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>2.205843682484746</v>
+        <v>2.205684165104159</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1279210809786271</v>
+        <v>0.1272830114562815</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>0.2137816411175577</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>801304</v>
+        <v>807265</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>3924280.08</v>
+        <v>3924399.3</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.2041913379434426</v>
+        <v>0.2057040933627727</v>
       </c>
       <c r="P10" s="6" t="n">
         <v>0.0098826338563442</v>
@@ -4991,7 +5438,7 @@
         <v>1.499500070299421</v>
       </c>
       <c r="S10" s="6" t="n">
-        <v>0.0888329469698458</v>
+        <v>0.0888855954773954</v>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
@@ -5006,46 +5453,46 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>275.4800109863281</v>
+        <v>276.0199890136719</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>300.9968014526367</v>
+        <v>301.0076010131836</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>276.0421009063721</v>
+        <v>276.0448007965088</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>61.14814244093061</v>
+        <v>61.55851569211629</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.0658844814841987</v>
+        <v>-0.0640534889080283</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.0840232386157003</v>
+        <v>-0.0822278004532938</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.0436034765783919</v>
+        <v>0.0456490803396021</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-6.667593425464077</v>
+        <v>-6.624518255191617</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-12.53550884642297</v>
+        <v>-12.52689381236847</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>5.867915420958891</v>
+        <v>5.902375557176857</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>5.61249043240821</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>318989</v>
+        <v>323752</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>1552087.78</v>
+        <v>1552183.04</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.2055225252788215</v>
+        <v>0.2085784934230437</v>
       </c>
       <c r="P11" s="6" t="n">
         <v>-0.0092015237095138</v>
@@ -5059,7 +5506,7 @@
         <v>11.86785343715123</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>0.0430806336716032</v>
+        <v>0.0429963550087794</v>
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
@@ -5074,46 +5521,46 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>104.8600006103516</v>
+        <v>104.9599990844727</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>112.2729997253418</v>
+        <v>112.2749996948242</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>101.2299499320984</v>
+        <v>101.230449924469</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>64.98261344099689</v>
+        <v>65.05409098398465</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.1841896894013712</v>
+        <v>0.1853189776077493</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.1323127684374249</v>
+        <v>-0.1314853089803814</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.0033489471530663</v>
+        <v>0.0043057787680036</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.6672858586099579</v>
+        <v>0.6752629448646275</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.7672677601444363</v>
+        <v>-0.7656723428935024</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>1.434553618754394</v>
+        <v>1.44093528775813</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>1.911196160245703</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>554821</v>
+        <v>562461</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>1509064.42</v>
+        <v>1509217.22</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.3676589234010302</v>
+        <v>0.3726839268372514</v>
       </c>
       <c r="P12" s="6" t="n">
         <v>0</v>
@@ -5127,7 +5574,7 @@
         <v>5.971429007393973</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>0.0569466810283852</v>
+        <v>0.0568924262526728</v>
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
@@ -5142,46 +5589,46 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>239.6999969482422</v>
+        <v>238.6300964355469</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>227.4351998901367</v>
+        <v>227.4138018798828</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>161.8396501922607</v>
+        <v>161.8343006896973</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>41.5707735141641</v>
+        <v>41.24271373225548</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.0442964822714296</v>
+        <v>-0.0485622632335516</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.5026328393198476</v>
+        <v>0.495925840297531</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.5358492067620082</v>
+        <v>0.5289939465423255</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.457086675416463</v>
+        <v>5.371738486369566</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>10.0608063474832</v>
+        <v>10.04373670967382</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>-4.603719672066736</v>
+        <v>-4.671998223304254</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>-4.078359216969876</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>2341768</v>
+        <v>2375619</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>8663237.359999999</v>
+        <v>8663914.380000001</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2703109591354888</v>
+        <v>0.2741969617663742</v>
       </c>
       <c r="P13" s="6" t="n">
         <v>0.06596166699561611</v>
@@ -5195,7 +5642,7 @@
         <v>26.78535788399833</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>0.1117453409470923</v>
+        <v>0.1122463523423708</v>
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
@@ -5210,46 +5657,46 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>358.3150024414062</v>
+        <v>358.5450134277344</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>372.2675006103516</v>
+        <v>372.2721008300781</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>319.9711748504639</v>
+        <v>319.9723249053955</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>59.93802393421079</v>
+        <v>60.08777128483414</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.0037950129619953</v>
+        <v>-0.0031555251088707</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.0763119116272694</v>
+        <v>0.077002822034881</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.07971740570595789</v>
+        <v>0.080410502181824</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-2.024739069103475</v>
+        <v>-2.006390614353677</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-2.645989984175904</v>
+        <v>-2.642320293225944</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.6212509150724284</v>
+        <v>0.6359296788722668</v>
       </c>
       <c r="L14" s="6" t="n">
         <v>0.5974640052565006</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>8365326</v>
+        <v>8529115</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>31758776.52</v>
+        <v>31762052.3</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.2634020235235434</v>
+        <v>0.2685316087084209</v>
       </c>
       <c r="P14" s="6" t="n">
         <v>-0.0040282924977889</v>
@@ -5263,7 +5710,7 @@
         <v>9.963572910853795</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>0.027806742232299</v>
+        <v>0.0277889038690032</v>
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
@@ -5278,46 +5725,46 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>107.254997253418</v>
+        <v>107.375</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>117.4262997436524</v>
+        <v>117.428699798584</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>63.21427495956421</v>
+        <v>63.21487497329712</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>31.22796125679511</v>
+        <v>31.35155293469214</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.1389981735877428</v>
+        <v>-0.1380348377374095</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.6808493174286585</v>
+        <v>0.6827299434120371</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1.434294006137628</v>
+        <v>1.437017627173527</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-2.019237047322904</v>
+        <v>-2.0096641786497</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>1.40613065726318</v>
+        <v>1.408045230997821</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-3.425367704586084</v>
+        <v>-3.417709409647521</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>-3.642499733942029</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>57579114</v>
+        <v>57992221</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>129984342.28</v>
+        <v>129992604.42</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.4429696145707189</v>
+        <v>0.4461193870124323</v>
       </c>
       <c r="P15" s="6" t="n">
         <v>0.0469355722360184</v>
@@ -5331,7 +5778,7 @@
         <v>9.479286193847656</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>0.0883808348011082</v>
+        <v>0.0882820600125509</v>
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
@@ -5346,46 +5793,46 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>39.2599983215332</v>
+        <v>39.22909927368164</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>54.90060012817383</v>
+        <v>54.8999821472168</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>48.68895003318787</v>
+        <v>48.68879553794861</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>17.37451029198574</v>
+        <v>17.28480087008961</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-0.3213483257204239</v>
+        <v>-0.3218824492928798</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.0978747249518869</v>
+        <v>0.0970106575776734</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.2294406725487126</v>
+        <v>-0.2300471307899073</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-4.178613585850314</v>
+        <v>-4.181078467160411</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-2.739296848873526</v>
+        <v>-2.739789825135545</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-1.439316736976789</v>
+        <v>-1.441288642024866</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>-1.449196603544823</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>9952777</v>
+        <v>10044903</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>28828661.54</v>
+        <v>28830504.06</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.3452389555509</v>
+        <v>0.3484123267180921</v>
       </c>
       <c r="P16" s="6" t="n">
         <v>0.0298353862022756</v>
@@ -5399,7 +5846,7 @@
         <v>3.701071330479213</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>0.0942707969615286</v>
+        <v>0.0943450499502602</v>
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
@@ -5447,13 +5894,13 @@
         <v>-0.0068890358413925</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>651707</v>
+        <v>660169</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1050756.14</v>
+        <v>1050925.38</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.6202266874214982</v>
+        <v>0.6281787580389391</v>
       </c>
       <c r="P17" s="6" t="n">
         <v>0.018661516252568</v>
@@ -5482,46 +5929,46 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1156.650024414062</v>
+        <v>1157.2099609375</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1097.808602294922</v>
+        <v>1097.819801025391</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1000.576053161621</v>
+        <v>1000.578852844238</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>57.90061457309466</v>
+        <v>58.0041452805042</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.0208738079559245</v>
+        <v>0.0213680149492496</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.2538211646764905</v>
+        <v>0.2544281419376692</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.0699815211970975</v>
+        <v>0.0704995013297873</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>27.79359099238536</v>
+        <v>27.83825829340026</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>34.64561104131542</v>
+        <v>34.6545445015184</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-6.852020048930058</v>
+        <v>-6.816286208118143</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>-3.468572913063639</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>1296300</v>
+        <v>1303164</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>3185826</v>
+        <v>3185963.28</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.4068960451700752</v>
+        <v>0.4090329628657867</v>
       </c>
       <c r="P18" s="6" t="n">
         <v>-0.013419399271567</v>
@@ -5535,7 +5982,7 @@
         <v>41.49965122767857</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>0.035879177237472</v>
+        <v>0.0358618164624664</v>
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
@@ -5550,46 +5997,46 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>15.09000015258789</v>
+        <v>15.10999965667725</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>27.45520004272461</v>
+        <v>27.4556000328064</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>19.02107503414154</v>
+        <v>19.02117503166198</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>23.93237667223939</v>
+        <v>23.97503582866533</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.4331329948589719</v>
+        <v>-0.4323816987110064</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.3624841527693582</v>
+        <v>-0.361639222307808</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.2140625232830634</v>
+        <v>-0.2130208824864672</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-3.4081556807919</v>
+        <v>-3.406560278756281</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-3.194661498361118</v>
+        <v>-3.194342417953994</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.2134941824307819</v>
+        <v>-0.2122178608022866</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>-0.2400474448421516</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>4987252</v>
+        <v>5024598</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>14266393.04</v>
+        <v>14267139.96</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.3495804430746287</v>
+        <v>0.352179765116708</v>
       </c>
       <c r="P19" s="6" t="n">
         <v>0.0323432829789085</v>
@@ -5603,7 +6050,7 @@
         <v>1.624493053981236</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.1076536141520608</v>
+        <v>0.1075111244799637</v>
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
@@ -5618,46 +6065,46 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>223.2400054931641</v>
+        <v>223.2899932861328</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>233.8506002807617</v>
+        <v>233.8516000366211</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>128.1954502105713</v>
+        <v>128.1957001495361</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>33.74884357057235</v>
+        <v>33.76812818833493</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.2018591499812879</v>
+        <v>-0.201680430672074</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.6680863964642205</v>
+        <v>0.668459913555193</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>1.693207951947976</v>
+        <v>1.693811013756841</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-4.965489741146996</v>
+        <v>-4.961502110938653</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>4.131300354216811</v>
+        <v>4.132097880258479</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-9.096790095363808</v>
+        <v>-9.093599991197133</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>-9.60956168128553</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>12421556</v>
+        <v>12488233</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>45222425.12</v>
+        <v>45223758.66</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.2746769101179065</v>
+        <v>0.2761431904386516</v>
       </c>
       <c r="P20" s="6" t="n">
         <v>0.0645198535414377</v>
@@ -5671,7 +6118,7 @@
         <v>21.60285949707031</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>0.09676966030056749</v>
+        <v>0.0967479965364481</v>
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
@@ -5686,46 +6133,46 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>986.6900024414062</v>
+        <v>982.6099853515624</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>916.8088012695312</v>
+        <v>916.7272009277344</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>472.4614002990722</v>
+        <v>472.4410002136231</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>45.09481845458335</v>
+        <v>44.75504296621285</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.0051751888893269</v>
+        <v>0.0010187345431718</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>1.118906486882573</v>
+        <v>1.110144692745741</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1.852777102295608</v>
+        <v>1.840980713052704</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>9.730162532634949</v>
+        <v>9.404691083872422</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>34.47285079863222</v>
+        <v>34.40775650887971</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-24.74268826599728</v>
+        <v>-25.00306542500729</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>-28.83193491040208</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>21002428</v>
+        <v>21197929</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>53931352.56</v>
+        <v>53935262.58</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.3894289129247086</v>
+        <v>0.3930254157668736</v>
       </c>
       <c r="P21" s="6" t="n">
         <v>0.0543756800501934</v>
@@ -5739,7 +6186,7 @@
         <v>89.7650146484375</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>0.090975903704637</v>
+        <v>0.09135365606560671</v>
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
@@ -5754,46 +6201,46 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>195.6199951171875</v>
+        <v>195.7400054931641</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>224.0189999389648</v>
+        <v>224.0214001464844</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>136.7465754318237</v>
+        <v>136.7471754837036</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>30.17674820438588</v>
+        <v>30.19478996682716</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-0.1581167386669705</v>
+        <v>-0.1576002540066962</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.2079782151909468</v>
+        <v>0.2087192944435545</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.8226031098472144</v>
+        <v>0.8237212536460516</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-6.531008743388725</v>
+        <v>-6.521435266102856</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.4660696362119878</v>
+        <v>0.4679843316691616</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-6.997078379600713</v>
+        <v>-6.989419597772017</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>-6.66147091221397</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>11812291</v>
+        <v>11903657</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>17933503.82</v>
+        <v>17935331.14</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6586716750145929</v>
+        <v>0.6636987578920163</v>
       </c>
       <c r="P22" s="6" t="n">
         <v>0.0310198990532244</v>
@@ -5807,7 +6254,7 @@
         <v>25.56014360700335</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>0.1306622239290588</v>
+        <v>0.1305821134652824</v>
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
@@ -5822,46 +6269,46 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>210.6649932861328</v>
+        <v>211.0950012207031</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>209.3065002441406</v>
+        <v>209.315100402832</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>191.9644254302979</v>
+        <v>191.9665754699707</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>59.89200508010831</v>
+        <v>60.21059301407551</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.0266825419347123</v>
+        <v>0.028778199274027</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.0720319534628273</v>
+        <v>0.07422017770887369</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.1390991159572245</v>
+        <v>0.141424237233821</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.6771988701766531</v>
+        <v>-0.6428962429174874</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-2.276778305307872</v>
+        <v>-2.269917779856038</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1.599579435131218</v>
+        <v>1.627021536938551</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>1.206196025562167</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>69664661</v>
+        <v>70491184</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>157780057.22</v>
+        <v>157796587.68</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.4415302049413213</v>
+        <v>0.4467218527117392</v>
       </c>
       <c r="P23" s="6" t="n">
         <v>0.0229450115312453</v>
@@ -5875,7 +6322,7 @@
         <v>6.875713893345424</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>0.0326381416584319</v>
+        <v>0.0325716566170923</v>
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
@@ -5890,46 +6337,46 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>91.61000061035156</v>
+        <v>91.63009643554688</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>106.6387994384766</v>
+        <v>106.6392013549805</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>104.4497496795654</v>
+        <v>104.4498501586914</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>17.3715982489269</v>
+        <v>17.43425787840226</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>-0.0926109207498903</v>
+        <v>-0.0924118733511427</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.2106668745697536</v>
+        <v>-0.210493724254244</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.1655888528424689</v>
+        <v>-0.1654058140864097</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-4.112526871587747</v>
+        <v>-4.110923785817192</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-3.342953990944306</v>
+        <v>-3.342633373790195</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.7695728806434405</v>
+        <v>-0.7682904120269969</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>-0.7934742332941171</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>2583527</v>
+        <v>2599321</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3255388.54</v>
+        <v>3255704.42</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.7936155602489158</v>
+        <v>0.7983897383411729</v>
       </c>
       <c r="P24" s="6" t="n">
         <v>0.0177384274683925</v>
@@ -5943,7 +6390,7 @@
         <v>4.48357173374721</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>0.0489419463363761</v>
+        <v>0.048931212649121</v>
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
@@ -5958,46 +6405,46 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>25.67000007629395</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>35.87680007934571</v>
+        <v>35.87940006256103</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>25.36909998416901</v>
+        <v>25.36974997997284</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>41.34382605723892</v>
+        <v>41.6717492429667</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.1759229409099713</v>
+        <v>-0.1717496130653933</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.2434423859295348</v>
+        <v>-0.239610993073733</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.0090408623194964</v>
+        <v>0.0141508921165698</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-2.452062917496278</v>
+        <v>-2.441692614073304</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-2.397204211740594</v>
+        <v>-2.395130151055999</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.0548587057556839</v>
+        <v>-0.0465624630173051</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>-0.0149246408257801</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>2754942</v>
+        <v>2822304</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>13303652.84</v>
+        <v>13305000.08</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.2070816213511476</v>
+        <v>0.2121235612950105</v>
       </c>
       <c r="P25" s="6" t="n">
         <v>0.0084746235925221</v>
@@ -6011,7 +6458,7 @@
         <v>2.376357078552246</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>0.09257331793881809</v>
+        <v>0.0921068662334964</v>
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
@@ -6026,46 +6473,46 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>13.72999954223633</v>
+        <v>13.72000026702881</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>11.47280002593994</v>
+        <v>11.47260004043579</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>9.128375008106232</v>
+        <v>9.128325011730194</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>75.22726711162801</v>
+        <v>75.17084129057541</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.2096915489670152</v>
+        <v>0.2088105555862711</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.5620022300138776</v>
+        <v>0.5608646560376644</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.6002330611100726</v>
+        <v>0.5990676444088565</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.6794169924334295</v>
+        <v>0.6786193294539125</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.6466647847539466</v>
+        <v>0.6465052521580432</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.0327522076794828</v>
+        <v>0.0321140772958692</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>0.042571941463545</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>154245</v>
+        <v>156045</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>663226.9</v>
+        <v>663262.9</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.2325674667297119</v>
+        <v>0.235268699636298</v>
       </c>
       <c r="P26" s="6" t="n">
         <v>-0.0110537672736636</v>
@@ -6079,7 +6526,7 @@
         <v>0.6038284982953753</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>0.0439787704608345</v>
+        <v>0.0440108226343453</v>
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
@@ -6094,46 +6541,46 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>79.76999664306641</v>
+        <v>79.86000061035156</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>107.0335998535156</v>
+        <v>107.0353999328613</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>77.06840009689331</v>
+        <v>77.06885011672973</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>38.03211555661516</v>
+        <v>38.11896320533445</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-0.2209200398615189</v>
+        <v>-0.2200410090204048</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.1045416130538494</v>
+        <v>0.1057878601566444</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.0924915215208377</v>
+        <v>-0.09146758561955499</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-7.631721769611005</v>
+        <v>-7.624541965952915</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-6.247604396903024</v>
+        <v>-6.246168436171407</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-1.384117372707981</v>
+        <v>-1.378373529781509</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>-1.60128212643402</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>10508638</v>
+        <v>10563231</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>28176464.76</v>
+        <v>28177556.62</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.372958001988891</v>
+        <v>0.3748810140799213</v>
       </c>
       <c r="P27" s="6" t="n">
         <v>0.0264563885114627</v>
@@ -6147,7 +6594,7 @@
         <v>7.732856750488281</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>0.0969394142648546</v>
+        <v>0.0968301614248414</v>
       </c>
       <c r="T27" s="6" t="inlineStr">
         <is>
@@ -6162,46 +6609,46 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>18.69009971618652</v>
+        <v>18.69499969482422</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>16.94940193176269</v>
+        <v>16.94949993133545</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>21.97362552165985</v>
+        <v>21.97365002155304</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>62.96362228035989</v>
+        <v>62.99719808877189</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.1272677805904842</v>
+        <v>0.1275633160947209</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.0435566652942844</v>
+        <v>0.0438302542769444</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.2973646824002849</v>
+        <v>-0.297180472679705</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.4148641979685088</v>
+        <v>0.415255079455278</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.3736153305422402</v>
+        <v>0.373693506839594</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.0412488674262686</v>
+        <v>0.0415615726156839</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>0.0328078631428616</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>55594214</v>
+        <v>57235365</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>76305962.28</v>
+        <v>76338785.3</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.7285697256002156</v>
+        <v>0.7497547252693841</v>
       </c>
       <c r="P28" s="6" t="n">
         <v>0.0044125718372439</v>
@@ -6215,7 +6662,7 @@
         <v>0.9414285932268416</v>
       </c>
       <c r="S28" s="6" t="n">
-        <v>0.0503704425082076</v>
+        <v>0.0503572403634475</v>
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
@@ -6230,46 +6677,46 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>6.409999847412109</v>
+        <v>6.414999961853027</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>5.93439998626709</v>
+        <v>5.934499988555908</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>4.497000005245209</v>
+        <v>4.497025005817413</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>62.49999561730699</v>
+        <v>62.57668446039076</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.2975708042843141</v>
+        <v>0.2985829731877558</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.0545723231484529</v>
+        <v>-0.0538348431652393</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.3965140815514099</v>
+        <v>0.3976034310665943</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.3307068762252978</v>
+        <v>0.3311057457533479</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.3108915948112808</v>
+        <v>0.3109713687168909</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.0198152814140169</v>
+        <v>0.020134377036457</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>0.0646032293833483</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>302245</v>
+        <v>306591</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>1212176.9</v>
+        <v>1212263.82</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2493406696662838</v>
+        <v>0.2529078200156134</v>
       </c>
       <c r="P29" s="6" t="n">
         <v>0.0046656626141934</v>
@@ -6283,7 +6730,7 @@
         <v>0.6430713449205671</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>0.1003231451214764</v>
+        <v>0.1002449491417939</v>
       </c>
       <c r="T29" s="6" t="inlineStr">
         <is>
@@ -6298,46 +6745,46 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>395.3999938964844</v>
+        <v>395.7807922363281</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>409.9109991455078</v>
+        <v>409.9186151123047</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>417.7475</v>
+        <v>417.7494039916992</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>54.10686010531468</v>
+        <v>54.21071674379002</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-0.0271387421648671</v>
+        <v>-0.0262018075224783</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.0856671626680707</v>
+        <v>0.08671273742666601</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.1192979298333598</v>
+        <v>-0.1184497510488548</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-1.357557226626113</v>
+        <v>-1.327180151083041</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-1.263583439462306</v>
+        <v>-1.257508024353691</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.09397378716380771</v>
+        <v>-0.0696721267293503</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>0.3816312784934397</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>15410750</v>
+        <v>15571986</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>48277505</v>
+        <v>48280729.72</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.3192118151093351</v>
+        <v>0.3225300464659174</v>
       </c>
       <c r="P30" s="6" t="n">
         <v>0.0109940121352903</v>
@@ -6351,7 +6798,7 @@
         <v>18.56714085170201</v>
       </c>
       <c r="S30" s="6" t="n">
-        <v>0.0469578683315885</v>
+        <v>0.046912688073592</v>
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
@@ -6366,46 +6813,46 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>422.5</v>
+        <v>422.989990234375</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>425.035400390625</v>
+        <v>425.0452001953125</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>349.7338000488281</v>
+        <v>349.73625</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>45.63563934448866</v>
+        <v>45.80252323519223</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-0.0033731811867222</v>
+        <v>-0.0022173530008412</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.1121640046027405</v>
+        <v>0.1134538259075421</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.2734726286005009</v>
+        <v>0.2749495260011116</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>1.33645379619486</v>
+        <v>1.375541336259005</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>5.408671297613364</v>
+        <v>5.416488805626193</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-4.072217501418504</v>
+        <v>-4.040947469367188</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>-3.711786865119478</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9313232</v>
+        <v>9421048</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>13661668.64</v>
+        <v>13663824.96</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.6817053059486297</v>
+        <v>0.6894883407522808</v>
       </c>
       <c r="P31" s="6" t="n">
         <v>0.0220361706931489</v>
@@ -6419,7 +6866,7 @@
         <v>19.97285679408482</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>0.0472730338321534</v>
+        <v>0.0472182729029073</v>
       </c>
       <c r="T31" s="6" t="inlineStr">
         <is>
@@ -6434,46 +6881,46 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>303.7749938964844</v>
+        <v>303.9100036621094</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>324.2373010253907</v>
+        <v>324.2400012207031</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>238.4754252624512</v>
+        <v>238.4761003112793</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>45.64846508307077</v>
+        <v>45.6853713981408</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.0029880767124081</v>
+        <v>0.0034338447574493</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.0216901731258978</v>
+        <v>-0.0212553730828108</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.7865964599034774</v>
+        <v>0.7873904948772719</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-1.942878575165537</v>
+        <v>-1.932108565372118</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-1.188219567146564</v>
+        <v>-1.18606556518788</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.7546590080189728</v>
+        <v>-0.746043000184238</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>-0.1480541656201379</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>2015025</v>
+        <v>2035475</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>6149798.5</v>
+        <v>6150207.5</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3276570768944706</v>
+        <v>0.3309603781661025</v>
       </c>
       <c r="P32" s="6" t="n">
         <v>0.031582057136426</v>
@@ -6487,7 +6934,7 @@
         <v>21.269287109375</v>
       </c>
       <c r="S32" s="6" t="n">
-        <v>0.0700165831181707</v>
+        <v>0.0699854787702955</v>
       </c>
       <c r="T32" s="6" t="inlineStr">
         <is>
@@ -6502,46 +6949,46 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>883.1300048828125</v>
+        <v>881.9500122070312</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>877.2855969238282</v>
+        <v>877.2619970703125</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>479.5924999237061</v>
+        <v>479.5865999603271</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>38.28450466392492</v>
+        <v>38.17454872190672</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-0.0514585563189684</v>
+        <v>-0.0527259483790617</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.6555376440480138</v>
+        <v>0.6533256001998196</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1.747075944701178</v>
+        <v>1.743405443782129</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-3.620273612546043</v>
+        <v>-3.714404082408805</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>11.30772997159282</v>
+        <v>11.28890387762027</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-14.92800358413886</v>
+        <v>-15.00330796002907</v>
       </c>
       <c r="L33" s="6" t="n">
         <v>-17.58862389405815</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>2119632</v>
+        <v>2140328</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>4341636.64</v>
+        <v>4342050.56</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.4882103629934356</v>
+        <v>0.4929302343268891</v>
       </c>
       <c r="P33" s="6" t="n">
         <v>0.0451049293978258</v>
@@ -6555,7 +7002,7 @@
         <v>84.29928588867188</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>0.0954551259979645</v>
+        <v>0.0955828388478816</v>
       </c>
       <c r="T33" s="6" t="inlineStr">
         <is>
@@ -6570,46 +7017,46 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>27.79500007629395</v>
+        <v>27.80999946594238</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>33.45629981994629</v>
+        <v>33.45659980773926</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>34.37742489814758</v>
+        <v>34.37749989509582</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>27.49490920476378</v>
+        <v>27.58339839891339</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>-0.0874917625830535</v>
+        <v>-0.0869993334924669</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.0218749741421033</v>
+        <v>0.0224264222754753</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.07719125823897641</v>
+        <v>-0.07669327054872049</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-1.885041278107142</v>
+        <v>-1.883844745599575</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-1.848609097076966</v>
+        <v>-1.848369790575453</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.0364321810301755</v>
+        <v>-0.0354749550241217</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>-0.1129581202809464</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>11935377</v>
+        <v>12005690</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>55530711.54</v>
+        <v>55532117.8</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.214932902334642</v>
+        <v>0.2161936276811687</v>
       </c>
       <c r="P34" s="6" t="n">
         <v>0.0112075006381963</v>
@@ -6623,7 +7070,7 @@
         <v>1.774999754769462</v>
       </c>
       <c r="S34" s="6" t="n">
-        <v>0.0638603975498219</v>
+        <v>0.06382595429184459</v>
       </c>
       <c r="T34" s="6" t="inlineStr">
         <is>
@@ -6638,46 +7085,46 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>268.2900085449219</v>
+        <v>268.3299865722656</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>226.105</v>
+        <v>226.1057995605469</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>160.4408002471924</v>
+        <v>160.4410001373291</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>75.85609116382497</v>
+        <v>75.86654638577177</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.1669857140828072</v>
+        <v>0.1671596072033168</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>1.426426781997002</v>
+        <v>1.426788345056187</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1.119696683193505</v>
+        <v>1.120012540248417</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>12.09894213943574</v>
+        <v>12.10213126982214</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>11.57890772792168</v>
+        <v>11.57954555399896</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.5200344115140574</v>
+        <v>0.5225857158231797</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>0.3955764881293149</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>2277530</v>
+        <v>2290189</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>6065846.6</v>
+        <v>6066099.78</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.3754677871346104</v>
+        <v>0.3775389596377526</v>
       </c>
       <c r="P35" s="6" t="n">
         <v>-0.0192129762097973</v>
@@ -6691,7 +7138,7 @@
         <v>13.84728785923549</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v>0.0516131328719121</v>
+        <v>0.0516054431192176</v>
       </c>
       <c r="T35" s="6" t="inlineStr">
         <is>
@@ -6706,7 +7153,7 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>185.9349975585937</v>
+        <v>185.1950073242188</v>
       </c>
       <c r="C36" s="6" t="inlineStr"/>
       <c r="D36" s="6" t="inlineStr"/>
@@ -6715,19 +7162,19 @@
       <c r="G36" s="6" t="inlineStr"/>
       <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" s="6" t="n">
-        <v>0.5368538404126468</v>
+        <v>0.477823280405488</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.07770045698869921</v>
+        <v>-0.089506568990131</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.614554297401346</v>
+        <v>0.567329849395619</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>-0.9253561253561428</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>49039454</v>
+        <v>49507041</v>
       </c>
       <c r="N36" s="6" t="inlineStr"/>
       <c r="O36" s="6" t="inlineStr"/>
@@ -6754,46 +7201,46 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>8.564999580383301</v>
+        <v>8.569999694824219</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>10.93830001831055</v>
+        <v>10.93840002059936</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>18.45027497291565</v>
+        <v>18.45029997348785</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>20.61458650817841</v>
+        <v>20.71610473444554</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-0.1339737833107386</v>
+        <v>-0.1334682105840102</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.1643902848406535</v>
+        <v>-0.1639024687976371</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.5656693773522072</v>
+        <v>-0.5654158218443462</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.6488859888733618</v>
+        <v>-0.6484871193453117</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.5323910070937335</v>
+        <v>-0.5323112331881235</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.1164949817796282</v>
+        <v>-0.1161758861571882</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>-0.1257283657885731</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>16231048</v>
+        <v>16348850</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>33059536.96</v>
+        <v>33061893</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.4909641662446321</v>
+        <v>0.4944922542698931</v>
       </c>
       <c r="P37" s="6" t="n">
         <v>0.0299401183926648</v>
@@ -6807,7 +7254,7 @@
         <v>0.6735711097717285</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>0.0786422817012659</v>
+        <v>0.07859639833809159</v>
       </c>
       <c r="T37" s="6" t="inlineStr">
         <is>
@@ -6822,46 +7269,46 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>45.86000061035156</v>
+        <v>46.04000091552734</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>60.62179985046387</v>
+        <v>60.62539985656738</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>81.45749980926513</v>
+        <v>81.45839981079102</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>23.24043212585009</v>
+        <v>23.88758665037871</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-0.2022960641601671</v>
+        <v>-0.1991650796425027</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.2171389693258757</v>
+        <v>-0.214066243147155</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.5525853598990091</v>
+        <v>-0.5508292593607089</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-3.830179072280572</v>
+        <v>-3.815820073577093</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-3.481366097262078</v>
+        <v>-3.478494297521382</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.348812975018494</v>
+        <v>-0.3373257760557111</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>-0.3462640816307631</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>3854113</v>
+        <v>3888785</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>12376802.26</v>
+        <v>12377495.7</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.3113981236054748</v>
+        <v>0.3141818906065142</v>
       </c>
       <c r="P38" s="6" t="n">
         <v>0.0251036384349932</v>
@@ -6875,7 +7322,7 @@
         <v>3.443371636526925</v>
       </c>
       <c r="S38" s="6" t="n">
-        <v>0.0750844219515706</v>
+        <v>0.0747908681158523</v>
       </c>
       <c r="T38" s="6" t="inlineStr">
         <is>
@@ -6890,46 +7337,46 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>7.735000133514404</v>
+        <v>7.744999885559082</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>9.765699996948245</v>
+        <v>9.765899991989135</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>12.02972501516342</v>
+        <v>12.02977501392364</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>26.64093014772622</v>
+        <v>26.82926709831341</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>-0.154644758907996</v>
+        <v>-0.1535518897865124</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.121022731151955</v>
+        <v>-0.119886395716962</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.4980531985655153</v>
+        <v>-0.4974042853829266</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.5930955829841373</v>
+        <v>-0.5922978819663278</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.4881778846429772</v>
+        <v>-0.4880183444394153</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.1049176983411601</v>
+        <v>-0.1042795375269125</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>-0.1257187896488844</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>31379033</v>
+        <v>31976126</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>37265790.66</v>
+        <v>37277732.52</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.842033201074178</v>
+        <v>0.8577808744897341</v>
       </c>
       <c r="P39" s="6" t="n">
         <v>0.0100267124430337</v>
@@ -6943,7 +7390,7 @@
         <v>0.5577142919812884</v>
       </c>
       <c r="S39" s="6" t="n">
-        <v>0.0721026867943815</v>
+        <v>0.0720095933146717</v>
       </c>
       <c r="T39" s="6" t="inlineStr">
         <is>
@@ -6991,13 +7438,13 @@
         <v>0.0561779742976243</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>20269023</v>
+        <v>20502401</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>28649648.46</v>
+        <v>28654316.02</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.7074789426578535</v>
+        <v>0.7155083019845888</v>
       </c>
       <c r="P40" s="6" t="n">
         <v>-0.0154083063419491</v>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -473,7 +473,7 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>369.7999877929688</v>
+        <v>370.9100036621094</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.082723417254077</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.2793673206823957</v>
+        <v>0.2825782202322912</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>75</v>
@@ -573,13 +573,13 @@
         <v>12</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.0324499740295236</v>
+        <v>0.0323528615608106</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>276.9441441127233</v>
+        <v>278.0541599818638</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>509.0837533133371</v>
+        <v>510.1937691824777</v>
       </c>
     </row>
     <row r="3">
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>982.6099853515624</v>
+        <v>985.6799926757812</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.0543756800501934</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.3930254157668736</v>
+        <v>0.3954902609149611</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>75</v>
@@ -614,13 +614,13 @@
         <v>12</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.0122123733514743</v>
+        <v>0.0121743365891237</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>803.0799560546874</v>
+        <v>806.1499633789062</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1251.905029296875</v>
+        <v>1254.975036621094</v>
       </c>
     </row>
     <row r="4">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>238.6300964355469</v>
+        <v>239.8249969482422</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.06596166699561611</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.2741969617663742</v>
+        <v>0.2759027722730133</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>75</v>
@@ -655,13 +655,13 @@
         <v>12</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.0502870349517759</v>
+        <v>0.0500364855736442</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>185.0593806675502</v>
+        <v>186.2542811802456</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>318.9861700875418</v>
+        <v>320.1810706002371</v>
       </c>
     </row>
   </sheetData>
@@ -675,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB40"/>
+  <dimension ref="A1:AD40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -704,8 +704,10 @@
     <col width="16" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="35" customWidth="1" min="27" max="27"/>
-    <col width="23" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="35" customWidth="1" min="28" max="28"/>
+    <col width="35" customWidth="1" min="29" max="29"/>
+    <col width="35" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -841,10 +843,20 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>add_more_signal</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>add_more_reason</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>decision_reasons</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>warnings</t>
         </is>
@@ -867,7 +879,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>181.9550018310547</v>
+        <v>182.3500061035156</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>89</v>
@@ -887,28 +899,28 @@
         <v>75</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>62.13229147846583</v>
+        <v>62.31512866084653</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.0151807899125376</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.3464883768441935</v>
+        <v>0.3492585386965051</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1.565119362447711</v>
+        <v>1.590327612314166</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>161.0305916922433</v>
+        <v>161.4255959647042</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>213.3416170392718</v>
+        <v>213.7366213117327</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>10.46220506940569</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0.053341</v>
@@ -933,12 +945,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -957,7 +971,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>211.0950012207031</v>
+        <v>211.25</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>89</v>
@@ -977,22 +991,22 @@
         <v>75</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>60.21059301407551</v>
+        <v>60.32419239286454</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.0229450115312453</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.4467218527117392</v>
+        <v>0.4515156748948139</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1.627021536938551</v>
+        <v>1.636913196927858</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>200.781430380685</v>
+        <v>200.9364291599818</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>224.846429007394</v>
+        <v>225.0014277866908</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>6.875713893345424</v>
@@ -1001,7 +1015,7 @@
         <v>13.95</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.066092</v>
+        <v>0.06604400000000001</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>1.12</v>
@@ -1023,12 +1037,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1047,7 +1063,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>554.9249877929688</v>
+        <v>556.2000122070312</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>82</v>
@@ -1067,28 +1083,28 @@
         <v>50</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>55.80068861027303</v>
+        <v>55.98630573472487</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0.0624019610194614</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.4386895932335694</v>
+        <v>0.4410737275619771</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>-2.625700490868056</v>
+        <v>-2.544331411452166</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>497.8478349958147</v>
+        <v>499.1228594098772</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>631.0278581891741</v>
+        <v>632.3028826032366</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>38.05143519810268</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>10.85</v>
+        <v>10.88</v>
       </c>
       <c r="R4" s="2" t="n">
         <v>0.019555</v>
@@ -1113,12 +1129,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1137,7 +1155,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>982.6099853515624</v>
+        <v>985.6799926757812</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>82</v>
@@ -1157,28 +1175,28 @@
         <v>50</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>44.75504296621285</v>
+        <v>45.01109675160277</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0.0543756800501934</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.3930254157668736</v>
+        <v>0.3954902609149611</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-25.00306542500729</v>
+        <v>-24.80714472967248</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>803.0799560546874</v>
+        <v>806.1499633789062</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1251.905029296875</v>
+        <v>1254.975036621094</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>89.7650146484375</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>6.11</v>
+        <v>6.13</v>
       </c>
       <c r="R5" s="2" t="n">
         <v>0.006217</v>
@@ -1203,12 +1221,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1227,7 +1247,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1157.2099609375</v>
+        <v>1156.849975585938</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>82</v>
@@ -1247,22 +1267,22 @@
         <v>50</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>58.0041452805042</v>
+        <v>57.93754253826302</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>-0.013419399271567</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.4090329628657867</v>
+        <v>0.413620923096229</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-6.816286208118143</v>
+        <v>-6.839259632263456</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1094.960484095982</v>
+        <v>1094.60049874442</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1240.209263392857</v>
+        <v>1239.849278041295</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>41.49965122767857</v>
@@ -1271,7 +1291,7 @@
         <v>13.95</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.012056</v>
+        <v>0.01206</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>1.12</v>
@@ -1293,12 +1313,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1317,7 +1339,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7.675000190734863</v>
+        <v>7.664999961853027</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>82</v>
@@ -1337,28 +1359,28 @@
         <v>50</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>50.04831028267274</v>
+        <v>49.95178289261076</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>-0.0049382666628676</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.4820637547508388</v>
+        <v>0.4873476996211151</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-0.1229024096039831</v>
+        <v>-0.123540600848864</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>6.197786058698382</v>
+        <v>6.187785829816546</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>9.890821388789586</v>
+        <v>9.88082115990775</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>0.7386070660182408</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="R7" s="2" t="n">
         <v>0.755569</v>
@@ -1383,12 +1405,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1407,7 +1431,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>369.7999877929688</v>
+        <v>370.9100036621094</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>82</v>
@@ -1427,28 +1451,28 @@
         <v>50</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46.14272736888983</v>
+        <v>46.31162813235188</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0.082723417254077</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.2793673206823957</v>
+        <v>0.2825782202322912</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-11.19471155768165</v>
+        <v>-11.12387293811257</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>276.9441441127233</v>
+        <v>278.0541599818638</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>509.0837533133371</v>
+        <v>510.1937691824777</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>46.42792184012277</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>4.45</v>
+        <v>4.46</v>
       </c>
       <c r="R8" s="2" t="n">
         <v>0.01202</v>
@@ -1473,12 +1497,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1497,7 +1523,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>16.8700008392334</v>
+        <v>16.84000015258789</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>79</v>
@@ -1517,22 +1543,22 @@
         <v>75</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>74.5523124039135</v>
+        <v>74.48015284749306</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>0.0098826338563442</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.2057040933627727</v>
+        <v>0.2077549597178633</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.1272830114562815</v>
+        <v>0.1253684377216397</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>13.87100069863456</v>
+        <v>13.84100001198905</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>21.36850105013166</v>
+        <v>21.33850036348615</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.499500070299421</v>
@@ -1550,7 +1576,7 @@
         <v>13.95</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>0.1195052135307623</v>
+        <v>0.1175143466997992</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" s="3" t="inlineStr"/>
@@ -1567,10 +1593,20 @@
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Held, but not strong enough to add</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AB9" s="3" t="inlineStr">
+      <c r="AD9" s="3" t="inlineStr">
         <is>
           <t>RSI overbought</t>
         </is>
@@ -1593,7 +1629,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>13.72000026702881</v>
+        <v>13.71000003814697</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>79</v>
@@ -1613,22 +1649,22 @@
         <v>75</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>75.17084129057541</v>
+        <v>75.11415241761875</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>-0.0110537672736636</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.235268699636298</v>
+        <v>0.2368562874856362</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.0321140772958692</v>
+        <v>0.0314758860509889</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>12.51234327043806</v>
+        <v>12.50234304155622</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>15.53148576191494</v>
+        <v>15.5214855330331</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.6038284982953753</v>
@@ -1659,12 +1695,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA10" s="3" t="inlineStr">
+      <c r="AA10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AB10" s="3" t="inlineStr">
+      <c r="AD10" s="3" t="inlineStr">
         <is>
           <t>RSI overbought</t>
         </is>
@@ -1687,7 +1725,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>268.3299865722656</v>
+        <v>268.0299987792969</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>79</v>
@@ -1707,22 +1745,22 @@
         <v>75</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>75.86654638577177</v>
+        <v>75.78787063755613</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>-0.0192129762097973</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.3775389596377526</v>
+        <v>0.3787496131587292</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.5225857158231797</v>
+        <v>0.5034411957020701</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>247.5590547834124</v>
+        <v>247.2590669904436</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>296.0245622907366</v>
+        <v>295.7245744977678</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>13.84728785923549</v>
@@ -1731,7 +1769,7 @@
         <v>6.98</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.025997</v>
+        <v>0.026026</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>1.12</v>
@@ -1753,12 +1791,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA11" s="3" t="inlineStr">
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AC11" s="3" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AB11" s="3" t="inlineStr">
+      <c r="AD11" s="3" t="inlineStr">
         <is>
           <t>RSI overbought</t>
         </is>
@@ -1781,7 +1821,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>393.3099060058594</v>
+        <v>393.9299926757813</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>79</v>
@@ -1801,22 +1841,22 @@
         <v>75</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>55.3837022728646</v>
+        <v>55.60892184553344</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0.030087289573326</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.3702226400205015</v>
+        <v>0.3725360264533705</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.248055099082121</v>
+        <v>3.28762758172099</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>370.8045567103795</v>
+        <v>371.4246433803014</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>423.3170383998326</v>
+        <v>423.9371250697545</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>15.00356619698661</v>
@@ -1825,7 +1865,7 @@
         <v>6.98</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.017736</v>
+        <v>0.017708</v>
       </c>
       <c r="S12" s="4" t="n">
         <v>1.12</v>
@@ -1847,12 +1887,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA12" s="4" t="inlineStr">
+      <c r="AA12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="inlineStr">
         <is>
           <t>Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AB12" s="4" t="inlineStr"/>
+      <c r="AD12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1871,7 +1913,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6.414999961853027</v>
+        <v>6.429999828338623</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>78</v>
@@ -1891,28 +1933,28 @@
         <v>75</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>62.57668446039076</v>
+        <v>62.8078769713569</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>0.0046656626141934</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2529078200156134</v>
+        <v>0.2582419959877393</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.020134377036457</v>
+        <v>0.0210916334731448</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>5.128857272011893</v>
+        <v>5.143857138497489</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>8.344213996614728</v>
+        <v>8.359213863100324</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0.6430713449205671</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="R13" s="4" t="n">
         <v>0.433909</v>
@@ -1937,12 +1979,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA13" s="4" t="inlineStr">
+      <c r="AA13" s="4" t="inlineStr"/>
+      <c r="AB13" s="4" t="inlineStr"/>
+      <c r="AC13" s="4" t="inlineStr">
         <is>
           <t>Strong trend; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AB13" s="4" t="inlineStr"/>
+      <c r="AD13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1961,7 +2005,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>238.6300964355469</v>
+        <v>239.8249969482422</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>75</v>
@@ -1981,28 +2025,28 @@
         <v>50</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>41.24271373225548</v>
+        <v>41.60886297383517</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>0.06596166699561611</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2741969617663742</v>
+        <v>0.2759027722730133</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.671998223304254</v>
+        <v>-4.595742464089508</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>185.0593806675502</v>
+        <v>186.2542811802456</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>318.9861700875418</v>
+        <v>320.1810706002371</v>
       </c>
       <c r="P14" s="4" t="n">
         <v>26.78535788399833</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="R14" s="4" t="n">
         <v>0.010417</v>
@@ -2027,123 +2071,139 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA14" s="4" t="inlineStr">
+      <c r="AA14" s="4" t="inlineStr"/>
+      <c r="AB14" s="4" t="inlineStr"/>
+      <c r="AC14" s="4" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="AB14" s="4" t="inlineStr"/>
+      <c r="AD14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Internet/Software</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>QUALITY</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>358.5450134277344</v>
-      </c>
-      <c r="E15" s="5" t="n">
+      <c r="D15" s="3" t="n">
+        <v>358.0578918457031</v>
+      </c>
+      <c r="E15" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="I15" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J15" s="5" t="n">
-        <v>60.08777128483414</v>
-      </c>
-      <c r="K15" s="5" t="n">
+      <c r="J15" s="3" t="n">
+        <v>59.76929787069184</v>
+      </c>
+      <c r="K15" s="3" t="n">
         <v>-0.0040282924977889</v>
       </c>
-      <c r="L15" s="5" t="n">
-        <v>0.2685316087084209</v>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>0.6359296788722668</v>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v>343.5996540614537</v>
-      </c>
-      <c r="O15" s="5" t="n">
-        <v>378.472159249442</v>
-      </c>
-      <c r="P15" s="5" t="n">
+      <c r="L15" s="3" t="n">
+        <v>0.2738245992637517</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>0.6048427175118514</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>343.1125324794224</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>377.9850376674107</v>
+      </c>
+      <c r="P15" s="3" t="n">
         <v>9.963572910853795</v>
       </c>
-      <c r="Q15" s="5" t="n">
+      <c r="Q15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R15" s="5" t="n">
+      <c r="R15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S15" s="5" t="n">
+      <c r="S15" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="T15" s="5" t="n">
+      <c r="T15" s="3" t="n">
         <v>13.95</v>
       </c>
-      <c r="U15" s="5" t="n">
-        <v>-0.0225593676998241</v>
-      </c>
-      <c r="V15" s="5" t="inlineStr"/>
-      <c r="W15" s="5" t="inlineStr"/>
-      <c r="X15" s="5" t="n">
+      <c r="U15" s="3" t="n">
+        <v>-0.0238873248859967</v>
+      </c>
+      <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="Y15" s="5" t="n">
+      <c r="Y15" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z15" s="5" t="inlineStr">
+      <c r="Z15" s="3" t="inlineStr">
         <is>
           <t>Already held</t>
         </is>
       </c>
-      <c r="AA15" s="5" t="inlineStr">
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>Do not average down</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
         <is>
           <t>Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AB15" s="5" t="inlineStr"/>
+      <c r="AD15" s="3" t="inlineStr">
+        <is>
+          <t>Do not average down</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>CELC</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Internet/E-Commerce</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>246.5249938964844</v>
+        <v>104.7900009155273</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>68</v>
@@ -2163,25 +2223,25 @@
         <v>75</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>65.43192876681358</v>
+        <v>64.93240438722938</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.0071974396379796</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0.3079046776428261</v>
+        <v>0.3752177474627413</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>1.67978495280924</v>
+        <v>1.43008640176276</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>235.3082128252302</v>
+        <v>92.8471429007394</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>261.48070199149</v>
+        <v>122.7042879377093</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>7.47785404750279</v>
+        <v>5.971429007393973</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -2209,22 +2269,24 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA16" s="5" t="inlineStr">
+      <c r="AA16" s="5" t="inlineStr"/>
+      <c r="AB16" s="5" t="inlineStr"/>
+      <c r="AC16" s="5" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AB16" s="5" t="inlineStr"/>
+      <c r="AD16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>CELC</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -2233,10 +2295,10 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>104.9599990844727</v>
+        <v>18.68499946594238</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -2247,31 +2309,31 @@
         <v>40</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>75</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>65.05409098398465</v>
+        <v>62.92860938357886</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0</v>
+        <v>0.0044125718372439</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.3726839268372514</v>
+        <v>0.7645216566459045</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>1.44093528775813</v>
+        <v>0.0409233813708038</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>93.01714106968473</v>
+        <v>16.8021422794887</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>122.8742861066546</v>
+        <v>21.50928524562291</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>5.971429007393973</v>
+        <v>0.9414285932268416</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -2285,7 +2347,9 @@
       <c r="T17" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U17" s="5" t="inlineStr"/>
+      <c r="U17" s="5" t="n">
+        <v>0.0155648686062401</v>
+      </c>
       <c r="V17" s="5" t="inlineStr"/>
       <c r="W17" s="5" t="inlineStr"/>
       <c r="X17" s="5" t="n">
@@ -2296,37 +2360,47 @@
       </c>
       <c r="Z17" s="5" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>Already held</t>
         </is>
       </c>
       <c r="AA17" s="5" t="inlineStr">
         <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AB17" s="5" t="inlineStr">
+        <is>
+          <t>Held, but not strong enough to add</t>
+        </is>
+      </c>
+      <c r="AC17" s="5" t="inlineStr">
+        <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AB17" s="5" t="inlineStr"/>
+      <c r="AD17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>18.69499969482422</v>
+        <v>423.4599914550781</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -2337,31 +2411,31 @@
         <v>40</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>62.99719808877189</v>
+        <v>45.96163923757332</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.0044125718372439</v>
+        <v>0.0220361706931489</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.7497547252693841</v>
+        <v>0.6981613034098922</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.0415615726156839</v>
+        <v>-4.01095308947049</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>16.81214250837053</v>
+        <v>393.5007062639509</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>21.51928547450474</v>
+        <v>463.4057050432478</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.9414285932268416</v>
+        <v>19.97285679408482</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -2375,9 +2449,7 @@
       <c r="T18" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U18" s="5" t="n">
-        <v>0.016108399857013</v>
-      </c>
+      <c r="U18" s="5" t="inlineStr"/>
       <c r="V18" s="5" t="inlineStr"/>
       <c r="W18" s="5" t="inlineStr"/>
       <c r="X18" s="5" t="n">
@@ -2388,25 +2460,27 @@
       </c>
       <c r="Z18" s="5" t="inlineStr">
         <is>
-          <t>Already held</t>
-        </is>
-      </c>
-      <c r="AA18" s="5" t="inlineStr">
-        <is>
-          <t>MACD/volume acceleration</t>
-        </is>
-      </c>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AA18" s="5" t="inlineStr"/>
       <c r="AB18" s="5" t="inlineStr"/>
+      <c r="AC18" s="5" t="inlineStr">
+        <is>
+          <t>Positive momentum</t>
+        </is>
+      </c>
+      <c r="AD18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Data Storage</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2415,7 +2489,7 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>422.989990234375</v>
+        <v>884.8900146484375</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>65</v>
@@ -2426,7 +2500,7 @@
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>75</v>
@@ -2435,25 +2509,25 @@
         <v>50</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>45.80252323519223</v>
+        <v>38.44778386563386</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.0220361706931489</v>
+        <v>0.0451049293978258</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.6894883407522808</v>
+        <v>0.5028856273667869</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>-4.040947469367188</v>
+        <v>-14.81568387260039</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>393.0307050432477</v>
+        <v>758.4410858154297</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>462.9357038225447</v>
+        <v>1053.488586425781</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>19.97285679408482</v>
+        <v>84.29928588867188</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2481,22 +2555,24 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA19" s="5" t="inlineStr">
-        <is>
-          <t>Positive momentum</t>
-        </is>
-      </c>
+      <c r="AA19" s="5" t="inlineStr"/>
       <c r="AB19" s="5" t="inlineStr"/>
+      <c r="AC19" s="5" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum</t>
+        </is>
+      </c>
+      <c r="AD19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Data Storage</t>
+          <t>Data Centers</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2505,45 +2581,45 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>881.9500122070312</v>
+        <v>303.8349914550781</v>
       </c>
       <c r="E20" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H20" s="5" t="n">
         <v>65</v>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>75</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>50</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>38.17454872190672</v>
+        <v>45.66485867189928</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.0451049293978258</v>
+        <v>0.031582057136426</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.4929302343268891</v>
+        <v>0.3331311105125306</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>-15.00330796002907</v>
+        <v>-0.7508301039947693</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>755.5010833740234</v>
+        <v>271.9310607910156</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>1050.548583984375</v>
+        <v>346.3735656738281</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>84.29928588867188</v>
+        <v>21.269287109375</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2571,22 +2647,20 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA20" s="5" t="inlineStr">
-        <is>
-          <t>Strong trend; Positive momentum</t>
-        </is>
-      </c>
+      <c r="AA20" s="5" t="inlineStr"/>
       <c r="AB20" s="5" t="inlineStr"/>
+      <c r="AC20" s="5" t="inlineStr"/>
+      <c r="AD20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Data Centers</t>
+          <t>Internet/E-Commerce</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -2595,10 +2669,10 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>303.9100036621094</v>
+        <v>246.3350067138672</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -2609,31 +2683,31 @@
         <v>40</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>45.6853713981408</v>
+        <v>65.12433937744606</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.031582057136426</v>
+        <v>-0.0071974396379796</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.3309603781661025</v>
+        <v>0.3120038893087236</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>-0.746043000184238</v>
+        <v>1.667660414659275</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>272.0060729980469</v>
+        <v>235.118225642613</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>346.4485778808594</v>
+        <v>261.2907148088728</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>21.269287109375</v>
+        <v>7.47785404750279</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2663,6 +2737,12 @@
       </c>
       <c r="AA21" s="5" t="inlineStr"/>
       <c r="AB21" s="5" t="inlineStr"/>
+      <c r="AC21" s="5" t="inlineStr">
+        <is>
+          <t>MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="AD21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2681,7 +2761,7 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>284.6000061035156</v>
+        <v>284.4100036621094</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>55</v>
@@ -2701,22 +2781,22 @@
         <v>50</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>28.65271378907748</v>
+        <v>28.62432369505791</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>0.0376936349020097</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.5519305243966304</v>
+        <v>0.5547548299860414</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-9.881871489402789</v>
+        <v>-9.893997001332997</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>225.8374328613281</v>
+        <v>225.6474304199219</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>372.7438659667969</v>
+        <v>372.5538635253906</v>
       </c>
       <c r="P22" s="5" t="n">
         <v>29.38128662109375</v>
@@ -2747,12 +2827,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA22" s="5" t="inlineStr">
+      <c r="AA22" s="5" t="inlineStr"/>
+      <c r="AB22" s="5" t="inlineStr"/>
+      <c r="AC22" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="AB22" s="5" t="inlineStr"/>
+      <c r="AD22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2771,7 +2853,7 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>223.2899932861328</v>
+        <v>224</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>55</v>
@@ -2791,22 +2873,22 @@
         <v>50</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>33.76812818833493</v>
+        <v>34.04083201590227</v>
       </c>
       <c r="K23" s="5" t="n">
         <v>0.0645198535414377</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.2761431904386516</v>
+        <v>0.2782483061201892</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-9.093599991197133</v>
+        <v>-9.048289021423289</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>190.8857040405273</v>
+        <v>191.5957107543945</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>266.4957122802734</v>
+        <v>267.2057189941406</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>21.60285949707031</v>
@@ -2837,12 +2919,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA23" s="5" t="inlineStr">
+      <c r="AA23" s="5" t="inlineStr"/>
+      <c r="AB23" s="5" t="inlineStr"/>
+      <c r="AC23" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="AB23" s="5" t="inlineStr"/>
+      <c r="AD23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2861,7 +2945,7 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>195.7400054931641</v>
+        <v>196.1999969482422</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>55</v>
@@ -2881,22 +2965,22 @@
         <v>50</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>30.19478996682716</v>
+        <v>30.26414306552548</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>0.0310198990532244</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.6636987578920163</v>
+        <v>0.6750087269428927</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>-6.989419597772017</v>
+        <v>-6.960064017732826</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>144.6197182791574</v>
+        <v>145.0797097342355</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>272.4204363141741</v>
+        <v>272.8804277692523</v>
       </c>
       <c r="P24" s="5" t="n">
         <v>25.56014360700335</v>
@@ -2927,12 +3011,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA24" s="5" t="inlineStr">
+      <c r="AA24" s="5" t="inlineStr"/>
+      <c r="AB24" s="5" t="inlineStr"/>
+      <c r="AC24" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="AB24" s="5" t="inlineStr"/>
+      <c r="AD24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2951,7 +3037,7 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>107.375</v>
+        <v>107.2399978637695</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>55</v>
@@ -2971,22 +3057,22 @@
         <v>50</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>31.35155293469214</v>
+        <v>31.21248198408246</v>
       </c>
       <c r="K25" s="5" t="n">
         <v>0.0469355722360184</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.4461193870124323</v>
+        <v>0.4503242821149934</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-3.417709409647521</v>
+        <v>-3.426324930592146</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>93.15607070922852</v>
+        <v>93.02106857299805</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>126.3335723876953</v>
+        <v>126.1985702514648</v>
       </c>
       <c r="P25" s="5" t="n">
         <v>9.479286193847656</v>
@@ -3017,12 +3103,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA25" s="5" t="inlineStr">
+      <c r="AA25" s="5" t="inlineStr"/>
+      <c r="AB25" s="5" t="inlineStr"/>
+      <c r="AC25" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="AB25" s="5" t="inlineStr"/>
+      <c r="AD25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -3041,7 +3129,7 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>25.79999923706055</v>
+        <v>25.86009979248047</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>54</v>
@@ -3061,22 +3149,22 @@
         <v>50</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>41.6717492429667</v>
+        <v>41.82511788429533</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>0.0084746235925221</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.2121235612950105</v>
+        <v>0.2175772153887832</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>-0.0465624630173051</v>
+        <v>-0.0427269859762597</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>21.04728507995605</v>
+        <v>21.10738563537598</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>32.92907047271729</v>
+        <v>32.98917102813721</v>
       </c>
       <c r="P26" s="5" t="n">
         <v>2.376357078552246</v>
@@ -3109,6 +3197,8 @@
       </c>
       <c r="AA26" s="5" t="inlineStr"/>
       <c r="AB26" s="5" t="inlineStr"/>
+      <c r="AC26" s="5" t="inlineStr"/>
+      <c r="AD26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -3127,7 +3217,7 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>276.0199890136719</v>
+        <v>275.6400146484375</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>51</v>
@@ -3147,22 +3237,22 @@
         <v>75</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>61.55851569211629</v>
+        <v>61.26917068773249</v>
       </c>
       <c r="K27" s="5" t="n">
         <v>-0.0092015237095138</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>0.2085784934230437</v>
+        <v>0.2110169677476387</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>5.902375557176857</v>
+        <v>5.878126480877018</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>258.2182088579451</v>
+        <v>257.8382344927107</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>299.7556958879744</v>
+        <v>299.37572152274</v>
       </c>
       <c r="P27" s="5" t="n">
         <v>11.86785343715123</v>
@@ -3193,12 +3283,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA27" s="5" t="inlineStr">
+      <c r="AA27" s="5" t="inlineStr"/>
+      <c r="AB27" s="5" t="inlineStr"/>
+      <c r="AC27" s="5" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AB27" s="5" t="inlineStr"/>
+      <c r="AD27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -3217,7 +3309,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>395.7807922363281</v>
+        <v>395.7799987792969</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>43</v>
@@ -3237,22 +3329,22 @@
         <v>50</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>54.21071674379002</v>
+        <v>54.21050082981659</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0.0109940121352903</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.3225300464659174</v>
+        <v>0.3256883095764366</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>-0.0696721267293503</v>
+        <v>-0.0697227633033923</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>367.9300809587751</v>
+        <v>367.9292875017438</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>432.9150739397322</v>
+        <v>432.9142804827009</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>18.56714085170201</v>
@@ -3270,7 +3362,7 @@
         <v>13.95</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>-0.0427002882642661</v>
+        <v>-0.0427022074483251</v>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
@@ -3293,10 +3385,20 @@
           <t>Already held</t>
         </is>
       </c>
-      <c r="AA28" s="3" t="inlineStr"/>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>Signal score weakened</t>
+          <t>Do not average down</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr"/>
+      <c r="AD28" s="3" t="inlineStr">
+        <is>
+          <t>Do not average down; Signal score weakened</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3419,7 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>79.86000061035156</v>
+        <v>79.84999847412109</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>43</v>
@@ -3337,22 +3439,22 @@
         <v>50</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>38.11896320533445</v>
+        <v>38.10932385566196</v>
       </c>
       <c r="K29" s="5" t="n">
         <v>0.0264563885114627</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.3748810140799213</v>
+        <v>0.3780170853995899</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>-1.378373529781509</v>
+        <v>-1.379011842748928</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>64.394287109375</v>
+        <v>64.38428497314453</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>103.0585708618164</v>
+        <v>103.0485687255859</v>
       </c>
       <c r="P29" s="5" t="n">
         <v>7.732856750488281</v>
@@ -3385,6 +3487,8 @@
       </c>
       <c r="AA29" s="5" t="inlineStr"/>
       <c r="AB29" s="5" t="inlineStr"/>
+      <c r="AC29" s="5" t="inlineStr"/>
+      <c r="AD29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3429,7 +3533,7 @@
         <v>-0.0154083063419491</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.7155083019845888</v>
+        <v>0.7279997013311943</v>
       </c>
       <c r="M30" s="5" t="n">
         <v>0.0704685085412049</v>
@@ -3469,12 +3573,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA30" s="5" t="inlineStr">
+      <c r="AA30" s="5" t="inlineStr"/>
+      <c r="AB30" s="5" t="inlineStr"/>
+      <c r="AC30" s="5" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AB30" s="5" t="inlineStr"/>
+      <c r="AD30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3493,7 +3599,7 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>27.80999946594238</v>
+        <v>27.84499931335449</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>33</v>
@@ -3513,22 +3619,22 @@
         <v>50</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>27.58339839891339</v>
+        <v>27.78904304325279</v>
       </c>
       <c r="K31" s="5" t="n">
         <v>0.0112075006381963</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.2161936276811687</v>
+        <v>0.2177604757923567</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>-0.0354749550241217</v>
+        <v>-0.0332413465283076</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>24.25999995640346</v>
+        <v>24.29499980381556</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>33.13499873025077</v>
+        <v>33.16999857766287</v>
       </c>
       <c r="P31" s="5" t="n">
         <v>1.774999754769462</v>
@@ -3561,6 +3667,8 @@
       </c>
       <c r="AA31" s="5" t="inlineStr"/>
       <c r="AB31" s="5" t="inlineStr"/>
+      <c r="AC31" s="5" t="inlineStr"/>
+      <c r="AD31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3579,7 +3687,7 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>39.22909927368164</v>
+        <v>39.46440124511719</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>33</v>
@@ -3599,22 +3707,22 @@
         <v>50</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>17.28480087008961</v>
+        <v>17.96308832256679</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>0.0298353862022756</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.3484123267180921</v>
+        <v>0.3520177438940802</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>-1.441288642024866</v>
+        <v>-1.426272219916156</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>31.82695661272321</v>
+        <v>32.06225858415876</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>50.33231326511928</v>
+        <v>50.56761523655483</v>
       </c>
       <c r="P32" s="5" t="n">
         <v>3.701071330479213</v>
@@ -3647,6 +3755,8 @@
       </c>
       <c r="AA32" s="5" t="inlineStr"/>
       <c r="AB32" s="5" t="inlineStr"/>
+      <c r="AC32" s="5" t="inlineStr"/>
+      <c r="AD32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3665,7 +3775,7 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>69.66000366210938</v>
+        <v>69.69999694824219</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>32</v>
@@ -3685,22 +3795,22 @@
         <v>50</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>47.09922336809468</v>
+        <v>47.13743316355389</v>
       </c>
       <c r="K33" s="5" t="n">
         <v>0.0334417645102432</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.291092015097882</v>
+        <v>0.292970186665529</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>-0.747463190953888</v>
+        <v>-0.7449109128645111</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>55.74943215506417</v>
+        <v>55.78942544119698</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>90.52586092267715</v>
+        <v>90.56585420880998</v>
       </c>
       <c r="P33" s="5" t="n">
         <v>6.955285753522601</v>
@@ -3733,6 +3843,8 @@
       </c>
       <c r="AA33" s="5" t="inlineStr"/>
       <c r="AB33" s="5" t="inlineStr"/>
+      <c r="AC33" s="5" t="inlineStr"/>
+      <c r="AD33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3751,7 +3863,7 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>7.820000171661377</v>
+        <v>7.835000038146973</v>
       </c>
       <c r="E34" s="5" t="n">
         <v>32</v>
@@ -3771,22 +3883,22 @@
         <v>50</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>44.40366879365192</v>
+        <v>44.55626486353297</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>0.018661516252568</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0.6281787580389391</v>
+        <v>0.6337696104940953</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>-0.0748262672022259</v>
+        <v>-0.0738690107655368</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>6.431714670998709</v>
+        <v>6.446714537484305</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>9.902428422655378</v>
+        <v>9.917428289140974</v>
       </c>
       <c r="P34" s="5" t="n">
         <v>0.6941427503313337</v>
@@ -3819,6 +3931,8 @@
       </c>
       <c r="AA34" s="5" t="inlineStr"/>
       <c r="AB34" s="5" t="inlineStr"/>
+      <c r="AC34" s="5" t="inlineStr"/>
+      <c r="AD34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -3837,7 +3951,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>185.1950073242188</v>
+        <v>184.3399963378907</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>29</v>
@@ -3862,13 +3976,13 @@
       </c>
       <c r="L35" s="3" t="inlineStr"/>
       <c r="M35" s="3" t="n">
-        <v>0.567329849395619</v>
+        <v>0.5127650457097526</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>170.3794067382813</v>
+        <v>169.5927966308594</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>212.9742584228516</v>
+        <v>211.9909957885743</v>
       </c>
       <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="3" t="n">
@@ -3897,12 +4011,14 @@
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA35" s="3" t="inlineStr">
+      <c r="AA35" s="3" t="inlineStr"/>
+      <c r="AB35" s="3" t="inlineStr"/>
+      <c r="AC35" s="3" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AB35" s="3" t="inlineStr">
+      <c r="AD35" s="3" t="inlineStr">
         <is>
           <t>Missing ATR</t>
         </is>
@@ -3925,7 +4041,7 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>15.10999965667725</v>
+        <v>15.15499973297119</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>22</v>
@@ -3945,22 +4061,22 @@
         <v>50</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>23.97503582866533</v>
+        <v>24.09476173102698</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>0.0323432829789085</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.352179765116708</v>
+        <v>0.3545207037936516</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>-0.2122178608022866</v>
+        <v>-0.2093460610615922</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>11.86101354871478</v>
+        <v>11.90601362500872</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>19.98347881862095</v>
+        <v>20.0284788949149</v>
       </c>
       <c r="P36" s="5" t="n">
         <v>1.624493053981236</v>
@@ -3993,6 +4109,8 @@
       </c>
       <c r="AA36" s="5" t="inlineStr"/>
       <c r="AB36" s="5" t="inlineStr"/>
+      <c r="AC36" s="5" t="inlineStr"/>
+      <c r="AD36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -4011,7 +4129,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>91.63009643554688</v>
+        <v>91.68000030517578</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>22</v>
@@ -4031,22 +4149,22 @@
         <v>50</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>17.43425787840226</v>
+        <v>17.58944999670975</v>
       </c>
       <c r="K37" s="5" t="n">
         <v>0.0177384274683925</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.7983897383411729</v>
+        <v>0.802274535494354</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>-0.7682904120269969</v>
+        <v>-0.7651056636518181</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>84.90473883492606</v>
+        <v>84.95464270455497</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>100.5972399030413</v>
+        <v>100.6471437726702</v>
       </c>
       <c r="P37" s="5" t="n">
         <v>4.48357173374721</v>
@@ -4079,6 +4197,8 @@
       </c>
       <c r="AA37" s="5" t="inlineStr"/>
       <c r="AB37" s="5" t="inlineStr"/>
+      <c r="AC37" s="5" t="inlineStr"/>
+      <c r="AD37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -4097,7 +4217,7 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>8.569999694824219</v>
+        <v>8.595000267028809</v>
       </c>
       <c r="E38" s="5" t="n">
         <v>22</v>
@@ -4117,22 +4237,22 @@
         <v>50</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>20.71610473444554</v>
+        <v>21.21982595865489</v>
       </c>
       <c r="K38" s="5" t="n">
         <v>0.0299401183926648</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.4944922542698931</v>
+        <v>0.4980625979259259</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>-0.1161758861571882</v>
+        <v>-0.1145804080449862</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>7.222857475280762</v>
+        <v>7.247858047485352</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>10.5907130241394</v>
+        <v>10.61571359634399</v>
       </c>
       <c r="P38" s="5" t="n">
         <v>0.6735711097717285</v>
@@ -4165,6 +4285,8 @@
       </c>
       <c r="AA38" s="5" t="inlineStr"/>
       <c r="AB38" s="5" t="inlineStr"/>
+      <c r="AC38" s="5" t="inlineStr"/>
+      <c r="AD38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -4183,7 +4305,7 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>46.04000091552734</v>
+        <v>46.15000152587891</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>22</v>
@@ -4203,22 +4325,22 @@
         <v>50</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>23.88758665037871</v>
+        <v>24.27772708696961</v>
       </c>
       <c r="K39" s="5" t="n">
         <v>0.0251036384349932</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.3141818906065142</v>
+        <v>0.3161810453460449</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>-0.3373257760557111</v>
+        <v>-0.3303057940845564</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>39.15325764247349</v>
+        <v>39.26325825282505</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>56.37011582510812</v>
+        <v>56.48011643545968</v>
       </c>
       <c r="P39" s="5" t="n">
         <v>3.443371636526925</v>
@@ -4251,6 +4373,8 @@
       </c>
       <c r="AA39" s="5" t="inlineStr"/>
       <c r="AB39" s="5" t="inlineStr"/>
+      <c r="AC39" s="5" t="inlineStr"/>
+      <c r="AD39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -4269,7 +4393,7 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>7.744999885559082</v>
+        <v>7.751699924468994</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>22</v>
@@ -4289,22 +4413,22 @@
         <v>50</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>26.82926709831341</v>
+        <v>26.95491660880916</v>
       </c>
       <c r="K40" s="5" t="n">
         <v>0.0100267124430337</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0.8577808744897341</v>
+        <v>0.8755305405588308</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>-0.1042795375269125</v>
+        <v>-0.1038519566961955</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>6.629571301596505</v>
+        <v>6.636271340506418</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>9.418142761502947</v>
+        <v>9.424842800412859</v>
       </c>
       <c r="P40" s="5" t="n">
         <v>0.5577142919812884</v>
@@ -4337,6 +4461,8 @@
       </c>
       <c r="AA40" s="5" t="inlineStr"/>
       <c r="AB40" s="5" t="inlineStr"/>
+      <c r="AC40" s="5" t="inlineStr"/>
+      <c r="AD40" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4355,7 +4481,7 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -4417,19 +4543,19 @@
         <v>15.06915790595363</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>16.8700008392334</v>
+        <v>16.84000015258789</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>12.59556302699257</v>
+        <v>12.57316376672592</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>11.251008816</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.34455421099257</v>
+        <v>1.322154950725922</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.1195052135307623</v>
+        <v>0.1175143466997992</v>
       </c>
     </row>
     <row r="3">
@@ -4445,19 +4571,19 @@
         <v>366.8202462424581</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>358.5450134277344</v>
+        <v>358.0578918457031</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.95257826083588</v>
+        <v>18.92682916501739</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>19.3900045021</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.4374262412641201</v>
+        <v>-0.4631753370826033</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.0225593676998241</v>
+        <v>-0.0238873248859967</v>
       </c>
     </row>
     <row r="4">
@@ -4473,19 +4599,19 @@
         <v>18.39862725025694</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>18.69499969482422</v>
+        <v>18.68499946594238</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>11.43224469588089</v>
+        <v>11.42612942091656</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>11.251008945</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.1812357508808908</v>
+        <v>0.1751204759165574</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.016108399857013</v>
+        <v>0.0155648686062401</v>
       </c>
     </row>
     <row r="5">
@@ -4501,19 +4627,19 @@
         <v>413.4345674446258</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>395.7807922363281</v>
+        <v>395.7799987792969</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.77058454733124</v>
+        <v>10.77056295458038</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>11.2510057355</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.4804211881687621</v>
+        <v>-0.480442780919617</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.0427002882642661</v>
+        <v>-0.0427022074483251</v>
       </c>
     </row>
   </sheetData>
@@ -4841,46 +4967,46 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>369.7999877929688</v>
+        <v>370.9100036621094</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>331.9717990112305</v>
+        <v>331.9939993286133</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>201.2460000228882</v>
+        <v>201.2515501022339</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>46.14272736888983</v>
+        <v>46.31162813235188</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.0072177419053192</v>
+        <v>0.0102410726627577</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.167643461680674</v>
+        <v>1.174150002298657</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>1.14289837224264</v>
+        <v>1.149330636379102</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>14.88285726158</v>
+        <v>14.97140553604134</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>26.07756881926165</v>
+        <v>26.09527847415392</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-11.19471155768165</v>
+        <v>-11.12387293811257</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>-10.00415359792669</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>1710040</v>
+        <v>1729806</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>6121116.8</v>
+        <v>6121512.12</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>0.2793673206823957</v>
+        <v>0.2825782202322912</v>
       </c>
       <c r="P2" s="6" t="n">
         <v>0.082723417254077</v>
@@ -4894,7 +5020,7 @@
         <v>46.42792184012277</v>
       </c>
       <c r="S2" s="6" t="n">
-        <v>0.1255487381630615</v>
+        <v>0.1251730106541358</v>
       </c>
       <c r="T2" s="6" t="inlineStr">
         <is>
@@ -4909,46 +5035,46 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>554.9249877929688</v>
+        <v>556.2000122070312</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>489.8498999023437</v>
+        <v>489.875400390625</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>291.5014246368408</v>
+        <v>291.5077997589111</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>55.80068861027303</v>
+        <v>55.98630573472487</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.08474887082516711</v>
+        <v>0.0872412460539877</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.175579142425809</v>
+        <v>1.180577865825075</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1.671890708603197</v>
+        <v>1.678029783181052</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>17.32775388529046</v>
+        <v>17.42946523456033</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>19.95345437615852</v>
+        <v>19.97379664601249</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-2.625700490868056</v>
+        <v>-2.544331411452166</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>-3.577422784539042</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>14857813</v>
+        <v>14939279</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>33868624.26</v>
+        <v>33870253.58</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.4386895932335694</v>
+        <v>0.4410737275619771</v>
       </c>
       <c r="P3" s="6" t="n">
         <v>0.0624019610194614</v>
@@ -4962,7 +5088,7 @@
         <v>38.05143519810268</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0.06857041228119801</v>
+        <v>0.0684132225152469</v>
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
@@ -4977,46 +5103,46 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>246.5249938964844</v>
+        <v>246.3350067138672</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>253.349299621582</v>
+        <v>253.3454998779297</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>233.5977749633789</v>
+        <v>233.5968250274658</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>65.43192876681358</v>
+        <v>65.12433937744606</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0334311077036382</v>
+        <v>0.0326346827185757</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.0100193170555353</v>
+        <v>-0.0107822564955705</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.0002231211729983</v>
+        <v>-0.000547711714072</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.7308611153262063</v>
+        <v>-0.7460167880136623</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-2.410646068135446</v>
+        <v>-2.413677202672937</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>1.67978495280924</v>
+        <v>1.667660414659275</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>1.780135958077288</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>14999948</v>
+        <v>15200900</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>48716206.96</v>
+        <v>48720226</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.3079046776428261</v>
+        <v>0.3120038893087236</v>
       </c>
       <c r="P4" s="6" t="n">
         <v>-0.0071974396379796</v>
@@ -5030,7 +5156,7 @@
         <v>7.47785404750279</v>
       </c>
       <c r="S4" s="6" t="n">
-        <v>0.0303330462737694</v>
+        <v>0.0303564407968566</v>
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
@@ -5045,46 +5171,46 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>181.9550018310547</v>
+        <v>182.3500061035156</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>160.7804995727539</v>
+        <v>160.7883996582031</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>144.3300746536255</v>
+        <v>144.3320496749878</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>62.13229147846583</v>
+        <v>62.31512866084653</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.114647119015653</v>
+        <v>0.1170668951683648</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.1786940959149896</v>
+        <v>0.1812529110018275</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.4742748706087554</v>
+        <v>0.4774753590087004</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5.962122843660154</v>
+        <v>5.993633155993223</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.397003481212443</v>
+        <v>4.403305543679057</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>1.565119362447711</v>
+        <v>1.590327612314166</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>1.773262942271622</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>3584682</v>
+        <v>3613543</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>10345749.64</v>
+        <v>10346326.86</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.3464883768441935</v>
+        <v>0.3492585386965051</v>
       </c>
       <c r="P5" s="6" t="n">
         <v>0.0151807899125376</v>
@@ -5098,7 +5224,7 @@
         <v>10.46220506940569</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>0.057498859410965</v>
+        <v>0.0573743061103412</v>
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
@@ -5113,46 +5239,46 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>284.6000061035156</v>
+        <v>284.4100036621094</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>312.6273983764648</v>
+        <v>312.6235983276367</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>182.8286249923706</v>
+        <v>182.8276749801636</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>28.65271378907748</v>
+        <v>28.62432369505791</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-0.2526456555024522</v>
+        <v>-0.2531445983942469</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.7652896907866331</v>
+        <v>0.7641111618202046</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1.560734278085872</v>
+        <v>1.559024700593973</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-7.881989710769687</v>
+        <v>-7.897146600682447</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>1.9998817786331</v>
+        <v>1.996850400650548</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-9.881871489402789</v>
+        <v>-9.893997001332997</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>-9.368367243321137</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>6173868</v>
+        <v>6205815</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>11185951.36</v>
+        <v>11186590.3</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.5519305243966304</v>
+        <v>0.5547548299860414</v>
       </c>
       <c r="P6" s="6" t="n">
         <v>0.0376936349020097</v>
@@ -5166,7 +5292,7 @@
         <v>29.38128662109375</v>
       </c>
       <c r="S6" s="6" t="n">
-        <v>0.1032371257589049</v>
+        <v>0.1033060941695985</v>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
@@ -5181,46 +5307,46 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>69.66000366210938</v>
+        <v>69.69999694824219</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>86.04640022277832</v>
+        <v>86.04720008850097</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>83.07134986877442</v>
+        <v>83.07154983520508</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>47.09922336809468</v>
+        <v>47.13743316355389</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.1547142268343596</v>
+        <v>-0.1542289303369005</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.2135033995469223</v>
+        <v>-0.2130518551608931</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.2920011780238076</v>
+        <v>-0.2915947008779503</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-4.773904030846637</v>
+        <v>-4.770713683234916</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-4.026440839892749</v>
+        <v>-4.025802770370405</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>-0.747463190953888</v>
+        <v>-0.7449109128645111</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>-0.7205249641778009</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>6735554</v>
+        <v>6779269</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>23138917.08</v>
+        <v>23139791.38</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.291092015097882</v>
+        <v>0.292970186665529</v>
       </c>
       <c r="P7" s="6" t="n">
         <v>0.0334417645102432</v>
@@ -5234,7 +5360,7 @@
         <v>6.955285753522601</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>0.0998461870208863</v>
+        <v>0.0997888960983377</v>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
@@ -5249,46 +5375,46 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>393.3099060058594</v>
+        <v>393.9299926757813</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>405.5399987792969</v>
+        <v>405.5524005126953</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>362.9420497131348</v>
+        <v>362.9451501464844</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>55.3837022728646</v>
+        <v>55.60892184553344</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0294184271630162</v>
+        <v>0.0310413932635604</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.0329058964933317</v>
+        <v>0.034534360887233</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.1166915066236082</v>
+        <v>0.1184520661902466</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-3.476292335560629</v>
+        <v>-3.426826732262043</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-6.72434743464275</v>
+        <v>-6.714454313983033</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>3.248055099082121</v>
+        <v>3.28762758172099</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>3.038872772970159</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>10158458</v>
+        <v>10222411</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>27438781.16</v>
+        <v>27440060.22</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3702226400205015</v>
+        <v>0.3725360264533705</v>
       </c>
       <c r="P8" s="6" t="n">
         <v>0.030087289573326</v>
@@ -5302,7 +5428,7 @@
         <v>15.00356619698661</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>0.038146931892336</v>
+        <v>0.0380868846646441</v>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
@@ -5317,46 +5443,46 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>7.675000190734863</v>
+        <v>7.664999961853027</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>5.822099995613098</v>
+        <v>5.821899991035462</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4.045225000381469</v>
+        <v>4.04517499923706</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>50.04831028267274</v>
+        <v>49.95178289261076</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.3853791053398705</v>
+        <v>0.3835740098614055</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.7286036242845428</v>
+        <v>0.7263513205113541</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.797423940285247</v>
+        <v>0.7950819662977748</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.6088825822721207</v>
+        <v>0.6080848432160195</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.7317849918761038</v>
+        <v>0.7316254440648836</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-0.1229024096039831</v>
+        <v>-0.123540600848864</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>-0.0949479297406228</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>3766833</v>
+        <v>3808528</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>7813972.66</v>
+        <v>7814806.56</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4820637547508388</v>
+        <v>0.4873476996211151</v>
       </c>
       <c r="P9" s="6" t="n">
         <v>-0.0049382666628676</v>
@@ -5370,7 +5496,7 @@
         <v>0.7386070660182408</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>0.0962354459495486</v>
+        <v>0.09636100061240981</v>
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
@@ -5385,46 +5511,46 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>16.8700008392334</v>
+        <v>16.84000015258789</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>9.902800045013429</v>
+        <v>9.902200031280518</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.552399994134903</v>
+        <v>6.552249990701675</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>74.5523124039135</v>
+        <v>74.48015284749306</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1.130050590495383</v>
+        <v>1.126262625046329</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>3.712290837640407</v>
+        <v>3.70391075739324</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>2.275728257637982</v>
+        <v>2.269902881698185</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>2.332967176560441</v>
+        <v>2.330573959392138</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>2.205684165104159</v>
+        <v>2.205205521670499</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1272830114562815</v>
+        <v>0.1253684377216397</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>0.2137816411175577</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>807265</v>
+        <v>815347</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>3924399.3</v>
+        <v>3924560.94</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.2057040933627727</v>
+        <v>0.2077549597178633</v>
       </c>
       <c r="P10" s="6" t="n">
         <v>0.0098826338563442</v>
@@ -5438,7 +5564,7 @@
         <v>1.499500070299421</v>
       </c>
       <c r="S10" s="6" t="n">
-        <v>0.0888855954773954</v>
+        <v>0.0890439463605934</v>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
@@ -5453,46 +5579,46 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>276.0199890136719</v>
+        <v>275.6400146484375</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>301.0076010131836</v>
+        <v>301.0000015258789</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>276.0448007965088</v>
+        <v>276.0429009246826</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>61.55851569211629</v>
+        <v>61.26917068773249</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.0640534889080283</v>
+        <v>-0.0653419306716712</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.0822278004532938</v>
+        <v>-0.0834912231140897</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.0456490803396021</v>
+        <v>0.0442096199332029</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-6.624518255191617</v>
+        <v>-6.654829600566416</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-12.52689381236847</v>
+        <v>-12.53295608144343</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>5.902375557176857</v>
+        <v>5.878126480877018</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>5.61249043240821</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>323752</v>
+        <v>327553</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>1552183.04</v>
+        <v>1552259.06</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.2085784934230437</v>
+        <v>0.2110169677476387</v>
       </c>
       <c r="P11" s="6" t="n">
         <v>-0.0092015237095138</v>
@@ -5506,7 +5632,7 @@
         <v>11.86785343715123</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>0.0429963550087794</v>
+        <v>0.0430556262024872</v>
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
@@ -5521,46 +5647,46 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>104.9599990844727</v>
+        <v>104.7900009155273</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>112.2749996948242</v>
+        <v>112.2715997314453</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>101.230449924469</v>
+        <v>101.2295999336243</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>65.05409098398465</v>
+        <v>64.93240438722938</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.1853189776077493</v>
+        <v>0.1833991790409899</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.1314853089803814</v>
+        <v>-0.1328919963704662</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.0043057787680036</v>
+        <v>0.0026791577224531</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.6752629448646275</v>
+        <v>0.6617018373704155</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.7656723428935024</v>
+        <v>-0.7683845643923448</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>1.44093528775813</v>
+        <v>1.43008640176276</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>1.911196160245703</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>562461</v>
+        <v>566314</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>1509217.22</v>
+        <v>1509294.28</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.3726839268372514</v>
+        <v>0.3752177474627413</v>
       </c>
       <c r="P12" s="6" t="n">
         <v>0</v>
@@ -5574,7 +5700,7 @@
         <v>5.971429007393973</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>0.0568924262526728</v>
+        <v>0.0569847213972984</v>
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
@@ -5589,46 +5715,46 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>238.6300964355469</v>
+        <v>239.8249969482422</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>227.4138018798828</v>
+        <v>227.4376998901367</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>161.8343006896973</v>
+        <v>161.8402751922607</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>41.24271373225548</v>
+        <v>41.60886297383517</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.0485622632335516</v>
+        <v>-0.0437980970347294</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.495925840297531</v>
+        <v>0.5034164401012673</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.5289939465423255</v>
+        <v>0.5366501293873294</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.371738486369566</v>
+        <v>5.467058185387998</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>10.04373670967382</v>
+        <v>10.06280064947751</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>-4.671998223304254</v>
+        <v>-4.595742464089508</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>-4.078359216969876</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>2375619</v>
+        <v>2390480</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>8663914.380000001</v>
+        <v>8664211.6</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2741969617663742</v>
+        <v>0.2759027722730133</v>
       </c>
       <c r="P13" s="6" t="n">
         <v>0.06596166699561611</v>
@@ -5642,7 +5768,7 @@
         <v>26.78535788399833</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>0.1122463523423708</v>
+        <v>0.111687097778965</v>
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
@@ -5657,46 +5783,46 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>358.5450134277344</v>
+        <v>358.0578918457031</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>372.2721008300781</v>
+        <v>372.2623583984375</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>319.9723249053955</v>
+        <v>319.9698892974853</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>60.08777128483414</v>
+        <v>59.76929787069184</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.0031555251088707</v>
+        <v>-0.0045098444815091</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.077002822034881</v>
+        <v>0.0755395990116232</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.080410502181824</v>
+        <v>0.07894264946220431</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-2.006390614353677</v>
+        <v>-2.045249316054196</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-2.642320293225944</v>
+        <v>-2.650092033566048</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.6359296788722668</v>
+        <v>0.6048427175118514</v>
       </c>
       <c r="L14" s="6" t="n">
         <v>0.5974640052565006</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>8529115</v>
+        <v>8698157</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>31762052.3</v>
+        <v>31765433.14</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.2685316087084209</v>
+        <v>0.2738245992637517</v>
       </c>
       <c r="P14" s="6" t="n">
         <v>-0.0040282924977889</v>
@@ -5710,7 +5836,7 @@
         <v>9.963572910853795</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>0.0277889038690032</v>
+        <v>0.0278267094169994</v>
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
@@ -5725,46 +5851,46 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>107.375</v>
+        <v>107.2399978637695</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>117.428699798584</v>
+        <v>117.4259997558594</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>63.21487497329712</v>
+        <v>63.21419996261596</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>31.35155293469214</v>
+        <v>31.21248198408246</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.1380348377374095</v>
+        <v>-0.1391185829133042</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.6827299434120371</v>
+        <v>0.6806142541262667</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1.437017627173527</v>
+        <v>1.43395357515304</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-2.0096641786497</v>
+        <v>-2.020433579830481</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>1.408045230997821</v>
+        <v>1.405891350761665</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-3.417709409647521</v>
+        <v>-3.426324930592146</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>-3.642499733942029</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>57992221</v>
+        <v>58543794</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>129992604.42</v>
+        <v>130003635.88</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.4461193870124323</v>
+        <v>0.4503242821149934</v>
       </c>
       <c r="P15" s="6" t="n">
         <v>0.0469355722360184</v>
@@ -5778,7 +5904,7 @@
         <v>9.479286193847656</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>0.0882820600125509</v>
+        <v>0.0883931964068994</v>
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
@@ -5793,46 +5919,46 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>39.22909927368164</v>
+        <v>39.46440124511719</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>54.8999821472168</v>
+        <v>54.90468818664551</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>48.68879553794861</v>
+        <v>48.68997204780579</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>17.28480087008961</v>
+        <v>17.96308832256679</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-0.3218824492928798</v>
+        <v>-0.3178149993768558</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.0970106575776734</v>
+        <v>0.1035906906447852</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.2300471307899073</v>
+        <v>-0.2254288389761277</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-4.181078467160411</v>
+        <v>-4.162307939524524</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-2.739789825135545</v>
+        <v>-2.736035719608368</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-1.441288642024866</v>
+        <v>-1.426272219916156</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>-1.449196603544823</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>10044903</v>
+        <v>10149586</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>28830504.06</v>
+        <v>28832597.72</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.3484123267180921</v>
+        <v>0.3520177438940802</v>
       </c>
       <c r="P16" s="6" t="n">
         <v>0.0298353862022756</v>
@@ -5846,7 +5972,7 @@
         <v>3.701071330479213</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>0.0943450499502602</v>
+        <v>0.0937825283979732</v>
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
@@ -5861,46 +5987,46 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>7.820000171661377</v>
+        <v>7.835000038146973</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>8.697199954986573</v>
+        <v>8.697499952316285</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>8.190649969577789</v>
+        <v>8.190724968910217</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>44.40366879365192</v>
+        <v>44.55626486353297</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-0.029174441292498</v>
+        <v>-0.0273122605454708</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.1645298655451619</v>
+        <v>-0.162927315648176</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.0498176662672744</v>
+        <v>-0.0479950821457789</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.0322851046196444</v>
+        <v>0.0334816751655058</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.1071113718218703</v>
+        <v>0.1073506859310426</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.0748262672022259</v>
+        <v>-0.0738690107655368</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>-0.0068890358413925</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>660169</v>
+        <v>666120</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1050925.38</v>
+        <v>1051044.4</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.6281787580389391</v>
+        <v>0.6337696104940953</v>
       </c>
       <c r="P17" s="6" t="n">
         <v>0.018661516252568</v>
@@ -5914,7 +6040,7 @@
         <v>0.6941427503313337</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>0.0887650556385936</v>
+        <v>0.08859511767092509</v>
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
@@ -5929,46 +6055,46 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1157.2099609375</v>
+        <v>1156.849975585938</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1097.819801025391</v>
+        <v>1097.812601318359</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1000.578852844238</v>
+        <v>1000.57705291748</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>58.0041452805042</v>
+        <v>57.93754253826302</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.0213680149492496</v>
+        <v>0.021050287366229</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.2544281419376692</v>
+        <v>0.2540379139142954</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.0704995013297873</v>
+        <v>0.07016648990373479</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>27.83825829340026</v>
+        <v>27.80954151321862</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>34.6545445015184</v>
+        <v>34.64880114548208</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-6.816286208118143</v>
+        <v>-6.839259632263456</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>-3.468572913063639</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>1303164</v>
+        <v>1317903</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>3185963.28</v>
+        <v>3186258.06</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.4090329628657867</v>
+        <v>0.413620923096229</v>
       </c>
       <c r="P18" s="6" t="n">
         <v>-0.013419399271567</v>
@@ -5982,7 +6108,7 @@
         <v>41.49965122767857</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>0.0358618164624664</v>
+        <v>0.0358729758425756</v>
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
@@ -5997,46 +6123,46 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>15.10999965667725</v>
+        <v>15.15499973297119</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>27.4556000328064</v>
+        <v>27.45650003433228</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>19.02117503166198</v>
+        <v>19.02140003204346</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>23.97503582866533</v>
+        <v>24.09476173102698</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.4323816987110064</v>
+        <v>-0.4306912375962335</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.361639222307808</v>
+        <v>-0.3597380784062913</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.2130208824864672</v>
+        <v>-0.2106771286059566</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-3.406560278756281</v>
+        <v>-3.402970529080413</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-3.194342417953994</v>
+        <v>-3.193624468018821</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.2122178608022866</v>
+        <v>-0.2093460610615922</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>-0.2400474448421516</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>5024598</v>
+        <v>5058235</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>14267139.96</v>
+        <v>14267812.7</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.352179765116708</v>
+        <v>0.3545207037936516</v>
       </c>
       <c r="P19" s="6" t="n">
         <v>0.0323432829789085</v>
@@ -6050,7 +6176,7 @@
         <v>1.624493053981236</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.1075111244799637</v>
+        <v>0.1071918893173578</v>
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
@@ -6065,46 +6191,46 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>223.2899932861328</v>
+        <v>224</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>233.8516000366211</v>
+        <v>233.8658001708984</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>128.1957001495361</v>
+        <v>128.1992501831055</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>33.76812818833493</v>
+        <v>34.04083201590227</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.201680430672074</v>
+        <v>-0.1991419727425776</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.668459913555193</v>
+        <v>0.6737652016382305</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>1.693811013756841</v>
+        <v>1.702376663643381</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-4.961502110938653</v>
+        <v>-4.904863398721346</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>4.132097880258479</v>
+        <v>4.143425622701941</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-9.093599991197133</v>
+        <v>-9.048289021423289</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>-9.60956168128553</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>12488233</v>
+        <v>12583967</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>45223758.66</v>
+        <v>45225673.34</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.2761431904386516</v>
+        <v>0.2782483061201892</v>
       </c>
       <c r="P20" s="6" t="n">
         <v>0.0645198535414377</v>
@@ -6118,7 +6244,7 @@
         <v>21.60285949707031</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>0.0967479965364481</v>
+        <v>0.0964413370404924</v>
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
@@ -6133,46 +6259,46 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>982.6099853515624</v>
+        <v>985.6799926757812</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>916.7272009277344</v>
+        <v>916.7886010742188</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>472.4410002136231</v>
+        <v>472.4563502502442</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>44.75504296621285</v>
+        <v>45.01109675160277</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.0010187345431718</v>
+        <v>0.0041462570521437</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>1.110144692745741</v>
+        <v>1.11673750144753</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1.840980713052704</v>
+        <v>1.849856901700345</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>9.404691083872422</v>
+        <v>9.649591953040954</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>34.40775650887971</v>
+        <v>34.45673668271343</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-25.00306542500729</v>
+        <v>-24.80714472967248</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>-28.83193491040208</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>21197929</v>
+        <v>21331931</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>53935262.58</v>
+        <v>53937942.62</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.3930254157668736</v>
+        <v>0.3954902609149611</v>
       </c>
       <c r="P21" s="6" t="n">
         <v>0.0543756800501934</v>
@@ -6186,7 +6312,7 @@
         <v>89.7650146484375</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>0.09135365606560671</v>
+        <v>0.09106912518814179</v>
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
@@ -6201,46 +6327,46 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>195.7400054931641</v>
+        <v>196.1999969482422</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>224.0214001464844</v>
+        <v>224.030599975586</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>136.7471754837036</v>
+        <v>136.749475440979</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>30.19478996682716</v>
+        <v>30.26414306552548</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-0.1576002540066962</v>
+        <v>-0.1556206040933297</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.2087192944435545</v>
+        <v>0.2115597998662006</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.8237212536460516</v>
+        <v>0.8280070213459552</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-6.521435266102856</v>
+        <v>-6.484740791053866</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.4679843316691616</v>
+        <v>0.4753232266789595</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-6.989419597772017</v>
+        <v>-6.960064017732826</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>-6.66147091221397</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>11903657</v>
+        <v>12109281</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>17935331.14</v>
+        <v>17939443.62</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6636987578920163</v>
+        <v>0.6750087269428927</v>
       </c>
       <c r="P22" s="6" t="n">
         <v>0.0310198990532244</v>
@@ -6254,7 +6380,7 @@
         <v>25.56014360700335</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>0.1305821134652824</v>
+        <v>0.1302759633260654</v>
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
@@ -6269,46 +6395,46 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>211.0950012207031</v>
+        <v>211.25</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>209.315100402832</v>
+        <v>209.318200378418</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>191.9665754699707</v>
+        <v>191.9673504638672</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>60.21059301407551</v>
+        <v>60.32419239286454</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.028778199274027</v>
+        <v>0.0295335907524258</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.07422017770887369</v>
+        <v>0.07500893544959771</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.141424237233821</v>
+        <v>0.1422623402794072</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.6428962429174874</v>
+        <v>-0.6305316679308532</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-2.269917779856038</v>
+        <v>-2.267444864858712</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1.627021536938551</v>
+        <v>1.636913196927858</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>1.206196025562167</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>70491184</v>
+        <v>71254526</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>157796587.68</v>
+        <v>157811854.52</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.4467218527117392</v>
+        <v>0.4515156748948139</v>
       </c>
       <c r="P23" s="6" t="n">
         <v>0.0229450115312453</v>
@@ -6322,7 +6448,7 @@
         <v>6.875713893345424</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>0.0325716566170923</v>
+        <v>0.0325477580750079</v>
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
@@ -6337,46 +6463,46 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>91.63009643554688</v>
+        <v>91.68000030517578</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>106.6392013549805</v>
+        <v>106.640199432373</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>104.4498501586914</v>
+        <v>104.4500996780396</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>17.43425787840226</v>
+        <v>17.58944999670975</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>-0.0924118733511427</v>
+        <v>-0.0919175798677687</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.210493724254244</v>
+        <v>-0.2100637408777261</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.1654058140864097</v>
+        <v>-0.1649512747912757</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-4.110923785817192</v>
+        <v>-4.106942850348219</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-3.342633373790195</v>
+        <v>-3.341837186696401</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.7682904120269969</v>
+        <v>-0.7651056636518181</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>-0.7934742332941171</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>2599321</v>
+        <v>2612175</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3255704.42</v>
+        <v>3255961.5</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.7983897383411729</v>
+        <v>0.802274535494354</v>
       </c>
       <c r="P24" s="6" t="n">
         <v>0.0177384274683925</v>
@@ -6390,7 +6516,7 @@
         <v>4.48357173374721</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>0.048931212649121</v>
+        <v>0.04890457808489</v>
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
@@ -6405,46 +6531,46 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>25.79999923706055</v>
+        <v>25.86009979248047</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>35.87940006256103</v>
+        <v>35.88060207366944</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>25.36974997997284</v>
+        <v>25.37005048274994</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>41.6717492429667</v>
+        <v>41.82511788429533</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.1717496130653933</v>
+        <v>-0.1698202212144808</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.239610993073733</v>
+        <v>-0.2378396828798231</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.0141508921165698</v>
+        <v>0.0165133352831674</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-2.441692614073304</v>
+        <v>-2.436898267771998</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-2.395130151055999</v>
+        <v>-2.394171281795738</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.0465624630173051</v>
+        <v>-0.0427269859762597</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>-0.0149246408257801</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>2822304</v>
+        <v>2895182</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>13305000.08</v>
+        <v>13306457.64</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.2121235612950105</v>
+        <v>0.2175772153887832</v>
       </c>
       <c r="P25" s="6" t="n">
         <v>0.0084746235925221</v>
@@ -6458,7 +6584,7 @@
         <v>2.376357078552246</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>0.0921068662334964</v>
+        <v>0.0918928038801782</v>
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
@@ -6473,46 +6599,46 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>13.72000026702881</v>
+        <v>13.71000003814697</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>11.47260004043579</v>
+        <v>11.47240003585815</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>9.128325011730194</v>
+        <v>9.128275010585783</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>75.17084129057541</v>
+        <v>75.11415241761875</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.2088105555862711</v>
+        <v>0.2079294781813607</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.5608646560376644</v>
+        <v>0.559726973566079</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.5990676444088565</v>
+        <v>0.5979021165567866</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.6786193294539125</v>
+        <v>0.6778215903978122</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.6465052521580432</v>
+        <v>0.6463457043468233</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.0321140772958692</v>
+        <v>0.0314758860509889</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>0.042571941463545</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>156045</v>
+        <v>157103</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>663262.9</v>
+        <v>663284.0600000001</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.235268699636298</v>
+        <v>0.2368562874856362</v>
       </c>
       <c r="P26" s="6" t="n">
         <v>-0.0110537672736636</v>
@@ -6526,7 +6652,7 @@
         <v>0.6038284982953753</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>0.0440108226343453</v>
+        <v>0.0440429246254756</v>
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
@@ -6541,46 +6667,46 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>79.86000061035156</v>
+        <v>79.84999847412109</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>107.0353999328613</v>
+        <v>107.0351998901367</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>77.06885011672973</v>
+        <v>77.06880010604858</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>38.11896320533445</v>
+        <v>38.10932385566196</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-0.2200410090204048</v>
+        <v>-0.2201386956723248</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.1057878601566444</v>
+        <v>0.1056493647805518</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.09146758561955499</v>
+        <v>-0.0915813755633188</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-7.624541965952915</v>
+        <v>-7.625339857162189</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-6.246168436171407</v>
+        <v>-6.246328014413261</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-1.378373529781509</v>
+        <v>-1.379011842748928</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>-1.60128212643402</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>10563231</v>
+        <v>10652271</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>28177556.62</v>
+        <v>28179337.42</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.3748810140799213</v>
+        <v>0.3780170853995899</v>
       </c>
       <c r="P27" s="6" t="n">
         <v>0.0264563885114627</v>
@@ -6594,7 +6720,7 @@
         <v>7.732856750488281</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>0.0968301614248414</v>
+        <v>0.09684229052295409</v>
       </c>
       <c r="T27" s="6" t="inlineStr">
         <is>
@@ -6609,46 +6735,46 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>18.69499969482422</v>
+        <v>18.68499946594238</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>16.94949993133545</v>
+        <v>16.94929992675781</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>21.97365002155304</v>
+        <v>21.97360002040863</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>62.99719808877189</v>
+        <v>62.92860938357886</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.1275633160947209</v>
+        <v>0.1269601659784451</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.0438302542769444</v>
+        <v>0.0432718942006165</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.297180472679705</v>
+        <v>-0.297556421128518</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.415255079455278</v>
+        <v>0.4144573403991778</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.373693506839594</v>
+        <v>0.373533959028374</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.0415615726156839</v>
+        <v>0.0409233813708038</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>0.0328078631428616</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>57235365</v>
+        <v>58380159</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>76338785.3</v>
+        <v>76361681.18000001</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.7497547252693841</v>
+        <v>0.7645216566459045</v>
       </c>
       <c r="P28" s="6" t="n">
         <v>0.0044125718372439</v>
@@ -6662,7 +6788,7 @@
         <v>0.9414285932268416</v>
       </c>
       <c r="S28" s="6" t="n">
-        <v>0.0503572403634475</v>
+        <v>0.0503841916047579</v>
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
@@ -6677,46 +6803,46 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>6.414999961853027</v>
+        <v>6.429999828338623</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>5.934499988555908</v>
+        <v>5.93479998588562</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>4.497025005817413</v>
+        <v>4.497100005149841</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>62.57668446039076</v>
+        <v>62.8078769713569</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.2985829731877558</v>
+        <v>0.301619383372341</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.0538348431652393</v>
+        <v>-0.0516224735455606</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.3976034310665943</v>
+        <v>0.4008713757260598</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.3311057457533479</v>
+        <v>0.3323023162992076</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.3109713687168909</v>
+        <v>0.3112106828260628</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.020134377036457</v>
+        <v>0.0210916334731448</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>0.0646032293833483</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>306591</v>
+        <v>313091</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>1212263.82</v>
+        <v>1212393.82</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2529078200156134</v>
+        <v>0.2582419959877393</v>
       </c>
       <c r="P29" s="6" t="n">
         <v>0.0046656626141934</v>
@@ -6730,7 +6856,7 @@
         <v>0.6430713449205671</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>0.1002449491417939</v>
+        <v>0.1000110983030497</v>
       </c>
       <c r="T29" s="6" t="inlineStr">
         <is>
@@ -6745,46 +6871,46 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>395.7807922363281</v>
+        <v>395.7799987792969</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>409.9186151123047</v>
+        <v>409.9185992431641</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>417.7494039916992</v>
+        <v>417.7494000244141</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>54.21071674379002</v>
+        <v>54.21050082981659</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-0.0262018075224783</v>
+        <v>-0.0262037597825122</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.08671273742666601</v>
+        <v>0.0867105587967795</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.1184497510488548</v>
+        <v>-0.1184515183712139</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-1.327180151083041</v>
+        <v>-1.327243446800594</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-1.257508024353691</v>
+        <v>-1.257520683497202</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.0696721267293503</v>
+        <v>-0.0697227633033923</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>0.3816312784934397</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>15571986</v>
+        <v>15725469</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>48280729.72</v>
+        <v>48283799.38</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.3225300464659174</v>
+        <v>0.3256883095764366</v>
       </c>
       <c r="P30" s="6" t="n">
         <v>0.0109940121352903</v>
@@ -6798,7 +6924,7 @@
         <v>18.56714085170201</v>
       </c>
       <c r="S30" s="6" t="n">
-        <v>0.046912688073592</v>
+        <v>0.0469127821238278</v>
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
@@ -6813,46 +6939,46 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>422.989990234375</v>
+        <v>423.4599914550781</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>425.0452001953125</v>
+        <v>425.0546002197266</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>349.73625</v>
+        <v>349.7386000061035</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>45.80252323519223</v>
+        <v>45.96163923757332</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-0.0022173530008412</v>
+        <v>-0.0011086765004205</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.1134538259075421</v>
+        <v>0.1146910293153182</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.2749495260011116</v>
+        <v>0.2763661737880329</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>1.375541336259005</v>
+        <v>1.413034311129877</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>5.416488805626193</v>
+        <v>5.423987400600367</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-4.040947469367188</v>
+        <v>-4.01095308947049</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>-3.711786865119478</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9421048</v>
+        <v>9541232</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>13663824.96</v>
+        <v>13666228.64</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.6894883407522808</v>
+        <v>0.6981613034098922</v>
       </c>
       <c r="P31" s="6" t="n">
         <v>0.0220361706931489</v>
@@ -6866,7 +6992,7 @@
         <v>19.97285679408482</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>0.0472182729029073</v>
+        <v>0.04716586500995</v>
       </c>
       <c r="T31" s="6" t="inlineStr">
         <is>
@@ -6881,46 +7007,46 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>303.9100036621094</v>
+        <v>303.8349914550781</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>324.2400012207031</v>
+        <v>324.2385009765625</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>238.4761003112793</v>
+        <v>238.4757252502441</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>45.6853713981408</v>
+        <v>45.66485867189928</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.0034338447574493</v>
+        <v>0.003186173452135</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.0212553730828108</v>
+        <v>-0.0214969505027718</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.7873904948772719</v>
+        <v>0.7869493244510541</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-1.932108565372118</v>
+        <v>-1.938092445135282</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-1.18606556518788</v>
+        <v>-1.187262341140513</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.746043000184238</v>
+        <v>-0.7508301039947693</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>-0.1480541656201379</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>2035475</v>
+        <v>2048915</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>6150207.5</v>
+        <v>6150476.3</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3309603781661025</v>
+        <v>0.3331311105125306</v>
       </c>
       <c r="P32" s="6" t="n">
         <v>0.031582057136426</v>
@@ -6934,7 +7060,7 @@
         <v>21.269287109375</v>
       </c>
       <c r="S32" s="6" t="n">
-        <v>0.0699854787702955</v>
+        <v>0.0700027571133776</v>
       </c>
       <c r="T32" s="6" t="inlineStr">
         <is>
@@ -6949,46 +7075,46 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>881.9500122070312</v>
+        <v>884.8900146484375</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>877.2619970703125</v>
+        <v>877.3207971191406</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>479.5865999603271</v>
+        <v>479.6012999725342</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>38.17454872190672</v>
+        <v>38.44778386563386</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-0.0527259483790617</v>
+        <v>-0.0495681866171711</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.6533256001998196</v>
+        <v>0.6588370024717727</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1.743405443782129</v>
+        <v>1.752550654497987</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-3.714404082408805</v>
+        <v>-3.479873973122949</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>11.28890387762027</v>
+        <v>11.33580989947744</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-15.00330796002907</v>
+        <v>-14.81568387260039</v>
       </c>
       <c r="L33" s="6" t="n">
         <v>-17.58862389405815</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>2140328</v>
+        <v>2183994</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>4342050.56</v>
+        <v>4342923.88</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.4929302343268891</v>
+        <v>0.5028856273667869</v>
       </c>
       <c r="P33" s="6" t="n">
         <v>0.0451049293978258</v>
@@ -7002,7 +7128,7 @@
         <v>84.29928588867188</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>0.0955828388478816</v>
+        <v>0.0952652696868362</v>
       </c>
       <c r="T33" s="6" t="inlineStr">
         <is>
@@ -7017,46 +7143,46 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>27.80999946594238</v>
+        <v>27.84499931335449</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>33.45659980773926</v>
+        <v>33.4572998046875</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>34.37749989509582</v>
+        <v>34.37767489433288</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>27.58339839891339</v>
+        <v>27.78904304325279</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>-0.0869993334924669</v>
+        <v>-0.0858502905356681</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.0224264222754753</v>
+        <v>0.0237131813354161</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.07669327054872049</v>
+        <v>-0.0755312570547992</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-1.883844745599575</v>
+        <v>-1.881052734979807</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-1.848369790575453</v>
+        <v>-1.8478113884515</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.0354749550241217</v>
+        <v>-0.0332413465283076</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>-0.1129581202809464</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>12005690</v>
+        <v>12093081</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>55532117.8</v>
+        <v>55533865.62</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2161936276811687</v>
+        <v>0.2177604757923567</v>
       </c>
       <c r="P34" s="6" t="n">
         <v>0.0112075006381963</v>
@@ -7070,7 +7196,7 @@
         <v>1.774999754769462</v>
       </c>
       <c r="S34" s="6" t="n">
-        <v>0.06382595429184459</v>
+        <v>0.0637457280854796</v>
       </c>
       <c r="T34" s="6" t="inlineStr">
         <is>
@@ -7085,46 +7211,46 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>268.3299865722656</v>
+        <v>268.0299987792969</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>226.1057995605469</v>
+        <v>226.0997998046875</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>160.4410001373291</v>
+        <v>160.4395001983643</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>75.86654638577177</v>
+        <v>75.78787063755613</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.1671596072033168</v>
+        <v>0.1658547450852958</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>1.426788345056187</v>
+        <v>1.424075242100623</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1.120012540248417</v>
+        <v>1.117642406775303</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>12.10213126982214</v>
+        <v>12.07820061967075</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>11.57954555399896</v>
+        <v>11.57475942396868</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.5225857158231797</v>
+        <v>0.5034411957020701</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>0.3955764881293149</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>2290189</v>
+        <v>2297589</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>6066099.78</v>
+        <v>6066247.78</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.3775389596377526</v>
+        <v>0.3787496131587292</v>
       </c>
       <c r="P35" s="6" t="n">
         <v>-0.0192129762097973</v>
@@ -7138,7 +7264,7 @@
         <v>13.84728785923549</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v>0.0516054431192176</v>
+        <v>0.051663201590497</v>
       </c>
       <c r="T35" s="6" t="inlineStr">
         <is>
@@ -7153,7 +7279,7 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>185.1950073242188</v>
+        <v>184.3399963378907</v>
       </c>
       <c r="C36" s="6" t="inlineStr"/>
       <c r="D36" s="6" t="inlineStr"/>
@@ -7162,19 +7288,19 @@
       <c r="G36" s="6" t="inlineStr"/>
       <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" s="6" t="n">
-        <v>0.477823280405488</v>
+        <v>0.4096172757981549</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.089506568990131</v>
+        <v>-0.1031477699115976</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.567329849395619</v>
+        <v>0.5127650457097526</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>-0.9253561253561428</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>49507041</v>
+        <v>49818486</v>
       </c>
       <c r="N36" s="6" t="inlineStr"/>
       <c r="O36" s="6" t="inlineStr"/>
@@ -7201,46 +7327,46 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>8.569999694824219</v>
+        <v>8.595000267028809</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>10.93840002059936</v>
+        <v>10.93890003204346</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>18.45029997348785</v>
+        <v>18.45042497634888</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>20.71610473444554</v>
+        <v>21.21982595865489</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-0.1334682105840102</v>
+        <v>-0.1309403469503685</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.1639024687976371</v>
+        <v>-0.1614633885825552</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.5654158218443462</v>
+        <v>-0.5641480443050408</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.6484871193453117</v>
+        <v>-0.6464927717050593</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.5323112331881235</v>
+        <v>-0.531912363660073</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.1161758861571882</v>
+        <v>-0.1145804080449862</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>-0.1257283657885731</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>16348850</v>
+        <v>16468080</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>33061893</v>
+        <v>33064277.6</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.4944922542698931</v>
+        <v>0.4980625979259259</v>
       </c>
       <c r="P37" s="6" t="n">
         <v>0.0299401183926648</v>
@@ -7254,7 +7380,7 @@
         <v>0.6735711097717285</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>0.07859639833809159</v>
+        <v>0.0783677822972976</v>
       </c>
       <c r="T37" s="6" t="inlineStr">
         <is>
@@ -7269,46 +7395,46 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>46.04000091552734</v>
+        <v>46.15000152587891</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>60.62539985656738</v>
+        <v>60.62759986877441</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>81.45839981079102</v>
+        <v>81.45894981384278</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>23.88758665037871</v>
+        <v>24.27772708696961</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-0.1991650796425027</v>
+        <v>-0.1972516928423634</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.214066243147155</v>
+        <v>-0.2121884588024429</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.5508292593607089</v>
+        <v>-0.5497560826743522</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-3.815820073577093</v>
+        <v>-3.80704509611315</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-3.478494297521382</v>
+        <v>-3.476739302028593</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.3373257760557111</v>
+        <v>-0.3303057940845564</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>-0.3462640816307631</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>3888785</v>
+        <v>3913687</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>12377495.7</v>
+        <v>12377993.74</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.3141818906065142</v>
+        <v>0.3161810453460449</v>
       </c>
       <c r="P38" s="6" t="n">
         <v>0.0251036384349932</v>
@@ -7322,7 +7448,7 @@
         <v>3.443371636526925</v>
       </c>
       <c r="S38" s="6" t="n">
-        <v>0.0747908681158523</v>
+        <v>0.0746126007080635</v>
       </c>
       <c r="T38" s="6" t="inlineStr">
         <is>
@@ -7337,46 +7463,46 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>7.744999885559082</v>
+        <v>7.751699924468994</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>9.765899991989135</v>
+        <v>9.766033992767332</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>12.02977501392364</v>
+        <v>12.02980851411819</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>26.82926709831341</v>
+        <v>26.95491660880916</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>-0.1535518897865124</v>
+        <v>-0.1528196450663768</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.119886395716962</v>
+        <v>-0.1191250276755196</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.4974042853829266</v>
+        <v>-0.4969695002449477</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.5922978819663278</v>
+        <v>-0.5917634059279315</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.4880183444394153</v>
+        <v>-0.487911449231736</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.1042795375269125</v>
+        <v>-0.1038519566961955</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>-0.1257187896488844</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>31976126</v>
+        <v>32649586</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>37277732.52</v>
+        <v>37291201.72</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.8577808744897341</v>
+        <v>0.8755305405588308</v>
       </c>
       <c r="P39" s="6" t="n">
         <v>0.0100267124430337</v>
@@ -7390,7 +7516,7 @@
         <v>0.5577142919812884</v>
       </c>
       <c r="S39" s="6" t="n">
-        <v>0.0720095933146717</v>
+        <v>0.07194735315034689</v>
       </c>
       <c r="T39" s="6" t="inlineStr">
         <is>
@@ -7438,13 +7564,13 @@
         <v>0.0561779742976243</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>20502401</v>
+        <v>20865622</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>28654316.02</v>
+        <v>28661580.44</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.7155083019845888</v>
+        <v>0.7279997013311943</v>
       </c>
       <c r="P40" s="6" t="n">
         <v>-0.0154083063419491</v>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -480,7 +480,7 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>370.9100036621094</v>
+        <v>370.0549926757813</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.082723417254077</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.2825782202322912</v>
+        <v>0.2836450710782</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>75</v>
@@ -573,13 +573,13 @@
         <v>12</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.0323528615608106</v>
+        <v>0.0324276127535283</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>278.0541599818638</v>
+        <v>277.1991489955358</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>510.1937691824777</v>
+        <v>509.3387581961496</v>
       </c>
     </row>
     <row r="3">
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>985.6799926757812</v>
+        <v>986.780029296875</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.0543756800501934</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.3954902609149611</v>
+        <v>0.3974323205734726</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>75</v>
@@ -614,13 +614,13 @@
         <v>12</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.0121743365891237</v>
+        <v>0.0121607649564518</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>806.1499633789062</v>
+        <v>807.25</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1254.975036621094</v>
+        <v>1256.075073242188</v>
       </c>
     </row>
     <row r="4">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>239.8249969482422</v>
+        <v>240</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.06596166699561611</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.2759027722730133</v>
+        <v>0.2778866728713306</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>75</v>
@@ -655,13 +655,13 @@
         <v>12</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.0500364855736442</v>
+        <v>0.05</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>186.2542811802456</v>
+        <v>186.4292842320033</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>320.1810706002371</v>
+        <v>320.356073651995</v>
       </c>
     </row>
   </sheetData>
@@ -675,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD40"/>
+  <dimension ref="A1:AF40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -700,14 +700,16 @@
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="21" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="23" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="17" customWidth="1" min="27" max="27"/>
-    <col width="35" customWidth="1" min="28" max="28"/>
-    <col width="35" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="29" max="29"/>
     <col width="35" customWidth="1" min="30" max="30"/>
+    <col width="35" customWidth="1" min="31" max="31"/>
+    <col width="35" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -823,40 +825,50 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>exit_action</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>exit_priority</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>exit_reason</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>position_count</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>open_slots</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>position_rule</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>add_more_signal</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>add_more_reason</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>decision_reasons</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>warnings</t>
         </is>
@@ -879,7 +891,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>182.3500061035156</v>
+        <v>182.3800048828125</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>89</v>
@@ -899,22 +911,22 @@
         <v>75</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>62.31512866084653</v>
+        <v>62.32894220433992</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.0151807899125376</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.3492585386965051</v>
+        <v>0.3518022926258758</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1.590327612314166</v>
+        <v>1.592242064326245</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>161.4255959647042</v>
+        <v>161.4555947440011</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>213.7366213117327</v>
+        <v>213.7666200910296</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>10.46220506940569</v>
@@ -934,25 +946,27 @@
       <c r="U2" s="2" t="inlineStr"/>
       <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="n">
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Y2" s="2" t="n">
+      <c r="AA2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -971,7 +985,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>211.25</v>
+        <v>211.3399963378907</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>89</v>
@@ -991,22 +1005,22 @@
         <v>75</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>60.32419239286454</v>
+        <v>60.3898539976604</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.0229450115312453</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.4515156748948139</v>
+        <v>0.4553032362727894</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1.636913196927858</v>
+        <v>1.642656552964186</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>200.9364291599818</v>
+        <v>201.0264254978725</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>225.0014277866908</v>
+        <v>225.0914241245815</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>6.875713893345424</v>
@@ -1015,7 +1029,7 @@
         <v>13.95</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.06604400000000001</v>
+        <v>0.066015</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>1.12</v>
@@ -1026,25 +1040,27 @@
       <c r="U3" s="2" t="inlineStr"/>
       <c r="V3" s="2" t="inlineStr"/>
       <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="n">
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Y3" s="2" t="n">
+      <c r="AA3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1063,7 +1079,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>556.2000122070312</v>
+        <v>556.010009765625</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>82</v>
@@ -1083,28 +1099,28 @@
         <v>50</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>55.98630573472487</v>
+        <v>55.95874423080636</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0.0624019610194614</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.4410737275619771</v>
+        <v>0.4423987360224728</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>-2.544331411452166</v>
+        <v>-2.556456923382285</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>499.1228594098772</v>
+        <v>498.932856968471</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>632.3028826032366</v>
+        <v>632.1128801618304</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>38.05143519810268</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>10.88</v>
+        <v>10.87</v>
       </c>
       <c r="R4" s="2" t="n">
         <v>0.019555</v>
@@ -1118,25 +1134,27 @@
       <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="n">
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Y4" s="2" t="n">
+      <c r="AA4" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1155,7 +1173,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>985.6799926757812</v>
+        <v>986.780029296875</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>82</v>
@@ -1175,22 +1193,22 @@
         <v>50</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>45.01109675160277</v>
+        <v>45.10226858546104</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0.0543756800501934</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.3954902609149611</v>
+        <v>0.3974323205734726</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-24.80714472967248</v>
+        <v>-24.73694296240046</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>806.1499633789062</v>
+        <v>807.25</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1254.975036621094</v>
+        <v>1256.075073242188</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>89.7650146484375</v>
@@ -1210,25 +1228,27 @@
       <c r="U5" s="2" t="inlineStr"/>
       <c r="V5" s="2" t="inlineStr"/>
       <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="n">
+      <c r="X5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Y5" s="2" t="n">
+      <c r="AA5" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
+      <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr">
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1247,7 +1267,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1156.849975585938</v>
+        <v>1157.300048828125</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>82</v>
@@ -1267,22 +1287,22 @@
         <v>50</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>57.93754253826302</v>
+        <v>58.02083686703796</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>-0.013419399271567</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.413620923096229</v>
+        <v>0.4153383493550943</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-6.839259632263456</v>
+        <v>-6.810537009400178</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1094.60049874442</v>
+        <v>1095.050571986607</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1239.849278041295</v>
+        <v>1240.299351283482</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>41.49965122767857</v>
@@ -1291,7 +1311,7 @@
         <v>13.95</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.01206</v>
+        <v>0.012055</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>1.12</v>
@@ -1302,25 +1322,27 @@
       <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" s="2" t="inlineStr"/>
       <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="n">
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Y6" s="2" t="n">
+      <c r="AA6" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1339,7 +1361,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7.664999961853027</v>
+        <v>7.667600154876709</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>82</v>
@@ -1359,22 +1381,22 @@
         <v>50</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>49.95178289261076</v>
+        <v>49.97684546433793</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>-0.0049382666628676</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.4873476996211151</v>
+        <v>0.4885043269260495</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-0.123540600848864</v>
+        <v>-0.1233746626046179</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>6.187785829816546</v>
+        <v>6.190386022840228</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>9.88082115990775</v>
+        <v>9.883421352931432</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>0.7386070660182408</v>
@@ -1394,25 +1416,27 @@
       <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="2" t="inlineStr"/>
       <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="n">
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Y7" s="2" t="n">
+      <c r="AA7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Z7" s="2" t="inlineStr">
+      <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
-      <c r="AC7" s="2" t="inlineStr">
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1431,7 +1455,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>370.9100036621094</v>
+        <v>370.0549926757813</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>82</v>
@@ -1451,28 +1475,28 @@
         <v>50</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46.31162813235188</v>
+        <v>46.18162304129646</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0.082723417254077</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.2825782202322912</v>
+        <v>0.2836450710782</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-11.12387293811257</v>
+        <v>-11.17843774179846</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>278.0541599818638</v>
+        <v>277.1991489955358</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>510.1937691824777</v>
+        <v>509.3387581961496</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>46.42792184012277</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
       <c r="R8" s="2" t="n">
         <v>0.01202</v>
@@ -1486,25 +1510,27 @@
       <c r="U8" s="2" t="inlineStr"/>
       <c r="V8" s="2" t="inlineStr"/>
       <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="n">
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Y8" s="2" t="n">
+      <c r="AA8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Z8" s="2" t="inlineStr">
+      <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
-      <c r="AC8" s="2" t="inlineStr">
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1523,7 +1549,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>16.84000015258789</v>
+        <v>16.86000061035156</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>79</v>
@@ -1543,22 +1569,22 @@
         <v>75</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>74.48015284749306</v>
+        <v>74.52830460284595</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>0.0098826338563442</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.2077549597178633</v>
+        <v>0.2092578568328409</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.1253684377216397</v>
+        <v>0.1266448202114016</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>13.84100001198905</v>
+        <v>13.86100046975272</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>21.33850036348615</v>
+        <v>21.35850082124983</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.499500070299421</v>
@@ -1576,37 +1602,51 @@
         <v>13.95</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>0.1175143466997992</v>
+        <v>0.1188415912537745</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="n">
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>No exit trigger</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="Y9" s="3" t="n">
+      <c r="AA9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z9" s="3" t="inlineStr">
+      <c r="AB9" s="3" t="inlineStr">
         <is>
           <t>Already held</t>
         </is>
       </c>
-      <c r="AA9" s="3" t="inlineStr">
+      <c r="AC9" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AB9" s="3" t="inlineStr">
+      <c r="AD9" s="3" t="inlineStr">
         <is>
           <t>Held, but not strong enough to add</t>
         </is>
       </c>
-      <c r="AC9" s="3" t="inlineStr">
+      <c r="AE9" s="3" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AD9" s="3" t="inlineStr">
+      <c r="AF9" s="3" t="inlineStr">
         <is>
           <t>RSI overbought</t>
         </is>
@@ -1629,7 +1669,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>13.71000003814697</v>
+        <v>13.6899995803833</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>79</v>
@@ -1649,28 +1689,28 @@
         <v>75</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>75.11415241761875</v>
+        <v>74.99999453168354</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>-0.0110537672736636</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.2368562874856362</v>
+        <v>0.2407317971659961</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.0314758860509889</v>
+        <v>0.0301995035612271</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>12.50234304155622</v>
+        <v>12.48234258379255</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>15.5214855330331</v>
+        <v>15.50148507526943</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.6038284982953753</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>6.34</v>
+        <v>6.33</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>0.462108</v>
@@ -1684,25 +1724,27 @@
       <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="n">
+      <c r="X10" s="3" t="inlineStr"/>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="Y10" s="3" t="n">
+      <c r="AA10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z10" s="3" t="inlineStr">
+      <c r="AB10" s="3" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
-      <c r="AC10" s="3" t="inlineStr">
+      <c r="AC10" s="3" t="inlineStr"/>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AD10" s="3" t="inlineStr">
+      <c r="AF10" s="3" t="inlineStr">
         <is>
           <t>RSI overbought</t>
         </is>
@@ -1725,7 +1767,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>268.0299987792969</v>
+        <v>267.8599853515625</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>79</v>
@@ -1745,22 +1787,22 @@
         <v>75</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>75.78787063755613</v>
+        <v>75.74305421730782</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>-0.0192129762097973</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.3787496131587292</v>
+        <v>0.38066052588573</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.5034411957020701</v>
+        <v>0.4925913359264129</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>247.2590669904436</v>
+        <v>247.0890535627093</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>295.7245744977678</v>
+        <v>295.5545610700335</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>13.84728785923549</v>
@@ -1769,7 +1811,7 @@
         <v>6.98</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.026026</v>
+        <v>0.026043</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>1.12</v>
@@ -1780,25 +1822,27 @@
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr"/>
       <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="n">
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="Y11" s="3" t="n">
+      <c r="AA11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z11" s="3" t="inlineStr">
+      <c r="AB11" s="3" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
-      <c r="AC11" s="3" t="inlineStr">
+      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AD11" s="3" t="inlineStr">
+      <c r="AF11" s="3" t="inlineStr">
         <is>
           <t>RSI overbought</t>
         </is>
@@ -1821,7 +1865,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>393.9299926757813</v>
+        <v>393.760009765625</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>79</v>
@@ -1841,22 +1885,22 @@
         <v>75</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>55.60892184553344</v>
+        <v>55.54740946415497</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0.030087289573326</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.3725360264533705</v>
+        <v>0.3741449206336948</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.28762758172099</v>
+        <v>3.276779669505886</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>371.4246433803014</v>
+        <v>371.2546604701451</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>423.9371250697545</v>
+        <v>423.7671421595982</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>15.00356619698661</v>
@@ -1865,7 +1909,7 @@
         <v>6.98</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.017708</v>
+        <v>0.017716</v>
       </c>
       <c r="S12" s="4" t="n">
         <v>1.12</v>
@@ -1876,25 +1920,27 @@
       <c r="U12" s="4" t="inlineStr"/>
       <c r="V12" s="4" t="inlineStr"/>
       <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="n">
+      <c r="X12" s="4" t="inlineStr"/>
+      <c r="Y12" s="4" t="inlineStr"/>
+      <c r="Z12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Y12" s="4" t="n">
+      <c r="AA12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Z12" s="4" t="inlineStr">
+      <c r="AB12" s="4" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="inlineStr">
+      <c r="AC12" s="4" t="inlineStr"/>
+      <c r="AD12" s="4" t="inlineStr"/>
+      <c r="AE12" s="4" t="inlineStr">
         <is>
           <t>Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AD12" s="4" t="inlineStr"/>
+      <c r="AF12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1913,7 +1959,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6.429999828338623</v>
+        <v>6.420000076293945</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>78</v>
@@ -1933,22 +1979,22 @@
         <v>75</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>62.8078769713569</v>
+        <v>62.65356173241101</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>0.0046656626141934</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2582419959877393</v>
+        <v>0.2593661301968964</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.0210916334731448</v>
+        <v>0.0204534726588978</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>5.143857138497489</v>
+        <v>5.133857386452811</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>8.359213863100324</v>
+        <v>8.349214111055646</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0.6430713449205671</v>
@@ -1968,25 +2014,27 @@
       <c r="U13" s="4" t="inlineStr"/>
       <c r="V13" s="4" t="inlineStr"/>
       <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="n">
+      <c r="X13" s="4" t="inlineStr"/>
+      <c r="Y13" s="4" t="inlineStr"/>
+      <c r="Z13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Y13" s="4" t="n">
+      <c r="AA13" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Z13" s="4" t="inlineStr">
+      <c r="AB13" s="4" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr"/>
-      <c r="AC13" s="4" t="inlineStr">
+      <c r="AC13" s="4" t="inlineStr"/>
+      <c r="AD13" s="4" t="inlineStr"/>
+      <c r="AE13" s="4" t="inlineStr">
         <is>
           <t>Strong trend; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AD13" s="4" t="inlineStr"/>
+      <c r="AF13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2005,7 +2053,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>239.8249969482422</v>
+        <v>240</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>75</v>
@@ -2025,22 +2073,22 @@
         <v>50</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>41.60886297383517</v>
+        <v>41.66210579173344</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>0.06596166699561611</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2759027722730133</v>
+        <v>0.2778866728713306</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.595742464089508</v>
+        <v>-4.584574178165363</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>186.2542811802456</v>
+        <v>186.4292842320033</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>320.1810706002371</v>
+        <v>320.356073651995</v>
       </c>
       <c r="P14" s="4" t="n">
         <v>26.78535788399833</v>
@@ -2060,25 +2108,27 @@
       <c r="U14" s="4" t="inlineStr"/>
       <c r="V14" s="4" t="inlineStr"/>
       <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="n">
+      <c r="X14" s="4" t="inlineStr"/>
+      <c r="Y14" s="4" t="inlineStr"/>
+      <c r="Z14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Y14" s="4" t="n">
+      <c r="AA14" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Z14" s="4" t="inlineStr">
+      <c r="AB14" s="4" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="inlineStr">
+      <c r="AC14" s="4" t="inlineStr"/>
+      <c r="AD14" s="4" t="inlineStr"/>
+      <c r="AE14" s="4" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="AD14" s="4" t="inlineStr"/>
+      <c r="AF14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2097,7 +2147,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>358.0578918457031</v>
+        <v>358.1199951171875</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>71</v>
@@ -2117,22 +2167,22 @@
         <v>75</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>59.76929787069184</v>
+        <v>59.81018252640515</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>-0.0040282924977889</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.2738245992637517</v>
+        <v>0.2760469549390547</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.6048427175118514</v>
+        <v>0.6088060032133988</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>343.1125324794224</v>
+        <v>343.1746357509068</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>377.9850376674107</v>
+        <v>378.0471409388951</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.963572910853795</v>
@@ -2150,37 +2200,51 @@
         <v>13.95</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>-0.0238873248859967</v>
+        <v>-0.0237180232399711</v>
       </c>
       <c r="V15" s="3" t="inlineStr"/>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="n">
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>No exit trigger</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="Y15" s="3" t="n">
+      <c r="AA15" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z15" s="3" t="inlineStr">
+      <c r="AB15" s="3" t="inlineStr">
         <is>
           <t>Already held</t>
         </is>
       </c>
-      <c r="AA15" s="3" t="inlineStr">
+      <c r="AC15" s="3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AB15" s="3" t="inlineStr">
+      <c r="AD15" s="3" t="inlineStr">
         <is>
           <t>Do not average down</t>
         </is>
       </c>
-      <c r="AC15" s="3" t="inlineStr">
+      <c r="AE15" s="3" t="inlineStr">
         <is>
           <t>Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AD15" s="3" t="inlineStr">
+      <c r="AF15" s="3" t="inlineStr">
         <is>
           <t>Do not average down</t>
         </is>
@@ -2189,12 +2253,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>CELC</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -2203,10 +2267,10 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>104.7900009155273</v>
+        <v>18.66410064697266</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -2217,31 +2281,31 @@
         <v>40</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>75</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>64.93240438722938</v>
+        <v>62.78444622690394</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0</v>
+        <v>0.0044125718372439</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0.3752177474627413</v>
+        <v>0.7704010989148591</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>1.43008640176276</v>
+        <v>0.0395896675676066</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>92.8471429007394</v>
+        <v>16.78124346051897</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>122.7042879377093</v>
+        <v>21.48838642665318</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>5.971429007393973</v>
+        <v>0.9414285932268416</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -2255,50 +2319,74 @@
       <c r="T16" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U16" s="5" t="inlineStr"/>
+      <c r="U16" s="5" t="n">
+        <v>0.0144289784832726</v>
+      </c>
       <c r="V16" s="5" t="inlineStr"/>
-      <c r="W16" s="5" t="inlineStr"/>
-      <c r="X16" s="5" t="n">
+      <c r="W16" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X16" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Y16" s="5" t="inlineStr">
+        <is>
+          <t>No exit trigger</t>
+        </is>
+      </c>
+      <c r="Z16" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y16" s="5" t="n">
+      <c r="AA16" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z16" s="5" t="inlineStr">
-        <is>
-          <t>6 open slot(s)</t>
-        </is>
-      </c>
-      <c r="AA16" s="5" t="inlineStr"/>
-      <c r="AB16" s="5" t="inlineStr"/>
+      <c r="AB16" s="5" t="inlineStr">
+        <is>
+          <t>Already held</t>
+        </is>
+      </c>
       <c r="AC16" s="5" t="inlineStr">
         <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AD16" s="5" t="inlineStr">
+        <is>
+          <t>Held, but not strong enough to add</t>
+        </is>
+      </c>
+      <c r="AE16" s="5" t="inlineStr">
+        <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AD16" s="5" t="inlineStr"/>
+      <c r="AF16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>18.68499946594238</v>
+        <v>423.1400146484375</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -2309,31 +2397,31 @@
         <v>40</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>62.92860938357886</v>
+        <v>45.85341478993548</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.0044125718372439</v>
+        <v>0.0220361706931489</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.7645216566459045</v>
+        <v>0.7037350139585496</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0.0409233813708038</v>
+        <v>-4.031373261746126</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>16.8021422794887</v>
+        <v>393.1807294573102</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>21.50928524562291</v>
+        <v>463.0857282366072</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0.9414285932268416</v>
+        <v>19.97285679408482</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -2347,48 +2435,40 @@
       <c r="T17" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U17" s="5" t="n">
-        <v>0.0155648686062401</v>
-      </c>
+      <c r="U17" s="5" t="inlineStr"/>
       <c r="V17" s="5" t="inlineStr"/>
       <c r="W17" s="5" t="inlineStr"/>
-      <c r="X17" s="5" t="n">
+      <c r="X17" s="5" t="inlineStr"/>
+      <c r="Y17" s="5" t="inlineStr"/>
+      <c r="Z17" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y17" s="5" t="n">
+      <c r="AA17" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z17" s="5" t="inlineStr">
-        <is>
-          <t>Already held</t>
-        </is>
-      </c>
-      <c r="AA17" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="AB17" s="5" t="inlineStr">
         <is>
-          <t>Held, but not strong enough to add</t>
-        </is>
-      </c>
-      <c r="AC17" s="5" t="inlineStr">
-        <is>
-          <t>MACD/volume acceleration</t>
-        </is>
-      </c>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AC17" s="5" t="inlineStr"/>
       <c r="AD17" s="5" t="inlineStr"/>
+      <c r="AE17" s="5" t="inlineStr">
+        <is>
+          <t>Positive momentum</t>
+        </is>
+      </c>
+      <c r="AF17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Data Storage</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -2397,7 +2477,7 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>423.4599914550781</v>
+        <v>884.3150024414062</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>65</v>
@@ -2408,7 +2488,7 @@
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>75</v>
@@ -2417,25 +2497,25 @@
         <v>50</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>45.96163923757332</v>
+        <v>38.39453407767014</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.0220361706931489</v>
+        <v>0.0451049293978258</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.6981613034098922</v>
+        <v>0.5080974678985236</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>-4.01095308947049</v>
+        <v>-14.8523798083197</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>393.5007062639509</v>
+        <v>757.8660736083984</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>463.4057050432478</v>
+        <v>1052.91357421875</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>19.97285679408482</v>
+        <v>84.29928588867188</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -2452,35 +2532,37 @@
       <c r="U18" s="5" t="inlineStr"/>
       <c r="V18" s="5" t="inlineStr"/>
       <c r="W18" s="5" t="inlineStr"/>
-      <c r="X18" s="5" t="n">
+      <c r="X18" s="5" t="inlineStr"/>
+      <c r="Y18" s="5" t="inlineStr"/>
+      <c r="Z18" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y18" s="5" t="n">
+      <c r="AA18" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z18" s="5" t="inlineStr">
+      <c r="AB18" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA18" s="5" t="inlineStr"/>
-      <c r="AB18" s="5" t="inlineStr"/>
-      <c r="AC18" s="5" t="inlineStr">
-        <is>
-          <t>Positive momentum</t>
-        </is>
-      </c>
+      <c r="AC18" s="5" t="inlineStr"/>
       <c r="AD18" s="5" t="inlineStr"/>
+      <c r="AE18" s="5" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum</t>
+        </is>
+      </c>
+      <c r="AF18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Data Storage</t>
+          <t>Data Centers</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2489,45 +2571,45 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>884.8900146484375</v>
+        <v>303.7799987792969</v>
       </c>
       <c r="E19" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>65</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>75</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>50</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>38.44778386563386</v>
+        <v>45.64983215523345</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.0451049293978258</v>
+        <v>0.031582057136426</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.5028856273667869</v>
+        <v>0.3352880878259753</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>-14.81568387260039</v>
+        <v>-0.7543396080901967</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>758.4410858154297</v>
+        <v>271.8760681152344</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>1053.488586425781</v>
+        <v>346.3185729980469</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>84.29928588867188</v>
+        <v>21.269287109375</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2544,35 +2626,33 @@
       <c r="U19" s="5" t="inlineStr"/>
       <c r="V19" s="5" t="inlineStr"/>
       <c r="W19" s="5" t="inlineStr"/>
-      <c r="X19" s="5" t="n">
+      <c r="X19" s="5" t="inlineStr"/>
+      <c r="Y19" s="5" t="inlineStr"/>
+      <c r="Z19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y19" s="5" t="n">
+      <c r="AA19" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z19" s="5" t="inlineStr">
+      <c r="AB19" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA19" s="5" t="inlineStr"/>
-      <c r="AB19" s="5" t="inlineStr"/>
-      <c r="AC19" s="5" t="inlineStr">
-        <is>
-          <t>Strong trend; Positive momentum</t>
-        </is>
-      </c>
+      <c r="AC19" s="5" t="inlineStr"/>
       <c r="AD19" s="5" t="inlineStr"/>
+      <c r="AE19" s="5" t="inlineStr"/>
+      <c r="AF19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Data Centers</t>
+          <t>Internet/E-Commerce</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2581,10 +2661,10 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>303.8349914550781</v>
+        <v>246.4400024414062</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -2595,31 +2675,31 @@
         <v>40</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>45.66485867189928</v>
+        <v>65.29396912736486</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.031582057136426</v>
+        <v>-0.0071974396379796</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.3331311105125306</v>
+        <v>0.3137200976709515</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>-0.7508301039947693</v>
+        <v>1.674360996701665</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>271.9310607910156</v>
+        <v>235.2232213701521</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>346.3735656738281</v>
+        <v>261.3957105364119</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>21.269287109375</v>
+        <v>7.47785404750279</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2636,40 +2716,46 @@
       <c r="U20" s="5" t="inlineStr"/>
       <c r="V20" s="5" t="inlineStr"/>
       <c r="W20" s="5" t="inlineStr"/>
-      <c r="X20" s="5" t="n">
+      <c r="X20" s="5" t="inlineStr"/>
+      <c r="Y20" s="5" t="inlineStr"/>
+      <c r="Z20" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y20" s="5" t="n">
+      <c r="AA20" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z20" s="5" t="inlineStr">
+      <c r="AB20" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA20" s="5" t="inlineStr"/>
-      <c r="AB20" s="5" t="inlineStr"/>
       <c r="AC20" s="5" t="inlineStr"/>
       <c r="AD20" s="5" t="inlineStr"/>
+      <c r="AE20" s="5" t="inlineStr">
+        <is>
+          <t>MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="AF20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>CELC</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Internet/E-Commerce</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>246.3350067138672</v>
+        <v>104.4499969482422</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>56</v>
@@ -2689,25 +2775,25 @@
         <v>75</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>65.12433937744606</v>
+        <v>64.68646542671178</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.0071974396379796</v>
+        <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.3120038893087236</v>
+        <v>0.3926476014849354</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>1.667660414659275</v>
+        <v>1.408388142881888</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>235.118225642613</v>
+        <v>92.50713893345426</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>261.2907148088728</v>
+        <v>122.3642839704241</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>7.47785404750279</v>
+        <v>5.971429007393973</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2724,25 +2810,27 @@
       <c r="U21" s="5" t="inlineStr"/>
       <c r="V21" s="5" t="inlineStr"/>
       <c r="W21" s="5" t="inlineStr"/>
-      <c r="X21" s="5" t="n">
+      <c r="X21" s="5" t="inlineStr"/>
+      <c r="Y21" s="5" t="inlineStr"/>
+      <c r="Z21" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y21" s="5" t="n">
+      <c r="AA21" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z21" s="5" t="inlineStr">
+      <c r="AB21" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA21" s="5" t="inlineStr"/>
-      <c r="AB21" s="5" t="inlineStr"/>
-      <c r="AC21" s="5" t="inlineStr">
+      <c r="AC21" s="5" t="inlineStr"/>
+      <c r="AD21" s="5" t="inlineStr"/>
+      <c r="AE21" s="5" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AD21" s="5" t="inlineStr"/>
+      <c r="AF21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2761,7 +2849,7 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>284.4100036621094</v>
+        <v>284.3699951171875</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>55</v>
@@ -2781,22 +2869,22 @@
         <v>50</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>28.62432369505791</v>
+        <v>28.61835280220669</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>0.0376936349020097</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.5547548299860414</v>
+        <v>0.5560909738241342</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-9.893997001332997</v>
+        <v>-9.896550253202626</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>225.6474304199219</v>
+        <v>225.607421875</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>372.5538635253906</v>
+        <v>372.5138549804688</v>
       </c>
       <c r="P22" s="5" t="n">
         <v>29.38128662109375</v>
@@ -2816,25 +2904,27 @@
       <c r="U22" s="5" t="inlineStr"/>
       <c r="V22" s="5" t="inlineStr"/>
       <c r="W22" s="5" t="inlineStr"/>
-      <c r="X22" s="5" t="n">
+      <c r="X22" s="5" t="inlineStr"/>
+      <c r="Y22" s="5" t="inlineStr"/>
+      <c r="Z22" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y22" s="5" t="n">
+      <c r="AA22" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z22" s="5" t="inlineStr">
+      <c r="AB22" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA22" s="5" t="inlineStr"/>
-      <c r="AB22" s="5" t="inlineStr"/>
-      <c r="AC22" s="5" t="inlineStr">
+      <c r="AC22" s="5" t="inlineStr"/>
+      <c r="AD22" s="5" t="inlineStr"/>
+      <c r="AE22" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="AD22" s="5" t="inlineStr"/>
+      <c r="AF22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2853,7 +2943,7 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>224</v>
+        <v>223.8999938964844</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>55</v>
@@ -2873,22 +2963,22 @@
         <v>50</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>34.04083201590227</v>
+        <v>34.00255700129621</v>
       </c>
       <c r="K23" s="5" t="n">
         <v>0.0645198535414377</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.2782483061201892</v>
+        <v>0.2791699060516664</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-9.048289021423289</v>
+        <v>-9.054671177317168</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>191.5957107543945</v>
+        <v>191.4957046508789</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>267.2057189941406</v>
+        <v>267.105712890625</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>21.60285949707031</v>
@@ -2908,25 +2998,27 @@
       <c r="U23" s="5" t="inlineStr"/>
       <c r="V23" s="5" t="inlineStr"/>
       <c r="W23" s="5" t="inlineStr"/>
-      <c r="X23" s="5" t="n">
+      <c r="X23" s="5" t="inlineStr"/>
+      <c r="Y23" s="5" t="inlineStr"/>
+      <c r="Z23" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y23" s="5" t="n">
+      <c r="AA23" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z23" s="5" t="inlineStr">
+      <c r="AB23" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA23" s="5" t="inlineStr"/>
-      <c r="AB23" s="5" t="inlineStr"/>
-      <c r="AC23" s="5" t="inlineStr">
+      <c r="AC23" s="5" t="inlineStr"/>
+      <c r="AD23" s="5" t="inlineStr"/>
+      <c r="AE23" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="AD23" s="5" t="inlineStr"/>
+      <c r="AF23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2945,7 +3037,7 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>196.1999969482422</v>
+        <v>195.3300018310547</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>55</v>
@@ -2965,22 +3057,22 @@
         <v>50</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>30.26414306552548</v>
+        <v>30.13324092386908</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>0.0310198990532244</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.6750087269428927</v>
+        <v>0.6783245440176552</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>-6.960064017732826</v>
+        <v>-7.015585073644512</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>145.0797097342355</v>
+        <v>144.209714617048</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>272.8804277692523</v>
+        <v>272.0104326520648</v>
       </c>
       <c r="P24" s="5" t="n">
         <v>25.56014360700335</v>
@@ -3000,25 +3092,27 @@
       <c r="U24" s="5" t="inlineStr"/>
       <c r="V24" s="5" t="inlineStr"/>
       <c r="W24" s="5" t="inlineStr"/>
-      <c r="X24" s="5" t="n">
+      <c r="X24" s="5" t="inlineStr"/>
+      <c r="Y24" s="5" t="inlineStr"/>
+      <c r="Z24" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y24" s="5" t="n">
+      <c r="AA24" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z24" s="5" t="inlineStr">
+      <c r="AB24" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA24" s="5" t="inlineStr"/>
-      <c r="AB24" s="5" t="inlineStr"/>
-      <c r="AC24" s="5" t="inlineStr">
+      <c r="AC24" s="5" t="inlineStr"/>
+      <c r="AD24" s="5" t="inlineStr"/>
+      <c r="AE24" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="AD24" s="5" t="inlineStr"/>
+      <c r="AF24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -3037,7 +3131,7 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>107.2399978637695</v>
+        <v>107.2900009155273</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>55</v>
@@ -3057,22 +3151,22 @@
         <v>50</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>31.21248198408246</v>
+        <v>31.26405772394173</v>
       </c>
       <c r="K25" s="5" t="n">
         <v>0.0469355722360184</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.4503242821149934</v>
+        <v>0.452336790926341</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-3.426324930592146</v>
+        <v>-3.423133852645206</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>93.02106857299805</v>
+        <v>93.07107162475586</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>126.1985702514648</v>
+        <v>126.2485733032227</v>
       </c>
       <c r="P25" s="5" t="n">
         <v>9.479286193847656</v>
@@ -3092,25 +3186,27 @@
       <c r="U25" s="5" t="inlineStr"/>
       <c r="V25" s="5" t="inlineStr"/>
       <c r="W25" s="5" t="inlineStr"/>
-      <c r="X25" s="5" t="n">
+      <c r="X25" s="5" t="inlineStr"/>
+      <c r="Y25" s="5" t="inlineStr"/>
+      <c r="Z25" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y25" s="5" t="n">
+      <c r="AA25" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z25" s="5" t="inlineStr">
+      <c r="AB25" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA25" s="5" t="inlineStr"/>
-      <c r="AB25" s="5" t="inlineStr"/>
-      <c r="AC25" s="5" t="inlineStr">
+      <c r="AC25" s="5" t="inlineStr"/>
+      <c r="AD25" s="5" t="inlineStr"/>
+      <c r="AE25" s="5" t="inlineStr">
         <is>
           <t>Positive momentum</t>
         </is>
       </c>
-      <c r="AD25" s="5" t="inlineStr"/>
+      <c r="AF25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -3129,7 +3225,7 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>25.86009979248047</v>
+        <v>25.8799991607666</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>54</v>
@@ -3149,22 +3245,22 @@
         <v>50</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>41.82511788429533</v>
+        <v>41.87614750781767</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>0.0084746235925221</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.2175772153887832</v>
+        <v>0.2193628369840065</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>-0.0427269859762597</v>
+        <v>-0.0414570547807908</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>21.10738563537598</v>
+        <v>21.12728500366211</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>32.98917102813721</v>
+        <v>33.00907039642334</v>
       </c>
       <c r="P26" s="5" t="n">
         <v>2.376357078552246</v>
@@ -3184,21 +3280,23 @@
       <c r="U26" s="5" t="inlineStr"/>
       <c r="V26" s="5" t="inlineStr"/>
       <c r="W26" s="5" t="inlineStr"/>
-      <c r="X26" s="5" t="n">
+      <c r="X26" s="5" t="inlineStr"/>
+      <c r="Y26" s="5" t="inlineStr"/>
+      <c r="Z26" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y26" s="5" t="n">
+      <c r="AA26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z26" s="5" t="inlineStr">
+      <c r="AB26" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA26" s="5" t="inlineStr"/>
-      <c r="AB26" s="5" t="inlineStr"/>
       <c r="AC26" s="5" t="inlineStr"/>
       <c r="AD26" s="5" t="inlineStr"/>
+      <c r="AE26" s="5" t="inlineStr"/>
+      <c r="AF26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -3217,7 +3315,7 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>275.6400146484375</v>
+        <v>275.6300048828125</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>51</v>
@@ -3237,22 +3335,22 @@
         <v>75</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>61.26917068773249</v>
+        <v>61.26158516193371</v>
       </c>
       <c r="K27" s="5" t="n">
         <v>-0.0092015237095138</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>0.2110169677476387</v>
+        <v>0.2122511899361767</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>5.878126480877018</v>
+        <v>5.877487681019421</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>257.8382344927107</v>
+        <v>257.8282247270857</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>299.37572152274</v>
+        <v>299.365711757115</v>
       </c>
       <c r="P27" s="5" t="n">
         <v>11.86785343715123</v>
@@ -3272,25 +3370,27 @@
       <c r="U27" s="5" t="inlineStr"/>
       <c r="V27" s="5" t="inlineStr"/>
       <c r="W27" s="5" t="inlineStr"/>
-      <c r="X27" s="5" t="n">
+      <c r="X27" s="5" t="inlineStr"/>
+      <c r="Y27" s="5" t="inlineStr"/>
+      <c r="Z27" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y27" s="5" t="n">
+      <c r="AA27" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z27" s="5" t="inlineStr">
+      <c r="AB27" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA27" s="5" t="inlineStr"/>
-      <c r="AB27" s="5" t="inlineStr"/>
-      <c r="AC27" s="5" t="inlineStr">
+      <c r="AC27" s="5" t="inlineStr"/>
+      <c r="AD27" s="5" t="inlineStr"/>
+      <c r="AE27" s="5" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AD27" s="5" t="inlineStr"/>
+      <c r="AF27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -3309,7 +3409,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>395.7799987792969</v>
+        <v>395.6700134277344</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>43</v>
@@ -3329,22 +3429,22 @@
         <v>50</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>54.21050082981659</v>
+        <v>54.18055211500717</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0.0109940121352903</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.3256883095764366</v>
+        <v>0.3274414442007423</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>-0.0697227633033923</v>
+        <v>-0.07674177149429259</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>367.9292875017438</v>
+        <v>367.8193021501813</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>432.9142804827009</v>
+        <v>432.8042951311384</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>18.56714085170201</v>
@@ -3362,43 +3462,53 @@
         <v>13.95</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>-0.0427022074483251</v>
+        <v>-0.0429682358848012</v>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>Signal score weakened</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="n">
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>Trend and score weakened</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="Y28" s="3" t="n">
+      <c r="AA28" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z28" s="3" t="inlineStr">
+      <c r="AB28" s="3" t="inlineStr">
         <is>
           <t>Already held</t>
         </is>
       </c>
-      <c r="AA28" s="3" t="inlineStr">
+      <c r="AC28" s="3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AB28" s="3" t="inlineStr">
+      <c r="AD28" s="3" t="inlineStr">
         <is>
           <t>Do not average down</t>
         </is>
       </c>
-      <c r="AC28" s="3" t="inlineStr"/>
-      <c r="AD28" s="3" t="inlineStr">
-        <is>
-          <t>Do not average down; Signal score weakened</t>
+      <c r="AE28" s="3" t="inlineStr"/>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>Do not average down; Trend and score weakened</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3529,7 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>79.84999847412109</v>
+        <v>79.90499877929688</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>43</v>
@@ -3439,22 +3549,22 @@
         <v>50</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>38.10932385566196</v>
+        <v>38.16229213562648</v>
       </c>
       <c r="K29" s="5" t="n">
         <v>0.0264563885114627</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.3780170853995899</v>
+        <v>0.3795012627222269</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>-1.379011842748928</v>
+        <v>-1.375501851763356</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>64.38428497314453</v>
+        <v>64.43928527832031</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>103.0485687255859</v>
+        <v>103.1035690307617</v>
       </c>
       <c r="P29" s="5" t="n">
         <v>7.732856750488281</v>
@@ -3474,21 +3584,23 @@
       <c r="U29" s="5" t="inlineStr"/>
       <c r="V29" s="5" t="inlineStr"/>
       <c r="W29" s="5" t="inlineStr"/>
-      <c r="X29" s="5" t="n">
+      <c r="X29" s="5" t="inlineStr"/>
+      <c r="Y29" s="5" t="inlineStr"/>
+      <c r="Z29" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y29" s="5" t="n">
+      <c r="AA29" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z29" s="5" t="inlineStr">
+      <c r="AB29" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA29" s="5" t="inlineStr"/>
-      <c r="AB29" s="5" t="inlineStr"/>
       <c r="AC29" s="5" t="inlineStr"/>
       <c r="AD29" s="5" t="inlineStr"/>
+      <c r="AE29" s="5" t="inlineStr"/>
+      <c r="AF29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3507,7 +3619,7 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>6.824999809265137</v>
+        <v>6.810200214385986</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>39</v>
@@ -3527,22 +3639,22 @@
         <v>75</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>58.071274466897</v>
+        <v>57.80947035309124</v>
       </c>
       <c r="K30" s="5" t="n">
         <v>-0.0154083063419491</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.7279997013311943</v>
+        <v>0.7378436143208397</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.0704685085412049</v>
+        <v>0.06952403297057019</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>6.01371397290911</v>
+        <v>5.998914378029959</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>8.041928563799177</v>
+        <v>8.027128968920026</v>
       </c>
       <c r="P30" s="5" t="n">
         <v>0.4056429181780134</v>
@@ -3562,25 +3674,27 @@
       <c r="U30" s="5" t="inlineStr"/>
       <c r="V30" s="5" t="inlineStr"/>
       <c r="W30" s="5" t="inlineStr"/>
-      <c r="X30" s="5" t="n">
+      <c r="X30" s="5" t="inlineStr"/>
+      <c r="Y30" s="5" t="inlineStr"/>
+      <c r="Z30" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y30" s="5" t="n">
+      <c r="AA30" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z30" s="5" t="inlineStr">
+      <c r="AB30" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA30" s="5" t="inlineStr"/>
-      <c r="AB30" s="5" t="inlineStr"/>
-      <c r="AC30" s="5" t="inlineStr">
+      <c r="AC30" s="5" t="inlineStr"/>
+      <c r="AD30" s="5" t="inlineStr"/>
+      <c r="AE30" s="5" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AD30" s="5" t="inlineStr"/>
+      <c r="AF30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3625,7 +3739,7 @@
         <v>0.0112075006381963</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.2177604757923567</v>
+        <v>0.2185076392289275</v>
       </c>
       <c r="M31" s="5" t="n">
         <v>-0.0332413465283076</v>
@@ -3654,21 +3768,23 @@
       <c r="U31" s="5" t="inlineStr"/>
       <c r="V31" s="5" t="inlineStr"/>
       <c r="W31" s="5" t="inlineStr"/>
-      <c r="X31" s="5" t="n">
+      <c r="X31" s="5" t="inlineStr"/>
+      <c r="Y31" s="5" t="inlineStr"/>
+      <c r="Z31" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y31" s="5" t="n">
+      <c r="AA31" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z31" s="5" t="inlineStr">
+      <c r="AB31" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA31" s="5" t="inlineStr"/>
-      <c r="AB31" s="5" t="inlineStr"/>
       <c r="AC31" s="5" t="inlineStr"/>
       <c r="AD31" s="5" t="inlineStr"/>
+      <c r="AE31" s="5" t="inlineStr"/>
+      <c r="AF31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3687,7 +3803,7 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>39.46440124511719</v>
+        <v>39.54999923706055</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>33</v>
@@ -3707,22 +3823,22 @@
         <v>50</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>17.96308832256679</v>
+        <v>18.20708401865569</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>0.0298353862022756</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.3520177438940802</v>
+        <v>0.3543801665930444</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>-1.426272219916156</v>
+        <v>-1.420809556042851</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>32.06225858415876</v>
+        <v>32.14785657610212</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>50.56761523655483</v>
+        <v>50.65321322849819</v>
       </c>
       <c r="P32" s="5" t="n">
         <v>3.701071330479213</v>
@@ -3742,21 +3858,23 @@
       <c r="U32" s="5" t="inlineStr"/>
       <c r="V32" s="5" t="inlineStr"/>
       <c r="W32" s="5" t="inlineStr"/>
-      <c r="X32" s="5" t="n">
+      <c r="X32" s="5" t="inlineStr"/>
+      <c r="Y32" s="5" t="inlineStr"/>
+      <c r="Z32" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y32" s="5" t="n">
+      <c r="AA32" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z32" s="5" t="inlineStr">
+      <c r="AB32" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA32" s="5" t="inlineStr"/>
-      <c r="AB32" s="5" t="inlineStr"/>
       <c r="AC32" s="5" t="inlineStr"/>
       <c r="AD32" s="5" t="inlineStr"/>
+      <c r="AE32" s="5" t="inlineStr"/>
+      <c r="AF32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3775,7 +3893,7 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>69.69999694824219</v>
+        <v>69.76000213623047</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>32</v>
@@ -3795,22 +3913,22 @@
         <v>50</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>47.13743316355389</v>
+        <v>47.19465901020189</v>
       </c>
       <c r="K33" s="5" t="n">
         <v>0.0334417645102432</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.292970186665529</v>
+        <v>0.2940843051902342</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>-0.7449109128645111</v>
+        <v>-0.7410815219501519</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>55.78942544119698</v>
+        <v>55.84943062918526</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>90.56585420880998</v>
+        <v>90.62585939679826</v>
       </c>
       <c r="P33" s="5" t="n">
         <v>6.955285753522601</v>
@@ -3830,21 +3948,23 @@
       <c r="U33" s="5" t="inlineStr"/>
       <c r="V33" s="5" t="inlineStr"/>
       <c r="W33" s="5" t="inlineStr"/>
-      <c r="X33" s="5" t="n">
+      <c r="X33" s="5" t="inlineStr"/>
+      <c r="Y33" s="5" t="inlineStr"/>
+      <c r="Z33" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y33" s="5" t="n">
+      <c r="AA33" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z33" s="5" t="inlineStr">
+      <c r="AB33" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA33" s="5" t="inlineStr"/>
-      <c r="AB33" s="5" t="inlineStr"/>
       <c r="AC33" s="5" t="inlineStr"/>
       <c r="AD33" s="5" t="inlineStr"/>
+      <c r="AE33" s="5" t="inlineStr"/>
+      <c r="AF33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3863,7 +3983,7 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>7.835000038146973</v>
+        <v>7.860000133514404</v>
       </c>
       <c r="E34" s="5" t="n">
         <v>32</v>
@@ -3883,22 +4003,22 @@
         <v>50</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>44.55626486353297</v>
+        <v>44.80874184046107</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>0.018661516252568</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0.6337696104940953</v>
+        <v>0.6455428043839868</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>-0.0738690107655368</v>
+        <v>-0.0722735630839688</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>6.446714537484305</v>
+        <v>6.471714632851737</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>9.917428289140974</v>
+        <v>9.942428384508403</v>
       </c>
       <c r="P34" s="5" t="n">
         <v>0.6941427503313337</v>
@@ -3918,21 +4038,23 @@
       <c r="U34" s="5" t="inlineStr"/>
       <c r="V34" s="5" t="inlineStr"/>
       <c r="W34" s="5" t="inlineStr"/>
-      <c r="X34" s="5" t="n">
+      <c r="X34" s="5" t="inlineStr"/>
+      <c r="Y34" s="5" t="inlineStr"/>
+      <c r="Z34" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y34" s="5" t="n">
+      <c r="AA34" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z34" s="5" t="inlineStr">
+      <c r="AB34" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA34" s="5" t="inlineStr"/>
-      <c r="AB34" s="5" t="inlineStr"/>
       <c r="AC34" s="5" t="inlineStr"/>
       <c r="AD34" s="5" t="inlineStr"/>
+      <c r="AE34" s="5" t="inlineStr"/>
+      <c r="AF34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -3951,7 +4073,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>184.3399963378907</v>
+        <v>183.3200073242188</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>29</v>
@@ -3976,13 +4098,13 @@
       </c>
       <c r="L35" s="3" t="inlineStr"/>
       <c r="M35" s="3" t="n">
-        <v>0.5127650457097526</v>
+        <v>0.4476717297375126</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>169.5927966308594</v>
+        <v>168.6544067382813</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>211.9909957885743</v>
+        <v>210.8180084228516</v>
       </c>
       <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="3" t="n">
@@ -4000,25 +4122,27 @@
       <c r="U35" s="3" t="inlineStr"/>
       <c r="V35" s="3" t="inlineStr"/>
       <c r="W35" s="3" t="inlineStr"/>
-      <c r="X35" s="3" t="n">
+      <c r="X35" s="3" t="inlineStr"/>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="Y35" s="3" t="n">
+      <c r="AA35" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z35" s="3" t="inlineStr">
+      <c r="AB35" s="3" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA35" s="3" t="inlineStr"/>
-      <c r="AB35" s="3" t="inlineStr"/>
-      <c r="AC35" s="3" t="inlineStr">
+      <c r="AC35" s="3" t="inlineStr"/>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AD35" s="3" t="inlineStr">
+      <c r="AF35" s="3" t="inlineStr">
         <is>
           <t>Missing ATR</t>
         </is>
@@ -4041,7 +4165,7 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>15.15499973297119</v>
+        <v>15.18000030517578</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>22</v>
@@ -4061,22 +4185,22 @@
         <v>50</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>24.09476173102698</v>
+        <v>24.26404581176152</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>0.0323432829789085</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.3545207037936516</v>
+        <v>0.3557917486030802</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>-0.2093460610615922</v>
+        <v>-0.2077505829493904</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>11.90601362500872</v>
+        <v>11.93101419721331</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>20.0284788949149</v>
+        <v>20.05347946711949</v>
       </c>
       <c r="P36" s="5" t="n">
         <v>1.624493053981236</v>
@@ -4096,21 +4220,23 @@
       <c r="U36" s="5" t="inlineStr"/>
       <c r="V36" s="5" t="inlineStr"/>
       <c r="W36" s="5" t="inlineStr"/>
-      <c r="X36" s="5" t="n">
+      <c r="X36" s="5" t="inlineStr"/>
+      <c r="Y36" s="5" t="inlineStr"/>
+      <c r="Z36" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y36" s="5" t="n">
+      <c r="AA36" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z36" s="5" t="inlineStr">
+      <c r="AB36" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA36" s="5" t="inlineStr"/>
-      <c r="AB36" s="5" t="inlineStr"/>
       <c r="AC36" s="5" t="inlineStr"/>
       <c r="AD36" s="5" t="inlineStr"/>
+      <c r="AE36" s="5" t="inlineStr"/>
+      <c r="AF36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -4129,7 +4255,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>91.68000030517578</v>
+        <v>91.66999816894533</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>22</v>
@@ -4149,22 +4275,22 @@
         <v>50</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>17.58944999670975</v>
+        <v>17.55839190490563</v>
       </c>
       <c r="K37" s="5" t="n">
         <v>0.0177384274683925</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.802274535494354</v>
+        <v>0.8043091700338481</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>-0.7651056636518181</v>
+        <v>-0.765743976619226</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>84.95464270455497</v>
+        <v>84.94464056832452</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>100.6471437726702</v>
+        <v>100.6371416364398</v>
       </c>
       <c r="P37" s="5" t="n">
         <v>4.48357173374721</v>
@@ -4184,21 +4310,23 @@
       <c r="U37" s="5" t="inlineStr"/>
       <c r="V37" s="5" t="inlineStr"/>
       <c r="W37" s="5" t="inlineStr"/>
-      <c r="X37" s="5" t="n">
+      <c r="X37" s="5" t="inlineStr"/>
+      <c r="Y37" s="5" t="inlineStr"/>
+      <c r="Z37" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y37" s="5" t="n">
+      <c r="AA37" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z37" s="5" t="inlineStr">
+      <c r="AB37" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA37" s="5" t="inlineStr"/>
-      <c r="AB37" s="5" t="inlineStr"/>
       <c r="AC37" s="5" t="inlineStr"/>
       <c r="AD37" s="5" t="inlineStr"/>
+      <c r="AE37" s="5" t="inlineStr"/>
+      <c r="AF37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -4217,7 +4345,7 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>8.595000267028809</v>
+        <v>8.604999542236328</v>
       </c>
       <c r="E38" s="5" t="n">
         <v>22</v>
@@ -4237,22 +4365,22 @@
         <v>50</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>21.21982595865489</v>
+        <v>21.41950780719866</v>
       </c>
       <c r="K38" s="5" t="n">
         <v>0.0299401183926648</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.4980625979259259</v>
+        <v>0.5004059941865834</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>-0.1145804080449862</v>
+        <v>-0.1139422776613741</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>7.247858047485352</v>
+        <v>7.257857322692871</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>10.61571359634399</v>
+        <v>10.62571287155151</v>
       </c>
       <c r="P38" s="5" t="n">
         <v>0.6735711097717285</v>
@@ -4272,21 +4400,23 @@
       <c r="U38" s="5" t="inlineStr"/>
       <c r="V38" s="5" t="inlineStr"/>
       <c r="W38" s="5" t="inlineStr"/>
-      <c r="X38" s="5" t="n">
+      <c r="X38" s="5" t="inlineStr"/>
+      <c r="Y38" s="5" t="inlineStr"/>
+      <c r="Z38" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y38" s="5" t="n">
+      <c r="AA38" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z38" s="5" t="inlineStr">
+      <c r="AB38" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA38" s="5" t="inlineStr"/>
-      <c r="AB38" s="5" t="inlineStr"/>
       <c r="AC38" s="5" t="inlineStr"/>
       <c r="AD38" s="5" t="inlineStr"/>
+      <c r="AE38" s="5" t="inlineStr"/>
+      <c r="AF38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -4305,7 +4435,7 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>46.15000152587891</v>
+        <v>46.27999877929688</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>22</v>
@@ -4325,22 +4455,22 @@
         <v>50</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>24.27772708696961</v>
+        <v>24.73366460018019</v>
       </c>
       <c r="K39" s="5" t="n">
         <v>0.0251036384349932</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.3161810453460449</v>
+        <v>0.3183198712545969</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>-0.3303057940845564</v>
+        <v>-0.3220096730687136</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>39.26325825282505</v>
+        <v>39.39325550624303</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>56.48011643545968</v>
+        <v>56.61011368887766</v>
       </c>
       <c r="P39" s="5" t="n">
         <v>3.443371636526925</v>
@@ -4360,21 +4490,23 @@
       <c r="U39" s="5" t="inlineStr"/>
       <c r="V39" s="5" t="inlineStr"/>
       <c r="W39" s="5" t="inlineStr"/>
-      <c r="X39" s="5" t="n">
+      <c r="X39" s="5" t="inlineStr"/>
+      <c r="Y39" s="5" t="inlineStr"/>
+      <c r="Z39" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y39" s="5" t="n">
+      <c r="AA39" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z39" s="5" t="inlineStr">
+      <c r="AB39" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA39" s="5" t="inlineStr"/>
-      <c r="AB39" s="5" t="inlineStr"/>
       <c r="AC39" s="5" t="inlineStr"/>
       <c r="AD39" s="5" t="inlineStr"/>
+      <c r="AE39" s="5" t="inlineStr"/>
+      <c r="AF39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -4393,7 +4525,7 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>7.751699924468994</v>
+        <v>7.770500183105469</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>22</v>
@@ -4413,22 +4545,22 @@
         <v>50</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>26.95491660880916</v>
+        <v>27.30519493945793</v>
       </c>
       <c r="K40" s="5" t="n">
         <v>0.0100267124430337</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0.8755305405588308</v>
+        <v>0.8921217787785596</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>-0.1038519566961955</v>
+        <v>-0.1026521681108479</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>6.636271340506418</v>
+        <v>6.655071599142892</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>9.424842800412859</v>
+        <v>9.443643059049334</v>
       </c>
       <c r="P40" s="5" t="n">
         <v>0.5577142919812884</v>
@@ -4448,21 +4580,23 @@
       <c r="U40" s="5" t="inlineStr"/>
       <c r="V40" s="5" t="inlineStr"/>
       <c r="W40" s="5" t="inlineStr"/>
-      <c r="X40" s="5" t="n">
+      <c r="X40" s="5" t="inlineStr"/>
+      <c r="Y40" s="5" t="inlineStr"/>
+      <c r="Z40" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Y40" s="5" t="n">
+      <c r="AA40" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z40" s="5" t="inlineStr">
+      <c r="AB40" s="5" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AA40" s="5" t="inlineStr"/>
-      <c r="AB40" s="5" t="inlineStr"/>
       <c r="AC40" s="5" t="inlineStr"/>
       <c r="AD40" s="5" t="inlineStr"/>
+      <c r="AE40" s="5" t="inlineStr"/>
+      <c r="AF40" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4543,19 +4677,19 @@
         <v>15.06915790595363</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>16.84000015258789</v>
+        <v>16.86000061035156</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>12.57316376672592</v>
+        <v>12.58809660690369</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>11.251008816</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.322154950725922</v>
+        <v>1.337087790903686</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.1175143466997992</v>
+        <v>0.1188415912537745</v>
       </c>
     </row>
     <row r="3">
@@ -4571,19 +4705,19 @@
         <v>366.8202462424581</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>358.0578918457031</v>
+        <v>358.1199951171875</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.92682916501739</v>
+        <v>18.93011192469605</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>19.3900045021</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.4631753370826033</v>
+        <v>-0.4598925774039522</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.0238873248859967</v>
+        <v>-0.0237180232399711</v>
       </c>
     </row>
     <row r="4">
@@ -4599,19 +4733,19 @@
         <v>18.39862725025694</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>18.68499946594238</v>
+        <v>18.66410064697266</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>11.42612942091656</v>
+        <v>11.41334951098251</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>11.251008945</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.1751204759165574</v>
+        <v>0.1623405659825127</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.0155648686062401</v>
+        <v>0.0144289784832726</v>
       </c>
     </row>
     <row r="5">
@@ -4627,19 +4761,19 @@
         <v>413.4345674446258</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>395.7799987792969</v>
+        <v>395.6700134277344</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.77056295458038</v>
+        <v>10.76756986711578</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>11.2510057355</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.480442780919617</v>
+        <v>-0.4834358683842161</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.0427022074483251</v>
+        <v>-0.0429682358848012</v>
       </c>
     </row>
   </sheetData>
@@ -4967,46 +5101,46 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>370.9100036621094</v>
+        <v>370.0549926757813</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>331.9939993286133</v>
+        <v>331.9768991088867</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>201.2515501022339</v>
+        <v>201.2472750473023</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>46.31162813235188</v>
+        <v>46.18162304129646</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.0102410726627577</v>
+        <v>0.0079122942328466</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.174150002298657</v>
+        <v>1.169138214750365</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>1.149330636379102</v>
+        <v>1.144376061713519</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>14.97140553604134</v>
+        <v>14.90319953143398</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>26.09527847415392</v>
+        <v>26.08163727323245</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-11.12387293811257</v>
+        <v>-11.17843774179846</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>-10.00415359792669</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>1729806</v>
+        <v>1736374</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>6121512.12</v>
+        <v>6121643.48</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>0.2825782202322912</v>
+        <v>0.2836450710782</v>
       </c>
       <c r="P2" s="6" t="n">
         <v>0.082723417254077</v>
@@ -5020,7 +5154,7 @@
         <v>46.42792184012277</v>
       </c>
       <c r="S2" s="6" t="n">
-        <v>0.1251730106541358</v>
+        <v>0.1254622225318818</v>
       </c>
       <c r="T2" s="6" t="inlineStr">
         <is>
@@ -5035,46 +5169,46 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>556.2000122070312</v>
+        <v>556.010009765625</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>489.875400390625</v>
+        <v>489.8716003417969</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>291.5077997589111</v>
+        <v>291.5068497467041</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>55.98630573472487</v>
+        <v>55.95874423080636</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.0872412460539877</v>
+        <v>0.0868698356141928</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.180577865825075</v>
+        <v>1.179832962716319</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1.678029783181052</v>
+        <v>1.677114946457219</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>17.42946523456033</v>
+        <v>17.41430834464768</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>19.97379664601249</v>
+        <v>19.97076526802996</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-2.544331411452166</v>
+        <v>-2.556456923382285</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>-3.577422784539042</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>14939279</v>
+        <v>14984558</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>33870253.58</v>
+        <v>33871159.16</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.4410737275619771</v>
+        <v>0.4423987360224728</v>
       </c>
       <c r="P3" s="6" t="n">
         <v>0.0624019610194614</v>
@@ -5088,7 +5222,7 @@
         <v>38.05143519810268</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0.0684132225152469</v>
+        <v>0.0684366010139682</v>
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
@@ -5103,46 +5237,46 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>246.3350067138672</v>
+        <v>246.4400024414062</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>253.3454998779297</v>
+        <v>253.3475997924805</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>233.5968250274658</v>
+        <v>233.5973500061035</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>65.12433937744606</v>
+        <v>65.29396912736486</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0326346827185757</v>
+        <v>0.0330748240985625</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.0107822564955705</v>
+        <v>-0.0103606207806173</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.000547711714072</v>
+        <v>-0.0001217137142381</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.7460167880136623</v>
+        <v>-0.7376410604606747</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-2.413677202672937</v>
+        <v>-2.41200205716234</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>1.667660414659275</v>
+        <v>1.674360996701665</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>1.780135958077288</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>15200900</v>
+        <v>15285042</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>48720226</v>
+        <v>48721908.84</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.3120038893087236</v>
+        <v>0.3137200976709515</v>
       </c>
       <c r="P4" s="6" t="n">
         <v>-0.0071974396379796</v>
@@ -5156,7 +5290,7 @@
         <v>7.47785404750279</v>
       </c>
       <c r="S4" s="6" t="n">
-        <v>0.0303564407968566</v>
+        <v>0.0303435074396281</v>
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
@@ -5171,46 +5305,46 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>182.3500061035156</v>
+        <v>182.3800048828125</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>160.7883996582031</v>
+        <v>160.7889996337891</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>144.3320496749878</v>
+        <v>144.3321996688843</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>62.31512866084653</v>
+        <v>62.32894220433992</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.1170668951683648</v>
+        <v>0.1172506661698804</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.1812529110018275</v>
+        <v>0.1814472413784922</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.4774753590087004</v>
+        <v>0.4777184215572496</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5.993633155993223</v>
+        <v>5.996026221008321</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.403305543679057</v>
+        <v>4.403784156682076</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>1.590327612314166</v>
+        <v>1.592242064326245</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>1.773262942271622</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>3613543</v>
+        <v>3640048</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>10346326.86</v>
+        <v>10346856.96</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.3492585386965051</v>
+        <v>0.3518022926258758</v>
       </c>
       <c r="P5" s="6" t="n">
         <v>0.0151807899125376</v>
@@ -5224,7 +5358,7 @@
         <v>10.46220506940569</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>0.0573743061103412</v>
+        <v>0.0573648688962813</v>
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
@@ -5239,46 +5373,46 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>284.4100036621094</v>
+        <v>284.3699951171875</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>312.6235983276367</v>
+        <v>312.6227981567383</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>182.8276749801636</v>
+        <v>182.827474937439</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>28.62432369505791</v>
+        <v>28.61835280220669</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-0.2531445983942469</v>
+        <v>-0.2532496600921498</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.7641111618202046</v>
+        <v>0.7638630006452947</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1.559024700593973</v>
+        <v>1.558664717283359</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-7.897146600682447</v>
+        <v>-7.900338165519486</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>1.996850400650548</v>
+        <v>1.996212087683141</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-9.893997001332997</v>
+        <v>-9.896550253202626</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>-9.368367243321137</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>6205815</v>
+        <v>6220930</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>11186590.3</v>
+        <v>11186892.6</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.5547548299860414</v>
+        <v>0.5560909738241342</v>
       </c>
       <c r="P6" s="6" t="n">
         <v>0.0376936349020097</v>
@@ -5292,7 +5426,7 @@
         <v>29.38128662109375</v>
       </c>
       <c r="S6" s="6" t="n">
-        <v>0.1033060941695985</v>
+        <v>0.1033206284966382</v>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
@@ -5307,46 +5441,46 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>69.69999694824219</v>
+        <v>69.76000213623047</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>86.04720008850097</v>
+        <v>86.04840019226074</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>83.07154983520508</v>
+        <v>83.07184986114503</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>47.13743316355389</v>
+        <v>47.19465901020189</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.1542289303369005</v>
+        <v>-0.1535008004337117</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.2130518551608931</v>
+        <v>-0.2123743663024191</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.2915947008779503</v>
+        <v>-0.2909848300744081</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-4.770713683234916</v>
+        <v>-4.765926944591968</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-4.025802770370405</v>
+        <v>-4.024845422641816</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>-0.7449109128645111</v>
+        <v>-0.7410815219501519</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>-0.7205249641778009</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>6779269</v>
+        <v>6805202</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>23139791.38</v>
+        <v>23140310.04</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.292970186665529</v>
+        <v>0.2940843051902342</v>
       </c>
       <c r="P7" s="6" t="n">
         <v>0.0334417645102432</v>
@@ -5360,7 +5494,7 @@
         <v>6.955285753522601</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>0.0997888960983377</v>
+        <v>0.0997030610741669</v>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
@@ -5375,46 +5509,46 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>393.9299926757813</v>
+        <v>393.760009765625</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>405.5524005126953</v>
+        <v>405.5490008544922</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>362.9451501464844</v>
+        <v>362.9443002319336</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>55.60892184553344</v>
+        <v>55.54740946415497</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0310413932635604</v>
+        <v>0.0305964933580518</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.034534360887233</v>
+        <v>0.0340879537474116</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.1184520661902466</v>
+        <v>0.1179694481093285</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-3.426826732262043</v>
+        <v>-3.440386622530923</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-6.714454313983033</v>
+        <v>-6.717166292036809</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>3.28762758172099</v>
+        <v>3.276779669505886</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>3.038872772970159</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>10222411</v>
+        <v>10266892</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>27440060.22</v>
+        <v>27440949.84</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3725360264533705</v>
+        <v>0.3741449206336948</v>
       </c>
       <c r="P8" s="6" t="n">
         <v>0.030087289573326</v>
@@ -5428,7 +5562,7 @@
         <v>15.00356619698661</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>0.0380868846646441</v>
+        <v>0.038103326454906</v>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
@@ -5443,46 +5577,46 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>7.664999961853027</v>
+        <v>7.667600154876709</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>5.821899991035462</v>
+        <v>5.821951994895935</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4.04517499923706</v>
+        <v>4.045188000202179</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>49.95178289261076</v>
+        <v>49.97684546433793</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.3835740098614055</v>
+        <v>0.3840433587858796</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.7263513205113541</v>
+        <v>0.7269369495631945</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.7950819662977748</v>
+        <v>0.7956909108025281</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.6080848432160195</v>
+        <v>0.6082922660213272</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.7316254440648836</v>
+        <v>0.7316669286259452</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-0.123540600848864</v>
+        <v>-0.1233746626046179</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>-0.0949479297406228</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>3808528</v>
+        <v>3817656</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>7814806.56</v>
+        <v>7814989.12</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4873476996211151</v>
+        <v>0.4885043269260495</v>
       </c>
       <c r="P9" s="6" t="n">
         <v>-0.0049382666628676</v>
@@ -5496,7 +5630,7 @@
         <v>0.7386070660182408</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>0.09636100061240981</v>
+        <v>0.0963283232170727</v>
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
@@ -5511,46 +5645,46 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>16.84000015258789</v>
+        <v>16.86000061035156</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>9.902200031280518</v>
+        <v>9.902600040435791</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.552249990701675</v>
+        <v>6.552349992990494</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>74.48015284749306</v>
+        <v>74.52830460284595</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1.126262625046329</v>
+        <v>1.128787935345699</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>3.70391075739324</v>
+        <v>3.709497477558018</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>2.269902881698185</v>
+        <v>2.27378646565805</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>2.330573959392138</v>
+        <v>2.332169437504341</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>2.205205521670499</v>
+        <v>2.205524617292939</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1253684377216397</v>
+        <v>0.1266448202114016</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>0.2137816411175577</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>815347</v>
+        <v>821270</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>3924560.94</v>
+        <v>3924679.4</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.2077549597178633</v>
+        <v>0.2092578568328409</v>
       </c>
       <c r="P10" s="6" t="n">
         <v>0.0098826338563442</v>
@@ -5564,7 +5698,7 @@
         <v>1.499500070299421</v>
       </c>
       <c r="S10" s="6" t="n">
-        <v>0.0890439463605934</v>
+        <v>0.0889383164896667</v>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
@@ -5579,46 +5713,46 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>275.6400146484375</v>
+        <v>275.6300048828125</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>301.0000015258789</v>
+        <v>300.9998013305664</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>276.0429009246826</v>
+        <v>276.0428508758545</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>61.26917068773249</v>
+        <v>61.26158516193371</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.0653419306716712</v>
+        <v>-0.06537587243526249</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.0834912231140897</v>
+        <v>-0.08352450579280959</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.0442096199332029</v>
+        <v>0.0441716998453947</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-6.654829600566416</v>
+        <v>-6.655628100388412</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-12.53295608144343</v>
+        <v>-12.53311578140783</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>5.878126480877018</v>
+        <v>5.877487681019421</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>5.61249043240821</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>327553</v>
+        <v>329477</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>1552259.06</v>
+        <v>1552297.54</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.2110169677476387</v>
+        <v>0.2122511899361767</v>
       </c>
       <c r="P11" s="6" t="n">
         <v>-0.0092015237095138</v>
@@ -5632,7 +5766,7 @@
         <v>11.86785343715123</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>0.0430556262024872</v>
+        <v>0.0430571898084789</v>
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
@@ -5647,46 +5781,46 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>104.7900009155273</v>
+        <v>104.4499969482422</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>112.2715997314453</v>
+        <v>112.2647996520996</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>101.2295999336243</v>
+        <v>101.2278999137878</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>64.93240438722938</v>
+        <v>64.68646542671178</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.1833991790409899</v>
+        <v>0.1795594957483035</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.1328919963704662</v>
+        <v>-0.1357054342817456</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.0026791577224531</v>
+        <v>-0.0005741573702205</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.6617018373704155</v>
+        <v>0.6345790137693257</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.7683845643923448</v>
+        <v>-0.7738091291125627</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>1.43008640176276</v>
+        <v>1.408388142881888</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>1.911196160245703</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>566314</v>
+        <v>592829</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>1509294.28</v>
+        <v>1509824.58</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.3752177474627413</v>
+        <v>0.3926476014849354</v>
       </c>
       <c r="P12" s="6" t="n">
         <v>0</v>
@@ -5700,7 +5834,7 @@
         <v>5.971429007393973</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>0.0569847213972984</v>
+        <v>0.0571702171552286</v>
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
@@ -5715,46 +5849,46 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>239.8249969482422</v>
+        <v>240</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>227.4376998901367</v>
+        <v>227.4411999511719</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>161.8402751922607</v>
+        <v>161.8411502075195</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>41.60886297383517</v>
+        <v>41.66210579173344</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.0437980970347294</v>
+        <v>-0.043100345535741</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.5034164401012673</v>
+        <v>0.5045135003261336</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.5366501293873294</v>
+        <v>0.5377714406165539</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.467058185387998</v>
+        <v>5.48101854279318</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>10.06280064947751</v>
+        <v>10.06559272095854</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>-4.595742464089508</v>
+        <v>-4.584574178165363</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>-4.078359216969876</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>2390480</v>
+        <v>2407765</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>8664211.6</v>
+        <v>8664557.300000001</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2759027722730133</v>
+        <v>0.2778866728713306</v>
       </c>
       <c r="P13" s="6" t="n">
         <v>0.06596166699561611</v>
@@ -5768,7 +5902,7 @@
         <v>26.78535788399833</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>0.111687097778965</v>
+        <v>0.111605657849993</v>
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
@@ -5783,46 +5917,46 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>358.0578918457031</v>
+        <v>358.1199951171875</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>372.2623583984375</v>
+        <v>372.2636004638672</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>319.9698892974853</v>
+        <v>319.9701998138428</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>59.76929787069184</v>
+        <v>59.81018252640515</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.0045098444815091</v>
+        <v>-0.0043371819127008</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.0755395990116232</v>
+        <v>0.07572614573836969</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.07894264946220431</v>
+        <v>0.07912978643028</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-2.045249316054196</v>
+        <v>-2.040295208927262</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-2.650092033566048</v>
+        <v>-2.649101212140661</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.6048427175118514</v>
+        <v>0.6088060032133988</v>
       </c>
       <c r="L14" s="6" t="n">
         <v>0.5974640052565006</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>8698157</v>
+        <v>8769143</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>31765433.14</v>
+        <v>31766852.86</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.2738245992637517</v>
+        <v>0.2760469549390547</v>
       </c>
       <c r="P14" s="6" t="n">
         <v>-0.0040282924977889</v>
@@ -5836,7 +5970,7 @@
         <v>9.963572910853795</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>0.0278267094169994</v>
+        <v>0.0278218838565364</v>
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
@@ -5851,46 +5985,46 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>107.2399978637695</v>
+        <v>107.2900009155273</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>117.4259997558594</v>
+        <v>117.4269998168945</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>63.21419996261596</v>
+        <v>63.21444997787476</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>31.21248198408246</v>
+        <v>31.26405772394173</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.1391185829133042</v>
+        <v>-0.1387171776642048</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.6806142541262667</v>
+        <v>0.6813978781770686</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1.43395357515304</v>
+        <v>1.435088460541131</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-2.020433579830481</v>
+        <v>-2.016444732396806</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>1.405891350761665</v>
+        <v>1.4066891202484</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-3.426324930592146</v>
+        <v>-3.423133852645206</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>-3.642499733942029</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>58543794</v>
+        <v>58807816</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>130003635.88</v>
+        <v>130008916.32</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.4503242821149934</v>
+        <v>0.452336790926341</v>
       </c>
       <c r="P15" s="6" t="n">
         <v>0.0469355722360184</v>
@@ -5904,7 +6038,7 @@
         <v>9.479286193847656</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>0.0883931964068994</v>
+        <v>0.0883520003071953</v>
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
@@ -5919,46 +6053,46 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>39.46440124511719</v>
+        <v>39.54999923706055</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>54.90468818664551</v>
+        <v>54.90640014648437</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>48.68997204780579</v>
+        <v>48.6904000377655</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>17.96308832256679</v>
+        <v>18.20708401865569</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-0.3178149993768558</v>
+        <v>-0.3163353451987896</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.1035906906447852</v>
+        <v>0.1059843706213252</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.2254288389761277</v>
+        <v>-0.2237487999052427</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-4.162307939524524</v>
+        <v>-4.155479609682892</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-2.736035719608368</v>
+        <v>-2.734670053640041</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-1.426272219916156</v>
+        <v>-1.420809556042851</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>-1.449196603544823</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>10149586</v>
+        <v>10218187</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>28832597.72</v>
+        <v>28833969.74</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.3520177438940802</v>
+        <v>0.3543801665930444</v>
       </c>
       <c r="P16" s="6" t="n">
         <v>0.0298353862022756</v>
@@ -5972,7 +6106,7 @@
         <v>3.701071330479213</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>0.0937825283979732</v>
+        <v>0.0935795550410808</v>
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
@@ -5987,46 +6121,46 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>7.835000038146973</v>
+        <v>7.860000133514404</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>8.697499952316285</v>
+        <v>8.697999954223633</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>8.190724968910217</v>
+        <v>8.190849969387054</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>44.55626486353297</v>
+        <v>44.80874184046107</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-0.0273122605454708</v>
+        <v>-0.0242085865019866</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.162927315648176</v>
+        <v>-0.1602563651904378</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.0479950821457789</v>
+        <v>-0.0449574033173498</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.0334816751655058</v>
+        <v>0.0354759847674657</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.1073506859310426</v>
+        <v>0.1077495478514346</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.0738690107655368</v>
+        <v>-0.0722735630839688</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>-0.0068890358413925</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>666120</v>
+        <v>678656</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1051044.4</v>
+        <v>1051295.12</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.6337696104940953</v>
+        <v>0.6455428043839868</v>
       </c>
       <c r="P17" s="6" t="n">
         <v>0.018661516252568</v>
@@ -6040,7 +6174,7 @@
         <v>0.6941427503313337</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>0.08859511767092509</v>
+        <v>0.0883133255140245</v>
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
@@ -6055,46 +6189,46 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1156.849975585938</v>
+        <v>1157.300048828125</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1097.812601318359</v>
+        <v>1097.821602783203</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1000.57705291748</v>
+        <v>1000.579303283691</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>57.93754253826302</v>
+        <v>58.02083686703796</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.021050287366229</v>
+        <v>0.0214475276505956</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.2540379139142954</v>
+        <v>0.2545257981876694</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.07016648990373479</v>
+        <v>0.07058283887893151</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>27.80954151321862</v>
+        <v>27.84544479179772</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>34.64880114548208</v>
+        <v>34.6559818011979</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-6.839259632263456</v>
+        <v>-6.810537009400178</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>-3.468572913063639</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>1317903</v>
+        <v>1323421</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>3186258.06</v>
+        <v>3186368.42</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.413620923096229</v>
+        <v>0.4153383493550943</v>
       </c>
       <c r="P18" s="6" t="n">
         <v>-0.013419399271567</v>
@@ -6108,7 +6242,7 @@
         <v>41.49965122767857</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>0.0358729758425756</v>
+        <v>0.0358590248654191</v>
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
@@ -6123,46 +6257,46 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>15.15499973297119</v>
+        <v>15.18000030517578</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>27.45650003433228</v>
+        <v>27.45700004577637</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>19.02140003204346</v>
+        <v>19.02152503490448</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>24.09476173102698</v>
+        <v>24.26404581176152</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.4306912375962335</v>
+        <v>-0.4297520726294261</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.3597380784062913</v>
+        <v>-0.3586818649663248</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.2106771286059566</v>
+        <v>-0.2093750155220423</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-3.402970529080413</v>
+        <v>-3.400976181440161</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-3.193624468018821</v>
+        <v>-3.19322559849077</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.2093460610615922</v>
+        <v>-0.2077505829493904</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>-0.2400474448421516</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>5058235</v>
+        <v>5076500</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>14267812.7</v>
+        <v>14268178</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.3545207037936516</v>
+        <v>0.3557917486030802</v>
       </c>
       <c r="P19" s="6" t="n">
         <v>0.0323432829789085</v>
@@ -6176,7 +6310,7 @@
         <v>1.624493053981236</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.1071918893173578</v>
+        <v>0.1070153505482702</v>
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
@@ -6191,46 +6325,46 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>224</v>
+        <v>223.8999938964844</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>233.8658001708984</v>
+        <v>233.8638000488281</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>128.1992501831055</v>
+        <v>128.1987501525879</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>34.04083201590227</v>
+        <v>34.00255700129621</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.1991419727425776</v>
+        <v>-0.1994995204692528</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.6737652016382305</v>
+        <v>0.6730179394238738</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>1.702376663643381</v>
+        <v>1.701170171856048</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-4.904863398721346</v>
+        <v>-4.912841093588696</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>4.143425622701941</v>
+        <v>4.141830083728471</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-9.048289021423289</v>
+        <v>-9.054671177317168</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>-9.60956168128553</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>12583967</v>
+        <v>12625881</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>45225673.34</v>
+        <v>45226511.62</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.2782483061201892</v>
+        <v>0.2791699060516664</v>
       </c>
       <c r="P20" s="6" t="n">
         <v>0.0645198535414377</v>
@@ -6244,7 +6378,7 @@
         <v>21.60285949707031</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>0.0964413370404924</v>
+        <v>0.09648441306817521</v>
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
@@ -6259,46 +6393,46 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>985.6799926757812</v>
+        <v>986.780029296875</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>916.7886010742188</v>
+        <v>916.8106018066406</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>472.4563502502442</v>
+        <v>472.4618504333496</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>45.01109675160277</v>
+        <v>45.10226858546104</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.0041462570521437</v>
+        <v>0.0052669023568061</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>1.11673750144753</v>
+        <v>1.119099818615513</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1.849856901700345</v>
+        <v>1.853037393320385</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>9.649591953040954</v>
+        <v>9.737344162130968</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>34.45673668271343</v>
+        <v>34.47428712453143</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-24.80714472967248</v>
+        <v>-24.73694296240046</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>-28.83193491040208</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>21331931</v>
+        <v>21437521</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>53937942.62</v>
+        <v>53940054.42</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.3954902609149611</v>
+        <v>0.3974323205734726</v>
       </c>
       <c r="P21" s="6" t="n">
         <v>0.0543756800501934</v>
@@ -6312,7 +6446,7 @@
         <v>89.7650146484375</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>0.09106912518814179</v>
+        <v>0.0909676037043424</v>
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
@@ -6327,46 +6461,46 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>196.1999969482422</v>
+        <v>195.3300018310547</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>224.030599975586</v>
+        <v>224.0132000732422</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>136.749475440979</v>
+        <v>136.7451254653931</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>30.26414306552548</v>
+        <v>30.13324092386908</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-0.1556206040933297</v>
+        <v>-0.1593647731194195</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.2115597998662006</v>
+        <v>0.2061874699657964</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.8280070213459552</v>
+        <v>0.819901225181366</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-6.484740791053866</v>
+        <v>-6.554142110943474</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.4753232266789595</v>
+        <v>0.4614429627010381</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-6.960064017732826</v>
+        <v>-7.015585073644512</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>-6.66147091221397</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>12109281</v>
+        <v>12169583</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>17939443.62</v>
+        <v>17940649.66</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6750087269428927</v>
+        <v>0.6783245440176552</v>
       </c>
       <c r="P22" s="6" t="n">
         <v>0.0310198990532244</v>
@@ -6380,7 +6514,7 @@
         <v>25.56014360700335</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>0.1302759633260654</v>
+        <v>0.1308562093247247</v>
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
@@ -6395,46 +6529,46 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>211.25</v>
+        <v>211.3399963378907</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>209.318200378418</v>
+        <v>209.3200003051758</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>191.9673504638672</v>
+        <v>191.9678004455566</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>60.32419239286454</v>
+        <v>60.3898539976604</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.0295335907524258</v>
+        <v>0.0299721907661683</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.07500893544959771</v>
+        <v>0.0754669087863559</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.1422623402794072</v>
+        <v>0.1427489647884512</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.6305316679308532</v>
+        <v>-0.6233524728854434</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-2.267444864858712</v>
+        <v>-2.266009025849629</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1.636913196927858</v>
+        <v>1.642656552964186</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>1.206196025562167</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>71254526</v>
+        <v>71857741</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>157811854.52</v>
+        <v>157823918.82</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.4515156748948139</v>
+        <v>0.4553032362727894</v>
       </c>
       <c r="P23" s="6" t="n">
         <v>0.0229450115312453</v>
@@ -6448,7 +6582,7 @@
         <v>6.875713893345424</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>0.0325477580750079</v>
+        <v>0.0325338980433808</v>
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
@@ -6463,46 +6597,46 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>91.68000030517578</v>
+        <v>91.66999816894533</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>106.640199432373</v>
+        <v>106.6399993896484</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>104.4500996780396</v>
+        <v>104.4500496673584</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>17.58944999670975</v>
+        <v>17.55839190490563</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>-0.0919175798677687</v>
+        <v>-0.0920166501562114</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.2100637408777261</v>
+        <v>-0.2101499216156278</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.1649512747912757</v>
+        <v>-0.1650423772245306</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-4.106942850348219</v>
+        <v>-4.107740741557478</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-3.341837186696401</v>
+        <v>-3.341996764938252</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.7651056636518181</v>
+        <v>-0.765743976619226</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>-0.7934742332941171</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>2612175</v>
+        <v>2618908</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3255961.5</v>
+        <v>3256096.16</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.802274535494354</v>
+        <v>0.8043091700338481</v>
       </c>
       <c r="P24" s="6" t="n">
         <v>0.0177384274683925</v>
@@ -6516,7 +6650,7 @@
         <v>4.48357173374721</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>0.04890457808489</v>
+        <v>0.0489099140755311</v>
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
@@ -6531,46 +6665,46 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>25.86009979248047</v>
+        <v>25.8799991607666</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>35.88060207366944</v>
+        <v>35.88100006103516</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>25.37005048274994</v>
+        <v>25.37014997959137</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>41.82511788429533</v>
+        <v>41.87614750781767</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.1698202212144808</v>
+        <v>-0.1691813971846308</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.2378396828798231</v>
+        <v>-0.2372531998822649</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.0165133352831674</v>
+        <v>0.0172955431396293</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-2.436898267771998</v>
+        <v>-2.435310853777661</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-2.394171281795738</v>
+        <v>-2.39385379899687</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.0427269859762597</v>
+        <v>-0.0414570547807908</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>-0.0149246408257801</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>2895182</v>
+        <v>2919047</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>13306457.64</v>
+        <v>13306934.94</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.2175772153887832</v>
+        <v>0.2193628369840065</v>
       </c>
       <c r="P25" s="6" t="n">
         <v>0.0084746235925221</v>
@@ -6584,7 +6718,7 @@
         <v>2.376357078552246</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>0.0918928038801782</v>
+        <v>0.09182214666199599</v>
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
@@ -6599,46 +6733,46 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>13.71000003814697</v>
+        <v>13.6899995803833</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>11.47240003585815</v>
+        <v>11.47200002670288</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>9.128275010585783</v>
+        <v>9.128175008296967</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>75.11415241761875</v>
+        <v>74.99999453168354</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.2079294781813607</v>
+        <v>0.2061673233715402</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.559726973566079</v>
+        <v>0.5574516086229084</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.5979021165567866</v>
+        <v>0.595571060852647</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.6778215903978122</v>
+        <v>0.6762261122856099</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.6463457043468233</v>
+        <v>0.6460266087243828</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.0314758860509889</v>
+        <v>0.0301995035612271</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>0.042571941463545</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>157103</v>
+        <v>159686</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>663284.0600000001</v>
+        <v>663335.72</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.2368562874856362</v>
+        <v>0.2407317971659961</v>
       </c>
       <c r="P26" s="6" t="n">
         <v>-0.0110537672736636</v>
@@ -6652,7 +6786,7 @@
         <v>0.6038284982953753</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>0.0440429246254756</v>
+        <v>0.04410726930632</v>
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
@@ -6667,46 +6801,46 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>79.84999847412109</v>
+        <v>79.90499877929688</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>107.0351998901367</v>
+        <v>107.0362998962402</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>77.06880010604858</v>
+        <v>77.06907510757446</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>38.10932385566196</v>
+        <v>38.16229213562648</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-0.2201386956723248</v>
+        <v>-0.2196015308563893</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.1056493647805518</v>
+        <v>0.1064109308875325</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.0915813755633188</v>
+        <v>-0.0909556610670615</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-7.625339857162189</v>
+        <v>-7.620952368430224</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-6.246328014413261</v>
+        <v>-6.245450516666868</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-1.379011842748928</v>
+        <v>-1.375501851763356</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>-1.60128212643402</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>10652271</v>
+        <v>10694414</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>28179337.42</v>
+        <v>28180180.28</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.3780170853995899</v>
+        <v>0.3795012627222269</v>
       </c>
       <c r="P27" s="6" t="n">
         <v>0.0264563885114627</v>
@@ -6720,7 +6854,7 @@
         <v>7.732856750488281</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>0.09684229052295409</v>
+        <v>0.09677563192068819</v>
       </c>
       <c r="T27" s="6" t="inlineStr">
         <is>
@@ -6735,46 +6869,46 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>18.68499946594238</v>
+        <v>18.66410064697266</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>16.94929992675781</v>
+        <v>16.94888195037842</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>21.97360002040863</v>
+        <v>21.97349552631378</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>62.92860938357886</v>
+        <v>62.78444622690394</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.1269601659784451</v>
+        <v>0.1256996823194647</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.0432718942006165</v>
+        <v>0.0421050142928678</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.297556421128518</v>
+        <v>-0.2983420910033306</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.4144573403991778</v>
+        <v>0.4127901981451813</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.373533959028374</v>
+        <v>0.3732005305775747</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.0409233813708038</v>
+        <v>0.0395896675676066</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>0.0328078631428616</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>58380159</v>
+        <v>58836149</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>76361681.18000001</v>
+        <v>76370800.98</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.7645216566459045</v>
+        <v>0.7704010989148591</v>
       </c>
       <c r="P28" s="6" t="n">
         <v>0.0044125718372439</v>
@@ -6788,7 +6922,7 @@
         <v>0.9414285932268416</v>
       </c>
       <c r="S28" s="6" t="n">
-        <v>0.0503841916047579</v>
+        <v>0.0504406084725835</v>
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
@@ -6803,46 +6937,46 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>6.429999828338623</v>
+        <v>6.420000076293945</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>5.93479998588562</v>
+        <v>5.934599990844727</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>4.497100005149841</v>
+        <v>4.497050006389617</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>62.8078769713569</v>
+        <v>62.65356173241101</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.301619383372341</v>
+        <v>0.2995951420911973</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.0516224735455606</v>
+        <v>-0.0530973631820257</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.4008713757260598</v>
+        <v>0.3986927805817788</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.3323023162992076</v>
+        <v>0.3315046152813989</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.3112106828260628</v>
+        <v>0.3110511426225011</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.0210916334731448</v>
+        <v>0.0204534726588978</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>0.0646032293833483</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>313091</v>
+        <v>314461</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>1212393.82</v>
+        <v>1212421.22</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2582419959877393</v>
+        <v>0.2593661301968964</v>
       </c>
       <c r="P29" s="6" t="n">
         <v>0.0046656626141934</v>
@@ -6856,7 +6990,7 @@
         <v>0.6430713449205671</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>0.1000110983030497</v>
+        <v>0.1001668749654892</v>
       </c>
       <c r="T29" s="6" t="inlineStr">
         <is>
@@ -6871,46 +7005,46 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>395.7799987792969</v>
+        <v>395.6700134277344</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>409.9185992431641</v>
+        <v>409.9163995361328</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>417.7494000244141</v>
+        <v>417.7488500976563</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>54.21050082981659</v>
+        <v>54.18055211500717</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-0.0262037597825122</v>
+        <v>-0.0264743730579705</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.0867105587967795</v>
+        <v>0.0864085671771308</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.1184515183712139</v>
+        <v>-0.1186964964397631</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-1.327243446800594</v>
+        <v>-1.33601720703922</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-1.257520683497202</v>
+        <v>-1.259275435544927</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.0697227633033923</v>
+        <v>-0.07674177149429259</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>0.3816312784934397</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>15725469</v>
+        <v>15810675</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>48283799.38</v>
+        <v>48285503.5</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.3256883095764366</v>
+        <v>0.3274414442007423</v>
       </c>
       <c r="P30" s="6" t="n">
         <v>0.0109940121352903</v>
@@ -6924,7 +7058,7 @@
         <v>18.56714085170201</v>
       </c>
       <c r="S30" s="6" t="n">
-        <v>0.0469127821238278</v>
+        <v>0.0469258225834521</v>
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
@@ -6939,46 +7073,46 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>423.4599914550781</v>
+        <v>423.1400146484375</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>425.0546002197266</v>
+        <v>425.0482006835937</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>349.7386000061035</v>
+        <v>349.7370001220703</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>45.96163923757332</v>
+        <v>45.85341478993548</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-0.0011086765004205</v>
+        <v>-0.001863463404317</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.1146910293153182</v>
+        <v>0.1138487412995705</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.2763661737880329</v>
+        <v>0.2754017200482843</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>1.413034311129877</v>
+        <v>1.387509095785333</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>5.423987400600367</v>
+        <v>5.418882357531459</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-4.01095308947049</v>
+        <v>-4.031373261746126</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>-3.711786865119478</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9541232</v>
+        <v>9618491</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>13666228.64</v>
+        <v>13667773.82</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.6981613034098922</v>
+        <v>0.7037350139585496</v>
       </c>
       <c r="P31" s="6" t="n">
         <v>0.0220361706931489</v>
@@ -6992,7 +7126,7 @@
         <v>19.97285679408482</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>0.04716586500995</v>
+        <v>0.0472015316506502</v>
       </c>
       <c r="T31" s="6" t="inlineStr">
         <is>
@@ -7007,46 +7141,46 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>303.8349914550781</v>
+        <v>303.7799987792969</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>324.2385009765625</v>
+        <v>324.2374011230469</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>238.4757252502441</v>
+        <v>238.4754502868653</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>45.66485867189928</v>
+        <v>45.64983215523345</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.003186173452135</v>
+        <v>0.0030046015676041</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.0214969505027718</v>
+        <v>-0.021674054860286</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.7869493244510541</v>
+        <v>0.7866258951963576</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-1.938092445135282</v>
+        <v>-1.942479325254567</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-1.187262341140513</v>
+        <v>-1.18813971716437</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.7508301039947693</v>
+        <v>-0.7543396080901967</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>-0.1480541656201379</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>2048915</v>
+        <v>2062271</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>6150476.3</v>
+        <v>6150743.42</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3331311105125306</v>
+        <v>0.3352880878259753</v>
       </c>
       <c r="P32" s="6" t="n">
         <v>0.031582057136426</v>
@@ -7060,7 +7194,7 @@
         <v>21.269287109375</v>
       </c>
       <c r="S32" s="6" t="n">
-        <v>0.0700027571133776</v>
+        <v>0.0700154295702253</v>
       </c>
       <c r="T32" s="6" t="inlineStr">
         <is>
@@ -7075,46 +7209,46 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>884.8900146484375</v>
+        <v>884.3150024414062</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>877.3207971191406</v>
+        <v>877.309296875</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>479.6012999725342</v>
+        <v>479.598424911499</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>38.44778386563386</v>
+        <v>38.39453407767014</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-0.0495681866171711</v>
+        <v>-0.0501857886757309</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.6588370024717727</v>
+        <v>0.6577590701749829</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1.752550654497987</v>
+        <v>1.750762013875302</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-3.479873973122949</v>
+        <v>-3.525743892772084</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>11.33580989947744</v>
+        <v>11.32663591554761</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-14.81568387260039</v>
+        <v>-14.8523798083197</v>
       </c>
       <c r="L33" s="6" t="n">
         <v>-17.58862389405815</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>2183994</v>
+        <v>2206861</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>4342923.88</v>
+        <v>4343381.22</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.5028856273667869</v>
+        <v>0.5080974678985236</v>
       </c>
       <c r="P33" s="6" t="n">
         <v>0.0451049293978258</v>
@@ -7128,7 +7262,7 @@
         <v>84.29928588867188</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>0.0952652696868362</v>
+        <v>0.0953272144608419</v>
       </c>
       <c r="T33" s="6" t="inlineStr">
         <is>
@@ -7176,13 +7310,13 @@
         <v>-0.1129581202809464</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>12093081</v>
+        <v>12134756</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>55533865.62</v>
+        <v>55534699.12</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2177604757923567</v>
+        <v>0.2185076392289275</v>
       </c>
       <c r="P34" s="6" t="n">
         <v>0.0112075006381963</v>
@@ -7211,46 +7345,46 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>268.0299987792969</v>
+        <v>267.8599853515625</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>226.0997998046875</v>
+        <v>226.0963995361328</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>160.4395001983643</v>
+        <v>160.4386501312256</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>75.78787063755613</v>
+        <v>75.74305421730782</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.1658547450852958</v>
+        <v>0.1651152347231907</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>1.424075242100623</v>
+        <v>1.422537633090914</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1.117642406775303</v>
+        <v>1.116299170399034</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>12.07820061967075</v>
+        <v>12.06463829495118</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>11.57475942396868</v>
+        <v>11.57204695902477</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.5034411957020701</v>
+        <v>0.4925913359264129</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>0.3955764881293149</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>2297589</v>
+        <v>2309270</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>6066247.78</v>
+        <v>6066481.4</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.3787496131587292</v>
+        <v>0.38066052588573</v>
       </c>
       <c r="P35" s="6" t="n">
         <v>-0.0192129762097973</v>
@@ -7264,7 +7398,7 @@
         <v>13.84728785923549</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v>0.051663201590497</v>
+        <v>0.0516959927443478</v>
       </c>
       <c r="T35" s="6" t="inlineStr">
         <is>
@@ -7279,7 +7413,7 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>184.3399963378907</v>
+        <v>183.3200073242188</v>
       </c>
       <c r="C36" s="6" t="inlineStr"/>
       <c r="D36" s="6" t="inlineStr"/>
@@ -7288,19 +7422,19 @@
       <c r="G36" s="6" t="inlineStr"/>
       <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" s="6" t="n">
-        <v>0.4096172757981549</v>
+        <v>0.328250630832855</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.1031477699115976</v>
+        <v>-0.1194210989046576</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.5127650457097526</v>
+        <v>0.4476717297375126</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>-0.9253561253561428</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>49818486</v>
+        <v>50067470</v>
       </c>
       <c r="N36" s="6" t="inlineStr"/>
       <c r="O36" s="6" t="inlineStr"/>
@@ -7327,46 +7461,46 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>8.595000267028809</v>
+        <v>8.604999542236328</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>10.93890003204346</v>
+        <v>10.93910001754761</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>18.45042497634888</v>
+        <v>18.45047497272492</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>21.21982595865489</v>
+        <v>21.41950780719866</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-0.1309403469503685</v>
+        <v>-0.1299292979250497</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.1614633885825552</v>
+        <v>-0.1604878495379191</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.5641480443050408</v>
+        <v>-0.5636409816500868</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.6464927717050593</v>
+        <v>-0.645695108725544</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.531912363660073</v>
+        <v>-0.5317528310641699</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.1145804080449862</v>
+        <v>-0.1139422776613741</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>-0.1257283657885731</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>16468080</v>
+        <v>16546346</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>33064277.6</v>
+        <v>33065842.92</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.4980625979259259</v>
+        <v>0.5004059941865834</v>
       </c>
       <c r="P37" s="6" t="n">
         <v>0.0299401183926648</v>
@@ -7380,7 +7514,7 @@
         <v>0.6735711097717285</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>0.0783677822972976</v>
+        <v>0.0782767165141157</v>
       </c>
       <c r="T37" s="6" t="inlineStr">
         <is>
@@ -7395,46 +7529,46 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>46.15000152587891</v>
+        <v>46.27999877929688</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>60.62759986877441</v>
+        <v>60.63019981384277</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>81.45894981384278</v>
+        <v>81.45959980010986</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>24.27772708696961</v>
+        <v>24.73366460018019</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-0.1972516928423634</v>
+        <v>-0.1949904778550161</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.2121884588024429</v>
+        <v>-0.2099693183218249</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.5497560826743522</v>
+        <v>-0.5484878167873475</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-3.80704509611315</v>
+        <v>-3.796674944843346</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-3.476739302028593</v>
+        <v>-3.474665271774632</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.3303057940845564</v>
+        <v>-0.3220096730687136</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>-0.3462640816307631</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>3913687</v>
+        <v>3940331</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>12377993.74</v>
+        <v>12378526.62</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.3161810453460449</v>
+        <v>0.3183198712545969</v>
       </c>
       <c r="P38" s="6" t="n">
         <v>0.0251036384349932</v>
@@ -7448,7 +7582,7 @@
         <v>3.443371636526925</v>
       </c>
       <c r="S38" s="6" t="n">
-        <v>0.0746126007080635</v>
+        <v>0.074403019173529</v>
       </c>
       <c r="T38" s="6" t="inlineStr">
         <is>
@@ -7463,46 +7597,46 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>7.751699924468994</v>
+        <v>7.770500183105469</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>9.766033992767332</v>
+        <v>9.766409997940064</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>12.02980851411819</v>
+        <v>12.02990251541138</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>26.95491660880916</v>
+        <v>27.30519493945793</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>-0.1528196450663768</v>
+        <v>-0.1507649719056915</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.1191250276755196</v>
+        <v>-0.1169886346949526</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.4969695002449477</v>
+        <v>-0.4957494964277749</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.5917634059279315</v>
+        <v>-0.5902636701962471</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.487911449231736</v>
+        <v>-0.4876115020853991</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.1038519566961955</v>
+        <v>-0.1026521681108479</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>-0.1257187896488844</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>32649586</v>
+        <v>33279533</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>37291201.72</v>
+        <v>37303800.66</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.8755305405588308</v>
+        <v>0.8921217787785596</v>
       </c>
       <c r="P39" s="6" t="n">
         <v>0.0100267124430337</v>
@@ -7516,7 +7650,7 @@
         <v>0.5577142919812884</v>
       </c>
       <c r="S39" s="6" t="n">
-        <v>0.07194735315034689</v>
+        <v>0.0717732808492642</v>
       </c>
       <c r="T39" s="6" t="inlineStr">
         <is>
@@ -7531,46 +7665,46 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>6.824999809265137</v>
+        <v>6.810200214385986</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>7.679700021743774</v>
+        <v>7.679404029846191</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>10.25875001192093</v>
+        <v>10.25867601394653</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>58.071274466897</v>
+        <v>57.80947035309124</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>-0.0108696065312592</v>
+        <v>-0.0130144753246794</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.0208034412182567</v>
+        <v>-0.0229267690984062</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.4101123604767019</v>
+        <v>-0.4113914957636088</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.2347152578761129</v>
+        <v>-0.2358958523394063</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.3051837664173178</v>
+        <v>-0.3054198853099765</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.0704685085412049</v>
+        <v>0.06952403297057019</v>
       </c>
       <c r="L40" s="6" t="n">
         <v>0.0561779742976243</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>20865622</v>
+        <v>21151990</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>28661580.44</v>
+        <v>28667307.8</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.7279997013311943</v>
+        <v>0.7378436143208397</v>
       </c>
       <c r="P40" s="6" t="n">
         <v>-0.0154083063419491</v>
@@ -7584,7 +7718,7 @@
         <v>0.4056429181780134</v>
       </c>
       <c r="S40" s="6" t="n">
-        <v>0.0594348614672986</v>
+        <v>0.059564022408787</v>
       </c>
       <c r="T40" s="6" t="inlineStr">
         <is>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -480,8 +480,8 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>370.0549926757813</v>
+        <v>369.1400146484375</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.082723417254077</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.2836450710782</v>
+        <v>0.2859555038411281</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>75</v>
@@ -573,13 +573,13 @@
         <v>12</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.0324276127535283</v>
+        <v>0.0325079902579204</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>277.1991489955358</v>
+        <v>276.284170968192</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>509.3387581961496</v>
+        <v>508.4237801688058</v>
       </c>
     </row>
     <row r="3">
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>986.780029296875</v>
+        <v>985.5789794921876</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.0543756800501934</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.3974323205734726</v>
+        <v>0.3999018034307867</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>75</v>
@@ -614,13 +614,13 @@
         <v>12</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.0121607649564518</v>
+        <v>0.0121755843516294</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>807.25</v>
+        <v>806.0489501953126</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1256.075073242188</v>
+        <v>1254.8740234375</v>
       </c>
     </row>
     <row r="4">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>240</v>
+        <v>239.2899932861328</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.06596166699561611</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.2778866728713306</v>
+        <v>0.2805843400320134</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>75</v>
@@ -655,13 +655,13 @@
         <v>12</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.05</v>
+        <v>0.0501483569588758</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>186.4292842320033</v>
+        <v>185.7192775181361</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>320.356073651995</v>
+        <v>319.6460669381278</v>
       </c>
     </row>
   </sheetData>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>182.3800048828125</v>
+        <v>182.6000061035156</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>89</v>
@@ -911,28 +911,28 @@
         <v>75</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>62.32894220433992</v>
+        <v>62.42993757952711</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.0151807899125376</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.3518022926258758</v>
+        <v>0.3561460819408269</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1.592242064326245</v>
+        <v>1.606282028268555</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>161.4555947440011</v>
+        <v>161.6755959647042</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>213.7666200910296</v>
+        <v>213.9866213117327</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>10.46220506940569</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>9.73</v>
+        <v>9.74</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0.053341</v>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>211.3399963378907</v>
+        <v>211.4349975585937</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>89</v>
@@ -1005,22 +1005,22 @@
         <v>75</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>60.3898539976604</v>
+        <v>60.45893179215103</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.0229450115312453</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.4553032362727894</v>
+        <v>0.4617450771906775</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1.642656552964186</v>
+        <v>1.648719308929313</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>201.0264254978725</v>
+        <v>201.1214267185756</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>225.0914241245815</v>
+        <v>225.1864253452846</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>6.875713893345424</v>
@@ -1029,7 +1029,7 @@
         <v>13.95</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.066015</v>
+        <v>0.065986</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>1.12</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>556.010009765625</v>
+        <v>554.2330932617188</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>82</v>
@@ -1099,28 +1099,28 @@
         <v>50</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>55.95874423080636</v>
+        <v>55.69930630970238</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0.0624019610194614</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.4423987360224728</v>
+        <v>0.4455891291291103</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>-2.556456923382285</v>
+        <v>-2.669855583460667</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>498.932856968471</v>
+        <v>497.1559404645647</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>632.1128801618304</v>
+        <v>630.3359636579241</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>38.05143519810268</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>10.87</v>
+        <v>10.84</v>
       </c>
       <c r="R4" s="2" t="n">
         <v>0.019555</v>
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>986.780029296875</v>
+        <v>985.5789794921876</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>82</v>
@@ -1193,22 +1193,22 @@
         <v>50</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>45.10226858546104</v>
+        <v>45.00270952258949</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0.0543756800501934</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.3974323205734726</v>
+        <v>0.3999018034307867</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-24.73694296240046</v>
+        <v>-24.8135911550642</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>807.25</v>
+        <v>806.0489501953126</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1256.075073242188</v>
+        <v>1254.8740234375</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>89.7650146484375</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1157.300048828125</v>
+        <v>1156.03857421875</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>82</v>
@@ -1287,22 +1287,22 @@
         <v>50</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>58.02083686703796</v>
+        <v>57.78798045611461</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>-0.013419399271567</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.4153383493550943</v>
+        <v>0.4179615676830365</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-6.810537009400178</v>
+        <v>-6.89104137193597</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1095.050571986607</v>
+        <v>1093.789097377232</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1240.299351283482</v>
+        <v>1239.037876674107</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>41.49965122767857</v>
@@ -1311,7 +1311,7 @@
         <v>13.95</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.012055</v>
+        <v>0.012069</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>1.12</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7.667600154876709</v>
+        <v>7.700099945068359</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>82</v>
@@ -1381,28 +1381,28 @@
         <v>50</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>49.97684546433793</v>
+        <v>50.29223738542261</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>-0.0049382666628676</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.4885043269260495</v>
+        <v>0.492464935245167</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-0.1233746626046179</v>
+        <v>-0.1213006019200216</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>6.190386022840228</v>
+        <v>6.222885813031878</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>9.883421352931432</v>
+        <v>9.915921143123082</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>0.7386070660182408</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>5.79</v>
+        <v>5.82</v>
       </c>
       <c r="R7" s="2" t="n">
         <v>0.755569</v>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>370.0549926757813</v>
+        <v>369.1400146484375</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>82</v>
@@ -1475,28 +1475,28 @@
         <v>50</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46.18162304129646</v>
+        <v>46.04180070856442</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0.082723417254077</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.2836450710782</v>
+        <v>0.2859555038411281</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-11.17843774179846</v>
+        <v>-11.23682950194807</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>277.1991489955358</v>
+        <v>276.284170968192</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>509.3387581961496</v>
+        <v>508.4237801688058</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>46.42792184012277</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="R8" s="2" t="n">
         <v>0.01202</v>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>16.86000061035156</v>
+        <v>16.78000068664551</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>79</v>
@@ -1569,22 +1569,22 @@
         <v>75</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>74.52830460284595</v>
+        <v>74.33460369032056</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>0.0098826338563442</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.2092578568328409</v>
+        <v>0.2124610111069697</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.1266448202114016</v>
+        <v>0.1215394119748887</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>13.86100046975272</v>
+        <v>13.78100054604667</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>21.35850082124983</v>
+        <v>21.27850089754377</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.499500070299421</v>
@@ -1602,7 +1602,7 @@
         <v>13.95</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>0.1188415912537745</v>
+        <v>0.1135327396108803</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" s="3" t="inlineStr">
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>13.6899995803833</v>
+        <v>13.69999980926514</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>79</v>
@@ -1689,22 +1689,22 @@
         <v>75</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>74.99999453168354</v>
+        <v>75.05720409307425</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>-0.0110537672736636</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.2407317971659961</v>
+        <v>0.2419274868476246</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.0301995035612271</v>
+        <v>0.0308376948061073</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>12.48234258379255</v>
+        <v>12.49234281267438</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>15.50148507526943</v>
+        <v>15.51148530415126</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.6038284982953753</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>267.8599853515625</v>
+        <v>268.0700073242188</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>79</v>
@@ -1787,22 +1787,22 @@
         <v>75</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>75.74305421730782</v>
+        <v>75.79839303697977</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>-0.0192129762097973</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.38066052588573</v>
+        <v>0.3834355941984572</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.4925913359264129</v>
+        <v>0.5059944475717248</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>247.0890535627093</v>
+        <v>247.2990755353655</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>295.5545610700335</v>
+        <v>295.7645830426897</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>13.84728785923549</v>
@@ -1811,7 +1811,7 @@
         <v>6.98</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.026043</v>
+        <v>0.026023</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>1.12</v>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>393.760009765625</v>
+        <v>393.8800048828125</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>79</v>
@@ -1885,22 +1885,22 @@
         <v>75</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>55.54740946415497</v>
+        <v>55.59085024466999</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0.030087289573326</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.3741449206336948</v>
+        <v>0.3773469538089753</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.276779669505886</v>
+        <v>3.284437477554338</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>371.2546604701451</v>
+        <v>371.3746555873326</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>423.7671421595982</v>
+        <v>423.8871372767857</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>15.00356619698661</v>
@@ -1909,7 +1909,7 @@
         <v>6.98</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.017716</v>
+        <v>0.017711</v>
       </c>
       <c r="S12" s="4" t="n">
         <v>1.12</v>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6.420000076293945</v>
+        <v>6.409999847412109</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>78</v>
@@ -1979,28 +1979,28 @@
         <v>75</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>62.65356173241101</v>
+        <v>62.49999561730699</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>0.0046656626141934</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2593661301968964</v>
+        <v>0.266428961265994</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.0204534726588978</v>
+        <v>0.0198152814140169</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>5.133857386452811</v>
+        <v>5.123857157570975</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>8.349214111055646</v>
+        <v>8.33921388217381</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0.6430713449205671</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="R13" s="4" t="n">
         <v>0.433909</v>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>240</v>
+        <v>239.2899932861328</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>75</v>
@@ -2073,28 +2073,28 @@
         <v>50</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>41.66210579173344</v>
+        <v>41.44548941404696</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>0.06596166699561611</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2778866728713306</v>
+        <v>0.2805843400320134</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.584574178165363</v>
+        <v>-4.62988514793923</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>186.4292842320033</v>
+        <v>185.7192775181361</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>320.356073651995</v>
+        <v>319.6460669381278</v>
       </c>
       <c r="P14" s="4" t="n">
         <v>26.78535788399833</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="R14" s="4" t="n">
         <v>0.010417</v>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>358.1199951171875</v>
+        <v>357.7049865722656</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>71</v>
@@ -2167,22 +2167,22 @@
         <v>75</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>59.81018252640515</v>
+        <v>59.5353799756744</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>-0.0040282924977889</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.2760469549390547</v>
+        <v>0.2815317723858271</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.6088060032133988</v>
+        <v>0.5823211274121287</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>343.1746357509068</v>
+        <v>342.7596272059849</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>378.0471409388951</v>
+        <v>377.6321323939732</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.963572910853795</v>
@@ -2200,7 +2200,7 @@
         <v>13.95</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>-0.0237180232399711</v>
+        <v>-0.024849390848965</v>
       </c>
       <c r="V15" s="3" t="inlineStr"/>
       <c r="W15" s="3" t="inlineStr">
@@ -2253,24 +2253,24 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Internet/E-Commerce</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>18.66410064697266</v>
+        <v>246.75</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -2281,31 +2281,31 @@
         <v>40</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>75</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>62.78444622690394</v>
+        <v>65.79999320984146</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.0044125718372439</v>
+        <v>-0.0071974396379796</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0.7704010989148591</v>
+        <v>0.3176584110623274</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.0395896675676066</v>
+        <v>1.694144316680325</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>16.78124346051897</v>
+        <v>235.5332189287458</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>21.48838642665318</v>
+        <v>261.7057080950056</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.9414285932268416</v>
+        <v>7.47785404750279</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -2319,25 +2319,11 @@
       <c r="T16" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U16" s="5" t="n">
-        <v>0.0144289784832726</v>
-      </c>
+      <c r="U16" s="5" t="inlineStr"/>
       <c r="V16" s="5" t="inlineStr"/>
-      <c r="W16" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="X16" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="Y16" s="5" t="inlineStr">
-        <is>
-          <t>No exit trigger</t>
-        </is>
-      </c>
+      <c r="W16" s="5" t="inlineStr"/>
+      <c r="X16" s="5" t="inlineStr"/>
+      <c r="Y16" s="5" t="inlineStr"/>
       <c r="Z16" s="5" t="n">
         <v>4</v>
       </c>
@@ -2346,19 +2332,11 @@
       </c>
       <c r="AB16" s="5" t="inlineStr">
         <is>
-          <t>Already held</t>
-        </is>
-      </c>
-      <c r="AC16" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="AD16" s="5" t="inlineStr">
-        <is>
-          <t>Held, but not strong enough to add</t>
-        </is>
-      </c>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AC16" s="5" t="inlineStr"/>
+      <c r="AD16" s="5" t="inlineStr"/>
       <c r="AE16" s="5" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
@@ -2369,24 +2347,24 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>423.1400146484375</v>
+        <v>18.6299991607666</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -2397,31 +2375,31 @@
         <v>40</v>
       </c>
       <c r="H17" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="I17" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="I17" s="5" t="n">
-        <v>50</v>
-      </c>
       <c r="J17" s="5" t="n">
-        <v>45.85341478993548</v>
+        <v>62.54678624610271</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.0220361706931489</v>
+        <v>0.0044125718372439</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.7037350139585496</v>
+        <v>0.7828609923310054</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>-4.031373261746126</v>
+        <v>0.0374133903852264</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>393.1807294573102</v>
+        <v>16.74714197431292</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>463.0857282366072</v>
+        <v>21.45428494044713</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>19.97285679408482</v>
+        <v>0.9414285932268416</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -2435,11 +2413,25 @@
       <c r="T17" s="5" t="n">
         <v>13.95</v>
       </c>
-      <c r="U17" s="5" t="inlineStr"/>
+      <c r="U17" s="5" t="n">
+        <v>0.0125754985609823</v>
+      </c>
       <c r="V17" s="5" t="inlineStr"/>
-      <c r="W17" s="5" t="inlineStr"/>
-      <c r="X17" s="5" t="inlineStr"/>
-      <c r="Y17" s="5" t="inlineStr"/>
+      <c r="W17" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X17" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Y17" s="5" t="inlineStr">
+        <is>
+          <t>No exit trigger</t>
+        </is>
+      </c>
       <c r="Z17" s="5" t="n">
         <v>4</v>
       </c>
@@ -2448,14 +2440,22 @@
       </c>
       <c r="AB17" s="5" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
-        </is>
-      </c>
-      <c r="AC17" s="5" t="inlineStr"/>
-      <c r="AD17" s="5" t="inlineStr"/>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AC17" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AD17" s="5" t="inlineStr">
+        <is>
+          <t>Held, but not strong enough to add</t>
+        </is>
+      </c>
       <c r="AE17" s="5" t="inlineStr">
         <is>
-          <t>Positive momentum</t>
+          <t>MACD/volume acceleration</t>
         </is>
       </c>
       <c r="AF17" s="5" t="inlineStr"/>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>884.3150024414062</v>
+        <v>884.8400268554688</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>65</v>
@@ -2497,22 +2497,22 @@
         <v>50</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>38.39453407767014</v>
+        <v>38.44315833178496</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>0.0451049293978258</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.5080974678985236</v>
+        <v>0.5226062973268892</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>-14.8523798083197</v>
+        <v>-14.81887397676708</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>757.8660736083984</v>
+        <v>758.3910980224609</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>1052.91357421875</v>
+        <v>1053.438598632812</v>
       </c>
       <c r="P18" s="5" t="n">
         <v>84.29928588867188</v>
@@ -2557,12 +2557,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Data Centers</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>303.7799987792969</v>
+        <v>423.3699951171875</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -2585,31 +2585,31 @@
         <v>40</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>50</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>45.64983215523345</v>
+        <v>45.93124389648438</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.031582057136426</v>
+        <v>0.0220361706931489</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.3352880878259753</v>
+        <v>0.7110841172580539</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>-0.7543396080901967</v>
+        <v>-4.016696445506819</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>271.8760681152344</v>
+        <v>393.4107099260602</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>346.3185729980469</v>
+        <v>463.3157087053572</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>21.269287109375</v>
+        <v>19.97285679408482</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2641,18 +2641,22 @@
       </c>
       <c r="AC19" s="5" t="inlineStr"/>
       <c r="AD19" s="5" t="inlineStr"/>
-      <c r="AE19" s="5" t="inlineStr"/>
+      <c r="AE19" s="5" t="inlineStr">
+        <is>
+          <t>Positive momentum</t>
+        </is>
+      </c>
       <c r="AF19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Internet/E-Commerce</t>
+          <t>Data Centers</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2661,10 +2665,10 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>246.4400024414062</v>
+        <v>303.7799987792969</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -2675,31 +2679,31 @@
         <v>40</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>65.29396912736486</v>
+        <v>45.64983215523345</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.0071974396379796</v>
+        <v>0.031582057136426</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.3137200976709515</v>
+        <v>0.3382401427889498</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>1.674360996701665</v>
+        <v>-0.7543396080901967</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>235.2232213701521</v>
+        <v>271.8760681152344</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>261.3957105364119</v>
+        <v>346.3185729980469</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>7.47785404750279</v>
+        <v>21.269287109375</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2731,11 +2735,7 @@
       </c>
       <c r="AC20" s="5" t="inlineStr"/>
       <c r="AD20" s="5" t="inlineStr"/>
-      <c r="AE20" s="5" t="inlineStr">
-        <is>
-          <t>MACD/volume acceleration</t>
-        </is>
-      </c>
+      <c r="AE20" s="5" t="inlineStr"/>
       <c r="AF20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>104.4499969482422</v>
+        <v>104.3850021362305</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>56</v>
@@ -2775,22 +2775,22 @@
         <v>75</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>64.68646542671178</v>
+        <v>64.63905871110767</v>
       </c>
       <c r="K21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.3926476014849354</v>
+        <v>0.399719912029342</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>1.408388142881888</v>
+        <v>1.404240325819019</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>92.50713893345426</v>
+        <v>92.44214412144254</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>122.3642839704241</v>
+        <v>122.2992891584124</v>
       </c>
       <c r="P21" s="5" t="n">
         <v>5.971429007393973</v>
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>284.3699951171875</v>
+        <v>284.0150146484375</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>55</v>
@@ -2869,22 +2869,22 @@
         <v>50</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>28.61835280220669</v>
+        <v>28.56548425991689</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>0.0376936349020097</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.5560909738241342</v>
+        <v>0.5593897862464283</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-9.896550253202626</v>
+        <v>-9.919204277419208</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>225.607421875</v>
+        <v>225.25244140625</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>372.5138549804688</v>
+        <v>372.1588745117188</v>
       </c>
       <c r="P22" s="5" t="n">
         <v>29.38128662109375</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>223.8999938964844</v>
+        <v>223.610107421875</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>55</v>
@@ -2963,22 +2963,22 @@
         <v>50</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>34.00255700129621</v>
+        <v>33.89135825856491</v>
       </c>
       <c r="K23" s="5" t="n">
         <v>0.0645198535414377</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.2791699060516664</v>
+        <v>0.2813797905007987</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-9.054671177317168</v>
+        <v>-9.073171054899062</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>191.4957046508789</v>
+        <v>191.2058181762696</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>267.105712890625</v>
+        <v>266.8158264160156</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>21.60285949707031</v>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>195.3300018310547</v>
+        <v>194.8000030517578</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>55</v>
@@ -3057,22 +3057,22 @@
         <v>50</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>30.13324092386908</v>
+        <v>30.05404926893323</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>0.0310198990532244</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.6783245440176552</v>
+        <v>0.6879874794197867</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>-7.015585073644512</v>
+        <v>-7.049408357565459</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>144.209714617048</v>
+        <v>143.6797158377511</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>272.0104326520648</v>
+        <v>271.4804338727679</v>
       </c>
       <c r="P24" s="5" t="n">
         <v>25.56014360700335</v>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>107.2900009155273</v>
+        <v>107.1252975463867</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>55</v>
@@ -3151,22 +3151,22 @@
         <v>50</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>31.26405772394173</v>
+        <v>31.09388122372084</v>
       </c>
       <c r="K25" s="5" t="n">
         <v>0.0469355722360184</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.452336790926341</v>
+        <v>0.4559808237337823</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-3.423133852645206</v>
+        <v>-3.433644836886661</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>93.07107162475586</v>
+        <v>92.90636825561523</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>126.2485733032227</v>
+        <v>126.083869934082</v>
       </c>
       <c r="P25" s="5" t="n">
         <v>9.479286193847656</v>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>25.8799991607666</v>
+        <v>25.79000091552734</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>54</v>
@@ -3245,22 +3245,22 @@
         <v>50</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>41.87614750781767</v>
+        <v>41.64634391000573</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>0.0084746235925221</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.2193628369840065</v>
+        <v>0.2247595512712267</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>-0.0414570547807908</v>
+        <v>-0.047200532539652</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>21.12728500366211</v>
+        <v>21.03728675842285</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>33.00907039642334</v>
+        <v>32.91907215118408</v>
       </c>
       <c r="P26" s="5" t="n">
         <v>2.376357078552246</v>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>275.6300048828125</v>
+        <v>275.8200073242188</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>51</v>
@@ -3335,22 +3335,22 @@
         <v>75</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>61.26158516193371</v>
+        <v>61.40589269742587</v>
       </c>
       <c r="K27" s="5" t="n">
         <v>-0.0092015237095138</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>0.2122511899361767</v>
+        <v>0.2162921337819961</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>5.877487681019421</v>
+        <v>5.889613192949628</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>257.8282247270857</v>
+        <v>258.0182271684919</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>299.365711757115</v>
+        <v>299.5557141985212</v>
       </c>
       <c r="P27" s="5" t="n">
         <v>11.86785343715123</v>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>395.6700134277344</v>
+        <v>396.4700012207031</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>43</v>
@@ -3429,22 +3429,22 @@
         <v>50</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>54.18055211500717</v>
+        <v>54.39749703737699</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0.0109940121352903</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.3274414442007423</v>
+        <v>0.3323232779455088</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>-0.07674177149429259</v>
+        <v>-0.0256884194643622</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>367.8193021501813</v>
+        <v>368.6192899431501</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>432.8042951311384</v>
+        <v>433.6042829241072</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>18.56714085170201</v>
@@ -3462,7 +3462,7 @@
         <v>13.95</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>-0.0429682358848012</v>
+        <v>-0.0410332554647716</v>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>79.90499877929688</v>
+        <v>79.69999694824219</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>43</v>
@@ -3549,22 +3549,22 @@
         <v>50</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>38.16229213562648</v>
+        <v>37.96440194934276</v>
       </c>
       <c r="K29" s="5" t="n">
         <v>0.0264563885114627</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.3795012627222269</v>
+        <v>0.3821291971000387</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>-1.375501851763356</v>
+        <v>-1.388584589699603</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>64.43928527832031</v>
+        <v>64.23428344726562</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>103.1035690307617</v>
+        <v>102.898567199707</v>
       </c>
       <c r="P29" s="5" t="n">
         <v>7.732856750488281</v>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>6.810200214385986</v>
+        <v>6.755599975585938</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>39</v>
@@ -3639,22 +3639,22 @@
         <v>75</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>57.80947035309124</v>
+        <v>56.81464694877543</v>
       </c>
       <c r="K30" s="5" t="n">
         <v>-0.0154083063419491</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.7378436143208397</v>
+        <v>0.7641688977343057</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.06952403297057019</v>
+        <v>0.0660395732864647</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>5.998914378029959</v>
+        <v>5.944314139229911</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>8.027128968920026</v>
+        <v>7.972528730119977</v>
       </c>
       <c r="P30" s="5" t="n">
         <v>0.4056429181780134</v>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>27.84499931335449</v>
+        <v>27.8799991607666</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>33</v>
@@ -3733,22 +3733,22 @@
         <v>50</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>27.78904304325279</v>
+        <v>27.99352303841286</v>
       </c>
       <c r="K31" s="5" t="n">
         <v>0.0112075006381963</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.2185076392289275</v>
+        <v>0.2212469510187358</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>-0.0332413465283076</v>
+        <v>-0.0310077380324909</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>24.29499980381556</v>
+        <v>24.32999965122768</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>33.16999857766287</v>
+        <v>33.20499842507499</v>
       </c>
       <c r="P31" s="5" t="n">
         <v>1.774999754769462</v>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>39.54999923706055</v>
+        <v>39.47999954223633</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>33</v>
@@ -3823,22 +3823,22 @@
         <v>50</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>18.20708401865569</v>
+        <v>18.00765942440978</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>0.0298353862022756</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.3543801665930444</v>
+        <v>0.3582093751977441</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>-1.420809556042851</v>
+        <v>-1.425276773034479</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>32.14785657610212</v>
+        <v>32.0778568812779</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>50.65321322849819</v>
+        <v>50.58321353367397</v>
       </c>
       <c r="P32" s="5" t="n">
         <v>3.701071330479213</v>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>69.76000213623047</v>
+        <v>69.52999877929688</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>32</v>
@@ -3913,22 +3913,22 @@
         <v>50</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>47.19465901020189</v>
+        <v>46.97463350219822</v>
       </c>
       <c r="K33" s="5" t="n">
         <v>0.0334417645102432</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.2940843051902342</v>
+        <v>0.2956045433749245</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>-0.7410815219501519</v>
+        <v>-0.7557597988598808</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>55.84943062918526</v>
+        <v>55.61942727225167</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>90.62585939679826</v>
+        <v>90.39585603986468</v>
       </c>
       <c r="P33" s="5" t="n">
         <v>6.955285753522601</v>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>7.860000133514404</v>
+        <v>7.875</v>
       </c>
       <c r="E34" s="5" t="n">
         <v>32</v>
@@ -4003,22 +4003,22 @@
         <v>50</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>44.80874184046107</v>
+        <v>44.95912539838206</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>0.018661516252568</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0.6455428043839868</v>
+        <v>0.6553610860174324</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>-0.0722735630839688</v>
+        <v>-0.0713163066472826</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>6.471714632851737</v>
+        <v>6.486714499337332</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>9.942428384508403</v>
+        <v>9.957428250994001</v>
       </c>
       <c r="P34" s="5" t="n">
         <v>0.6941427503313337</v>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>183.3200073242188</v>
+        <v>183.6900024414062</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>29</v>
@@ -4098,13 +4098,13 @@
       </c>
       <c r="L35" s="3" t="inlineStr"/>
       <c r="M35" s="3" t="n">
-        <v>0.4476717297375126</v>
+        <v>0.4712839537403533</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>168.6544067382813</v>
+        <v>168.9948022460938</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>210.8180084228516</v>
+        <v>211.2435028076172</v>
       </c>
       <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="3" t="n">
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>15.18000030517578</v>
+        <v>15.14500045776367</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>22</v>
@@ -4185,22 +4185,22 @@
         <v>50</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>24.26404581176152</v>
+        <v>24.05006002564733</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>0.0323432829789085</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.3557917486030802</v>
+        <v>0.3596563270903872</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>-0.2077505829493904</v>
+        <v>-0.2099841914452045</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>11.93101419721331</v>
+        <v>11.8960143498012</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>20.05347946711949</v>
+        <v>20.01847961970737</v>
       </c>
       <c r="P36" s="5" t="n">
         <v>1.624493053981236</v>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>91.66999816894533</v>
+        <v>91.34999847412109</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>22</v>
@@ -4275,22 +4275,22 @@
         <v>50</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>17.55839190490563</v>
+        <v>16.55224026953708</v>
       </c>
       <c r="K37" s="5" t="n">
         <v>0.0177384274683925</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.8043091700338481</v>
+        <v>0.8151162320841647</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>-0.765743976619226</v>
+        <v>-0.7861656095652823</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>84.94464056832452</v>
+        <v>84.62464087350028</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>100.6371416364398</v>
+        <v>100.3171419416155</v>
       </c>
       <c r="P37" s="5" t="n">
         <v>4.48357173374721</v>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>8.604999542236328</v>
+        <v>8.590000152587891</v>
       </c>
       <c r="E38" s="5" t="n">
         <v>22</v>
@@ -4365,22 +4365,22 @@
         <v>50</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>21.41950780719866</v>
+        <v>21.1195944189902</v>
       </c>
       <c r="K38" s="5" t="n">
         <v>0.0299401183926648</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.5004059941865834</v>
+        <v>0.5057160648407767</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>-0.1139422776613741</v>
+        <v>-0.1148995036674277</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>7.257857322692871</v>
+        <v>7.242857933044434</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>10.62571287155151</v>
+        <v>10.61071348190308</v>
       </c>
       <c r="P38" s="5" t="n">
         <v>0.6735711097717285</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>46.27999877929688</v>
+        <v>46.31499862670898</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>22</v>
@@ -4455,22 +4455,22 @@
         <v>50</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>24.73366460018019</v>
+        <v>24.85548245838408</v>
       </c>
       <c r="K39" s="5" t="n">
         <v>0.0251036384349932</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.3183198712545969</v>
+        <v>0.3220388577256476</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>-0.3220096730687136</v>
+        <v>-0.3197760645728964</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>39.39325550624303</v>
+        <v>39.42825535365512</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>56.61011368887766</v>
+        <v>56.64511353628976</v>
       </c>
       <c r="P39" s="5" t="n">
         <v>3.443371636526925</v>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>7.770500183105469</v>
+        <v>7.755000114440918</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>22</v>
@@ -4545,22 +4545,22 @@
         <v>50</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>27.30519493945793</v>
+        <v>27.01664839096489</v>
       </c>
       <c r="K40" s="5" t="n">
         <v>0.0100267124430337</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0.8921217787785596</v>
+        <v>0.907197787237713</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>-0.1026521681108479</v>
+        <v>-0.1036413462820309</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>6.655071599142892</v>
+        <v>6.639571530478341</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>9.443643059049334</v>
+        <v>9.428142990384783</v>
       </c>
       <c r="P40" s="5" t="n">
         <v>0.5577142919812884</v>
@@ -4677,19 +4677,19 @@
         <v>15.06915790595363</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>16.86000061035156</v>
+        <v>16.78000068664551</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>12.58809660690369</v>
+        <v>12.52836667026665</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>11.251008816</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.337087790903686</v>
+        <v>1.277357854266647</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.1188415912537745</v>
+        <v>0.1135327396108803</v>
       </c>
     </row>
     <row r="3">
@@ -4705,19 +4705,19 @@
         <v>366.8202462424581</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>358.1199951171875</v>
+        <v>357.7049865722656</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.93011192469605</v>
+        <v>18.90817470166412</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>19.3900045021</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.4598925774039522</v>
+        <v>-0.4818298004358752</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.0237180232399711</v>
+        <v>-0.024849390848965</v>
       </c>
     </row>
     <row r="4">
@@ -4733,19 +4733,19 @@
         <v>18.39862725025694</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>18.66410064697266</v>
+        <v>18.6299991607666</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>11.41334951098251</v>
+        <v>11.39249599179745</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>11.251008945</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.1623405659825127</v>
+        <v>0.1414870467974474</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.0144289784832726</v>
+        <v>0.0125754985609823</v>
       </c>
     </row>
     <row r="5">
@@ -4761,19 +4761,19 @@
         <v>413.4345674446258</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>395.6700134277344</v>
+        <v>396.4700012207031</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.76756986711578</v>
+        <v>10.78934034291962</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>11.2510057355</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.4834358683842161</v>
+        <v>-0.4616653925803824</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.0429682358848012</v>
+        <v>-0.0410332554647716</v>
       </c>
     </row>
   </sheetData>
@@ -5101,46 +5101,46 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>370.0549926757813</v>
+        <v>369.1400146484375</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>331.9768991088867</v>
+        <v>331.9585995483399</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>201.2472750473023</v>
+        <v>201.2427001571656</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>46.18162304129646</v>
+        <v>46.04180070856442</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.0079122942328466</v>
+        <v>0.0054201846249088</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.169138214750365</v>
+        <v>1.163774920526398</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>1.144376061713519</v>
+        <v>1.139073993054364</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>14.90319953143398</v>
+        <v>14.83020983124698</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>26.08163727323245</v>
+        <v>26.06703933319504</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-11.17843774179846</v>
+        <v>-11.23682950194807</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>-10.00415359792669</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>1736374</v>
+        <v>1750599</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>6121643.48</v>
+        <v>6121927.98</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>0.2836450710782</v>
+        <v>0.2859555038411281</v>
       </c>
       <c r="P2" s="6" t="n">
         <v>0.082723417254077</v>
@@ -5154,7 +5154,7 @@
         <v>46.42792184012277</v>
       </c>
       <c r="S2" s="6" t="n">
-        <v>0.1254622225318818</v>
+        <v>0.12577320257285</v>
       </c>
       <c r="T2" s="6" t="inlineStr">
         <is>
@@ -5169,46 +5169,46 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>556.010009765625</v>
+        <v>554.2330932617188</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>489.8716003417969</v>
+        <v>489.8360620117188</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>291.5068497467041</v>
+        <v>291.4979651641846</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>55.95874423080636</v>
+        <v>55.69930630970238</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.0868698356141928</v>
+        <v>0.0833963784559037</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.179832962716319</v>
+        <v>1.172866575242752</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1.677114946457219</v>
+        <v>1.668559327587661</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>17.41430834464768</v>
+        <v>17.2725600195497</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>19.97076526802996</v>
+        <v>19.94241560301037</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-2.556456923382285</v>
+        <v>-2.669855583460667</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>-3.577422784539042</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>14984558</v>
+        <v>15093592</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>33871159.16</v>
+        <v>33873339.84</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.4423987360224728</v>
+        <v>0.4455891291291103</v>
       </c>
       <c r="P3" s="6" t="n">
         <v>0.0624019610194614</v>
@@ -5222,7 +5222,7 @@
         <v>38.05143519810268</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0.0684366010139682</v>
+        <v>0.0686560143389599</v>
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
@@ -5237,46 +5237,46 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>246.4400024414062</v>
+        <v>246.75</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>253.3475997924805</v>
+        <v>253.3537997436524</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>233.5973500061035</v>
+        <v>233.5988999938965</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>65.29396912736486</v>
+        <v>65.79999320984146</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0330748240985625</v>
+        <v>0.0343743317683507</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.0103606207806173</v>
+        <v>-0.0091157506767096</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.0001217137142381</v>
+        <v>0.0011360359391006</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.7376410604606747</v>
+        <v>-0.7129119104873496</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-2.41200205716234</v>
+        <v>-2.407056227167675</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>1.674360996701665</v>
+        <v>1.694144316680325</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>1.780135958077288</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>15285042</v>
+        <v>15478151</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>48721908.84</v>
+        <v>48725771.02</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.3137200976709515</v>
+        <v>0.3176584110623274</v>
       </c>
       <c r="P4" s="6" t="n">
         <v>-0.0071974396379796</v>
@@ -5290,7 +5290,7 @@
         <v>7.47785404750279</v>
       </c>
       <c r="S4" s="6" t="n">
-        <v>0.0303435074396281</v>
+        <v>0.0303053862107509</v>
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
@@ -5305,46 +5305,46 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>182.3800048828125</v>
+        <v>182.6000061035156</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>160.7889996337891</v>
+        <v>160.7933996582031</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>144.3321996688843</v>
+        <v>144.3332996749878</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>62.32894220433992</v>
+        <v>62.42993757952711</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.1172506661698804</v>
+        <v>0.118598382497373</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.1814472413784922</v>
+        <v>0.1828723967044099</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.4777184215572496</v>
+        <v>0.4795009626686339</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5.996026221008321</v>
+        <v>6.013576175936208</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.403784156682076</v>
+        <v>4.407294147667653</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>1.592242064326245</v>
+        <v>1.606282028268555</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>1.773262942271622</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>3640048</v>
+        <v>3685315</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>10346856.96</v>
+        <v>10347762.3</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.3518022926258758</v>
+        <v>0.3561460819408269</v>
       </c>
       <c r="P5" s="6" t="n">
         <v>0.0151807899125376</v>
@@ -5358,7 +5358,7 @@
         <v>10.46220506940569</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>0.0573648688962813</v>
+        <v>0.0572957542152254</v>
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
@@ -5373,46 +5373,46 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>284.3699951171875</v>
+        <v>284.0150146484375</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>312.6227981567383</v>
+        <v>312.6156985473633</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>182.827474937439</v>
+        <v>182.8257000350952</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>28.61835280220669</v>
+        <v>28.56548425991689</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-0.2532496600921498</v>
+        <v>-0.2541818322279282</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.7638630006452947</v>
+        <v>0.7616611617539524</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1.558664717283359</v>
+        <v>1.555470723485451</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-7.900338165519486</v>
+        <v>-7.928655695790212</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>1.996212087683141</v>
+        <v>1.990548581628996</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-9.896550253202626</v>
+        <v>-9.919204277419208</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>-9.368367243321137</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>6220930</v>
+        <v>6258251</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>11186892.6</v>
+        <v>11187639.02</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.5560909738241342</v>
+        <v>0.5593897862464283</v>
       </c>
       <c r="P6" s="6" t="n">
         <v>0.0376936349020097</v>
@@ -5426,7 +5426,7 @@
         <v>29.38128662109375</v>
       </c>
       <c r="S6" s="6" t="n">
-        <v>0.1033206284966382</v>
+        <v>0.1034497653494228</v>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
@@ -5441,46 +5441,46 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>69.76000213623047</v>
+        <v>69.52999877929688</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>86.04840019226074</v>
+        <v>86.04380012512208</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>83.07184986114503</v>
+        <v>83.07069984436035</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>47.19465901020189</v>
+        <v>46.97463350219822</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.1535008004337117</v>
+        <v>-0.156291764475852</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.2123743663024191</v>
+        <v>-0.2149712202905199</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.2909848300744081</v>
+        <v>-0.2933225001461673</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-4.765926944591968</v>
+        <v>-4.784274790729128</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-4.024845422641816</v>
+        <v>-4.028514991869248</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>-0.7410815219501519</v>
+        <v>-0.7557597988598808</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>-0.7205249641778009</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>6805202</v>
+        <v>6840590</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>23140310.04</v>
+        <v>23141017.8</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.2940843051902342</v>
+        <v>0.2956045433749245</v>
       </c>
       <c r="P7" s="6" t="n">
         <v>0.0334417645102432</v>
@@ -5494,7 +5494,7 @@
         <v>6.955285753522601</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>0.0997030610741669</v>
+        <v>0.1000328761057535</v>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
@@ -5509,46 +5509,46 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>393.760009765625</v>
+        <v>393.8800048828125</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>405.5490008544922</v>
+        <v>405.551400756836</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>362.9443002319336</v>
+        <v>362.9449002075195</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>55.54740946415497</v>
+        <v>55.59085024466999</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0305964933580518</v>
+        <v>0.0309105591441307</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.0340879537474116</v>
+        <v>0.0344030835272639</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.1179694481093285</v>
+        <v>0.1183101400831472</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-3.440386622530923</v>
+        <v>-3.430814362470357</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-6.717166292036809</v>
+        <v>-6.715251840024695</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>3.276779669505886</v>
+        <v>3.284437477554338</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>3.038872772970159</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>10266892</v>
+        <v>10355427</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>27440949.84</v>
+        <v>27442720.54</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3741449206336948</v>
+        <v>0.3773469538089753</v>
       </c>
       <c r="P8" s="6" t="n">
         <v>0.030087289573326</v>
@@ -5562,7 +5562,7 @@
         <v>15.00356619698661</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>0.038103326454906</v>
+        <v>0.0380917183177411</v>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
@@ -5577,46 +5577,46 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>7.667600154876709</v>
+        <v>7.700099945068359</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>5.821951994895935</v>
+        <v>5.822601990699768</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4.045188000202179</v>
+        <v>4.045350499153137</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>49.97684546433793</v>
+        <v>50.29223738542261</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.3840433587858796</v>
+        <v>0.3899097469475105</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.7269369495631945</v>
+        <v>0.7342567220345482</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.7956909108025281</v>
+        <v>0.80330210291888</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.6082922660213272</v>
+        <v>0.6108848418770725</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.7316669286259452</v>
+        <v>0.7321854437970942</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-0.1233746626046179</v>
+        <v>-0.1213006019200216</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>-0.0949479297406228</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>3817656</v>
+        <v>3848916</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>7814989.12</v>
+        <v>7815614.32</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4885043269260495</v>
+        <v>0.492464935245167</v>
       </c>
       <c r="P9" s="6" t="n">
         <v>-0.0049382666628676</v>
@@ -5630,7 +5630,7 @@
         <v>0.7386070660182408</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>0.0963283232170727</v>
+        <v>0.0959217505340683</v>
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
@@ -5645,46 +5645,46 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>16.86000061035156</v>
+        <v>16.78000068664551</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>9.902600040435791</v>
+        <v>9.901000041961669</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.552349992990494</v>
+        <v>6.551949993371964</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>74.52830460284595</v>
+        <v>74.33460369032056</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1.128787935345699</v>
+        <v>1.118686934975066</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>3.709497477558018</v>
+        <v>3.687151129677866</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>2.27378646565805</v>
+        <v>2.258252500177541</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>2.332169437504341</v>
+        <v>2.3257876772087</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>2.205524617292939</v>
+        <v>2.204248265233811</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1266448202114016</v>
+        <v>0.1215394119748887</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>0.2137816411175577</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>821270</v>
+        <v>833895</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>3924679.4</v>
+        <v>3924931.9</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.2092578568328409</v>
+        <v>0.2124610111069697</v>
       </c>
       <c r="P10" s="6" t="n">
         <v>0.0098826338563442</v>
@@ -5698,7 +5698,7 @@
         <v>1.499500070299421</v>
       </c>
       <c r="S10" s="6" t="n">
-        <v>0.0889383164896667</v>
+        <v>0.08936233664714981</v>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
@@ -5713,46 +5713,46 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>275.6300048828125</v>
+        <v>275.8200073242188</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>300.9998013305664</v>
+        <v>301.0036013793945</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>276.0428508758545</v>
+        <v>276.0438008880615</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>61.26158516193371</v>
+        <v>61.40589269742587</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.06537587243526249</v>
+        <v>-0.0647315998129477</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.08352450579280959</v>
+        <v>-0.08289274372662089</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.0441716998453947</v>
+        <v>0.0448914878536061</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-6.655628100388412</v>
+        <v>-6.640471210475653</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-12.53311578140783</v>
+        <v>-12.53008440342528</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>5.877487681019421</v>
+        <v>5.889613192949628</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>5.61249043240821</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>329477</v>
+        <v>335777</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>1552297.54</v>
+        <v>1552423.54</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.2122511899361767</v>
+        <v>0.2162921337819961</v>
       </c>
       <c r="P11" s="6" t="n">
         <v>-0.0092015237095138</v>
@@ -5766,7 +5766,7 @@
         <v>11.86785343715123</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>0.0430571898084789</v>
+        <v>0.0430275292654926</v>
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
@@ -5781,46 +5781,46 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>104.4499969482422</v>
+        <v>104.3850021362305</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>112.2647996520996</v>
+        <v>112.2634997558594</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>101.2278999137878</v>
+        <v>101.2275749397278</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>64.68646542671178</v>
+        <v>64.63905871110767</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.1795594957483035</v>
+        <v>0.1788255058016998</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.1357054342817456</v>
+        <v>-0.1362432482067135</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.0005741573702205</v>
+        <v>-0.0011960577690646</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.6345790137693257</v>
+        <v>0.629394242440739</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.7738091291125627</v>
+        <v>-0.7748460833782801</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>1.408388142881888</v>
+        <v>1.404240325819019</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>1.911196160245703</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>592829</v>
+        <v>603593</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>1509824.58</v>
+        <v>1510039.86</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.3926476014849354</v>
+        <v>0.399719912029342</v>
       </c>
       <c r="P12" s="6" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
         <v>5.971429007393973</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>0.0571702171552286</v>
+        <v>0.0572058139118567</v>
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
@@ -5849,46 +5849,46 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>240</v>
+        <v>239.2899932861328</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>227.4411999511719</v>
+        <v>227.4269998168945</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>161.8411502075195</v>
+        <v>161.8376001739502</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>41.66210579173344</v>
+        <v>41.44548941404696</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.043100345535741</v>
+        <v>-0.045931200448936</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.5045135003261336</v>
+        <v>0.5000626057997362</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.5377714406165539</v>
+        <v>0.5332221570864248</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.48101854279318</v>
+        <v>5.424379830575845</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>10.06559272095854</v>
+        <v>10.05426497851508</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>-4.584574178165363</v>
+        <v>-4.62988514793923</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>-4.078359216969876</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>2407765</v>
+        <v>2431271</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>8664557.300000001</v>
+        <v>8665027.42</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2778866728713306</v>
+        <v>0.2805843400320134</v>
       </c>
       <c r="P13" s="6" t="n">
         <v>0.06596166699561611</v>
@@ -5902,7 +5902,7 @@
         <v>26.78535788399833</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>0.111605657849993</v>
+        <v>0.1119368073698323</v>
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
@@ -5917,46 +5917,46 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>358.1199951171875</v>
+        <v>357.7049865722656</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>372.2636004638672</v>
+        <v>372.2553002929688</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>319.9701998138428</v>
+        <v>319.9681247711181</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>59.81018252640515</v>
+        <v>59.5353799756744</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.0043371819127008</v>
+        <v>-0.0054910090739906</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.07572614573836969</v>
+        <v>0.0744795369241058</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.07912978643028</v>
+        <v>0.07787923329570361</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-2.040295208927262</v>
+        <v>-2.07340130367885</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-2.649101212140661</v>
+        <v>-2.655722431090978</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.6088060032133988</v>
+        <v>0.5823211274121287</v>
       </c>
       <c r="L14" s="6" t="n">
         <v>0.5974640052565006</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>8769143</v>
+        <v>8944365</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>31766852.86</v>
+        <v>31770357.3</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.2760469549390547</v>
+        <v>0.2815317723858271</v>
       </c>
       <c r="P14" s="6" t="n">
         <v>-0.0040282924977889</v>
@@ -5970,7 +5970,7 @@
         <v>9.963572910853795</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>0.0278218838565364</v>
+        <v>0.0278541627454804</v>
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
@@ -5985,46 +5985,46 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>107.2900009155273</v>
+        <v>107.1252975463867</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>117.4269998168945</v>
+        <v>117.4237057495117</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>63.21444997787476</v>
+        <v>63.21362646102905</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>31.26405772394173</v>
+        <v>31.09388122372084</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.1387171776642048</v>
+        <v>-0.1400393529033805</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.6813978781770686</v>
+        <v>0.6788167252920043</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1.435088460541131</v>
+        <v>1.431350299760218</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-2.016444732396806</v>
+        <v>-2.029583462698625</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>1.4066891202484</v>
+        <v>1.404061374188036</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-3.423133852645206</v>
+        <v>-3.433644836886661</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>-3.642499733942029</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>58807816</v>
+        <v>59285933</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>130008916.32</v>
+        <v>130018478.66</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.452336790926341</v>
+        <v>0.4559808237337823</v>
       </c>
       <c r="P15" s="6" t="n">
         <v>0.0469355722360184</v>
@@ -6038,7 +6038,7 @@
         <v>9.479286193847656</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>0.0883520003071953</v>
+        <v>0.0884878400430392</v>
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
@@ -6053,46 +6053,46 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>39.54999923706055</v>
+        <v>39.47999954223633</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>54.90640014648437</v>
+        <v>54.90500015258789</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>48.6904000377655</v>
+        <v>48.69005003929138</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>18.20708401865569</v>
+        <v>18.00765942440978</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-0.3163353451987896</v>
+        <v>-0.3175453658845383</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.1059843706213252</v>
+        <v>0.1040268846562861</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.2237487999052427</v>
+        <v>-0.2251226898714061</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-4.155479609682892</v>
+        <v>-4.161063630922428</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-2.734670053640041</v>
+        <v>-2.735786857887948</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-1.420809556042851</v>
+        <v>-1.425276773034479</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>-1.449196603544823</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>10218187</v>
+        <v>10329395</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>28833969.74</v>
+        <v>28836193.9</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.3543801665930444</v>
+        <v>0.3582093751977441</v>
       </c>
       <c r="P16" s="6" t="n">
         <v>0.0298353862022756</v>
@@ -6106,7 +6106,7 @@
         <v>3.701071330479213</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>0.0935795550410808</v>
+        <v>0.093745475516527</v>
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
@@ -6121,46 +6121,46 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>7.860000133514404</v>
+        <v>7.875</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>8.697999954223633</v>
+        <v>8.698299951553345</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>8.190849969387054</v>
+        <v>8.190924968719482</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>44.80874184046107</v>
+        <v>44.95912539838206</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-0.0242085865019866</v>
+        <v>-0.0223464057549596</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.1602563651904378</v>
+        <v>-0.158653815293452</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.0449574033173498</v>
+        <v>-0.0431348191958543</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.0354759847674657</v>
+        <v>0.0366725553133235</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.1077495478514346</v>
+        <v>0.1079888619606061</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.0722735630839688</v>
+        <v>-0.0713163066472826</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>-0.0068890358413925</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>678656</v>
+        <v>689115</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1051295.12</v>
+        <v>1051504.3</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.6455428043839868</v>
+        <v>0.6553610860174324</v>
       </c>
       <c r="P17" s="6" t="n">
         <v>0.018661516252568</v>
@@ -6174,7 +6174,7 @@
         <v>0.6941427503313337</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>0.0883133255140245</v>
+        <v>0.0881451111531852</v>
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
@@ -6189,46 +6189,46 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1157.300048828125</v>
+        <v>1156.03857421875</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1097.821602783203</v>
+        <v>1097.796373291016</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1000.579303283691</v>
+        <v>1000.572995910644</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>58.02083686703796</v>
+        <v>57.78798045611461</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.0214475276505956</v>
+        <v>0.0203341343501766</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.2545257981876694</v>
+        <v>0.2531583460365854</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.07058283887893151</v>
+        <v>0.06941588734389451</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>27.84544479179772</v>
+        <v>27.74481433862797</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>34.6559818011979</v>
+        <v>34.63585571056394</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-6.810537009400178</v>
+        <v>-6.89104137193597</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>-3.468572913063639</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>1323421</v>
+        <v>1331850</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>3186368.42</v>
+        <v>3186537</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.4153383493550943</v>
+        <v>0.4179615676830365</v>
       </c>
       <c r="P18" s="6" t="n">
         <v>-0.013419399271567</v>
@@ -6242,7 +6242,7 @@
         <v>41.49965122767857</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>0.0358590248654191</v>
+        <v>0.0358981543982855</v>
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
@@ -6257,46 +6257,46 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>15.18000030517578</v>
+        <v>15.14500045776367</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>27.45700004577637</v>
+        <v>27.45630004882813</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>19.02152503490448</v>
+        <v>19.02135003566742</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>24.26404581176152</v>
+        <v>24.05006002564733</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.4297520726294261</v>
+        <v>-0.4310668677574761</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.3586818649663248</v>
+        <v>-0.3601605234918549</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.2093750155220423</v>
+        <v>-0.211197924168987</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-3.400976181440161</v>
+        <v>-3.403768192059928</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-3.19322559849077</v>
+        <v>-3.193784000614724</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.2077505829493904</v>
+        <v>-0.2099841914452045</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>-0.2400474448421516</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>5076500</v>
+        <v>5132040</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>14268178</v>
+        <v>14269288.8</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.3557917486030802</v>
+        <v>0.3596563270903872</v>
       </c>
       <c r="P19" s="6" t="n">
         <v>0.0323432829789085</v>
@@ -6310,7 +6310,7 @@
         <v>1.624493053981236</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.1070153505482702</v>
+        <v>0.1072626612664434</v>
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
@@ -6325,46 +6325,46 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>223.8999938964844</v>
+        <v>223.610107421875</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>233.8638000488281</v>
+        <v>233.8580023193359</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>128.1987501525879</v>
+        <v>128.1973007202149</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>34.00255700129621</v>
+        <v>33.89135825856491</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.1994995204692528</v>
+        <v>-0.2005359397111468</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.6730179394238738</v>
+        <v>0.6708518595416115</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>1.701170171856048</v>
+        <v>1.697672928802074</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-4.912841093588696</v>
+        <v>-4.935965940566064</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>4.141830083728471</v>
+        <v>4.137205114332998</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-9.054671177317168</v>
+        <v>-9.073171054899062</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>-9.60956168128553</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>12625881</v>
+        <v>12726392</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>45226511.62</v>
+        <v>45228521.84</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.2791699060516664</v>
+        <v>0.2813797905007987</v>
       </c>
       <c r="P20" s="6" t="n">
         <v>0.0645198535414377</v>
@@ -6378,7 +6378,7 @@
         <v>21.60285949707031</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>0.09648441306817521</v>
+        <v>0.09660949474127831</v>
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
@@ -6393,46 +6393,46 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>986.780029296875</v>
+        <v>985.5789794921876</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>916.8106018066406</v>
+        <v>916.7865808105468</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>472.4618504333496</v>
+        <v>472.4558451843262</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>45.10226858546104</v>
+        <v>45.00270952258949</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.0052669023568061</v>
+        <v>0.0040433514327011</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>1.119099818615513</v>
+        <v>1.116520576689554</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1.853037393320385</v>
+        <v>1.84956484634712</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>9.737344162130968</v>
+        <v>9.641533921301289</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>34.47428712453143</v>
+        <v>34.45512507636549</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-24.73694296240046</v>
+        <v>-24.8135911550642</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>-28.83193491040208</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>21437521</v>
+        <v>21571799</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>53940054.42</v>
+        <v>53942739.98</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.3974323205734726</v>
+        <v>0.3999018034307867</v>
       </c>
       <c r="P21" s="6" t="n">
         <v>0.0543756800501934</v>
@@ -6446,7 +6446,7 @@
         <v>89.7650146484375</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>0.0909676037043424</v>
+        <v>0.09107845897310859</v>
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
@@ -6461,46 +6461,46 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>195.3300018310547</v>
+        <v>194.8000030517578</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>224.0132000732422</v>
+        <v>224.0026000976562</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>136.7451254653931</v>
+        <v>136.7424754714966</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>30.13324092386908</v>
+        <v>30.05404926893323</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-0.1593647731194195</v>
+        <v>-0.1616457112236746</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.2061874699657964</v>
+        <v>0.2029146604603831</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.819901225181366</v>
+        <v>0.8149631950848872</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-6.554142110943474</v>
+        <v>-6.596421215844657</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.4614429627010381</v>
+        <v>0.4529871417208013</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-7.015585073644512</v>
+        <v>-7.049408357565459</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>-6.66147091221397</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>12169583</v>
+        <v>12345361</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>17940649.66</v>
+        <v>17944165.22</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6783245440176552</v>
+        <v>0.6879874794197867</v>
       </c>
       <c r="P22" s="6" t="n">
         <v>0.0310198990532244</v>
@@ -6514,7 +6514,7 @@
         <v>25.56014360700335</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>0.1308562093247247</v>
+        <v>0.1312122341199968</v>
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
@@ -6529,46 +6529,46 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>211.3399963378907</v>
+        <v>211.4349975585937</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>209.3200003051758</v>
+        <v>209.3219003295899</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>191.9678004455566</v>
+        <v>191.9682754516602</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>60.3898539976604</v>
+        <v>60.45893179215103</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.0299721907661683</v>
+        <v>0.0304351822354054</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.0754669087863559</v>
+        <v>0.0759503509692409</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.1427489647884512</v>
+        <v>0.1432626514946748</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.6233524728854434</v>
+        <v>-0.6157740279290351</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-2.266009025849629</v>
+        <v>-2.264493336858348</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1.642656552964186</v>
+        <v>1.648719308929313</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>1.206196025562167</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>71857741</v>
+        <v>72883894</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>157823918.82</v>
+        <v>157844441.88</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.4553032362727894</v>
+        <v>0.4617450771906775</v>
       </c>
       <c r="P23" s="6" t="n">
         <v>0.0229450115312453</v>
@@ -6582,7 +6582,7 @@
         <v>6.875713893345424</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>0.0325338980433808</v>
+        <v>0.0325192800280852</v>
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
@@ -6597,46 +6597,46 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>91.66999816894533</v>
+        <v>91.34999847412109</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>106.6399993896484</v>
+        <v>106.633599395752</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>104.4500496673584</v>
+        <v>104.4484496688843</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>17.55839190490563</v>
+        <v>16.55224026953708</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>-0.0920166501562114</v>
+        <v>-0.09518621926997969</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.2101499216156278</v>
+        <v>-0.2129071135987025</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.1650423772245306</v>
+        <v>-0.1679570296715274</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-4.107740741557478</v>
+        <v>-4.133267782740049</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-3.341996764938252</v>
+        <v>-3.347102173174767</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.765743976619226</v>
+        <v>-0.7861656095652823</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>-0.7934742332941171</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>2618908</v>
+        <v>2654680</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3256096.16</v>
+        <v>3256811.6</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.8043091700338481</v>
+        <v>0.8151162320841647</v>
       </c>
       <c r="P24" s="6" t="n">
         <v>0.0177384274683925</v>
@@ -6650,7 +6650,7 @@
         <v>4.48357173374721</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>0.0489099140755311</v>
+        <v>0.0490812458526463</v>
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
@@ -6665,46 +6665,46 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>25.8799991607666</v>
+        <v>25.79000091552734</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>35.88100006103516</v>
+        <v>35.87920009613037</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>25.37014997959137</v>
+        <v>25.36969998836517</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>41.87614750781767</v>
+        <v>41.64634391000573</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.1691813971846308</v>
+        <v>-0.1720705864732792</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.2372531998822649</v>
+        <v>-0.2399056680352207</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.0172955431396293</v>
+        <v>0.0137578763412824</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-2.435310853777661</v>
+        <v>-2.442490200976238</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-2.39385379899687</v>
+        <v>-2.395289668436586</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.0414570547807908</v>
+        <v>-0.047200532539652</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>-0.0149246408257801</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>2919047</v>
+        <v>2991185</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>13306934.94</v>
+        <v>13308377.7</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.2193628369840065</v>
+        <v>0.2247595512712267</v>
       </c>
       <c r="P25" s="6" t="n">
         <v>0.0084746235925221</v>
@@ -6718,7 +6718,7 @@
         <v>2.376357078552246</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>0.09182214666199599</v>
+        <v>0.09214257441617681</v>
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
@@ -6733,46 +6733,46 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>13.6899995803833</v>
+        <v>13.69999980926514</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>11.47200002670288</v>
+        <v>11.47220003128052</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>9.128175008296967</v>
+        <v>9.128225009441376</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>74.99999453168354</v>
+        <v>75.05720409307425</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.2061673233715402</v>
+        <v>0.2070484007764506</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.5574516086229084</v>
+        <v>0.5585892910944936</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.595571060852647</v>
+        <v>0.5967365887047169</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.6762261122856099</v>
+        <v>0.6770238513417102</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.6460266087243828</v>
+        <v>0.6461861565356029</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.0301995035612271</v>
+        <v>0.0308376948061073</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>0.042571941463545</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>159686</v>
+        <v>160483</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>663335.72</v>
+        <v>663351.66</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.2407317971659961</v>
+        <v>0.2419274868476246</v>
       </c>
       <c r="P26" s="6" t="n">
         <v>-0.0110537672736636</v>
@@ -6786,7 +6786,7 @@
         <v>0.6038284982953753</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>0.04410726930632</v>
+        <v>0.0440750734818998</v>
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
@@ -6801,46 +6801,46 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>79.90499877929688</v>
+        <v>79.69999694824219</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>107.0362998962402</v>
+        <v>107.0321998596191</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>77.06907510757446</v>
+        <v>77.06805009841919</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>38.16229213562648</v>
+        <v>37.96440194934276</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-0.2196015308563893</v>
+        <v>-0.2216036973987929</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.1064109308875325</v>
+        <v>0.1035723567032396</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.0909556610670615</v>
+        <v>-0.09328787753459281</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-7.620952368430224</v>
+        <v>-7.637305790850533</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-6.245450516666868</v>
+        <v>-6.24872120115093</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-1.375501851763356</v>
+        <v>-1.388584589699603</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>-1.60128212643402</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>10694414</v>
+        <v>10769040</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>28180180.28</v>
+        <v>28181672.8</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.3795012627222269</v>
+        <v>0.3821291971000387</v>
       </c>
       <c r="P27" s="6" t="n">
         <v>0.0264563885114627</v>
@@ -6854,7 +6854,7 @@
         <v>7.732856750488281</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>0.09677563192068819</v>
+        <v>0.0970245551641621</v>
       </c>
       <c r="T27" s="6" t="inlineStr">
         <is>
@@ -6869,46 +6869,46 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>18.66410064697266</v>
+        <v>18.6299991607666</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>16.94888195037842</v>
+        <v>16.9481999206543</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>21.97349552631378</v>
+        <v>21.97332501888275</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>62.78444622690394</v>
+        <v>62.54678624610271</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.1256996823194647</v>
+        <v>0.1236428978584891</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.0421050142928678</v>
+        <v>0.04020096702896</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.2983420910033306</v>
+        <v>-0.2996241017445714</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.4127901981451813</v>
+        <v>0.4100698516672061</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.3732005305775747</v>
+        <v>0.3726564612819796</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.0395896675676066</v>
+        <v>0.0374133903852264</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>0.0328078631428616</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>58836149</v>
+        <v>59802857</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>76370800.98</v>
+        <v>76390135.14</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.7704010989148591</v>
+        <v>0.7828609923310054</v>
       </c>
       <c r="P28" s="6" t="n">
         <v>0.0044125718372439</v>
@@ -6922,7 +6922,7 @@
         <v>0.9414285932268416</v>
       </c>
       <c r="S28" s="6" t="n">
-        <v>0.0504406084725835</v>
+        <v>0.0505329380373467</v>
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
@@ -6937,46 +6937,46 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>6.420000076293945</v>
+        <v>6.409999847412109</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>5.934599990844727</v>
+        <v>5.93439998626709</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>4.497050006389617</v>
+        <v>4.497000005245209</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>62.65356173241101</v>
+        <v>62.49999561730699</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.2995951420911973</v>
+        <v>0.2975708042843141</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.0530973631820257</v>
+        <v>-0.0545723231484529</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.3986927805817788</v>
+        <v>0.3965140815514099</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.3315046152813989</v>
+        <v>0.3307068762252978</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.3110511426225011</v>
+        <v>0.3108915948112808</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.0204534726588978</v>
+        <v>0.0198152814140169</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>0.0646032293833483</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>314461</v>
+        <v>323070</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>1212421.22</v>
+        <v>1212593.4</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2593661301968964</v>
+        <v>0.266428961265994</v>
       </c>
       <c r="P29" s="6" t="n">
         <v>0.0046656626141934</v>
@@ -6990,7 +6990,7 @@
         <v>0.6430713449205671</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>0.1001668749654892</v>
+        <v>0.1003231451214764</v>
       </c>
       <c r="T29" s="6" t="inlineStr">
         <is>
@@ -7005,46 +7005,46 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>395.6700134277344</v>
+        <v>396.4700012207031</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>409.9163995361328</v>
+        <v>409.9323992919922</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>417.7488500976563</v>
+        <v>417.7528500366211</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>54.18055211500717</v>
+        <v>54.39749703737699</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-0.0264743730579705</v>
+        <v>-0.0245060444223255</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.0864085671771308</v>
+        <v>0.0886051288634439</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.1186964964397631</v>
+        <v>-0.1169146276581463</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-1.33601720703922</v>
+        <v>-1.272200517001806</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-1.259275435544927</v>
+        <v>-1.246512097537444</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.07674177149429259</v>
+        <v>-0.0256884194643622</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>0.3816312784934397</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>15810675</v>
+        <v>16047974</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>48285503.5</v>
+        <v>48290249.48</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.3274414442007423</v>
+        <v>0.3323232779455088</v>
       </c>
       <c r="P30" s="6" t="n">
         <v>0.0109940121352903</v>
@@ -7058,7 +7058,7 @@
         <v>18.56714085170201</v>
       </c>
       <c r="S30" s="6" t="n">
-        <v>0.0469258225834521</v>
+        <v>0.0468311367683181</v>
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
@@ -7073,46 +7073,46 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>423.1400146484375</v>
+        <v>423.3699951171875</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>425.0482006835937</v>
+        <v>425.0528002929688</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>349.7370001220703</v>
+        <v>349.738150024414</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>45.85341478993548</v>
+        <v>45.93124389648438</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-0.001863463404317</v>
+        <v>-0.0013209670659514</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.1138487412995705</v>
+        <v>0.1144541282797015</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.2754017200482843</v>
+        <v>0.2760949125502152</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>1.387509095785333</v>
+        <v>1.405855116084467</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>5.418882357531459</v>
+        <v>5.422551561591286</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-4.031373261746126</v>
+        <v>-4.016696445506819</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>-3.711786865119478</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9618491</v>
+        <v>9720386</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>13667773.82</v>
+        <v>13669811.72</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.7037350139585496</v>
+        <v>0.7110841172580539</v>
       </c>
       <c r="P31" s="6" t="n">
         <v>0.0220361706931489</v>
@@ -7126,7 +7126,7 @@
         <v>19.97285679408482</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>0.0472015316506502</v>
+        <v>0.0471758911222709</v>
       </c>
       <c r="T31" s="6" t="inlineStr">
         <is>
@@ -7174,13 +7174,13 @@
         <v>-0.1480541656201379</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>2062271</v>
+        <v>2080552</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>6150743.42</v>
+        <v>6151109.04</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3352880878259753</v>
+        <v>0.3382401427889498</v>
       </c>
       <c r="P32" s="6" t="n">
         <v>0.031582057136426</v>
@@ -7209,46 +7209,46 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>884.3150024414062</v>
+        <v>884.8400268554688</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>877.309296875</v>
+        <v>877.3197973632813</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>479.598424911499</v>
+        <v>479.6010500335693</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>38.39453407767014</v>
+        <v>38.44315833178496</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-0.0501857886757309</v>
+        <v>-0.0496218768927215</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.6577590701749829</v>
+        <v>0.6587432941020592</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1.750762013875302</v>
+        <v>1.752395161804008</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-3.525743892772084</v>
+        <v>-3.48386160333132</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>11.32663591554761</v>
+        <v>11.33501237343576</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-14.8523798083197</v>
+        <v>-14.81887397676708</v>
       </c>
       <c r="L33" s="6" t="n">
         <v>-17.58862389405815</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>2206861</v>
+        <v>2270544</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>4343381.22</v>
+        <v>4344654.88</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.5080974678985236</v>
+        <v>0.5226062973268892</v>
       </c>
       <c r="P33" s="6" t="n">
         <v>0.0451049293978258</v>
@@ -7262,7 +7262,7 @@
         <v>84.29928588867188</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>0.0953272144608419</v>
+        <v>0.0952706515642758</v>
       </c>
       <c r="T33" s="6" t="inlineStr">
         <is>
@@ -7277,46 +7277,46 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>27.84499931335449</v>
+        <v>27.8799991607666</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>33.4572998046875</v>
+        <v>33.45799980163574</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>34.37767489433288</v>
+        <v>34.37784989356994</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>27.78904304325279</v>
+        <v>27.99352303841286</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>-0.0858502905356681</v>
+        <v>-0.0847012475788694</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.0237131813354161</v>
+        <v>0.0249999403953569</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.0755312570547992</v>
+        <v>-0.0743692435608779</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-1.881052734979807</v>
+        <v>-1.878260724360036</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-1.8478113884515</v>
+        <v>-1.847252986327545</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.0332413465283076</v>
+        <v>-0.0310077380324909</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>-0.1129581202809464</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>12134756</v>
+        <v>12287559</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>55534699.12</v>
+        <v>55537755.18</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2185076392289275</v>
+        <v>0.2212469510187358</v>
       </c>
       <c r="P34" s="6" t="n">
         <v>0.0112075006381963</v>
@@ -7330,7 +7330,7 @@
         <v>1.774999754769462</v>
       </c>
       <c r="S34" s="6" t="n">
-        <v>0.0637457280854796</v>
+        <v>0.0636657033070246</v>
       </c>
       <c r="T34" s="6" t="inlineStr">
         <is>
@@ -7345,46 +7345,46 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>267.8599853515625</v>
+        <v>268.0700073242188</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>226.0963995361328</v>
+        <v>226.100599975586</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>160.4386501312256</v>
+        <v>160.4397002410889</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>75.74305421730782</v>
+        <v>75.79839303697977</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.1651152347231907</v>
+        <v>0.1660287709486454</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>1.422537633090914</v>
+        <v>1.424437081162144</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1.116299170399034</v>
+        <v>1.11795850494247</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>12.06463829495118</v>
+        <v>12.08139218450782</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>11.57204695902477</v>
+        <v>11.5753977369361</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.4925913359264129</v>
+        <v>0.5059944475717248</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>0.3955764881293149</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>2309270</v>
+        <v>2326235</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>6066481.4</v>
+        <v>6066820.7</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.38066052588573</v>
+        <v>0.3834355941984572</v>
       </c>
       <c r="P35" s="6" t="n">
         <v>-0.0192129762097973</v>
@@ -7398,7 +7398,7 @@
         <v>13.84728785923549</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v>0.0516959927443478</v>
+        <v>0.0516554910318177</v>
       </c>
       <c r="T35" s="6" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>183.3200073242188</v>
+        <v>183.6900024414062</v>
       </c>
       <c r="C36" s="6" t="inlineStr"/>
       <c r="D36" s="6" t="inlineStr"/>
@@ -7422,19 +7422,19 @@
       <c r="G36" s="6" t="inlineStr"/>
       <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" s="6" t="n">
-        <v>0.328250630832855</v>
+        <v>0.3577659108364059</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.1194210989046576</v>
+        <v>-0.1135180429039474</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.4476717297375126</v>
+        <v>0.4712839537403533</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>-0.9253561253561428</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>50067470</v>
+        <v>50585241</v>
       </c>
       <c r="N36" s="6" t="inlineStr"/>
       <c r="O36" s="6" t="inlineStr"/>
@@ -7461,46 +7461,46 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>8.604999542236328</v>
+        <v>8.590000152587891</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>10.93910001754761</v>
+        <v>10.93880002975464</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>18.45047497272492</v>
+        <v>18.45039997577668</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>21.41950780719866</v>
+        <v>21.1195944189902</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-0.1299292979250497</v>
+        <v>-0.1314459196770968</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.1604878495379191</v>
+        <v>-0.1619512046255716</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.5636409816500868</v>
+        <v>-0.5644015998129018</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.645695108725544</v>
+        <v>-0.6468916412331112</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.5317528310641699</v>
+        <v>-0.5319921375656834</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.1139422776613741</v>
+        <v>-0.1148995036674277</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>-0.1257283657885731</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>16546346</v>
+        <v>16723722</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>33065842.92</v>
+        <v>33069390.44</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.5004059941865834</v>
+        <v>0.5057160648407767</v>
       </c>
       <c r="P37" s="6" t="n">
         <v>0.0299401183926648</v>
@@ -7514,7 +7514,7 @@
         <v>0.6735711097717285</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>0.0782767165141157</v>
+        <v>0.07841339904619241</v>
       </c>
       <c r="T37" s="6" t="inlineStr">
         <is>
@@ -7529,46 +7529,46 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>46.27999877929688</v>
+        <v>46.31499862670898</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>60.63019981384277</v>
+        <v>60.63089981079101</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>81.45959980010986</v>
+        <v>81.45977479934692</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>24.73366460018019</v>
+        <v>24.85548245838408</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-0.1949904778550161</v>
+        <v>-0.1943816789962535</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.2099693183218249</v>
+        <v>-0.2093718474048207</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.5484878167873475</v>
+        <v>-0.5481463548613758</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-3.796674944843346</v>
+        <v>-3.793882934223575</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-3.474665271774632</v>
+        <v>-3.474106869650678</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.3220096730687136</v>
+        <v>-0.3197760645728964</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>-0.3462640816307631</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>3940331</v>
+        <v>3986665</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>12378526.62</v>
+        <v>12379453.3</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.3183198712545969</v>
+        <v>0.3220388577256476</v>
       </c>
       <c r="P38" s="6" t="n">
         <v>0.0251036384349932</v>
@@ -7582,7 +7582,7 @@
         <v>3.443371636526925</v>
       </c>
       <c r="S38" s="6" t="n">
-        <v>0.074403019173529</v>
+        <v>0.07434679344978321</v>
       </c>
       <c r="T38" s="6" t="inlineStr">
         <is>
@@ -7597,46 +7597,46 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>7.770500183105469</v>
+        <v>7.755000114440918</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>9.766409997940064</v>
+        <v>9.766099996566773</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>12.02990251541138</v>
+        <v>12.02982501506805</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>27.30519493945793</v>
+        <v>27.01664839096489</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>-0.1507649719056915</v>
+        <v>-0.1524589685516761</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.1169886346949526</v>
+        <v>-0.1187500060959294</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.4957494964277749</v>
+        <v>-0.4967553412569786</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.5902636701962471</v>
+        <v>-0.5915001429102258</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.4876115020853991</v>
+        <v>-0.4878587966281948</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.1026521681108479</v>
+        <v>-0.1036413462820309</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>-0.1257187896488844</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>33279533</v>
+        <v>33852318</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>37303800.66</v>
+        <v>37315256.36</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.8921217787785596</v>
+        <v>0.907197787237713</v>
       </c>
       <c r="P39" s="6" t="n">
         <v>0.0100267124430337</v>
@@ -7650,7 +7650,7 @@
         <v>0.5577142919812884</v>
       </c>
       <c r="S39" s="6" t="n">
-        <v>0.0717732808492642</v>
+        <v>0.0719167354933683</v>
       </c>
       <c r="T39" s="6" t="inlineStr">
         <is>
@@ -7665,46 +7665,46 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>6.810200214385986</v>
+        <v>6.755599975585938</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>7.679404029846191</v>
+        <v>7.67831202507019</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>10.25867601394653</v>
+        <v>10.25840301275253</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>57.80947035309124</v>
+        <v>56.81464694877543</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>-0.0130144753246794</v>
+        <v>-0.0209275533022734</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.0229267690984062</v>
+        <v>-0.0307603760487082</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.4113914957636088</v>
+        <v>-0.4161106176512674</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.2358958523394063</v>
+        <v>-0.2402514269445381</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.3054198853099765</v>
+        <v>-0.3062910002310029</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.06952403297057019</v>
+        <v>0.0660395732864647</v>
       </c>
       <c r="L40" s="6" t="n">
         <v>0.0561779742976243</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>21151990</v>
+        <v>21918378</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>28667307.8</v>
+        <v>28682635.56</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.7378436143208397</v>
+        <v>0.7641688977343057</v>
       </c>
       <c r="P40" s="6" t="n">
         <v>-0.0154083063419491</v>
@@ -7718,7 +7718,7 @@
         <v>0.4056429181780134</v>
       </c>
       <c r="S40" s="6" t="n">
-        <v>0.059564022408787</v>
+        <v>0.0600454318852457</v>
       </c>
       <c r="T40" s="6" t="inlineStr">
         <is>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -466,7 +466,7 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -538,13 +538,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>369.7300109863281</v>
+        <v>368.364990234375</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.082723417254077</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.2866642642115858</v>
+        <v>0.3098805794520953</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>75</v>
@@ -558,19 +558,19 @@
         <v>12</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.0324561156612297</v>
+        <v>0.0325763856993166</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>276.8741673060826</v>
+        <v>275.5091465541295</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>509.0137765066965</v>
+        <v>507.6487557547433</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -579,13 +579,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>986.25</v>
+        <v>238.5599975585937</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.0543756800501934</v>
+        <v>0.06596166699561611</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.4005134441903988</v>
+        <v>0.3081548827254273</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>75</v>
@@ -599,19 +599,19 @@
         <v>12</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.0121673003802281</v>
+        <v>0.0503018113799763</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>806.719970703125</v>
+        <v>184.989281790597</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1255.545043945312</v>
+        <v>318.9160712105887</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>239.5500030517578</v>
+        <v>981.2349853515624</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.06596166699561611</v>
+        <v>0.0543756800501934</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.2808836292303273</v>
+        <v>0.4266627673210695</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>75</v>
@@ -640,13 +640,13 @@
         <v>12</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.0500939254732852</v>
+        <v>0.0122294864931875</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>185.9792872837612</v>
+        <v>801.7049560546874</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>319.9060767037528</v>
+        <v>1250.530029296875</v>
       </c>
     </row>
   </sheetData>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>182.7550048828125</v>
+        <v>181.9600067138672</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>89</v>
@@ -896,28 +896,28 @@
         <v>75</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>62.50076790432738</v>
+        <v>62.13461920486363</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.0151807899125376</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.358127197006905</v>
+        <v>0.3998422937932429</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1.616173688257884</v>
+        <v>1.565438762376488</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>161.8305947440011</v>
+        <v>161.0355965750558</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>214.1416200910296</v>
+        <v>213.3466219220843</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>10.46220506940569</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>9.75</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0.053341</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>211.35009765625</v>
+        <v>212.1750030517578</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>89</v>
@@ -990,31 +990,31 @@
         <v>75</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>60.39721038718096</v>
+        <v>60.98887129446162</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.0229450115312453</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.4632066539208285</v>
+        <v>0.5219375965261863</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1.643301195503378</v>
+        <v>1.69594473071526</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>201.0365268162318</v>
+        <v>201.7521476745605</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>225.1015254429408</v>
+        <v>226.0721435546875</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>6.875713893345424</v>
+        <v>6.948570251464844</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>13.95</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.066012</v>
+        <v>0.065756</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>1.12</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>554.469970703125</v>
+        <v>553.489990234375</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>82</v>
@@ -1084,28 +1084,28 @@
         <v>50</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>55.73406793368378</v>
+        <v>55.58990122403013</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0.0624019610194614</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.4463275772090378</v>
+        <v>0.4730084692137635</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>-2.654738618538957</v>
+        <v>-2.717278682641592</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>497.392817905971</v>
+        <v>496.412837437221</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>630.5728410993304</v>
+        <v>629.5928606305804</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>38.05143519810268</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>10.84</v>
+        <v>10.82</v>
       </c>
       <c r="R4" s="2" t="n">
         <v>0.019555</v>
@@ -1144,12 +1144,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>BFLY</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>986.25</v>
+        <v>7.619999885559082</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>82</v>
@@ -1178,31 +1178,31 @@
         <v>50</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>45.05837714358105</v>
+        <v>49.52198674958101</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.0543756800501934</v>
+        <v>-0.0049382666628676</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.4005134441903988</v>
+        <v>0.532959655238795</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-24.77076819388193</v>
+        <v>-0.1264124005895605</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>806.719970703125</v>
+        <v>6.142785753522601</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1255.545043945312</v>
+        <v>9.835821083613803</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>89.7650146484375</v>
+        <v>0.7386070660182408</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>6.13</v>
+        <v>5.76</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.006217</v>
+        <v>0.755569</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>1.12</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1155.849975585938</v>
+        <v>1154.025024414062</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>82</v>
@@ -1272,22 +1272,22 @@
         <v>50</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>57.75332742343394</v>
+        <v>57.42014603587688</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>-0.013419399271567</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.4189032319337272</v>
+        <v>0.4580057730416195</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-6.903077296081101</v>
+        <v>-7.019541416451538</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1093.60049874442</v>
+        <v>1091.775547572545</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1238.849278041295</v>
+        <v>1237.02432686942</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>41.49965122767857</v>
@@ -1296,7 +1296,7 @@
         <v>13.95</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.012071</v>
+        <v>0.01209</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>1.12</v>
@@ -1332,12 +1332,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BFLY</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7.715000152587891</v>
+        <v>368.364990234375</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>82</v>
@@ -1366,31 +1366,31 @@
         <v>50</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>50.43817014886233</v>
+        <v>45.92279579419217</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.0049382666628676</v>
+        <v>0.082723417254077</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.4927610051708153</v>
+        <v>0.3098805794520953</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-0.1203497054857275</v>
+        <v>-11.28628974945518</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>6.237786020551409</v>
+        <v>275.5091465541295</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>9.930821350642614</v>
+        <v>507.6487557547433</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.7386070660182408</v>
+        <v>46.42792184012277</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>5.83</v>
+        <v>4.43</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.755569</v>
+        <v>0.01202</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>1.12</v>
@@ -1424,117 +1424,117 @@
       <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>ALAB</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>369.7300109863281</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="H8" s="2" t="n">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>393.6900024414063</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>BUY SMALL</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H8" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>46.13204403486358</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>0.082723417254077</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0.2866642642115858</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>-11.19917731400292</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>276.8741673060826</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>509.0137765066965</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>46.42792184012277</v>
-      </c>
-      <c r="Q8" s="2" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>0.01202</v>
-      </c>
-      <c r="S8" s="2" t="n">
+      <c r="I8" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>55.52202604846918</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.030087289573326</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.4014549875260613</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>3.27231196562413</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>371.1846531459264</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>423.6971348353795</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>15.00356619698661</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.017719</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="T8" s="2" t="n">
+      <c r="T8" s="3" t="n">
         <v>13.95</v>
       </c>
-      <c r="U8" s="2" t="inlineStr"/>
-      <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="inlineStr"/>
-      <c r="Y8" s="2" t="inlineStr"/>
-      <c r="Z8" s="2" t="n">
+      <c r="U8" s="3" t="inlineStr"/>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AA8" s="2" t="n">
+      <c r="AA8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
+      <c r="AB8" s="3" t="inlineStr">
         <is>
           <t>6 open slot(s)</t>
         </is>
       </c>
-      <c r="AC8" s="2" t="inlineStr"/>
-      <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="inlineStr">
-        <is>
-          <t>Strong trend; Positive momentum</t>
-        </is>
-      </c>
-      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AC8" s="3" t="inlineStr"/>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Positive momentum; MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>BLZE</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Gaming/Digital Media</t>
+          <t>Cloud Software</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>16.79999923706055</v>
+        <v>266.9100036621094</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>79</v>
@@ -1554,31 +1554,31 @@
         <v>75</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>74.38330110685949</v>
+        <v>75.48954865203949</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.0098826338563442</v>
+        <v>-0.0192129762097973</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.2133256018345131</v>
+        <v>0.4124541976099978</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.1228156727421159</v>
+        <v>0.4319657238359742</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>13.8009990964617</v>
+        <v>246.1390718732561</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>21.29849944795881</v>
+        <v>294.6045793805803</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>1.499500070299421</v>
+        <v>13.84728785923549</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>0.026136</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>1.12</v>
@@ -1586,25 +1586,11 @@
       <c r="T9" s="3" t="n">
         <v>13.95</v>
       </c>
-      <c r="U9" s="3" t="n">
-        <v>0.1148598575918484</v>
-      </c>
+      <c r="U9" s="3" t="inlineStr"/>
       <c r="V9" s="3" t="inlineStr"/>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>No exit trigger</t>
-        </is>
-      </c>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="inlineStr"/>
       <c r="Z9" s="3" t="n">
         <v>4</v>
       </c>
@@ -1613,19 +1599,11 @@
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>Already held</t>
-        </is>
-      </c>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>Held, but not strong enough to add</t>
-        </is>
-      </c>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr"/>
+      <c r="AD9" s="3" t="inlineStr"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
@@ -1654,7 +1632,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>13.71000003814697</v>
+        <v>13.68000030517578</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>79</v>
@@ -1674,28 +1652,28 @@
         <v>75</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>75.11415241761875</v>
+        <v>74.94252742525934</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>-0.0110537672736636</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.2434366442298766</v>
+        <v>0.2683889709853157</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.0314758860509889</v>
+        <v>0.029561373177612</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>12.50234304155622</v>
+        <v>12.47234330858503</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>15.5214855330331</v>
+        <v>15.49148580006191</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.6038284982953753</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>6.34</v>
+        <v>6.32</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>0.462108</v>
@@ -1738,21 +1716,21 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>BLZE</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Cloud Software</t>
+          <t>Gaming/Digital Media</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>268.3349914550781</v>
+        <v>16.70000076293945</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>79</v>
@@ -1772,31 +1750,31 @@
         <v>75</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>75.86785464606048</v>
+        <v>74.13793418441759</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.0192129762097973</v>
+        <v>0.0098826338563442</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.3852121946677656</v>
+        <v>0.2313873601797258</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.5229051157519322</v>
+        <v>0.1164340037383775</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>247.5640596662249</v>
+        <v>13.70100062234061</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>296.0295671735491</v>
+        <v>21.19850097383772</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>13.84728785923549</v>
+        <v>1.499500070299421</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>6.98</v>
+        <v>0</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.025997</v>
+        <v>0</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>1.12</v>
@@ -1804,11 +1782,25 @@
       <c r="T11" s="3" t="n">
         <v>13.95</v>
       </c>
-      <c r="U11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="n">
+        <v>0.1082238879679861</v>
+      </c>
       <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr"/>
-      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>No exit trigger</t>
+        </is>
+      </c>
       <c r="Z11" s="3" t="n">
         <v>4</v>
       </c>
@@ -1817,11 +1809,19 @@
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
-        </is>
-      </c>
-      <c r="AC11" s="3" t="inlineStr"/>
-      <c r="AD11" s="3" t="inlineStr"/>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>Held, but not strong enough to add</t>
+        </is>
+      </c>
       <c r="AE11" s="3" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
@@ -1836,24 +1836,24 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>STTK</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>394.1300048828125</v>
+        <v>6.440000057220459</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1861,40 +1861,40 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>75</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>55.68108339379057</v>
+        <v>62.89926016459427</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.030087289573326</v>
+        <v>0.0046656626141934</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.3780343234888427</v>
+        <v>0.313019261723703</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>3.300391893508749</v>
+        <v>0.0217298247180257</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>371.6246555873326</v>
+        <v>5.153857367379325</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>424.1371372767857</v>
+        <v>8.36921409198216</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>15.00356619698661</v>
+        <v>0.6430713449205671</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>6.98</v>
+        <v>2.79</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.017699</v>
+        <v>0.433909</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>1.12</v>
@@ -1922,7 +1922,7 @@
       <c r="AD12" s="3" t="inlineStr"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>Positive momentum; MACD/volume acceleration</t>
+          <t>Strong trend; MACD/volume acceleration</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr"/>
@@ -1930,12 +1930,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>STTK</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>6.409999847412109</v>
+        <v>981.2349853515624</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1958,37 +1958,37 @@
         <v>80</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>62.49999561730699</v>
+        <v>44.63958636842999</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.0046656626141934</v>
+        <v>0.0543756800501934</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.2667874229547377</v>
+        <v>0.4266627673210695</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0.0198152814140169</v>
+        <v>-25.09081471275649</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>5.123857157570975</v>
+        <v>801.7049560546874</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>8.33921388217381</v>
+        <v>1250.530029296875</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.6430713449205671</v>
+        <v>89.7650146484375</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>0.433909</v>
+        <v>0.003108</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>1.12</v>
@@ -2016,7 +2016,7 @@
       <c r="AD13" s="3" t="inlineStr"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>Strong trend; MACD/volume acceleration</t>
+          <t>Strong trend; Positive momentum</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr"/>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>239.5500030517578</v>
+        <v>238.5599975585937</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>75</v>
@@ -2058,28 +2058,28 @@
         <v>50</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>41.52500238076169</v>
+        <v>41.22109092680138</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0.06596166699561611</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.2808836292303273</v>
+        <v>0.3081548827254273</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>-4.613291932127268</v>
+        <v>-4.676471769867648</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>185.9792872837612</v>
+        <v>184.989281790597</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>319.9060767037528</v>
+        <v>318.9160712105887</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>26.78535788399833</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>0.010417</v>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>357.8800048828125</v>
+        <v>357.9649963378906</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>71</v>
@@ -2152,22 +2152,22 @@
         <v>75</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>59.6517272255997</v>
+        <v>59.70798614779127</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>-0.0040282924977889</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.2828378621307953</v>
+        <v>0.3110084458729493</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5934903871165398</v>
+        <v>0.5989143432240915</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>342.9346455165318</v>
+        <v>343.0196369716099</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>377.8071507045201</v>
+        <v>377.8921421595982</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>9.963572910853795</v>
@@ -2185,7 +2185,7 @@
         <v>13.95</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.0243722680283474</v>
+        <v>-0.0241405701982828</v>
       </c>
       <c r="V15" s="4" t="inlineStr"/>
       <c r="W15" s="4" t="inlineStr">
@@ -2238,24 +2238,24 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Internet/E-Commerce</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>246.7601013183593</v>
+        <v>18.56500053405762</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
@@ -2266,31 +2266,31 @@
         <v>40</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>75</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>65.81661406780198</v>
+        <v>62.08528783568838</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.0071974396379796</v>
+        <v>0.0044125718372439</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.319099537120721</v>
+        <v>0.8860310313498829</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.694788959219471</v>
+        <v>0.0332653298772992</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>235.5433202471052</v>
+        <v>16.68214334760393</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>261.7158094133649</v>
+        <v>21.38928631373814</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>7.47785404750279</v>
+        <v>0.9414285932268416</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
@@ -2304,11 +2304,25 @@
       <c r="T16" s="4" t="n">
         <v>13.95</v>
       </c>
-      <c r="U16" s="4" t="inlineStr"/>
+      <c r="U16" s="4" t="n">
+        <v>0.0090427009329377</v>
+      </c>
       <c r="V16" s="4" t="inlineStr"/>
-      <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="4" t="inlineStr"/>
-      <c r="Y16" s="4" t="inlineStr"/>
+      <c r="W16" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X16" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Y16" s="4" t="inlineStr">
+        <is>
+          <t>No exit trigger</t>
+        </is>
+      </c>
       <c r="Z16" s="4" t="n">
         <v>4</v>
       </c>
@@ -2317,11 +2331,19 @@
       </c>
       <c r="AB16" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
-        </is>
-      </c>
-      <c r="AC16" s="4" t="inlineStr"/>
-      <c r="AD16" s="4" t="inlineStr"/>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AD16" s="4" t="inlineStr">
+        <is>
+          <t>Held, but not strong enough to add</t>
+        </is>
+      </c>
       <c r="AE16" s="4" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
@@ -2332,24 +2354,24 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>18.68510055541992</v>
+        <v>422.989990234375</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
@@ -2360,31 +2382,31 @@
         <v>40</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>62.9293039995192</v>
+        <v>45.80252323519223</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.0044125718372439</v>
+        <v>0.0220361706931489</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.7883278911443727</v>
+        <v>0.7548747682153525</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.040929832665095</v>
+        <v>-4.040947469367188</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>16.80224336896623</v>
+        <v>393.0307050432477</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>21.50938633510044</v>
+        <v>462.9357038225447</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.9414285932268416</v>
+        <v>19.97285679408482</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
@@ -2398,25 +2420,11 @@
       <c r="T17" s="4" t="n">
         <v>13.95</v>
       </c>
-      <c r="U17" s="4" t="n">
-        <v>0.0155703630094997</v>
-      </c>
+      <c r="U17" s="4" t="inlineStr"/>
       <c r="V17" s="4" t="inlineStr"/>
-      <c r="W17" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="X17" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="Y17" s="4" t="inlineStr">
-        <is>
-          <t>No exit trigger</t>
-        </is>
-      </c>
+      <c r="W17" s="4" t="inlineStr"/>
+      <c r="X17" s="4" t="inlineStr"/>
+      <c r="Y17" s="4" t="inlineStr"/>
       <c r="Z17" s="4" t="n">
         <v>4</v>
       </c>
@@ -2425,22 +2433,14 @@
       </c>
       <c r="AB17" s="4" t="inlineStr">
         <is>
-          <t>Already held</t>
-        </is>
-      </c>
-      <c r="AC17" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="AD17" s="4" t="inlineStr">
-        <is>
-          <t>Held, but not strong enough to add</t>
-        </is>
-      </c>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AD17" s="4" t="inlineStr"/>
       <c r="AE17" s="4" t="inlineStr">
         <is>
-          <t>MACD/volume acceleration</t>
+          <t>Positive momentum</t>
         </is>
       </c>
       <c r="AF17" s="4" t="inlineStr"/>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>885.8699951171875</v>
+        <v>879.0349731445312</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>65</v>
@@ -2482,22 +2482,22 @@
         <v>50</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>38.53832446966886</v>
+        <v>37.9012279970176</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>0.0451049293978258</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.5236166295290705</v>
+        <v>0.6024776914882387</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-14.75314380849785</v>
+        <v>-15.18933894293512</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>759.4210662841797</v>
+        <v>752.5860443115234</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1054.468566894531</v>
+        <v>1047.633544921875</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>84.29928588867188</v>
@@ -2542,12 +2542,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Data Centers</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>423.5700073242188</v>
+        <v>303.2900085449219</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
@@ -2570,31 +2570,31 @@
         <v>40</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>50</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>45.99874957947848</v>
+        <v>45.51637972582078</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.0220361706931489</v>
+        <v>0.031582057136426</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.7128527822324831</v>
+        <v>0.3962776464705639</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-4.003932133719059</v>
+        <v>-0.7856096401414672</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>393.6107221330916</v>
+        <v>271.3860778808594</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>463.5157209123885</v>
+        <v>345.8285827636719</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>19.97285679408482</v>
+        <v>21.269287109375</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
@@ -2626,22 +2626,18 @@
       </c>
       <c r="AC19" s="4" t="inlineStr"/>
       <c r="AD19" s="4" t="inlineStr"/>
-      <c r="AE19" s="4" t="inlineStr">
-        <is>
-          <t>Positive momentum</t>
-        </is>
-      </c>
+      <c r="AE19" s="4" t="inlineStr"/>
       <c r="AF19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Data Centers</t>
+          <t>Internet/E-Commerce</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2650,10 +2646,10 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>304.2199096679688</v>
+        <v>246.4450073242188</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
@@ -2664,31 +2660,31 @@
         <v>40</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>45.77031353903932</v>
+        <v>65.30207701967382</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.031582057136426</v>
+        <v>-0.0071974396379796</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3391196681344074</v>
+        <v>0.3574128495100627</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7262655228872175</v>
+        <v>1.674680396630441</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>272.3159790039062</v>
+        <v>235.1992972237724</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>346.7584838867188</v>
+        <v>261.4392874581473</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>21.269287109375</v>
+        <v>7.497140066964286</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
@@ -2720,7 +2716,11 @@
       </c>
       <c r="AC20" s="4" t="inlineStr"/>
       <c r="AD20" s="4" t="inlineStr"/>
-      <c r="AE20" s="4" t="inlineStr"/>
+      <c r="AE20" s="4" t="inlineStr">
+        <is>
+          <t>MACD/volume acceleration</t>
+        </is>
+      </c>
       <c r="AF20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>104.1699981689453</v>
+        <v>101.9199981689453</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>56</v>
@@ -2760,25 +2760,25 @@
         <v>75</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>64.48132547579638</v>
+        <v>61.78305163129135</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.4003972079316982</v>
+        <v>0.4527524421361122</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.390519274915364</v>
+        <v>1.246929531325618</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>92.22714015415738</v>
+        <v>89.80142538888116</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>122.0842851911272</v>
+        <v>120.0978573390416</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>5.971429007393973</v>
+        <v>6.059286390032087</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>284.0849914550781</v>
+        <v>284.3847045898437</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>55</v>
@@ -2854,22 +2854,22 @@
         <v>50</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>28.57589069884973</v>
+        <v>28.62054776079645</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>0.0376936349020097</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.5599767397473132</v>
+        <v>0.5898495564600381</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-9.914738521097938</v>
+        <v>-9.895611529021703</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>225.3224182128907</v>
+        <v>225.6221313476562</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>372.2288513183594</v>
+        <v>372.5285644531249</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>29.38128662109375</v>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>223.8800048828125</v>
+        <v>223.5269927978516</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>55</v>
@@ -2948,22 +2948,22 @@
         <v>50</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>33.99490134302415</v>
+        <v>33.85940682526719</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>0.0645198535414377</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.2815938185806411</v>
+        <v>0.300387486229015</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-9.05594682947174</v>
+        <v>-9.078475236033322</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>191.475715637207</v>
+        <v>191.1227035522461</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>267.0857238769531</v>
+        <v>266.7327117919922</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>21.60285949707031</v>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>195.3800048828125</v>
+        <v>195.4440002441407</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>55</v>
@@ -3042,22 +3042,22 @@
         <v>50</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>30.14073385754547</v>
+        <v>30.15032897033954</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>0.0310198990532244</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.6898714365460202</v>
+        <v>0.7415714487874523</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-7.012393995697595</v>
+        <v>-7.008309961242444</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>144.2597176688058</v>
+        <v>144.3237130301339</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>272.0604357038226</v>
+        <v>272.1244310651507</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>25.56014360700335</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>107.2350006103516</v>
+        <v>108.60009765625</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>55</v>
@@ -3136,25 +3136,25 @@
         <v>50</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>31.20732330339128</v>
+        <v>32.58833144019887</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>0.0469355722360184</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.4569902219755921</v>
+        <v>0.5125645030376157</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.426643843630789</v>
+        <v>-3.33952653927714</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>93.01607131958008</v>
+        <v>94.28798648289272</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>126.1935729980469</v>
+        <v>127.6829125540597</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>9.479286193847656</v>
+        <v>9.541407448904854</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>25.82500076293945</v>
+        <v>25.68000030517578</v>
       </c>
       <c r="E26" s="4" t="n">
         <v>54</v>
@@ -3230,22 +3230,22 @@
         <v>50</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>41.73541298197256</v>
+        <v>41.36886831176119</v>
       </c>
       <c r="K26" s="4" t="n">
         <v>0.0084746235925221</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.2254074852720216</v>
+        <v>0.2475597880393733</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.0449669240438348</v>
+        <v>-0.0542205145108036</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>21.07228660583496</v>
+        <v>20.92728614807129</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>32.95407199859619</v>
+        <v>32.80907154083252</v>
       </c>
       <c r="P26" s="4" t="n">
         <v>2.376357078552246</v>
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>275.6900024414062</v>
+        <v>273.7200012207031</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>51</v>
@@ -3320,22 +3320,22 @@
         <v>75</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>61.30708019557833</v>
+        <v>59.84774036913862</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>-0.0092015237095138</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.2167160741542863</v>
+        <v>0.2569222941521288</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.88131658504367</v>
+        <v>5.755595709420415</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>257.8882222856794</v>
+        <v>255.9182210649763</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>299.4257093157088</v>
+        <v>297.4557080950056</v>
       </c>
       <c r="P27" s="4" t="n">
         <v>11.86785343715123</v>
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>396.5599975585938</v>
+        <v>396.0499877929688</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>43</v>
@@ -3414,22 +3414,22 @@
         <v>50</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>54.42177423372955</v>
+        <v>54.28385236539413</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>0.0109940121352903</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.3342505129947347</v>
+        <v>0.3591522442967725</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.0199450634280342</v>
+        <v>-0.0524926951944539</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>368.7092862810407</v>
+        <v>368.1992765154158</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>433.6942792619978</v>
+        <v>433.1842694963729</v>
       </c>
       <c r="P28" s="4" t="n">
         <v>18.56714085170201</v>
@@ -3447,7 +3447,7 @@
         <v>13.95</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.0408155757036262</v>
+        <v>-0.0420491681648886</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>79.83499908447266</v>
+        <v>79.03959655761719</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>43</v>
@@ -3534,22 +3534,22 @@
         <v>50</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>38.09486287767558</v>
+        <v>37.31820954520452</v>
       </c>
       <c r="K29" s="4" t="n">
         <v>0.0264563885114627</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.383364680100515</v>
+        <v>0.4093820761292379</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.379969068754979</v>
+        <v>-1.430729799813575</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>64.36928558349609</v>
+        <v>63.57388305664063</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>103.0335693359375</v>
+        <v>102.238166809082</v>
       </c>
       <c r="P29" s="4" t="n">
         <v>7.732856750488281</v>
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6.775000095367432</v>
+        <v>6.769999980926514</v>
       </c>
       <c r="E30" s="4" t="n">
         <v>39</v>
@@ -3624,22 +3624,22 @@
         <v>75</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>57.17344823713204</v>
+        <v>57.08154365904792</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>-0.0154083063419491</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.7711507195753267</v>
+        <v>0.9010949756444936</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.06727764360870241</v>
+        <v>0.0669585479862623</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.963714259011405</v>
+        <v>5.958714144570487</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.991928849901472</v>
+        <v>7.986928735460554</v>
       </c>
       <c r="P30" s="4" t="n">
         <v>0.4056429181780134</v>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>27.9099006652832</v>
+        <v>27.78499984741211</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>33</v>
@@ -3718,22 +3718,22 @@
         <v>50</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>28.16730183888978</v>
+        <v>27.43579240581289</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>0.0112075006381963</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.2221729599943951</v>
+        <v>0.2535316716832742</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.0290994938696083</v>
+        <v>-0.0370703722750587</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>24.35990115574428</v>
+        <v>24.23500033787318</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>33.23489992959159</v>
+        <v>33.1099991117205</v>
       </c>
       <c r="P31" s="4" t="n">
         <v>1.774999754769462</v>
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>39.63980102539063</v>
+        <v>39.27999877929688</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>33</v>
@@ -3808,22 +3808,22 @@
         <v>50</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>18.46150735910098</v>
+        <v>17.4324740918985</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>0.0298353862022756</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.3605210142088432</v>
+        <v>0.3917250137666157</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.415078615704978</v>
+        <v>-1.438040354487022</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>32.23765836443221</v>
+        <v>31.87785611833846</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>50.74301501682827</v>
+        <v>50.38321277073453</v>
       </c>
       <c r="P32" s="4" t="n">
         <v>3.701071330479213</v>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>69.73000335693359</v>
+        <v>69.53610229492188</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>32</v>
@@ -3898,22 +3898,22 @@
         <v>50</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>47.16606522058868</v>
+        <v>46.9804959194845</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>0.0334417645102432</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.2963062066651367</v>
+        <v>0.3131508734816722</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.7429959739622536</v>
+        <v>-0.7553702867516128</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>55.81943184988839</v>
+        <v>55.62553078787667</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>90.5958606175014</v>
+        <v>90.40195955548968</v>
       </c>
       <c r="P33" s="4" t="n">
         <v>6.955285753522601</v>
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>7.864999771118164</v>
+        <v>7.880000114440918</v>
       </c>
       <c r="E34" s="4" t="n">
         <v>32</v>
@@ -3988,22 +3988,22 @@
         <v>50</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>44.85895772680138</v>
+        <v>45.00907288667684</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>0.018661516252568</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.6570166384036633</v>
+        <v>0.7302975838331116</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.07195449789216279</v>
+        <v>-0.07099721102484099</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.476714270455497</v>
+        <v>6.49171461377825</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>9.947428022112163</v>
+        <v>9.962428365434921</v>
       </c>
       <c r="P34" s="4" t="n">
         <v>0.6941427503313337</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>183.5726013183593</v>
+        <v>186.8500061035156</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>29</v>
@@ -4083,13 +4083,13 @@
       </c>
       <c r="L35" s="4" t="inlineStr"/>
       <c r="M35" s="4" t="n">
-        <v>0.4637916883379285</v>
+        <v>0.6729480051114388</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>168.8867932128906</v>
+        <v>171.9020056152343</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>211.1084915161132</v>
+        <v>214.8775070190429</v>
       </c>
       <c r="P35" s="4" t="inlineStr"/>
       <c r="Q35" s="4" t="n">
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>15.15999984741211</v>
+        <v>14.89999961853027</v>
       </c>
       <c r="E36" s="4" t="n">
         <v>22</v>
@@ -4170,25 +4170,25 @@
         <v>50</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>24.12867906119573</v>
+        <v>23.53454946433199</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>0.0323432829789085</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.3601037693941117</v>
+        <v>0.4117522985775755</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>-0.2090269654391505</v>
+        <v>-0.2256195726384504</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>11.91101373944964</v>
+        <v>11.63099929264613</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>20.03347900935581</v>
+        <v>19.80350010735648</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>1.624493053981236</v>
+        <v>1.634500162942069</v>
       </c>
       <c r="Q36" s="4" t="n">
         <v>0</v>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>91.4268035888672</v>
+        <v>91.27999877929688</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>22</v>
@@ -4260,22 +4260,22 @@
         <v>50</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>16.79596631516891</v>
+        <v>16.32886286692583</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>0.0177384274683925</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>0.8168933898374361</v>
+        <v>0.8757062652812388</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>-0.7812640865729326</v>
+        <v>-0.7906328265569047</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>84.70144598824639</v>
+        <v>84.55464117867606</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>100.3939470563616</v>
+        <v>100.2471422467913</v>
       </c>
       <c r="P37" s="4" t="n">
         <v>4.48357173374721</v>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>8.591699600219727</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="E38" s="4" t="n">
         <v>22</v>
@@ -4350,22 +4350,22 @@
         <v>50</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>21.15368988899225</v>
+        <v>21.31980309769909</v>
       </c>
       <c r="K38" s="4" t="n">
         <v>0.0299401183926648</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.5066804764858122</v>
+        <v>0.5401360683617086</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-0.1147910488897834</v>
+        <v>-0.1142613124225461</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>7.244557380676269</v>
+        <v>7.252858161926269</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>10.61241292953491</v>
+        <v>10.62071371078491</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>0.6735711097717285</v>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>46.31999969482422</v>
+        <v>45.97499847412109</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>22</v>
@@ -4440,22 +4440,22 @@
         <v>50</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>24.87285661301692</v>
+        <v>23.65514622294652</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>0.0251036384349932</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>0.3229469686759906</v>
+        <v>0.3466929337294923</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>-0.3194569080891871</v>
+        <v>-0.3414740800087021</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>39.43325642177037</v>
+        <v>39.08825520106723</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>56.65011460440499</v>
+        <v>56.30511338370187</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>3.443371636526925</v>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>7.760000228881836</v>
+        <v>7.704999923706055</v>
       </c>
       <c r="E40" s="4" t="n">
         <v>22</v>
@@ -4530,22 +4530,22 @@
         <v>50</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>27.1099796021057</v>
+        <v>26.07003852546879</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>0.0100267124430337</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.9106918327089401</v>
+        <v>1.021877445593526</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>-0.1033222506595922</v>
+        <v>-0.1068322416451681</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>6.644571644919259</v>
+        <v>6.589571339743478</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>9.4331431048257</v>
+        <v>9.37814279964992</v>
       </c>
       <c r="P40" s="4" t="n">
         <v>0.5577142919812884</v>
@@ -4662,19 +4662,19 @@
         <v>15.06915790595363</v>
       </c>
       <c r="D2" t="n">
-        <v>16.79999923706055</v>
+        <v>16.70000076293945</v>
       </c>
       <c r="E2" t="n">
-        <v>12.54329808637039</v>
+        <v>12.46863673362961</v>
       </c>
       <c r="F2" t="n">
         <v>11.251008816</v>
       </c>
       <c r="G2" t="n">
-        <v>1.292289270370391</v>
+        <v>1.217627917629608</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1148598575918484</v>
+        <v>0.1082238879679861</v>
       </c>
     </row>
     <row r="3">
@@ -4690,19 +4690,19 @@
         <v>366.8202462424581</v>
       </c>
       <c r="D3" t="n">
-        <v>357.8800048828125</v>
+        <v>357.9649963378906</v>
       </c>
       <c r="E3" t="n">
-        <v>18.91742611530396</v>
+        <v>18.92191873727204</v>
       </c>
       <c r="F3" t="n">
         <v>19.3900045021</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4725783867960444</v>
+        <v>-0.4680857648279648</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0243722680283474</v>
+        <v>-0.0241405701982828</v>
       </c>
     </row>
     <row r="4">
@@ -4718,19 +4718,19 @@
         <v>18.39862725025694</v>
       </c>
       <c r="D4" t="n">
-        <v>18.68510055541992</v>
+        <v>18.56500053405762</v>
       </c>
       <c r="E4" t="n">
-        <v>11.42619123849678</v>
+        <v>11.35274845408344</v>
       </c>
       <c r="F4" t="n">
         <v>11.251008945</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1751822934967783</v>
+        <v>0.1017395090834423</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0155703630094997</v>
+        <v>0.0090427009329377</v>
       </c>
     </row>
     <row r="5">
@@ -4746,19 +4746,19 @@
         <v>413.4345674446258</v>
       </c>
       <c r="D5" t="n">
-        <v>396.5599975585938</v>
+        <v>396.0499877929688</v>
       </c>
       <c r="E5" t="n">
-        <v>10.79178945916077</v>
+        <v>10.77791030330383</v>
       </c>
       <c r="F5" t="n">
         <v>11.2510057355</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4592162763392338</v>
+        <v>-0.4730954321961658</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0408155757036262</v>
+        <v>-0.0420491681648886</v>
       </c>
     </row>
   </sheetData>
@@ -4778,11 +4778,11 @@
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -4808,27 +4808,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>portfolio_value_usd</t>
+          <t>account_equity_usd</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>account_pnl_usd</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>account_return_pct</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>realized_pnl_usd</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>unrealized_pnl_usd</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>total_pnl_usd</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>total_return_pct</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -4865,22 +4865,22 @@
         <v>55.81</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>53.68</v>
+        <v>53.52</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>109.49</v>
+        <v>109.33</v>
       </c>
       <c r="E2" s="5" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>-0.039971511869609</v>
+      </c>
+      <c r="G2" s="5" t="n">
         <v>-3.16</v>
       </c>
-      <c r="F2" s="5" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>-2.62</v>
-      </c>
       <c r="H2" s="5" t="n">
-        <v>-0.0230340794712689</v>
+        <v>0.38</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>0</v>
@@ -5043,46 +5043,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>369.7300109863281</v>
+        <v>368.364990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>331.9703994750977</v>
+        <v>331.9430990600586</v>
       </c>
       <c r="D2" t="n">
-        <v>201.245650138855</v>
+        <v>201.2388250350952</v>
       </c>
       <c r="E2" t="n">
-        <v>46.13204403486358</v>
+        <v>45.92279579419217</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0070271473041918</v>
+        <v>0.0033092642192258</v>
       </c>
       <c r="G2" t="n">
-        <v>1.167233281117151</v>
+        <v>1.159231987429477</v>
       </c>
       <c r="H2" t="n">
-        <v>1.14249287416261</v>
+        <v>1.134582920555269</v>
       </c>
       <c r="I2" t="n">
-        <v>14.87727506617841</v>
+        <v>14.76838452186308</v>
       </c>
       <c r="J2" t="n">
-        <v>26.07645238018133</v>
+        <v>26.05467427131826</v>
       </c>
       <c r="K2" t="n">
-        <v>-11.19917731400292</v>
+        <v>-11.28628974945518</v>
       </c>
       <c r="L2" t="n">
         <v>-10.00415359792669</v>
       </c>
       <c r="M2" t="n">
-        <v>1754963</v>
+        <v>1897980</v>
       </c>
       <c r="N2" t="n">
-        <v>6122015.26</v>
+        <v>6124875.6</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2866642642115858</v>
+        <v>0.3098805794520953</v>
       </c>
       <c r="P2" t="n">
         <v>0.082723417254077</v>
@@ -5096,7 +5096,7 @@
         <v>46.42792184012277</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1255725000961298</v>
+        <v>0.1260378240901304</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -5111,46 +5111,46 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>554.469970703125</v>
+        <v>553.489990234375</v>
       </c>
       <c r="C3" t="n">
-        <v>489.8407995605469</v>
+        <v>489.8211999511719</v>
       </c>
       <c r="D3" t="n">
-        <v>291.4991495513916</v>
+        <v>291.4942496490478</v>
       </c>
       <c r="E3" t="n">
-        <v>55.73406793368378</v>
+        <v>55.58990122403013</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0838594185833836</v>
+        <v>0.08194378542522419</v>
       </c>
       <c r="G3" t="n">
-        <v>1.17379525142813</v>
+        <v>1.169953245544999</v>
       </c>
       <c r="H3" t="n">
-        <v>1.669699861261029</v>
+        <v>1.664981384409807</v>
       </c>
       <c r="I3" t="n">
-        <v>17.29145622570184</v>
+        <v>17.21328114557355</v>
       </c>
       <c r="J3" t="n">
-        <v>19.9461948442408</v>
+        <v>19.93055982821513</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.654738618538957</v>
+        <v>-2.717278682641592</v>
       </c>
       <c r="L3" t="n">
         <v>-3.577422784539042</v>
       </c>
       <c r="M3" t="n">
-        <v>15118831</v>
+        <v>16031247</v>
       </c>
       <c r="N3" t="n">
-        <v>33873844.62</v>
+        <v>33892092.94</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4463275772090378</v>
+        <v>0.4730084692137635</v>
       </c>
       <c r="P3" t="n">
         <v>0.0624019610194614</v>
@@ -5164,7 +5164,7 @@
         <v>38.05143519810268</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0686266835151587</v>
+        <v>0.068748190336721</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -5179,46 +5179,46 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>246.7601013183593</v>
+        <v>246.4450073242188</v>
       </c>
       <c r="C4" t="n">
-        <v>253.3540017700195</v>
+        <v>253.3476998901367</v>
       </c>
       <c r="D4" t="n">
-        <v>233.5989505004883</v>
+        <v>233.5973750305176</v>
       </c>
       <c r="E4" t="n">
-        <v>65.81661406780198</v>
+        <v>65.30207701967382</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03441667642662</v>
+        <v>0.0330958045334754</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.009075186391969201</v>
+        <v>-0.0103405224643109</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0011770199059497</v>
+        <v>-0.00010140745876</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7121061073134172</v>
+        <v>-0.7372418105497047</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.406895066532888</v>
+        <v>-2.411922207180146</v>
       </c>
       <c r="K4" t="n">
-        <v>1.694788959219471</v>
+        <v>1.674680396630441</v>
       </c>
       <c r="L4" t="n">
         <v>1.780135958077288</v>
       </c>
       <c r="M4" t="n">
-        <v>15548822</v>
+        <v>17429163</v>
       </c>
       <c r="N4" t="n">
-        <v>48727184.44</v>
+        <v>48764791.26</v>
       </c>
       <c r="O4" t="n">
-        <v>0.319099537120721</v>
+        <v>0.3574128495100627</v>
       </c>
       <c r="P4" t="n">
         <v>-0.0071974396379796</v>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>7.47785404750279</v>
+        <v>7.497140066964286</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0303041456359882</v>
+        <v>0.0304211481026319</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -5247,46 +5247,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>182.7550048828125</v>
+        <v>181.9600067138672</v>
       </c>
       <c r="C5" t="n">
-        <v>160.7964996337891</v>
+        <v>160.7805996704102</v>
       </c>
       <c r="D5" t="n">
-        <v>144.3340746688843</v>
+        <v>144.3300996780396</v>
       </c>
       <c r="E5" t="n">
-        <v>62.50076790432738</v>
+        <v>62.13461920486363</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1195478971633927</v>
+        <v>0.1146777786740951</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1838764699323658</v>
+        <v>0.1787265172596215</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4807568270471498</v>
+        <v>0.4743154222445256</v>
       </c>
       <c r="I5" t="n">
-        <v>6.025940750922871</v>
+        <v>5.962522093571124</v>
       </c>
       <c r="J5" t="n">
-        <v>4.409767062664987</v>
+        <v>4.397083331194636</v>
       </c>
       <c r="K5" t="n">
-        <v>1.616173688257884</v>
+        <v>1.565438762376488</v>
       </c>
       <c r="L5" t="n">
         <v>1.773262942271622</v>
       </c>
       <c r="M5" t="n">
-        <v>3705963</v>
+        <v>4141118</v>
       </c>
       <c r="N5" t="n">
-        <v>10348175.26</v>
+        <v>10356878.36</v>
       </c>
       <c r="O5" t="n">
-        <v>0.358127197006905</v>
+        <v>0.3998422937932429</v>
       </c>
       <c r="P5" t="n">
         <v>0.0151807899125376</v>
@@ -5300,7 +5300,7 @@
         <v>10.46220506940569</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0572471603506253</v>
+        <v>0.0574972778818235</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -5315,46 +5315,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>284.0849914550781</v>
+        <v>284.3847045898437</v>
       </c>
       <c r="C6" t="n">
-        <v>312.6170980834961</v>
+        <v>312.6230923461914</v>
       </c>
       <c r="D6" t="n">
-        <v>182.8260499191284</v>
+        <v>182.8275484848022</v>
       </c>
       <c r="E6" t="n">
-        <v>28.57589069884973</v>
+        <v>28.62054776079645</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2539980744298419</v>
+        <v>-0.2532110332894121</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7620952071956519</v>
+        <v>0.7639542391550633</v>
       </c>
       <c r="H6" t="n">
-        <v>1.55610035104551</v>
+        <v>1.558797068126773</v>
       </c>
       <c r="I6" t="n">
-        <v>-7.923073500388625</v>
+        <v>-7.899164760293331</v>
       </c>
       <c r="J6" t="n">
-        <v>1.991665020709313</v>
+        <v>1.996446768728372</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.914738521097938</v>
+        <v>-9.895611529021703</v>
       </c>
       <c r="L6" t="n">
         <v>-9.368367243321137</v>
       </c>
       <c r="M6" t="n">
-        <v>6264892</v>
+        <v>6603092</v>
       </c>
       <c r="N6" t="n">
-        <v>11187771.84</v>
+        <v>11194535.84</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5599767397473132</v>
+        <v>0.5898495564600381</v>
       </c>
       <c r="P6" t="n">
         <v>0.0376936349020097</v>
@@ -5368,7 +5368,7 @@
         <v>29.38128662109375</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1034242832421499</v>
+        <v>0.1033152843556377</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -5383,46 +5383,46 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69.73000335693359</v>
+        <v>69.53610229492188</v>
       </c>
       <c r="C7" t="n">
-        <v>86.0478002166748</v>
+        <v>86.04392219543458</v>
       </c>
       <c r="D7" t="n">
-        <v>83.07169986724854</v>
+        <v>83.07073036193847</v>
       </c>
       <c r="E7" t="n">
-        <v>47.16606522058868</v>
+        <v>46.9804959194845</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1538648190960561</v>
+        <v>-0.1562177016757819</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2127130676617986</v>
+        <v>-0.2149023085185201</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2912897267049902</v>
+        <v>-0.2932604662437091</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.768320009607095</v>
+        <v>-4.783787900593794</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.025324035644841</v>
+        <v>-4.028417613842181</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7429959739622536</v>
+        <v>-0.7553702867516128</v>
       </c>
       <c r="L7" t="n">
         <v>-0.7205249641778009</v>
       </c>
       <c r="M7" t="n">
-        <v>6856924</v>
+        <v>7249189</v>
       </c>
       <c r="N7" t="n">
-        <v>23141344.48</v>
+        <v>23149189.78</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2963062066651367</v>
+        <v>0.3131508734816722</v>
       </c>
       <c r="P7" t="n">
         <v>0.0334417645102432</v>
@@ -5436,7 +5436,7 @@
         <v>6.955285753522601</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0997459546634455</v>
+        <v>0.1000240957427165</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -5451,46 +5451,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>394.1300048828125</v>
+        <v>393.6900024414063</v>
       </c>
       <c r="C8" t="n">
-        <v>405.556400756836</v>
+        <v>405.5476007080078</v>
       </c>
       <c r="D8" t="n">
-        <v>362.9461502075195</v>
+        <v>362.9439501953125</v>
       </c>
       <c r="E8" t="n">
-        <v>55.68108339379057</v>
+        <v>55.52202604846918</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0315648894898987</v>
+        <v>0.0304132616914023</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0350596306169257</v>
+        <v>0.0339041013275283</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1190199439105945</v>
+        <v>0.1177706822426092</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.410871342527344</v>
+        <v>-3.445971252383117</v>
       </c>
       <c r="J8" t="n">
-        <v>-6.711263236036093</v>
+        <v>-6.718283218007247</v>
       </c>
       <c r="K8" t="n">
-        <v>3.300391893508749</v>
+        <v>3.27231196562413</v>
       </c>
       <c r="L8" t="n">
         <v>3.038872772970159</v>
       </c>
       <c r="M8" t="n">
-        <v>10374434</v>
+        <v>11022372</v>
       </c>
       <c r="N8" t="n">
-        <v>27443100.68</v>
+        <v>27456059.44</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3780343234888427</v>
+        <v>0.4014549875260613</v>
       </c>
       <c r="P8" t="n">
         <v>0.030087289573326</v>
@@ -5504,7 +5504,7 @@
         <v>15.00356619698661</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0380675564182119</v>
+        <v>0.0381101021208168</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -5519,46 +5519,46 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.715000152587891</v>
+        <v>7.619999885559082</v>
       </c>
       <c r="C9" t="n">
-        <v>5.822899994850158</v>
+        <v>5.820999989509582</v>
       </c>
       <c r="D9" t="n">
-        <v>4.045425000190735</v>
+        <v>4.044949998855591</v>
       </c>
       <c r="E9" t="n">
-        <v>50.43817014886233</v>
+        <v>49.52198674958101</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3925993151103499</v>
+        <v>0.3754512523516937</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7376126245857879</v>
+        <v>0.7162161683235146</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8067916128922028</v>
+        <v>0.7845433066970831</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6120734624199402</v>
+        <v>0.604495093540149</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7324231679056677</v>
+        <v>0.7309074941297095</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1203497054857275</v>
+        <v>-0.1264124005895605</v>
       </c>
       <c r="L9" t="n">
         <v>-0.0949479297406228</v>
       </c>
       <c r="M9" t="n">
-        <v>3851253</v>
+        <v>4168817</v>
       </c>
       <c r="N9" t="n">
-        <v>7815661.06</v>
+        <v>7822012.34</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4927610051708153</v>
+        <v>0.532959655238795</v>
       </c>
       <c r="P9" t="n">
         <v>-0.0049382666628676</v>
@@ -5572,7 +5572,7 @@
         <v>0.7386070660182408</v>
       </c>
       <c r="S9" t="n">
-        <v>0.09573649402592491</v>
+        <v>0.0969300626129929</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -5587,46 +5587,46 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16.79999923706055</v>
+        <v>16.70000076293945</v>
       </c>
       <c r="C10" t="n">
-        <v>9.901400012969971</v>
+        <v>9.89940004348755</v>
       </c>
       <c r="D10" t="n">
-        <v>6.552049986124039</v>
+        <v>6.551549993753433</v>
       </c>
       <c r="E10" t="n">
-        <v>74.38330110685949</v>
+        <v>74.13793418441759</v>
       </c>
       <c r="F10" t="n">
-        <v>1.12121200444759</v>
+        <v>1.108585934604434</v>
       </c>
       <c r="G10" t="n">
-        <v>3.692737317063685</v>
+        <v>3.664804781797714</v>
       </c>
       <c r="H10" t="n">
-        <v>2.262135713778455</v>
+        <v>2.242718534697032</v>
       </c>
       <c r="I10" t="n">
-        <v>2.327383003167734</v>
+        <v>2.319405916913061</v>
       </c>
       <c r="J10" t="n">
-        <v>2.204567330425618</v>
+        <v>2.202971913174683</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1228156727421159</v>
+        <v>0.1164340037383775</v>
       </c>
       <c r="L10" t="n">
         <v>0.2137816411175577</v>
       </c>
       <c r="M10" t="n">
-        <v>837303</v>
+        <v>908525</v>
       </c>
       <c r="N10" t="n">
-        <v>3925000.06</v>
+        <v>3926424.5</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2133256018345131</v>
+        <v>0.2313873601797258</v>
       </c>
       <c r="P10" t="n">
         <v>0.0098826338563442</v>
@@ -5640,7 +5640,7 @@
         <v>1.499500070299421</v>
       </c>
       <c r="S10" t="n">
-        <v>0.08925596061882821</v>
+        <v>0.0897904192691477</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -5655,46 +5655,46 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>275.6900024414062</v>
+        <v>273.7200012207031</v>
       </c>
       <c r="C11" t="n">
-        <v>301.0010012817383</v>
+        <v>300.9616012573242</v>
       </c>
       <c r="D11" t="n">
-        <v>276.0431508636474</v>
+        <v>276.033300857544</v>
       </c>
       <c r="E11" t="n">
-        <v>61.30708019557833</v>
+        <v>59.84774036913862</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.06517242881568799</v>
+        <v>-0.07185243694101499</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0833250126636533</v>
+        <v>-0.089875307661835</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0443989891521958</v>
+        <v>0.0369360152854949</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.650841970358101</v>
+        <v>-6.807993064887171</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.53215855540177</v>
+        <v>-12.56358877430759</v>
       </c>
       <c r="K11" t="n">
-        <v>5.88131658504367</v>
+        <v>5.755595709420415</v>
       </c>
       <c r="L11" t="n">
         <v>5.61249043240821</v>
       </c>
       <c r="M11" t="n">
-        <v>336438</v>
+        <v>399178</v>
       </c>
       <c r="N11" t="n">
-        <v>1552436.76</v>
+        <v>1553691.56</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2167160741542863</v>
+        <v>0.2569222941521288</v>
       </c>
       <c r="P11" t="n">
         <v>-0.0092015237095138</v>
@@ -5708,7 +5708,7 @@
         <v>11.86785343715123</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0430478194060503</v>
+        <v>0.0433576405970496</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -5723,46 +5723,46 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104.1699981689453</v>
+        <v>101.9199981689453</v>
       </c>
       <c r="C12" t="n">
-        <v>112.2591996765137</v>
+        <v>112.2141996765137</v>
       </c>
       <c r="D12" t="n">
-        <v>101.2264999198914</v>
+        <v>101.2152499198914</v>
       </c>
       <c r="E12" t="n">
-        <v>64.48132547579638</v>
+        <v>61.78305163129135</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1763974543067779</v>
+        <v>0.1509880819470179</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1380223460139111</v>
+        <v>-0.1566404678873824</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0032533150926736</v>
+        <v>-0.0247823549358371</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6122429288111704</v>
+        <v>0.4327557493239879</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7782763461041938</v>
+        <v>-0.8141737820016303</v>
       </c>
       <c r="K12" t="n">
-        <v>1.390519274915364</v>
+        <v>1.246929531325618</v>
       </c>
       <c r="L12" t="n">
         <v>1.911196160245703</v>
       </c>
       <c r="M12" t="n">
-        <v>604624</v>
+        <v>684406</v>
       </c>
       <c r="N12" t="n">
-        <v>1510060.48</v>
+        <v>1511656.12</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4003972079316982</v>
+        <v>0.4527524421361122</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -5773,10 +5773,10 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>5.971429007393973</v>
+        <v>6.059286390032087</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0573238851143049</v>
+        <v>0.0594513981445334</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -5791,46 +5791,46 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>239.5500030517578</v>
+        <v>238.5599975585937</v>
       </c>
       <c r="C13" t="n">
-        <v>227.432200012207</v>
+        <v>227.4123999023437</v>
       </c>
       <c r="D13" t="n">
-        <v>161.8389002227783</v>
+        <v>161.8339501953125</v>
       </c>
       <c r="E13" t="n">
-        <v>41.52500238076169</v>
+        <v>41.22109092680138</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0448945202202532</v>
+        <v>-0.0488417531966132</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5016925566439006</v>
+        <v>0.4954864040194742</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5348881387191731</v>
+        <v>0.5285447963298346</v>
       </c>
       <c r="I13" t="n">
-        <v>5.445121350340799</v>
+        <v>5.366146553165322</v>
       </c>
       <c r="J13" t="n">
-        <v>10.05841328246807</v>
+        <v>10.04261832303297</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.613291932127268</v>
+        <v>-4.676471769867648</v>
       </c>
       <c r="L13" t="n">
         <v>-4.078359216969876</v>
       </c>
       <c r="M13" t="n">
-        <v>2433879</v>
+        <v>2671652</v>
       </c>
       <c r="N13" t="n">
-        <v>8665079.58</v>
+        <v>8669835.039999999</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2808836292303273</v>
+        <v>0.3081548827254273</v>
       </c>
       <c r="P13" t="n">
         <v>0.06596166699561611</v>
@@ -5844,7 +5844,7 @@
         <v>26.78535788399833</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1118153101346903</v>
+        <v>0.1122793350021705</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -5859,46 +5859,46 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>357.8800048828125</v>
+        <v>357.9649963378906</v>
       </c>
       <c r="C14" t="n">
-        <v>372.2588006591797</v>
+        <v>372.2605004882813</v>
       </c>
       <c r="D14" t="n">
-        <v>319.9689998626709</v>
+        <v>319.9694248199463</v>
       </c>
       <c r="E14" t="n">
-        <v>59.6517272255997</v>
+        <v>59.70798614779127</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0050044145618943</v>
+        <v>-0.0047681171397168</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0750052595176644</v>
+        <v>0.07526055810930531</v>
       </c>
       <c r="H14" t="n">
-        <v>0.07840661929664459</v>
+        <v>0.07866272566327411</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.059439729048336</v>
+        <v>-2.052659783913896</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.652930116164876</v>
+        <v>-2.651574127137988</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5934903871165398</v>
+        <v>0.5989143432240915</v>
       </c>
       <c r="L14" t="n">
         <v>0.5974640052565006</v>
       </c>
       <c r="M14" t="n">
-        <v>8986096</v>
+        <v>9886711</v>
       </c>
       <c r="N14" t="n">
-        <v>31771191.92</v>
+        <v>31789204.22</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2828378621307953</v>
+        <v>0.3110084458729493</v>
       </c>
       <c r="P14" t="n">
         <v>-0.0040282924977889</v>
@@ -5912,7 +5912,7 @@
         <v>9.963572910853795</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0278405408933543</v>
+        <v>0.0278339307272629</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -5927,46 +5927,46 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>107.2350006103516</v>
+        <v>108.60009765625</v>
       </c>
       <c r="C15" t="n">
-        <v>117.425899810791</v>
+        <v>117.453201751709</v>
       </c>
       <c r="D15" t="n">
-        <v>63.21417497634888</v>
+        <v>63.22100046157837</v>
       </c>
       <c r="E15" t="n">
-        <v>31.20732330339128</v>
+        <v>32.58833144019887</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1391586989398773</v>
+        <v>-0.1282002253969481</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6805359395468837</v>
+        <v>0.7019290913494134</v>
       </c>
       <c r="H15" t="n">
-        <v>1.433840155877911</v>
+        <v>1.464822838659349</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.020832221128785</v>
+        <v>-1.911935590686724</v>
       </c>
       <c r="J15" t="n">
-        <v>1.405811622502004</v>
+        <v>1.427590948590416</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.426643843630789</v>
+        <v>-3.33952653927714</v>
       </c>
       <c r="L15" t="n">
         <v>-3.642499733942029</v>
       </c>
       <c r="M15" t="n">
-        <v>59418384</v>
+        <v>66719056</v>
       </c>
       <c r="N15" t="n">
-        <v>130021127.68</v>
+        <v>130167141.12</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4569902219755921</v>
+        <v>0.5125645030376157</v>
       </c>
       <c r="P15" t="n">
         <v>0.0469355722360184</v>
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>9.479286193847656</v>
+        <v>9.541407448904854</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0883973156142511</v>
+        <v>0.08785818479745849</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -5995,46 +5995,46 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>39.63980102539063</v>
+        <v>39.27999877929688</v>
       </c>
       <c r="C16" t="n">
-        <v>54.90819618225098</v>
+        <v>54.9010001373291</v>
       </c>
       <c r="D16" t="n">
-        <v>48.69084904670715</v>
+        <v>48.68905003547668</v>
       </c>
       <c r="E16" t="n">
-        <v>18.46150735910098</v>
+        <v>17.4324740918985</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3147830238383966</v>
+        <v>-0.3210025961043269</v>
       </c>
       <c r="G16" t="n">
-        <v>0.108495606430752</v>
+        <v>0.09843402189546729</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2219862525650001</v>
+        <v>-0.2290481218624677</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.148315934260552</v>
+        <v>-4.177018107738107</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.733237318555573</v>
+        <v>-2.738977753251084</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.415078615704978</v>
+        <v>-1.438040354487022</v>
       </c>
       <c r="L16" t="n">
         <v>-1.449196603544823</v>
       </c>
       <c r="M16" t="n">
-        <v>10396538</v>
+        <v>11303490</v>
       </c>
       <c r="N16" t="n">
-        <v>28837536.76</v>
+        <v>28855675.8</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3605210142088432</v>
+        <v>0.3917250137666157</v>
       </c>
       <c r="P16" t="n">
         <v>0.0298353862022756</v>
@@ -6048,7 +6048,7 @@
         <v>3.701071330479213</v>
       </c>
       <c r="S16" t="n">
-        <v>0.09336755570767249</v>
+        <v>0.0942227964739632</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -6063,46 +6063,46 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7.864999771118164</v>
+        <v>7.880000114440918</v>
       </c>
       <c r="C17" t="n">
-        <v>8.698099946975708</v>
+        <v>8.698399953842163</v>
       </c>
       <c r="D17" t="n">
-        <v>8.190874967575073</v>
+        <v>8.190949969291687</v>
       </c>
       <c r="E17" t="n">
-        <v>44.85895772680138</v>
+        <v>45.00907288667684</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0235878990514166</v>
+        <v>-0.0217256591067309</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1597222158542044</v>
+        <v>-0.1581196150130758</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0443499139027877</v>
+        <v>-0.0425272718423876</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0358748162572233</v>
+        <v>0.0370714248413754</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1078293141493861</v>
+        <v>0.1080686358662165</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.07195449789216279</v>
+        <v>-0.07099721102484099</v>
       </c>
       <c r="L17" t="n">
         <v>-0.0068890358413925</v>
       </c>
       <c r="M17" t="n">
-        <v>690879</v>
+        <v>769079</v>
       </c>
       <c r="N17" t="n">
-        <v>1051539.58</v>
+        <v>1053103.58</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6570166384036633</v>
+        <v>0.7302975838331116</v>
       </c>
       <c r="P17" t="n">
         <v>0.018661516252568</v>
@@ -6116,7 +6116,7 @@
         <v>0.6941427503313337</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0882571863358932</v>
+        <v>0.08808918023481301</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -6131,46 +6131,46 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1155.849975585938</v>
+        <v>1154.025024414062</v>
       </c>
       <c r="C18" t="n">
-        <v>1097.792601318359</v>
+        <v>1097.756102294922</v>
       </c>
       <c r="D18" t="n">
-        <v>1000.57205291748</v>
+        <v>1000.562928161621</v>
       </c>
       <c r="E18" t="n">
-        <v>57.75332742343394</v>
+        <v>57.42014603587688</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0201676748331309</v>
+        <v>0.0185569500565423</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2529539030741869</v>
+        <v>0.2509756362212059</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0692414205235314</v>
+        <v>0.0675532140740633</v>
       </c>
       <c r="I18" t="n">
-        <v>27.72976943344656</v>
+        <v>27.58418928298352</v>
       </c>
       <c r="J18" t="n">
-        <v>34.63284672952766</v>
+        <v>34.60373069943505</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.903077296081101</v>
+        <v>-7.019541416451538</v>
       </c>
       <c r="L18" t="n">
         <v>-3.468572913063639</v>
       </c>
       <c r="M18" t="n">
-        <v>1334876</v>
+        <v>1460632</v>
       </c>
       <c r="N18" t="n">
-        <v>3186597.52</v>
+        <v>3189112.64</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4189032319337272</v>
+        <v>0.4580057730416195</v>
       </c>
       <c r="P18" t="n">
         <v>-0.013419399271567</v>
@@ -6184,7 +6184,7 @@
         <v>41.49965122767857</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0359040118564185</v>
+        <v>0.0359607897140266</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -6199,46 +6199,46 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15.15999984741211</v>
+        <v>14.89999961853027</v>
       </c>
       <c r="C19" t="n">
-        <v>27.45660003662109</v>
+        <v>27.45140003204345</v>
       </c>
       <c r="D19" t="n">
-        <v>19.02142503261566</v>
+        <v>19.02012503147125</v>
       </c>
       <c r="E19" t="n">
-        <v>24.12867906119573</v>
+        <v>23.53454946433199</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.430503404602872</v>
+        <v>-0.4402705053047864</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.359526835718298</v>
+        <v>-0.3705112137514115</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2104167059891738</v>
+        <v>-0.2239583840386715</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.402571659552361</v>
+        <v>-3.423312418551486</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.19354469411321</v>
+        <v>-3.197692845913036</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2090269654391505</v>
+        <v>-0.2256195726384504</v>
       </c>
       <c r="L19" t="n">
         <v>-0.2400474448421516</v>
       </c>
       <c r="M19" t="n">
-        <v>5138471</v>
+        <v>5881585</v>
       </c>
       <c r="N19" t="n">
-        <v>14269417.42</v>
+        <v>14284279.7</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3601037693941117</v>
+        <v>0.4117522985775755</v>
       </c>
       <c r="P19" t="n">
         <v>0.0323432829789085</v>
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>1.624493053981236</v>
+        <v>1.634500162942069</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1071565349823236</v>
+        <v>0.1096980003213782</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -6267,46 +6267,46 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>223.8800048828125</v>
+        <v>223.5269927978516</v>
       </c>
       <c r="C20" t="n">
-        <v>233.8634002685547</v>
+        <v>233.8563400268554</v>
       </c>
       <c r="D20" t="n">
-        <v>128.1986502075195</v>
+        <v>128.1968851470947</v>
       </c>
       <c r="E20" t="n">
-        <v>33.99490134302415</v>
+        <v>33.85940682526719</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1995709863712887</v>
+        <v>-0.2008330960228952</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6728685781939674</v>
+        <v>0.6702308132673362</v>
       </c>
       <c r="H20" t="n">
-        <v>1.700929020766422</v>
+        <v>1.696670218889714</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.914435658781912</v>
+        <v>-4.94259616698389</v>
       </c>
       <c r="J20" t="n">
-        <v>4.141511170689828</v>
+        <v>4.135879069049432</v>
       </c>
       <c r="K20" t="n">
-        <v>-9.05594682947174</v>
+        <v>-9.078475236033322</v>
       </c>
       <c r="L20" t="n">
         <v>-9.60956168128553</v>
       </c>
       <c r="M20" t="n">
-        <v>12736127</v>
+        <v>13591278</v>
       </c>
       <c r="N20" t="n">
-        <v>45228716.54</v>
+        <v>45245819.56</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2815938185806411</v>
+        <v>0.300387486229015</v>
       </c>
       <c r="P20" t="n">
         <v>0.0645198535414377</v>
@@ -6320,7 +6320,7 @@
         <v>21.60285949707031</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0964930276304848</v>
+        <v>0.0966454173013772</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -6335,46 +6335,46 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>986.25</v>
+        <v>981.2349853515624</v>
       </c>
       <c r="C21" t="n">
-        <v>916.8000012207032</v>
+        <v>916.6997009277344</v>
       </c>
       <c r="D21" t="n">
-        <v>472.4592002868652</v>
+        <v>472.434125213623</v>
       </c>
       <c r="E21" t="n">
-        <v>45.05837714358105</v>
+        <v>44.63958636842999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0047269432031864</v>
+        <v>-0.0003820254536893</v>
       </c>
       <c r="G21" t="n">
-        <v>1.117961586229852</v>
+        <v>1.107191894590034</v>
       </c>
       <c r="H21" t="n">
-        <v>1.85150494094129</v>
+        <v>1.837005230879021</v>
       </c>
       <c r="I21" t="n">
-        <v>9.695062622779121</v>
+        <v>9.29500447418593</v>
       </c>
       <c r="J21" t="n">
-        <v>34.46583081666105</v>
+        <v>34.38581918694242</v>
       </c>
       <c r="K21" t="n">
-        <v>-24.77076819388193</v>
+        <v>-25.09081471275649</v>
       </c>
       <c r="L21" t="n">
         <v>-28.83193491040208</v>
       </c>
       <c r="M21" t="n">
-        <v>21605059</v>
+        <v>23027783</v>
       </c>
       <c r="N21" t="n">
-        <v>53943405.18</v>
+        <v>53971859.66</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4005134441903988</v>
+        <v>0.4266627673210695</v>
       </c>
       <c r="P21" t="n">
         <v>0.0543756800501934</v>
@@ -6388,7 +6388,7 @@
         <v>89.7650146484375</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0910164914052598</v>
+        <v>0.0914816695169872</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -6403,46 +6403,46 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>195.3800048828125</v>
+        <v>195.4440002441407</v>
       </c>
       <c r="C22" t="n">
-        <v>224.0142001342773</v>
+        <v>224.0154800415039</v>
       </c>
       <c r="D22" t="n">
-        <v>136.7453754806519</v>
+        <v>136.7456954574585</v>
       </c>
       <c r="E22" t="n">
-        <v>30.14073385754547</v>
+        <v>30.15032897033954</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1591495766500338</v>
+        <v>-0.1588741619437159</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2064962451356369</v>
+        <v>0.2068914245870592</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8203671065836278</v>
+        <v>0.8209633551649784</v>
       </c>
       <c r="I22" t="n">
-        <v>-6.550153263509827</v>
+        <v>-6.54504822044089</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4622407321877673</v>
+        <v>0.4632617408015549</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.012393995697595</v>
+        <v>-7.008309961242444</v>
       </c>
       <c r="L22" t="n">
         <v>-6.66147091221397</v>
       </c>
       <c r="M22" t="n">
-        <v>12379640</v>
+        <v>13321356</v>
       </c>
       <c r="N22" t="n">
-        <v>17944850.8</v>
+        <v>17963685.12</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6898714365460202</v>
+        <v>0.7415714487874523</v>
       </c>
       <c r="P22" t="n">
         <v>0.0310198990532244</v>
@@ -6456,7 +6456,7 @@
         <v>25.56014360700335</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1308227196653728</v>
+        <v>0.1307798836243356</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -6471,46 +6471,46 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>211.35009765625</v>
+        <v>212.1750030517578</v>
       </c>
       <c r="C23" t="n">
-        <v>209.320202331543</v>
+        <v>209.3367004394531</v>
       </c>
       <c r="D23" t="n">
-        <v>191.9678509521484</v>
+        <v>191.971975479126</v>
       </c>
       <c r="E23" t="n">
-        <v>60.39721038718096</v>
+        <v>60.98887129446162</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0300214198623192</v>
+        <v>0.0340416225315178</v>
       </c>
       <c r="G23" t="n">
-        <v>0.07551831237213651</v>
+        <v>0.0797160906967351</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1428035842230031</v>
+        <v>0.1472639788624439</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6225466697114541</v>
+        <v>-0.5567422506966011</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.265847865214832</v>
+        <v>-2.252686981411861</v>
       </c>
       <c r="K23" t="n">
-        <v>1.643301195503378</v>
+        <v>1.69594473071526</v>
       </c>
       <c r="L23" t="n">
         <v>1.206196025562167</v>
       </c>
       <c r="M23" t="n">
-        <v>73116753</v>
+        <v>82485174</v>
       </c>
       <c r="N23" t="n">
-        <v>157849099.06</v>
+        <v>158036467.48</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4632066539208285</v>
+        <v>0.5219375965261863</v>
       </c>
       <c r="P23" t="n">
         <v>0.0229450115312453</v>
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>6.875713893345424</v>
+        <v>6.948570251464844</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0325323431102852</v>
+        <v>0.0327492407282766</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -6539,46 +6539,46 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>91.4268035888672</v>
+        <v>91.27999877929688</v>
       </c>
       <c r="C24" t="n">
-        <v>106.6351354980469</v>
+        <v>106.6321994018555</v>
       </c>
       <c r="D24" t="n">
-        <v>104.448833694458</v>
+        <v>104.4480996704102</v>
       </c>
       <c r="E24" t="n">
-        <v>16.79596631516891</v>
+        <v>16.32886286692583</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0944254712961031</v>
+        <v>-0.0958795601521012</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2122453428218479</v>
+        <v>-0.2135102472907299</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.167257465830507</v>
+        <v>-0.1685946077227206</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.127140878999612</v>
+        <v>-4.138851803979577</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.345876792426679</v>
+        <v>-3.348218977422672</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7812640865729326</v>
+        <v>-0.7906328265569047</v>
       </c>
       <c r="L24" t="n">
         <v>-0.7934742332941171</v>
       </c>
       <c r="M24" t="n">
-        <v>2660564</v>
+        <v>2855528</v>
       </c>
       <c r="N24" t="n">
-        <v>3256929.28</v>
+        <v>3260828.56</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8168933898374361</v>
+        <v>0.8757062652812388</v>
       </c>
       <c r="P24" t="n">
         <v>0.0177384274683925</v>
@@ -6592,7 +6592,7 @@
         <v>4.48357173374721</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0490400140631533</v>
+        <v>0.049118884681275</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -6607,46 +6607,46 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25.82500076293945</v>
+        <v>25.68000030517578</v>
       </c>
       <c r="C25" t="n">
-        <v>35.87990009307861</v>
+        <v>35.87700008392334</v>
       </c>
       <c r="D25" t="n">
-        <v>25.36987498760224</v>
+        <v>25.36914998531342</v>
       </c>
       <c r="E25" t="n">
-        <v>41.73541298197256</v>
+        <v>41.36886831176119</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1709469958523892</v>
+        <v>-0.1756019062709888</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2388741370273424</v>
+        <v>-0.2431476547538232</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0151336564779713</v>
+        <v>0.009433953069178</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.439698190356467</v>
+        <v>-2.451265178440178</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.394731266312632</v>
+        <v>-2.397044663929374</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0449669240438348</v>
+        <v>-0.0542205145108036</v>
       </c>
       <c r="L25" t="n">
         <v>-0.0149246408257801</v>
       </c>
       <c r="M25" t="n">
-        <v>2999847</v>
+        <v>3296129</v>
       </c>
       <c r="N25" t="n">
-        <v>13308550.94</v>
+        <v>13314476.58</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2254074852720216</v>
+        <v>0.2475597880393733</v>
       </c>
       <c r="P25" t="n">
         <v>0.0084746235925221</v>
@@ -6660,7 +6660,7 @@
         <v>2.376357078552246</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0920176963542426</v>
+        <v>0.09253726831433461</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -6675,46 +6675,46 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13.71000003814697</v>
+        <v>13.68000030517578</v>
       </c>
       <c r="C26" t="n">
-        <v>11.47240003585815</v>
+        <v>11.47180004119873</v>
       </c>
       <c r="D26" t="n">
-        <v>9.128275010585783</v>
+        <v>9.128125011920927</v>
       </c>
       <c r="E26" t="n">
-        <v>75.11415241761875</v>
+        <v>74.94252742525934</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2079294781813607</v>
+        <v>0.2052863299907961</v>
       </c>
       <c r="G26" t="n">
-        <v>0.559726973566079</v>
+        <v>0.556314034646695</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5979021165567866</v>
+        <v>0.5944056441514309</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6778215903978122</v>
+        <v>0.6754284493060911</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6463457043468233</v>
+        <v>0.645867076128479</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0314758860509889</v>
+        <v>0.029561373177612</v>
       </c>
       <c r="L26" t="n">
         <v>0.042571941463545</v>
       </c>
       <c r="M26" t="n">
-        <v>161489</v>
+        <v>178131</v>
       </c>
       <c r="N26" t="n">
-        <v>663371.78</v>
+        <v>663704.62</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2434366442298766</v>
+        <v>0.2683889709853157</v>
       </c>
       <c r="P26" t="n">
         <v>-0.0110537672736636</v>
@@ -6728,7 +6728,7 @@
         <v>0.6038284982953753</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0440429246254756</v>
+        <v>0.0441395091246393</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -6743,46 +6743,46 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>79.83499908447266</v>
+        <v>79.03959655761719</v>
       </c>
       <c r="C27" t="n">
-        <v>107.0348999023438</v>
+        <v>107.0189918518066</v>
       </c>
       <c r="D27" t="n">
-        <v>77.06872510910034</v>
+        <v>77.06474809646606</v>
       </c>
       <c r="E27" t="n">
-        <v>38.09486287767558</v>
+        <v>37.31820954520452</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2202851883936634</v>
+        <v>-0.2280535498703397</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1054416745369226</v>
+        <v>0.09442807008647761</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.09175201708081659</v>
+        <v>-0.1008009648970609</v>
       </c>
       <c r="I27" t="n">
-        <v>-7.626536389669752</v>
+        <v>-7.689987303492998</v>
       </c>
       <c r="J27" t="n">
-        <v>-6.246567320914774</v>
+        <v>-6.259257503679423</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.379969068754979</v>
+        <v>-1.430729799813575</v>
       </c>
       <c r="L27" t="n">
         <v>-1.60128212643402</v>
       </c>
       <c r="M27" t="n">
-        <v>10804127</v>
+        <v>11543412</v>
       </c>
       <c r="N27" t="n">
-        <v>28182374.54</v>
+        <v>28197160.24</v>
       </c>
       <c r="O27" t="n">
-        <v>0.383364680100515</v>
+        <v>0.4093820761292379</v>
       </c>
       <c r="P27" t="n">
         <v>0.0264563885114627</v>
@@ -6796,7 +6796,7 @@
         <v>7.732856750488281</v>
       </c>
       <c r="S27" t="n">
-        <v>0.09686048524039211</v>
+        <v>0.09783522547273241</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -6811,46 +6811,46 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18.68510055541992</v>
+        <v>18.56500053405762</v>
       </c>
       <c r="C28" t="n">
-        <v>16.94930194854736</v>
+        <v>16.94689994812012</v>
       </c>
       <c r="D28" t="n">
-        <v>21.97360052585602</v>
+        <v>21.97300002574921</v>
       </c>
       <c r="E28" t="n">
-        <v>62.9293039995192</v>
+        <v>62.08528783568838</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1269662630519072</v>
+        <v>0.1197225946613795</v>
       </c>
       <c r="G28" t="n">
-        <v>0.043277538504268</v>
+        <v>0.0365717862772707</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2975526207722739</v>
+        <v>-0.3020676591046031</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4144654045170419</v>
+        <v>0.4048847760322971</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3735355718519468</v>
+        <v>0.3716194461549978</v>
       </c>
       <c r="K28" t="n">
-        <v>0.040929832665095</v>
+        <v>0.0332653298772992</v>
       </c>
       <c r="L28" t="n">
         <v>0.0328078631428616</v>
       </c>
       <c r="M28" t="n">
-        <v>60227164</v>
+        <v>67826209</v>
       </c>
       <c r="N28" t="n">
-        <v>76398621.28</v>
+        <v>76550602.18000001</v>
       </c>
       <c r="O28" t="n">
-        <v>0.7883278911443727</v>
+        <v>0.8860310313498829</v>
       </c>
       <c r="P28" t="n">
         <v>0.0044125718372439</v>
@@ -6864,7 +6864,7 @@
         <v>0.9414285932268416</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0503839190179666</v>
+        <v>0.050709860821161</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -6879,46 +6879,46 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6.409999847412109</v>
+        <v>6.440000057220459</v>
       </c>
       <c r="C29" t="n">
-        <v>5.93439998626709</v>
+        <v>5.934999990463257</v>
       </c>
       <c r="D29" t="n">
-        <v>4.497000005245209</v>
+        <v>4.497150006294251</v>
       </c>
       <c r="E29" t="n">
-        <v>62.49999561730699</v>
+        <v>62.89926016459427</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2975708042843141</v>
+        <v>0.303643721179224</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0545723231484529</v>
+        <v>-0.0501475135791332</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3965140815514099</v>
+        <v>0.4030500747564287</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3307068762252978</v>
+        <v>0.3331000553553087</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3108915948112808</v>
+        <v>0.311370230637283</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0198152814140169</v>
+        <v>0.0217298247180257</v>
       </c>
       <c r="L29" t="n">
         <v>0.0646032293833483</v>
       </c>
       <c r="M29" t="n">
-        <v>323507</v>
+        <v>379921</v>
       </c>
       <c r="N29" t="n">
-        <v>1212602.14</v>
+        <v>1213730.42</v>
       </c>
       <c r="O29" t="n">
-        <v>0.2667874229547377</v>
+        <v>0.313019261723703</v>
       </c>
       <c r="P29" t="n">
         <v>0.0046656626141934</v>
@@ -6932,7 +6932,7 @@
         <v>0.6430713449205671</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1003231451214764</v>
+        <v>0.0998557980134739</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -6947,46 +6947,46 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>396.5599975585938</v>
+        <v>396.0499877929688</v>
       </c>
       <c r="C30" t="n">
-        <v>409.93419921875</v>
+        <v>409.9239990234375</v>
       </c>
       <c r="D30" t="n">
-        <v>417.7533000183105</v>
+        <v>417.7507499694824</v>
       </c>
       <c r="E30" t="n">
-        <v>54.42177423372955</v>
+        <v>54.28385236539413</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0242846130823347</v>
+        <v>-0.0255394657625399</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0888522357686449</v>
+        <v>0.0874518795123824</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1167141725182596</v>
+        <v>-0.1178501529515541</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.265021321956397</v>
+        <v>-1.305705861664421</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.245076258528362</v>
+        <v>-1.253213166469967</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.0199450634280342</v>
+        <v>-0.0524926951944539</v>
       </c>
       <c r="L30" t="n">
         <v>0.3816312784934397</v>
       </c>
       <c r="M30" t="n">
-        <v>16141667</v>
+        <v>17352925</v>
       </c>
       <c r="N30" t="n">
-        <v>48292123.34</v>
+        <v>48316348.5</v>
       </c>
       <c r="O30" t="n">
-        <v>0.3342505129947347</v>
+        <v>0.3591522442967725</v>
       </c>
       <c r="P30" t="n">
         <v>0.0109940121352903</v>
@@ -7000,7 +7000,7 @@
         <v>18.56714085170201</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0468205087906241</v>
+        <v>0.0468808014745042</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -7015,46 +7015,46 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>423.5700073242188</v>
+        <v>422.989990234375</v>
       </c>
       <c r="C31" t="n">
-        <v>425.0568005371094</v>
+        <v>425.0452001953125</v>
       </c>
       <c r="D31" t="n">
-        <v>349.7391500854492</v>
+        <v>349.73625</v>
       </c>
       <c r="E31" t="n">
-        <v>45.99874957947848</v>
+        <v>45.80252323519223</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0008491622621233</v>
+        <v>-0.0022173530008412</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1149806285806278</v>
+        <v>0.1134538259075421</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2766977766236833</v>
+        <v>0.2749495260011116</v>
       </c>
       <c r="I31" t="n">
-        <v>1.421810505819167</v>
+        <v>1.375541336259005</v>
       </c>
       <c r="J31" t="n">
-        <v>5.425742639538226</v>
+        <v>5.416488805626193</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.003932133719059</v>
+        <v>-4.040947469367188</v>
       </c>
       <c r="L31" t="n">
         <v>-3.711786865119478</v>
       </c>
       <c r="M31" t="n">
-        <v>9744913</v>
+        <v>10328172</v>
       </c>
       <c r="N31" t="n">
-        <v>13670302.26</v>
+        <v>13681967.44</v>
       </c>
       <c r="O31" t="n">
-        <v>0.7128527822324831</v>
+        <v>0.7548747682153525</v>
       </c>
       <c r="P31" t="n">
         <v>0.0220361706931489</v>
@@ -7068,7 +7068,7 @@
         <v>19.97285679408482</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0471536143936573</v>
+        <v>0.0472182729029073</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -7083,46 +7083,46 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>304.2199096679688</v>
+        <v>303.2900085449219</v>
       </c>
       <c r="C32" t="n">
-        <v>324.2461993408203</v>
+        <v>324.2276013183593</v>
       </c>
       <c r="D32" t="n">
-        <v>238.4776498413086</v>
+        <v>238.4730003356934</v>
       </c>
       <c r="E32" t="n">
-        <v>45.77031353903932</v>
+        <v>45.51637972582078</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0044570758825381</v>
+        <v>0.001386777939399</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.0202573182822803</v>
+        <v>-0.0232520723765163</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7892131497504371</v>
+        <v>0.7837441082299823</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.907386718750842</v>
+        <v>-1.981566865318655</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.181121195863625</v>
+        <v>-1.195957225177187</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.7262655228872175</v>
+        <v>-0.7856096401414672</v>
       </c>
       <c r="L32" t="n">
         <v>-0.1480541656201379</v>
       </c>
       <c r="M32" t="n">
-        <v>2085999</v>
+        <v>2440399</v>
       </c>
       <c r="N32" t="n">
-        <v>6151217.98</v>
+        <v>6158305.98</v>
       </c>
       <c r="O32" t="n">
-        <v>0.3391196681344074</v>
+        <v>0.3962776464705639</v>
       </c>
       <c r="P32" t="n">
         <v>0.031582057136426</v>
@@ -7136,7 +7136,7 @@
         <v>21.269287109375</v>
       </c>
       <c r="S32" t="n">
-        <v>0.06991418521091761</v>
+        <v>0.07012854532009639</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -7151,46 +7151,46 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>885.8699951171875</v>
+        <v>879.0349731445312</v>
       </c>
       <c r="C33" t="n">
-        <v>877.3403967285157</v>
+        <v>877.2036962890625</v>
       </c>
       <c r="D33" t="n">
-        <v>479.6061998748779</v>
+        <v>479.5720247650146</v>
       </c>
       <c r="E33" t="n">
-        <v>38.53832446966886</v>
+        <v>37.9012279970176</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.0485156212151715</v>
+        <v>-0.0558568977811231</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6606740984230792</v>
+        <v>0.6478609949037064</v>
       </c>
       <c r="H33" t="n">
-        <v>1.75559899478435</v>
+        <v>1.734337884484876</v>
       </c>
       <c r="I33" t="n">
-        <v>-3.401698892994773</v>
+        <v>-3.946942811041367</v>
       </c>
       <c r="J33" t="n">
-        <v>11.35144491550308</v>
+        <v>11.24239613189376</v>
       </c>
       <c r="K33" t="n">
-        <v>-14.75314380849785</v>
+        <v>-15.18933894293512</v>
       </c>
       <c r="L33" t="n">
         <v>-17.58862389405815</v>
       </c>
       <c r="M33" t="n">
-        <v>2274980</v>
+        <v>2621790</v>
       </c>
       <c r="N33" t="n">
-        <v>4344743.6</v>
+        <v>4351679.8</v>
       </c>
       <c r="O33" t="n">
-        <v>0.5236166295290705</v>
+        <v>0.6024776914882387</v>
       </c>
       <c r="P33" t="n">
         <v>0.0451049293978258</v>
@@ -7204,7 +7204,7 @@
         <v>84.29928588867188</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0951598839031909</v>
+        <v>0.0958998088404969</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -7219,46 +7219,46 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27.9099006652832</v>
+        <v>27.78499984741211</v>
       </c>
       <c r="C34" t="n">
-        <v>33.45859783172607</v>
+        <v>33.45609981536865</v>
       </c>
       <c r="D34" t="n">
-        <v>34.37799940109253</v>
+        <v>34.37737489700317</v>
       </c>
       <c r="E34" t="n">
-        <v>28.16730183888978</v>
+        <v>27.43579240581289</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0837195829230801</v>
+        <v>-0.0878200695161596</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0260992603835144</v>
+        <v>0.0215073186788188</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.0733764977546542</v>
+        <v>-0.07752327114080911</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.875875419156433</v>
+        <v>-1.885839017163246</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.846775925286824</v>
+        <v>-1.848768644888187</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.0290994938696083</v>
+        <v>-0.0370703722750587</v>
       </c>
       <c r="L34" t="n">
         <v>-0.1129581202809464</v>
       </c>
       <c r="M34" t="n">
-        <v>12339217</v>
+        <v>14089718</v>
       </c>
       <c r="N34" t="n">
-        <v>55538788.34</v>
+        <v>55573798.36</v>
       </c>
       <c r="O34" t="n">
-        <v>0.2221729599943951</v>
+        <v>0.2535316716832742</v>
       </c>
       <c r="P34" t="n">
         <v>0.0112075006381963</v>
@@ -7272,7 +7272,7 @@
         <v>1.774999754769462</v>
       </c>
       <c r="S34" t="n">
-        <v>0.0635974945255668</v>
+        <v>0.0638833818433432</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -7287,46 +7287,46 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>268.3349914550781</v>
+        <v>266.9100036621094</v>
       </c>
       <c r="C35" t="n">
-        <v>226.1058996582032</v>
+        <v>226.0773999023438</v>
       </c>
       <c r="D35" t="n">
-        <v>160.4410251617432</v>
+        <v>160.4339002227783</v>
       </c>
       <c r="E35" t="n">
-        <v>75.86785464606048</v>
+        <v>75.48954865203949</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1671813770290904</v>
+        <v>0.1609830828542311</v>
       </c>
       <c r="G35" t="n">
-        <v>1.42683360943917</v>
+        <v>1.413945956396737</v>
       </c>
       <c r="H35" t="n">
-        <v>1.120052082658344</v>
+        <v>1.108793586992669</v>
       </c>
       <c r="I35" t="n">
-        <v>12.10253051973308</v>
+        <v>11.98885627983813</v>
       </c>
       <c r="J35" t="n">
-        <v>11.57962540398115</v>
+        <v>11.55689055600216</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5229051157519322</v>
+        <v>0.4319657238359742</v>
       </c>
       <c r="L35" t="n">
         <v>0.3955764881293149</v>
       </c>
       <c r="M35" t="n">
-        <v>2337097</v>
+        <v>2503750</v>
       </c>
       <c r="N35" t="n">
-        <v>6067037.94</v>
+        <v>6070371</v>
       </c>
       <c r="O35" t="n">
-        <v>0.3852121946677656</v>
+        <v>0.4124541976099978</v>
       </c>
       <c r="P35" t="n">
         <v>-0.0192129762097973</v>
@@ -7340,7 +7340,7 @@
         <v>13.84728785923549</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0516044805940028</v>
+        <v>0.0518799882703731</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>183.5726013183593</v>
+        <v>186.8500061035156</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
@@ -7364,19 +7364,19 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.3484005790833748</v>
+        <v>0.6098459750502627</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.1153911092545536</v>
+        <v>-0.063102030061176</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4637916883379285</v>
+        <v>0.6729480051114388</v>
       </c>
       <c r="L36" t="n">
         <v>-0.9253561253561428</v>
       </c>
       <c r="M36" t="n">
-        <v>50647413</v>
+        <v>55688004</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -7403,46 +7403,46 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8.591699600219727</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="C37" t="n">
-        <v>10.93883401870728</v>
+        <v>10.93900003433228</v>
       </c>
       <c r="D37" t="n">
-        <v>18.45040847301483</v>
+        <v>18.45044997692108</v>
       </c>
       <c r="E37" t="n">
-        <v>21.15368988899225</v>
+        <v>21.31980309769909</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.1312740847354546</v>
+        <v>-0.1304347742236401</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.161785404856612</v>
+        <v>-0.1609755725395388</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.5643154209239054</v>
+        <v>-0.5638944887971797</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6467560727610557</v>
+        <v>-0.6460939021770091</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5319650238712723</v>
+        <v>-0.531832589754463</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.1147910488897834</v>
+        <v>-0.1142613124225461</v>
       </c>
       <c r="L37" t="n">
         <v>-0.1257283657885731</v>
       </c>
       <c r="M37" t="n">
-        <v>16755941</v>
+        <v>17874401</v>
       </c>
       <c r="N37" t="n">
-        <v>33070034.82</v>
+        <v>33092404.02</v>
       </c>
       <c r="O37" t="n">
-        <v>0.5066804764858122</v>
+        <v>0.5401360683617086</v>
       </c>
       <c r="P37" t="n">
         <v>0.0299401183926648</v>
@@ -7456,7 +7456,7 @@
         <v>0.6735711097717285</v>
       </c>
       <c r="S37" t="n">
-        <v>0.078397888789606</v>
+        <v>0.0783222185923457</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -7471,46 +7471,46 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>46.31999969482422</v>
+        <v>45.97499847412109</v>
       </c>
       <c r="C38" t="n">
-        <v>60.63099983215332</v>
+        <v>60.62409980773926</v>
       </c>
       <c r="D38" t="n">
-        <v>81.45979980468751</v>
+        <v>81.45807479858398</v>
       </c>
       <c r="E38" t="n">
-        <v>24.87285661301692</v>
+        <v>23.65514622294652</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.194294688772402</v>
+        <v>-0.2002957534902754</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.2092864758111212</v>
+        <v>-0.2151758785069101</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.5480975639529344</v>
+        <v>-0.5514634295207699</v>
       </c>
       <c r="I38" t="n">
-        <v>-3.793483988618938</v>
+        <v>-3.821005453518332</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.474027080529751</v>
+        <v>-3.47953137350963</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.3194569080891871</v>
+        <v>-0.3414740800087021</v>
       </c>
       <c r="L38" t="n">
         <v>-0.3462640816307631</v>
       </c>
       <c r="M38" t="n">
-        <v>3997980</v>
+        <v>4294000</v>
       </c>
       <c r="N38" t="n">
-        <v>12379679.6</v>
+        <v>12385600</v>
       </c>
       <c r="O38" t="n">
-        <v>0.3229469686759906</v>
+        <v>0.3466929337294923</v>
       </c>
       <c r="P38" t="n">
         <v>0.0251036384349932</v>
@@ -7524,7 +7524,7 @@
         <v>3.443371636526925</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0743387663906156</v>
+        <v>0.07489661230690781</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -7539,46 +7539,46 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7.760000228881836</v>
+        <v>7.704999923706055</v>
       </c>
       <c r="C39" t="n">
-        <v>9.766199998855591</v>
+        <v>9.765099992752075</v>
       </c>
       <c r="D39" t="n">
-        <v>12.02985001564026</v>
+        <v>12.02957501411438</v>
       </c>
       <c r="E39" t="n">
-        <v>27.1099796021057</v>
+        <v>26.07003852546879</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.1519125079342579</v>
+        <v>-0.1579234704991521</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.1181818112854131</v>
+        <v>-0.1244318458290133</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.4964308691940047</v>
+        <v>-0.5</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5911012733821774</v>
+        <v>-0.5954887621141474</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.4877790227225852</v>
+        <v>-0.4886565204689792</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.1033222506595922</v>
+        <v>-0.1068322416451681</v>
       </c>
       <c r="L39" t="n">
         <v>-0.1257187896488844</v>
       </c>
       <c r="M39" t="n">
-        <v>33985118</v>
+        <v>38220902</v>
       </c>
       <c r="N39" t="n">
-        <v>37317912.36</v>
+        <v>37402628.04</v>
       </c>
       <c r="O39" t="n">
-        <v>0.9106918327089401</v>
+        <v>1.021877445593526</v>
       </c>
       <c r="P39" t="n">
         <v>0.0100267124430337</v>
@@ -7592,7 +7592,7 @@
         <v>0.5577142919812884</v>
       </c>
       <c r="S39" t="n">
-        <v>0.0718703963313737</v>
+        <v>0.07238342602254449</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -7607,46 +7607,46 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>6.775000095367432</v>
+        <v>6.769999980926514</v>
       </c>
       <c r="C40" t="n">
-        <v>7.67870002746582</v>
+        <v>7.678600025177002</v>
       </c>
       <c r="D40" t="n">
-        <v>10.25850001335144</v>
+        <v>10.25847501277924</v>
       </c>
       <c r="E40" t="n">
-        <v>57.17344823713204</v>
+        <v>57.08154365904792</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.0181159417785984</v>
+        <v>-0.0188405960353824</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0279770015342937</v>
+        <v>-0.0286943780897355</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.414433857038199</v>
+        <v>-0.4148660190583203</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.238703839041741</v>
+        <v>-0.2391027085697912</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.3059814826504435</v>
+        <v>-0.3060612565560535</v>
       </c>
       <c r="K40" t="n">
-        <v>0.06727764360870241</v>
+        <v>0.0669585479862623</v>
       </c>
       <c r="L40" t="n">
         <v>0.0561779742976243</v>
       </c>
       <c r="M40" t="n">
-        <v>22121772</v>
+        <v>25917857</v>
       </c>
       <c r="N40" t="n">
-        <v>28686703.44</v>
+        <v>28762625.14</v>
       </c>
       <c r="O40" t="n">
-        <v>0.7711507195753267</v>
+        <v>0.9010949756444936</v>
       </c>
       <c r="P40" t="n">
         <v>-0.0154083063419491</v>
@@ -7660,7 +7660,7 @@
         <v>0.4056429181780134</v>
       </c>
       <c r="S40" t="n">
-        <v>0.0598734926152077</v>
+        <v>0.0599177133413372</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -458,15 +458,15 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -538,13 +538,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>368.364990234375</v>
+        <v>983.1199951171876</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.082723417254077</v>
+        <v>0.0548345836529482</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.3098805794520953</v>
+        <v>0.5614175632723557</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>75</v>
@@ -558,19 +558,19 @@
         <v>12</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.0325763856993166</v>
+        <v>0.0122060379807142</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>275.5091465541295</v>
+        <v>803.5899658203126</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>507.6487557547433</v>
+        <v>1252.4150390625</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -579,13 +579,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>238.5599975585937</v>
+        <v>361.7799987792969</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.06596166699561611</v>
+        <v>0.0828062753684488</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.3081548827254273</v>
+        <v>0.5222684036760127</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>75</v>
@@ -599,19 +599,19 @@
         <v>12</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.0503018113799763</v>
+        <v>0.033169329538642</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>184.989281790597</v>
+        <v>268.7313014439174</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>318.9160712105887</v>
+        <v>501.3530447823661</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>981.2349853515624</v>
+        <v>236.1799926757812</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.0543756800501934</v>
+        <v>0.06596166699561611</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.4266627673210695</v>
+        <v>0.4711035474840427</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>75</v>
@@ -640,13 +640,13 @@
         <v>12</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.0122294864931875</v>
+        <v>0.0508087068004661</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>801.7049560546874</v>
+        <v>182.3964189801897</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1250.530029296875</v>
+        <v>316.8553532191685</v>
       </c>
     </row>
   </sheetData>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>181.9600067138672</v>
+        <v>182.5700073242188</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>89</v>
@@ -896,28 +896,28 @@
         <v>75</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>62.13461920486363</v>
+        <v>62.41619801793815</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.0151807899125376</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.3998422937932429</v>
+        <v>0.5532368110555725</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1.565438762376488</v>
+        <v>1.604367574336539</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>161.0355965750558</v>
+        <v>161.6455971854074</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>213.3466219220843</v>
+        <v>213.9566225324358</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>10.46220506940569</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0.053341</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>212.1750030517578</v>
+        <v>211.8000030517578</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>89</v>
@@ -990,22 +990,22 @@
         <v>75</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>60.98887129446162</v>
+        <v>60.72211027619969</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.0229450115312453</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.5219375965261863</v>
+        <v>0.7433680375253153</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1.69594473071526</v>
+        <v>1.672013119512536</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>201.7521476745605</v>
+        <v>201.3771476745605</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>226.0721435546875</v>
+        <v>225.6971435546875</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>6.948570251464844</v>
@@ -1014,7 +1014,7 @@
         <v>13.95</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.065756</v>
+        <v>0.065872</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>1.12</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>553.489990234375</v>
+        <v>548.1300048828125</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>82</v>
@@ -1084,28 +1084,28 @@
         <v>50</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>55.58990122403013</v>
+        <v>54.78446864042778</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.0624019610194614</v>
+        <v>0.061434448913282</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.4730084692137635</v>
+        <v>0.6129772245272506</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>-2.717278682641592</v>
+        <v>-3.059340407885674</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>496.412837437221</v>
+        <v>491.0528520856585</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>629.5928606305804</v>
+        <v>624.2328752790179</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>38.05143519810268</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>10.82</v>
+        <v>10.72</v>
       </c>
       <c r="R4" s="2" t="n">
         <v>0.019555</v>
@@ -1144,12 +1144,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BFLY</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7.619999885559082</v>
+        <v>983.1199951171876</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>82</v>
@@ -1178,31 +1178,31 @@
         <v>50</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>49.52198674958101</v>
+        <v>44.79774534214121</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.0049382666628676</v>
+        <v>0.0548345836529482</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.532959655238795</v>
+        <v>0.5614175632723557</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-0.1264124005895605</v>
+        <v>-24.97051779036101</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>6.142785753522601</v>
+        <v>803.5899658203126</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>9.835821083613803</v>
+        <v>1252.4150390625</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.7386070660182408</v>
+        <v>89.7650146484375</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>5.76</v>
+        <v>6.11</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.755569</v>
+        <v>0.006217</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>1.12</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1154.025024414062</v>
+        <v>1152.5400390625</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>82</v>
@@ -1272,22 +1272,22 @@
         <v>50</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>57.42014603587688</v>
+        <v>57.15185573112131</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>-0.013419399271567</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.4580057730416195</v>
+        <v>0.6295299805039047</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-7.019541416451538</v>
+        <v>-7.114309765361639</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1091.775547572545</v>
+        <v>1090.290562220982</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1237.02432686942</v>
+        <v>1235.539341517857</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>41.49965122767857</v>
@@ -1296,7 +1296,7 @@
         <v>13.95</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.01209</v>
+        <v>0.012105</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>1.12</v>
@@ -1332,12 +1332,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>BFLY</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>368.364990234375</v>
+        <v>7.75</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>82</v>
@@ -1366,31 +1366,31 @@
         <v>50</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>45.92279579419217</v>
+        <v>50.78431291884531</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.082723417254077</v>
+        <v>-0.0049382666628676</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.3098805794520953</v>
+        <v>0.7423618671893375</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-11.28628974945518</v>
+        <v>-0.1181160971051057</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>275.5091465541295</v>
+        <v>6.272785867963519</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>507.6487557547433</v>
+        <v>9.965821198054725</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46.42792184012277</v>
+        <v>0.7386070660182408</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>4.43</v>
+        <v>5.86</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.01202</v>
+        <v>0.755569</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>1.12</v>
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>393.6900024414063</v>
+        <v>389.1099853515625</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>79</v>
@@ -1460,22 +1460,22 @@
         <v>75</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>55.52202604846918</v>
+        <v>53.7959635185359</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.030087289573326</v>
+        <v>0.030386704331899</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.4014549875260613</v>
+        <v>0.617956632747811</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>3.27231196562413</v>
+        <v>2.98002598495759</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>371.1846531459264</v>
+        <v>366.6046360560826</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>423.6971348353795</v>
+        <v>419.1171177455357</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>15.00356619698661</v>
@@ -1484,7 +1484,7 @@
         <v>6.98</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.017719</v>
+        <v>0.017928</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>1.12</v>
@@ -1520,21 +1520,21 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>BLZE</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Cloud Software</t>
+          <t>Gaming/Digital Media</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>266.9100036621094</v>
+        <v>16.54999923706055</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>79</v>
@@ -1554,31 +1554,31 @@
         <v>75</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>75.48954865203949</v>
+        <v>73.76093226909819</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>-0.0192129762097973</v>
+        <v>0.0129709127575936</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.4124541976099978</v>
+        <v>0.4283640919771998</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.4319657238359742</v>
+        <v>0.1068612566533073</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>246.1390718732561</v>
+        <v>13.5509990964617</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>294.6045793805803</v>
+        <v>21.04849944795881</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>13.84728785923549</v>
+        <v>1.499500070299421</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>6.98</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.026136</v>
+        <v>0</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>1.12</v>
@@ -1586,11 +1586,25 @@
       <c r="T9" s="3" t="n">
         <v>13.95</v>
       </c>
-      <c r="U9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="n">
+        <v>0.0982696803861781</v>
+      </c>
       <c r="V9" s="3" t="inlineStr"/>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr"/>
-      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>No exit trigger</t>
+        </is>
+      </c>
       <c r="Z9" s="3" t="n">
         <v>4</v>
       </c>
@@ -1599,11 +1613,19 @@
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
-        </is>
-      </c>
-      <c r="AC9" s="3" t="inlineStr"/>
-      <c r="AD9" s="3" t="inlineStr"/>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr">
+        <is>
+          <t>Held, but not strong enough to add</t>
+        </is>
+      </c>
       <c r="AE9" s="3" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
@@ -1632,7 +1654,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>13.68000030517578</v>
+        <v>13.6899995803833</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>79</v>
@@ -1652,28 +1674,28 @@
         <v>75</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>74.94252742525934</v>
+        <v>74.99999453168354</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>-0.0110537672736636</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.2683889709853157</v>
+        <v>0.5429485849005998</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.029561373177612</v>
+        <v>0.0301995026588746</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>12.47234330858503</v>
+        <v>12.48234258379255</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>15.49148580006191</v>
+        <v>15.50148507526943</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.6038284982953753</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>6.32</v>
+        <v>6.33</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>0.462108</v>
@@ -1716,21 +1738,21 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>BLZE</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Gaming/Digital Media</t>
+          <t>Cloud Software</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>16.70000076293945</v>
+        <v>270.7300109863281</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>79</v>
@@ -1750,31 +1772,31 @@
         <v>75</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>74.13793418441759</v>
+        <v>76.47804213242863</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.0098826338563442</v>
+        <v>-0.0178872721149254</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.2313873601797258</v>
+        <v>0.5887063417673052</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.1164340037383775</v>
+        <v>0.6757496704129959</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>13.70100062234061</v>
+        <v>249.8390797206334</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>21.19850097383772</v>
+        <v>298.5845860072545</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>1.499500070299421</v>
+        <v>13.92728751046317</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0</v>
+        <v>0.025767</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>1.12</v>
@@ -1782,25 +1804,11 @@
       <c r="T11" s="3" t="n">
         <v>13.95</v>
       </c>
-      <c r="U11" s="3" t="n">
-        <v>0.1082238879679861</v>
-      </c>
+      <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>No exit trigger</t>
-        </is>
-      </c>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
       <c r="Z11" s="3" t="n">
         <v>4</v>
       </c>
@@ -1809,19 +1817,11 @@
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>Already held</t>
-        </is>
-      </c>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>Held, but not strong enough to add</t>
-        </is>
-      </c>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AD11" s="3" t="inlineStr"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>6.440000057220459</v>
+        <v>6.289999961853027</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>78</v>
@@ -1870,28 +1870,28 @@
         <v>75</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>62.89926016459427</v>
+        <v>60.71428368691744</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0.0046656626141934</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.313019261723703</v>
+        <v>0.606299066718476</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.0217298247180257</v>
+        <v>0.0121571690035722</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>5.153857367379325</v>
+        <v>5.003857272011893</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>8.36921409198216</v>
+        <v>8.219213996614728</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.6430713449205671</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.433909</v>
@@ -1930,7 +1930,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>981.2349853515624</v>
+        <v>236.1799926757812</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>75</v>
@@ -1964,31 +1964,31 @@
         <v>50</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>44.63958636842999</v>
+        <v>40.54773982640063</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.0543756800501934</v>
+        <v>0.06596166699561611</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.4266627673210695</v>
+        <v>0.4711035474840427</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-25.09081471275649</v>
+        <v>-4.82835811389501</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>801.7049560546874</v>
+        <v>182.3964189801897</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1250.530029296875</v>
+        <v>316.8553532191685</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>89.7650146484375</v>
+        <v>26.89178684779576</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>0.003108</v>
+        <v>0.010376</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>1.12</v>
@@ -2024,7 +2024,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>238.5599975585937</v>
+        <v>361.7799987792969</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>75</v>
@@ -2058,31 +2058,31 @@
         <v>50</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>41.22109092680138</v>
+        <v>44.89807856597774</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.06596166699561611</v>
+        <v>0.0828062753684488</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.3081548827254273</v>
+        <v>0.5222684036760127</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>-4.676471769867648</v>
+        <v>-11.70652851646093</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>184.989281790597</v>
+        <v>268.7313014439174</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>318.9160712105887</v>
+        <v>501.3530447823661</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>26.78535788399833</v>
+        <v>46.52434866768973</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>2.49</v>
+        <v>2.17</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.010417</v>
+        <v>0.005998</v>
       </c>
       <c r="S14" s="3" t="n">
         <v>1.12</v>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>357.9649963378906</v>
+        <v>359.510009765625</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>71</v>
@@ -2152,25 +2152,25 @@
         <v>75</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>59.70798614779127</v>
+        <v>60.70401435938903</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.0040282924977889</v>
+        <v>-0.0037303974496513</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3110084458729493</v>
+        <v>0.5684630349666104</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5989143432240915</v>
+        <v>0.6975134915938646</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>343.0196369716099</v>
+        <v>344.4660775320871</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>377.8921421595982</v>
+        <v>379.5685860770089</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>9.963572910853795</v>
+        <v>10.02928815569196</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>13.95</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.0241405701982828</v>
+        <v>-0.0199286613858312</v>
       </c>
       <c r="V15" s="4" t="inlineStr"/>
       <c r="W15" s="4" t="inlineStr">
@@ -2238,24 +2238,24 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Internet/E-Commerce</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>18.56500053405762</v>
+        <v>247.4900054931641</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
@@ -2266,31 +2266,31 @@
         <v>40</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>75</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>62.08528783568838</v>
+        <v>66.88540664531003</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.0044125718372439</v>
+        <v>-0.0071165521984971</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8860310313498829</v>
+        <v>0.5759421788162938</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0332653298772992</v>
+        <v>1.741369739733408</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>16.68214334760393</v>
+        <v>236.1392958504813</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>21.38928631373814</v>
+        <v>262.6242850167411</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.9414285932268416</v>
+        <v>7.567139761788504</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
@@ -2304,25 +2304,11 @@
       <c r="T16" s="4" t="n">
         <v>13.95</v>
       </c>
-      <c r="U16" s="4" t="n">
-        <v>0.0090427009329377</v>
-      </c>
+      <c r="U16" s="4" t="inlineStr"/>
       <c r="V16" s="4" t="inlineStr"/>
-      <c r="W16" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="Y16" s="4" t="inlineStr">
-        <is>
-          <t>No exit trigger</t>
-        </is>
-      </c>
+      <c r="W16" s="4" t="inlineStr"/>
+      <c r="X16" s="4" t="inlineStr"/>
+      <c r="Y16" s="4" t="inlineStr"/>
       <c r="Z16" s="4" t="n">
         <v>4</v>
       </c>
@@ -2331,19 +2317,11 @@
       </c>
       <c r="AB16" s="4" t="inlineStr">
         <is>
-          <t>Already held</t>
-        </is>
-      </c>
-      <c r="AC16" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="AD16" s="4" t="inlineStr">
-        <is>
-          <t>Held, but not strong enough to add</t>
-        </is>
-      </c>
+          <t>6 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AC16" s="4" t="inlineStr"/>
+      <c r="AD16" s="4" t="inlineStr"/>
       <c r="AE16" s="4" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
@@ -2354,24 +2332,24 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>CELC</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>422.989990234375</v>
+        <v>111.0500030517578</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
@@ -2382,31 +2360,31 @@
         <v>40</v>
       </c>
       <c r="H17" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="I17" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="I17" s="4" t="n">
-        <v>50</v>
-      </c>
       <c r="J17" s="4" t="n">
-        <v>45.80252323519223</v>
+        <v>68.91793789745947</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.0220361706931489</v>
+        <v>0</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.7548747682153525</v>
+        <v>1.339588038518872</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-4.040947469367188</v>
+        <v>1.829585113648181</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>393.0307050432477</v>
+        <v>97.80785914829798</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>462.9357038225447</v>
+        <v>130.9132189069475</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>19.97285679408482</v>
+        <v>6.621071951729911</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
@@ -2440,7 +2418,7 @@
       <c r="AD17" s="4" t="inlineStr"/>
       <c r="AE17" s="4" t="inlineStr">
         <is>
-          <t>Positive momentum</t>
+          <t>MACD/volume acceleration</t>
         </is>
       </c>
       <c r="AF17" s="4" t="inlineStr"/>
@@ -2448,24 +2426,24 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Data Storage</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>879.0349731445312</v>
+        <v>18.54999923706055</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
@@ -2473,34 +2451,34 @@
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H18" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="I18" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="I18" s="4" t="n">
-        <v>50</v>
-      </c>
       <c r="J18" s="4" t="n">
-        <v>37.9012279970176</v>
+        <v>61.97715680636227</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.0451049293978258</v>
+        <v>0.0044125718372439</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.6024776914882387</v>
+        <v>1.151572395702875</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-15.18933894293512</v>
+        <v>0.0323079814383454</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>752.5860443115234</v>
+        <v>16.66714205060686</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1047.633544921875</v>
+        <v>21.37428501674108</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>84.29928588867188</v>
+        <v>0.9414285932268416</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
@@ -2514,11 +2492,25 @@
       <c r="T18" s="4" t="n">
         <v>13.95</v>
       </c>
-      <c r="U18" s="4" t="inlineStr"/>
+      <c r="U18" s="4" t="n">
+        <v>0.0082273522227855</v>
+      </c>
       <c r="V18" s="4" t="inlineStr"/>
-      <c r="W18" s="4" t="inlineStr"/>
-      <c r="X18" s="4" t="inlineStr"/>
-      <c r="Y18" s="4" t="inlineStr"/>
+      <c r="W18" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X18" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Y18" s="4" t="inlineStr">
+        <is>
+          <t>No exit trigger</t>
+        </is>
+      </c>
       <c r="Z18" s="4" t="n">
         <v>4</v>
       </c>
@@ -2527,14 +2519,22 @@
       </c>
       <c r="AB18" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
-        </is>
-      </c>
-      <c r="AC18" s="4" t="inlineStr"/>
-      <c r="AD18" s="4" t="inlineStr"/>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AC18" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AD18" s="4" t="inlineStr">
+        <is>
+          <t>Held, but not strong enough to add</t>
+        </is>
+      </c>
       <c r="AE18" s="4" t="inlineStr">
         <is>
-          <t>Strong trend; Positive momentum</t>
+          <t>MACD/volume acceleration</t>
         </is>
       </c>
       <c r="AF18" s="4" t="inlineStr"/>
@@ -2542,12 +2542,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Data Centers</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>303.2900085449219</v>
+        <v>420.3900146484375</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
@@ -2570,31 +2570,31 @@
         <v>40</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>50</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>45.51637972582078</v>
+        <v>44.9811782697946</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.031582057136426</v>
+        <v>0.0220361706931489</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3962776464705639</v>
+        <v>1.029289744141061</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.7856096401414672</v>
+        <v>-4.206871821347955</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>271.3860778808594</v>
+        <v>390.4307294573102</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>345.8285827636719</v>
+        <v>460.3357282366072</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>21.269287109375</v>
+        <v>19.97285679408482</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
@@ -2626,18 +2626,22 @@
       </c>
       <c r="AC19" s="4" t="inlineStr"/>
       <c r="AD19" s="4" t="inlineStr"/>
-      <c r="AE19" s="4" t="inlineStr"/>
+      <c r="AE19" s="4" t="inlineStr">
+        <is>
+          <t>Positive momentum</t>
+        </is>
+      </c>
       <c r="AF19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Internet/E-Commerce</t>
+          <t>Data Storage</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2646,10 +2650,10 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>246.4450073242188</v>
+        <v>878.3099975585938</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
@@ -2657,34 +2661,34 @@
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>65.30207701967382</v>
+        <v>37.83287697052316</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.0071974396379796</v>
+        <v>0.0470279063556459</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3574128495100627</v>
+        <v>0.8371986766170606</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.674680396630441</v>
+        <v>-15.2356051912122</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>235.1992972237724</v>
+        <v>751.8610687255859</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>261.4392874581473</v>
+        <v>1046.908569335938</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>7.497140066964286</v>
+        <v>84.29928588867188</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
@@ -2718,7 +2722,7 @@
       <c r="AD20" s="4" t="inlineStr"/>
       <c r="AE20" s="4" t="inlineStr">
         <is>
-          <t>MACD/volume acceleration</t>
+          <t>Strong trend; Positive momentum</t>
         </is>
       </c>
       <c r="AF20" s="4" t="inlineStr"/>
@@ -2726,24 +2730,24 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>CELC</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Data Centers</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>101.9199981689453</v>
+        <v>303.5799865722656</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
@@ -2754,31 +2758,31 @@
         <v>40</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>61.78305163129135</v>
+        <v>45.59526295678533</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>0.031582057136426</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.4527524421361122</v>
+        <v>0.503724278424144</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.246929531325618</v>
+        <v>-0.767103914790201</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>89.80142538888116</v>
+        <v>271.6760559082031</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>120.0978573390416</v>
+        <v>346.1185607910156</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>6.059286390032087</v>
+        <v>21.269287109375</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
@@ -2810,11 +2814,7 @@
       </c>
       <c r="AC21" s="4" t="inlineStr"/>
       <c r="AD21" s="4" t="inlineStr"/>
-      <c r="AE21" s="4" t="inlineStr">
-        <is>
-          <t>MACD/volume acceleration</t>
-        </is>
-      </c>
+      <c r="AE21" s="4" t="inlineStr"/>
       <c r="AF21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>284.3847045898437</v>
+        <v>281.1700134277344</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>55</v>
@@ -2854,22 +2854,22 @@
         <v>50</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>28.62054776079645</v>
+        <v>28.14872105545106</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.0376936349020097</v>
+        <v>0.0369410809341018</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.5898495564600381</v>
+        <v>0.7404378179758314</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-9.895611529021703</v>
+        <v>-10.10076560394868</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>225.6221313476562</v>
+        <v>222.4074401855469</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>372.5285644531249</v>
+        <v>369.3138732910156</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>29.38128662109375</v>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>223.5269927978516</v>
+        <v>222.4400024414062</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>55</v>
@@ -2948,22 +2948,22 @@
         <v>50</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>33.85940682526719</v>
+        <v>33.43867797240382</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>0.0645198535414377</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.300387486229015</v>
+        <v>0.4410012102813088</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-9.078475236033322</v>
+        <v>-9.147844421365978</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>191.1227035522461</v>
+        <v>190.0357131958008</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>266.7327117919922</v>
+        <v>265.6457214355469</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>21.60285949707031</v>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>195.4440002441407</v>
+        <v>194.0899963378907</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>55</v>
@@ -3042,22 +3042,22 @@
         <v>50</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>30.15032897033954</v>
+        <v>29.94861110189596</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>0.0310198990532244</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.7415714487874523</v>
+        <v>0.9630161260402392</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-7.008309961242444</v>
+        <v>-7.094719324305856</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>144.3237130301339</v>
+        <v>142.9697091238839</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>272.1244310651507</v>
+        <v>270.7704271589007</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>25.56014360700335</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>108.60009765625</v>
+        <v>107.7600021362305</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>55</v>
@@ -3136,25 +3136,25 @@
         <v>50</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>32.58833144019887</v>
+        <v>31.74508778177839</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.0469355722360184</v>
+        <v>0.0471295624603021</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.5125645030376157</v>
+        <v>0.6930888135448485</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.33952653927714</v>
+        <v>-3.393139473478043</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>94.28798648289272</v>
+        <v>93.41143008640836</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>127.6829125540597</v>
+        <v>126.8914315359933</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>9.541407448904854</v>
+        <v>9.565714699881417</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>25.68000030517578</v>
+        <v>25.55999946594238</v>
       </c>
       <c r="E26" s="4" t="n">
         <v>54</v>
@@ -3230,22 +3230,22 @@
         <v>50</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>41.36886831176119</v>
+        <v>41.0703537322088</v>
       </c>
       <c r="K26" s="4" t="n">
         <v>0.0084746235925221</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.2475597880393733</v>
+        <v>0.3954853718663363</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.0542205145108036</v>
+        <v>-0.0618786872852585</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>20.92728614807129</v>
+        <v>20.80728530883789</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>32.80907154083252</v>
+        <v>32.68907070159912</v>
       </c>
       <c r="P26" s="4" t="n">
         <v>2.376357078552246</v>
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>273.7200012207031</v>
+        <v>274.9800109863281</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>51</v>
@@ -3320,22 +3320,22 @@
         <v>75</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>59.84774036913862</v>
+        <v>60.77300060323681</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>-0.0092015237095138</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.2569222941521288</v>
+        <v>0.5141545369292413</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.755595709420415</v>
+        <v>5.836006585191056</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>255.9182210649763</v>
+        <v>257.1782308306013</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>297.4557080950056</v>
+        <v>298.7157178606306</v>
       </c>
       <c r="P27" s="4" t="n">
         <v>11.86785343715123</v>
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>396.0499877929688</v>
+        <v>396.1799926757813</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>43</v>
@@ -3414,22 +3414,22 @@
         <v>50</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>54.28385236539413</v>
+        <v>54.31908877476581</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.0109940121352903</v>
+        <v>0.0108673065184357</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.3591522442967725</v>
+        <v>0.4681728500583489</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.0524926951944539</v>
+        <v>-0.0441960990382355</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>368.1992765154158</v>
+        <v>368.3292813982283</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>433.1842694963729</v>
+        <v>433.3142743791853</v>
       </c>
       <c r="P28" s="4" t="n">
         <v>18.56714085170201</v>
@@ -3447,7 +3447,7 @@
         <v>13.95</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.0420491681648886</v>
+        <v>-0.0417347172383101</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>79.03959655761719</v>
+        <v>78.80999755859375</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>43</v>
@@ -3534,22 +3534,22 @@
         <v>50</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>37.31820954520452</v>
+        <v>37.0903849686533</v>
       </c>
       <c r="K29" s="4" t="n">
         <v>0.0264563885114627</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.4093820761292379</v>
+        <v>0.5506274104002613</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.430729799813575</v>
+        <v>-1.445382268877453</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>63.57388305664063</v>
+        <v>63.34428405761719</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>102.238166809082</v>
+        <v>102.0085678100586</v>
       </c>
       <c r="P29" s="4" t="n">
         <v>7.732856750488281</v>
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6.769999980926514</v>
+        <v>6.690000057220459</v>
       </c>
       <c r="E30" s="4" t="n">
         <v>39</v>
@@ -3624,22 +3624,22 @@
         <v>75</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>57.08154365904792</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.0154083063419491</v>
+        <v>-0.0130970052862066</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.9010949756444936</v>
+        <v>1.124438604401397</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.0669585479862623</v>
+        <v>0.0618531394617651</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.958714144570487</v>
+        <v>5.878714220864432</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.986928735460554</v>
+        <v>7.906928811754499</v>
       </c>
       <c r="P30" s="4" t="n">
         <v>0.4056429181780134</v>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>27.78499984741211</v>
+        <v>27.64999961853028</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>33</v>
@@ -3718,22 +3718,22 @@
         <v>50</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>27.43579240581289</v>
+        <v>26.66666562011045</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.0112075006381963</v>
+        <v>0.0108459594618766</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.2535316716832742</v>
+        <v>0.3915780978295909</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.0370703722750587</v>
+        <v>-0.0456857648926987</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>24.23500033787318</v>
+        <v>24.10000010899135</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>33.1099991117205</v>
+        <v>32.97499888283866</v>
       </c>
       <c r="P31" s="4" t="n">
         <v>1.774999754769462</v>
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>39.27999877929688</v>
+        <v>39.29000091552734</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>33</v>
@@ -3808,22 +3808,22 @@
         <v>50</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>17.4324740918985</v>
+        <v>17.46143102526288</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>0.0298353862022756</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.3917250137666157</v>
+        <v>0.4783985469704708</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.438040354487022</v>
+        <v>-1.437402043324314</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>31.87785611833846</v>
+        <v>31.88785825456892</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>50.38321277073453</v>
+        <v>50.39321490696499</v>
       </c>
       <c r="P32" s="4" t="n">
         <v>3.701071330479213</v>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>69.53610229492188</v>
+        <v>68.81999969482422</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>32</v>
@@ -3898,22 +3898,22 @@
         <v>50</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>46.9804959194845</v>
+        <v>46.28371831749488</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.0334417645102432</v>
+        <v>0.0325539640224045</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.3131508734816722</v>
+        <v>0.3938147053188749</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.7553702867516128</v>
+        <v>-0.8010702754847339</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>55.62553078787667</v>
+        <v>54.90942818777901</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>90.40195955548968</v>
+        <v>89.68585695539201</v>
       </c>
       <c r="P33" s="4" t="n">
         <v>6.955285753522601</v>
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>7.880000114440918</v>
+        <v>7.940000057220459</v>
       </c>
       <c r="E34" s="4" t="n">
         <v>32</v>
@@ -3988,25 +3988,25 @@
         <v>50</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>45.00907288667684</v>
+        <v>45.60143417545741</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.018661516252568</v>
+        <v>0.0167310315006482</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.7302975838331116</v>
+        <v>1.233258246517002</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.07099721102484099</v>
+        <v>-0.0671681559513998</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.49171461377825</v>
+        <v>6.538857460021973</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>9.962428365434921</v>
+        <v>10.04171395301819</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.6941427503313337</v>
+        <v>0.7005712985992432</v>
       </c>
       <c r="Q34" s="4" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>186.8500061035156</v>
+        <v>193.9199981689453</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>29</v>
@@ -4083,13 +4083,13 @@
       </c>
       <c r="L35" s="4" t="inlineStr"/>
       <c r="M35" s="4" t="n">
-        <v>0.6729480051114388</v>
+        <v>1.1241383819366</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>171.9020056152343</v>
+        <v>178.4063983154297</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>214.8775070190429</v>
+        <v>223.0079978942871</v>
       </c>
       <c r="P35" s="4" t="inlineStr"/>
       <c r="Q35" s="4" t="n">
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>14.89999961853027</v>
+        <v>14.90999984741211</v>
       </c>
       <c r="E36" s="4" t="n">
         <v>22</v>
@@ -4170,25 +4170,25 @@
         <v>50</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>23.53454946433199</v>
+        <v>23.55515812624178</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>0.0323432829789085</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.4117522985775755</v>
+        <v>0.7211097549224948</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>-0.2256195726384504</v>
+        <v>-0.2249813813743664</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>11.63099929264613</v>
+        <v>11.62385668073382</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>19.80350010735648</v>
+        <v>19.83921459742955</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>1.634500162942069</v>
+        <v>1.643071583339146</v>
       </c>
       <c r="Q36" s="4" t="n">
         <v>0</v>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>91.27999877929688</v>
+        <v>91.56999969482422</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>22</v>
@@ -4260,22 +4260,22 @@
         <v>50</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>16.32886286692583</v>
+        <v>17.24659021688664</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>0.0177384274683925</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>0.8757062652812388</v>
+        <v>1.140096641520877</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>-0.7906328265569047</v>
+        <v>-0.7721256443558535</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>84.55464117867606</v>
+        <v>84.84464209420341</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>100.2471422467913</v>
+        <v>100.5371431623186</v>
       </c>
       <c r="P37" s="4" t="n">
         <v>4.48357173374721</v>
@@ -4356,10 +4356,10 @@
         <v>0.0299401183926648</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.5401360683617086</v>
+        <v>0.6631252334389868</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-0.1142613124225461</v>
+        <v>-0.1142613107714314</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>7.252858161926269</v>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>45.97499847412109</v>
+        <v>46.2400016784668</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>22</v>
@@ -4440,22 +4440,22 @@
         <v>50</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>23.65514622294652</v>
+        <v>24.59396920131374</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>0.0251036384349932</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>0.3466929337294923</v>
+        <v>0.4949668589162981</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>-0.3414740800087021</v>
+        <v>-0.3245621974062178</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>39.08825520106723</v>
+        <v>39.35325840541294</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>56.30511338370187</v>
+        <v>56.57011658804757</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>3.443371636526925</v>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>7.704999923706055</v>
+        <v>7.889999866485596</v>
       </c>
       <c r="E40" s="4" t="n">
         <v>22</v>
@@ -4530,25 +4530,25 @@
         <v>50</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>26.07003852546879</v>
+        <v>29.45544376243362</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>0.0100267124430337</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>1.021877445593526</v>
+        <v>1.236660633684115</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>-0.1068322416451681</v>
+        <v>-0.0950259749563091</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>6.589571339743478</v>
+        <v>6.760285581861224</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>9.37814279964992</v>
+        <v>9.584571293422156</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>0.5577142919812884</v>
+        <v>0.5648571423121861</v>
       </c>
       <c r="Q40" s="4" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
@@ -4625,17 +4625,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>cost_basis</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>current_price</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>market_value</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>cost_basis</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -4662,19 +4662,19 @@
         <v>15.06915790595363</v>
       </c>
       <c r="D2" t="n">
-        <v>16.70000076293945</v>
+        <v>11.251008816</v>
       </c>
       <c r="E2" t="n">
-        <v>12.46863673362961</v>
+        <v>16.54999923706055</v>
       </c>
       <c r="F2" t="n">
-        <v>11.251008816</v>
+        <v>12.35664185637039</v>
       </c>
       <c r="G2" t="n">
-        <v>1.217627917629608</v>
+        <v>1.105633040370392</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1082238879679861</v>
+        <v>0.0982696803861781</v>
       </c>
     </row>
     <row r="3">
@@ -4687,22 +4687,22 @@
         <v>0.05285969</v>
       </c>
       <c r="C3" t="n">
-        <v>366.8202462424581</v>
+        <v>366.8202462424582</v>
       </c>
       <c r="D3" t="n">
-        <v>357.9649963378906</v>
+        <v>19.39000450210001</v>
       </c>
       <c r="E3" t="n">
-        <v>18.92191873727204</v>
+        <v>359.510009765625</v>
       </c>
       <c r="F3" t="n">
-        <v>19.3900045021</v>
+        <v>19.00358766810791</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4680857648279648</v>
+        <v>-0.3864168339920937</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0241405701982828</v>
+        <v>-0.0199286613858312</v>
       </c>
     </row>
     <row r="4">
@@ -4718,19 +4718,19 @@
         <v>18.39862725025694</v>
       </c>
       <c r="D4" t="n">
-        <v>18.56500053405762</v>
+        <v>11.251008945</v>
       </c>
       <c r="E4" t="n">
-        <v>11.35274845408344</v>
+        <v>18.54999923706055</v>
       </c>
       <c r="F4" t="n">
-        <v>11.251008945</v>
+        <v>11.34357495845223</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1017395090834423</v>
+        <v>0.0925660134522257</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0090427009329377</v>
+        <v>0.0082273522227855</v>
       </c>
     </row>
     <row r="5">
@@ -4746,19 +4746,19 @@
         <v>413.4345674446258</v>
       </c>
       <c r="D5" t="n">
-        <v>396.0499877929688</v>
+        <v>11.2510057355</v>
       </c>
       <c r="E5" t="n">
-        <v>10.77791030330383</v>
+        <v>396.1799926757813</v>
       </c>
       <c r="F5" t="n">
-        <v>11.2510057355</v>
+        <v>10.7814481924823</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4730954321961658</v>
+        <v>-0.4695575430176983</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0420491681648886</v>
+        <v>-0.0417347172383101</v>
       </c>
     </row>
   </sheetData>
@@ -4780,7 +4780,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
@@ -4865,22 +4865,22 @@
         <v>55.81</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>53.52</v>
+        <v>53.49</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>109.33</v>
+        <v>109.29</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-4.55</v>
+        <v>-4.59</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.039971511869609</v>
+        <v>-0.0402872964926867</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>-3.16</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
@@ -5043,49 +5043,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>368.364990234375</v>
+        <v>361.7799987792969</v>
       </c>
       <c r="C2" t="n">
-        <v>331.9430990600586</v>
+        <v>331.811399230957</v>
       </c>
       <c r="D2" t="n">
-        <v>201.2388250350952</v>
+        <v>201.2059000778198</v>
       </c>
       <c r="E2" t="n">
-        <v>45.92279579419217</v>
+        <v>44.89807856597774</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0033092642192258</v>
+        <v>-0.0146261615319583</v>
       </c>
       <c r="G2" t="n">
-        <v>1.159231987429477</v>
+        <v>1.120632976764246</v>
       </c>
       <c r="H2" t="n">
-        <v>1.134582920555269</v>
+        <v>1.096424543226661</v>
       </c>
       <c r="I2" t="n">
-        <v>14.76838452186308</v>
+        <v>14.24308604988727</v>
       </c>
       <c r="J2" t="n">
-        <v>26.05467427131826</v>
+        <v>25.9496145663482</v>
       </c>
       <c r="K2" t="n">
-        <v>-11.28628974945518</v>
+        <v>-11.70652851646093</v>
       </c>
       <c r="L2" t="n">
-        <v>-10.00415359792669</v>
+        <v>-10.00415359369676</v>
       </c>
       <c r="M2" t="n">
-        <v>1897980</v>
+        <v>3212650</v>
       </c>
       <c r="N2" t="n">
-        <v>6124875.6</v>
+        <v>6151339</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3098805794520953</v>
+        <v>0.5222684036760127</v>
       </c>
       <c r="P2" t="n">
-        <v>0.082723417254077</v>
+        <v>0.0828062753684488</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>46.42792184012277</v>
+        <v>46.52434866768973</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1260378240901304</v>
+        <v>0.12859845437744</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -5111,49 +5111,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>553.489990234375</v>
+        <v>548.1300048828125</v>
       </c>
       <c r="C3" t="n">
-        <v>489.8211999511719</v>
+        <v>489.7140002441406</v>
       </c>
       <c r="D3" t="n">
-        <v>291.4942496490478</v>
+        <v>291.46744972229</v>
       </c>
       <c r="E3" t="n">
-        <v>55.58990122403013</v>
+        <v>54.78446864042778</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08194378542522419</v>
+        <v>0.07146626470504359</v>
       </c>
       <c r="G3" t="n">
-        <v>1.169953245544999</v>
+        <v>1.148939464239267</v>
       </c>
       <c r="H3" t="n">
-        <v>1.664981384409807</v>
+        <v>1.63917376108391</v>
       </c>
       <c r="I3" t="n">
-        <v>17.21328114557355</v>
+        <v>16.78570392830397</v>
       </c>
       <c r="J3" t="n">
-        <v>19.93055982821513</v>
+        <v>19.84504433618965</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.717278682641592</v>
+        <v>-3.059340407885674</v>
       </c>
       <c r="L3" t="n">
-        <v>-3.577422784539042</v>
+        <v>-3.577422765110406</v>
       </c>
       <c r="M3" t="n">
-        <v>16031247</v>
+        <v>20834788</v>
       </c>
       <c r="N3" t="n">
-        <v>33892092.94</v>
+        <v>33989497.76</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4730084692137635</v>
+        <v>0.6129772245272506</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0624019610194614</v>
+        <v>0.061434448913282</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>38.05143519810268</v>
       </c>
       <c r="S3" t="n">
-        <v>0.068748190336721</v>
+        <v>0.06942045656894461</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -5179,49 +5179,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>246.4450073242188</v>
+        <v>247.4900054931641</v>
       </c>
       <c r="C4" t="n">
-        <v>253.3476998901367</v>
+        <v>253.3685998535156</v>
       </c>
       <c r="D4" t="n">
-        <v>233.5973750305176</v>
+        <v>233.6026000213623</v>
       </c>
       <c r="E4" t="n">
-        <v>65.30207701967382</v>
+        <v>66.88540664531003</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0330958045334754</v>
+        <v>0.0374764297926526</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0103405224643109</v>
+        <v>-0.0061440798050218</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.00010140745876</v>
+        <v>0.0041384520120466</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7372418105497047</v>
+        <v>-0.6538801359475315</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.411922207180146</v>
+        <v>-2.395249875680939</v>
       </c>
       <c r="K4" t="n">
-        <v>1.674680396630441</v>
+        <v>1.741369739733408</v>
       </c>
       <c r="L4" t="n">
-        <v>1.780135958077288</v>
+        <v>1.780135959445799</v>
       </c>
       <c r="M4" t="n">
-        <v>17429163</v>
+        <v>28210343</v>
       </c>
       <c r="N4" t="n">
-        <v>48764791.26</v>
+        <v>48981206.86</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3574128495100627</v>
+        <v>0.5759421788162938</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0071974396379796</v>
+        <v>-0.0071165521984971</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>7.497140066964286</v>
+        <v>7.567139761788504</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0304211481026319</v>
+        <v>0.0305755367644432</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -5247,46 +5247,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>181.9600067138672</v>
+        <v>182.5700073242188</v>
       </c>
       <c r="C5" t="n">
-        <v>160.7805996704102</v>
+        <v>160.7927996826172</v>
       </c>
       <c r="D5" t="n">
-        <v>144.3300996780396</v>
+        <v>144.3331496810913</v>
       </c>
       <c r="E5" t="n">
-        <v>62.13461920486363</v>
+        <v>62.41619801793815</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1146777786740951</v>
+        <v>0.1184146114958575</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1787265172596215</v>
+        <v>0.1826780663277449</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4743154222445256</v>
+        <v>0.4792579001200847</v>
       </c>
       <c r="I5" t="n">
-        <v>5.962522093571124</v>
+        <v>6.011183115000847</v>
       </c>
       <c r="J5" t="n">
-        <v>4.397083331194636</v>
+        <v>4.406815540664308</v>
       </c>
       <c r="K5" t="n">
-        <v>1.565438762376488</v>
+        <v>1.604367574336539</v>
       </c>
       <c r="L5" t="n">
-        <v>1.773262942271622</v>
+        <v>1.773262940198125</v>
       </c>
       <c r="M5" t="n">
-        <v>4141118</v>
+        <v>5747709</v>
       </c>
       <c r="N5" t="n">
-        <v>10356878.36</v>
+        <v>10389238.18</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3998422937932429</v>
+        <v>0.5532368110555725</v>
       </c>
       <c r="P5" t="n">
         <v>0.0151807899125376</v>
@@ -5300,7 +5300,7 @@
         <v>10.46220506940569</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0574972778818235</v>
+        <v>0.057305168700718</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -5315,49 +5315,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>284.3847045898437</v>
+        <v>281.1700134277344</v>
       </c>
       <c r="C6" t="n">
-        <v>312.6230923461914</v>
+        <v>312.5587985229492</v>
       </c>
       <c r="D6" t="n">
-        <v>182.8275484848022</v>
+        <v>182.8114750289917</v>
       </c>
       <c r="E6" t="n">
-        <v>28.62054776079645</v>
+        <v>28.14872105545106</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2532110332894121</v>
+        <v>-0.261652752736693</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7639542391550633</v>
+        <v>0.7440144603573406</v>
       </c>
       <c r="H6" t="n">
-        <v>1.558797068126773</v>
+        <v>1.529872367930951</v>
       </c>
       <c r="I6" t="n">
-        <v>-7.899164760293331</v>
+        <v>-8.155607370604741</v>
       </c>
       <c r="J6" t="n">
-        <v>1.996446768728372</v>
+        <v>1.945158233343941</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.895611529021703</v>
+        <v>-10.10076560394868</v>
       </c>
       <c r="L6" t="n">
-        <v>-9.368367243321137</v>
+        <v>-9.368367237992228</v>
       </c>
       <c r="M6" t="n">
-        <v>6603092</v>
+        <v>8314663</v>
       </c>
       <c r="N6" t="n">
-        <v>11194535.84</v>
+        <v>11229387.26</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5898495564600381</v>
+        <v>0.7404378179758314</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0376936349020097</v>
+        <v>0.0369410809341018</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>29.38128662109375</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1033152843556377</v>
+        <v>0.1044965153392691</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -5383,49 +5383,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69.53610229492188</v>
+        <v>68.81999969482422</v>
       </c>
       <c r="C7" t="n">
-        <v>86.04392219543458</v>
+        <v>86.02960014343262</v>
       </c>
       <c r="D7" t="n">
-        <v>83.07073036193847</v>
+        <v>83.06714984893799</v>
       </c>
       <c r="E7" t="n">
-        <v>46.9804959194845</v>
+        <v>46.28371831749488</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1562177016757819</v>
+        <v>-0.1649072122725022</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2149023085185201</v>
+        <v>-0.2229874683081221</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2932604662437091</v>
+        <v>-0.3005386713919957</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.783787900593794</v>
+        <v>-4.840912907633864</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.028417613842181</v>
+        <v>-4.039842632149131</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7553702867516128</v>
+        <v>-0.8010702754847339</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7205249641778009</v>
+        <v>-0.7205249574182222</v>
       </c>
       <c r="M7" t="n">
-        <v>7249189</v>
+        <v>9131826</v>
       </c>
       <c r="N7" t="n">
-        <v>23149189.78</v>
+        <v>23188128.52</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3131508734816722</v>
+        <v>0.3938147053188749</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0334417645102432</v>
+        <v>0.0325539640224045</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>6.955285753522601</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1000240957427165</v>
+        <v>0.1010648907928677</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -5451,49 +5451,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>393.6900024414063</v>
+        <v>389.1099853515625</v>
       </c>
       <c r="C8" t="n">
-        <v>405.5476007080078</v>
+        <v>405.456000366211</v>
       </c>
       <c r="D8" t="n">
-        <v>362.9439501953125</v>
+        <v>362.9210501098633</v>
       </c>
       <c r="E8" t="n">
-        <v>55.52202604846918</v>
+        <v>53.7959635185359</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0304132616914023</v>
+        <v>0.0184258850273209</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0339041013275283</v>
+        <v>0.0218761137637739</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1177706822426092</v>
+        <v>0.1047670276020285</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.445971252383117</v>
+        <v>-3.811328762817595</v>
       </c>
       <c r="J8" t="n">
-        <v>-6.718283218007247</v>
+        <v>-6.791354747775185</v>
       </c>
       <c r="K8" t="n">
-        <v>3.27231196562413</v>
+        <v>2.98002598495759</v>
       </c>
       <c r="L8" t="n">
-        <v>3.038872772970159</v>
+        <v>3.038872784042606</v>
       </c>
       <c r="M8" t="n">
-        <v>11022372</v>
+        <v>17041674</v>
       </c>
       <c r="N8" t="n">
-        <v>27456059.44</v>
+        <v>27577459.48</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4014549875260613</v>
+        <v>0.617956632747811</v>
       </c>
       <c r="P8" t="n">
-        <v>0.030087289573326</v>
+        <v>0.030386704331899</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>15.00356619698661</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0381101021208168</v>
+        <v>0.0385586768826578</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -5519,46 +5519,46 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.619999885559082</v>
+        <v>7.75</v>
       </c>
       <c r="C9" t="n">
-        <v>5.820999989509582</v>
+        <v>5.8235999917984</v>
       </c>
       <c r="D9" t="n">
-        <v>4.044949998855591</v>
+        <v>4.045599999427796</v>
       </c>
       <c r="E9" t="n">
-        <v>49.52198674958101</v>
+        <v>50.78431291884531</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3754512523516937</v>
+        <v>0.398916977141597</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7162161683235146</v>
+        <v>0.7454954730004386</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7845433066970831</v>
+        <v>0.8149882985054226</v>
       </c>
       <c r="I9" t="n">
-        <v>0.604495093540149</v>
+        <v>0.6148654732844969</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7309074941297095</v>
+        <v>0.7329815703896027</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1264124005895605</v>
+        <v>-0.1181160971051057</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0949479297406228</v>
+        <v>-0.09494792986503239</v>
       </c>
       <c r="M9" t="n">
-        <v>4168817</v>
+        <v>5831517</v>
       </c>
       <c r="N9" t="n">
-        <v>7822012.34</v>
+        <v>7855356.34</v>
       </c>
       <c r="O9" t="n">
-        <v>0.532959655238795</v>
+        <v>0.7423618671893375</v>
       </c>
       <c r="P9" t="n">
         <v>-0.0049382666628676</v>
@@ -5572,7 +5572,7 @@
         <v>0.7386070660182408</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0969300626129929</v>
+        <v>0.0953041375507407</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -5587,49 +5587,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16.70000076293945</v>
+        <v>16.54999923706055</v>
       </c>
       <c r="C10" t="n">
-        <v>9.89940004348755</v>
+        <v>9.89640001296997</v>
       </c>
       <c r="D10" t="n">
-        <v>6.551549993753433</v>
+        <v>6.550799986124039</v>
       </c>
       <c r="E10" t="n">
-        <v>74.13793418441759</v>
+        <v>73.76093226909819</v>
       </c>
       <c r="F10" t="n">
-        <v>1.108585934604434</v>
+        <v>1.089646348186008</v>
       </c>
       <c r="G10" t="n">
-        <v>3.664804781797714</v>
+        <v>3.622904913340839</v>
       </c>
       <c r="H10" t="n">
-        <v>2.242718534697032</v>
+        <v>2.213592025356996</v>
       </c>
       <c r="I10" t="n">
-        <v>2.319405916913061</v>
+        <v>2.307439983510296</v>
       </c>
       <c r="J10" t="n">
-        <v>2.202971913174683</v>
+        <v>2.200578726856989</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1164340037383775</v>
+        <v>0.1068612566533073</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2137816411175577</v>
+        <v>0.2137816409724133</v>
       </c>
       <c r="M10" t="n">
-        <v>908525</v>
+        <v>1688639</v>
       </c>
       <c r="N10" t="n">
-        <v>3926424.5</v>
+        <v>3942064.78</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2313873601797258</v>
+        <v>0.4283640919771998</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0098826338563442</v>
+        <v>0.0129709127575936</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>1.499500070299421</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0897904192691477</v>
+        <v>0.0906042380317201</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -5655,46 +5655,46 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>273.7200012207031</v>
+        <v>274.9800109863281</v>
       </c>
       <c r="C11" t="n">
-        <v>300.9616012573242</v>
+        <v>300.9868014526367</v>
       </c>
       <c r="D11" t="n">
-        <v>276.033300857544</v>
+        <v>276.0396009063721</v>
       </c>
       <c r="E11" t="n">
-        <v>59.84774036913862</v>
+        <v>60.77300060323681</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.07185243694101499</v>
+        <v>-0.0675799139679773</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.089875307661835</v>
+        <v>-0.0856857490063902</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0369360152854949</v>
+        <v>0.0417093219483664</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.807993064887171</v>
+        <v>-6.707479457149645</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.56358877430759</v>
+        <v>-12.5434860423407</v>
       </c>
       <c r="K11" t="n">
-        <v>5.755595709420415</v>
+        <v>5.836006585191056</v>
       </c>
       <c r="L11" t="n">
-        <v>5.61249043240821</v>
+        <v>5.612490428240474</v>
       </c>
       <c r="M11" t="n">
-        <v>399178</v>
+        <v>802990</v>
       </c>
       <c r="N11" t="n">
-        <v>1553691.56</v>
+        <v>1561767.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2569222941521288</v>
+        <v>0.5141545369292413</v>
       </c>
       <c r="P11" t="n">
         <v>-0.0092015237095138</v>
@@ -5708,7 +5708,7 @@
         <v>11.86785343715123</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0433576405970496</v>
+        <v>0.043158967790358</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -5723,46 +5723,46 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>101.9199981689453</v>
+        <v>111.0500030517578</v>
       </c>
       <c r="C12" t="n">
-        <v>112.2141996765137</v>
+        <v>112.3967997741699</v>
       </c>
       <c r="D12" t="n">
-        <v>101.2152499198914</v>
+        <v>101.2608999443054</v>
       </c>
       <c r="E12" t="n">
-        <v>61.78305163129135</v>
+        <v>68.91793789745947</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1509880819470179</v>
+        <v>0.2540937235976002</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1566404678873824</v>
+        <v>-0.08109222628134211</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0247823549358371</v>
+        <v>0.0625777512376504</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4327557493239879</v>
+        <v>1.161075227032811</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8141737820016303</v>
+        <v>-0.6685098866153706</v>
       </c>
       <c r="K12" t="n">
-        <v>1.246929531325618</v>
+        <v>1.829585113648181</v>
       </c>
       <c r="L12" t="n">
-        <v>1.911196160245703</v>
+        <v>1.911196160307923</v>
       </c>
       <c r="M12" t="n">
-        <v>684406</v>
+        <v>2061902</v>
       </c>
       <c r="N12" t="n">
-        <v>1511656.12</v>
+        <v>1539206.04</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4527524421361122</v>
+        <v>1.339588038518872</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -5773,10 +5773,10 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>6.059286390032087</v>
+        <v>6.621071951729911</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0594513981445334</v>
+        <v>0.0596224382690379</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -5791,46 +5791,46 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>238.5599975585937</v>
+        <v>236.1799926757812</v>
       </c>
       <c r="C13" t="n">
-        <v>227.4123999023437</v>
+        <v>227.3647998046875</v>
       </c>
       <c r="D13" t="n">
-        <v>161.8339501953125</v>
+        <v>161.8220501708985</v>
       </c>
       <c r="E13" t="n">
-        <v>41.22109092680138</v>
+        <v>40.54773982640063</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0488417531966132</v>
+        <v>-0.058331027571557</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4954864040194742</v>
+        <v>0.4805666145318343</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5285447963298346</v>
+        <v>0.5132951982576803</v>
       </c>
       <c r="I13" t="n">
-        <v>5.366146553165322</v>
+        <v>5.176288597925236</v>
       </c>
       <c r="J13" t="n">
-        <v>10.04261832303297</v>
+        <v>10.00464671182025</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.676471769867648</v>
+        <v>-4.82835811389501</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.078359216969876</v>
+        <v>-4.078359208904043</v>
       </c>
       <c r="M13" t="n">
-        <v>2671652</v>
+        <v>4098014</v>
       </c>
       <c r="N13" t="n">
-        <v>8669835.039999999</v>
+        <v>8698754.279999999</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3081548827254273</v>
+        <v>0.4711035474840427</v>
       </c>
       <c r="P13" t="n">
         <v>0.06596166699561611</v>
@@ -5841,10 +5841,10 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>26.78535788399833</v>
+        <v>26.89178684779576</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1122793350021705</v>
+        <v>0.1138614094408571</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -5859,49 +5859,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>357.9649963378906</v>
+        <v>359.510009765625</v>
       </c>
       <c r="C14" t="n">
-        <v>372.2605004882813</v>
+        <v>372.2914007568359</v>
       </c>
       <c r="D14" t="n">
-        <v>319.9694248199463</v>
+        <v>319.977149887085</v>
       </c>
       <c r="E14" t="n">
-        <v>59.70798614779127</v>
+        <v>60.70401435938903</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0047681171397168</v>
+        <v>-0.0004725948443551</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07526055810930531</v>
+        <v>0.0799014923279795</v>
       </c>
       <c r="H14" t="n">
-        <v>0.07866272566327411</v>
+        <v>0.08331834398404769</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.052659783913896</v>
+        <v>-1.929410851302862</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.651574127137988</v>
+        <v>-2.626924342896726</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5989143432240915</v>
+        <v>0.6975134915938646</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5974640052565006</v>
+        <v>0.5974640061688676</v>
       </c>
       <c r="M14" t="n">
-        <v>9886711</v>
+        <v>18165860</v>
       </c>
       <c r="N14" t="n">
-        <v>31789204.22</v>
+        <v>31956097.2</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3110084458729493</v>
+        <v>0.5684630349666104</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0040282924977889</v>
+        <v>-0.0037303974496513</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -5909,10 +5909,10 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>9.963572910853795</v>
+        <v>10.02928815569196</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0278339307272629</v>
+        <v>0.0278971040673675</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -5927,49 +5927,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>108.60009765625</v>
+        <v>107.7600021362305</v>
       </c>
       <c r="C15" t="n">
-        <v>117.453201751709</v>
+        <v>117.4363998413086</v>
       </c>
       <c r="D15" t="n">
-        <v>63.22100046157837</v>
+        <v>63.21679998397827</v>
       </c>
       <c r="E15" t="n">
-        <v>32.58833144019887</v>
+        <v>31.74508778177839</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1282002253969481</v>
+        <v>-0.1349441888077021</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7019290913494134</v>
+        <v>0.6887635138233303</v>
       </c>
       <c r="H15" t="n">
-        <v>1.464822838659349</v>
+        <v>1.44575575981607</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.911935590686724</v>
+        <v>-1.978951755975629</v>
       </c>
       <c r="J15" t="n">
-        <v>1.427590948590416</v>
+        <v>1.414187717502414</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.33952653927714</v>
+        <v>-3.393139473478043</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.642499733942029</v>
+        <v>-3.642499734729958</v>
       </c>
       <c r="M15" t="n">
-        <v>66719056</v>
+        <v>90554427</v>
       </c>
       <c r="N15" t="n">
-        <v>130167141.12</v>
+        <v>130653424.54</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5125645030376157</v>
+        <v>0.6930888135448485</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0469355722360184</v>
+        <v>0.0471295624603021</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>9.541407448904854</v>
+        <v>9.565714699881417</v>
       </c>
       <c r="S15" t="n">
-        <v>0.08785818479745849</v>
+        <v>0.088768694415841</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -5995,46 +5995,46 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>39.27999877929688</v>
+        <v>39.29000091552734</v>
       </c>
       <c r="C16" t="n">
-        <v>54.9010001373291</v>
+        <v>54.90120018005371</v>
       </c>
       <c r="D16" t="n">
-        <v>48.68905003547668</v>
+        <v>48.68910004615784</v>
       </c>
       <c r="E16" t="n">
-        <v>17.4324740918985</v>
+        <v>17.46143102526288</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3210025961043269</v>
+        <v>-0.3208296983256874</v>
       </c>
       <c r="G16" t="n">
-        <v>0.09843402189546729</v>
+        <v>0.09871372370474971</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2290481218624677</v>
+        <v>-0.2288518090836513</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.177018107738107</v>
+        <v>-4.176220212693849</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.738977753251084</v>
+        <v>-2.738818169369535</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.438040354487022</v>
+        <v>-1.437402043324314</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.449196603544823</v>
+        <v>-1.449196605493906</v>
       </c>
       <c r="M16" t="n">
-        <v>11303490</v>
+        <v>13830161</v>
       </c>
       <c r="N16" t="n">
-        <v>28855675.8</v>
+        <v>28909287.22</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3917250137666157</v>
+        <v>0.4783985469704708</v>
       </c>
       <c r="P16" t="n">
         <v>0.0298353862022756</v>
@@ -6048,7 +6048,7 @@
         <v>3.701071330479213</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0942227964739632</v>
+        <v>0.0941988099831414</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -6063,49 +6063,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7.880000114440918</v>
+        <v>7.940000057220459</v>
       </c>
       <c r="C17" t="n">
-        <v>8.698399953842163</v>
+        <v>8.699599952697755</v>
       </c>
       <c r="D17" t="n">
-        <v>8.190949969291687</v>
+        <v>8.191249969005584</v>
       </c>
       <c r="E17" t="n">
-        <v>45.00907288667684</v>
+        <v>45.60143417545741</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0217256591067309</v>
+        <v>-0.014276876920964</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1581196150130758</v>
+        <v>-0.1517093644809897</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0425272718423876</v>
+        <v>-0.0352368774175008</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0370714248413754</v>
+        <v>0.0418577474089811</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1080686358662165</v>
+        <v>0.109025903360381</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.07099721102484099</v>
+        <v>-0.0671681559513998</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0068890358413925</v>
+        <v>-0.00688903703365</v>
       </c>
       <c r="M17" t="n">
-        <v>769079</v>
+        <v>1312323</v>
       </c>
       <c r="N17" t="n">
-        <v>1053103.58</v>
+        <v>1064110.46</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7302975838331116</v>
+        <v>1.233258246517002</v>
       </c>
       <c r="P17" t="n">
-        <v>0.018661516252568</v>
+        <v>0.0167310315006482</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>0.6941427503313337</v>
+        <v>0.7005712985992432</v>
       </c>
       <c r="S17" t="n">
-        <v>0.08808918023481301</v>
+        <v>0.0882331603967885</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -6131,46 +6131,46 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1154.025024414062</v>
+        <v>1152.5400390625</v>
       </c>
       <c r="C18" t="n">
-        <v>1097.756102294922</v>
+        <v>1097.726402587891</v>
       </c>
       <c r="D18" t="n">
-        <v>1000.562928161621</v>
+        <v>1000.555503234863</v>
       </c>
       <c r="E18" t="n">
-        <v>57.42014603587688</v>
+        <v>57.15185573112131</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0185569500565423</v>
+        <v>0.0172462833737863</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2509756362212059</v>
+        <v>0.24936589600271</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0675532140740633</v>
+        <v>0.0661794995952822</v>
       </c>
       <c r="I18" t="n">
-        <v>27.58418928298352</v>
+        <v>27.4657290256198</v>
       </c>
       <c r="J18" t="n">
-        <v>34.60373069943505</v>
+        <v>34.58003879098143</v>
       </c>
       <c r="K18" t="n">
-        <v>-7.019541416451538</v>
+        <v>-7.114309765361639</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.468572913063639</v>
+        <v>-3.468572970271296</v>
       </c>
       <c r="M18" t="n">
-        <v>1460632</v>
+        <v>2014654</v>
       </c>
       <c r="N18" t="n">
-        <v>3189112.64</v>
+        <v>3200251.08</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4580057730416195</v>
+        <v>0.6295299805039047</v>
       </c>
       <c r="P18" t="n">
         <v>-0.013419399271567</v>
@@ -6184,7 +6184,7 @@
         <v>41.49965122767857</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0359607897140266</v>
+        <v>0.03600712324184</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -6199,46 +6199,46 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14.89999961853027</v>
+        <v>14.90999984741211</v>
       </c>
       <c r="C19" t="n">
-        <v>27.45140003204345</v>
+        <v>27.45160003662109</v>
       </c>
       <c r="D19" t="n">
-        <v>19.02012503147125</v>
+        <v>19.02017503261566</v>
       </c>
       <c r="E19" t="n">
-        <v>23.53454946433199</v>
+        <v>23.55515812624178</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4402705053047864</v>
+        <v>-0.4398948393180634</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3705112137514115</v>
+        <v>-0.3700887283754248</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2239583840386715</v>
+        <v>-0.2234375388051057</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.423312418551486</v>
+        <v>-3.422514679536182</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.197692845913036</v>
+        <v>-3.197533298161815</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2256195726384504</v>
+        <v>-0.2249813813743664</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2400474448421516</v>
+        <v>-0.2400474448214149</v>
       </c>
       <c r="M19" t="n">
-        <v>5881585</v>
+        <v>10365734</v>
       </c>
       <c r="N19" t="n">
-        <v>14284279.7</v>
+        <v>14374696.68</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4117522985775755</v>
+        <v>0.7211097549224948</v>
       </c>
       <c r="P19" t="n">
         <v>0.0323432829789085</v>
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>1.634500162942069</v>
+        <v>1.643071583339146</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1096980003213782</v>
+        <v>0.1101993024918997</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -6267,46 +6267,46 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>223.5269927978516</v>
+        <v>222.4400024414062</v>
       </c>
       <c r="C20" t="n">
-        <v>233.8563400268554</v>
+        <v>233.8346002197265</v>
       </c>
       <c r="D20" t="n">
-        <v>128.1968851470947</v>
+        <v>128.1914501953125</v>
       </c>
       <c r="E20" t="n">
-        <v>33.85940682526719</v>
+        <v>33.43867797240382</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2008330960228952</v>
+        <v>-0.2047193681323177</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6702308132673362</v>
+        <v>0.6621086407979857</v>
       </c>
       <c r="H20" t="n">
-        <v>1.696670218889714</v>
+        <v>1.683556569903718</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.94259616698389</v>
+        <v>-5.029307648001776</v>
       </c>
       <c r="J20" t="n">
-        <v>4.135879069049432</v>
+        <v>4.118536773364202</v>
       </c>
       <c r="K20" t="n">
-        <v>-9.078475236033322</v>
+        <v>-9.147844421365978</v>
       </c>
       <c r="L20" t="n">
-        <v>-9.60956168128553</v>
+        <v>-9.60956168149287</v>
       </c>
       <c r="M20" t="n">
-        <v>13591278</v>
+        <v>20011700</v>
       </c>
       <c r="N20" t="n">
-        <v>45245819.56</v>
+        <v>45377880</v>
       </c>
       <c r="O20" t="n">
-        <v>0.300387486229015</v>
+        <v>0.4410012102813088</v>
       </c>
       <c r="P20" t="n">
         <v>0.0645198535414377</v>
@@ -6320,7 +6320,7 @@
         <v>21.60285949707031</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0966454173013772</v>
+        <v>0.0971176913323438</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -6335,49 +6335,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>981.2349853515624</v>
+        <v>983.1199951171876</v>
       </c>
       <c r="C21" t="n">
-        <v>916.6997009277344</v>
+        <v>916.7374011230468</v>
       </c>
       <c r="D21" t="n">
-        <v>472.434125213623</v>
+        <v>472.4435502624512</v>
       </c>
       <c r="E21" t="n">
-        <v>44.63958636842999</v>
+        <v>44.79774534214121</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0003820254536893</v>
+        <v>0.0015382991087689</v>
       </c>
       <c r="G21" t="n">
-        <v>1.107191894590034</v>
+        <v>1.11123993339689</v>
       </c>
       <c r="H21" t="n">
-        <v>1.837005230879021</v>
+        <v>1.842455283766628</v>
       </c>
       <c r="I21" t="n">
-        <v>9.29500447418593</v>
+        <v>9.445375617460741</v>
       </c>
       <c r="J21" t="n">
-        <v>34.38581918694242</v>
+        <v>34.41589340782176</v>
       </c>
       <c r="K21" t="n">
-        <v>-25.09081471275649</v>
+        <v>-24.97051779036101</v>
       </c>
       <c r="L21" t="n">
-        <v>-28.83193491040208</v>
+        <v>-28.83193490729185</v>
       </c>
       <c r="M21" t="n">
-        <v>23027783</v>
+        <v>30387447</v>
       </c>
       <c r="N21" t="n">
-        <v>53971859.66</v>
+        <v>54126284.94</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4266627673210695</v>
+        <v>0.5614175632723557</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0543756800501934</v>
+        <v>0.0548345836529482</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>89.7650146484375</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0914816695169872</v>
+        <v>0.0913062648448499</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -6403,46 +6403,46 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>195.4440002441407</v>
+        <v>194.0899963378907</v>
       </c>
       <c r="C22" t="n">
-        <v>224.0154800415039</v>
+        <v>223.9883999633789</v>
       </c>
       <c r="D22" t="n">
-        <v>136.7456954574585</v>
+        <v>136.7389254379272</v>
       </c>
       <c r="E22" t="n">
-        <v>30.15032897033954</v>
+        <v>29.94861110189596</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1588741619437159</v>
+        <v>-0.1647013434839698</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2068914245870592</v>
+        <v>0.1985302791885346</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8209633551649784</v>
+        <v>0.8083480203736746</v>
       </c>
       <c r="I22" t="n">
-        <v>-6.54504822044089</v>
+        <v>-6.653059934508008</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4632617408015549</v>
+        <v>0.4416593897978491</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.008309961242444</v>
+        <v>-7.094719324305856</v>
       </c>
       <c r="L22" t="n">
-        <v>-6.66147091221397</v>
+        <v>-6.661470908937844</v>
       </c>
       <c r="M22" t="n">
-        <v>13321356</v>
+        <v>17379284</v>
       </c>
       <c r="N22" t="n">
-        <v>17963685.12</v>
+        <v>18046721.68</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7415714487874523</v>
+        <v>0.9630161260402392</v>
       </c>
       <c r="P22" t="n">
         <v>0.0310198990532244</v>
@@ -6456,7 +6456,7 @@
         <v>25.56014360700335</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1307798836243356</v>
+        <v>0.1316922257162897</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -6471,46 +6471,46 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>212.1750030517578</v>
+        <v>211.8000030517578</v>
       </c>
       <c r="C23" t="n">
-        <v>209.3367004394531</v>
+        <v>209.3292004394532</v>
       </c>
       <c r="D23" t="n">
-        <v>191.971975479126</v>
+        <v>191.970100479126</v>
       </c>
       <c r="E23" t="n">
-        <v>60.98887129446162</v>
+        <v>60.72211027619969</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0340416225315178</v>
+        <v>0.0322140481100636</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0797160906967351</v>
+        <v>0.07780779081132171</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1472639788624439</v>
+        <v>0.1452362942347289</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5567422506966011</v>
+        <v>-0.5866568076601197</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.252686981411861</v>
+        <v>-2.258669927172656</v>
       </c>
       <c r="K23" t="n">
-        <v>1.69594473071526</v>
+        <v>1.672013119512536</v>
       </c>
       <c r="L23" t="n">
-        <v>1.206196025562167</v>
+        <v>1.206196039309396</v>
       </c>
       <c r="M23" t="n">
-        <v>82485174</v>
+        <v>118014431</v>
       </c>
       <c r="N23" t="n">
-        <v>158036467.48</v>
+        <v>158756396.62</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5219375965261863</v>
+        <v>0.7433680375253153</v>
       </c>
       <c r="P23" t="n">
         <v>0.0229450115312453</v>
@@ -6524,7 +6524,7 @@
         <v>6.948570251464844</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0327492407282766</v>
+        <v>0.0328072245106002</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -6539,46 +6539,46 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>91.27999877929688</v>
+        <v>91.56999969482422</v>
       </c>
       <c r="C24" t="n">
-        <v>106.6321994018555</v>
+        <v>106.637999420166</v>
       </c>
       <c r="D24" t="n">
-        <v>104.4480996704102</v>
+        <v>104.4495496749878</v>
       </c>
       <c r="E24" t="n">
-        <v>16.32886286692583</v>
+        <v>17.24659021688664</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0958795601521012</v>
+        <v>-0.0930071263351723</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2135102472907299</v>
+        <v>-0.2110115317847183</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1685946077227206</v>
+        <v>-0.1659531930846929</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.138851803979577</v>
+        <v>-4.115717830504863</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.348218977422672</v>
+        <v>-3.34359218614901</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7906328265569047</v>
+        <v>-0.7721256443558535</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7934742332941171</v>
+        <v>-0.7934742319256261</v>
       </c>
       <c r="M24" t="n">
-        <v>2855528</v>
+        <v>3737849</v>
       </c>
       <c r="N24" t="n">
-        <v>3260828.56</v>
+        <v>3278536.98</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8757062652812388</v>
+        <v>1.140096641520877</v>
       </c>
       <c r="P24" t="n">
         <v>0.0177384274683925</v>
@@ -6592,7 +6592,7 @@
         <v>4.48357173374721</v>
       </c>
       <c r="S24" t="n">
-        <v>0.049118884681275</v>
+        <v>0.0489633258566084</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -6607,46 +6607,46 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25.68000030517578</v>
+        <v>25.55999946594238</v>
       </c>
       <c r="C25" t="n">
-        <v>35.87700008392334</v>
+        <v>35.87460006713867</v>
       </c>
       <c r="D25" t="n">
-        <v>25.36914998531342</v>
+        <v>25.36854998111725</v>
       </c>
       <c r="E25" t="n">
-        <v>41.36886831176119</v>
+        <v>41.0703537322088</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1756019062709888</v>
+        <v>-0.1794542607076809</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2431476547538232</v>
+        <v>-0.2466843726481373</v>
       </c>
       <c r="H25" t="n">
-        <v>0.009433953069178</v>
+        <v>0.0047169390473917</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.451265178440178</v>
+        <v>-2.460837895898564</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.397044663929374</v>
+        <v>-2.398959208613305</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0542205145108036</v>
+        <v>-0.0618786872852585</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0149246408257801</v>
+        <v>-0.0149246403488736</v>
       </c>
       <c r="M25" t="n">
-        <v>3296129</v>
+        <v>5281531</v>
       </c>
       <c r="N25" t="n">
-        <v>13314476.58</v>
+        <v>13354554.62</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2475597880393733</v>
+        <v>0.3954853718663363</v>
       </c>
       <c r="P25" t="n">
         <v>0.0084746235925221</v>
@@ -6660,7 +6660,7 @@
         <v>2.376357078552246</v>
       </c>
       <c r="S25" t="n">
-        <v>0.09253726831433461</v>
+        <v>0.09297171863084901</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -6675,46 +6675,46 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13.68000030517578</v>
+        <v>13.6899995803833</v>
       </c>
       <c r="C26" t="n">
-        <v>11.47180004119873</v>
+        <v>11.47200002670288</v>
       </c>
       <c r="D26" t="n">
-        <v>9.128125011920927</v>
+        <v>9.128175008296967</v>
       </c>
       <c r="E26" t="n">
-        <v>74.94252742525934</v>
+        <v>74.99999453168354</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2052863299907961</v>
+        <v>0.2061673233715402</v>
       </c>
       <c r="G26" t="n">
-        <v>0.556314034646695</v>
+        <v>0.5574516086229084</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5944056441514309</v>
+        <v>0.595571060852647</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6754284493060911</v>
+        <v>0.6762261142031036</v>
       </c>
       <c r="J26" t="n">
-        <v>0.645867076128479</v>
+        <v>0.646026611544229</v>
       </c>
       <c r="K26" t="n">
-        <v>0.029561373177612</v>
+        <v>0.0301995026588746</v>
       </c>
       <c r="L26" t="n">
-        <v>0.042571941463545</v>
+        <v>0.0425719404890034</v>
       </c>
       <c r="M26" t="n">
-        <v>178131</v>
+        <v>362358</v>
       </c>
       <c r="N26" t="n">
-        <v>663704.62</v>
+        <v>667389.16</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2683889709853157</v>
+        <v>0.5429485849005998</v>
       </c>
       <c r="P26" t="n">
         <v>-0.0110537672736636</v>
@@ -6728,7 +6728,7 @@
         <v>0.6038284982953753</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0441395091246393</v>
+        <v>0.04410726930632</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -6743,46 +6743,46 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>79.03959655761719</v>
+        <v>78.80999755859375</v>
       </c>
       <c r="C27" t="n">
-        <v>107.0189918518066</v>
+        <v>107.0143998718262</v>
       </c>
       <c r="D27" t="n">
-        <v>77.06474809646606</v>
+        <v>77.06360010147095</v>
       </c>
       <c r="E27" t="n">
-        <v>37.31820954520452</v>
+        <v>37.0903849686533</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2280535498703397</v>
+        <v>-0.2302959465925986</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09442807008647761</v>
+        <v>0.0912489092564774</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1008009648970609</v>
+        <v>-0.1034130126221777</v>
       </c>
       <c r="I27" t="n">
-        <v>-7.689987303492998</v>
+        <v>-7.708302898829572</v>
       </c>
       <c r="J27" t="n">
-        <v>-6.259257503679423</v>
+        <v>-6.262920629952119</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.430729799813575</v>
+        <v>-1.445382268877453</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.60128212643402</v>
+        <v>-1.601282123551874</v>
       </c>
       <c r="M27" t="n">
-        <v>11543412</v>
+        <v>15572267</v>
       </c>
       <c r="N27" t="n">
-        <v>28197160.24</v>
+        <v>28280951.34</v>
       </c>
       <c r="O27" t="n">
-        <v>0.4093820761292379</v>
+        <v>0.5506274104002613</v>
       </c>
       <c r="P27" t="n">
         <v>0.0264563885114627</v>
@@ -6796,7 +6796,7 @@
         <v>7.732856750488281</v>
       </c>
       <c r="S27" t="n">
-        <v>0.09783522547273241</v>
+        <v>0.09812025111076859</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -6811,46 +6811,46 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18.56500053405762</v>
+        <v>18.54999923706055</v>
       </c>
       <c r="C28" t="n">
-        <v>16.94689994812012</v>
+        <v>16.94659992218018</v>
       </c>
       <c r="D28" t="n">
-        <v>21.97300002574921</v>
+        <v>21.97292501926422</v>
       </c>
       <c r="E28" t="n">
-        <v>62.08528783568838</v>
+        <v>61.97715680636227</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1197225946613795</v>
+        <v>0.1188178119674048</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0365717862772707</v>
+        <v>0.035734192914631</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3020676591046031</v>
+        <v>-0.3026316176302398</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4048847760322971</v>
+        <v>0.4036880928810831</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3716194461549978</v>
+        <v>0.3713801114427376</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0332653298772992</v>
+        <v>0.0323079814383454</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0328078631428616</v>
+        <v>0.0328078623756669</v>
       </c>
       <c r="M28" t="n">
-        <v>67826209</v>
+        <v>88638131</v>
       </c>
       <c r="N28" t="n">
-        <v>76550602.18000001</v>
+        <v>76971392.62</v>
       </c>
       <c r="O28" t="n">
-        <v>0.8860310313498829</v>
+        <v>1.151572395702875</v>
       </c>
       <c r="P28" t="n">
         <v>0.0044125718372439</v>
@@ -6864,7 +6864,7 @@
         <v>0.9414285932268416</v>
       </c>
       <c r="S28" t="n">
-        <v>0.050709860821161</v>
+        <v>0.0507508696467214</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -6879,46 +6879,46 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6.440000057220459</v>
+        <v>6.289999961853027</v>
       </c>
       <c r="C29" t="n">
-        <v>5.934999990463257</v>
+        <v>5.931999988555908</v>
       </c>
       <c r="D29" t="n">
-        <v>4.497150006294251</v>
+        <v>4.496400005817414</v>
       </c>
       <c r="E29" t="n">
-        <v>62.89926016459427</v>
+        <v>60.71428368691744</v>
       </c>
       <c r="F29" t="n">
-        <v>0.303643721179224</v>
+        <v>0.2732793297561537</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0501475135791332</v>
+        <v>-0.0722714207658075</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4030500747564287</v>
+        <v>0.3703703165035101</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3331000553553087</v>
+        <v>0.3211342359001525</v>
       </c>
       <c r="J29" t="n">
-        <v>0.311370230637283</v>
+        <v>0.3089770668965803</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0217298247180257</v>
+        <v>0.0121571690035722</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0646032293833483</v>
+        <v>0.0646032293232172</v>
       </c>
       <c r="M29" t="n">
-        <v>379921</v>
+        <v>740253</v>
       </c>
       <c r="N29" t="n">
-        <v>1213730.42</v>
+        <v>1220937.06</v>
       </c>
       <c r="O29" t="n">
-        <v>0.313019261723703</v>
+        <v>0.606299066718476</v>
       </c>
       <c r="P29" t="n">
         <v>0.0046656626141934</v>
@@ -6932,7 +6932,7 @@
         <v>0.6430713449205671</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0998557980134739</v>
+        <v>0.1022370983816538</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -6947,49 +6947,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>396.0499877929688</v>
+        <v>396.1799926757813</v>
       </c>
       <c r="C30" t="n">
-        <v>409.9239990234375</v>
+        <v>409.9265991210938</v>
       </c>
       <c r="D30" t="n">
-        <v>417.7507499694824</v>
+        <v>417.7513999938965</v>
       </c>
       <c r="E30" t="n">
-        <v>54.28385236539413</v>
+        <v>54.31908877476581</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0255394657625399</v>
+        <v>-0.0252195954646896</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0874518795123824</v>
+        <v>0.0878088396399361</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1178501529515541</v>
+        <v>-0.1175605839804055</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.305705861664421</v>
+        <v>-1.295335076813615</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.253213166469967</v>
+        <v>-1.251138977775379</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.0524926951944539</v>
+        <v>-0.0441960990382355</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3816312784934397</v>
+        <v>0.3816312658036853</v>
       </c>
       <c r="M30" t="n">
-        <v>17352925</v>
+        <v>22670942</v>
       </c>
       <c r="N30" t="n">
-        <v>48316348.5</v>
+        <v>48424298.84</v>
       </c>
       <c r="O30" t="n">
-        <v>0.3591522442967725</v>
+        <v>0.4681728500583489</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0109940121352903</v>
+        <v>0.0108673065184357</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>18.56714085170201</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0468808014745042</v>
+        <v>0.0468654177266762</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -7015,46 +7015,46 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>422.989990234375</v>
+        <v>420.3900146484375</v>
       </c>
       <c r="C31" t="n">
-        <v>425.0452001953125</v>
+        <v>424.9932006835937</v>
       </c>
       <c r="D31" t="n">
-        <v>349.73625</v>
+        <v>349.7232501220703</v>
       </c>
       <c r="E31" t="n">
-        <v>45.80252323519223</v>
+        <v>44.9811782697946</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0022173530008412</v>
+        <v>-0.008350383526770399</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1134538259075421</v>
+        <v>0.1066098039915053</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2749495260011116</v>
+        <v>0.2671128449508846</v>
       </c>
       <c r="I31" t="n">
-        <v>1.375541336259005</v>
+        <v>1.1681358426315</v>
       </c>
       <c r="J31" t="n">
-        <v>5.416488805626193</v>
+        <v>5.375007663979455</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.040947469367188</v>
+        <v>-4.206871821347955</v>
       </c>
       <c r="L31" t="n">
-        <v>-3.711786865119478</v>
+        <v>-3.711786847950947</v>
       </c>
       <c r="M31" t="n">
-        <v>10328172</v>
+        <v>14162977</v>
       </c>
       <c r="N31" t="n">
-        <v>13681967.44</v>
+        <v>13759951.54</v>
       </c>
       <c r="O31" t="n">
-        <v>0.7548747682153525</v>
+        <v>1.029289744141061</v>
       </c>
       <c r="P31" t="n">
         <v>0.0220361706931489</v>
@@ -7068,7 +7068,7 @@
         <v>19.97285679408482</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0472182729029073</v>
+        <v>0.0475103025717384</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -7083,46 +7083,46 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>303.2900085449219</v>
+        <v>303.5799865722656</v>
       </c>
       <c r="C32" t="n">
-        <v>324.2276013183593</v>
+        <v>324.2334008789063</v>
       </c>
       <c r="D32" t="n">
-        <v>238.4730003356934</v>
+        <v>238.4744502258301</v>
       </c>
       <c r="E32" t="n">
-        <v>45.51637972582078</v>
+        <v>45.59526295678533</v>
       </c>
       <c r="F32" t="n">
-        <v>0.001386777939399</v>
+        <v>0.0023442119276404</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.0232520723765163</v>
+        <v>-0.0223181957921105</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7837441082299823</v>
+        <v>0.7854495603821059</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.981566865318655</v>
+        <v>-1.958434725800657</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.195957225177187</v>
+        <v>-1.191330811010456</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.7856096401414672</v>
+        <v>-0.767103914790201</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.1480541656201379</v>
+        <v>-0.1480541601253728</v>
       </c>
       <c r="M32" t="n">
-        <v>2440399</v>
+        <v>3108865</v>
       </c>
       <c r="N32" t="n">
-        <v>6158305.98</v>
+        <v>6171759.3</v>
       </c>
       <c r="O32" t="n">
-        <v>0.3962776464705639</v>
+        <v>0.503724278424144</v>
       </c>
       <c r="P32" t="n">
         <v>0.031582057136426</v>
@@ -7136,7 +7136,7 @@
         <v>21.269287109375</v>
       </c>
       <c r="S32" t="n">
-        <v>0.07012854532009639</v>
+        <v>0.0700615588976316</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -7151,49 +7151,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>879.0349731445312</v>
+        <v>878.3099975585938</v>
       </c>
       <c r="C33" t="n">
-        <v>877.2036962890625</v>
+        <v>877.1891967773438</v>
       </c>
       <c r="D33" t="n">
-        <v>479.5720247650146</v>
+        <v>479.568399887085</v>
       </c>
       <c r="E33" t="n">
-        <v>37.9012279970176</v>
+        <v>37.83287697052316</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.0558568977811231</v>
+        <v>-0.0566355706663342</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6478609949037064</v>
+        <v>0.6465019374977761</v>
       </c>
       <c r="H33" t="n">
-        <v>1.734337884484876</v>
+        <v>1.732082765780254</v>
       </c>
       <c r="I33" t="n">
-        <v>-3.946942811041367</v>
+        <v>-4.004775621193289</v>
       </c>
       <c r="J33" t="n">
-        <v>11.24239613189376</v>
+        <v>11.23082957001891</v>
       </c>
       <c r="K33" t="n">
-        <v>-15.18933894293512</v>
+        <v>-15.2356051912122</v>
       </c>
       <c r="L33" t="n">
-        <v>-17.58862389405815</v>
+        <v>-17.58862389412036</v>
       </c>
       <c r="M33" t="n">
-        <v>2621790</v>
+        <v>3660836</v>
       </c>
       <c r="N33" t="n">
-        <v>4351679.8</v>
+        <v>4372720.72</v>
       </c>
       <c r="O33" t="n">
-        <v>0.6024776914882387</v>
+        <v>0.8371986766170606</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0451049293978258</v>
+        <v>0.0470279063556459</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>84.29928588867188</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0958998088404969</v>
+        <v>0.095978966564192</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -7219,49 +7219,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27.78499984741211</v>
+        <v>27.64999961853028</v>
       </c>
       <c r="C34" t="n">
-        <v>33.45609981536865</v>
+        <v>33.45339981079101</v>
       </c>
       <c r="D34" t="n">
-        <v>34.37737489700317</v>
+        <v>34.37669989585876</v>
       </c>
       <c r="E34" t="n">
-        <v>27.43579240581289</v>
+        <v>26.66666562011045</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0878200695161596</v>
+        <v>-0.09225211918587389</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0215073186788188</v>
+        <v>0.016544075109143</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.07752327114080911</v>
+        <v>-0.0820053503280708</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.885839017163246</v>
+        <v>-1.896608280225312</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.848768644888187</v>
+        <v>-1.850922515332613</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.0370703722750587</v>
+        <v>-0.0456857648926987</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.1129581202809464</v>
+        <v>-0.1129581131481429</v>
       </c>
       <c r="M34" t="n">
-        <v>14089718</v>
+        <v>21822512</v>
       </c>
       <c r="N34" t="n">
-        <v>55573798.36</v>
+        <v>55729654.24</v>
       </c>
       <c r="O34" t="n">
-        <v>0.2535316716832742</v>
+        <v>0.3915780978295909</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0112075006381963</v>
+        <v>0.0108459594618766</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>1.774999754769462</v>
       </c>
       <c r="S34" t="n">
-        <v>0.0638833818433432</v>
+        <v>0.06419529038907849</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -7287,49 +7287,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>266.9100036621094</v>
+        <v>270.7300109863281</v>
       </c>
       <c r="C35" t="n">
-        <v>226.0773999023438</v>
+        <v>226.1538000488281</v>
       </c>
       <c r="D35" t="n">
-        <v>160.4339002227783</v>
+        <v>160.4530002593994</v>
       </c>
       <c r="E35" t="n">
-        <v>75.48954865203949</v>
+        <v>76.47804213242863</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1609830828542311</v>
+        <v>0.1775990351188439</v>
       </c>
       <c r="G35" t="n">
-        <v>1.413945956396737</v>
+        <v>1.448494272710041</v>
       </c>
       <c r="H35" t="n">
-        <v>1.108793586992669</v>
+        <v>1.138974572482352</v>
       </c>
       <c r="I35" t="n">
-        <v>11.98885627983813</v>
+        <v>12.29358620165522</v>
       </c>
       <c r="J35" t="n">
-        <v>11.55689055600216</v>
+        <v>11.61783653124222</v>
       </c>
       <c r="K35" t="n">
-        <v>0.4319657238359742</v>
+        <v>0.6757496704129959</v>
       </c>
       <c r="L35" t="n">
-        <v>0.3955764881293149</v>
+        <v>0.3955764917786446</v>
       </c>
       <c r="M35" t="n">
-        <v>2503750</v>
+        <v>3586430</v>
       </c>
       <c r="N35" t="n">
-        <v>6070371</v>
+        <v>6092052.6</v>
       </c>
       <c r="O35" t="n">
-        <v>0.4124541976099978</v>
+        <v>0.5887063417673052</v>
       </c>
       <c r="P35" t="n">
-        <v>-0.0192129762097973</v>
+        <v>-0.0178872721149254</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -7337,10 +7337,10 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>13.84728785923549</v>
+        <v>13.92728751046317</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0518799882703731</v>
+        <v>0.0514434563782679</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>186.8500061035156</v>
+        <v>193.9199981689453</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
@@ -7364,19 +7364,19 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.6098459750502627</v>
+        <v>1.173833946081714</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.063102030061176</v>
+        <v>0.0496955641451142</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6729480051114388</v>
+        <v>1.1241383819366</v>
       </c>
       <c r="L36" t="n">
         <v>-0.9253561253561428</v>
       </c>
       <c r="M36" t="n">
-        <v>55688004</v>
+        <v>68533119</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -7424,25 +7424,25 @@
         <v>-0.5638944887971797</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6460939021770091</v>
+        <v>-0.6460939056856265</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.531832589754463</v>
+        <v>-0.5318325949141951</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.1142613124225461</v>
+        <v>-0.1142613107714314</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.1257283657885731</v>
+        <v>-0.125728364005369</v>
       </c>
       <c r="M37" t="n">
-        <v>17874401</v>
+        <v>22000846</v>
       </c>
       <c r="N37" t="n">
-        <v>33092404.02</v>
+        <v>33177512.92</v>
       </c>
       <c r="O37" t="n">
-        <v>0.5401360683617086</v>
+        <v>0.6631252334389868</v>
       </c>
       <c r="P37" t="n">
         <v>0.0299401183926648</v>
@@ -7471,46 +7471,46 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>45.97499847412109</v>
+        <v>46.2400016784668</v>
       </c>
       <c r="C38" t="n">
-        <v>60.62409980773926</v>
+        <v>60.62939987182617</v>
       </c>
       <c r="D38" t="n">
-        <v>81.45807479858398</v>
+        <v>81.45939981460572</v>
       </c>
       <c r="E38" t="n">
-        <v>23.65514622294652</v>
+        <v>24.59396920131374</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.2002957534902754</v>
+        <v>-0.1956862005835312</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.2151758785069101</v>
+        <v>-0.2106520957130826</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.5514634295207699</v>
+        <v>-0.5488780324052021</v>
       </c>
       <c r="I38" t="n">
-        <v>-3.821005453518332</v>
+        <v>-3.799865590804927</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.47953137350963</v>
+        <v>-3.475303393398709</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.3414740800087021</v>
+        <v>-0.3245621974062178</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.3462640816307631</v>
+        <v>-0.3462640846580571</v>
       </c>
       <c r="M38" t="n">
-        <v>4294000</v>
+        <v>6149099</v>
       </c>
       <c r="N38" t="n">
-        <v>12385600</v>
+        <v>12423253.98</v>
       </c>
       <c r="O38" t="n">
-        <v>0.3466929337294923</v>
+        <v>0.4949668589162981</v>
       </c>
       <c r="P38" t="n">
         <v>0.0251036384349932</v>
@@ -7524,7 +7524,7 @@
         <v>3.443371636526925</v>
       </c>
       <c r="S38" t="n">
-        <v>0.07489661230690781</v>
+        <v>0.07446737697958269</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -7539,46 +7539,46 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7.704999923706055</v>
+        <v>7.889999866485596</v>
       </c>
       <c r="C39" t="n">
-        <v>9.765099992752075</v>
+        <v>9.768799991607668</v>
       </c>
       <c r="D39" t="n">
-        <v>12.02957501411438</v>
+        <v>12.03050001382828</v>
       </c>
       <c r="E39" t="n">
-        <v>26.07003852546879</v>
+        <v>29.45544376243362</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.1579234704991521</v>
+        <v>-0.1377048966748554</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.1244318458290133</v>
+        <v>-0.1034091255142661</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.5</v>
+        <v>-0.4879948121601954</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5954887621141474</v>
+        <v>-0.5807309373062246</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.4886565204689792</v>
+        <v>-0.4857049623499154</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.1068322416451681</v>
+        <v>-0.0950259749563091</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.1257187896488844</v>
+        <v>-0.1257187869118775</v>
       </c>
       <c r="M39" t="n">
-        <v>38220902</v>
+        <v>46461445</v>
       </c>
       <c r="N39" t="n">
-        <v>37402628.04</v>
+        <v>37570084.9</v>
       </c>
       <c r="O39" t="n">
-        <v>1.021877445593526</v>
+        <v>1.236660633684115</v>
       </c>
       <c r="P39" t="n">
         <v>0.0100267124430337</v>
@@ -7589,10 +7589,10 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>0.5577142919812884</v>
+        <v>0.5648571423121861</v>
       </c>
       <c r="S39" t="n">
-        <v>0.07238342602254449</v>
+        <v>0.07159152748677899</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -7607,49 +7607,49 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>6.769999980926514</v>
+        <v>6.690000057220459</v>
       </c>
       <c r="C40" t="n">
-        <v>7.678600025177002</v>
+        <v>7.677000026702881</v>
       </c>
       <c r="D40" t="n">
-        <v>10.25847501277924</v>
+        <v>10.25807501316071</v>
       </c>
       <c r="E40" t="n">
-        <v>57.08154365904792</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.0188405960353824</v>
+        <v>-0.030434787716592</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0286943780897355</v>
+        <v>-0.0401721293256297</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.4148660190583203</v>
+        <v>-0.4217804465273066</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2391027085697912</v>
+        <v>-0.2454844682534638</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.3060612565560535</v>
+        <v>-0.3073376077152289</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0669585479862623</v>
+        <v>0.0618531394617651</v>
       </c>
       <c r="L40" t="n">
-        <v>0.0561779742976243</v>
+        <v>0.056177973986601</v>
       </c>
       <c r="M40" t="n">
-        <v>25917857</v>
+        <v>32492134</v>
       </c>
       <c r="N40" t="n">
-        <v>28762625.14</v>
+        <v>28896316.68</v>
       </c>
       <c r="O40" t="n">
-        <v>0.9010949756444936</v>
+        <v>1.124438604401397</v>
       </c>
       <c r="P40" t="n">
-        <v>-0.0154083063419491</v>
+        <v>-0.0130970052862066</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>0.4056429181780134</v>
       </c>
       <c r="S40" t="n">
-        <v>0.0599177133413372</v>
+        <v>0.060634217445216</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -453,200 +453,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>tier</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>gap_pct</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>volume_trend</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>premarket_score</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>premarket_action</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>buy_amount_usd</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>shares_to_buy</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>stop_loss</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>trim_price</t>
+          <t>status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>983.1199951171876</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.0548345836529482</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.5614175632723557</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>PREMARKET BUY</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0.0122060379807142</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>803.5899658203126</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>1252.4150390625</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>ALAB</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>361.7799987792969</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.0828062753684488</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.5222684036760127</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>PREMARKET BUY</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0.033169329538642</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>268.7313014439174</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>501.3530447823661</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CRDO</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>236.1799926757812</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.06596166699561611</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.4711035474840427</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>PREMARKET BUY</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0.0508087068004661</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>182.3964189801897</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>316.8553532191685</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>No data available yet</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1252,7 +1076,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1152.5400390625</v>
+        <v>1154.27001953125</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>82</v>
@@ -1272,31 +1096,31 @@
         <v>50</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>57.15185573112131</v>
+        <v>57.46465122763439</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>-0.013419399271567</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.6295299805039047</v>
+        <v>0.6297086252289054</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-7.114309765361639</v>
+        <v>-7.003906453395814</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1090.290562220982</v>
+        <v>1092.0189339774</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1235.539341517857</v>
+        <v>1237.271466936384</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>41.49965122767857</v>
+        <v>41.50072370256697</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>13.95</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.012105</v>
+        <v>0.012087</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>1.12</v>
@@ -3326,7 +3150,7 @@
         <v>-0.0092015237095138</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.5141545369292413</v>
+        <v>0.4371760260387756</v>
       </c>
       <c r="M27" s="4" t="n">
         <v>5.836006585191056</v>
@@ -3627,7 +3451,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.0130970052862066</v>
+        <v>-0.0154083063419491</v>
       </c>
       <c r="L30" s="4" t="n">
         <v>1.124438604401397</v>
@@ -4356,7 +4180,7 @@
         <v>0.0299401183926648</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.6631252334389868</v>
+        <v>0.7093138011733972</v>
       </c>
       <c r="M38" s="4" t="n">
         <v>-0.1142613107714314</v>
@@ -4446,7 +4270,7 @@
         <v>0.0251036384349932</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>0.4949668589162981</v>
+        <v>0.4382935699341941</v>
       </c>
       <c r="M39" s="4" t="n">
         <v>-0.3245621974062178</v>
@@ -5688,13 +5512,13 @@
         <v>5.612490428240474</v>
       </c>
       <c r="M11" t="n">
-        <v>802990</v>
+        <v>681707</v>
       </c>
       <c r="N11" t="n">
-        <v>1561767.8</v>
+        <v>1559342.14</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5141545369292413</v>
+        <v>0.4371760260387756</v>
       </c>
       <c r="P11" t="n">
         <v>-0.0092015237095138</v>
@@ -6131,46 +5955,46 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1152.5400390625</v>
+        <v>1154.27001953125</v>
       </c>
       <c r="C18" t="n">
-        <v>1097.726402587891</v>
+        <v>1097.761002197265</v>
       </c>
       <c r="D18" t="n">
-        <v>1000.555503234863</v>
+        <v>1000.564153137207</v>
       </c>
       <c r="E18" t="n">
-        <v>57.15185573112131</v>
+        <v>57.46465122763439</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0172462833737863</v>
+        <v>0.0187731858175199</v>
       </c>
       <c r="G18" t="n">
-        <v>0.24936589600271</v>
+        <v>0.2512412135840107</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0661794995952822</v>
+        <v>0.067779851555273</v>
       </c>
       <c r="I18" t="n">
-        <v>27.4657290256198</v>
+        <v>27.60373316557707</v>
       </c>
       <c r="J18" t="n">
-        <v>34.58003879098143</v>
+        <v>34.60763961897288</v>
       </c>
       <c r="K18" t="n">
-        <v>-7.114309765361639</v>
+        <v>-7.003906453395814</v>
       </c>
       <c r="L18" t="n">
         <v>-3.468572970271296</v>
       </c>
       <c r="M18" t="n">
-        <v>2014654</v>
+        <v>2015233</v>
       </c>
       <c r="N18" t="n">
-        <v>3200251.08</v>
+        <v>3200262.66</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6295299805039047</v>
+        <v>0.6297086252289054</v>
       </c>
       <c r="P18" t="n">
         <v>-0.013419399271567</v>
@@ -6181,10 +6005,10 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>41.49965122767857</v>
+        <v>41.50072370256697</v>
       </c>
       <c r="S18" t="n">
-        <v>0.03600712324184</v>
+        <v>0.0359540861326541</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -7436,13 +7260,13 @@
         <v>-0.125728364005369</v>
       </c>
       <c r="M37" t="n">
-        <v>22000846</v>
+        <v>23555320</v>
       </c>
       <c r="N37" t="n">
-        <v>33177512.92</v>
+        <v>33208602.4</v>
       </c>
       <c r="O37" t="n">
-        <v>0.6631252334389868</v>
+        <v>0.7093138011733972</v>
       </c>
       <c r="P37" t="n">
         <v>0.0299401183926648</v>
@@ -7504,13 +7328,13 @@
         <v>-0.3462640846580571</v>
       </c>
       <c r="M38" t="n">
-        <v>6149099</v>
+        <v>5438806</v>
       </c>
       <c r="N38" t="n">
-        <v>12423253.98</v>
+        <v>12409048.12</v>
       </c>
       <c r="O38" t="n">
-        <v>0.4949668589162981</v>
+        <v>0.4382935699341941</v>
       </c>
       <c r="P38" t="n">
         <v>0.0251036384349932</v>
@@ -7649,7 +7473,7 @@
         <v>1.124438604401397</v>
       </c>
       <c r="P40" t="n">
-        <v>-0.0130970052862066</v>
+        <v>-0.0154083063419491</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -741,41 +741,67 @@
         <v>10.46220506940569</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>9.74</v>
+        <v>0</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>0.053341</v>
+        <v>0</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="U2" s="2" t="inlineStr"/>
+        <v>9.369999999999999</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>-0.0273823999246683</v>
+      </c>
       <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>No exit trigger</t>
+        </is>
+      </c>
       <c r="Z2" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
-      <c r="AD2" s="2" t="inlineStr"/>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>Do not average down</t>
+        </is>
+      </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>Do not average down</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -835,16 +861,16 @@
         <v>6.948570251464844</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.065872</v>
+        <v>0.044229</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U3" s="2" t="inlineStr"/>
       <c r="V3" s="2" t="inlineStr"/>
@@ -852,14 +878,14 @@
       <c r="X3" s="2" t="inlineStr"/>
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr"/>
@@ -929,16 +955,16 @@
         <v>38.05143519810268</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>10.72</v>
+        <v>7.2</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.019555</v>
+        <v>0.01313</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" s="2" t="inlineStr"/>
@@ -946,14 +972,14 @@
       <c r="X4" s="2" t="inlineStr"/>
       <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -1023,16 +1049,16 @@
         <v>89.7650146484375</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>6.11</v>
+        <v>4.1</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.006217</v>
+        <v>0.004174</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U5" s="2" t="inlineStr"/>
       <c r="V5" s="2" t="inlineStr"/>
@@ -1040,14 +1066,14 @@
       <c r="X5" s="2" t="inlineStr"/>
       <c r="Y5" s="2" t="inlineStr"/>
       <c r="Z5" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -1076,7 +1102,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1154.27001953125</v>
+        <v>1152.5400390625</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>82</v>
@@ -1096,37 +1122,37 @@
         <v>50</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>57.46465122763439</v>
+        <v>57.15185573112131</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>-0.013419399271567</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.6297086252289054</v>
+        <v>0.6295299805039047</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-7.003906453395814</v>
+        <v>-7.114309765361639</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1092.0189339774</v>
+        <v>1090.290562220982</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1237.271466936384</v>
+        <v>1235.539341517857</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>41.50072370256697</v>
+        <v>41.49965122767857</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.012087</v>
+        <v>0.008128</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" s="2" t="inlineStr"/>
@@ -1134,14 +1160,14 @@
       <c r="X6" s="2" t="inlineStr"/>
       <c r="Y6" s="2" t="inlineStr"/>
       <c r="Z6" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -1211,16 +1237,16 @@
         <v>0.7386070660182408</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>5.86</v>
+        <v>3.93</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.755569</v>
+        <v>0.507323</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="2" t="inlineStr"/>
@@ -1228,14 +1254,14 @@
       <c r="X7" s="2" t="inlineStr"/>
       <c r="Y7" s="2" t="inlineStr"/>
       <c r="Z7" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -1305,16 +1331,16 @@
         <v>15.00356619698661</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>6.98</v>
+        <v>4.68</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.017928</v>
+        <v>0.012037</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U8" s="3" t="inlineStr"/>
       <c r="V8" s="3" t="inlineStr"/>
@@ -1322,14 +1348,14 @@
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="inlineStr"/>
       <c r="Z8" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA8" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr"/>
@@ -1381,7 +1407,7 @@
         <v>73.76093226909819</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.0129709127575936</v>
+        <v>0.0098826338563442</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>0.4283640919771998</v>
@@ -1405,13 +1431,13 @@
         <v>0</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>0.0982696803861781</v>
+        <v>0.09828562936622121</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" s="3" t="inlineStr">
@@ -1430,10 +1456,10 @@
         </is>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA9" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
@@ -1519,16 +1545,16 @@
         <v>0.6038284982953753</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>6.33</v>
+        <v>4.25</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.462108</v>
+        <v>0.31028</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="inlineStr"/>
@@ -1536,14 +1562,14 @@
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="inlineStr"/>
       <c r="Z10" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr"/>
@@ -1617,16 +1643,16 @@
         <v>13.92728751046317</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>6.98</v>
+        <v>4.68</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.025767</v>
+        <v>0.017301</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr"/>
@@ -1634,14 +1660,14 @@
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
       <c r="Z11" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr"/>
@@ -1715,16 +1741,16 @@
         <v>0.6430713449205671</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>2.73</v>
+        <v>1.83</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.433909</v>
+        <v>0.291346</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" s="3" t="inlineStr"/>
@@ -1732,14 +1758,14 @@
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="inlineStr"/>
       <c r="Z12" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr"/>
@@ -1809,16 +1835,16 @@
         <v>26.89178684779576</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>0.010376</v>
+        <v>0.006967</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U13" s="3" t="inlineStr"/>
       <c r="V13" s="3" t="inlineStr"/>
@@ -1826,14 +1852,14 @@
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="inlineStr"/>
       <c r="Z13" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr"/>
@@ -1903,16 +1929,16 @@
         <v>46.52434866768973</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>2.17</v>
+        <v>1.46</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.005998</v>
+        <v>0.004027</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U14" s="3" t="inlineStr"/>
       <c r="V14" s="3" t="inlineStr"/>
@@ -1920,14 +1946,14 @@
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="inlineStr"/>
       <c r="Z14" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr"/>
@@ -1979,7 +2005,7 @@
         <v>60.70401435938903</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.0037303974496513</v>
+        <v>-0.0040282924977889</v>
       </c>
       <c r="L15" s="4" t="n">
         <v>0.5684630349666104</v>
@@ -2003,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.0199286613858312</v>
+        <v>-0.0199286593032251</v>
       </c>
       <c r="V15" s="4" t="inlineStr"/>
       <c r="W15" s="4" t="inlineStr">
@@ -2028,10 +2054,10 @@
         </is>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB15" s="4" t="inlineStr">
         <is>
@@ -2123,10 +2149,10 @@
         <v>0</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U16" s="4" t="inlineStr"/>
       <c r="V16" s="4" t="inlineStr"/>
@@ -2134,14 +2160,14 @@
       <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="4" t="inlineStr"/>
       <c r="Z16" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB16" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC16" s="4" t="inlineStr"/>
@@ -2217,10 +2243,10 @@
         <v>0</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U17" s="4" t="inlineStr"/>
       <c r="V17" s="4" t="inlineStr"/>
@@ -2228,14 +2254,14 @@
       <c r="X17" s="4" t="inlineStr"/>
       <c r="Y17" s="4" t="inlineStr"/>
       <c r="Z17" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB17" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC17" s="4" t="inlineStr"/>
@@ -2311,13 +2337,13 @@
         <v>0</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.0082273522227855</v>
+        <v>0.008241993405466001</v>
       </c>
       <c r="V18" s="4" t="inlineStr"/>
       <c r="W18" s="4" t="inlineStr">
@@ -2336,10 +2362,10 @@
         </is>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB18" s="4" t="inlineStr">
         <is>
@@ -2427,10 +2453,10 @@
         <v>0</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U19" s="4" t="inlineStr"/>
       <c r="V19" s="4" t="inlineStr"/>
@@ -2438,14 +2464,14 @@
       <c r="X19" s="4" t="inlineStr"/>
       <c r="Y19" s="4" t="inlineStr"/>
       <c r="Z19" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB19" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC19" s="4" t="inlineStr"/>
@@ -2521,10 +2547,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U20" s="4" t="inlineStr"/>
       <c r="V20" s="4" t="inlineStr"/>
@@ -2532,14 +2558,14 @@
       <c r="X20" s="4" t="inlineStr"/>
       <c r="Y20" s="4" t="inlineStr"/>
       <c r="Z20" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB20" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC20" s="4" t="inlineStr"/>
@@ -2615,10 +2641,10 @@
         <v>0</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U21" s="4" t="inlineStr"/>
       <c r="V21" s="4" t="inlineStr"/>
@@ -2626,14 +2652,14 @@
       <c r="X21" s="4" t="inlineStr"/>
       <c r="Y21" s="4" t="inlineStr"/>
       <c r="Z21" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB21" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC21" s="4" t="inlineStr"/>
@@ -2705,10 +2731,10 @@
         <v>0</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U22" s="4" t="inlineStr"/>
       <c r="V22" s="4" t="inlineStr"/>
@@ -2716,14 +2742,14 @@
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="4" t="inlineStr"/>
       <c r="Z22" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB22" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC22" s="4" t="inlineStr"/>
@@ -2799,10 +2825,10 @@
         <v>0</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U23" s="4" t="inlineStr"/>
       <c r="V23" s="4" t="inlineStr"/>
@@ -2810,14 +2836,14 @@
       <c r="X23" s="4" t="inlineStr"/>
       <c r="Y23" s="4" t="inlineStr"/>
       <c r="Z23" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB23" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC23" s="4" t="inlineStr"/>
@@ -2893,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U24" s="4" t="inlineStr"/>
       <c r="V24" s="4" t="inlineStr"/>
@@ -2904,14 +2930,14 @@
       <c r="X24" s="4" t="inlineStr"/>
       <c r="Y24" s="4" t="inlineStr"/>
       <c r="Z24" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB24" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC24" s="4" t="inlineStr"/>
@@ -2963,7 +2989,7 @@
         <v>31.74508778177839</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.0471295624603021</v>
+        <v>0.0469355722360184</v>
       </c>
       <c r="L25" s="4" t="n">
         <v>0.6930888135448485</v>
@@ -2987,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U25" s="4" t="inlineStr"/>
       <c r="V25" s="4" t="inlineStr"/>
@@ -2998,14 +3024,14 @@
       <c r="X25" s="4" t="inlineStr"/>
       <c r="Y25" s="4" t="inlineStr"/>
       <c r="Z25" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB25" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC25" s="4" t="inlineStr"/>
@@ -3081,10 +3107,10 @@
         <v>0</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U26" s="4" t="inlineStr"/>
       <c r="V26" s="4" t="inlineStr"/>
@@ -3092,14 +3118,14 @@
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="inlineStr"/>
       <c r="Z26" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB26" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC26" s="4" t="inlineStr"/>
@@ -3171,10 +3197,10 @@
         <v>0</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U27" s="4" t="inlineStr"/>
       <c r="V27" s="4" t="inlineStr"/>
@@ -3182,14 +3208,14 @@
       <c r="X27" s="4" t="inlineStr"/>
       <c r="Y27" s="4" t="inlineStr"/>
       <c r="Z27" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB27" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC27" s="4" t="inlineStr"/>
@@ -3265,13 +3291,13 @@
         <v>0</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.0417347172383101</v>
+        <v>-0.0417207966187322</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
@@ -3294,10 +3320,10 @@
         </is>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB28" s="4" t="inlineStr">
         <is>
@@ -3385,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U29" s="4" t="inlineStr"/>
       <c r="V29" s="4" t="inlineStr"/>
@@ -3396,14 +3422,14 @@
       <c r="X29" s="4" t="inlineStr"/>
       <c r="Y29" s="4" t="inlineStr"/>
       <c r="Z29" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB29" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC29" s="4" t="inlineStr"/>
@@ -3475,10 +3501,10 @@
         <v>0</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U30" s="4" t="inlineStr"/>
       <c r="V30" s="4" t="inlineStr"/>
@@ -3486,14 +3512,14 @@
       <c r="X30" s="4" t="inlineStr"/>
       <c r="Y30" s="4" t="inlineStr"/>
       <c r="Z30" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB30" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC30" s="4" t="inlineStr"/>
@@ -3569,10 +3595,10 @@
         <v>0</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U31" s="4" t="inlineStr"/>
       <c r="V31" s="4" t="inlineStr"/>
@@ -3580,14 +3606,14 @@
       <c r="X31" s="4" t="inlineStr"/>
       <c r="Y31" s="4" t="inlineStr"/>
       <c r="Z31" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB31" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC31" s="4" t="inlineStr"/>
@@ -3659,31 +3685,61 @@
         <v>0</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="U32" s="4" t="inlineStr"/>
-      <c r="V32" s="4" t="inlineStr"/>
-      <c r="W32" s="4" t="inlineStr"/>
-      <c r="X32" s="4" t="inlineStr"/>
-      <c r="Y32" s="4" t="inlineStr"/>
+        <v>9.369999999999999</v>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>-0.279152934416247</v>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="W32" s="4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="X32" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Y32" s="4" t="inlineStr">
+        <is>
+          <t>Holding down 15%+</t>
+        </is>
+      </c>
       <c r="Z32" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB32" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
-        </is>
-      </c>
-      <c r="AC32" s="4" t="inlineStr"/>
-      <c r="AD32" s="4" t="inlineStr"/>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AC32" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AD32" s="4" t="inlineStr">
+        <is>
+          <t>Do not average down</t>
+        </is>
+      </c>
       <c r="AE32" s="4" t="inlineStr"/>
-      <c r="AF32" s="4" t="inlineStr"/>
+      <c r="AF32" s="4" t="inlineStr">
+        <is>
+          <t>Do not average down; Holding down 15%+</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -3749,31 +3805,61 @@
         <v>0</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="U33" s="4" t="inlineStr"/>
-      <c r="V33" s="4" t="inlineStr"/>
-      <c r="W33" s="4" t="inlineStr"/>
-      <c r="X33" s="4" t="inlineStr"/>
-      <c r="Y33" s="4" t="inlineStr"/>
+        <v>9.369999999999999</v>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>-0.1783850965372815</v>
+      </c>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="W33" s="4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="X33" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Y33" s="4" t="inlineStr">
+        <is>
+          <t>Holding down 15%+</t>
+        </is>
+      </c>
       <c r="Z33" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB33" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
-        </is>
-      </c>
-      <c r="AC33" s="4" t="inlineStr"/>
-      <c r="AD33" s="4" t="inlineStr"/>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AD33" s="4" t="inlineStr">
+        <is>
+          <t>Do not average down</t>
+        </is>
+      </c>
       <c r="AE33" s="4" t="inlineStr"/>
-      <c r="AF33" s="4" t="inlineStr"/>
+      <c r="AF33" s="4" t="inlineStr">
+        <is>
+          <t>Do not average down; Holding down 15%+</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -3815,7 +3901,7 @@
         <v>45.60143417545741</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.0167310315006482</v>
+        <v>0.018661516252568</v>
       </c>
       <c r="L34" s="4" t="n">
         <v>1.233258246517002</v>
@@ -3839,10 +3925,10 @@
         <v>0</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U34" s="4" t="inlineStr"/>
       <c r="V34" s="4" t="inlineStr"/>
@@ -3850,14 +3936,14 @@
       <c r="X34" s="4" t="inlineStr"/>
       <c r="Y34" s="4" t="inlineStr"/>
       <c r="Z34" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB34" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC34" s="4" t="inlineStr"/>
@@ -3923,10 +4009,10 @@
         <v>0</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U35" s="4" t="inlineStr"/>
       <c r="V35" s="4" t="inlineStr"/>
@@ -3934,14 +4020,14 @@
       <c r="X35" s="4" t="inlineStr"/>
       <c r="Y35" s="4" t="inlineStr"/>
       <c r="Z35" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB35" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC35" s="4" t="inlineStr"/>
@@ -4021,10 +4107,10 @@
         <v>0</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U36" s="4" t="inlineStr"/>
       <c r="V36" s="4" t="inlineStr"/>
@@ -4032,14 +4118,14 @@
       <c r="X36" s="4" t="inlineStr"/>
       <c r="Y36" s="4" t="inlineStr"/>
       <c r="Z36" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA36" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB36" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC36" s="4" t="inlineStr"/>
@@ -4111,10 +4197,10 @@
         <v>0</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U37" s="4" t="inlineStr"/>
       <c r="V37" s="4" t="inlineStr"/>
@@ -4122,14 +4208,14 @@
       <c r="X37" s="4" t="inlineStr"/>
       <c r="Y37" s="4" t="inlineStr"/>
       <c r="Z37" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB37" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC37" s="4" t="inlineStr"/>
@@ -4180,7 +4266,7 @@
         <v>0.0299401183926648</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.7093138011733972</v>
+        <v>0.6631252334389868</v>
       </c>
       <c r="M38" s="4" t="n">
         <v>-0.1142613107714314</v>
@@ -4201,10 +4287,10 @@
         <v>0</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U38" s="4" t="inlineStr"/>
       <c r="V38" s="4" t="inlineStr"/>
@@ -4212,14 +4298,14 @@
       <c r="X38" s="4" t="inlineStr"/>
       <c r="Y38" s="4" t="inlineStr"/>
       <c r="Z38" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB38" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC38" s="4" t="inlineStr"/>
@@ -4291,10 +4377,10 @@
         <v>0</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U39" s="4" t="inlineStr"/>
       <c r="V39" s="4" t="inlineStr"/>
@@ -4302,14 +4388,14 @@
       <c r="X39" s="4" t="inlineStr"/>
       <c r="Y39" s="4" t="inlineStr"/>
       <c r="Z39" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB39" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC39" s="4" t="inlineStr"/>
@@ -4381,10 +4467,10 @@
         <v>0</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>13.95</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U40" s="4" t="inlineStr"/>
       <c r="V40" s="4" t="inlineStr"/>
@@ -4392,14 +4478,14 @@
       <c r="X40" s="4" t="inlineStr"/>
       <c r="Y40" s="4" t="inlineStr"/>
       <c r="Z40" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB40" s="4" t="inlineStr">
         <is>
-          <t>6 open slot(s)</t>
+          <t>3 open slot(s)</t>
         </is>
       </c>
       <c r="AC40" s="4" t="inlineStr"/>
@@ -4418,11 +4504,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -4476,113 +4562,197 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BLZE</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.74662492</v>
+        <v>0.0958926225503501</v>
       </c>
       <c r="C2" t="n">
-        <v>15.06915790595363</v>
+        <v>187.7099564207744</v>
       </c>
       <c r="D2" t="n">
-        <v>11.251008816</v>
+        <v>17.99999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>16.54999923706055</v>
+        <v>182.5700073242188</v>
       </c>
       <c r="F2" t="n">
-        <v>12.35664185637039</v>
+        <v>17.50711680135596</v>
       </c>
       <c r="G2" t="n">
-        <v>1.105633040370392</v>
+        <v>-0.4928831986440301</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0982696803861781</v>
+        <v>-0.0273823999246683</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05285969</v>
+        <v>0.0050785182274897</v>
       </c>
       <c r="C3" t="n">
-        <v>366.8202462424582</v>
+        <v>83.76186873531681</v>
       </c>
       <c r="D3" t="n">
-        <v>19.39000450210001</v>
+        <v>0.4253861771409128</v>
       </c>
       <c r="E3" t="n">
-        <v>359.510009765625</v>
+        <v>68.81999969482422</v>
       </c>
       <c r="F3" t="n">
-        <v>19.00358766810791</v>
+        <v>0.3495036228660059</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3864168339920937</v>
+        <v>-0.0758825542749068</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0199286613858312</v>
+        <v>-0.1783850965372815</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>BLZE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6115135</v>
+        <v>0.7472324324324323</v>
       </c>
       <c r="C4" t="n">
-        <v>18.39862725025694</v>
+        <v>15.06893907608617</v>
       </c>
       <c r="D4" t="n">
-        <v>11.251008945</v>
+        <v>11.26</v>
       </c>
       <c r="E4" t="n">
-        <v>18.54999923706055</v>
+        <v>16.54999923706055</v>
       </c>
       <c r="F4" t="n">
-        <v>11.34357495845223</v>
+        <v>12.36669618666365</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0925660134522257</v>
+        <v>1.106696186663651</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0082273522227855</v>
+        <v>0.09828562936622121</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0528596778390104</v>
+      </c>
+      <c r="C5" t="n">
+        <v>366.8202454629822</v>
+      </c>
+      <c r="D5" t="n">
+        <v>19.38999999999995</v>
+      </c>
+      <c r="E5" t="n">
+        <v>359.510009765625</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19.00358329611042</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.3864167038895338</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.0199286593032251</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>IONQ</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0074388983079891</v>
+      </c>
+      <c r="C6" t="n">
+        <v>54.50532129684083</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4054595423714718</v>
+      </c>
+      <c r="E6" t="n">
+        <v>39.29000091552734</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2922743213314068</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.113185221040065</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.279152934416247</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.612011068068622</v>
+      </c>
+      <c r="C7" t="n">
+        <v>18.39836007465386</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="E7" t="n">
+        <v>18.54999923706055</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11.35280484574555</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0928048457455474</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.008241993405466001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0.02721351</v>
-      </c>
-      <c r="C5" t="n">
-        <v>413.4345674446258</v>
-      </c>
-      <c r="D5" t="n">
-        <v>11.2510057355</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="B8" t="n">
+        <v>0.0272356606329269</v>
+      </c>
+      <c r="C8" t="n">
+        <v>413.4285616111345</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11.25999999999997</v>
+      </c>
+      <c r="E8" t="n">
         <v>396.1799926757813</v>
       </c>
-      <c r="F5" t="n">
-        <v>10.7814481924823</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.4695575430176983</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.0417347172383101</v>
+      <c r="F8" t="n">
+        <v>10.79022383007304</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.4697761699269236</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.0417207966187322</v>
       </c>
     </row>
   </sheetData>
@@ -4686,25 +4856,25 @@
         <v>113.88</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>55.81</v>
+        <v>37.47</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>53.49</v>
+        <v>71.66</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>109.29</v>
+        <v>109.13</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-4.59</v>
+        <v>-4.75</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.0402872964926867</v>
+        <v>-0.0416806032301894</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-3.16</v>
+        <v>-3.06</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0.34</v>
+        <v>-0.34</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>0</v>
@@ -4719,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>-1.58</v>
+        <v>-1.53</v>
       </c>
     </row>
   </sheetData>
@@ -5453,7 +5623,7 @@
         <v>0.4283640919771998</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0129709127575936</v>
+        <v>0.0098826338563442</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -5725,7 +5895,7 @@
         <v>0.5684630349666104</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0037303974496513</v>
+        <v>-0.0040282924977889</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -5793,7 +5963,7 @@
         <v>0.6930888135448485</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0471295624603021</v>
+        <v>0.0469355722360184</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -5929,7 +6099,7 @@
         <v>1.233258246517002</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0167310315006482</v>
+        <v>0.018661516252568</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -5955,46 +6125,46 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1154.27001953125</v>
+        <v>1152.5400390625</v>
       </c>
       <c r="C18" t="n">
-        <v>1097.761002197265</v>
+        <v>1097.726402587891</v>
       </c>
       <c r="D18" t="n">
-        <v>1000.564153137207</v>
+        <v>1000.555503234863</v>
       </c>
       <c r="E18" t="n">
-        <v>57.46465122763439</v>
+        <v>57.15185573112131</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0187731858175199</v>
+        <v>0.0172462833737863</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2512412135840107</v>
+        <v>0.24936589600271</v>
       </c>
       <c r="H18" t="n">
-        <v>0.067779851555273</v>
+        <v>0.0661794995952822</v>
       </c>
       <c r="I18" t="n">
-        <v>27.60373316557707</v>
+        <v>27.4657290256198</v>
       </c>
       <c r="J18" t="n">
-        <v>34.60763961897288</v>
+        <v>34.58003879098143</v>
       </c>
       <c r="K18" t="n">
-        <v>-7.003906453395814</v>
+        <v>-7.114309765361639</v>
       </c>
       <c r="L18" t="n">
         <v>-3.468572970271296</v>
       </c>
       <c r="M18" t="n">
-        <v>2015233</v>
+        <v>2014654</v>
       </c>
       <c r="N18" t="n">
-        <v>3200262.66</v>
+        <v>3200251.08</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6297086252289054</v>
+        <v>0.6295299805039047</v>
       </c>
       <c r="P18" t="n">
         <v>-0.013419399271567</v>
@@ -6005,10 +6175,10 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>41.50072370256697</v>
+        <v>41.49965122767857</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0359540861326541</v>
+        <v>0.03600712324184</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -7260,13 +7430,13 @@
         <v>-0.125728364005369</v>
       </c>
       <c r="M37" t="n">
-        <v>23555320</v>
+        <v>22000846</v>
       </c>
       <c r="N37" t="n">
-        <v>33208602.4</v>
+        <v>33177512.92</v>
       </c>
       <c r="O37" t="n">
-        <v>0.7093138011733972</v>
+        <v>0.6631252334389868</v>
       </c>
       <c r="P37" t="n">
         <v>0.0299401183926648</v>
@@ -7503,7 +7673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7512,8 +7682,8 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
@@ -7596,10 +7766,10 @@
         <v>0.20096</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02721351</v>
+        <v>0.0272356606329269</v>
       </c>
       <c r="H2" t="n">
-        <v>11.0500457355</v>
+        <v>11.05904</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -7636,10 +7806,10 @@
         <v>0.20996</v>
       </c>
       <c r="G3" t="n">
-        <v>0.13442881</v>
+        <v>0.134428710462287</v>
       </c>
       <c r="H3" t="n">
-        <v>11.050048182</v>
+        <v>11.05004</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
@@ -7676,10 +7846,10 @@
         <v>0.20096</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6115135</v>
+        <v>0.612011068068622</v>
       </c>
       <c r="H4" t="n">
-        <v>11.050048945</v>
+        <v>11.05904</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -7716,10 +7886,10 @@
         <v>0.20096</v>
       </c>
       <c r="G5" t="n">
-        <v>0.74662492</v>
+        <v>0.7472324324324323</v>
       </c>
       <c r="H5" t="n">
-        <v>11.050048816</v>
+        <v>11.05904</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -7756,10 +7926,10 @@
         <v>0.21033</v>
       </c>
       <c r="G6" t="n">
-        <v>0.20695315</v>
+        <v>0.2069522705603021</v>
       </c>
       <c r="H6" t="n">
-        <v>11.06971704035</v>
+        <v>11.06967</v>
       </c>
       <c r="I6" t="n">
         <v>5</v>
@@ -7796,10 +7966,10 @@
         <v>0.18329</v>
       </c>
       <c r="G7" t="n">
-        <v>0.20695315</v>
+        <v>0.199513372252313</v>
       </c>
       <c r="H7" t="n">
-        <v>9.819720014350001</v>
+        <v>9.466710000000001</v>
       </c>
       <c r="I7" t="n">
         <v>5</v>
@@ -7836,10 +8006,10 @@
         <v>0.18516</v>
       </c>
       <c r="G8" t="n">
-        <v>0.13442881</v>
+        <v>0.1293501922347972</v>
       </c>
       <c r="H8" t="n">
-        <v>9.92998733708</v>
+        <v>9.55484</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -7876,10 +8046,10 @@
         <v>0.17994</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02592479</v>
+        <v>0.0259247720988803</v>
       </c>
       <c r="H9" t="n">
-        <v>9.470066539099999</v>
+        <v>9.47006</v>
       </c>
       <c r="I9" t="n">
         <v>6</v>
@@ -7916,10 +8086,10 @@
         <v>0.18161</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0269349</v>
+        <v>0.0269349057401301</v>
       </c>
       <c r="H10" t="n">
-        <v>9.558387962999999</v>
+        <v>9.558389999999999</v>
       </c>
       <c r="I10" t="n">
         <v>7</v>
@@ -7927,6 +8097,46 @@
       <c r="J10" t="inlineStr">
         <is>
           <t>Imported current workbook buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>184.21</v>
+      </c>
+      <c r="E11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0958926225503501</v>
+      </c>
+      <c r="H11" t="n">
+        <v>17.66438</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>First trade logged in Github</t>
         </is>
       </c>
     </row>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -747,10 +747,10 @@
         <v>0</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>-0.0273823999246683</v>
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -861,16 +861,16 @@
         <v>6.948570251464844</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.044229</v>
+        <v>0.017777</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U3" s="2" t="inlineStr"/>
       <c r="V3" s="2" t="inlineStr"/>
@@ -878,14 +878,14 @@
       <c r="X3" s="2" t="inlineStr"/>
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr"/>
@@ -940,7 +940,7 @@
         <v>0.061434448913282</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.6129772245272506</v>
+        <v>0.6202720503267012</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-3.059340407885674</v>
@@ -955,16 +955,16 @@
         <v>38.05143519810268</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>7.2</v>
+        <v>2.89</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.01313</v>
+        <v>0.005277</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" s="2" t="inlineStr"/>
@@ -972,14 +972,14 @@
       <c r="X4" s="2" t="inlineStr"/>
       <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         <v>44.79774534214121</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.0548345836529482</v>
+        <v>0.0543756800501934</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.5614175632723557</v>
+        <v>0.5629273561792737</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-24.97051779036101</v>
@@ -1049,16 +1049,16 @@
         <v>89.7650146484375</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>4.1</v>
+        <v>1.65</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.004174</v>
+        <v>0.001678</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U5" s="2" t="inlineStr"/>
       <c r="V5" s="2" t="inlineStr"/>
@@ -1066,14 +1066,14 @@
       <c r="X5" s="2" t="inlineStr"/>
       <c r="Y5" s="2" t="inlineStr"/>
       <c r="Z5" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -1128,7 +1128,7 @@
         <v>-0.013419399271567</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.6295299805039047</v>
+        <v>0.8194228060863006</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-7.114309765361639</v>
@@ -1143,16 +1143,16 @@
         <v>41.49965122767857</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.008128</v>
+        <v>0.003267</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" s="2" t="inlineStr"/>
@@ -1160,14 +1160,14 @@
       <c r="X6" s="2" t="inlineStr"/>
       <c r="Y6" s="2" t="inlineStr"/>
       <c r="Z6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -1237,41 +1237,67 @@
         <v>0.7386070660182408</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.507323</v>
+        <v>0</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>9.369999999999999</v>
-      </c>
-      <c r="U7" s="2" t="inlineStr"/>
+        <v>3.77</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>-0.0670394023961399</v>
+      </c>
       <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr"/>
-      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>No exit trigger</t>
+        </is>
+      </c>
       <c r="Z7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
-      <c r="AD7" s="2" t="inlineStr"/>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>Do not average down</t>
+        </is>
+      </c>
       <c r="AE7" s="2" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum</t>
         </is>
       </c>
-      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>Do not average down</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1316,7 +1342,7 @@
         <v>0.030386704331899</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.617956632747811</v>
+        <v>0.7218869927281159</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>2.98002598495759</v>
@@ -1331,16 +1357,16 @@
         <v>15.00356619698661</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>4.68</v>
+        <v>1.88</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.012037</v>
+        <v>0.004838</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U8" s="3" t="inlineStr"/>
       <c r="V8" s="3" t="inlineStr"/>
@@ -1348,14 +1374,14 @@
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="inlineStr"/>
       <c r="Z8" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA8" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr"/>
@@ -1407,10 +1433,10 @@
         <v>73.76093226909819</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.0098826338563442</v>
+        <v>0.0129709127575936</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.4283640919771998</v>
+        <v>0.4289365013454849</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>0.1068612566533073</v>
@@ -1431,13 +1457,13 @@
         <v>0</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>0.09828562936622121</v>
+        <v>0.0475067600157948</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" s="3" t="inlineStr">
@@ -1456,10 +1482,10 @@
         </is>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
@@ -1545,16 +1571,16 @@
         <v>0.6038284982953753</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>4.25</v>
+        <v>1.71</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.31028</v>
+        <v>0.124713</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="inlineStr"/>
@@ -1562,14 +1588,14 @@
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="inlineStr"/>
       <c r="Z10" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr"/>
@@ -1643,16 +1669,16 @@
         <v>13.92728751046317</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>4.68</v>
+        <v>1.88</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.017301</v>
+        <v>0.006954</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr"/>
@@ -1660,14 +1686,14 @@
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
       <c r="Z11" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr"/>
@@ -1726,7 +1752,7 @@
         <v>0.0046656626141934</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.606299066718476</v>
+        <v>0.6141227430503577</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0.0121571690035722</v>
@@ -1741,16 +1767,16 @@
         <v>0.6430713449205671</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>1.83</v>
+        <v>0.74</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.291346</v>
+        <v>0.117102</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" s="3" t="inlineStr"/>
@@ -1758,14 +1784,14 @@
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="inlineStr"/>
       <c r="Z12" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr"/>
@@ -1820,7 +1846,7 @@
         <v>0.06596166699561611</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.4711035474840427</v>
+        <v>0.4759122849309471</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>-4.82835811389501</v>
@@ -1835,16 +1861,16 @@
         <v>26.89178684779576</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>1.65</v>
+        <v>0.66</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>0.006967</v>
+        <v>0.0028</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U13" s="3" t="inlineStr"/>
       <c r="V13" s="3" t="inlineStr"/>
@@ -1852,14 +1878,14 @@
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="inlineStr"/>
       <c r="Z13" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr"/>
@@ -1929,16 +1955,16 @@
         <v>46.52434866768973</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>1.46</v>
+        <v>0.59</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.004027</v>
+        <v>0.001619</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U14" s="3" t="inlineStr"/>
       <c r="V14" s="3" t="inlineStr"/>
@@ -1946,14 +1972,14 @@
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="inlineStr"/>
       <c r="Z14" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr"/>
@@ -2005,7 +2031,7 @@
         <v>60.70401435938903</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.0040282924977889</v>
+        <v>-0.0037303974496513</v>
       </c>
       <c r="L15" s="4" t="n">
         <v>0.5684630349666104</v>
@@ -2029,10 +2055,10 @@
         <v>0</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>-0.0199286593032251</v>
@@ -2054,10 +2080,10 @@
         </is>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB15" s="4" t="inlineStr">
         <is>
@@ -2128,7 +2154,7 @@
         <v>-0.0071165521984971</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.5759421788162938</v>
+        <v>0.6096913242789158</v>
       </c>
       <c r="M16" s="4" t="n">
         <v>1.741369739733408</v>
@@ -2149,10 +2175,10 @@
         <v>0</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U16" s="4" t="inlineStr"/>
       <c r="V16" s="4" t="inlineStr"/>
@@ -2160,14 +2186,14 @@
       <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="4" t="inlineStr"/>
       <c r="Z16" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB16" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC16" s="4" t="inlineStr"/>
@@ -2243,10 +2269,10 @@
         <v>0</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U17" s="4" t="inlineStr"/>
       <c r="V17" s="4" t="inlineStr"/>
@@ -2254,14 +2280,14 @@
       <c r="X17" s="4" t="inlineStr"/>
       <c r="Y17" s="4" t="inlineStr"/>
       <c r="Z17" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB17" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC17" s="4" t="inlineStr"/>
@@ -2337,10 +2363,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U18" s="4" t="n">
         <v>0.008241993405466001</v>
@@ -2362,10 +2388,10 @@
         </is>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB18" s="4" t="inlineStr">
         <is>
@@ -2432,7 +2458,7 @@
         <v>0.0220361706931489</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.029289744141061</v>
+        <v>1.031400668318021</v>
       </c>
       <c r="M19" s="4" t="n">
         <v>-4.206871821347955</v>
@@ -2453,10 +2479,10 @@
         <v>0</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U19" s="4" t="inlineStr"/>
       <c r="V19" s="4" t="inlineStr"/>
@@ -2464,14 +2490,14 @@
       <c r="X19" s="4" t="inlineStr"/>
       <c r="Y19" s="4" t="inlineStr"/>
       <c r="Z19" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB19" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC19" s="4" t="inlineStr"/>
@@ -2523,10 +2549,10 @@
         <v>37.83287697052316</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.0470279063556459</v>
+        <v>0.0451049293978258</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.8371986766170606</v>
+        <v>0.8607449965404489</v>
       </c>
       <c r="M20" s="4" t="n">
         <v>-15.2356051912122</v>
@@ -2547,10 +2573,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U20" s="4" t="inlineStr"/>
       <c r="V20" s="4" t="inlineStr"/>
@@ -2558,14 +2584,14 @@
       <c r="X20" s="4" t="inlineStr"/>
       <c r="Y20" s="4" t="inlineStr"/>
       <c r="Z20" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB20" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC20" s="4" t="inlineStr"/>
@@ -2641,10 +2667,10 @@
         <v>0</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U21" s="4" t="inlineStr"/>
       <c r="V21" s="4" t="inlineStr"/>
@@ -2652,14 +2678,14 @@
       <c r="X21" s="4" t="inlineStr"/>
       <c r="Y21" s="4" t="inlineStr"/>
       <c r="Z21" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB21" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC21" s="4" t="inlineStr"/>
@@ -2731,10 +2757,10 @@
         <v>0</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U22" s="4" t="inlineStr"/>
       <c r="V22" s="4" t="inlineStr"/>
@@ -2742,14 +2768,14 @@
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="4" t="inlineStr"/>
       <c r="Z22" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB22" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC22" s="4" t="inlineStr"/>
@@ -2804,7 +2830,7 @@
         <v>0.0645198535414377</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.4410012102813088</v>
+        <v>0.4537013562573324</v>
       </c>
       <c r="M23" s="4" t="n">
         <v>-9.147844421365978</v>
@@ -2825,10 +2851,10 @@
         <v>0</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U23" s="4" t="inlineStr"/>
       <c r="V23" s="4" t="inlineStr"/>
@@ -2836,14 +2862,14 @@
       <c r="X23" s="4" t="inlineStr"/>
       <c r="Y23" s="4" t="inlineStr"/>
       <c r="Z23" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB23" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC23" s="4" t="inlineStr"/>
@@ -2919,10 +2945,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U24" s="4" t="inlineStr"/>
       <c r="V24" s="4" t="inlineStr"/>
@@ -2930,14 +2956,14 @@
       <c r="X24" s="4" t="inlineStr"/>
       <c r="Y24" s="4" t="inlineStr"/>
       <c r="Z24" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB24" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC24" s="4" t="inlineStr"/>
@@ -2989,10 +3015,10 @@
         <v>31.74508778177839</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.0469355722360184</v>
+        <v>0.0471295624603021</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.6930888135448485</v>
+        <v>0.6945210388425916</v>
       </c>
       <c r="M25" s="4" t="n">
         <v>-3.393139473478043</v>
@@ -3013,10 +3039,10 @@
         <v>0</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U25" s="4" t="inlineStr"/>
       <c r="V25" s="4" t="inlineStr"/>
@@ -3024,14 +3050,14 @@
       <c r="X25" s="4" t="inlineStr"/>
       <c r="Y25" s="4" t="inlineStr"/>
       <c r="Z25" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB25" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC25" s="4" t="inlineStr"/>
@@ -3107,10 +3133,10 @@
         <v>0</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U26" s="4" t="inlineStr"/>
       <c r="V26" s="4" t="inlineStr"/>
@@ -3118,14 +3144,14 @@
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="inlineStr"/>
       <c r="Z26" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB26" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC26" s="4" t="inlineStr"/>
@@ -3176,7 +3202,7 @@
         <v>-0.0092015237095138</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.4371760260387756</v>
+        <v>0.5211808135109326</v>
       </c>
       <c r="M27" s="4" t="n">
         <v>5.836006585191056</v>
@@ -3197,10 +3223,10 @@
         <v>0</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U27" s="4" t="inlineStr"/>
       <c r="V27" s="4" t="inlineStr"/>
@@ -3208,14 +3234,14 @@
       <c r="X27" s="4" t="inlineStr"/>
       <c r="Y27" s="4" t="inlineStr"/>
       <c r="Z27" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB27" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC27" s="4" t="inlineStr"/>
@@ -3291,10 +3317,10 @@
         <v>0</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U28" s="4" t="n">
         <v>-0.0417207966187322</v>
@@ -3320,10 +3346,10 @@
         </is>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB28" s="4" t="inlineStr">
         <is>
@@ -3411,10 +3437,10 @@
         <v>0</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U29" s="4" t="inlineStr"/>
       <c r="V29" s="4" t="inlineStr"/>
@@ -3422,14 +3448,14 @@
       <c r="X29" s="4" t="inlineStr"/>
       <c r="Y29" s="4" t="inlineStr"/>
       <c r="Z29" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB29" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC29" s="4" t="inlineStr"/>
@@ -3501,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U30" s="4" t="inlineStr"/>
       <c r="V30" s="4" t="inlineStr"/>
@@ -3512,14 +3538,14 @@
       <c r="X30" s="4" t="inlineStr"/>
       <c r="Y30" s="4" t="inlineStr"/>
       <c r="Z30" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB30" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC30" s="4" t="inlineStr"/>
@@ -3571,10 +3597,10 @@
         <v>26.66666562011045</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.0108459594618766</v>
+        <v>0.0112075006381963</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.3915780978295909</v>
+        <v>0.3929190728687195</v>
       </c>
       <c r="M31" s="4" t="n">
         <v>-0.0456857648926987</v>
@@ -3595,10 +3621,10 @@
         <v>0</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U31" s="4" t="inlineStr"/>
       <c r="V31" s="4" t="inlineStr"/>
@@ -3606,14 +3632,14 @@
       <c r="X31" s="4" t="inlineStr"/>
       <c r="Y31" s="4" t="inlineStr"/>
       <c r="Z31" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB31" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC31" s="4" t="inlineStr"/>
@@ -3664,7 +3690,7 @@
         <v>0.0298353862022756</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.4783985469704708</v>
+        <v>0.5932799502771825</v>
       </c>
       <c r="M32" s="4" t="n">
         <v>-1.437402043324314</v>
@@ -3685,10 +3711,10 @@
         <v>0</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U32" s="4" t="n">
         <v>-0.279152934416247</v>
@@ -3714,10 +3740,10 @@
         </is>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB32" s="4" t="inlineStr">
         <is>
@@ -3805,10 +3831,10 @@
         <v>0</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U33" s="4" t="n">
         <v>-0.1783850965372815</v>
@@ -3834,10 +3860,10 @@
         </is>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB33" s="4" t="inlineStr">
         <is>
@@ -3901,10 +3927,10 @@
         <v>45.60143417545741</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.018661516252568</v>
+        <v>0.0167310315006482</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>1.233258246517002</v>
+        <v>1.242075916545938</v>
       </c>
       <c r="M34" s="4" t="n">
         <v>-0.0671681559513998</v>
@@ -3925,10 +3951,10 @@
         <v>0</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U34" s="4" t="inlineStr"/>
       <c r="V34" s="4" t="inlineStr"/>
@@ -3936,14 +3962,14 @@
       <c r="X34" s="4" t="inlineStr"/>
       <c r="Y34" s="4" t="inlineStr"/>
       <c r="Z34" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB34" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC34" s="4" t="inlineStr"/>
@@ -4009,10 +4035,10 @@
         <v>0</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U35" s="4" t="inlineStr"/>
       <c r="V35" s="4" t="inlineStr"/>
@@ -4020,14 +4046,14 @@
       <c r="X35" s="4" t="inlineStr"/>
       <c r="Y35" s="4" t="inlineStr"/>
       <c r="Z35" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB35" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC35" s="4" t="inlineStr"/>
@@ -4086,7 +4112,7 @@
         <v>0.0323432829789085</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.7211097549224948</v>
+        <v>0.7220426106246575</v>
       </c>
       <c r="M36" s="4" t="n">
         <v>-0.2249813813743664</v>
@@ -4107,10 +4133,10 @@
         <v>0</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U36" s="4" t="inlineStr"/>
       <c r="V36" s="4" t="inlineStr"/>
@@ -4118,14 +4144,14 @@
       <c r="X36" s="4" t="inlineStr"/>
       <c r="Y36" s="4" t="inlineStr"/>
       <c r="Z36" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA36" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB36" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC36" s="4" t="inlineStr"/>
@@ -4197,10 +4223,10 @@
         <v>0</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U37" s="4" t="inlineStr"/>
       <c r="V37" s="4" t="inlineStr"/>
@@ -4208,14 +4234,14 @@
       <c r="X37" s="4" t="inlineStr"/>
       <c r="Y37" s="4" t="inlineStr"/>
       <c r="Z37" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB37" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC37" s="4" t="inlineStr"/>
@@ -4287,10 +4313,10 @@
         <v>0</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U38" s="4" t="inlineStr"/>
       <c r="V38" s="4" t="inlineStr"/>
@@ -4298,14 +4324,14 @@
       <c r="X38" s="4" t="inlineStr"/>
       <c r="Y38" s="4" t="inlineStr"/>
       <c r="Z38" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB38" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC38" s="4" t="inlineStr"/>
@@ -4377,10 +4403,10 @@
         <v>0</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U39" s="4" t="inlineStr"/>
       <c r="V39" s="4" t="inlineStr"/>
@@ -4388,14 +4414,14 @@
       <c r="X39" s="4" t="inlineStr"/>
       <c r="Y39" s="4" t="inlineStr"/>
       <c r="Z39" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB39" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC39" s="4" t="inlineStr"/>
@@ -4467,10 +4493,10 @@
         <v>0</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="U40" s="4" t="inlineStr"/>
       <c r="V40" s="4" t="inlineStr"/>
@@ -4478,14 +4504,14 @@
       <c r="X40" s="4" t="inlineStr"/>
       <c r="Y40" s="4" t="inlineStr"/>
       <c r="Z40" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB40" s="4" t="inlineStr">
         <is>
-          <t>3 open slot(s)</t>
+          <t>2 open slot(s)</t>
         </is>
       </c>
       <c r="AC40" s="4" t="inlineStr"/>
@@ -4504,7 +4530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4618,140 +4644,168 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BLZE</t>
+          <t>BFLY</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7472324324324323</v>
+        <v>1.444584151128558</v>
       </c>
       <c r="C4" t="n">
-        <v>15.06893907608617</v>
+        <v>8.306888865300923</v>
       </c>
       <c r="D4" t="n">
-        <v>11.26</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>16.54999923706055</v>
+        <v>7.75</v>
       </c>
       <c r="F4" t="n">
-        <v>12.36669618666365</v>
+        <v>11.19552717124632</v>
       </c>
       <c r="G4" t="n">
-        <v>1.106696186663651</v>
+        <v>-0.8044728287536795</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09828562936622121</v>
+        <v>-0.0670394023961399</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>BLZE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0528596778390104</v>
+        <v>1.345619017798286</v>
       </c>
       <c r="C5" t="n">
-        <v>366.8202454629822</v>
+        <v>15.79941998351495</v>
       </c>
       <c r="D5" t="n">
-        <v>19.38999999999995</v>
+        <v>21.26</v>
       </c>
       <c r="E5" t="n">
-        <v>359.510009765625</v>
+        <v>16.54999923706055</v>
       </c>
       <c r="F5" t="n">
-        <v>19.00358329611042</v>
+        <v>22.2699937179358</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3864167038895338</v>
+        <v>1.009993717935799</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0199286593032251</v>
+        <v>0.0475067600157948</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0074388983079891</v>
+        <v>0.0528596778390104</v>
       </c>
       <c r="C6" t="n">
-        <v>54.50532129684083</v>
+        <v>366.8202454629822</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4054595423714718</v>
+        <v>19.38999999999995</v>
       </c>
       <c r="E6" t="n">
-        <v>39.29000091552734</v>
+        <v>359.510009765625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2922743213314068</v>
+        <v>19.00358329611042</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.113185221040065</v>
+        <v>-0.3864167038895338</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.279152934416247</v>
+        <v>-0.0199286593032251</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.612011068068622</v>
+        <v>0.0074388983079891</v>
       </c>
       <c r="C7" t="n">
-        <v>18.39836007465386</v>
+        <v>54.50532129684083</v>
       </c>
       <c r="D7" t="n">
-        <v>11.26</v>
+        <v>0.4054595423714718</v>
       </c>
       <c r="E7" t="n">
-        <v>18.54999923706055</v>
+        <v>39.29000091552734</v>
       </c>
       <c r="F7" t="n">
-        <v>11.35280484574555</v>
+        <v>0.2922743213314068</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0928048457455474</v>
+        <v>-0.113185221040065</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008241993405466001</v>
+        <v>-0.279152934416247</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.612011068068622</v>
+      </c>
+      <c r="C8" t="n">
+        <v>18.39836007465386</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="E8" t="n">
+        <v>18.54999923706055</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11.35280484574555</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0928048457455474</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.008241993405466001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" t="n">
         <v>0.0272356606329269</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C9" t="n">
         <v>413.4285616111345</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" t="n">
         <v>11.25999999999997</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E9" t="n">
         <v>396.1799926757813</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F9" t="n">
         <v>10.79022383007304</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G9" t="n">
         <v>-0.4697761699269236</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H9" t="n">
         <v>-0.0417207966187322</v>
       </c>
     </row>
@@ -4856,25 +4910,25 @@
         <v>113.88</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>37.47</v>
+        <v>15.06</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>71.66</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>109.13</v>
+        <v>107.82</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-4.75</v>
+        <v>-6.06</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.0416806032301894</v>
+        <v>-0.0531961046130619</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>-3.06</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.34</v>
+        <v>-1.24</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>0</v>
@@ -5138,13 +5192,13 @@
         <v>-3.577422765110406</v>
       </c>
       <c r="M3" t="n">
-        <v>20834788</v>
+        <v>21085850</v>
       </c>
       <c r="N3" t="n">
-        <v>33989497.76</v>
+        <v>33994519</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6129772245272506</v>
+        <v>0.6202720503267012</v>
       </c>
       <c r="P3" t="n">
         <v>0.061434448913282</v>
@@ -5206,13 +5260,13 @@
         <v>1.780135959445799</v>
       </c>
       <c r="M4" t="n">
-        <v>28210343</v>
+        <v>29883823</v>
       </c>
       <c r="N4" t="n">
-        <v>48981206.86</v>
+        <v>49014676.46</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5759421788162938</v>
+        <v>0.6096913242789158</v>
       </c>
       <c r="P4" t="n">
         <v>-0.0071165521984971</v>
@@ -5478,13 +5532,13 @@
         <v>3.038872784042606</v>
       </c>
       <c r="M8" t="n">
-        <v>17041674</v>
+        <v>19949796</v>
       </c>
       <c r="N8" t="n">
-        <v>27577459.48</v>
+        <v>27635621.92</v>
       </c>
       <c r="O8" t="n">
-        <v>0.617956632747811</v>
+        <v>0.7218869927281159</v>
       </c>
       <c r="P8" t="n">
         <v>0.030386704331899</v>
@@ -5614,16 +5668,16 @@
         <v>0.2137816409724133</v>
       </c>
       <c r="M10" t="n">
-        <v>1688639</v>
+        <v>1690915</v>
       </c>
       <c r="N10" t="n">
-        <v>3942064.78</v>
+        <v>3942110.3</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4283640919771998</v>
+        <v>0.4289365013454849</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0098826338563442</v>
+        <v>0.0129709127575936</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -5682,13 +5736,13 @@
         <v>5.612490428240474</v>
       </c>
       <c r="M11" t="n">
-        <v>681707</v>
+        <v>814079</v>
       </c>
       <c r="N11" t="n">
-        <v>1559342.14</v>
+        <v>1561989.58</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4371760260387756</v>
+        <v>0.5211808135109326</v>
       </c>
       <c r="P11" t="n">
         <v>-0.0092015237095138</v>
@@ -5818,13 +5872,13 @@
         <v>-4.078359208904043</v>
       </c>
       <c r="M13" t="n">
-        <v>4098014</v>
+        <v>4140246</v>
       </c>
       <c r="N13" t="n">
-        <v>8698754.279999999</v>
+        <v>8699598.92</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4711035474840427</v>
+        <v>0.4759122849309471</v>
       </c>
       <c r="P13" t="n">
         <v>0.06596166699561611</v>
@@ -5895,7 +5949,7 @@
         <v>0.5684630349666104</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0040282924977889</v>
+        <v>-0.0037303974496513</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -5954,16 +6008,16 @@
         <v>-3.642499734729958</v>
       </c>
       <c r="M15" t="n">
-        <v>90554427</v>
+        <v>90744188</v>
       </c>
       <c r="N15" t="n">
-        <v>130653424.54</v>
+        <v>130657219.76</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6930888135448485</v>
+        <v>0.6945210388425916</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0469355722360184</v>
+        <v>0.0471295624603021</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -6022,13 +6076,13 @@
         <v>-1.449196605493906</v>
       </c>
       <c r="M16" t="n">
-        <v>13830161</v>
+        <v>17191181</v>
       </c>
       <c r="N16" t="n">
-        <v>28909287.22</v>
+        <v>28976507.62</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4783985469704708</v>
+        <v>0.5932799502771825</v>
       </c>
       <c r="P16" t="n">
         <v>0.0298353862022756</v>
@@ -6090,16 +6144,16 @@
         <v>-0.00688903703365</v>
       </c>
       <c r="M17" t="n">
-        <v>1312323</v>
+        <v>1321945</v>
       </c>
       <c r="N17" t="n">
-        <v>1064110.46</v>
+        <v>1064302.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.233258246517002</v>
+        <v>1.242075916545938</v>
       </c>
       <c r="P17" t="n">
-        <v>0.018661516252568</v>
+        <v>0.0167310315006482</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -6158,13 +6212,13 @@
         <v>-3.468572970271296</v>
       </c>
       <c r="M18" t="n">
-        <v>2014654</v>
+        <v>2632484</v>
       </c>
       <c r="N18" t="n">
-        <v>3200251.08</v>
+        <v>3212607.68</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6295299805039047</v>
+        <v>0.8194228060863006</v>
       </c>
       <c r="P18" t="n">
         <v>-0.013419399271567</v>
@@ -6226,13 +6280,13 @@
         <v>-0.2400474448214149</v>
       </c>
       <c r="M19" t="n">
-        <v>10365734</v>
+        <v>10379340</v>
       </c>
       <c r="N19" t="n">
-        <v>14374696.68</v>
+        <v>14374968.8</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7211097549224948</v>
+        <v>0.7220426106246575</v>
       </c>
       <c r="P19" t="n">
         <v>0.0323432829789085</v>
@@ -6294,13 +6348,13 @@
         <v>-9.60956168149287</v>
       </c>
       <c r="M20" t="n">
-        <v>20011700</v>
+        <v>20593283</v>
       </c>
       <c r="N20" t="n">
-        <v>45377880</v>
+        <v>45389511.66</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4410012102813088</v>
+        <v>0.4537013562573324</v>
       </c>
       <c r="P20" t="n">
         <v>0.0645198535414377</v>
@@ -6362,16 +6416,16 @@
         <v>-28.83193490729185</v>
       </c>
       <c r="M21" t="n">
-        <v>30387447</v>
+        <v>30470097</v>
       </c>
       <c r="N21" t="n">
-        <v>54126284.94</v>
+        <v>54127937.94</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5614175632723557</v>
+        <v>0.5629273561792737</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0548345836529482</v>
+        <v>0.0543756800501934</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -6906,13 +6960,13 @@
         <v>0.0646032293232172</v>
       </c>
       <c r="M29" t="n">
-        <v>740253</v>
+        <v>749924</v>
       </c>
       <c r="N29" t="n">
-        <v>1220937.06</v>
+        <v>1221130.48</v>
       </c>
       <c r="O29" t="n">
-        <v>0.606299066718476</v>
+        <v>0.6141227430503577</v>
       </c>
       <c r="P29" t="n">
         <v>0.0046656626141934</v>
@@ -7042,13 +7096,13 @@
         <v>-3.711786847950947</v>
       </c>
       <c r="M31" t="n">
-        <v>14162977</v>
+        <v>14192635</v>
       </c>
       <c r="N31" t="n">
-        <v>13759951.54</v>
+        <v>13760544.7</v>
       </c>
       <c r="O31" t="n">
-        <v>1.029289744141061</v>
+        <v>1.031400668318021</v>
       </c>
       <c r="P31" t="n">
         <v>0.0220361706931489</v>
@@ -7178,16 +7232,16 @@
         <v>-17.58862389412036</v>
       </c>
       <c r="M33" t="n">
-        <v>3660836</v>
+        <v>3765601</v>
       </c>
       <c r="N33" t="n">
-        <v>4372720.72</v>
+        <v>4374816.02</v>
       </c>
       <c r="O33" t="n">
-        <v>0.8371986766170606</v>
+        <v>0.8607449965404489</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0470279063556459</v>
+        <v>0.0451049293978258</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -7246,16 +7300,16 @@
         <v>-0.1129581131481429</v>
       </c>
       <c r="M34" t="n">
-        <v>21822512</v>
+        <v>21897836</v>
       </c>
       <c r="N34" t="n">
-        <v>55729654.24</v>
+        <v>55731160.72</v>
       </c>
       <c r="O34" t="n">
-        <v>0.3915780978295909</v>
+        <v>0.3929190728687195</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0108459594618766</v>
+        <v>0.0112075006381963</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -7673,7 +7727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7684,7 +7738,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -7769,10 +7823,12 @@
         <v>0.0272356606329269</v>
       </c>
       <c r="H2" t="n">
-        <v>11.05904</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
+        <v>11.05903999999997</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -7809,10 +7865,12 @@
         <v>0.134428710462287</v>
       </c>
       <c r="H3" t="n">
-        <v>11.05004</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
+        <v>11.05003999999999</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -7851,8 +7909,10 @@
       <c r="H4" t="n">
         <v>11.05904</v>
       </c>
-      <c r="I4" t="n">
-        <v>3</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -7891,8 +7951,10 @@
       <c r="H5" t="n">
         <v>11.05904</v>
       </c>
-      <c r="I5" t="n">
-        <v>4</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -7931,8 +7993,10 @@
       <c r="H6" t="n">
         <v>11.06967</v>
       </c>
-      <c r="I6" t="n">
-        <v>5</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -7971,8 +8035,10 @@
       <c r="H7" t="n">
         <v>9.466710000000001</v>
       </c>
-      <c r="I7" t="n">
-        <v>5</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -8011,8 +8077,10 @@
       <c r="H8" t="n">
         <v>9.55484</v>
       </c>
-      <c r="I8" t="n">
-        <v>2</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -8049,10 +8117,12 @@
         <v>0.0259247720988803</v>
       </c>
       <c r="H9" t="n">
-        <v>9.47006</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6</v>
+        <v>9.470059999999984</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -8089,10 +8159,12 @@
         <v>0.0269349057401301</v>
       </c>
       <c r="H10" t="n">
-        <v>9.558389999999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>7</v>
+        <v>9.558389999999967</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -8129,16 +8201,94 @@
         <v>0.0958926225503501</v>
       </c>
       <c r="H11" t="n">
-        <v>17.66438</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8</v>
+        <v>17.66437999999999</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>First trade logged in Github</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BFLY</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8.151999999999999</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.22375</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.444584151128558</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11.77625</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Second trade logged in Github</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BLZE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.18646</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5983865853658537</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9.81354</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Third trade logged in Github</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -937,7 +937,7 @@
         <v>54.78446864042778</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.061434448913282</v>
+        <v>0.0624019610194614</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0.6202720503267012</v>
@@ -1339,7 +1339,7 @@
         <v>53.7959635185359</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.030386704331899</v>
+        <v>0.030087289573326</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>0.7218869927281159</v>
@@ -1433,7 +1433,7 @@
         <v>73.76093226909819</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.0129709127575936</v>
+        <v>0.0098826338563442</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>0.4289365013454849</v>
@@ -1651,7 +1651,7 @@
         <v>76.47804213242863</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.0178872721149254</v>
+        <v>-0.0192129762097973</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>0.5887063417673052</v>
@@ -1937,7 +1937,7 @@
         <v>44.89807856597774</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.0828062753684488</v>
+        <v>0.082723417254077</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>0.5222684036760127</v>
@@ -2151,7 +2151,7 @@
         <v>66.88540664531003</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.0071165521984971</v>
+        <v>-0.0071974396379796</v>
       </c>
       <c r="L16" s="4" t="n">
         <v>0.6096913242789158</v>
@@ -2733,7 +2733,7 @@
         <v>28.14872105545106</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.0369410809341018</v>
+        <v>0.0376936349020097</v>
       </c>
       <c r="L22" s="4" t="n">
         <v>0.7404378179758314</v>
@@ -3293,7 +3293,7 @@
         <v>54.31908877476581</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.0108673065184357</v>
+        <v>0.0109940121352903</v>
       </c>
       <c r="L28" s="4" t="n">
         <v>0.4681728500583489</v>
@@ -3807,7 +3807,7 @@
         <v>46.28371831749488</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.0325539640224045</v>
+        <v>0.0334417645102432</v>
       </c>
       <c r="L33" s="4" t="n">
         <v>0.3938147053188749</v>
@@ -5133,7 +5133,7 @@
         <v>0.5222684036760127</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0828062753684488</v>
+        <v>0.082723417254077</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>0.6202720503267012</v>
       </c>
       <c r="P3" t="n">
-        <v>0.061434448913282</v>
+        <v>0.0624019610194614</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>0.6096913242789158</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0071165521984971</v>
+        <v>-0.0071974396379796</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>0.7404378179758314</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0369410809341018</v>
+        <v>0.0376936349020097</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>0.3938147053188749</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0325539640224045</v>
+        <v>0.0334417645102432</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>0.7218869927281159</v>
       </c>
       <c r="P8" t="n">
-        <v>0.030386704331899</v>
+        <v>0.030087289573326</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>0.4289365013454849</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0129709127575936</v>
+        <v>0.0098826338563442</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>0.4681728500583489</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0108673065184357</v>
+        <v>0.0109940121352903</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>0.5887063417673052</v>
       </c>
       <c r="P35" t="n">
-        <v>-0.0178872721149254</v>
+        <v>-0.0192129762097973</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -7825,10 +7825,8 @@
       <c r="H2" t="n">
         <v>11.05903999999997</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I2" t="n">
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -7867,10 +7865,8 @@
       <c r="H3" t="n">
         <v>11.05003999999999</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="I3" t="n">
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -7909,10 +7905,8 @@
       <c r="H4" t="n">
         <v>11.05904</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="I4" t="n">
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -7951,10 +7945,8 @@
       <c r="H5" t="n">
         <v>11.05904</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="I5" t="n">
+        <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -7993,10 +7985,8 @@
       <c r="H6" t="n">
         <v>11.06967</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="I6" t="n">
+        <v>5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -8035,10 +8025,8 @@
       <c r="H7" t="n">
         <v>9.466710000000001</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="I7" t="n">
+        <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -8077,10 +8065,8 @@
       <c r="H8" t="n">
         <v>9.55484</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="I8" t="n">
+        <v>2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -8119,10 +8105,8 @@
       <c r="H9" t="n">
         <v>9.470059999999984</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="I9" t="n">
+        <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -8161,10 +8145,8 @@
       <c r="H10" t="n">
         <v>9.558389999999967</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="I10" t="n">
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -8203,10 +8185,8 @@
       <c r="H11" t="n">
         <v>17.66437999999999</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="I11" t="n">
+        <v>8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -8245,12 +8225,14 @@
       <c r="H12" t="n">
         <v>11.77625</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Second trade logged in Github</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8283,12 +8265,14 @@
       <c r="H13" t="n">
         <v>9.81354</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>Third trade logged in Github</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -864,7 +864,7 @@
         <v>3.77</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.017777</v>
+        <v>0.017789</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>0.3</v>
@@ -958,7 +958,7 @@
         <v>2.89</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.005277</v>
+        <v>0.005281</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>0.3</v>
@@ -1052,7 +1052,7 @@
         <v>1.65</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.001678</v>
+        <v>0.001679</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>0.3</v>
@@ -1146,7 +1146,7 @@
         <v>3.77</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.003267</v>
+        <v>0.003269</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>0.3</v>
@@ -1360,7 +1360,7 @@
         <v>1.88</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.004838</v>
+        <v>0.004841</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>0.3</v>
@@ -1574,7 +1574,7 @@
         <v>1.71</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.124713</v>
+        <v>0.124795</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>0.3</v>
@@ -1672,7 +1672,7 @@
         <v>1.88</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.006954</v>
+        <v>0.006959</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>0.3</v>
@@ -1770,7 +1770,7 @@
         <v>0.74</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.117102</v>
+        <v>0.11718</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>0.3</v>
@@ -1864,7 +1864,7 @@
         <v>0.66</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>0.0028</v>
+        <v>0.002802</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>0.3</v>
@@ -1958,7 +1958,7 @@
         <v>0.59</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.001619</v>
+        <v>0.00162</v>
       </c>
       <c r="S14" s="3" t="n">
         <v>0.3</v>
@@ -2031,7 +2031,7 @@
         <v>60.70401435938903</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.0037303974496513</v>
+        <v>-0.0040282924977889</v>
       </c>
       <c r="L15" s="4" t="n">
         <v>0.5684630349666104</v>
@@ -3015,7 +3015,7 @@
         <v>31.74508778177839</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.0471295624603021</v>
+        <v>0.0469355722360184</v>
       </c>
       <c r="L25" s="4" t="n">
         <v>0.6945210388425916</v>
@@ -3927,7 +3927,7 @@
         <v>45.60143417545741</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.0167310315006482</v>
+        <v>0.018661516252568</v>
       </c>
       <c r="L34" s="4" t="n">
         <v>1.242075916545938</v>
@@ -4907,22 +4907,22 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
-        <v>113.88</v>
+        <v>113.89</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>15.06</v>
+        <v>15.07</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>92.76000000000001</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>107.82</v>
+        <v>107.83</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>-6.06</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.0531961046130619</v>
+        <v>-0.0531914337811527</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>-3.06</v>
@@ -5949,7 +5949,7 @@
         <v>0.5684630349666104</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0037303974496513</v>
+        <v>-0.0040282924977889</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>0.6945210388425916</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0471295624603021</v>
+        <v>0.0469355722360184</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>1.242075916545938</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0167310315006482</v>
+        <v>0.018661516252568</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -747,10 +747,10 @@
         <v>0</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>-0.0273823999246683</v>
@@ -861,16 +861,16 @@
         <v>6.948570251464844</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.017789</v>
+        <v>0.020739</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U3" s="2" t="inlineStr"/>
       <c r="V3" s="2" t="inlineStr"/>
@@ -955,16 +955,16 @@
         <v>38.05143519810268</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2.89</v>
+        <v>3.37</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.005281</v>
+        <v>0.006157</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" s="2" t="inlineStr"/>
@@ -1049,16 +1049,16 @@
         <v>89.7650146484375</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.001679</v>
+        <v>0.001957</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U5" s="2" t="inlineStr"/>
       <c r="V5" s="2" t="inlineStr"/>
@@ -1143,16 +1143,16 @@
         <v>41.49965122767857</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.003269</v>
+        <v>0.003811</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" s="2" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         <v>0</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>-0.0670394023961399</v>
@@ -1357,16 +1357,16 @@
         <v>15.00356619698661</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.004841</v>
+        <v>0.005644</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U8" s="3" t="inlineStr"/>
       <c r="V8" s="3" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>0.0475067600157948</v>
@@ -1571,16 +1571,16 @@
         <v>0.6038284982953753</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>1.71</v>
+        <v>1.99</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.124795</v>
+        <v>0.145488</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="inlineStr"/>
@@ -1669,16 +1669,16 @@
         <v>13.92728751046317</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.006959</v>
+        <v>0.008111999999999999</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr"/>
@@ -1767,16 +1767,16 @@
         <v>0.6430713449205671</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.74</v>
+        <v>0.86</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.11718</v>
+        <v>0.13661</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" s="3" t="inlineStr"/>
@@ -1861,16 +1861,16 @@
         <v>26.89178684779576</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>0.002802</v>
+        <v>0.003267</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U13" s="3" t="inlineStr"/>
       <c r="V13" s="3" t="inlineStr"/>
@@ -1955,16 +1955,16 @@
         <v>46.52434866768973</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.00162</v>
+        <v>0.001888</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U14" s="3" t="inlineStr"/>
       <c r="V14" s="3" t="inlineStr"/>
@@ -2055,10 +2055,10 @@
         <v>0</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>-0.0199286593032251</v>
@@ -2175,10 +2175,10 @@
         <v>0</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U16" s="4" t="inlineStr"/>
       <c r="V16" s="4" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         <v>0</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U17" s="4" t="inlineStr"/>
       <c r="V17" s="4" t="inlineStr"/>
@@ -2363,10 +2363,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U18" s="4" t="n">
         <v>0.008241993405466001</v>
@@ -2479,10 +2479,10 @@
         <v>0</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U19" s="4" t="inlineStr"/>
       <c r="V19" s="4" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U20" s="4" t="inlineStr"/>
       <c r="V20" s="4" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         <v>0</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U21" s="4" t="inlineStr"/>
       <c r="V21" s="4" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         <v>0</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U22" s="4" t="inlineStr"/>
       <c r="V22" s="4" t="inlineStr"/>
@@ -2851,10 +2851,10 @@
         <v>0</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U23" s="4" t="inlineStr"/>
       <c r="V23" s="4" t="inlineStr"/>
@@ -2945,10 +2945,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U24" s="4" t="inlineStr"/>
       <c r="V24" s="4" t="inlineStr"/>
@@ -3039,10 +3039,10 @@
         <v>0</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U25" s="4" t="inlineStr"/>
       <c r="V25" s="4" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         <v>0</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U26" s="4" t="inlineStr"/>
       <c r="V26" s="4" t="inlineStr"/>
@@ -3223,10 +3223,10 @@
         <v>0</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U27" s="4" t="inlineStr"/>
       <c r="V27" s="4" t="inlineStr"/>
@@ -3317,10 +3317,10 @@
         <v>0</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U28" s="4" t="n">
         <v>-0.0417207966187322</v>
@@ -3437,10 +3437,10 @@
         <v>0</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U29" s="4" t="inlineStr"/>
       <c r="V29" s="4" t="inlineStr"/>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U30" s="4" t="inlineStr"/>
       <c r="V30" s="4" t="inlineStr"/>
@@ -3621,10 +3621,10 @@
         <v>0</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U31" s="4" t="inlineStr"/>
       <c r="V31" s="4" t="inlineStr"/>
@@ -3711,10 +3711,10 @@
         <v>0</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U32" s="4" t="n">
         <v>-0.279152934416247</v>
@@ -3831,10 +3831,10 @@
         <v>0</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U33" s="4" t="n">
         <v>-0.1783850965372815</v>
@@ -3951,10 +3951,10 @@
         <v>0</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U34" s="4" t="inlineStr"/>
       <c r="V34" s="4" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
         <v>0</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U35" s="4" t="inlineStr"/>
       <c r="V35" s="4" t="inlineStr"/>
@@ -4133,10 +4133,10 @@
         <v>0</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U36" s="4" t="inlineStr"/>
       <c r="V36" s="4" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         <v>0</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U37" s="4" t="inlineStr"/>
       <c r="V37" s="4" t="inlineStr"/>
@@ -4313,10 +4313,10 @@
         <v>0</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U38" s="4" t="inlineStr"/>
       <c r="V38" s="4" t="inlineStr"/>
@@ -4403,10 +4403,10 @@
         <v>0</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U39" s="4" t="inlineStr"/>
       <c r="V39" s="4" t="inlineStr"/>
@@ -4493,10 +4493,10 @@
         <v>0</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>3.77</v>
+        <v>4.39</v>
       </c>
       <c r="U40" s="4" t="inlineStr"/>
       <c r="V40" s="4" t="inlineStr"/>
@@ -4910,19 +4910,19 @@
         <v>113.89</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>15.07</v>
+        <v>17.57</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>92.76000000000001</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>107.83</v>
+        <v>110.33</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-6.06</v>
+        <v>-3.56</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.0531914337811527</v>
+        <v>-0.0312492088272499</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>-3.06</v>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -878,14 +878,14 @@
       <c r="X3" s="2" t="inlineStr"/>
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr"/>
@@ -972,14 +972,14 @@
       <c r="X4" s="2" t="inlineStr"/>
       <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -1066,14 +1066,14 @@
       <c r="X5" s="2" t="inlineStr"/>
       <c r="Y5" s="2" t="inlineStr"/>
       <c r="Z5" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -1160,14 +1160,14 @@
       <c r="X6" s="2" t="inlineStr"/>
       <c r="Y6" s="2" t="inlineStr"/>
       <c r="Z6" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1374,14 +1374,14 @@
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="inlineStr"/>
       <c r="Z8" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA8" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA9" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
@@ -1588,14 +1588,14 @@
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="inlineStr"/>
       <c r="Z10" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr"/>
@@ -1686,14 +1686,14 @@
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
       <c r="Z11" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr"/>
@@ -1784,14 +1784,14 @@
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="inlineStr"/>
       <c r="Z12" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr"/>
@@ -1878,14 +1878,14 @@
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="inlineStr"/>
       <c r="Z13" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr"/>
@@ -1972,14 +1972,14 @@
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="inlineStr"/>
       <c r="Z14" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB15" s="4" t="inlineStr">
         <is>
@@ -2186,14 +2186,14 @@
       <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="4" t="inlineStr"/>
       <c r="Z16" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB16" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC16" s="4" t="inlineStr"/>
@@ -2280,14 +2280,14 @@
       <c r="X17" s="4" t="inlineStr"/>
       <c r="Y17" s="4" t="inlineStr"/>
       <c r="Z17" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB17" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC17" s="4" t="inlineStr"/>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB18" s="4" t="inlineStr">
         <is>
@@ -2490,14 +2490,14 @@
       <c r="X19" s="4" t="inlineStr"/>
       <c r="Y19" s="4" t="inlineStr"/>
       <c r="Z19" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB19" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC19" s="4" t="inlineStr"/>
@@ -2584,14 +2584,14 @@
       <c r="X20" s="4" t="inlineStr"/>
       <c r="Y20" s="4" t="inlineStr"/>
       <c r="Z20" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB20" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC20" s="4" t="inlineStr"/>
@@ -2678,14 +2678,14 @@
       <c r="X21" s="4" t="inlineStr"/>
       <c r="Y21" s="4" t="inlineStr"/>
       <c r="Z21" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB21" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC21" s="4" t="inlineStr"/>
@@ -2768,14 +2768,14 @@
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="4" t="inlineStr"/>
       <c r="Z22" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB22" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC22" s="4" t="inlineStr"/>
@@ -2862,14 +2862,14 @@
       <c r="X23" s="4" t="inlineStr"/>
       <c r="Y23" s="4" t="inlineStr"/>
       <c r="Z23" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB23" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC23" s="4" t="inlineStr"/>
@@ -2956,14 +2956,14 @@
       <c r="X24" s="4" t="inlineStr"/>
       <c r="Y24" s="4" t="inlineStr"/>
       <c r="Z24" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB24" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC24" s="4" t="inlineStr"/>
@@ -3050,14 +3050,14 @@
       <c r="X25" s="4" t="inlineStr"/>
       <c r="Y25" s="4" t="inlineStr"/>
       <c r="Z25" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB25" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC25" s="4" t="inlineStr"/>
@@ -3144,14 +3144,14 @@
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="inlineStr"/>
       <c r="Z26" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB26" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC26" s="4" t="inlineStr"/>
@@ -3234,14 +3234,14 @@
       <c r="X27" s="4" t="inlineStr"/>
       <c r="Y27" s="4" t="inlineStr"/>
       <c r="Z27" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB27" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC27" s="4" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB28" s="4" t="inlineStr">
         <is>
@@ -3448,14 +3448,14 @@
       <c r="X29" s="4" t="inlineStr"/>
       <c r="Y29" s="4" t="inlineStr"/>
       <c r="Z29" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB29" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC29" s="4" t="inlineStr"/>
@@ -3538,14 +3538,14 @@
       <c r="X30" s="4" t="inlineStr"/>
       <c r="Y30" s="4" t="inlineStr"/>
       <c r="Z30" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB30" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC30" s="4" t="inlineStr"/>
@@ -3632,14 +3632,14 @@
       <c r="X31" s="4" t="inlineStr"/>
       <c r="Y31" s="4" t="inlineStr"/>
       <c r="Z31" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB31" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC31" s="4" t="inlineStr"/>
@@ -3716,56 +3716,26 @@
       <c r="T32" s="4" t="n">
         <v>4.39</v>
       </c>
-      <c r="U32" s="4" t="n">
-        <v>-0.279152934416247</v>
-      </c>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="W32" s="4" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="X32" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="Y32" s="4" t="inlineStr">
-        <is>
-          <t>Holding down 15%+</t>
-        </is>
-      </c>
+      <c r="U32" s="4" t="inlineStr"/>
+      <c r="V32" s="4" t="inlineStr"/>
+      <c r="W32" s="4" t="inlineStr"/>
+      <c r="X32" s="4" t="inlineStr"/>
+      <c r="Y32" s="4" t="inlineStr"/>
       <c r="Z32" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB32" s="4" t="inlineStr">
         <is>
-          <t>Already held</t>
-        </is>
-      </c>
-      <c r="AC32" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AD32" s="4" t="inlineStr">
-        <is>
-          <t>Do not average down</t>
-        </is>
-      </c>
+          <t>4 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AC32" s="4" t="inlineStr"/>
+      <c r="AD32" s="4" t="inlineStr"/>
       <c r="AE32" s="4" t="inlineStr"/>
-      <c r="AF32" s="4" t="inlineStr">
-        <is>
-          <t>Do not average down; Holding down 15%+</t>
-        </is>
-      </c>
+      <c r="AF32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -3836,56 +3806,26 @@
       <c r="T33" s="4" t="n">
         <v>4.39</v>
       </c>
-      <c r="U33" s="4" t="n">
-        <v>-0.1783850965372815</v>
-      </c>
-      <c r="V33" s="4" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="W33" s="4" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="X33" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="Y33" s="4" t="inlineStr">
-        <is>
-          <t>Holding down 15%+</t>
-        </is>
-      </c>
+      <c r="U33" s="4" t="inlineStr"/>
+      <c r="V33" s="4" t="inlineStr"/>
+      <c r="W33" s="4" t="inlineStr"/>
+      <c r="X33" s="4" t="inlineStr"/>
+      <c r="Y33" s="4" t="inlineStr"/>
       <c r="Z33" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB33" s="4" t="inlineStr">
         <is>
-          <t>Already held</t>
-        </is>
-      </c>
-      <c r="AC33" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AD33" s="4" t="inlineStr">
-        <is>
-          <t>Do not average down</t>
-        </is>
-      </c>
+          <t>4 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AC33" s="4" t="inlineStr"/>
+      <c r="AD33" s="4" t="inlineStr"/>
       <c r="AE33" s="4" t="inlineStr"/>
-      <c r="AF33" s="4" t="inlineStr">
-        <is>
-          <t>Do not average down; Holding down 15%+</t>
-        </is>
-      </c>
+      <c r="AF33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -3962,14 +3902,14 @@
       <c r="X34" s="4" t="inlineStr"/>
       <c r="Y34" s="4" t="inlineStr"/>
       <c r="Z34" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB34" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC34" s="4" t="inlineStr"/>
@@ -4046,14 +3986,14 @@
       <c r="X35" s="4" t="inlineStr"/>
       <c r="Y35" s="4" t="inlineStr"/>
       <c r="Z35" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB35" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC35" s="4" t="inlineStr"/>
@@ -4144,14 +4084,14 @@
       <c r="X36" s="4" t="inlineStr"/>
       <c r="Y36" s="4" t="inlineStr"/>
       <c r="Z36" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA36" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB36" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC36" s="4" t="inlineStr"/>
@@ -4234,14 +4174,14 @@
       <c r="X37" s="4" t="inlineStr"/>
       <c r="Y37" s="4" t="inlineStr"/>
       <c r="Z37" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB37" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC37" s="4" t="inlineStr"/>
@@ -4324,14 +4264,14 @@
       <c r="X38" s="4" t="inlineStr"/>
       <c r="Y38" s="4" t="inlineStr"/>
       <c r="Z38" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB38" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC38" s="4" t="inlineStr"/>
@@ -4414,14 +4354,14 @@
       <c r="X39" s="4" t="inlineStr"/>
       <c r="Y39" s="4" t="inlineStr"/>
       <c r="Z39" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB39" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC39" s="4" t="inlineStr"/>
@@ -4504,14 +4444,14 @@
       <c r="X40" s="4" t="inlineStr"/>
       <c r="Y40" s="4" t="inlineStr"/>
       <c r="Z40" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB40" s="4" t="inlineStr">
         <is>
-          <t>2 open slot(s)</t>
+          <t>4 open slot(s)</t>
         </is>
       </c>
       <c r="AC40" s="4" t="inlineStr"/>
@@ -4530,7 +4470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4616,196 +4556,140 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ASTS</t>
+          <t>BFLY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0050785182274897</v>
+        <v>1.444584151128558</v>
       </c>
       <c r="C3" t="n">
-        <v>83.76186873531681</v>
+        <v>8.306888865300923</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4253861771409128</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>68.81999969482422</v>
+        <v>7.75</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3495036228660059</v>
+        <v>11.19552717124632</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0758825542749068</v>
+        <v>-0.8044728287536795</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1783850965372815</v>
+        <v>-0.0670394023961399</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BFLY</t>
+          <t>BLZE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.444584151128558</v>
+        <v>1.345619017798286</v>
       </c>
       <c r="C4" t="n">
-        <v>8.306888865300923</v>
+        <v>15.79941998351495</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>21.26</v>
       </c>
       <c r="E4" t="n">
-        <v>7.75</v>
+        <v>16.54999923706055</v>
       </c>
       <c r="F4" t="n">
-        <v>11.19552717124632</v>
+        <v>22.2699937179358</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8044728287536795</v>
+        <v>1.009993717935799</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0670394023961399</v>
+        <v>0.0475067600157948</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BLZE</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.345619017798286</v>
+        <v>0.0528596778390104</v>
       </c>
       <c r="C5" t="n">
-        <v>15.79941998351495</v>
+        <v>366.8202454629822</v>
       </c>
       <c r="D5" t="n">
-        <v>21.26</v>
+        <v>19.38999999999995</v>
       </c>
       <c r="E5" t="n">
-        <v>16.54999923706055</v>
+        <v>359.510009765625</v>
       </c>
       <c r="F5" t="n">
-        <v>22.2699937179358</v>
+        <v>19.00358329611042</v>
       </c>
       <c r="G5" t="n">
-        <v>1.009993717935799</v>
+        <v>-0.3864167038895338</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0475067600157948</v>
+        <v>-0.0199286593032251</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0528596778390104</v>
+        <v>0.612011068068622</v>
       </c>
       <c r="C6" t="n">
-        <v>366.8202454629822</v>
+        <v>18.39836007465386</v>
       </c>
       <c r="D6" t="n">
-        <v>19.38999999999995</v>
+        <v>11.26</v>
       </c>
       <c r="E6" t="n">
-        <v>359.510009765625</v>
+        <v>18.54999923706055</v>
       </c>
       <c r="F6" t="n">
-        <v>19.00358329611042</v>
+        <v>11.35280484574555</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3864167038895338</v>
+        <v>0.0928048457455474</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0199286593032251</v>
+        <v>0.008241993405466001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0074388983079891</v>
+        <v>0.0272356606329269</v>
       </c>
       <c r="C7" t="n">
-        <v>54.50532129684083</v>
+        <v>413.4285616111345</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4054595423714718</v>
+        <v>11.25999999999997</v>
       </c>
       <c r="E7" t="n">
-        <v>39.29000091552734</v>
+        <v>396.1799926757813</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2922743213314068</v>
+        <v>10.79022383007304</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.113185221040065</v>
+        <v>-0.4697761699269236</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.279152934416247</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SOFI</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.612011068068622</v>
-      </c>
-      <c r="C8" t="n">
-        <v>18.39836007465386</v>
-      </c>
-      <c r="D8" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="E8" t="n">
-        <v>18.54999923706055</v>
-      </c>
-      <c r="F8" t="n">
-        <v>11.35280484574555</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.0928048457455474</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.008241993405466001</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.0272356606329269</v>
-      </c>
-      <c r="C9" t="n">
-        <v>413.4285616111345</v>
-      </c>
-      <c r="D9" t="n">
-        <v>11.25999999999997</v>
-      </c>
-      <c r="E9" t="n">
-        <v>396.1799926757813</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10.79022383007304</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.4697761699269236</v>
-      </c>
-      <c r="H9" t="n">
         <v>-0.0417207966187322</v>
       </c>
     </row>
@@ -4913,22 +4797,22 @@
         <v>17.57</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>92.76000000000001</v>
+        <v>92.12</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>110.33</v>
+        <v>109.69</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-3.56</v>
+        <v>-4.2</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.0312492088272499</v>
+        <v>-0.0368842772634376</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-3.06</v>
+        <v>-3.16</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1.24</v>
+        <v>-1.05</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>0</v>
@@ -4943,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>-1.53</v>
+        <v>-1.58</v>
       </c>
     </row>
   </sheetData>
@@ -8020,10 +7904,10 @@
         <v>0.18329</v>
       </c>
       <c r="G7" t="n">
-        <v>0.199513372252313</v>
+        <v>0.2069522705603021</v>
       </c>
       <c r="H7" t="n">
-        <v>9.466710000000001</v>
+        <v>9.819678285815774</v>
       </c>
       <c r="I7" t="n">
         <v>5</v>
@@ -8060,10 +7944,10 @@
         <v>0.18516</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1293501922347972</v>
+        <v>0.134428710462287</v>
       </c>
       <c r="H8" t="n">
-        <v>9.55484</v>
+        <v>9.929979984428217</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>

--- a/output/trading_summary.xlsx
+++ b/output/trading_summary.xlsx
@@ -51,17 +51,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF40"/>
+  <dimension ref="A1:AG40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -492,33 +492,34 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="17" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="21" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="26" customWidth="1" min="25" max="25"/>
-    <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="17" customWidth="1" min="29" max="29"/>
-    <col width="28" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="17" customWidth="1" min="30" max="30"/>
     <col width="28" customWidth="1" min="31" max="31"/>
     <col width="28" customWidth="1" min="32" max="32"/>
+    <col width="28" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -549,135 +550,140 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>sort_priority</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>action</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>trend_score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>momentum_score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>accelerator_score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>rsi_14</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>gap_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>volume_trend</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>macd_histogram</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>stop_loss</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>trim_price</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>atr</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>buy_amount_usd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>shares_to_buy</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>risk_budget_usd</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>max_position_usd</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>holding_return_pct</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>sell_signal</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>exit_action</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>exit_priority</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>exit_reason</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>position_count</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>open_slots</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>position_rule</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>add_more_signal</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>add_more_reason</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>decision_reasons</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>warnings</t>
         </is>
@@ -686,414 +692,504 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Networking</t>
+          <t>Electric Vehicles</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>182.5700073242188</v>
+        <v>396.1799926757813</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>80</v>
+        <v>43</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>62.41619801793815</v>
+        <v>50</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.0151807899125376</v>
+        <v>54.31908877476581</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.5532368110555725</v>
+        <v>0.0109940121352903</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1.604367574336539</v>
+        <v>0.4681728500583489</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>161.6455971854074</v>
+        <v>-0.0441960990382355</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>213.9566225324358</v>
+        <v>368.3292813982283</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>10.46220506940569</v>
+        <v>433.3142743791853</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0</v>
+        <v>18.56714085170201</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="S2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="2" t="n">
         <v>0.35</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="U2" s="2" t="n">
         <v>4.39</v>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="V2" s="2" t="n">
+        <v>-0.0417207966187322</v>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>Trend and score weakened</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>Do not average down</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>Do not average down; Trend and score weakened</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>182.5700073242188</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>62.41619801793815</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.0151807899125376</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>0.5532368110555725</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>1.604367574336539</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>161.6455971854074</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>213.9566225324358</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>10.46220506940569</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="V3" s="3" t="n">
         <v>-0.0273823999246683</v>
       </c>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>No exit trigger</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="n">
+      <c r="AA3" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AA2" s="2" t="n">
+      <c r="AB3" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>Already held</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AD3" s="3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="AE3" s="3" t="inlineStr">
         <is>
           <t>Do not average down</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AF3" s="3" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AG3" s="3" t="inlineStr">
         <is>
           <t>Do not average down</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>211.8000030517578</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>BFLY</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Medical Devices</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H4" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="I4" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="J4" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>50.78431291884531</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>-0.0049382666628676</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0.7423618671893375</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1181160971051057</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>6.272785867963519</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>9.965821198054725</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.7386070660182408</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>-0.0670394023961399</v>
+      </c>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>No exit trigger</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Do not average down</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Do not average down</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>BLZE</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Gaming/Digital Media</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>MOMENTUM</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>16.54999923706055</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>BUY SMALL</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J5" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>60.72211027619969</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0.0229450115312453</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0.7433680375253153</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>1.672013119512536</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>201.3771476745605</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>225.6971435546875</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>6.948570251464844</v>
-      </c>
-      <c r="Q3" s="2" t="n">
+      <c r="K5" s="4" t="n">
+        <v>73.76093226909819</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0.0098826338563442</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0.4289365013454849</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0.1068612566533073</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>13.5509990964617</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>21.04849944795881</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>1.499500070299421</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U5" s="4" t="n">
         <v>4.39</v>
       </c>
-      <c r="R3" s="2" t="n">
-        <v>0.020739</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="U3" s="2" t="inlineStr"/>
-      <c r="V3" s="2" t="inlineStr"/>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr"/>
-      <c r="Y3" s="2" t="inlineStr"/>
-      <c r="Z3" s="2" t="n">
+      <c r="V5" s="4" t="n">
+        <v>0.0475067600157948</v>
+      </c>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>No exit trigger</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AA3" s="2" t="n">
+      <c r="AB5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>4 open slot(s)</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
-      <c r="AD3" s="2" t="inlineStr"/>
-      <c r="AE3" s="2" t="inlineStr">
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AE5" s="4" t="inlineStr">
+        <is>
+          <t>Held, but not strong enough to add</t>
+        </is>
+      </c>
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AF3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>548.1300048828125</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>54.78446864042778</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0.0624019610194614</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0.6202720503267012</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>-3.059340407885674</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>491.0528520856585</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>624.2328752790179</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>38.05143519810268</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>0.006157</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="U4" s="2" t="inlineStr"/>
-      <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr"/>
-      <c r="Y4" s="2" t="inlineStr"/>
-      <c r="Z4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>4 open slot(s)</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
-      <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr">
-        <is>
-          <t>Strong trend; Positive momentum</t>
-        </is>
-      </c>
-      <c r="AF4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>983.1199951171876</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>44.79774534214121</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0.0543756800501934</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0.5629273561792737</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>-24.97051779036101</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>803.5899658203126</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>1252.4150390625</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>89.7650146484375</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0.001957</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr"/>
-      <c r="Y5" s="2" t="inlineStr"/>
-      <c r="Z5" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>4 open slot(s)</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
-      <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="inlineStr">
-        <is>
-          <t>Strong trend; Positive momentum</t>
-        </is>
-      </c>
-      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="4" t="inlineStr">
+        <is>
+          <t>RSI overbought</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Healthcare/Pharma</t>
+          <t>Internet/Software</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1102,92 +1198,121 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1152.5400390625</v>
+        <v>359.510009765625</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>80</v>
+        <v>71</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>57.15185573112131</v>
+        <v>75</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.013419399271567</v>
+        <v>60.70401435938903</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.8194228060863006</v>
+        <v>-0.0040282924977889</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-7.114309765361639</v>
+        <v>0.5684630349666104</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1090.290562220982</v>
+        <v>0.6975134915938646</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1235.539341517857</v>
+        <v>344.4660775320871</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>41.49965122767857</v>
+        <v>379.5685860770089</v>
       </c>
       <c r="Q6" s="2" t="n">
+        <v>10.02928815569196</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U6" s="2" t="n">
         <v>4.39</v>
       </c>
-      <c r="R6" s="2" t="n">
-        <v>0.003811</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="U6" s="2" t="inlineStr"/>
-      <c r="V6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="n">
+        <v>-0.0199286593032251</v>
+      </c>
       <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr"/>
-      <c r="Y6" s="2" t="inlineStr"/>
-      <c r="Z6" s="2" t="n">
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>No exit trigger</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AA6" s="2" t="n">
+      <c r="AB6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>4 open slot(s)</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
-      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>Already held</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>Strong trend; Positive momentum</t>
-        </is>
-      </c>
-      <c r="AF6" s="2" t="inlineStr"/>
+          <t>Do not average down</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>Positive momentum; MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="AG6" s="2" t="inlineStr">
+        <is>
+          <t>Do not average down</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BFLY</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1196,113 +1321,112 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7.75</v>
+        <v>18.54999923706055</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>80</v>
+        <v>67</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>50.78431291884531</v>
+        <v>75</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.0049382666628676</v>
+        <v>61.97715680636227</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.7423618671893375</v>
+        <v>0.0044125718372439</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-0.1181160971051057</v>
+        <v>1.151572395702875</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>6.272785867963519</v>
+        <v>0.0323079814383454</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>9.965821198054725</v>
+        <v>16.66714205060686</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.7386070660182408</v>
+        <v>21.37428501674108</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0</v>
+        <v>0.9414285932268416</v>
       </c>
       <c r="R7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2" t="n">
         <v>0.35</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="U7" s="2" t="n">
         <v>4.39</v>
       </c>
-      <c r="U7" s="2" t="n">
-        <v>-0.0670394023961399</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="2" t="inlineStr">
+      <c r="V7" s="2" t="n">
+        <v>0.008241993405466001</v>
+      </c>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="X7" s="2" t="inlineStr">
+      <c r="Y7" s="2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="Y7" s="2" t="inlineStr">
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>No exit trigger</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="n">
+      <c r="AA7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AA7" s="2" t="n">
+      <c r="AB7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
+      <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>Already held</t>
         </is>
       </c>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>Do not average down</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AE7" s="2" t="inlineStr">
         <is>
-          <t>Strong trend; Positive momentum</t>
+          <t>Held, but not strong enough to add</t>
         </is>
       </c>
       <c r="AF7" s="2" t="inlineStr">
         <is>
-          <t>Do not average down</t>
-        </is>
-      </c>
+          <t>MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1316,904 +1440,879 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>389.1099853515625</v>
+        <v>211.8000030517578</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>BUY SMALL</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>40</v>
+        <v>89</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
       <c r="H8" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I8" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="J8" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J8" s="3" t="n">
-        <v>53.7959635185359</v>
-      </c>
       <c r="K8" s="3" t="n">
-        <v>0.030087289573326</v>
+        <v>60.72211027619969</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.7218869927281159</v>
+        <v>0.0229450115312453</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2.98002598495759</v>
+        <v>0.7433680375253153</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>366.6046360560826</v>
+        <v>1.672013119512536</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>419.1171177455357</v>
+        <v>201.3771476745605</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>15.00356619698661</v>
+        <v>225.6971435546875</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>2.2</v>
+        <v>6.948570251464844</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.005644</v>
+        <v>4.39</v>
       </c>
       <c r="S8" s="3" t="n">
+        <v>0.020739</v>
+      </c>
+      <c r="T8" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="U8" s="3" t="n">
         <v>4.39</v>
       </c>
-      <c r="U8" s="3" t="inlineStr"/>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" s="3" t="inlineStr"/>
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="n">
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AA8" s="3" t="n">
+      <c r="AB8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AB8" s="3" t="inlineStr">
+      <c r="AC8" s="3" t="inlineStr">
         <is>
           <t>4 open slot(s)</t>
         </is>
       </c>
-      <c r="AC8" s="3" t="inlineStr"/>
       <c r="AD8" s="3" t="inlineStr"/>
-      <c r="AE8" s="3" t="inlineStr">
-        <is>
-          <t>Positive momentum; MACD/volume acceleration</t>
-        </is>
-      </c>
-      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr"/>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>BLZE</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Gaming/Digital Media</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>16.54999923706055</v>
+        <v>548.1300048828125</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>BUY SMALL</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I9" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="J9" s="3" t="n">
-        <v>73.76093226909819</v>
+        <v>50</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.0098826338563442</v>
+        <v>54.78446864042778</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.4289365013454849</v>
+        <v>0.0624019610194614</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.1068612566533073</v>
+        <v>0.6202720503267012</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>13.5509990964617</v>
+        <v>-3.059340407885674</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>21.04849944795881</v>
+        <v>491.0528520856585</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>1.499500070299421</v>
+        <v>624.2328752790179</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>38.05143519810268</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S9" s="3" t="n">
+        <v>0.006157</v>
+      </c>
+      <c r="T9" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="T9" s="3" t="n">
+      <c r="U9" s="3" t="n">
         <v>4.39</v>
       </c>
-      <c r="U9" s="3" t="n">
-        <v>0.0475067600157948</v>
-      </c>
       <c r="V9" s="3" t="inlineStr"/>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>No exit trigger</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="n">
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr"/>
+      <c r="AA9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AA9" s="3" t="n">
+      <c r="AB9" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AB9" s="3" t="inlineStr">
-        <is>
-          <t>Already held</t>
-        </is>
-      </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>Held, but not strong enough to add</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr">
-        <is>
-          <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
-        </is>
-      </c>
+          <t>4 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr"/>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>RSI overbought</t>
-        </is>
-      </c>
+          <t>Strong trend; Positive momentum</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>PUBM</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>AdTech</t>
+          <t>Healthcare/Pharma</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>13.6899995803833</v>
+        <v>1152.5400390625</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>BUY SMALL</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="I10" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I10" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="J10" s="3" t="n">
-        <v>74.99999453168354</v>
+        <v>50</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-0.0110537672736636</v>
+        <v>57.15185573112131</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.5429485849005998</v>
+        <v>-0.013419399271567</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.0301995026588746</v>
+        <v>0.8194228060863006</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>12.48234258379255</v>
+        <v>-7.114309765361639</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>15.50148507526943</v>
+        <v>1090.290562220982</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.6038284982953753</v>
+        <v>1235.539341517857</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>1.99</v>
+        <v>41.49965122767857</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.145488</v>
+        <v>4.39</v>
       </c>
       <c r="S10" s="3" t="n">
+        <v>0.003811</v>
+      </c>
+      <c r="T10" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="T10" s="3" t="n">
+      <c r="U10" s="3" t="n">
         <v>4.39</v>
       </c>
-      <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" s="3" t="inlineStr"/>
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="inlineStr"/>
-      <c r="Z10" s="3" t="n">
+      <c r="Z10" s="3" t="inlineStr"/>
+      <c r="AA10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AA10" s="3" t="n">
+      <c r="AB10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AB10" s="3" t="inlineStr">
+      <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>4 open slot(s)</t>
         </is>
       </c>
-      <c r="AC10" s="3" t="inlineStr"/>
       <c r="AD10" s="3" t="inlineStr"/>
-      <c r="AE10" s="3" t="inlineStr">
-        <is>
-          <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
-        </is>
-      </c>
+      <c r="AE10" s="3" t="inlineStr"/>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>RSI overbought</t>
-        </is>
-      </c>
+          <t>Strong trend; Positive momentum</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Cloud Software</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>270.7300109863281</v>
+        <v>983.1199951171876</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>BUY SMALL</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="I11" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="J11" s="3" t="n">
-        <v>76.47804213242863</v>
+        <v>50</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.0192129762097973</v>
+        <v>44.79774534214121</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.5887063417673052</v>
+        <v>0.0543756800501934</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.6757496704129959</v>
+        <v>0.5629273561792737</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>249.8390797206334</v>
+        <v>-24.97051779036101</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>298.5845860072545</v>
+        <v>803.5899658203126</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>13.92728751046317</v>
+        <v>1252.4150390625</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>2.2</v>
+        <v>89.7650146484375</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.008111999999999999</v>
+        <v>1.92</v>
       </c>
       <c r="S11" s="3" t="n">
+        <v>0.001957</v>
+      </c>
+      <c r="T11" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="T11" s="3" t="n">
+      <c r="U11" s="3" t="n">
         <v>4.39</v>
       </c>
-      <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr"/>
       <c r="W11" s="3" t="inlineStr"/>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
-      <c r="Z11" s="3" t="n">
+      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="AA11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AA11" s="3" t="n">
+      <c r="AB11" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AB11" s="3" t="inlineStr">
+      <c r="AC11" s="3" t="inlineStr">
         <is>
           <t>4 open slot(s)</t>
         </is>
       </c>
-      <c r="AC11" s="3" t="inlineStr"/>
       <c r="AD11" s="3" t="inlineStr"/>
-      <c r="AE11" s="3" t="inlineStr">
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>389.1099853515625</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>BUY SMALL</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>53.7959635185359</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0.030087289573326</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0.7218869927281159</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>2.98002598495759</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>366.6046360560826</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>419.1171177455357</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>15.00356619698661</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>0.005644</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="V12" s="4" t="inlineStr"/>
+      <c r="W12" s="4" t="inlineStr"/>
+      <c r="X12" s="4" t="inlineStr"/>
+      <c r="Y12" s="4" t="inlineStr"/>
+      <c r="Z12" s="4" t="inlineStr"/>
+      <c r="AA12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>4 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AD12" s="4" t="inlineStr"/>
+      <c r="AE12" s="4" t="inlineStr"/>
+      <c r="AF12" s="4" t="inlineStr">
+        <is>
+          <t>Positive momentum; MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="AG12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>DDOG</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Cloud Software</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>270.7300109863281</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>BUY SMALL</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>76.47804213242863</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>-0.0192129762097973</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0.5887063417673052</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0.6757496704129959</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>249.8390797206334</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>298.5845860072545</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>13.92728751046317</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S13" s="4" t="n">
+        <v>0.008111999999999999</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="V13" s="4" t="inlineStr"/>
+      <c r="W13" s="4" t="inlineStr"/>
+      <c r="X13" s="4" t="inlineStr"/>
+      <c r="Y13" s="4" t="inlineStr"/>
+      <c r="Z13" s="4" t="inlineStr"/>
+      <c r="AA13" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>4 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AD13" s="4" t="inlineStr"/>
+      <c r="AE13" s="4" t="inlineStr"/>
+      <c r="AF13" s="4" t="inlineStr">
         <is>
           <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AF11" s="3" t="inlineStr">
+      <c r="AG13" s="4" t="inlineStr">
         <is>
           <t>RSI overbought</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>STTK</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>PUBM</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>AdTech</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>6.289999961853027</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="D14" s="4" t="n">
+        <v>13.6899995803833</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>BUY SMALL</t>
         </is>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="H14" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="H12" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="I12" s="3" t="n">
+      <c r="I14" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J12" s="3" t="n">
-        <v>60.71428368691744</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>0.0046656626141934</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>0.6141227430503577</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>0.0121571690035722</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>5.003857272011893</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>8.219213996614728</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>0.6430713449205671</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>0.13661</v>
-      </c>
-      <c r="S12" s="3" t="n">
+      <c r="K14" s="4" t="n">
+        <v>74.99999453168354</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>-0.0110537672736636</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0.5429485849005998</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0.0301995026588746</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>12.48234258379255</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>15.50148507526943</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>0.6038284982953753</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S14" s="4" t="n">
+        <v>0.145488</v>
+      </c>
+      <c r="T14" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="T12" s="3" t="n">
+      <c r="U14" s="4" t="n">
         <v>4.39</v>
       </c>
-      <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="3" t="inlineStr"/>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr"/>
-      <c r="Y12" s="3" t="inlineStr"/>
-      <c r="Z12" s="3" t="n">
+      <c r="V14" s="4" t="inlineStr"/>
+      <c r="W14" s="4" t="inlineStr"/>
+      <c r="X14" s="4" t="inlineStr"/>
+      <c r="Y14" s="4" t="inlineStr"/>
+      <c r="Z14" s="4" t="inlineStr"/>
+      <c r="AA14" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AA12" s="3" t="n">
+      <c r="AB14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="AB12" s="3" t="inlineStr">
+      <c r="AC14" s="4" t="inlineStr">
         <is>
           <t>4 open slot(s)</t>
         </is>
       </c>
-      <c r="AC12" s="3" t="inlineStr"/>
-      <c r="AD12" s="3" t="inlineStr"/>
-      <c r="AE12" s="3" t="inlineStr">
-        <is>
-          <t>Strong trend; MACD/volume acceleration</t>
-        </is>
-      </c>
-      <c r="AF12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>CRDO</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>236.1799926757812</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>BUY SMALL</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>40.54773982640063</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0.06596166699561611</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>0.4759122849309471</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>-4.82835811389501</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>182.3964189801897</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>316.8553532191685</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>26.89178684779576</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>0.003267</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="T13" s="3" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="U13" s="3" t="inlineStr"/>
-      <c r="V13" s="3" t="inlineStr"/>
-      <c r="W13" s="3" t="inlineStr"/>
-      <c r="X13" s="3" t="inlineStr"/>
-      <c r="Y13" s="3" t="inlineStr"/>
-      <c r="Z13" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB13" s="3" t="inlineStr">
-        <is>
-          <t>4 open slot(s)</t>
-        </is>
-      </c>
-      <c r="AC13" s="3" t="inlineStr"/>
-      <c r="AD13" s="3" t="inlineStr"/>
-      <c r="AE13" s="3" t="inlineStr">
-        <is>
-          <t>Strong trend; Positive momentum</t>
-        </is>
-      </c>
-      <c r="AF13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>ALAB</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>361.7799987792969</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>BUY SMALL</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>44.89807856597774</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0.082723417254077</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>0.5222684036760127</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>-11.70652851646093</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>268.7313014439174</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>501.3530447823661</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>46.52434866768973</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>0.001888</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="U14" s="3" t="inlineStr"/>
-      <c r="V14" s="3" t="inlineStr"/>
-      <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="inlineStr"/>
-      <c r="Y14" s="3" t="inlineStr"/>
-      <c r="Z14" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA14" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB14" s="3" t="inlineStr">
-        <is>
-          <t>4 open slot(s)</t>
-        </is>
-      </c>
-      <c r="AC14" s="3" t="inlineStr"/>
-      <c r="AD14" s="3" t="inlineStr"/>
-      <c r="AE14" s="3" t="inlineStr">
-        <is>
-          <t>Strong trend; Positive momentum</t>
-        </is>
-      </c>
-      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AD14" s="4" t="inlineStr"/>
+      <c r="AE14" s="4" t="inlineStr"/>
+      <c r="AF14" s="4" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum; MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="AG14" s="4" t="inlineStr">
+        <is>
+          <t>RSI overbought</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>STTK</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Internet/Software</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>359.510009765625</v>
+        <v>6.289999961853027</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>40</v>
+        <v>78</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>BUY SMALL</t>
+        </is>
       </c>
       <c r="H15" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="J15" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="I15" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>60.70401435938903</v>
-      </c>
       <c r="K15" s="4" t="n">
-        <v>-0.0040282924977889</v>
+        <v>60.71428368691744</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.5684630349666104</v>
+        <v>0.0046656626141934</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.6975134915938646</v>
+        <v>0.6141227430503577</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>344.4660775320871</v>
+        <v>0.0121571690035722</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>379.5685860770089</v>
+        <v>5.003857272011893</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>10.02928815569196</v>
+        <v>8.219213996614728</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0</v>
+        <v>0.6430713449205671</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="S15" s="4" t="n">
+        <v>0.13661</v>
+      </c>
+      <c r="T15" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="T15" s="4" t="n">
+      <c r="U15" s="4" t="n">
         <v>4.39</v>
       </c>
-      <c r="U15" s="4" t="n">
-        <v>-0.0199286593032251</v>
-      </c>
       <c r="V15" s="4" t="inlineStr"/>
-      <c r="W15" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="Y15" s="4" t="inlineStr">
-        <is>
-          <t>No exit trigger</t>
-        </is>
-      </c>
-      <c r="Z15" s="4" t="n">
+      <c r="W15" s="4" t="inlineStr"/>
+      <c r="X15" s="4" t="inlineStr"/>
+      <c r="Y15" s="4" t="inlineStr"/>
+      <c r="Z15" s="4" t="inlineStr"/>
+      <c r="AA15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AA15" s="4" t="n">
+      <c r="AB15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="AB15" s="4" t="inlineStr">
-        <is>
-          <t>Already held</t>
-        </is>
-      </c>
       <c r="AC15" s="4" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AD15" s="4" t="inlineStr">
-        <is>
-          <t>Do not average down</t>
-        </is>
-      </c>
-      <c r="AE15" s="4" t="inlineStr">
-        <is>
-          <t>Positive momentum; MACD/volume acceleration</t>
-        </is>
-      </c>
+          <t>4 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AD15" s="4" t="inlineStr"/>
+      <c r="AE15" s="4" t="inlineStr"/>
       <c r="AF15" s="4" t="inlineStr">
         <is>
-          <t>Do not average down</t>
-        </is>
-      </c>
+          <t>Strong trend; MACD/volume acceleration</t>
+        </is>
+      </c>
+      <c r="AG15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Internet/E-Commerce</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>247.4900054931641</v>
+        <v>361.7799987792969</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>40</v>
+        <v>75</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>BUY SMALL</t>
+        </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>75</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>66.88540664531003</v>
+        <v>50</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.0071974396379796</v>
+        <v>44.89807856597774</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.6096913242789158</v>
+        <v>0.082723417254077</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.741369739733408</v>
+        <v>0.5222684036760127</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>236.1392958504813</v>
+        <v>-11.70652851646093</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>262.6242850167411</v>
+        <v>268.7313014439174</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>7.567139761788504</v>
+        <v>501.3530447823661</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0</v>
+        <v>46.52434866768973</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="S16" s="4" t="n">
+        <v>0.001888</v>
+      </c>
+      <c r="T16" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="T16" s="4" t="n">
+      <c r="U16" s="4" t="n">
         <v>4.39</v>
       </c>
-      <c r="U16" s="4" t="inlineStr"/>
       <c r="V16" s="4" t="inlineStr"/>
       <c r="W16" s="4" t="inlineStr"/>
       <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="4" t="inlineStr"/>
-      <c r="Z16" s="4" t="n">
+      <c r="Z16" s="4" t="inlineStr"/>
+      <c r="AA16" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AA16" s="4" t="n">
+      <c r="AB16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="AB16" s="4" t="inlineStr">
+      <c r="AC16" s="4" t="inlineStr">
         <is>
           <t>4 open slot(s)</t>
         </is>
       </c>
-      <c r="AC16" s="4" t="inlineStr"/>
       <c r="AD16" s="4" t="inlineStr"/>
-      <c r="AE16" s="4" t="inlineStr">
-        <is>
-          <t>MACD/volume acceleration</t>
-        </is>
-      </c>
-      <c r="AF16" s="4" t="inlineStr"/>
+      <c r="AE16" s="4" t="inlineStr"/>
+      <c r="AF16" s="4" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum</t>
+        </is>
+      </c>
+      <c r="AG16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>CELC</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -2222,2242 +2321,2266 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>111.0500030517578</v>
+        <v>236.1799926757812</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>40</v>
+        <v>75</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>BUY SMALL</t>
+        </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>75</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>68.91793789745947</v>
+        <v>50</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>40.54773982640063</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.339588038518872</v>
+        <v>0.06596166699561611</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.829585113648181</v>
+        <v>0.4759122849309471</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>97.80785914829798</v>
+        <v>-4.82835811389501</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>130.9132189069475</v>
+        <v>182.3964189801897</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.621071951729911</v>
+        <v>316.8553532191685</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0</v>
+        <v>26.89178684779576</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="S17" s="4" t="n">
+        <v>0.003267</v>
+      </c>
+      <c r="T17" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="T17" s="4" t="n">
+      <c r="U17" s="4" t="n">
         <v>4.39</v>
       </c>
-      <c r="U17" s="4" t="inlineStr"/>
       <c r="V17" s="4" t="inlineStr"/>
       <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" s="4" t="inlineStr"/>
       <c r="Y17" s="4" t="inlineStr"/>
-      <c r="Z17" s="4" t="n">
+      <c r="Z17" s="4" t="inlineStr"/>
+      <c r="AA17" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AA17" s="4" t="n">
+      <c r="AB17" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="AB17" s="4" t="inlineStr">
+      <c r="AC17" s="4" t="inlineStr">
         <is>
           <t>4 open slot(s)</t>
         </is>
       </c>
-      <c r="AC17" s="4" t="inlineStr"/>
       <c r="AD17" s="4" t="inlineStr"/>
-      <c r="AE17" s="4" t="inlineStr">
+      <c r="AE17" s="4" t="inlineStr"/>
+      <c r="AF17" s="4" t="inlineStr">
+        <is>
+          <t>Strong trend; Positive momentum</t>
+        </is>
+      </c>
+      <c r="AG17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Internet/E-Commerce</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>247.4900054931641</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>66.88540664531003</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>-0.0071974396379796</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>0.6096913242789158</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>1.741369739733408</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>236.1392958504813</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>262.6242850167411</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>7.567139761788504</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr"/>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>4 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AF17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>SOFI</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Fintech</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="AG18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Biotech</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
-        <v>18.54999923706055</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="D19" s="2" t="n">
+        <v>111.0500030517578</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H19" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="H18" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="I18" s="4" t="n">
+      <c r="I19" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="J19" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="J18" s="4" t="n">
-        <v>61.97715680636227</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>0.0044125718372439</v>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>1.151572395702875</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>0.0323079814383454</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>16.66714205060686</v>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v>21.37428501674108</v>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v>0.9414285932268416</v>
-      </c>
-      <c r="Q18" s="4" t="n">
+      <c r="K19" s="2" t="n">
+        <v>68.91793789745947</v>
+      </c>
+      <c r="L19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R18" s="4" t="n">
+      <c r="M19" s="2" t="n">
+        <v>1.339588038518872</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>1.829585113648181</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>97.80785914829798</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>130.9132189069475</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>6.621071951729911</v>
+      </c>
+      <c r="R19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S18" s="4" t="n">
+      <c r="S19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2" t="n">
         <v>0.35</v>
       </c>
-      <c r="T18" s="4" t="n">
+      <c r="U19" s="2" t="n">
         <v>4.39</v>
       </c>
-      <c r="U18" s="4" t="n">
-        <v>0.008241993405466001</v>
-      </c>
-      <c r="V18" s="4" t="inlineStr"/>
-      <c r="W18" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="X18" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="Y18" s="4" t="inlineStr">
-        <is>
-          <t>No exit trigger</t>
-        </is>
-      </c>
-      <c r="Z18" s="4" t="n">
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr"/>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AA18" s="4" t="n">
+      <c r="AB19" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AB18" s="4" t="inlineStr">
-        <is>
-          <t>Already held</t>
-        </is>
-      </c>
-      <c r="AC18" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="AD18" s="4" t="inlineStr">
-        <is>
-          <t>Held, but not strong enough to add</t>
-        </is>
-      </c>
-      <c r="AE18" s="4" t="inlineStr">
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>4 open slot(s)</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr">
         <is>
           <t>MACD/volume acceleration</t>
         </is>
       </c>
-      <c r="AF18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="AG19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Data Storage</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>878.3099975585938</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>37.83287697052316</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0.0451049293978258</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>0.8607449965404489</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>-15.2356051912122</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>75